--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_CBD45AA8C66EC09B57DFBE4AB87199F6488E5AEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8181AE76-E2C1-4B2F-8266-D42C3C7126ED}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17895" windowHeight="8040"/>
+    <workbookView xWindow="-3690" yWindow="1440" windowWidth="31020" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,8 +18,19 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -27,12 +39,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -58,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -112,9 +124,6 @@
   </si>
   <si>
     <t>MainScene_1_1_4</t>
-  </si>
-  <si>
-    <t>MainScene_1_1_8</t>
   </si>
   <si>
     <t>-</t>
@@ -221,11 +230,37 @@
   <si>
     <t>회복 포션</t>
   </si>
+  <si>
+    <t>displayType</t>
+  </si>
+  <si>
+    <t>StoryBreak</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_8</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene_1_1_8</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_9</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -277,7 +312,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -318,12 +353,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -343,14 +393,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,7 +622,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -574,11 +630,11 @@
     <col min="2" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" customWidth="1"/>
     <col min="5" max="5" width="31.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.42578125" customWidth="1"/>
     <col min="12" max="12" width="16.42578125" customWidth="1"/>
     <col min="13" max="13" width="20.42578125" customWidth="1"/>
@@ -742,15 +798,17 @@
       <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -782,7 +840,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -821,7 +879,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -860,10 +918,10 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -901,7 +959,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -939,7 +997,9 @@
         <v>MainScene_1_1_8</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1013,7 +1073,6 @@
         <v>MainScene_1_1_10</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -28736,7 +28795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -28745,28 +28804,33 @@
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" customWidth="1"/>
     <col min="5" max="5" width="48.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="26" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>26</v>
+      <c r="F1" s="12" t="s">
+        <v>51</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="G1" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -28802,9 +28866,11 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -28841,9 +28907,11 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -28880,9 +28948,11 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -28919,9 +28989,11 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -28957,10 +29029,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>31</v>
+      <c r="E6" s="8" t="s">
+        <v>30</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -28996,10 +29070,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>32</v>
+      <c r="E7" s="8" t="s">
+        <v>31</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -29035,11 +29111,15 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_7</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>33</v>
+      <c r="E8" s="8" t="s">
+        <v>32</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -29075,9 +29155,11 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -29114,10 +29196,14 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -29152,8 +29238,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_10</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -29189,8 +29279,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -29226,8 +29320,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -29263,8 +29361,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -29301,7 +29403,9 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -29338,7 +29442,9 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -29375,7 +29481,9 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -29412,7 +29520,9 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -29449,7 +29559,9 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -29486,7 +29598,9 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -29523,7 +29637,9 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -29560,7 +29676,9 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -56974,7 +57092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -56991,16 +57109,16 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -58016,7 +58134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58029,58 +58147,58 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_CBD45AA8C66EC09B57DFBE4AB87199F6488E5AEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8181AE76-E2C1-4B2F-8266-D42C3C7126ED}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_CBD45AA8C66EC09B57DFBE4AB87199F6488E5AEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14F94D9-9C34-4B0B-BE09-AA43BCA06B2F}"/>
   <bookViews>
-    <workbookView xWindow="-3690" yWindow="1440" windowWidth="31020" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4350" yWindow="1470" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Choice3_Next_Scene</t>
   </si>
   <si>
-    <t>MainScript_1_1_1</t>
-  </si>
-  <si>
     <t>MainScript_1_1_2</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
   </si>
   <si>
     <t>MainScene_1_1_4</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>MainScript_1_1_5</t>
@@ -148,15 +142,6 @@
   </si>
   <si>
     <t>KOR</t>
-  </si>
-  <si>
-    <t>모험가는 긴 여정 끝에 라노스 마을에 도착하였다.</t>
-  </si>
-  <si>
-    <t>낮선 땅이지만 어쩐지 익숙하고 그리운 느낌이 든다</t>
-  </si>
-  <si>
-    <t>이제 무엇을 할까?</t>
   </si>
   <si>
     <t>광장으로 간다</t>
@@ -254,6 +239,22 @@
   </si>
   <si>
     <t>MainScript_1_1_9</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모험가는 긴 여정 끝에 라노스 마을에 도착하였다.\n</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>낮선 땅이지만 어쩐지 익숙하고 그리운 느낌이 든다\n</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 무엇을 할까?\n</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -372,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -407,6 +408,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,7 +715,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -750,7 +754,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -789,27 +793,23 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J4" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -918,10 +918,10 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -28820,16 +28820,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -28866,10 +28866,10 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -28907,10 +28907,10 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -28948,10 +28948,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -28989,10 +28989,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -29030,10 +29030,10 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -29071,10 +29071,10 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -29112,13 +29112,13 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -29155,10 +29155,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -29196,13 +29196,13 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -29239,10 +29239,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -29280,10 +29280,10 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -29321,10 +29321,10 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -29362,10 +29362,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -29404,7 +29404,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -29482,7 +29482,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -29521,7 +29521,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -29560,7 +29560,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -29599,7 +29599,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -29638,7 +29638,7 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -57109,16 +57109,16 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -58147,58 +58147,58 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_CBD45AA8C66EC09B57DFBE4AB87199F6488E5AEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14F94D9-9C34-4B0B-BE09-AA43BCA06B2F}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_CBD45AA8C66EC09B57DFBE4AB87199F6488E5AEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A089946-35CD-4447-B7FD-646E34E17139}"/>
   <bookViews>
-    <workbookView xWindow="-4350" yWindow="1470" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-480" yWindow="945" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -28802,7 +28802,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
     <col min="5" max="5" width="48.42578125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_CBD45AA8C66EC09B57DFBE4AB87199F6488E5AEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A089946-35CD-4447-B7FD-646E34E17139}"/>
   <bookViews>
-    <workbookView xWindow="-480" yWindow="945" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-480" yWindow="945" windowWidth="31020" windowHeight="11085" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,12 +38,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -70,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -145,11 +144,6 @@
   </si>
   <si>
     <t>광장으로 간다</t>
-  </si>
-  <si>
-    <t>모험가는 광장으로 발걸음을 향했다 
-광장에는 아이들이 뛰어놀고 있었으며 굉장히
-활지찬 광장이였다.</t>
   </si>
   <si>
     <t>아이가 말을 걸어왔다.
@@ -257,11 +251,23 @@
     <t>이제 무엇을 할까?\n</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Image003</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -626,7 +632,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -715,7 +721,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -803,10 +809,10 @@
         <v>16</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
@@ -998,7 +1004,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -28795,7 +28801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -28826,10 +28832,10 @@
         <v>23</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -28866,10 +28872,10 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -28907,10 +28913,10 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -28948,10 +28954,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -28992,7 +28998,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -29029,11 +29035,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>25</v>
+      <c r="E6" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -29071,10 +29077,10 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -29112,13 +29118,13 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -29155,10 +29161,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -29196,13 +29202,13 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -29239,10 +29245,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -29280,10 +29286,10 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -29321,10 +29327,10 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -29362,10 +29368,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -29404,7 +29410,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -29443,7 +29449,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -29482,7 +29488,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -29521,7 +29527,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -29560,7 +29566,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -29599,7 +29605,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -29638,7 +29644,7 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -29677,7 +29683,7 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -57087,12 +57093,12 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -57109,16 +57115,16 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -58134,7 +58140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58147,44 +58153,44 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
@@ -58192,13 +58198,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D25C7AE-6DB8-41EF-AB6E-41523D712C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-480" yWindow="945" windowWidth="31020" windowHeight="11085" activeTab="1"/>
+    <workbookView xWindow="8760" yWindow="4875" windowWidth="17310" windowHeight="9795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,12 +39,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -143,25 +144,6 @@
     <t>KOR</t>
   </si>
   <si>
-    <t>광장으로 간다</t>
-  </si>
-  <si>
-    <t>아이가 말을 걸어왔다.
-"형은 어디서 오셨어요?"
-주인공은 고향도 모르고 떠돌아 다닌다고 답했다.
-"새로오신거네요 그러면! 이거 선물이에요"</t>
-  </si>
-  <si>
-    <t>고마워
-회복 포션을 얻었다</t>
-  </si>
-  <si>
-    <t>이제 앞으로 나아가야지</t>
-  </si>
-  <si>
-    <t>여관으로 들어간다.</t>
-  </si>
-  <si>
     <t>Choice_No</t>
   </si>
   <si>
@@ -228,10 +210,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Break</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_1_1_9</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -240,34 +218,76 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>모험가는 긴 여정 끝에 라노스 마을에 도착하였다.\n</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>낮선 땅이지만 어쩐지 익숙하고 그리운 느낌이 든다\n</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 무엇을 할까?\n</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image003</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>TEXT</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Image</t>
+    <t>평온한 마을인 라노스마을
+해가 높이 떠올랐고, 바람은 따뜻했다.
+나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마을 사람들이 특별히 따돌리진 않았다
+하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.
+나는 그게 더 편했다.
+누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그날 아침도 평범했다,
+언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.
+모두가 자신만의 하루를 살고 있던 평범한 날이였다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 나는 이상한 기척을 순간 느꼈다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>"뭐지….?"</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마을 입구 쪽이였다.
+사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 그 잠깐의 고요함은 오래가지 않았다.
+사람들이 비명을 지르며 도망치기 시작했다.
+창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.
+그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>거칠게 짖는 괴수들,
+날이 빠진 무기를 들고도 거침없이 웃는 산적들.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 단순한 약탈이 아니었다.
+말살에 가까웠다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소년은 그 광경을 멍하니 바라보고만 있었다.
+누군가의 비명이 들려왔다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -379,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -400,9 +420,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -417,6 +434,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -632,7 +655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -721,7 +744,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -809,13 +832,13 @@
         <v>16</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -1004,7 +1027,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -28795,47 +28818,47 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.42578125" customWidth="1"/>
+    <col min="5" max="5" width="56.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:26" ht="16.5">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>45</v>
+      <c r="F1" s="11" t="s">
+        <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>46</v>
+      <c r="G1" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -28857,7 +28880,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" ht="16.5" customHeight="1">
+    <row r="2" spans="1:26" ht="60">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -28871,11 +28894,11 @@
         <f t="shared" ref="D2:D22" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>53</v>
+      <c r="E2" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -28898,7 +28921,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1">
+    <row r="3" spans="1:26" ht="90">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -28912,11 +28935,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_2</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>54</v>
+      <c r="E3" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -28939,7 +28962,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1">
+    <row r="4" spans="1:26" ht="75">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -28953,11 +28976,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_3</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>55</v>
+      <c r="E4" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -28980,7 +29003,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" spans="1:26" ht="16.5" customHeight="1">
+    <row r="5" spans="1:26" ht="16.5">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -28994,11 +29017,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_4</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
+      <c r="E5" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -29021,7 +29044,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" spans="1:26" ht="16.5" customHeight="1">
+    <row r="6" spans="1:26" ht="16.5">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -29035,11 +29058,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>56</v>
+      <c r="E6" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -29062,7 +29085,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1">
+    <row r="7" spans="1:26" ht="30">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -29076,11 +29099,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
+      <c r="E7" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -29103,7 +29126,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="16.5" customHeight="1">
+    <row r="8" spans="1:26" ht="45">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -29117,15 +29140,13 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_7</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>26</v>
+      <c r="E8" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -29146,7 +29167,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="16.5" customHeight="1">
+    <row r="9" spans="1:26" ht="90">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -29160,11 +29181,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_8</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>27</v>
+      <c r="E9" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -29187,7 +29208,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1">
+    <row r="10" spans="1:26" ht="30">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -29201,15 +29222,13 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_9</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="13" t="s">
         <v>56</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -29230,7 +29249,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="16.5" customHeight="1">
+    <row r="11" spans="1:26" ht="30">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -29244,11 +29263,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_10</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>28</v>
+      <c r="E11" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -29271,7 +29290,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" ht="16.5" customHeight="1">
+    <row r="12" spans="1:26" ht="30">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -29285,11 +29304,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>28</v>
+      <c r="E12" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -29312,7 +29331,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" ht="16.5" customHeight="1">
+    <row r="13" spans="1:26" ht="16.5">
       <c r="A13" s="7">
         <v>1</v>
       </c>
@@ -29326,11 +29345,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>28</v>
+      <c r="E13" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -29353,7 +29372,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="16.5" customHeight="1">
+    <row r="14" spans="1:26" ht="16.5">
       <c r="A14" s="7">
         <v>1</v>
       </c>
@@ -29367,11 +29386,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -29394,7 +29411,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="16.5" customHeight="1">
+    <row r="15" spans="1:26" ht="16.5">
       <c r="A15" s="7">
         <v>1</v>
       </c>
@@ -29410,7 +29427,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -29433,7 +29450,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" ht="16.5" customHeight="1">
+    <row r="16" spans="1:26" ht="16.5">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -29449,7 +29466,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -29472,7 +29489,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="16.5" customHeight="1">
+    <row r="17" spans="1:26" ht="16.5">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -29488,7 +29505,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -29511,7 +29528,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="16.5" customHeight="1">
+    <row r="18" spans="1:26" ht="16.5">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -29527,7 +29544,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -29550,7 +29567,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="16.5" customHeight="1">
+    <row r="19" spans="1:26" ht="16.5">
       <c r="A19" s="7">
         <v>1</v>
       </c>
@@ -29566,7 +29583,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -29589,7 +29606,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="16.5" customHeight="1">
+    <row r="20" spans="1:26" ht="16.5">
       <c r="A20" s="7">
         <v>1</v>
       </c>
@@ -29605,7 +29622,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -29628,7 +29645,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="16.5" customHeight="1">
+    <row r="21" spans="1:26" ht="16.5">
       <c r="A21" s="7">
         <v>1</v>
       </c>
@@ -29644,7 +29661,7 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -29667,7 +29684,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" ht="16.5" customHeight="1">
+    <row r="22" spans="1:26" ht="16.5">
       <c r="A22" s="7">
         <v>1</v>
       </c>
@@ -29683,7 +29700,7 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -29706,7 +29723,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="16.5" customHeight="1">
+    <row r="23" spans="1:26" ht="16.5">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -29734,7 +29751,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" ht="16.5" customHeight="1">
+    <row r="24" spans="1:26" ht="16.5">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -29762,7 +29779,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" spans="1:26" ht="16.5" customHeight="1">
+    <row r="25" spans="1:26" ht="16.5">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -29790,7 +29807,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="16.5" customHeight="1">
+    <row r="26" spans="1:26" ht="16.5">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -29818,7 +29835,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="16.5" customHeight="1">
+    <row r="27" spans="1:26" ht="16.5">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -29846,7 +29863,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="16.5" customHeight="1">
+    <row r="28" spans="1:26" ht="16.5">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -29874,7 +29891,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="16.5" customHeight="1">
+    <row r="29" spans="1:26" ht="16.5">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -29902,7 +29919,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="16.5" customHeight="1">
+    <row r="30" spans="1:26" ht="16.5">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -29930,7 +29947,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="16.5" customHeight="1">
+    <row r="31" spans="1:26" ht="16.5">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -29958,7 +29975,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="16.5" customHeight="1">
+    <row r="32" spans="1:26" ht="16.5">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -29986,7 +30003,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="16.5" customHeight="1">
+    <row r="33" spans="1:26" ht="16.5">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -30014,7 +30031,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="1:26" ht="16.5" customHeight="1">
+    <row r="34" spans="1:26" ht="16.5">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -30042,7 +30059,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" spans="1:26" ht="16.5" customHeight="1">
+    <row r="35" spans="1:26" ht="16.5">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -30070,7 +30087,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" spans="1:26" ht="16.5" customHeight="1">
+    <row r="36" spans="1:26" ht="16.5">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -30098,7 +30115,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="16.5" customHeight="1">
+    <row r="37" spans="1:26" ht="16.5">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -30126,7 +30143,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" spans="1:26" ht="16.5" customHeight="1">
+    <row r="38" spans="1:26" ht="16.5">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -30154,7 +30171,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" spans="1:26" ht="16.5" customHeight="1">
+    <row r="39" spans="1:26" ht="16.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -30182,7 +30199,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" spans="1:26" ht="16.5" customHeight="1">
+    <row r="40" spans="1:26" ht="16.5">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -30210,7 +30227,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" spans="1:26" ht="16.5" customHeight="1">
+    <row r="41" spans="1:26" ht="16.5">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -30238,7 +30255,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" spans="1:26" ht="16.5" customHeight="1">
+    <row r="42" spans="1:26" ht="16.5">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -30266,7 +30283,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43" spans="1:26" ht="16.5" customHeight="1">
+    <row r="43" spans="1:26" ht="16.5">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -30294,7 +30311,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" spans="1:26" ht="16.5" customHeight="1">
+    <row r="44" spans="1:26" ht="16.5">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -30322,7 +30339,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" spans="1:26" ht="16.5" customHeight="1">
+    <row r="45" spans="1:26" ht="16.5">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -30350,7 +30367,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" ht="16.5" customHeight="1">
+    <row r="46" spans="1:26" ht="16.5">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -30378,7 +30395,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" ht="16.5" customHeight="1">
+    <row r="47" spans="1:26" ht="16.5">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -30406,7 +30423,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" spans="1:26" ht="16.5" customHeight="1">
+    <row r="48" spans="1:26" ht="16.5">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -30434,7 +30451,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" spans="1:26" ht="16.5" customHeight="1">
+    <row r="49" spans="1:26" ht="16.5">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -30462,7 +30479,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" spans="1:26" ht="16.5" customHeight="1">
+    <row r="50" spans="1:26" ht="16.5">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -30490,7 +30507,7 @@
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
     </row>
-    <row r="51" spans="1:26" ht="16.5" customHeight="1">
+    <row r="51" spans="1:26" ht="16.5">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -30518,7 +30535,7 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
     </row>
-    <row r="52" spans="1:26" ht="16.5" customHeight="1">
+    <row r="52" spans="1:26" ht="16.5">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -30546,7 +30563,7 @@
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
     </row>
-    <row r="53" spans="1:26" ht="16.5" customHeight="1">
+    <row r="53" spans="1:26" ht="16.5">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -30574,7 +30591,7 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54" spans="1:26" ht="16.5" customHeight="1">
+    <row r="54" spans="1:26" ht="16.5">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -30602,7 +30619,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" spans="1:26" ht="16.5" customHeight="1">
+    <row r="55" spans="1:26" ht="16.5">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -30630,7 +30647,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" spans="1:26" ht="16.5" customHeight="1">
+    <row r="56" spans="1:26" ht="16.5">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -30658,7 +30675,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="16.5" customHeight="1">
+    <row r="57" spans="1:26" ht="16.5">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -30686,7 +30703,7 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58" spans="1:26" ht="16.5" customHeight="1">
+    <row r="58" spans="1:26" ht="16.5">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -30714,7 +30731,7 @@
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
     </row>
-    <row r="59" spans="1:26" ht="16.5" customHeight="1">
+    <row r="59" spans="1:26" ht="16.5">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -30742,7 +30759,7 @@
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
     </row>
-    <row r="60" spans="1:26" ht="16.5" customHeight="1">
+    <row r="60" spans="1:26" ht="16.5">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -30770,7 +30787,7 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61" spans="1:26" ht="16.5" customHeight="1">
+    <row r="61" spans="1:26" ht="16.5">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -30798,7 +30815,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" spans="1:26" ht="16.5" customHeight="1">
+    <row r="62" spans="1:26" ht="16.5">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -30826,7 +30843,7 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" spans="1:26" ht="16.5" customHeight="1">
+    <row r="63" spans="1:26" ht="16.5">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -30854,7 +30871,7 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64" spans="1:26" ht="16.5" customHeight="1">
+    <row r="64" spans="1:26" ht="16.5">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -30882,7 +30899,7 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65" spans="1:26" ht="16.5" customHeight="1">
+    <row r="65" spans="1:26" ht="16.5">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -30910,7 +30927,7 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66" spans="1:26" ht="16.5" customHeight="1">
+    <row r="66" spans="1:26" ht="16.5">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -30938,7 +30955,7 @@
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
     </row>
-    <row r="67" spans="1:26" ht="16.5" customHeight="1">
+    <row r="67" spans="1:26" ht="16.5">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -30966,7 +30983,7 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68" spans="1:26" ht="16.5" customHeight="1">
+    <row r="68" spans="1:26" ht="16.5">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -30994,7 +31011,7 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69" spans="1:26" ht="16.5" customHeight="1">
+    <row r="69" spans="1:26" ht="16.5">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -31022,7 +31039,7 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" spans="1:26" ht="16.5" customHeight="1">
+    <row r="70" spans="1:26" ht="16.5">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -31050,7 +31067,7 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71" spans="1:26" ht="16.5" customHeight="1">
+    <row r="71" spans="1:26" ht="16.5">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -31078,7 +31095,7 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
     </row>
-    <row r="72" spans="1:26" ht="16.5" customHeight="1">
+    <row r="72" spans="1:26" ht="16.5">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -31106,7 +31123,7 @@
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
     </row>
-    <row r="73" spans="1:26" ht="16.5" customHeight="1">
+    <row r="73" spans="1:26" ht="16.5">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -31134,7 +31151,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" spans="1:26" ht="16.5" customHeight="1">
+    <row r="74" spans="1:26" ht="16.5">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -31162,7 +31179,7 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75" spans="1:26" ht="16.5" customHeight="1">
+    <row r="75" spans="1:26" ht="16.5">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -31190,7 +31207,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" spans="1:26" ht="16.5" customHeight="1">
+    <row r="76" spans="1:26" ht="16.5">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -31218,7 +31235,7 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
     </row>
-    <row r="77" spans="1:26" ht="16.5" customHeight="1">
+    <row r="77" spans="1:26" ht="16.5">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -31246,7 +31263,7 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
     </row>
-    <row r="78" spans="1:26" ht="16.5" customHeight="1">
+    <row r="78" spans="1:26" ht="16.5">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -31274,7 +31291,7 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
     </row>
-    <row r="79" spans="1:26" ht="16.5" customHeight="1">
+    <row r="79" spans="1:26" ht="16.5">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -31302,7 +31319,7 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
     </row>
-    <row r="80" spans="1:26" ht="16.5" customHeight="1">
+    <row r="80" spans="1:26" ht="16.5">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -31330,7 +31347,7 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
     </row>
-    <row r="81" spans="1:26" ht="16.5" customHeight="1">
+    <row r="81" spans="1:26" ht="16.5">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -31358,7 +31375,7 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
     </row>
-    <row r="82" spans="1:26" ht="16.5" customHeight="1">
+    <row r="82" spans="1:26" ht="16.5">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -31386,7 +31403,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83" spans="1:26" ht="16.5" customHeight="1">
+    <row r="83" spans="1:26" ht="16.5">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -31414,7 +31431,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84" spans="1:26" ht="16.5" customHeight="1">
+    <row r="84" spans="1:26" ht="16.5">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -31442,7 +31459,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85" spans="1:26" ht="16.5" customHeight="1">
+    <row r="85" spans="1:26" ht="16.5">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -31470,7 +31487,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86" spans="1:26" ht="16.5" customHeight="1">
+    <row r="86" spans="1:26" ht="16.5">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -31498,7 +31515,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87" spans="1:26" ht="16.5" customHeight="1">
+    <row r="87" spans="1:26" ht="16.5">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -31526,7 +31543,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88" spans="1:26" ht="16.5" customHeight="1">
+    <row r="88" spans="1:26" ht="16.5">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -31554,7 +31571,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89" spans="1:26" ht="16.5" customHeight="1">
+    <row r="89" spans="1:26" ht="16.5">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -31582,7 +31599,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90" spans="1:26" ht="16.5" customHeight="1">
+    <row r="90" spans="1:26" ht="16.5">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -31610,7 +31627,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91" spans="1:26" ht="16.5" customHeight="1">
+    <row r="91" spans="1:26" ht="16.5">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -31638,7 +31655,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92" spans="1:26" ht="16.5" customHeight="1">
+    <row r="92" spans="1:26" ht="16.5">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -31666,7 +31683,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93" spans="1:26" ht="16.5" customHeight="1">
+    <row r="93" spans="1:26" ht="16.5">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -31694,7 +31711,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94" spans="1:26" ht="16.5" customHeight="1">
+    <row r="94" spans="1:26" ht="16.5">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -31722,7 +31739,7 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
     </row>
-    <row r="95" spans="1:26" ht="16.5" customHeight="1">
+    <row r="95" spans="1:26" ht="16.5">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -31750,7 +31767,7 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
     </row>
-    <row r="96" spans="1:26" ht="16.5" customHeight="1">
+    <row r="96" spans="1:26" ht="16.5">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -31778,7 +31795,7 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
     </row>
-    <row r="97" spans="1:26" ht="16.5" customHeight="1">
+    <row r="97" spans="1:26" ht="16.5">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -31806,7 +31823,7 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
     </row>
-    <row r="98" spans="1:26" ht="16.5" customHeight="1">
+    <row r="98" spans="1:26" ht="16.5">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -31834,7 +31851,7 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
     </row>
-    <row r="99" spans="1:26" ht="16.5" customHeight="1">
+    <row r="99" spans="1:26" ht="16.5">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -31862,7 +31879,7 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
     </row>
-    <row r="100" spans="1:26" ht="16.5" customHeight="1">
+    <row r="100" spans="1:26" ht="16.5">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -31890,7 +31907,7 @@
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
     </row>
-    <row r="101" spans="1:26" ht="16.5" customHeight="1">
+    <row r="101" spans="1:26" ht="16.5">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -31918,7 +31935,7 @@
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
     </row>
-    <row r="102" spans="1:26" ht="16.5" customHeight="1">
+    <row r="102" spans="1:26" ht="16.5">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -31946,7 +31963,7 @@
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
     </row>
-    <row r="103" spans="1:26" ht="16.5" customHeight="1">
+    <row r="103" spans="1:26" ht="16.5">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -31974,7 +31991,7 @@
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
     </row>
-    <row r="104" spans="1:26" ht="16.5" customHeight="1">
+    <row r="104" spans="1:26" ht="16.5">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -32002,7 +32019,7 @@
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
     </row>
-    <row r="105" spans="1:26" ht="16.5" customHeight="1">
+    <row r="105" spans="1:26" ht="16.5">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -32030,7 +32047,7 @@
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
     </row>
-    <row r="106" spans="1:26" ht="16.5" customHeight="1">
+    <row r="106" spans="1:26" ht="16.5">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -32058,7 +32075,7 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
     </row>
-    <row r="107" spans="1:26" ht="16.5" customHeight="1">
+    <row r="107" spans="1:26" ht="16.5">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -32086,7 +32103,7 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
     </row>
-    <row r="108" spans="1:26" ht="16.5" customHeight="1">
+    <row r="108" spans="1:26" ht="16.5">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -32114,7 +32131,7 @@
       <c r="Y108" s="5"/>
       <c r="Z108" s="5"/>
     </row>
-    <row r="109" spans="1:26" ht="16.5" customHeight="1">
+    <row r="109" spans="1:26" ht="16.5">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -32142,7 +32159,7 @@
       <c r="Y109" s="5"/>
       <c r="Z109" s="5"/>
     </row>
-    <row r="110" spans="1:26" ht="16.5" customHeight="1">
+    <row r="110" spans="1:26" ht="16.5">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -32170,7 +32187,7 @@
       <c r="Y110" s="5"/>
       <c r="Z110" s="5"/>
     </row>
-    <row r="111" spans="1:26" ht="16.5" customHeight="1">
+    <row r="111" spans="1:26" ht="16.5">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -32198,7 +32215,7 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
     </row>
-    <row r="112" spans="1:26" ht="16.5" customHeight="1">
+    <row r="112" spans="1:26" ht="16.5">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -32226,7 +32243,7 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
     </row>
-    <row r="113" spans="1:26" ht="16.5" customHeight="1">
+    <row r="113" spans="1:26" ht="16.5">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -32254,7 +32271,7 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
     </row>
-    <row r="114" spans="1:26" ht="16.5" customHeight="1">
+    <row r="114" spans="1:26" ht="16.5">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -32282,7 +32299,7 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
     </row>
-    <row r="115" spans="1:26" ht="16.5" customHeight="1">
+    <row r="115" spans="1:26" ht="16.5">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -32310,7 +32327,7 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
     </row>
-    <row r="116" spans="1:26" ht="16.5" customHeight="1">
+    <row r="116" spans="1:26" ht="16.5">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -32338,7 +32355,7 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117" spans="1:26" ht="16.5" customHeight="1">
+    <row r="117" spans="1:26" ht="16.5">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -32366,7 +32383,7 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118" spans="1:26" ht="16.5" customHeight="1">
+    <row r="118" spans="1:26" ht="16.5">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -32394,7 +32411,7 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119" spans="1:26" ht="16.5" customHeight="1">
+    <row r="119" spans="1:26" ht="16.5">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -32422,7 +32439,7 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120" spans="1:26" ht="16.5" customHeight="1">
+    <row r="120" spans="1:26" ht="16.5">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -32450,7 +32467,7 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
     </row>
-    <row r="121" spans="1:26" ht="16.5" customHeight="1">
+    <row r="121" spans="1:26" ht="16.5">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -32478,7 +32495,7 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
     </row>
-    <row r="122" spans="1:26" ht="16.5" customHeight="1">
+    <row r="122" spans="1:26" ht="16.5">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -32506,7 +32523,7 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
     </row>
-    <row r="123" spans="1:26" ht="16.5" customHeight="1">
+    <row r="123" spans="1:26" ht="16.5">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -32534,7 +32551,7 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
-    <row r="124" spans="1:26" ht="16.5" customHeight="1">
+    <row r="124" spans="1:26" ht="16.5">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -32562,7 +32579,7 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
-    <row r="125" spans="1:26" ht="16.5" customHeight="1">
+    <row r="125" spans="1:26" ht="16.5">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -32590,7 +32607,7 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
     </row>
-    <row r="126" spans="1:26" ht="16.5" customHeight="1">
+    <row r="126" spans="1:26" ht="16.5">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -32618,7 +32635,7 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
     </row>
-    <row r="127" spans="1:26" ht="16.5" customHeight="1">
+    <row r="127" spans="1:26" ht="16.5">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -32646,7 +32663,7 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128" spans="1:26" ht="16.5" customHeight="1">
+    <row r="128" spans="1:26" ht="16.5">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -32674,7 +32691,7 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129" spans="1:26" ht="16.5" customHeight="1">
+    <row r="129" spans="1:26" ht="16.5">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -32702,7 +32719,7 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130" spans="1:26" ht="16.5" customHeight="1">
+    <row r="130" spans="1:26" ht="16.5">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -32730,7 +32747,7 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131" spans="1:26" ht="16.5" customHeight="1">
+    <row r="131" spans="1:26" ht="16.5">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -32758,7 +32775,7 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132" spans="1:26" ht="16.5" customHeight="1">
+    <row r="132" spans="1:26" ht="16.5">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -32786,7 +32803,7 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133" spans="1:26" ht="16.5" customHeight="1">
+    <row r="133" spans="1:26" ht="16.5">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -32814,7 +32831,7 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134" spans="1:26" ht="16.5" customHeight="1">
+    <row r="134" spans="1:26" ht="16.5">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -32842,7 +32859,7 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135" spans="1:26" ht="16.5" customHeight="1">
+    <row r="135" spans="1:26" ht="16.5">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -32870,7 +32887,7 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136" spans="1:26" ht="16.5" customHeight="1">
+    <row r="136" spans="1:26" ht="16.5">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -32898,7 +32915,7 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137" spans="1:26" ht="16.5" customHeight="1">
+    <row r="137" spans="1:26" ht="16.5">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -32926,7 +32943,7 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138" spans="1:26" ht="16.5" customHeight="1">
+    <row r="138" spans="1:26" ht="16.5">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -32954,7 +32971,7 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139" spans="1:26" ht="16.5" customHeight="1">
+    <row r="139" spans="1:26" ht="16.5">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -32982,7 +32999,7 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140" spans="1:26" ht="16.5" customHeight="1">
+    <row r="140" spans="1:26" ht="16.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -33010,7 +33027,7 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141" spans="1:26" ht="16.5" customHeight="1">
+    <row r="141" spans="1:26" ht="16.5">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -33038,7 +33055,7 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142" spans="1:26" ht="16.5" customHeight="1">
+    <row r="142" spans="1:26" ht="16.5">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -33066,7 +33083,7 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143" spans="1:26" ht="16.5" customHeight="1">
+    <row r="143" spans="1:26" ht="16.5">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -33094,7 +33111,7 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144" spans="1:26" ht="16.5" customHeight="1">
+    <row r="144" spans="1:26" ht="16.5">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -33122,7 +33139,7 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145" spans="1:26" ht="16.5" customHeight="1">
+    <row r="145" spans="1:26" ht="16.5">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -33150,7 +33167,7 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146" spans="1:26" ht="16.5" customHeight="1">
+    <row r="146" spans="1:26" ht="16.5">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -33178,7 +33195,7 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
     </row>
-    <row r="147" spans="1:26" ht="16.5" customHeight="1">
+    <row r="147" spans="1:26" ht="16.5">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -33206,7 +33223,7 @@
       <c r="Y147" s="5"/>
       <c r="Z147" s="5"/>
     </row>
-    <row r="148" spans="1:26" ht="16.5" customHeight="1">
+    <row r="148" spans="1:26" ht="16.5">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -33234,7 +33251,7 @@
       <c r="Y148" s="5"/>
       <c r="Z148" s="5"/>
     </row>
-    <row r="149" spans="1:26" ht="16.5" customHeight="1">
+    <row r="149" spans="1:26" ht="16.5">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -33262,7 +33279,7 @@
       <c r="Y149" s="5"/>
       <c r="Z149" s="5"/>
     </row>
-    <row r="150" spans="1:26" ht="16.5" customHeight="1">
+    <row r="150" spans="1:26" ht="16.5">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -33290,7 +33307,7 @@
       <c r="Y150" s="5"/>
       <c r="Z150" s="5"/>
     </row>
-    <row r="151" spans="1:26" ht="16.5" customHeight="1">
+    <row r="151" spans="1:26" ht="16.5">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -33318,7 +33335,7 @@
       <c r="Y151" s="5"/>
       <c r="Z151" s="5"/>
     </row>
-    <row r="152" spans="1:26" ht="16.5" customHeight="1">
+    <row r="152" spans="1:26" ht="16.5">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -33346,7 +33363,7 @@
       <c r="Y152" s="5"/>
       <c r="Z152" s="5"/>
     </row>
-    <row r="153" spans="1:26" ht="16.5" customHeight="1">
+    <row r="153" spans="1:26" ht="16.5">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -33374,7 +33391,7 @@
       <c r="Y153" s="5"/>
       <c r="Z153" s="5"/>
     </row>
-    <row r="154" spans="1:26" ht="16.5" customHeight="1">
+    <row r="154" spans="1:26" ht="16.5">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -33402,7 +33419,7 @@
       <c r="Y154" s="5"/>
       <c r="Z154" s="5"/>
     </row>
-    <row r="155" spans="1:26" ht="16.5" customHeight="1">
+    <row r="155" spans="1:26" ht="16.5">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -33430,7 +33447,7 @@
       <c r="Y155" s="5"/>
       <c r="Z155" s="5"/>
     </row>
-    <row r="156" spans="1:26" ht="16.5" customHeight="1">
+    <row r="156" spans="1:26" ht="16.5">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -33458,7 +33475,7 @@
       <c r="Y156" s="5"/>
       <c r="Z156" s="5"/>
     </row>
-    <row r="157" spans="1:26" ht="16.5" customHeight="1">
+    <row r="157" spans="1:26" ht="16.5">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -33486,7 +33503,7 @@
       <c r="Y157" s="5"/>
       <c r="Z157" s="5"/>
     </row>
-    <row r="158" spans="1:26" ht="16.5" customHeight="1">
+    <row r="158" spans="1:26" ht="16.5">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -33514,7 +33531,7 @@
       <c r="Y158" s="5"/>
       <c r="Z158" s="5"/>
     </row>
-    <row r="159" spans="1:26" ht="16.5" customHeight="1">
+    <row r="159" spans="1:26" ht="16.5">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -33542,7 +33559,7 @@
       <c r="Y159" s="5"/>
       <c r="Z159" s="5"/>
     </row>
-    <row r="160" spans="1:26" ht="16.5" customHeight="1">
+    <row r="160" spans="1:26" ht="16.5">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -33570,7 +33587,7 @@
       <c r="Y160" s="5"/>
       <c r="Z160" s="5"/>
     </row>
-    <row r="161" spans="1:26" ht="16.5" customHeight="1">
+    <row r="161" spans="1:26" ht="16.5">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -33598,7 +33615,7 @@
       <c r="Y161" s="5"/>
       <c r="Z161" s="5"/>
     </row>
-    <row r="162" spans="1:26" ht="16.5" customHeight="1">
+    <row r="162" spans="1:26" ht="16.5">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -33626,7 +33643,7 @@
       <c r="Y162" s="5"/>
       <c r="Z162" s="5"/>
     </row>
-    <row r="163" spans="1:26" ht="16.5" customHeight="1">
+    <row r="163" spans="1:26" ht="16.5">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -33654,7 +33671,7 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
     </row>
-    <row r="164" spans="1:26" ht="16.5" customHeight="1">
+    <row r="164" spans="1:26" ht="16.5">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -33682,7 +33699,7 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165" spans="1:26" ht="16.5" customHeight="1">
+    <row r="165" spans="1:26" ht="16.5">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -33710,7 +33727,7 @@
       <c r="Y165" s="5"/>
       <c r="Z165" s="5"/>
     </row>
-    <row r="166" spans="1:26" ht="16.5" customHeight="1">
+    <row r="166" spans="1:26" ht="16.5">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -33738,7 +33755,7 @@
       <c r="Y166" s="5"/>
       <c r="Z166" s="5"/>
     </row>
-    <row r="167" spans="1:26" ht="16.5" customHeight="1">
+    <row r="167" spans="1:26" ht="16.5">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -33766,7 +33783,7 @@
       <c r="Y167" s="5"/>
       <c r="Z167" s="5"/>
     </row>
-    <row r="168" spans="1:26" ht="16.5" customHeight="1">
+    <row r="168" spans="1:26" ht="16.5">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -33794,7 +33811,7 @@
       <c r="Y168" s="5"/>
       <c r="Z168" s="5"/>
     </row>
-    <row r="169" spans="1:26" ht="16.5" customHeight="1">
+    <row r="169" spans="1:26" ht="16.5">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -33822,7 +33839,7 @@
       <c r="Y169" s="5"/>
       <c r="Z169" s="5"/>
     </row>
-    <row r="170" spans="1:26" ht="16.5" customHeight="1">
+    <row r="170" spans="1:26" ht="16.5">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -33850,7 +33867,7 @@
       <c r="Y170" s="5"/>
       <c r="Z170" s="5"/>
     </row>
-    <row r="171" spans="1:26" ht="16.5" customHeight="1">
+    <row r="171" spans="1:26" ht="16.5">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -33878,7 +33895,7 @@
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
     </row>
-    <row r="172" spans="1:26" ht="16.5" customHeight="1">
+    <row r="172" spans="1:26" ht="16.5">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -33906,7 +33923,7 @@
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
     </row>
-    <row r="173" spans="1:26" ht="16.5" customHeight="1">
+    <row r="173" spans="1:26" ht="16.5">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -33934,7 +33951,7 @@
       <c r="Y173" s="5"/>
       <c r="Z173" s="5"/>
     </row>
-    <row r="174" spans="1:26" ht="16.5" customHeight="1">
+    <row r="174" spans="1:26" ht="16.5">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -33962,7 +33979,7 @@
       <c r="Y174" s="5"/>
       <c r="Z174" s="5"/>
     </row>
-    <row r="175" spans="1:26" ht="16.5" customHeight="1">
+    <row r="175" spans="1:26" ht="16.5">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -33990,7 +34007,7 @@
       <c r="Y175" s="5"/>
       <c r="Z175" s="5"/>
     </row>
-    <row r="176" spans="1:26" ht="16.5" customHeight="1">
+    <row r="176" spans="1:26" ht="16.5">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -34018,7 +34035,7 @@
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
     </row>
-    <row r="177" spans="1:26" ht="16.5" customHeight="1">
+    <row r="177" spans="1:26" ht="16.5">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -34046,7 +34063,7 @@
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
     </row>
-    <row r="178" spans="1:26" ht="16.5" customHeight="1">
+    <row r="178" spans="1:26" ht="16.5">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -34074,7 +34091,7 @@
       <c r="Y178" s="5"/>
       <c r="Z178" s="5"/>
     </row>
-    <row r="179" spans="1:26" ht="16.5" customHeight="1">
+    <row r="179" spans="1:26" ht="16.5">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -34102,7 +34119,7 @@
       <c r="Y179" s="5"/>
       <c r="Z179" s="5"/>
     </row>
-    <row r="180" spans="1:26" ht="16.5" customHeight="1">
+    <row r="180" spans="1:26" ht="16.5">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -34130,7 +34147,7 @@
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
     </row>
-    <row r="181" spans="1:26" ht="16.5" customHeight="1">
+    <row r="181" spans="1:26" ht="16.5">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -34158,7 +34175,7 @@
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
     </row>
-    <row r="182" spans="1:26" ht="16.5" customHeight="1">
+    <row r="182" spans="1:26" ht="16.5">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -34186,7 +34203,7 @@
       <c r="Y182" s="5"/>
       <c r="Z182" s="5"/>
     </row>
-    <row r="183" spans="1:26" ht="16.5" customHeight="1">
+    <row r="183" spans="1:26" ht="16.5">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -34214,7 +34231,7 @@
       <c r="Y183" s="5"/>
       <c r="Z183" s="5"/>
     </row>
-    <row r="184" spans="1:26" ht="16.5" customHeight="1">
+    <row r="184" spans="1:26" ht="16.5">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -34242,7 +34259,7 @@
       <c r="Y184" s="5"/>
       <c r="Z184" s="5"/>
     </row>
-    <row r="185" spans="1:26" ht="16.5" customHeight="1">
+    <row r="185" spans="1:26" ht="16.5">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -34270,7 +34287,7 @@
       <c r="Y185" s="5"/>
       <c r="Z185" s="5"/>
     </row>
-    <row r="186" spans="1:26" ht="16.5" customHeight="1">
+    <row r="186" spans="1:26" ht="16.5">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -34298,7 +34315,7 @@
       <c r="Y186" s="5"/>
       <c r="Z186" s="5"/>
     </row>
-    <row r="187" spans="1:26" ht="16.5" customHeight="1">
+    <row r="187" spans="1:26" ht="16.5">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -34326,7 +34343,7 @@
       <c r="Y187" s="5"/>
       <c r="Z187" s="5"/>
     </row>
-    <row r="188" spans="1:26" ht="16.5" customHeight="1">
+    <row r="188" spans="1:26" ht="16.5">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -34354,7 +34371,7 @@
       <c r="Y188" s="5"/>
       <c r="Z188" s="5"/>
     </row>
-    <row r="189" spans="1:26" ht="16.5" customHeight="1">
+    <row r="189" spans="1:26" ht="16.5">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -34382,7 +34399,7 @@
       <c r="Y189" s="5"/>
       <c r="Z189" s="5"/>
     </row>
-    <row r="190" spans="1:26" ht="16.5" customHeight="1">
+    <row r="190" spans="1:26" ht="16.5">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -34410,7 +34427,7 @@
       <c r="Y190" s="5"/>
       <c r="Z190" s="5"/>
     </row>
-    <row r="191" spans="1:26" ht="16.5" customHeight="1">
+    <row r="191" spans="1:26" ht="16.5">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -34438,7 +34455,7 @@
       <c r="Y191" s="5"/>
       <c r="Z191" s="5"/>
     </row>
-    <row r="192" spans="1:26" ht="16.5" customHeight="1">
+    <row r="192" spans="1:26" ht="16.5">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -34466,7 +34483,7 @@
       <c r="Y192" s="5"/>
       <c r="Z192" s="5"/>
     </row>
-    <row r="193" spans="1:26" ht="16.5" customHeight="1">
+    <row r="193" spans="1:26" ht="16.5">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -34494,7 +34511,7 @@
       <c r="Y193" s="5"/>
       <c r="Z193" s="5"/>
     </row>
-    <row r="194" spans="1:26" ht="16.5" customHeight="1">
+    <row r="194" spans="1:26" ht="16.5">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -34522,7 +34539,7 @@
       <c r="Y194" s="5"/>
       <c r="Z194" s="5"/>
     </row>
-    <row r="195" spans="1:26" ht="16.5" customHeight="1">
+    <row r="195" spans="1:26" ht="16.5">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -34550,7 +34567,7 @@
       <c r="Y195" s="5"/>
       <c r="Z195" s="5"/>
     </row>
-    <row r="196" spans="1:26" ht="16.5" customHeight="1">
+    <row r="196" spans="1:26" ht="16.5">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -34578,7 +34595,7 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
     </row>
-    <row r="197" spans="1:26" ht="16.5" customHeight="1">
+    <row r="197" spans="1:26" ht="16.5">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -34606,7 +34623,7 @@
       <c r="Y197" s="5"/>
       <c r="Z197" s="5"/>
     </row>
-    <row r="198" spans="1:26" ht="16.5" customHeight="1">
+    <row r="198" spans="1:26" ht="16.5">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -34634,7 +34651,7 @@
       <c r="Y198" s="5"/>
       <c r="Z198" s="5"/>
     </row>
-    <row r="199" spans="1:26" ht="16.5" customHeight="1">
+    <row r="199" spans="1:26" ht="16.5">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -34662,7 +34679,7 @@
       <c r="Y199" s="5"/>
       <c r="Z199" s="5"/>
     </row>
-    <row r="200" spans="1:26" ht="16.5" customHeight="1">
+    <row r="200" spans="1:26" ht="16.5">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -34690,7 +34707,7 @@
       <c r="Y200" s="5"/>
       <c r="Z200" s="5"/>
     </row>
-    <row r="201" spans="1:26" ht="16.5" customHeight="1">
+    <row r="201" spans="1:26" ht="16.5">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -34718,7 +34735,7 @@
       <c r="Y201" s="5"/>
       <c r="Z201" s="5"/>
     </row>
-    <row r="202" spans="1:26" ht="16.5" customHeight="1">
+    <row r="202" spans="1:26" ht="16.5">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -34746,7 +34763,7 @@
       <c r="Y202" s="5"/>
       <c r="Z202" s="5"/>
     </row>
-    <row r="203" spans="1:26" ht="16.5" customHeight="1">
+    <row r="203" spans="1:26" ht="16.5">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -34774,7 +34791,7 @@
       <c r="Y203" s="5"/>
       <c r="Z203" s="5"/>
     </row>
-    <row r="204" spans="1:26" ht="16.5" customHeight="1">
+    <row r="204" spans="1:26" ht="16.5">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -34802,7 +34819,7 @@
       <c r="Y204" s="5"/>
       <c r="Z204" s="5"/>
     </row>
-    <row r="205" spans="1:26" ht="16.5" customHeight="1">
+    <row r="205" spans="1:26" ht="16.5">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -34830,7 +34847,7 @@
       <c r="Y205" s="5"/>
       <c r="Z205" s="5"/>
     </row>
-    <row r="206" spans="1:26" ht="16.5" customHeight="1">
+    <row r="206" spans="1:26" ht="16.5">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -34858,7 +34875,7 @@
       <c r="Y206" s="5"/>
       <c r="Z206" s="5"/>
     </row>
-    <row r="207" spans="1:26" ht="16.5" customHeight="1">
+    <row r="207" spans="1:26" ht="16.5">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -34886,7 +34903,7 @@
       <c r="Y207" s="5"/>
       <c r="Z207" s="5"/>
     </row>
-    <row r="208" spans="1:26" ht="16.5" customHeight="1">
+    <row r="208" spans="1:26" ht="16.5">
       <c r="A208" s="7"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -34914,7 +34931,7 @@
       <c r="Y208" s="5"/>
       <c r="Z208" s="5"/>
     </row>
-    <row r="209" spans="1:26" ht="16.5" customHeight="1">
+    <row r="209" spans="1:26" ht="16.5">
       <c r="A209" s="7"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
@@ -34942,7 +34959,7 @@
       <c r="Y209" s="5"/>
       <c r="Z209" s="5"/>
     </row>
-    <row r="210" spans="1:26" ht="16.5" customHeight="1">
+    <row r="210" spans="1:26" ht="16.5">
       <c r="A210" s="7"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
@@ -34970,7 +34987,7 @@
       <c r="Y210" s="5"/>
       <c r="Z210" s="5"/>
     </row>
-    <row r="211" spans="1:26" ht="16.5" customHeight="1">
+    <row r="211" spans="1:26" ht="16.5">
       <c r="A211" s="7"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
@@ -34998,7 +35015,7 @@
       <c r="Y211" s="5"/>
       <c r="Z211" s="5"/>
     </row>
-    <row r="212" spans="1:26" ht="16.5" customHeight="1">
+    <row r="212" spans="1:26" ht="16.5">
       <c r="A212" s="7"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
@@ -35026,7 +35043,7 @@
       <c r="Y212" s="5"/>
       <c r="Z212" s="5"/>
     </row>
-    <row r="213" spans="1:26" ht="16.5" customHeight="1">
+    <row r="213" spans="1:26" ht="16.5">
       <c r="A213" s="7"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
@@ -35054,7 +35071,7 @@
       <c r="Y213" s="5"/>
       <c r="Z213" s="5"/>
     </row>
-    <row r="214" spans="1:26" ht="16.5" customHeight="1">
+    <row r="214" spans="1:26" ht="16.5">
       <c r="A214" s="7"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
@@ -35082,7 +35099,7 @@
       <c r="Y214" s="5"/>
       <c r="Z214" s="5"/>
     </row>
-    <row r="215" spans="1:26" ht="16.5" customHeight="1">
+    <row r="215" spans="1:26" ht="16.5">
       <c r="A215" s="7"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
@@ -35110,7 +35127,7 @@
       <c r="Y215" s="5"/>
       <c r="Z215" s="5"/>
     </row>
-    <row r="216" spans="1:26" ht="16.5" customHeight="1">
+    <row r="216" spans="1:26" ht="16.5">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
@@ -35138,7 +35155,7 @@
       <c r="Y216" s="5"/>
       <c r="Z216" s="5"/>
     </row>
-    <row r="217" spans="1:26" ht="16.5" customHeight="1">
+    <row r="217" spans="1:26" ht="16.5">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -35166,7 +35183,7 @@
       <c r="Y217" s="5"/>
       <c r="Z217" s="5"/>
     </row>
-    <row r="218" spans="1:26" ht="16.5" customHeight="1">
+    <row r="218" spans="1:26" ht="16.5">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
@@ -35194,7 +35211,7 @@
       <c r="Y218" s="5"/>
       <c r="Z218" s="5"/>
     </row>
-    <row r="219" spans="1:26" ht="16.5" customHeight="1">
+    <row r="219" spans="1:26" ht="16.5">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
@@ -35222,7 +35239,7 @@
       <c r="Y219" s="5"/>
       <c r="Z219" s="5"/>
     </row>
-    <row r="220" spans="1:26" ht="16.5" customHeight="1">
+    <row r="220" spans="1:26" ht="16.5">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -35250,7 +35267,7 @@
       <c r="Y220" s="5"/>
       <c r="Z220" s="5"/>
     </row>
-    <row r="221" spans="1:26" ht="16.5" customHeight="1">
+    <row r="221" spans="1:26" ht="16.5">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -35278,7 +35295,7 @@
       <c r="Y221" s="5"/>
       <c r="Z221" s="5"/>
     </row>
-    <row r="222" spans="1:26" ht="16.5" customHeight="1">
+    <row r="222" spans="1:26" ht="16.5">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -35306,7 +35323,7 @@
       <c r="Y222" s="5"/>
       <c r="Z222" s="5"/>
     </row>
-    <row r="223" spans="1:26" ht="16.5" customHeight="1">
+    <row r="223" spans="1:26" ht="16.5">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -35334,7 +35351,7 @@
       <c r="Y223" s="5"/>
       <c r="Z223" s="5"/>
     </row>
-    <row r="224" spans="1:26" ht="16.5" customHeight="1">
+    <row r="224" spans="1:26" ht="16.5">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -35362,7 +35379,7 @@
       <c r="Y224" s="5"/>
       <c r="Z224" s="5"/>
     </row>
-    <row r="225" spans="1:26" ht="16.5" customHeight="1">
+    <row r="225" spans="1:26" ht="16.5">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -35390,7 +35407,7 @@
       <c r="Y225" s="5"/>
       <c r="Z225" s="5"/>
     </row>
-    <row r="226" spans="1:26" ht="16.5" customHeight="1">
+    <row r="226" spans="1:26" ht="16.5">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -35418,7 +35435,7 @@
       <c r="Y226" s="5"/>
       <c r="Z226" s="5"/>
     </row>
-    <row r="227" spans="1:26" ht="16.5" customHeight="1">
+    <row r="227" spans="1:26" ht="16.5">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -35446,7 +35463,7 @@
       <c r="Y227" s="5"/>
       <c r="Z227" s="5"/>
     </row>
-    <row r="228" spans="1:26" ht="16.5" customHeight="1">
+    <row r="228" spans="1:26" ht="16.5">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -35474,7 +35491,7 @@
       <c r="Y228" s="5"/>
       <c r="Z228" s="5"/>
     </row>
-    <row r="229" spans="1:26" ht="16.5" customHeight="1">
+    <row r="229" spans="1:26" ht="16.5">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -35502,7 +35519,7 @@
       <c r="Y229" s="5"/>
       <c r="Z229" s="5"/>
     </row>
-    <row r="230" spans="1:26" ht="16.5" customHeight="1">
+    <row r="230" spans="1:26" ht="16.5">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -35530,7 +35547,7 @@
       <c r="Y230" s="5"/>
       <c r="Z230" s="5"/>
     </row>
-    <row r="231" spans="1:26" ht="16.5" customHeight="1">
+    <row r="231" spans="1:26" ht="16.5">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -35558,7 +35575,7 @@
       <c r="Y231" s="5"/>
       <c r="Z231" s="5"/>
     </row>
-    <row r="232" spans="1:26" ht="16.5" customHeight="1">
+    <row r="232" spans="1:26" ht="16.5">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -35586,7 +35603,7 @@
       <c r="Y232" s="5"/>
       <c r="Z232" s="5"/>
     </row>
-    <row r="233" spans="1:26" ht="16.5" customHeight="1">
+    <row r="233" spans="1:26" ht="16.5">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -35614,7 +35631,7 @@
       <c r="Y233" s="5"/>
       <c r="Z233" s="5"/>
     </row>
-    <row r="234" spans="1:26" ht="16.5" customHeight="1">
+    <row r="234" spans="1:26" ht="16.5">
       <c r="A234" s="7"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
@@ -35642,7 +35659,7 @@
       <c r="Y234" s="5"/>
       <c r="Z234" s="5"/>
     </row>
-    <row r="235" spans="1:26" ht="16.5" customHeight="1">
+    <row r="235" spans="1:26" ht="16.5">
       <c r="A235" s="7"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
@@ -35670,7 +35687,7 @@
       <c r="Y235" s="5"/>
       <c r="Z235" s="5"/>
     </row>
-    <row r="236" spans="1:26" ht="16.5" customHeight="1">
+    <row r="236" spans="1:26" ht="16.5">
       <c r="A236" s="7"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
@@ -35698,7 +35715,7 @@
       <c r="Y236" s="5"/>
       <c r="Z236" s="5"/>
     </row>
-    <row r="237" spans="1:26" ht="16.5" customHeight="1">
+    <row r="237" spans="1:26" ht="16.5">
       <c r="A237" s="7"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
@@ -35726,7 +35743,7 @@
       <c r="Y237" s="5"/>
       <c r="Z237" s="5"/>
     </row>
-    <row r="238" spans="1:26" ht="16.5" customHeight="1">
+    <row r="238" spans="1:26" ht="16.5">
       <c r="A238" s="7"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
@@ -35754,7 +35771,7 @@
       <c r="Y238" s="5"/>
       <c r="Z238" s="5"/>
     </row>
-    <row r="239" spans="1:26" ht="16.5" customHeight="1">
+    <row r="239" spans="1:26" ht="16.5">
       <c r="A239" s="7"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
@@ -35782,7 +35799,7 @@
       <c r="Y239" s="5"/>
       <c r="Z239" s="5"/>
     </row>
-    <row r="240" spans="1:26" ht="16.5" customHeight="1">
+    <row r="240" spans="1:26" ht="16.5">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
@@ -35810,7 +35827,7 @@
       <c r="Y240" s="5"/>
       <c r="Z240" s="5"/>
     </row>
-    <row r="241" spans="1:26" ht="16.5" customHeight="1">
+    <row r="241" spans="1:26" ht="16.5">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -35838,7 +35855,7 @@
       <c r="Y241" s="5"/>
       <c r="Z241" s="5"/>
     </row>
-    <row r="242" spans="1:26" ht="16.5" customHeight="1">
+    <row r="242" spans="1:26" ht="16.5">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
@@ -35866,7 +35883,7 @@
       <c r="Y242" s="5"/>
       <c r="Z242" s="5"/>
     </row>
-    <row r="243" spans="1:26" ht="16.5" customHeight="1">
+    <row r="243" spans="1:26" ht="16.5">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
@@ -35894,7 +35911,7 @@
       <c r="Y243" s="5"/>
       <c r="Z243" s="5"/>
     </row>
-    <row r="244" spans="1:26" ht="16.5" customHeight="1">
+    <row r="244" spans="1:26" ht="16.5">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
@@ -35922,7 +35939,7 @@
       <c r="Y244" s="5"/>
       <c r="Z244" s="5"/>
     </row>
-    <row r="245" spans="1:26" ht="16.5" customHeight="1">
+    <row r="245" spans="1:26" ht="16.5">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -35950,7 +35967,7 @@
       <c r="Y245" s="5"/>
       <c r="Z245" s="5"/>
     </row>
-    <row r="246" spans="1:26" ht="16.5" customHeight="1">
+    <row r="246" spans="1:26" ht="16.5">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
@@ -35978,7 +35995,7 @@
       <c r="Y246" s="5"/>
       <c r="Z246" s="5"/>
     </row>
-    <row r="247" spans="1:26" ht="16.5" customHeight="1">
+    <row r="247" spans="1:26" ht="16.5">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
@@ -36006,7 +36023,7 @@
       <c r="Y247" s="5"/>
       <c r="Z247" s="5"/>
     </row>
-    <row r="248" spans="1:26" ht="16.5" customHeight="1">
+    <row r="248" spans="1:26" ht="16.5">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
@@ -36034,7 +36051,7 @@
       <c r="Y248" s="5"/>
       <c r="Z248" s="5"/>
     </row>
-    <row r="249" spans="1:26" ht="16.5" customHeight="1">
+    <row r="249" spans="1:26" ht="16.5">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
@@ -36062,7 +36079,7 @@
       <c r="Y249" s="5"/>
       <c r="Z249" s="5"/>
     </row>
-    <row r="250" spans="1:26" ht="16.5" customHeight="1">
+    <row r="250" spans="1:26" ht="16.5">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
@@ -36090,7 +36107,7 @@
       <c r="Y250" s="5"/>
       <c r="Z250" s="5"/>
     </row>
-    <row r="251" spans="1:26" ht="16.5" customHeight="1">
+    <row r="251" spans="1:26" ht="16.5">
       <c r="A251" s="7"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
@@ -36118,7 +36135,7 @@
       <c r="Y251" s="5"/>
       <c r="Z251" s="5"/>
     </row>
-    <row r="252" spans="1:26" ht="16.5" customHeight="1">
+    <row r="252" spans="1:26" ht="16.5">
       <c r="A252" s="7"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
@@ -36146,7 +36163,7 @@
       <c r="Y252" s="5"/>
       <c r="Z252" s="5"/>
     </row>
-    <row r="253" spans="1:26" ht="16.5" customHeight="1">
+    <row r="253" spans="1:26" ht="16.5">
       <c r="A253" s="7"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
@@ -36174,7 +36191,7 @@
       <c r="Y253" s="5"/>
       <c r="Z253" s="5"/>
     </row>
-    <row r="254" spans="1:26" ht="16.5" customHeight="1">
+    <row r="254" spans="1:26" ht="16.5">
       <c r="A254" s="7"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
@@ -36202,7 +36219,7 @@
       <c r="Y254" s="5"/>
       <c r="Z254" s="5"/>
     </row>
-    <row r="255" spans="1:26" ht="16.5" customHeight="1">
+    <row r="255" spans="1:26" ht="16.5">
       <c r="A255" s="7"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
@@ -36230,7 +36247,7 @@
       <c r="Y255" s="5"/>
       <c r="Z255" s="5"/>
     </row>
-    <row r="256" spans="1:26" ht="16.5" customHeight="1">
+    <row r="256" spans="1:26" ht="16.5">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
@@ -36258,7 +36275,7 @@
       <c r="Y256" s="5"/>
       <c r="Z256" s="5"/>
     </row>
-    <row r="257" spans="1:26" ht="16.5" customHeight="1">
+    <row r="257" spans="1:26" ht="16.5">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
@@ -36286,7 +36303,7 @@
       <c r="Y257" s="5"/>
       <c r="Z257" s="5"/>
     </row>
-    <row r="258" spans="1:26" ht="16.5" customHeight="1">
+    <row r="258" spans="1:26" ht="16.5">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
@@ -36314,7 +36331,7 @@
       <c r="Y258" s="5"/>
       <c r="Z258" s="5"/>
     </row>
-    <row r="259" spans="1:26" ht="16.5" customHeight="1">
+    <row r="259" spans="1:26" ht="16.5">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
@@ -36342,7 +36359,7 @@
       <c r="Y259" s="5"/>
       <c r="Z259" s="5"/>
     </row>
-    <row r="260" spans="1:26" ht="16.5" customHeight="1">
+    <row r="260" spans="1:26" ht="16.5">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
@@ -36370,7 +36387,7 @@
       <c r="Y260" s="5"/>
       <c r="Z260" s="5"/>
     </row>
-    <row r="261" spans="1:26" ht="16.5" customHeight="1">
+    <row r="261" spans="1:26" ht="16.5">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
@@ -36398,7 +36415,7 @@
       <c r="Y261" s="5"/>
       <c r="Z261" s="5"/>
     </row>
-    <row r="262" spans="1:26" ht="16.5" customHeight="1">
+    <row r="262" spans="1:26" ht="16.5">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
@@ -36426,7 +36443,7 @@
       <c r="Y262" s="5"/>
       <c r="Z262" s="5"/>
     </row>
-    <row r="263" spans="1:26" ht="16.5" customHeight="1">
+    <row r="263" spans="1:26" ht="16.5">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
@@ -36454,7 +36471,7 @@
       <c r="Y263" s="5"/>
       <c r="Z263" s="5"/>
     </row>
-    <row r="264" spans="1:26" ht="16.5" customHeight="1">
+    <row r="264" spans="1:26" ht="16.5">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
@@ -36482,7 +36499,7 @@
       <c r="Y264" s="5"/>
       <c r="Z264" s="5"/>
     </row>
-    <row r="265" spans="1:26" ht="16.5" customHeight="1">
+    <row r="265" spans="1:26" ht="16.5">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
@@ -36510,7 +36527,7 @@
       <c r="Y265" s="5"/>
       <c r="Z265" s="5"/>
     </row>
-    <row r="266" spans="1:26" ht="16.5" customHeight="1">
+    <row r="266" spans="1:26" ht="16.5">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
@@ -36538,7 +36555,7 @@
       <c r="Y266" s="5"/>
       <c r="Z266" s="5"/>
     </row>
-    <row r="267" spans="1:26" ht="16.5" customHeight="1">
+    <row r="267" spans="1:26" ht="16.5">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
@@ -36566,7 +36583,7 @@
       <c r="Y267" s="5"/>
       <c r="Z267" s="5"/>
     </row>
-    <row r="268" spans="1:26" ht="16.5" customHeight="1">
+    <row r="268" spans="1:26" ht="16.5">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
@@ -36594,7 +36611,7 @@
       <c r="Y268" s="5"/>
       <c r="Z268" s="5"/>
     </row>
-    <row r="269" spans="1:26" ht="16.5" customHeight="1">
+    <row r="269" spans="1:26" ht="16.5">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
@@ -36622,7 +36639,7 @@
       <c r="Y269" s="5"/>
       <c r="Z269" s="5"/>
     </row>
-    <row r="270" spans="1:26" ht="16.5" customHeight="1">
+    <row r="270" spans="1:26" ht="16.5">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
@@ -36650,7 +36667,7 @@
       <c r="Y270" s="5"/>
       <c r="Z270" s="5"/>
     </row>
-    <row r="271" spans="1:26" ht="16.5" customHeight="1">
+    <row r="271" spans="1:26" ht="16.5">
       <c r="A271" s="7"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
@@ -36678,7 +36695,7 @@
       <c r="Y271" s="5"/>
       <c r="Z271" s="5"/>
     </row>
-    <row r="272" spans="1:26" ht="16.5" customHeight="1">
+    <row r="272" spans="1:26" ht="16.5">
       <c r="A272" s="7"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
@@ -36706,7 +36723,7 @@
       <c r="Y272" s="5"/>
       <c r="Z272" s="5"/>
     </row>
-    <row r="273" spans="1:26" ht="16.5" customHeight="1">
+    <row r="273" spans="1:26" ht="16.5">
       <c r="A273" s="7"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
@@ -36734,7 +36751,7 @@
       <c r="Y273" s="5"/>
       <c r="Z273" s="5"/>
     </row>
-    <row r="274" spans="1:26" ht="16.5" customHeight="1">
+    <row r="274" spans="1:26" ht="16.5">
       <c r="A274" s="7"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
@@ -36762,7 +36779,7 @@
       <c r="Y274" s="5"/>
       <c r="Z274" s="5"/>
     </row>
-    <row r="275" spans="1:26" ht="16.5" customHeight="1">
+    <row r="275" spans="1:26" ht="16.5">
       <c r="A275" s="7"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
@@ -36790,7 +36807,7 @@
       <c r="Y275" s="5"/>
       <c r="Z275" s="5"/>
     </row>
-    <row r="276" spans="1:26" ht="16.5" customHeight="1">
+    <row r="276" spans="1:26" ht="16.5">
       <c r="A276" s="7"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
@@ -36818,7 +36835,7 @@
       <c r="Y276" s="5"/>
       <c r="Z276" s="5"/>
     </row>
-    <row r="277" spans="1:26" ht="16.5" customHeight="1">
+    <row r="277" spans="1:26" ht="16.5">
       <c r="A277" s="7"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
@@ -36846,7 +36863,7 @@
       <c r="Y277" s="5"/>
       <c r="Z277" s="5"/>
     </row>
-    <row r="278" spans="1:26" ht="16.5" customHeight="1">
+    <row r="278" spans="1:26" ht="16.5">
       <c r="A278" s="7"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
@@ -36874,7 +36891,7 @@
       <c r="Y278" s="5"/>
       <c r="Z278" s="5"/>
     </row>
-    <row r="279" spans="1:26" ht="16.5" customHeight="1">
+    <row r="279" spans="1:26" ht="16.5">
       <c r="A279" s="7"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
@@ -36902,7 +36919,7 @@
       <c r="Y279" s="5"/>
       <c r="Z279" s="5"/>
     </row>
-    <row r="280" spans="1:26" ht="16.5" customHeight="1">
+    <row r="280" spans="1:26" ht="16.5">
       <c r="A280" s="7"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
@@ -36930,7 +36947,7 @@
       <c r="Y280" s="5"/>
       <c r="Z280" s="5"/>
     </row>
-    <row r="281" spans="1:26" ht="16.5" customHeight="1">
+    <row r="281" spans="1:26" ht="16.5">
       <c r="A281" s="7"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
@@ -36958,7 +36975,7 @@
       <c r="Y281" s="5"/>
       <c r="Z281" s="5"/>
     </row>
-    <row r="282" spans="1:26" ht="16.5" customHeight="1">
+    <row r="282" spans="1:26" ht="16.5">
       <c r="A282" s="7"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
@@ -36986,7 +37003,7 @@
       <c r="Y282" s="5"/>
       <c r="Z282" s="5"/>
     </row>
-    <row r="283" spans="1:26" ht="16.5" customHeight="1">
+    <row r="283" spans="1:26" ht="16.5">
       <c r="A283" s="7"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
@@ -37014,7 +37031,7 @@
       <c r="Y283" s="5"/>
       <c r="Z283" s="5"/>
     </row>
-    <row r="284" spans="1:26" ht="16.5" customHeight="1">
+    <row r="284" spans="1:26" ht="16.5">
       <c r="A284" s="7"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
@@ -37042,7 +37059,7 @@
       <c r="Y284" s="5"/>
       <c r="Z284" s="5"/>
     </row>
-    <row r="285" spans="1:26" ht="16.5" customHeight="1">
+    <row r="285" spans="1:26" ht="16.5">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
@@ -37070,7 +37087,7 @@
       <c r="Y285" s="5"/>
       <c r="Z285" s="5"/>
     </row>
-    <row r="286" spans="1:26" ht="16.5" customHeight="1">
+    <row r="286" spans="1:26" ht="16.5">
       <c r="A286" s="7"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
@@ -37098,7 +37115,7 @@
       <c r="Y286" s="5"/>
       <c r="Z286" s="5"/>
     </row>
-    <row r="287" spans="1:26" ht="16.5" customHeight="1">
+    <row r="287" spans="1:26" ht="16.5">
       <c r="A287" s="7"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
@@ -37126,7 +37143,7 @@
       <c r="Y287" s="5"/>
       <c r="Z287" s="5"/>
     </row>
-    <row r="288" spans="1:26" ht="16.5" customHeight="1">
+    <row r="288" spans="1:26" ht="16.5">
       <c r="A288" s="7"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
@@ -37154,7 +37171,7 @@
       <c r="Y288" s="5"/>
       <c r="Z288" s="5"/>
     </row>
-    <row r="289" spans="1:26" ht="16.5" customHeight="1">
+    <row r="289" spans="1:26" ht="16.5">
       <c r="A289" s="7"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
@@ -37182,7 +37199,7 @@
       <c r="Y289" s="5"/>
       <c r="Z289" s="5"/>
     </row>
-    <row r="290" spans="1:26" ht="16.5" customHeight="1">
+    <row r="290" spans="1:26" ht="16.5">
       <c r="A290" s="7"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
@@ -37210,7 +37227,7 @@
       <c r="Y290" s="5"/>
       <c r="Z290" s="5"/>
     </row>
-    <row r="291" spans="1:26" ht="16.5" customHeight="1">
+    <row r="291" spans="1:26" ht="16.5">
       <c r="A291" s="7"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
@@ -37238,7 +37255,7 @@
       <c r="Y291" s="5"/>
       <c r="Z291" s="5"/>
     </row>
-    <row r="292" spans="1:26" ht="16.5" customHeight="1">
+    <row r="292" spans="1:26" ht="16.5">
       <c r="A292" s="7"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
@@ -37266,7 +37283,7 @@
       <c r="Y292" s="5"/>
       <c r="Z292" s="5"/>
     </row>
-    <row r="293" spans="1:26" ht="16.5" customHeight="1">
+    <row r="293" spans="1:26" ht="16.5">
       <c r="A293" s="7"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
@@ -37294,7 +37311,7 @@
       <c r="Y293" s="5"/>
       <c r="Z293" s="5"/>
     </row>
-    <row r="294" spans="1:26" ht="16.5" customHeight="1">
+    <row r="294" spans="1:26" ht="16.5">
       <c r="A294" s="7"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
@@ -37322,7 +37339,7 @@
       <c r="Y294" s="5"/>
       <c r="Z294" s="5"/>
     </row>
-    <row r="295" spans="1:26" ht="16.5" customHeight="1">
+    <row r="295" spans="1:26" ht="16.5">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
@@ -37350,7 +37367,7 @@
       <c r="Y295" s="5"/>
       <c r="Z295" s="5"/>
     </row>
-    <row r="296" spans="1:26" ht="16.5" customHeight="1">
+    <row r="296" spans="1:26" ht="16.5">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
@@ -37378,7 +37395,7 @@
       <c r="Y296" s="5"/>
       <c r="Z296" s="5"/>
     </row>
-    <row r="297" spans="1:26" ht="16.5" customHeight="1">
+    <row r="297" spans="1:26" ht="16.5">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
@@ -37406,7 +37423,7 @@
       <c r="Y297" s="5"/>
       <c r="Z297" s="5"/>
     </row>
-    <row r="298" spans="1:26" ht="16.5" customHeight="1">
+    <row r="298" spans="1:26" ht="16.5">
       <c r="A298" s="7"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
@@ -37434,7 +37451,7 @@
       <c r="Y298" s="5"/>
       <c r="Z298" s="5"/>
     </row>
-    <row r="299" spans="1:26" ht="16.5" customHeight="1">
+    <row r="299" spans="1:26" ht="16.5">
       <c r="A299" s="7"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
@@ -37462,7 +37479,7 @@
       <c r="Y299" s="5"/>
       <c r="Z299" s="5"/>
     </row>
-    <row r="300" spans="1:26" ht="16.5" customHeight="1">
+    <row r="300" spans="1:26" ht="16.5">
       <c r="A300" s="7"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
@@ -37490,7 +37507,7 @@
       <c r="Y300" s="5"/>
       <c r="Z300" s="5"/>
     </row>
-    <row r="301" spans="1:26" ht="16.5" customHeight="1">
+    <row r="301" spans="1:26" ht="16.5">
       <c r="A301" s="7"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
@@ -37518,7 +37535,7 @@
       <c r="Y301" s="5"/>
       <c r="Z301" s="5"/>
     </row>
-    <row r="302" spans="1:26" ht="16.5" customHeight="1">
+    <row r="302" spans="1:26" ht="16.5">
       <c r="A302" s="7"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
@@ -37546,7 +37563,7 @@
       <c r="Y302" s="5"/>
       <c r="Z302" s="5"/>
     </row>
-    <row r="303" spans="1:26" ht="16.5" customHeight="1">
+    <row r="303" spans="1:26" ht="16.5">
       <c r="A303" s="7"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
@@ -37574,7 +37591,7 @@
       <c r="Y303" s="5"/>
       <c r="Z303" s="5"/>
     </row>
-    <row r="304" spans="1:26" ht="16.5" customHeight="1">
+    <row r="304" spans="1:26" ht="16.5">
       <c r="A304" s="7"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
@@ -37602,7 +37619,7 @@
       <c r="Y304" s="5"/>
       <c r="Z304" s="5"/>
     </row>
-    <row r="305" spans="1:26" ht="16.5" customHeight="1">
+    <row r="305" spans="1:26" ht="16.5">
       <c r="A305" s="7"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
@@ -37630,7 +37647,7 @@
       <c r="Y305" s="5"/>
       <c r="Z305" s="5"/>
     </row>
-    <row r="306" spans="1:26" ht="16.5" customHeight="1">
+    <row r="306" spans="1:26" ht="16.5">
       <c r="A306" s="7"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
@@ -37658,7 +37675,7 @@
       <c r="Y306" s="5"/>
       <c r="Z306" s="5"/>
     </row>
-    <row r="307" spans="1:26" ht="16.5" customHeight="1">
+    <row r="307" spans="1:26" ht="16.5">
       <c r="A307" s="7"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
@@ -37686,7 +37703,7 @@
       <c r="Y307" s="5"/>
       <c r="Z307" s="5"/>
     </row>
-    <row r="308" spans="1:26" ht="16.5" customHeight="1">
+    <row r="308" spans="1:26" ht="16.5">
       <c r="A308" s="7"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
@@ -37714,7 +37731,7 @@
       <c r="Y308" s="5"/>
       <c r="Z308" s="5"/>
     </row>
-    <row r="309" spans="1:26" ht="16.5" customHeight="1">
+    <row r="309" spans="1:26" ht="16.5">
       <c r="A309" s="7"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
@@ -37742,7 +37759,7 @@
       <c r="Y309" s="5"/>
       <c r="Z309" s="5"/>
     </row>
-    <row r="310" spans="1:26" ht="16.5" customHeight="1">
+    <row r="310" spans="1:26" ht="16.5">
       <c r="A310" s="7"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
@@ -37770,7 +37787,7 @@
       <c r="Y310" s="5"/>
       <c r="Z310" s="5"/>
     </row>
-    <row r="311" spans="1:26" ht="16.5" customHeight="1">
+    <row r="311" spans="1:26" ht="16.5">
       <c r="A311" s="7"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
@@ -37798,7 +37815,7 @@
       <c r="Y311" s="5"/>
       <c r="Z311" s="5"/>
     </row>
-    <row r="312" spans="1:26" ht="16.5" customHeight="1">
+    <row r="312" spans="1:26" ht="16.5">
       <c r="A312" s="7"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
@@ -37826,7 +37843,7 @@
       <c r="Y312" s="5"/>
       <c r="Z312" s="5"/>
     </row>
-    <row r="313" spans="1:26" ht="16.5" customHeight="1">
+    <row r="313" spans="1:26" ht="16.5">
       <c r="A313" s="7"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
@@ -37854,7 +37871,7 @@
       <c r="Y313" s="5"/>
       <c r="Z313" s="5"/>
     </row>
-    <row r="314" spans="1:26" ht="16.5" customHeight="1">
+    <row r="314" spans="1:26" ht="16.5">
       <c r="A314" s="7"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
@@ -37882,7 +37899,7 @@
       <c r="Y314" s="5"/>
       <c r="Z314" s="5"/>
     </row>
-    <row r="315" spans="1:26" ht="16.5" customHeight="1">
+    <row r="315" spans="1:26" ht="16.5">
       <c r="A315" s="7"/>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
@@ -37910,7 +37927,7 @@
       <c r="Y315" s="5"/>
       <c r="Z315" s="5"/>
     </row>
-    <row r="316" spans="1:26" ht="16.5" customHeight="1">
+    <row r="316" spans="1:26" ht="16.5">
       <c r="A316" s="7"/>
       <c r="B316" s="7"/>
       <c r="C316" s="7"/>
@@ -37938,7 +37955,7 @@
       <c r="Y316" s="5"/>
       <c r="Z316" s="5"/>
     </row>
-    <row r="317" spans="1:26" ht="16.5" customHeight="1">
+    <row r="317" spans="1:26" ht="16.5">
       <c r="A317" s="7"/>
       <c r="B317" s="7"/>
       <c r="C317" s="7"/>
@@ -37966,7 +37983,7 @@
       <c r="Y317" s="5"/>
       <c r="Z317" s="5"/>
     </row>
-    <row r="318" spans="1:26" ht="16.5" customHeight="1">
+    <row r="318" spans="1:26" ht="16.5">
       <c r="A318" s="7"/>
       <c r="B318" s="7"/>
       <c r="C318" s="7"/>
@@ -37994,7 +38011,7 @@
       <c r="Y318" s="5"/>
       <c r="Z318" s="5"/>
     </row>
-    <row r="319" spans="1:26" ht="16.5" customHeight="1">
+    <row r="319" spans="1:26" ht="16.5">
       <c r="A319" s="7"/>
       <c r="B319" s="7"/>
       <c r="C319" s="7"/>
@@ -38022,7 +38039,7 @@
       <c r="Y319" s="5"/>
       <c r="Z319" s="5"/>
     </row>
-    <row r="320" spans="1:26" ht="16.5" customHeight="1">
+    <row r="320" spans="1:26" ht="16.5">
       <c r="A320" s="7"/>
       <c r="B320" s="7"/>
       <c r="C320" s="7"/>
@@ -38050,7 +38067,7 @@
       <c r="Y320" s="5"/>
       <c r="Z320" s="5"/>
     </row>
-    <row r="321" spans="1:26" ht="16.5" customHeight="1">
+    <row r="321" spans="1:26" ht="16.5">
       <c r="A321" s="7"/>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
@@ -38078,7 +38095,7 @@
       <c r="Y321" s="5"/>
       <c r="Z321" s="5"/>
     </row>
-    <row r="322" spans="1:26" ht="16.5" customHeight="1">
+    <row r="322" spans="1:26" ht="16.5">
       <c r="A322" s="7"/>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
@@ -38106,7 +38123,7 @@
       <c r="Y322" s="5"/>
       <c r="Z322" s="5"/>
     </row>
-    <row r="323" spans="1:26" ht="16.5" customHeight="1">
+    <row r="323" spans="1:26" ht="16.5">
       <c r="A323" s="7"/>
       <c r="B323" s="7"/>
       <c r="C323" s="7"/>
@@ -38134,7 +38151,7 @@
       <c r="Y323" s="5"/>
       <c r="Z323" s="5"/>
     </row>
-    <row r="324" spans="1:26" ht="16.5" customHeight="1">
+    <row r="324" spans="1:26" ht="16.5">
       <c r="A324" s="7"/>
       <c r="B324" s="7"/>
       <c r="C324" s="7"/>
@@ -38162,7 +38179,7 @@
       <c r="Y324" s="5"/>
       <c r="Z324" s="5"/>
     </row>
-    <row r="325" spans="1:26" ht="16.5" customHeight="1">
+    <row r="325" spans="1:26" ht="16.5">
       <c r="A325" s="7"/>
       <c r="B325" s="7"/>
       <c r="C325" s="7"/>
@@ -38190,7 +38207,7 @@
       <c r="Y325" s="5"/>
       <c r="Z325" s="5"/>
     </row>
-    <row r="326" spans="1:26" ht="16.5" customHeight="1">
+    <row r="326" spans="1:26" ht="16.5">
       <c r="A326" s="7"/>
       <c r="B326" s="7"/>
       <c r="C326" s="7"/>
@@ -38218,7 +38235,7 @@
       <c r="Y326" s="5"/>
       <c r="Z326" s="5"/>
     </row>
-    <row r="327" spans="1:26" ht="16.5" customHeight="1">
+    <row r="327" spans="1:26" ht="16.5">
       <c r="A327" s="7"/>
       <c r="B327" s="7"/>
       <c r="C327" s="7"/>
@@ -38246,7 +38263,7 @@
       <c r="Y327" s="5"/>
       <c r="Z327" s="5"/>
     </row>
-    <row r="328" spans="1:26" ht="16.5" customHeight="1">
+    <row r="328" spans="1:26" ht="16.5">
       <c r="A328" s="7"/>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
@@ -38274,7 +38291,7 @@
       <c r="Y328" s="5"/>
       <c r="Z328" s="5"/>
     </row>
-    <row r="329" spans="1:26" ht="16.5" customHeight="1">
+    <row r="329" spans="1:26" ht="16.5">
       <c r="A329" s="7"/>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
@@ -38302,7 +38319,7 @@
       <c r="Y329" s="5"/>
       <c r="Z329" s="5"/>
     </row>
-    <row r="330" spans="1:26" ht="16.5" customHeight="1">
+    <row r="330" spans="1:26" ht="16.5">
       <c r="A330" s="7"/>
       <c r="B330" s="7"/>
       <c r="C330" s="7"/>
@@ -38330,7 +38347,7 @@
       <c r="Y330" s="5"/>
       <c r="Z330" s="5"/>
     </row>
-    <row r="331" spans="1:26" ht="16.5" customHeight="1">
+    <row r="331" spans="1:26" ht="16.5">
       <c r="A331" s="7"/>
       <c r="B331" s="7"/>
       <c r="C331" s="7"/>
@@ -38358,7 +38375,7 @@
       <c r="Y331" s="5"/>
       <c r="Z331" s="5"/>
     </row>
-    <row r="332" spans="1:26" ht="16.5" customHeight="1">
+    <row r="332" spans="1:26" ht="16.5">
       <c r="A332" s="7"/>
       <c r="B332" s="7"/>
       <c r="C332" s="7"/>
@@ -38386,7 +38403,7 @@
       <c r="Y332" s="5"/>
       <c r="Z332" s="5"/>
     </row>
-    <row r="333" spans="1:26" ht="16.5" customHeight="1">
+    <row r="333" spans="1:26" ht="16.5">
       <c r="A333" s="7"/>
       <c r="B333" s="7"/>
       <c r="C333" s="7"/>
@@ -38414,7 +38431,7 @@
       <c r="Y333" s="5"/>
       <c r="Z333" s="5"/>
     </row>
-    <row r="334" spans="1:26" ht="16.5" customHeight="1">
+    <row r="334" spans="1:26" ht="16.5">
       <c r="A334" s="7"/>
       <c r="B334" s="7"/>
       <c r="C334" s="7"/>
@@ -38442,7 +38459,7 @@
       <c r="Y334" s="5"/>
       <c r="Z334" s="5"/>
     </row>
-    <row r="335" spans="1:26" ht="16.5" customHeight="1">
+    <row r="335" spans="1:26" ht="16.5">
       <c r="A335" s="7"/>
       <c r="B335" s="7"/>
       <c r="C335" s="7"/>
@@ -38470,7 +38487,7 @@
       <c r="Y335" s="5"/>
       <c r="Z335" s="5"/>
     </row>
-    <row r="336" spans="1:26" ht="16.5" customHeight="1">
+    <row r="336" spans="1:26" ht="16.5">
       <c r="A336" s="7"/>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
@@ -38498,7 +38515,7 @@
       <c r="Y336" s="5"/>
       <c r="Z336" s="5"/>
     </row>
-    <row r="337" spans="1:26" ht="16.5" customHeight="1">
+    <row r="337" spans="1:26" ht="16.5">
       <c r="A337" s="7"/>
       <c r="B337" s="7"/>
       <c r="C337" s="7"/>
@@ -38526,7 +38543,7 @@
       <c r="Y337" s="5"/>
       <c r="Z337" s="5"/>
     </row>
-    <row r="338" spans="1:26" ht="16.5" customHeight="1">
+    <row r="338" spans="1:26" ht="16.5">
       <c r="A338" s="7"/>
       <c r="B338" s="7"/>
       <c r="C338" s="7"/>
@@ -38554,7 +38571,7 @@
       <c r="Y338" s="5"/>
       <c r="Z338" s="5"/>
     </row>
-    <row r="339" spans="1:26" ht="16.5" customHeight="1">
+    <row r="339" spans="1:26" ht="16.5">
       <c r="A339" s="7"/>
       <c r="B339" s="7"/>
       <c r="C339" s="7"/>
@@ -38582,7 +38599,7 @@
       <c r="Y339" s="5"/>
       <c r="Z339" s="5"/>
     </row>
-    <row r="340" spans="1:26" ht="16.5" customHeight="1">
+    <row r="340" spans="1:26" ht="16.5">
       <c r="A340" s="7"/>
       <c r="B340" s="7"/>
       <c r="C340" s="7"/>
@@ -38610,7 +38627,7 @@
       <c r="Y340" s="5"/>
       <c r="Z340" s="5"/>
     </row>
-    <row r="341" spans="1:26" ht="16.5" customHeight="1">
+    <row r="341" spans="1:26" ht="16.5">
       <c r="A341" s="7"/>
       <c r="B341" s="7"/>
       <c r="C341" s="7"/>
@@ -38638,7 +38655,7 @@
       <c r="Y341" s="5"/>
       <c r="Z341" s="5"/>
     </row>
-    <row r="342" spans="1:26" ht="16.5" customHeight="1">
+    <row r="342" spans="1:26" ht="16.5">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="7"/>
@@ -38666,7 +38683,7 @@
       <c r="Y342" s="5"/>
       <c r="Z342" s="5"/>
     </row>
-    <row r="343" spans="1:26" ht="16.5" customHeight="1">
+    <row r="343" spans="1:26" ht="16.5">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="7"/>
@@ -38694,7 +38711,7 @@
       <c r="Y343" s="5"/>
       <c r="Z343" s="5"/>
     </row>
-    <row r="344" spans="1:26" ht="16.5" customHeight="1">
+    <row r="344" spans="1:26" ht="16.5">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="7"/>
@@ -38722,7 +38739,7 @@
       <c r="Y344" s="5"/>
       <c r="Z344" s="5"/>
     </row>
-    <row r="345" spans="1:26" ht="16.5" customHeight="1">
+    <row r="345" spans="1:26" ht="16.5">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="7"/>
@@ -38750,7 +38767,7 @@
       <c r="Y345" s="5"/>
       <c r="Z345" s="5"/>
     </row>
-    <row r="346" spans="1:26" ht="16.5" customHeight="1">
+    <row r="346" spans="1:26" ht="16.5">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="7"/>
@@ -38778,7 +38795,7 @@
       <c r="Y346" s="5"/>
       <c r="Z346" s="5"/>
     </row>
-    <row r="347" spans="1:26" ht="16.5" customHeight="1">
+    <row r="347" spans="1:26" ht="16.5">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
@@ -38806,7 +38823,7 @@
       <c r="Y347" s="5"/>
       <c r="Z347" s="5"/>
     </row>
-    <row r="348" spans="1:26" ht="16.5" customHeight="1">
+    <row r="348" spans="1:26" ht="16.5">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
@@ -38834,7 +38851,7 @@
       <c r="Y348" s="5"/>
       <c r="Z348" s="5"/>
     </row>
-    <row r="349" spans="1:26" ht="16.5" customHeight="1">
+    <row r="349" spans="1:26" ht="16.5">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
@@ -38862,7 +38879,7 @@
       <c r="Y349" s="5"/>
       <c r="Z349" s="5"/>
     </row>
-    <row r="350" spans="1:26" ht="16.5" customHeight="1">
+    <row r="350" spans="1:26" ht="16.5">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
@@ -38890,7 +38907,7 @@
       <c r="Y350" s="5"/>
       <c r="Z350" s="5"/>
     </row>
-    <row r="351" spans="1:26" ht="16.5" customHeight="1">
+    <row r="351" spans="1:26" ht="16.5">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
@@ -38918,7 +38935,7 @@
       <c r="Y351" s="5"/>
       <c r="Z351" s="5"/>
     </row>
-    <row r="352" spans="1:26" ht="16.5" customHeight="1">
+    <row r="352" spans="1:26" ht="16.5">
       <c r="A352" s="7"/>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
@@ -38946,7 +38963,7 @@
       <c r="Y352" s="5"/>
       <c r="Z352" s="5"/>
     </row>
-    <row r="353" spans="1:26" ht="16.5" customHeight="1">
+    <row r="353" spans="1:26" ht="16.5">
       <c r="A353" s="7"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
@@ -38974,7 +38991,7 @@
       <c r="Y353" s="5"/>
       <c r="Z353" s="5"/>
     </row>
-    <row r="354" spans="1:26" ht="16.5" customHeight="1">
+    <row r="354" spans="1:26" ht="16.5">
       <c r="A354" s="7"/>
       <c r="B354" s="7"/>
       <c r="C354" s="7"/>
@@ -39002,7 +39019,7 @@
       <c r="Y354" s="5"/>
       <c r="Z354" s="5"/>
     </row>
-    <row r="355" spans="1:26" ht="16.5" customHeight="1">
+    <row r="355" spans="1:26" ht="16.5">
       <c r="A355" s="7"/>
       <c r="B355" s="7"/>
       <c r="C355" s="7"/>
@@ -39030,7 +39047,7 @@
       <c r="Y355" s="5"/>
       <c r="Z355" s="5"/>
     </row>
-    <row r="356" spans="1:26" ht="16.5" customHeight="1">
+    <row r="356" spans="1:26" ht="16.5">
       <c r="A356" s="7"/>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
@@ -39058,7 +39075,7 @@
       <c r="Y356" s="5"/>
       <c r="Z356" s="5"/>
     </row>
-    <row r="357" spans="1:26" ht="16.5" customHeight="1">
+    <row r="357" spans="1:26" ht="16.5">
       <c r="A357" s="7"/>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
@@ -39086,7 +39103,7 @@
       <c r="Y357" s="5"/>
       <c r="Z357" s="5"/>
     </row>
-    <row r="358" spans="1:26" ht="16.5" customHeight="1">
+    <row r="358" spans="1:26" ht="16.5">
       <c r="A358" s="7"/>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
@@ -39114,7 +39131,7 @@
       <c r="Y358" s="5"/>
       <c r="Z358" s="5"/>
     </row>
-    <row r="359" spans="1:26" ht="16.5" customHeight="1">
+    <row r="359" spans="1:26" ht="16.5">
       <c r="A359" s="7"/>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
@@ -39142,7 +39159,7 @@
       <c r="Y359" s="5"/>
       <c r="Z359" s="5"/>
     </row>
-    <row r="360" spans="1:26" ht="16.5" customHeight="1">
+    <row r="360" spans="1:26" ht="16.5">
       <c r="A360" s="7"/>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
@@ -39170,7 +39187,7 @@
       <c r="Y360" s="5"/>
       <c r="Z360" s="5"/>
     </row>
-    <row r="361" spans="1:26" ht="16.5" customHeight="1">
+    <row r="361" spans="1:26" ht="16.5">
       <c r="A361" s="7"/>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
@@ -39198,7 +39215,7 @@
       <c r="Y361" s="5"/>
       <c r="Z361" s="5"/>
     </row>
-    <row r="362" spans="1:26" ht="16.5" customHeight="1">
+    <row r="362" spans="1:26" ht="16.5">
       <c r="A362" s="7"/>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
@@ -39226,7 +39243,7 @@
       <c r="Y362" s="5"/>
       <c r="Z362" s="5"/>
     </row>
-    <row r="363" spans="1:26" ht="16.5" customHeight="1">
+    <row r="363" spans="1:26" ht="16.5">
       <c r="A363" s="7"/>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
@@ -39254,7 +39271,7 @@
       <c r="Y363" s="5"/>
       <c r="Z363" s="5"/>
     </row>
-    <row r="364" spans="1:26" ht="16.5" customHeight="1">
+    <row r="364" spans="1:26" ht="16.5">
       <c r="A364" s="7"/>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
@@ -39282,7 +39299,7 @@
       <c r="Y364" s="5"/>
       <c r="Z364" s="5"/>
     </row>
-    <row r="365" spans="1:26" ht="16.5" customHeight="1">
+    <row r="365" spans="1:26" ht="16.5">
       <c r="A365" s="7"/>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
@@ -39310,7 +39327,7 @@
       <c r="Y365" s="5"/>
       <c r="Z365" s="5"/>
     </row>
-    <row r="366" spans="1:26" ht="16.5" customHeight="1">
+    <row r="366" spans="1:26" ht="16.5">
       <c r="A366" s="7"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
@@ -39338,7 +39355,7 @@
       <c r="Y366" s="5"/>
       <c r="Z366" s="5"/>
     </row>
-    <row r="367" spans="1:26" ht="16.5" customHeight="1">
+    <row r="367" spans="1:26" ht="16.5">
       <c r="A367" s="7"/>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
@@ -39366,7 +39383,7 @@
       <c r="Y367" s="5"/>
       <c r="Z367" s="5"/>
     </row>
-    <row r="368" spans="1:26" ht="16.5" customHeight="1">
+    <row r="368" spans="1:26" ht="16.5">
       <c r="A368" s="7"/>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
@@ -39394,7 +39411,7 @@
       <c r="Y368" s="5"/>
       <c r="Z368" s="5"/>
     </row>
-    <row r="369" spans="1:26" ht="16.5" customHeight="1">
+    <row r="369" spans="1:26" ht="16.5">
       <c r="A369" s="7"/>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
@@ -39422,7 +39439,7 @@
       <c r="Y369" s="5"/>
       <c r="Z369" s="5"/>
     </row>
-    <row r="370" spans="1:26" ht="16.5" customHeight="1">
+    <row r="370" spans="1:26" ht="16.5">
       <c r="A370" s="7"/>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
@@ -39450,7 +39467,7 @@
       <c r="Y370" s="5"/>
       <c r="Z370" s="5"/>
     </row>
-    <row r="371" spans="1:26" ht="16.5" customHeight="1">
+    <row r="371" spans="1:26" ht="16.5">
       <c r="A371" s="7"/>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
@@ -39478,7 +39495,7 @@
       <c r="Y371" s="5"/>
       <c r="Z371" s="5"/>
     </row>
-    <row r="372" spans="1:26" ht="16.5" customHeight="1">
+    <row r="372" spans="1:26" ht="16.5">
       <c r="A372" s="7"/>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
@@ -39506,7 +39523,7 @@
       <c r="Y372" s="5"/>
       <c r="Z372" s="5"/>
     </row>
-    <row r="373" spans="1:26" ht="16.5" customHeight="1">
+    <row r="373" spans="1:26" ht="16.5">
       <c r="A373" s="7"/>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
@@ -39534,7 +39551,7 @@
       <c r="Y373" s="5"/>
       <c r="Z373" s="5"/>
     </row>
-    <row r="374" spans="1:26" ht="16.5" customHeight="1">
+    <row r="374" spans="1:26" ht="16.5">
       <c r="A374" s="7"/>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
@@ -39562,7 +39579,7 @@
       <c r="Y374" s="5"/>
       <c r="Z374" s="5"/>
     </row>
-    <row r="375" spans="1:26" ht="16.5" customHeight="1">
+    <row r="375" spans="1:26" ht="16.5">
       <c r="A375" s="7"/>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
@@ -39590,7 +39607,7 @@
       <c r="Y375" s="5"/>
       <c r="Z375" s="5"/>
     </row>
-    <row r="376" spans="1:26" ht="16.5" customHeight="1">
+    <row r="376" spans="1:26" ht="16.5">
       <c r="A376" s="7"/>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
@@ -39618,7 +39635,7 @@
       <c r="Y376" s="5"/>
       <c r="Z376" s="5"/>
     </row>
-    <row r="377" spans="1:26" ht="16.5" customHeight="1">
+    <row r="377" spans="1:26" ht="16.5">
       <c r="A377" s="7"/>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
@@ -39646,7 +39663,7 @@
       <c r="Y377" s="5"/>
       <c r="Z377" s="5"/>
     </row>
-    <row r="378" spans="1:26" ht="16.5" customHeight="1">
+    <row r="378" spans="1:26" ht="16.5">
       <c r="A378" s="7"/>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
@@ -39674,7 +39691,7 @@
       <c r="Y378" s="5"/>
       <c r="Z378" s="5"/>
     </row>
-    <row r="379" spans="1:26" ht="16.5" customHeight="1">
+    <row r="379" spans="1:26" ht="16.5">
       <c r="A379" s="7"/>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
@@ -39702,7 +39719,7 @@
       <c r="Y379" s="5"/>
       <c r="Z379" s="5"/>
     </row>
-    <row r="380" spans="1:26" ht="16.5" customHeight="1">
+    <row r="380" spans="1:26" ht="16.5">
       <c r="A380" s="7"/>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
@@ -39730,7 +39747,7 @@
       <c r="Y380" s="5"/>
       <c r="Z380" s="5"/>
     </row>
-    <row r="381" spans="1:26" ht="16.5" customHeight="1">
+    <row r="381" spans="1:26" ht="16.5">
       <c r="A381" s="7"/>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
@@ -39758,7 +39775,7 @@
       <c r="Y381" s="5"/>
       <c r="Z381" s="5"/>
     </row>
-    <row r="382" spans="1:26" ht="16.5" customHeight="1">
+    <row r="382" spans="1:26" ht="16.5">
       <c r="A382" s="7"/>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
@@ -39786,7 +39803,7 @@
       <c r="Y382" s="5"/>
       <c r="Z382" s="5"/>
     </row>
-    <row r="383" spans="1:26" ht="16.5" customHeight="1">
+    <row r="383" spans="1:26" ht="16.5">
       <c r="A383" s="7"/>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
@@ -39814,7 +39831,7 @@
       <c r="Y383" s="5"/>
       <c r="Z383" s="5"/>
     </row>
-    <row r="384" spans="1:26" ht="16.5" customHeight="1">
+    <row r="384" spans="1:26" ht="16.5">
       <c r="A384" s="7"/>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
@@ -39842,7 +39859,7 @@
       <c r="Y384" s="5"/>
       <c r="Z384" s="5"/>
     </row>
-    <row r="385" spans="1:26" ht="16.5" customHeight="1">
+    <row r="385" spans="1:26" ht="16.5">
       <c r="A385" s="7"/>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
@@ -39870,7 +39887,7 @@
       <c r="Y385" s="5"/>
       <c r="Z385" s="5"/>
     </row>
-    <row r="386" spans="1:26" ht="16.5" customHeight="1">
+    <row r="386" spans="1:26" ht="16.5">
       <c r="A386" s="7"/>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
@@ -39898,7 +39915,7 @@
       <c r="Y386" s="5"/>
       <c r="Z386" s="5"/>
     </row>
-    <row r="387" spans="1:26" ht="16.5" customHeight="1">
+    <row r="387" spans="1:26" ht="16.5">
       <c r="A387" s="7"/>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
@@ -39926,7 +39943,7 @@
       <c r="Y387" s="5"/>
       <c r="Z387" s="5"/>
     </row>
-    <row r="388" spans="1:26" ht="16.5" customHeight="1">
+    <row r="388" spans="1:26" ht="16.5">
       <c r="A388" s="7"/>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
@@ -39954,7 +39971,7 @@
       <c r="Y388" s="5"/>
       <c r="Z388" s="5"/>
     </row>
-    <row r="389" spans="1:26" ht="16.5" customHeight="1">
+    <row r="389" spans="1:26" ht="16.5">
       <c r="A389" s="7"/>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
@@ -39982,7 +39999,7 @@
       <c r="Y389" s="5"/>
       <c r="Z389" s="5"/>
     </row>
-    <row r="390" spans="1:26" ht="16.5" customHeight="1">
+    <row r="390" spans="1:26" ht="16.5">
       <c r="A390" s="7"/>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
@@ -40010,7 +40027,7 @@
       <c r="Y390" s="5"/>
       <c r="Z390" s="5"/>
     </row>
-    <row r="391" spans="1:26" ht="16.5" customHeight="1">
+    <row r="391" spans="1:26" ht="16.5">
       <c r="A391" s="7"/>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
@@ -40038,7 +40055,7 @@
       <c r="Y391" s="5"/>
       <c r="Z391" s="5"/>
     </row>
-    <row r="392" spans="1:26" ht="16.5" customHeight="1">
+    <row r="392" spans="1:26" ht="16.5">
       <c r="A392" s="7"/>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
@@ -40066,7 +40083,7 @@
       <c r="Y392" s="5"/>
       <c r="Z392" s="5"/>
     </row>
-    <row r="393" spans="1:26" ht="16.5" customHeight="1">
+    <row r="393" spans="1:26" ht="16.5">
       <c r="A393" s="7"/>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
@@ -40094,7 +40111,7 @@
       <c r="Y393" s="5"/>
       <c r="Z393" s="5"/>
     </row>
-    <row r="394" spans="1:26" ht="16.5" customHeight="1">
+    <row r="394" spans="1:26" ht="16.5">
       <c r="A394" s="7"/>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
@@ -40122,7 +40139,7 @@
       <c r="Y394" s="5"/>
       <c r="Z394" s="5"/>
     </row>
-    <row r="395" spans="1:26" ht="16.5" customHeight="1">
+    <row r="395" spans="1:26" ht="16.5">
       <c r="A395" s="7"/>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
@@ -40150,7 +40167,7 @@
       <c r="Y395" s="5"/>
       <c r="Z395" s="5"/>
     </row>
-    <row r="396" spans="1:26" ht="16.5" customHeight="1">
+    <row r="396" spans="1:26" ht="16.5">
       <c r="A396" s="7"/>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
@@ -40178,7 +40195,7 @@
       <c r="Y396" s="5"/>
       <c r="Z396" s="5"/>
     </row>
-    <row r="397" spans="1:26" ht="16.5" customHeight="1">
+    <row r="397" spans="1:26" ht="16.5">
       <c r="A397" s="7"/>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
@@ -40206,7 +40223,7 @@
       <c r="Y397" s="5"/>
       <c r="Z397" s="5"/>
     </row>
-    <row r="398" spans="1:26" ht="16.5" customHeight="1">
+    <row r="398" spans="1:26" ht="16.5">
       <c r="A398" s="7"/>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
@@ -40234,7 +40251,7 @@
       <c r="Y398" s="5"/>
       <c r="Z398" s="5"/>
     </row>
-    <row r="399" spans="1:26" ht="16.5" customHeight="1">
+    <row r="399" spans="1:26" ht="16.5">
       <c r="A399" s="7"/>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
@@ -40262,7 +40279,7 @@
       <c r="Y399" s="5"/>
       <c r="Z399" s="5"/>
     </row>
-    <row r="400" spans="1:26" ht="16.5" customHeight="1">
+    <row r="400" spans="1:26" ht="16.5">
       <c r="A400" s="7"/>
       <c r="B400" s="7"/>
       <c r="C400" s="7"/>
@@ -40290,7 +40307,7 @@
       <c r="Y400" s="5"/>
       <c r="Z400" s="5"/>
     </row>
-    <row r="401" spans="1:26" ht="16.5" customHeight="1">
+    <row r="401" spans="1:26" ht="16.5">
       <c r="A401" s="7"/>
       <c r="B401" s="7"/>
       <c r="C401" s="7"/>
@@ -40318,7 +40335,7 @@
       <c r="Y401" s="5"/>
       <c r="Z401" s="5"/>
     </row>
-    <row r="402" spans="1:26" ht="16.5" customHeight="1">
+    <row r="402" spans="1:26" ht="16.5">
       <c r="A402" s="7"/>
       <c r="B402" s="7"/>
       <c r="C402" s="7"/>
@@ -40346,7 +40363,7 @@
       <c r="Y402" s="5"/>
       <c r="Z402" s="5"/>
     </row>
-    <row r="403" spans="1:26" ht="16.5" customHeight="1">
+    <row r="403" spans="1:26" ht="16.5">
       <c r="A403" s="7"/>
       <c r="B403" s="7"/>
       <c r="C403" s="7"/>
@@ -40374,7 +40391,7 @@
       <c r="Y403" s="5"/>
       <c r="Z403" s="5"/>
     </row>
-    <row r="404" spans="1:26" ht="16.5" customHeight="1">
+    <row r="404" spans="1:26" ht="16.5">
       <c r="A404" s="7"/>
       <c r="B404" s="7"/>
       <c r="C404" s="7"/>
@@ -40402,7 +40419,7 @@
       <c r="Y404" s="5"/>
       <c r="Z404" s="5"/>
     </row>
-    <row r="405" spans="1:26" ht="16.5" customHeight="1">
+    <row r="405" spans="1:26" ht="16.5">
       <c r="A405" s="7"/>
       <c r="B405" s="7"/>
       <c r="C405" s="7"/>
@@ -40430,7 +40447,7 @@
       <c r="Y405" s="5"/>
       <c r="Z405" s="5"/>
     </row>
-    <row r="406" spans="1:26" ht="16.5" customHeight="1">
+    <row r="406" spans="1:26" ht="16.5">
       <c r="A406" s="7"/>
       <c r="B406" s="7"/>
       <c r="C406" s="7"/>
@@ -40458,7 +40475,7 @@
       <c r="Y406" s="5"/>
       <c r="Z406" s="5"/>
     </row>
-    <row r="407" spans="1:26" ht="16.5" customHeight="1">
+    <row r="407" spans="1:26" ht="16.5">
       <c r="A407" s="7"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
@@ -40486,7 +40503,7 @@
       <c r="Y407" s="5"/>
       <c r="Z407" s="5"/>
     </row>
-    <row r="408" spans="1:26" ht="16.5" customHeight="1">
+    <row r="408" spans="1:26" ht="16.5">
       <c r="A408" s="7"/>
       <c r="B408" s="7"/>
       <c r="C408" s="7"/>
@@ -40514,7 +40531,7 @@
       <c r="Y408" s="5"/>
       <c r="Z408" s="5"/>
     </row>
-    <row r="409" spans="1:26" ht="16.5" customHeight="1">
+    <row r="409" spans="1:26" ht="16.5">
       <c r="A409" s="7"/>
       <c r="B409" s="7"/>
       <c r="C409" s="7"/>
@@ -40542,7 +40559,7 @@
       <c r="Y409" s="5"/>
       <c r="Z409" s="5"/>
     </row>
-    <row r="410" spans="1:26" ht="16.5" customHeight="1">
+    <row r="410" spans="1:26" ht="16.5">
       <c r="A410" s="7"/>
       <c r="B410" s="7"/>
       <c r="C410" s="7"/>
@@ -40570,7 +40587,7 @@
       <c r="Y410" s="5"/>
       <c r="Z410" s="5"/>
     </row>
-    <row r="411" spans="1:26" ht="16.5" customHeight="1">
+    <row r="411" spans="1:26" ht="16.5">
       <c r="A411" s="7"/>
       <c r="B411" s="7"/>
       <c r="C411" s="7"/>
@@ -40598,7 +40615,7 @@
       <c r="Y411" s="5"/>
       <c r="Z411" s="5"/>
     </row>
-    <row r="412" spans="1:26" ht="16.5" customHeight="1">
+    <row r="412" spans="1:26" ht="16.5">
       <c r="A412" s="7"/>
       <c r="B412" s="7"/>
       <c r="C412" s="7"/>
@@ -40626,7 +40643,7 @@
       <c r="Y412" s="5"/>
       <c r="Z412" s="5"/>
     </row>
-    <row r="413" spans="1:26" ht="16.5" customHeight="1">
+    <row r="413" spans="1:26" ht="16.5">
       <c r="A413" s="7"/>
       <c r="B413" s="7"/>
       <c r="C413" s="7"/>
@@ -40654,7 +40671,7 @@
       <c r="Y413" s="5"/>
       <c r="Z413" s="5"/>
     </row>
-    <row r="414" spans="1:26" ht="16.5" customHeight="1">
+    <row r="414" spans="1:26" ht="16.5">
       <c r="A414" s="7"/>
       <c r="B414" s="7"/>
       <c r="C414" s="7"/>
@@ -40682,7 +40699,7 @@
       <c r="Y414" s="5"/>
       <c r="Z414" s="5"/>
     </row>
-    <row r="415" spans="1:26" ht="16.5" customHeight="1">
+    <row r="415" spans="1:26" ht="16.5">
       <c r="A415" s="7"/>
       <c r="B415" s="7"/>
       <c r="C415" s="7"/>
@@ -40710,7 +40727,7 @@
       <c r="Y415" s="5"/>
       <c r="Z415" s="5"/>
     </row>
-    <row r="416" spans="1:26" ht="16.5" customHeight="1">
+    <row r="416" spans="1:26" ht="16.5">
       <c r="A416" s="7"/>
       <c r="B416" s="7"/>
       <c r="C416" s="7"/>
@@ -40738,7 +40755,7 @@
       <c r="Y416" s="5"/>
       <c r="Z416" s="5"/>
     </row>
-    <row r="417" spans="1:26" ht="16.5" customHeight="1">
+    <row r="417" spans="1:26" ht="16.5">
       <c r="A417" s="7"/>
       <c r="B417" s="7"/>
       <c r="C417" s="7"/>
@@ -40766,7 +40783,7 @@
       <c r="Y417" s="5"/>
       <c r="Z417" s="5"/>
     </row>
-    <row r="418" spans="1:26" ht="16.5" customHeight="1">
+    <row r="418" spans="1:26" ht="16.5">
       <c r="A418" s="7"/>
       <c r="B418" s="7"/>
       <c r="C418" s="7"/>
@@ -40794,7 +40811,7 @@
       <c r="Y418" s="5"/>
       <c r="Z418" s="5"/>
     </row>
-    <row r="419" spans="1:26" ht="16.5" customHeight="1">
+    <row r="419" spans="1:26" ht="16.5">
       <c r="A419" s="7"/>
       <c r="B419" s="7"/>
       <c r="C419" s="7"/>
@@ -40822,7 +40839,7 @@
       <c r="Y419" s="5"/>
       <c r="Z419" s="5"/>
     </row>
-    <row r="420" spans="1:26" ht="16.5" customHeight="1">
+    <row r="420" spans="1:26" ht="16.5">
       <c r="A420" s="7"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
@@ -40850,7 +40867,7 @@
       <c r="Y420" s="5"/>
       <c r="Z420" s="5"/>
     </row>
-    <row r="421" spans="1:26" ht="16.5" customHeight="1">
+    <row r="421" spans="1:26" ht="16.5">
       <c r="A421" s="7"/>
       <c r="B421" s="7"/>
       <c r="C421" s="7"/>
@@ -40878,7 +40895,7 @@
       <c r="Y421" s="5"/>
       <c r="Z421" s="5"/>
     </row>
-    <row r="422" spans="1:26" ht="16.5" customHeight="1">
+    <row r="422" spans="1:26" ht="16.5">
       <c r="A422" s="7"/>
       <c r="B422" s="7"/>
       <c r="C422" s="7"/>
@@ -40906,7 +40923,7 @@
       <c r="Y422" s="5"/>
       <c r="Z422" s="5"/>
     </row>
-    <row r="423" spans="1:26" ht="16.5" customHeight="1">
+    <row r="423" spans="1:26" ht="16.5">
       <c r="A423" s="7"/>
       <c r="B423" s="7"/>
       <c r="C423" s="7"/>
@@ -40934,7 +40951,7 @@
       <c r="Y423" s="5"/>
       <c r="Z423" s="5"/>
     </row>
-    <row r="424" spans="1:26" ht="16.5" customHeight="1">
+    <row r="424" spans="1:26" ht="16.5">
       <c r="A424" s="7"/>
       <c r="B424" s="7"/>
       <c r="C424" s="7"/>
@@ -40962,7 +40979,7 @@
       <c r="Y424" s="5"/>
       <c r="Z424" s="5"/>
     </row>
-    <row r="425" spans="1:26" ht="16.5" customHeight="1">
+    <row r="425" spans="1:26" ht="16.5">
       <c r="A425" s="7"/>
       <c r="B425" s="7"/>
       <c r="C425" s="7"/>
@@ -40990,7 +41007,7 @@
       <c r="Y425" s="5"/>
       <c r="Z425" s="5"/>
     </row>
-    <row r="426" spans="1:26" ht="16.5" customHeight="1">
+    <row r="426" spans="1:26" ht="16.5">
       <c r="A426" s="7"/>
       <c r="B426" s="7"/>
       <c r="C426" s="7"/>
@@ -41018,7 +41035,7 @@
       <c r="Y426" s="5"/>
       <c r="Z426" s="5"/>
     </row>
-    <row r="427" spans="1:26" ht="16.5" customHeight="1">
+    <row r="427" spans="1:26" ht="16.5">
       <c r="A427" s="7"/>
       <c r="B427" s="7"/>
       <c r="C427" s="7"/>
@@ -41046,7 +41063,7 @@
       <c r="Y427" s="5"/>
       <c r="Z427" s="5"/>
     </row>
-    <row r="428" spans="1:26" ht="16.5" customHeight="1">
+    <row r="428" spans="1:26" ht="16.5">
       <c r="A428" s="7"/>
       <c r="B428" s="7"/>
       <c r="C428" s="7"/>
@@ -41074,7 +41091,7 @@
       <c r="Y428" s="5"/>
       <c r="Z428" s="5"/>
     </row>
-    <row r="429" spans="1:26" ht="16.5" customHeight="1">
+    <row r="429" spans="1:26" ht="16.5">
       <c r="A429" s="7"/>
       <c r="B429" s="7"/>
       <c r="C429" s="7"/>
@@ -41102,7 +41119,7 @@
       <c r="Y429" s="5"/>
       <c r="Z429" s="5"/>
     </row>
-    <row r="430" spans="1:26" ht="16.5" customHeight="1">
+    <row r="430" spans="1:26" ht="16.5">
       <c r="A430" s="7"/>
       <c r="B430" s="7"/>
       <c r="C430" s="7"/>
@@ -41130,7 +41147,7 @@
       <c r="Y430" s="5"/>
       <c r="Z430" s="5"/>
     </row>
-    <row r="431" spans="1:26" ht="16.5" customHeight="1">
+    <row r="431" spans="1:26" ht="16.5">
       <c r="A431" s="7"/>
       <c r="B431" s="7"/>
       <c r="C431" s="7"/>
@@ -41158,7 +41175,7 @@
       <c r="Y431" s="5"/>
       <c r="Z431" s="5"/>
     </row>
-    <row r="432" spans="1:26" ht="16.5" customHeight="1">
+    <row r="432" spans="1:26" ht="16.5">
       <c r="A432" s="7"/>
       <c r="B432" s="7"/>
       <c r="C432" s="7"/>
@@ -41186,7 +41203,7 @@
       <c r="Y432" s="5"/>
       <c r="Z432" s="5"/>
     </row>
-    <row r="433" spans="1:26" ht="16.5" customHeight="1">
+    <row r="433" spans="1:26" ht="16.5">
       <c r="A433" s="7"/>
       <c r="B433" s="7"/>
       <c r="C433" s="7"/>
@@ -41214,7 +41231,7 @@
       <c r="Y433" s="5"/>
       <c r="Z433" s="5"/>
     </row>
-    <row r="434" spans="1:26" ht="16.5" customHeight="1">
+    <row r="434" spans="1:26" ht="16.5">
       <c r="A434" s="7"/>
       <c r="B434" s="7"/>
       <c r="C434" s="7"/>
@@ -41242,7 +41259,7 @@
       <c r="Y434" s="5"/>
       <c r="Z434" s="5"/>
     </row>
-    <row r="435" spans="1:26" ht="16.5" customHeight="1">
+    <row r="435" spans="1:26" ht="16.5">
       <c r="A435" s="7"/>
       <c r="B435" s="7"/>
       <c r="C435" s="7"/>
@@ -41270,7 +41287,7 @@
       <c r="Y435" s="5"/>
       <c r="Z435" s="5"/>
     </row>
-    <row r="436" spans="1:26" ht="16.5" customHeight="1">
+    <row r="436" spans="1:26" ht="16.5">
       <c r="A436" s="7"/>
       <c r="B436" s="7"/>
       <c r="C436" s="7"/>
@@ -41298,7 +41315,7 @@
       <c r="Y436" s="5"/>
       <c r="Z436" s="5"/>
     </row>
-    <row r="437" spans="1:26" ht="16.5" customHeight="1">
+    <row r="437" spans="1:26" ht="16.5">
       <c r="A437" s="7"/>
       <c r="B437" s="7"/>
       <c r="C437" s="7"/>
@@ -41326,7 +41343,7 @@
       <c r="Y437" s="5"/>
       <c r="Z437" s="5"/>
     </row>
-    <row r="438" spans="1:26" ht="16.5" customHeight="1">
+    <row r="438" spans="1:26" ht="16.5">
       <c r="A438" s="7"/>
       <c r="B438" s="7"/>
       <c r="C438" s="7"/>
@@ -41354,7 +41371,7 @@
       <c r="Y438" s="5"/>
       <c r="Z438" s="5"/>
     </row>
-    <row r="439" spans="1:26" ht="16.5" customHeight="1">
+    <row r="439" spans="1:26" ht="16.5">
       <c r="A439" s="7"/>
       <c r="B439" s="7"/>
       <c r="C439" s="7"/>
@@ -41382,7 +41399,7 @@
       <c r="Y439" s="5"/>
       <c r="Z439" s="5"/>
     </row>
-    <row r="440" spans="1:26" ht="16.5" customHeight="1">
+    <row r="440" spans="1:26" ht="16.5">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="7"/>
@@ -41410,7 +41427,7 @@
       <c r="Y440" s="5"/>
       <c r="Z440" s="5"/>
     </row>
-    <row r="441" spans="1:26" ht="16.5" customHeight="1">
+    <row r="441" spans="1:26" ht="16.5">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="7"/>
@@ -41438,7 +41455,7 @@
       <c r="Y441" s="5"/>
       <c r="Z441" s="5"/>
     </row>
-    <row r="442" spans="1:26" ht="16.5" customHeight="1">
+    <row r="442" spans="1:26" ht="16.5">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="7"/>
@@ -41466,7 +41483,7 @@
       <c r="Y442" s="5"/>
       <c r="Z442" s="5"/>
     </row>
-    <row r="443" spans="1:26" ht="16.5" customHeight="1">
+    <row r="443" spans="1:26" ht="16.5">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="7"/>
@@ -41494,7 +41511,7 @@
       <c r="Y443" s="5"/>
       <c r="Z443" s="5"/>
     </row>
-    <row r="444" spans="1:26" ht="16.5" customHeight="1">
+    <row r="444" spans="1:26" ht="16.5">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="7"/>
@@ -41522,7 +41539,7 @@
       <c r="Y444" s="5"/>
       <c r="Z444" s="5"/>
     </row>
-    <row r="445" spans="1:26" ht="16.5" customHeight="1">
+    <row r="445" spans="1:26" ht="16.5">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="7"/>
@@ -41550,7 +41567,7 @@
       <c r="Y445" s="5"/>
       <c r="Z445" s="5"/>
     </row>
-    <row r="446" spans="1:26" ht="16.5" customHeight="1">
+    <row r="446" spans="1:26" ht="16.5">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="7"/>
@@ -41578,7 +41595,7 @@
       <c r="Y446" s="5"/>
       <c r="Z446" s="5"/>
     </row>
-    <row r="447" spans="1:26" ht="16.5" customHeight="1">
+    <row r="447" spans="1:26" ht="16.5">
       <c r="A447" s="7"/>
       <c r="B447" s="7"/>
       <c r="C447" s="7"/>
@@ -41606,7 +41623,7 @@
       <c r="Y447" s="5"/>
       <c r="Z447" s="5"/>
     </row>
-    <row r="448" spans="1:26" ht="16.5" customHeight="1">
+    <row r="448" spans="1:26" ht="16.5">
       <c r="A448" s="7"/>
       <c r="B448" s="7"/>
       <c r="C448" s="7"/>
@@ -41634,7 +41651,7 @@
       <c r="Y448" s="5"/>
       <c r="Z448" s="5"/>
     </row>
-    <row r="449" spans="1:26" ht="16.5" customHeight="1">
+    <row r="449" spans="1:26" ht="16.5">
       <c r="A449" s="7"/>
       <c r="B449" s="7"/>
       <c r="C449" s="7"/>
@@ -41662,7 +41679,7 @@
       <c r="Y449" s="5"/>
       <c r="Z449" s="5"/>
     </row>
-    <row r="450" spans="1:26" ht="16.5" customHeight="1">
+    <row r="450" spans="1:26" ht="16.5">
       <c r="A450" s="7"/>
       <c r="B450" s="7"/>
       <c r="C450" s="7"/>
@@ -41690,7 +41707,7 @@
       <c r="Y450" s="5"/>
       <c r="Z450" s="5"/>
     </row>
-    <row r="451" spans="1:26" ht="16.5" customHeight="1">
+    <row r="451" spans="1:26" ht="16.5">
       <c r="A451" s="7"/>
       <c r="B451" s="7"/>
       <c r="C451" s="7"/>
@@ -41718,7 +41735,7 @@
       <c r="Y451" s="5"/>
       <c r="Z451" s="5"/>
     </row>
-    <row r="452" spans="1:26" ht="16.5" customHeight="1">
+    <row r="452" spans="1:26" ht="16.5">
       <c r="A452" s="7"/>
       <c r="B452" s="7"/>
       <c r="C452" s="7"/>
@@ -41746,7 +41763,7 @@
       <c r="Y452" s="5"/>
       <c r="Z452" s="5"/>
     </row>
-    <row r="453" spans="1:26" ht="16.5" customHeight="1">
+    <row r="453" spans="1:26" ht="16.5">
       <c r="A453" s="7"/>
       <c r="B453" s="7"/>
       <c r="C453" s="7"/>
@@ -41774,7 +41791,7 @@
       <c r="Y453" s="5"/>
       <c r="Z453" s="5"/>
     </row>
-    <row r="454" spans="1:26" ht="16.5" customHeight="1">
+    <row r="454" spans="1:26" ht="16.5">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="7"/>
@@ -41802,7 +41819,7 @@
       <c r="Y454" s="5"/>
       <c r="Z454" s="5"/>
     </row>
-    <row r="455" spans="1:26" ht="16.5" customHeight="1">
+    <row r="455" spans="1:26" ht="16.5">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="7"/>
@@ -41830,7 +41847,7 @@
       <c r="Y455" s="5"/>
       <c r="Z455" s="5"/>
     </row>
-    <row r="456" spans="1:26" ht="16.5" customHeight="1">
+    <row r="456" spans="1:26" ht="16.5">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="7"/>
@@ -41858,7 +41875,7 @@
       <c r="Y456" s="5"/>
       <c r="Z456" s="5"/>
     </row>
-    <row r="457" spans="1:26" ht="16.5" customHeight="1">
+    <row r="457" spans="1:26" ht="16.5">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="7"/>
@@ -41886,7 +41903,7 @@
       <c r="Y457" s="5"/>
       <c r="Z457" s="5"/>
     </row>
-    <row r="458" spans="1:26" ht="16.5" customHeight="1">
+    <row r="458" spans="1:26" ht="16.5">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="7"/>
@@ -41914,7 +41931,7 @@
       <c r="Y458" s="5"/>
       <c r="Z458" s="5"/>
     </row>
-    <row r="459" spans="1:26" ht="16.5" customHeight="1">
+    <row r="459" spans="1:26" ht="16.5">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="7"/>
@@ -41942,7 +41959,7 @@
       <c r="Y459" s="5"/>
       <c r="Z459" s="5"/>
     </row>
-    <row r="460" spans="1:26" ht="16.5" customHeight="1">
+    <row r="460" spans="1:26" ht="16.5">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="7"/>
@@ -41970,7 +41987,7 @@
       <c r="Y460" s="5"/>
       <c r="Z460" s="5"/>
     </row>
-    <row r="461" spans="1:26" ht="16.5" customHeight="1">
+    <row r="461" spans="1:26" ht="16.5">
       <c r="A461" s="7"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
@@ -41998,7 +42015,7 @@
       <c r="Y461" s="5"/>
       <c r="Z461" s="5"/>
     </row>
-    <row r="462" spans="1:26" ht="16.5" customHeight="1">
+    <row r="462" spans="1:26" ht="16.5">
       <c r="A462" s="7"/>
       <c r="B462" s="7"/>
       <c r="C462" s="7"/>
@@ -42026,7 +42043,7 @@
       <c r="Y462" s="5"/>
       <c r="Z462" s="5"/>
     </row>
-    <row r="463" spans="1:26" ht="16.5" customHeight="1">
+    <row r="463" spans="1:26" ht="16.5">
       <c r="A463" s="7"/>
       <c r="B463" s="7"/>
       <c r="C463" s="7"/>
@@ -42054,7 +42071,7 @@
       <c r="Y463" s="5"/>
       <c r="Z463" s="5"/>
     </row>
-    <row r="464" spans="1:26" ht="16.5" customHeight="1">
+    <row r="464" spans="1:26" ht="16.5">
       <c r="A464" s="7"/>
       <c r="B464" s="7"/>
       <c r="C464" s="7"/>
@@ -42082,7 +42099,7 @@
       <c r="Y464" s="5"/>
       <c r="Z464" s="5"/>
     </row>
-    <row r="465" spans="1:26" ht="16.5" customHeight="1">
+    <row r="465" spans="1:26" ht="16.5">
       <c r="A465" s="7"/>
       <c r="B465" s="7"/>
       <c r="C465" s="7"/>
@@ -42110,7 +42127,7 @@
       <c r="Y465" s="5"/>
       <c r="Z465" s="5"/>
     </row>
-    <row r="466" spans="1:26" ht="16.5" customHeight="1">
+    <row r="466" spans="1:26" ht="16.5">
       <c r="A466" s="7"/>
       <c r="B466" s="7"/>
       <c r="C466" s="7"/>
@@ -42138,7 +42155,7 @@
       <c r="Y466" s="5"/>
       <c r="Z466" s="5"/>
     </row>
-    <row r="467" spans="1:26" ht="16.5" customHeight="1">
+    <row r="467" spans="1:26" ht="16.5">
       <c r="A467" s="7"/>
       <c r="B467" s="7"/>
       <c r="C467" s="7"/>
@@ -42166,7 +42183,7 @@
       <c r="Y467" s="5"/>
       <c r="Z467" s="5"/>
     </row>
-    <row r="468" spans="1:26" ht="16.5" customHeight="1">
+    <row r="468" spans="1:26" ht="16.5">
       <c r="A468" s="7"/>
       <c r="B468" s="7"/>
       <c r="C468" s="7"/>
@@ -42194,7 +42211,7 @@
       <c r="Y468" s="5"/>
       <c r="Z468" s="5"/>
     </row>
-    <row r="469" spans="1:26" ht="16.5" customHeight="1">
+    <row r="469" spans="1:26" ht="16.5">
       <c r="A469" s="7"/>
       <c r="B469" s="7"/>
       <c r="C469" s="7"/>
@@ -42222,7 +42239,7 @@
       <c r="Y469" s="5"/>
       <c r="Z469" s="5"/>
     </row>
-    <row r="470" spans="1:26" ht="16.5" customHeight="1">
+    <row r="470" spans="1:26" ht="16.5">
       <c r="A470" s="7"/>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
@@ -42250,7 +42267,7 @@
       <c r="Y470" s="5"/>
       <c r="Z470" s="5"/>
     </row>
-    <row r="471" spans="1:26" ht="16.5" customHeight="1">
+    <row r="471" spans="1:26" ht="16.5">
       <c r="A471" s="7"/>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
@@ -42278,7 +42295,7 @@
       <c r="Y471" s="5"/>
       <c r="Z471" s="5"/>
     </row>
-    <row r="472" spans="1:26" ht="16.5" customHeight="1">
+    <row r="472" spans="1:26" ht="16.5">
       <c r="A472" s="7"/>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
@@ -42306,7 +42323,7 @@
       <c r="Y472" s="5"/>
       <c r="Z472" s="5"/>
     </row>
-    <row r="473" spans="1:26" ht="16.5" customHeight="1">
+    <row r="473" spans="1:26" ht="16.5">
       <c r="A473" s="7"/>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
@@ -42334,7 +42351,7 @@
       <c r="Y473" s="5"/>
       <c r="Z473" s="5"/>
     </row>
-    <row r="474" spans="1:26" ht="16.5" customHeight="1">
+    <row r="474" spans="1:26" ht="16.5">
       <c r="A474" s="7"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
@@ -42362,7 +42379,7 @@
       <c r="Y474" s="5"/>
       <c r="Z474" s="5"/>
     </row>
-    <row r="475" spans="1:26" ht="16.5" customHeight="1">
+    <row r="475" spans="1:26" ht="16.5">
       <c r="A475" s="7"/>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
@@ -42390,7 +42407,7 @@
       <c r="Y475" s="5"/>
       <c r="Z475" s="5"/>
     </row>
-    <row r="476" spans="1:26" ht="16.5" customHeight="1">
+    <row r="476" spans="1:26" ht="16.5">
       <c r="A476" s="7"/>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
@@ -42418,7 +42435,7 @@
       <c r="Y476" s="5"/>
       <c r="Z476" s="5"/>
     </row>
-    <row r="477" spans="1:26" ht="16.5" customHeight="1">
+    <row r="477" spans="1:26" ht="16.5">
       <c r="A477" s="7"/>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
@@ -42446,7 +42463,7 @@
       <c r="Y477" s="5"/>
       <c r="Z477" s="5"/>
     </row>
-    <row r="478" spans="1:26" ht="16.5" customHeight="1">
+    <row r="478" spans="1:26" ht="16.5">
       <c r="A478" s="7"/>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
@@ -42474,7 +42491,7 @@
       <c r="Y478" s="5"/>
       <c r="Z478" s="5"/>
     </row>
-    <row r="479" spans="1:26" ht="16.5" customHeight="1">
+    <row r="479" spans="1:26" ht="16.5">
       <c r="A479" s="7"/>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
@@ -42502,7 +42519,7 @@
       <c r="Y479" s="5"/>
       <c r="Z479" s="5"/>
     </row>
-    <row r="480" spans="1:26" ht="16.5" customHeight="1">
+    <row r="480" spans="1:26" ht="16.5">
       <c r="A480" s="7"/>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
@@ -42530,7 +42547,7 @@
       <c r="Y480" s="5"/>
       <c r="Z480" s="5"/>
     </row>
-    <row r="481" spans="1:26" ht="16.5" customHeight="1">
+    <row r="481" spans="1:26" ht="16.5">
       <c r="A481" s="7"/>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
@@ -42558,7 +42575,7 @@
       <c r="Y481" s="5"/>
       <c r="Z481" s="5"/>
     </row>
-    <row r="482" spans="1:26" ht="16.5" customHeight="1">
+    <row r="482" spans="1:26" ht="16.5">
       <c r="A482" s="7"/>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
@@ -42586,7 +42603,7 @@
       <c r="Y482" s="5"/>
       <c r="Z482" s="5"/>
     </row>
-    <row r="483" spans="1:26" ht="16.5" customHeight="1">
+    <row r="483" spans="1:26" ht="16.5">
       <c r="A483" s="7"/>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
@@ -42614,7 +42631,7 @@
       <c r="Y483" s="5"/>
       <c r="Z483" s="5"/>
     </row>
-    <row r="484" spans="1:26" ht="16.5" customHeight="1">
+    <row r="484" spans="1:26" ht="16.5">
       <c r="A484" s="7"/>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
@@ -42642,7 +42659,7 @@
       <c r="Y484" s="5"/>
       <c r="Z484" s="5"/>
     </row>
-    <row r="485" spans="1:26" ht="16.5" customHeight="1">
+    <row r="485" spans="1:26" ht="16.5">
       <c r="A485" s="7"/>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
@@ -42670,7 +42687,7 @@
       <c r="Y485" s="5"/>
       <c r="Z485" s="5"/>
     </row>
-    <row r="486" spans="1:26" ht="16.5" customHeight="1">
+    <row r="486" spans="1:26" ht="16.5">
       <c r="A486" s="7"/>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
@@ -42698,7 +42715,7 @@
       <c r="Y486" s="5"/>
       <c r="Z486" s="5"/>
     </row>
-    <row r="487" spans="1:26" ht="16.5" customHeight="1">
+    <row r="487" spans="1:26" ht="16.5">
       <c r="A487" s="7"/>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
@@ -42726,7 +42743,7 @@
       <c r="Y487" s="5"/>
       <c r="Z487" s="5"/>
     </row>
-    <row r="488" spans="1:26" ht="16.5" customHeight="1">
+    <row r="488" spans="1:26" ht="16.5">
       <c r="A488" s="7"/>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
@@ -42754,7 +42771,7 @@
       <c r="Y488" s="5"/>
       <c r="Z488" s="5"/>
     </row>
-    <row r="489" spans="1:26" ht="16.5" customHeight="1">
+    <row r="489" spans="1:26" ht="16.5">
       <c r="A489" s="7"/>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
@@ -42782,7 +42799,7 @@
       <c r="Y489" s="5"/>
       <c r="Z489" s="5"/>
     </row>
-    <row r="490" spans="1:26" ht="16.5" customHeight="1">
+    <row r="490" spans="1:26" ht="16.5">
       <c r="A490" s="7"/>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
@@ -42810,7 +42827,7 @@
       <c r="Y490" s="5"/>
       <c r="Z490" s="5"/>
     </row>
-    <row r="491" spans="1:26" ht="16.5" customHeight="1">
+    <row r="491" spans="1:26" ht="16.5">
       <c r="A491" s="7"/>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
@@ -42838,7 +42855,7 @@
       <c r="Y491" s="5"/>
       <c r="Z491" s="5"/>
     </row>
-    <row r="492" spans="1:26" ht="16.5" customHeight="1">
+    <row r="492" spans="1:26" ht="16.5">
       <c r="A492" s="7"/>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
@@ -42866,7 +42883,7 @@
       <c r="Y492" s="5"/>
       <c r="Z492" s="5"/>
     </row>
-    <row r="493" spans="1:26" ht="16.5" customHeight="1">
+    <row r="493" spans="1:26" ht="16.5">
       <c r="A493" s="7"/>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
@@ -42894,7 +42911,7 @@
       <c r="Y493" s="5"/>
       <c r="Z493" s="5"/>
     </row>
-    <row r="494" spans="1:26" ht="16.5" customHeight="1">
+    <row r="494" spans="1:26" ht="16.5">
       <c r="A494" s="7"/>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
@@ -42922,7 +42939,7 @@
       <c r="Y494" s="5"/>
       <c r="Z494" s="5"/>
     </row>
-    <row r="495" spans="1:26" ht="16.5" customHeight="1">
+    <row r="495" spans="1:26" ht="16.5">
       <c r="A495" s="7"/>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
@@ -42950,7 +42967,7 @@
       <c r="Y495" s="5"/>
       <c r="Z495" s="5"/>
     </row>
-    <row r="496" spans="1:26" ht="16.5" customHeight="1">
+    <row r="496" spans="1:26" ht="16.5">
       <c r="A496" s="7"/>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
@@ -42978,7 +42995,7 @@
       <c r="Y496" s="5"/>
       <c r="Z496" s="5"/>
     </row>
-    <row r="497" spans="1:26" ht="16.5" customHeight="1">
+    <row r="497" spans="1:26" ht="16.5">
       <c r="A497" s="7"/>
       <c r="B497" s="7"/>
       <c r="C497" s="7"/>
@@ -43006,7 +43023,7 @@
       <c r="Y497" s="5"/>
       <c r="Z497" s="5"/>
     </row>
-    <row r="498" spans="1:26" ht="16.5" customHeight="1">
+    <row r="498" spans="1:26" ht="16.5">
       <c r="A498" s="7"/>
       <c r="B498" s="7"/>
       <c r="C498" s="7"/>
@@ -43034,7 +43051,7 @@
       <c r="Y498" s="5"/>
       <c r="Z498" s="5"/>
     </row>
-    <row r="499" spans="1:26" ht="16.5" customHeight="1">
+    <row r="499" spans="1:26" ht="16.5">
       <c r="A499" s="7"/>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
@@ -43062,7 +43079,7 @@
       <c r="Y499" s="5"/>
       <c r="Z499" s="5"/>
     </row>
-    <row r="500" spans="1:26" ht="16.5" customHeight="1">
+    <row r="500" spans="1:26" ht="16.5">
       <c r="A500" s="7"/>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
@@ -43090,7 +43107,7 @@
       <c r="Y500" s="5"/>
       <c r="Z500" s="5"/>
     </row>
-    <row r="501" spans="1:26" ht="16.5" customHeight="1">
+    <row r="501" spans="1:26" ht="16.5">
       <c r="A501" s="7"/>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
@@ -43118,7 +43135,7 @@
       <c r="Y501" s="5"/>
       <c r="Z501" s="5"/>
     </row>
-    <row r="502" spans="1:26" ht="16.5" customHeight="1">
+    <row r="502" spans="1:26" ht="16.5">
       <c r="A502" s="7"/>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
@@ -43146,7 +43163,7 @@
       <c r="Y502" s="5"/>
       <c r="Z502" s="5"/>
     </row>
-    <row r="503" spans="1:26" ht="16.5" customHeight="1">
+    <row r="503" spans="1:26" ht="16.5">
       <c r="A503" s="7"/>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
@@ -43174,7 +43191,7 @@
       <c r="Y503" s="5"/>
       <c r="Z503" s="5"/>
     </row>
-    <row r="504" spans="1:26" ht="16.5" customHeight="1">
+    <row r="504" spans="1:26" ht="16.5">
       <c r="A504" s="7"/>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
@@ -43202,7 +43219,7 @@
       <c r="Y504" s="5"/>
       <c r="Z504" s="5"/>
     </row>
-    <row r="505" spans="1:26" ht="16.5" customHeight="1">
+    <row r="505" spans="1:26" ht="16.5">
       <c r="A505" s="7"/>
       <c r="B505" s="7"/>
       <c r="C505" s="7"/>
@@ -43230,7 +43247,7 @@
       <c r="Y505" s="5"/>
       <c r="Z505" s="5"/>
     </row>
-    <row r="506" spans="1:26" ht="16.5" customHeight="1">
+    <row r="506" spans="1:26" ht="16.5">
       <c r="A506" s="7"/>
       <c r="B506" s="7"/>
       <c r="C506" s="7"/>
@@ -43258,7 +43275,7 @@
       <c r="Y506" s="5"/>
       <c r="Z506" s="5"/>
     </row>
-    <row r="507" spans="1:26" ht="16.5" customHeight="1">
+    <row r="507" spans="1:26" ht="16.5">
       <c r="A507" s="7"/>
       <c r="B507" s="7"/>
       <c r="C507" s="7"/>
@@ -43286,7 +43303,7 @@
       <c r="Y507" s="5"/>
       <c r="Z507" s="5"/>
     </row>
-    <row r="508" spans="1:26" ht="16.5" customHeight="1">
+    <row r="508" spans="1:26" ht="16.5">
       <c r="A508" s="7"/>
       <c r="B508" s="7"/>
       <c r="C508" s="7"/>
@@ -43314,7 +43331,7 @@
       <c r="Y508" s="5"/>
       <c r="Z508" s="5"/>
     </row>
-    <row r="509" spans="1:26" ht="16.5" customHeight="1">
+    <row r="509" spans="1:26" ht="16.5">
       <c r="A509" s="7"/>
       <c r="B509" s="7"/>
       <c r="C509" s="7"/>
@@ -43342,7 +43359,7 @@
       <c r="Y509" s="5"/>
       <c r="Z509" s="5"/>
     </row>
-    <row r="510" spans="1:26" ht="16.5" customHeight="1">
+    <row r="510" spans="1:26" ht="16.5">
       <c r="A510" s="7"/>
       <c r="B510" s="7"/>
       <c r="C510" s="7"/>
@@ -43370,7 +43387,7 @@
       <c r="Y510" s="5"/>
       <c r="Z510" s="5"/>
     </row>
-    <row r="511" spans="1:26" ht="16.5" customHeight="1">
+    <row r="511" spans="1:26" ht="16.5">
       <c r="A511" s="7"/>
       <c r="B511" s="7"/>
       <c r="C511" s="7"/>
@@ -43398,7 +43415,7 @@
       <c r="Y511" s="5"/>
       <c r="Z511" s="5"/>
     </row>
-    <row r="512" spans="1:26" ht="16.5" customHeight="1">
+    <row r="512" spans="1:26" ht="16.5">
       <c r="A512" s="7"/>
       <c r="B512" s="7"/>
       <c r="C512" s="7"/>
@@ -43426,7 +43443,7 @@
       <c r="Y512" s="5"/>
       <c r="Z512" s="5"/>
     </row>
-    <row r="513" spans="1:26" ht="16.5" customHeight="1">
+    <row r="513" spans="1:26" ht="16.5">
       <c r="A513" s="7"/>
       <c r="B513" s="7"/>
       <c r="C513" s="7"/>
@@ -43454,7 +43471,7 @@
       <c r="Y513" s="5"/>
       <c r="Z513" s="5"/>
     </row>
-    <row r="514" spans="1:26" ht="16.5" customHeight="1">
+    <row r="514" spans="1:26" ht="16.5">
       <c r="A514" s="7"/>
       <c r="B514" s="7"/>
       <c r="C514" s="7"/>
@@ -43482,7 +43499,7 @@
       <c r="Y514" s="5"/>
       <c r="Z514" s="5"/>
     </row>
-    <row r="515" spans="1:26" ht="16.5" customHeight="1">
+    <row r="515" spans="1:26" ht="16.5">
       <c r="A515" s="7"/>
       <c r="B515" s="7"/>
       <c r="C515" s="7"/>
@@ -43510,7 +43527,7 @@
       <c r="Y515" s="5"/>
       <c r="Z515" s="5"/>
     </row>
-    <row r="516" spans="1:26" ht="16.5" customHeight="1">
+    <row r="516" spans="1:26" ht="16.5">
       <c r="A516" s="7"/>
       <c r="B516" s="7"/>
       <c r="C516" s="7"/>
@@ -43538,7 +43555,7 @@
       <c r="Y516" s="5"/>
       <c r="Z516" s="5"/>
     </row>
-    <row r="517" spans="1:26" ht="16.5" customHeight="1">
+    <row r="517" spans="1:26" ht="16.5">
       <c r="A517" s="7"/>
       <c r="B517" s="7"/>
       <c r="C517" s="7"/>
@@ -43566,7 +43583,7 @@
       <c r="Y517" s="5"/>
       <c r="Z517" s="5"/>
     </row>
-    <row r="518" spans="1:26" ht="16.5" customHeight="1">
+    <row r="518" spans="1:26" ht="16.5">
       <c r="A518" s="7"/>
       <c r="B518" s="7"/>
       <c r="C518" s="7"/>
@@ -43594,7 +43611,7 @@
       <c r="Y518" s="5"/>
       <c r="Z518" s="5"/>
     </row>
-    <row r="519" spans="1:26" ht="16.5" customHeight="1">
+    <row r="519" spans="1:26" ht="16.5">
       <c r="A519" s="7"/>
       <c r="B519" s="7"/>
       <c r="C519" s="7"/>
@@ -43622,7 +43639,7 @@
       <c r="Y519" s="5"/>
       <c r="Z519" s="5"/>
     </row>
-    <row r="520" spans="1:26" ht="16.5" customHeight="1">
+    <row r="520" spans="1:26" ht="16.5">
       <c r="A520" s="7"/>
       <c r="B520" s="7"/>
       <c r="C520" s="7"/>
@@ -43650,7 +43667,7 @@
       <c r="Y520" s="5"/>
       <c r="Z520" s="5"/>
     </row>
-    <row r="521" spans="1:26" ht="16.5" customHeight="1">
+    <row r="521" spans="1:26" ht="16.5">
       <c r="A521" s="7"/>
       <c r="B521" s="7"/>
       <c r="C521" s="7"/>
@@ -43678,7 +43695,7 @@
       <c r="Y521" s="5"/>
       <c r="Z521" s="5"/>
     </row>
-    <row r="522" spans="1:26" ht="16.5" customHeight="1">
+    <row r="522" spans="1:26" ht="16.5">
       <c r="A522" s="7"/>
       <c r="B522" s="7"/>
       <c r="C522" s="7"/>
@@ -43706,7 +43723,7 @@
       <c r="Y522" s="5"/>
       <c r="Z522" s="5"/>
     </row>
-    <row r="523" spans="1:26" ht="16.5" customHeight="1">
+    <row r="523" spans="1:26" ht="16.5">
       <c r="A523" s="7"/>
       <c r="B523" s="7"/>
       <c r="C523" s="7"/>
@@ -43734,7 +43751,7 @@
       <c r="Y523" s="5"/>
       <c r="Z523" s="5"/>
     </row>
-    <row r="524" spans="1:26" ht="16.5" customHeight="1">
+    <row r="524" spans="1:26" ht="16.5">
       <c r="A524" s="7"/>
       <c r="B524" s="7"/>
       <c r="C524" s="7"/>
@@ -43762,7 +43779,7 @@
       <c r="Y524" s="5"/>
       <c r="Z524" s="5"/>
     </row>
-    <row r="525" spans="1:26" ht="16.5" customHeight="1">
+    <row r="525" spans="1:26" ht="16.5">
       <c r="A525" s="7"/>
       <c r="B525" s="7"/>
       <c r="C525" s="7"/>
@@ -43790,7 +43807,7 @@
       <c r="Y525" s="5"/>
       <c r="Z525" s="5"/>
     </row>
-    <row r="526" spans="1:26" ht="16.5" customHeight="1">
+    <row r="526" spans="1:26" ht="16.5">
       <c r="A526" s="7"/>
       <c r="B526" s="7"/>
       <c r="C526" s="7"/>
@@ -43818,7 +43835,7 @@
       <c r="Y526" s="5"/>
       <c r="Z526" s="5"/>
     </row>
-    <row r="527" spans="1:26" ht="16.5" customHeight="1">
+    <row r="527" spans="1:26" ht="16.5">
       <c r="A527" s="7"/>
       <c r="B527" s="7"/>
       <c r="C527" s="7"/>
@@ -43846,7 +43863,7 @@
       <c r="Y527" s="5"/>
       <c r="Z527" s="5"/>
     </row>
-    <row r="528" spans="1:26" ht="16.5" customHeight="1">
+    <row r="528" spans="1:26" ht="16.5">
       <c r="A528" s="7"/>
       <c r="B528" s="7"/>
       <c r="C528" s="7"/>
@@ -43874,7 +43891,7 @@
       <c r="Y528" s="5"/>
       <c r="Z528" s="5"/>
     </row>
-    <row r="529" spans="1:26" ht="16.5" customHeight="1">
+    <row r="529" spans="1:26" ht="16.5">
       <c r="A529" s="7"/>
       <c r="B529" s="7"/>
       <c r="C529" s="7"/>
@@ -43902,7 +43919,7 @@
       <c r="Y529" s="5"/>
       <c r="Z529" s="5"/>
     </row>
-    <row r="530" spans="1:26" ht="16.5" customHeight="1">
+    <row r="530" spans="1:26" ht="16.5">
       <c r="A530" s="7"/>
       <c r="B530" s="7"/>
       <c r="C530" s="7"/>
@@ -43930,7 +43947,7 @@
       <c r="Y530" s="5"/>
       <c r="Z530" s="5"/>
     </row>
-    <row r="531" spans="1:26" ht="16.5" customHeight="1">
+    <row r="531" spans="1:26" ht="16.5">
       <c r="A531" s="7"/>
       <c r="B531" s="7"/>
       <c r="C531" s="7"/>
@@ -43958,7 +43975,7 @@
       <c r="Y531" s="5"/>
       <c r="Z531" s="5"/>
     </row>
-    <row r="532" spans="1:26" ht="16.5" customHeight="1">
+    <row r="532" spans="1:26" ht="16.5">
       <c r="A532" s="7"/>
       <c r="B532" s="7"/>
       <c r="C532" s="7"/>
@@ -43986,7 +44003,7 @@
       <c r="Y532" s="5"/>
       <c r="Z532" s="5"/>
     </row>
-    <row r="533" spans="1:26" ht="16.5" customHeight="1">
+    <row r="533" spans="1:26" ht="16.5">
       <c r="A533" s="7"/>
       <c r="B533" s="7"/>
       <c r="C533" s="7"/>
@@ -44014,7 +44031,7 @@
       <c r="Y533" s="5"/>
       <c r="Z533" s="5"/>
     </row>
-    <row r="534" spans="1:26" ht="16.5" customHeight="1">
+    <row r="534" spans="1:26" ht="16.5">
       <c r="A534" s="7"/>
       <c r="B534" s="7"/>
       <c r="C534" s="7"/>
@@ -44042,7 +44059,7 @@
       <c r="Y534" s="5"/>
       <c r="Z534" s="5"/>
     </row>
-    <row r="535" spans="1:26" ht="16.5" customHeight="1">
+    <row r="535" spans="1:26" ht="16.5">
       <c r="A535" s="7"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
@@ -44070,7 +44087,7 @@
       <c r="Y535" s="5"/>
       <c r="Z535" s="5"/>
     </row>
-    <row r="536" spans="1:26" ht="16.5" customHeight="1">
+    <row r="536" spans="1:26" ht="16.5">
       <c r="A536" s="7"/>
       <c r="B536" s="7"/>
       <c r="C536" s="7"/>
@@ -44098,7 +44115,7 @@
       <c r="Y536" s="5"/>
       <c r="Z536" s="5"/>
     </row>
-    <row r="537" spans="1:26" ht="16.5" customHeight="1">
+    <row r="537" spans="1:26" ht="16.5">
       <c r="A537" s="7"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
@@ -44126,7 +44143,7 @@
       <c r="Y537" s="5"/>
       <c r="Z537" s="5"/>
     </row>
-    <row r="538" spans="1:26" ht="16.5" customHeight="1">
+    <row r="538" spans="1:26" ht="16.5">
       <c r="A538" s="7"/>
       <c r="B538" s="7"/>
       <c r="C538" s="7"/>
@@ -44154,7 +44171,7 @@
       <c r="Y538" s="5"/>
       <c r="Z538" s="5"/>
     </row>
-    <row r="539" spans="1:26" ht="16.5" customHeight="1">
+    <row r="539" spans="1:26" ht="16.5">
       <c r="A539" s="7"/>
       <c r="B539" s="7"/>
       <c r="C539" s="7"/>
@@ -44182,7 +44199,7 @@
       <c r="Y539" s="5"/>
       <c r="Z539" s="5"/>
     </row>
-    <row r="540" spans="1:26" ht="16.5" customHeight="1">
+    <row r="540" spans="1:26" ht="16.5">
       <c r="A540" s="7"/>
       <c r="B540" s="7"/>
       <c r="C540" s="7"/>
@@ -44210,7 +44227,7 @@
       <c r="Y540" s="5"/>
       <c r="Z540" s="5"/>
     </row>
-    <row r="541" spans="1:26" ht="16.5" customHeight="1">
+    <row r="541" spans="1:26" ht="16.5">
       <c r="A541" s="7"/>
       <c r="B541" s="7"/>
       <c r="C541" s="7"/>
@@ -44238,7 +44255,7 @@
       <c r="Y541" s="5"/>
       <c r="Z541" s="5"/>
     </row>
-    <row r="542" spans="1:26" ht="16.5" customHeight="1">
+    <row r="542" spans="1:26" ht="16.5">
       <c r="A542" s="7"/>
       <c r="B542" s="7"/>
       <c r="C542" s="7"/>
@@ -44266,7 +44283,7 @@
       <c r="Y542" s="5"/>
       <c r="Z542" s="5"/>
     </row>
-    <row r="543" spans="1:26" ht="16.5" customHeight="1">
+    <row r="543" spans="1:26" ht="16.5">
       <c r="A543" s="7"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
@@ -44294,7 +44311,7 @@
       <c r="Y543" s="5"/>
       <c r="Z543" s="5"/>
     </row>
-    <row r="544" spans="1:26" ht="16.5" customHeight="1">
+    <row r="544" spans="1:26" ht="16.5">
       <c r="A544" s="7"/>
       <c r="B544" s="7"/>
       <c r="C544" s="7"/>
@@ -44322,7 +44339,7 @@
       <c r="Y544" s="5"/>
       <c r="Z544" s="5"/>
     </row>
-    <row r="545" spans="1:26" ht="16.5" customHeight="1">
+    <row r="545" spans="1:26" ht="16.5">
       <c r="A545" s="7"/>
       <c r="B545" s="7"/>
       <c r="C545" s="7"/>
@@ -44350,7 +44367,7 @@
       <c r="Y545" s="5"/>
       <c r="Z545" s="5"/>
     </row>
-    <row r="546" spans="1:26" ht="16.5" customHeight="1">
+    <row r="546" spans="1:26" ht="16.5">
       <c r="A546" s="7"/>
       <c r="B546" s="7"/>
       <c r="C546" s="7"/>
@@ -44378,7 +44395,7 @@
       <c r="Y546" s="5"/>
       <c r="Z546" s="5"/>
     </row>
-    <row r="547" spans="1:26" ht="16.5" customHeight="1">
+    <row r="547" spans="1:26" ht="16.5">
       <c r="A547" s="7"/>
       <c r="B547" s="7"/>
       <c r="C547" s="7"/>
@@ -44406,7 +44423,7 @@
       <c r="Y547" s="5"/>
       <c r="Z547" s="5"/>
     </row>
-    <row r="548" spans="1:26" ht="16.5" customHeight="1">
+    <row r="548" spans="1:26" ht="16.5">
       <c r="A548" s="7"/>
       <c r="B548" s="7"/>
       <c r="C548" s="7"/>
@@ -44434,7 +44451,7 @@
       <c r="Y548" s="5"/>
       <c r="Z548" s="5"/>
     </row>
-    <row r="549" spans="1:26" ht="16.5" customHeight="1">
+    <row r="549" spans="1:26" ht="16.5">
       <c r="A549" s="7"/>
       <c r="B549" s="7"/>
       <c r="C549" s="7"/>
@@ -44462,7 +44479,7 @@
       <c r="Y549" s="5"/>
       <c r="Z549" s="5"/>
     </row>
-    <row r="550" spans="1:26" ht="16.5" customHeight="1">
+    <row r="550" spans="1:26" ht="16.5">
       <c r="A550" s="7"/>
       <c r="B550" s="7"/>
       <c r="C550" s="7"/>
@@ -44490,7 +44507,7 @@
       <c r="Y550" s="5"/>
       <c r="Z550" s="5"/>
     </row>
-    <row r="551" spans="1:26" ht="16.5" customHeight="1">
+    <row r="551" spans="1:26" ht="16.5">
       <c r="A551" s="7"/>
       <c r="B551" s="7"/>
       <c r="C551" s="7"/>
@@ -44518,7 +44535,7 @@
       <c r="Y551" s="5"/>
       <c r="Z551" s="5"/>
     </row>
-    <row r="552" spans="1:26" ht="16.5" customHeight="1">
+    <row r="552" spans="1:26" ht="16.5">
       <c r="A552" s="7"/>
       <c r="B552" s="7"/>
       <c r="C552" s="7"/>
@@ -44546,7 +44563,7 @@
       <c r="Y552" s="5"/>
       <c r="Z552" s="5"/>
     </row>
-    <row r="553" spans="1:26" ht="16.5" customHeight="1">
+    <row r="553" spans="1:26" ht="16.5">
       <c r="A553" s="7"/>
       <c r="B553" s="7"/>
       <c r="C553" s="7"/>
@@ -44574,7 +44591,7 @@
       <c r="Y553" s="5"/>
       <c r="Z553" s="5"/>
     </row>
-    <row r="554" spans="1:26" ht="16.5" customHeight="1">
+    <row r="554" spans="1:26" ht="16.5">
       <c r="A554" s="7"/>
       <c r="B554" s="7"/>
       <c r="C554" s="7"/>
@@ -44602,7 +44619,7 @@
       <c r="Y554" s="5"/>
       <c r="Z554" s="5"/>
     </row>
-    <row r="555" spans="1:26" ht="16.5" customHeight="1">
+    <row r="555" spans="1:26" ht="16.5">
       <c r="A555" s="7"/>
       <c r="B555" s="7"/>
       <c r="C555" s="7"/>
@@ -44630,7 +44647,7 @@
       <c r="Y555" s="5"/>
       <c r="Z555" s="5"/>
     </row>
-    <row r="556" spans="1:26" ht="16.5" customHeight="1">
+    <row r="556" spans="1:26" ht="16.5">
       <c r="A556" s="7"/>
       <c r="B556" s="7"/>
       <c r="C556" s="7"/>
@@ -44658,7 +44675,7 @@
       <c r="Y556" s="5"/>
       <c r="Z556" s="5"/>
     </row>
-    <row r="557" spans="1:26" ht="16.5" customHeight="1">
+    <row r="557" spans="1:26" ht="16.5">
       <c r="A557" s="7"/>
       <c r="B557" s="7"/>
       <c r="C557" s="7"/>
@@ -44686,7 +44703,7 @@
       <c r="Y557" s="5"/>
       <c r="Z557" s="5"/>
     </row>
-    <row r="558" spans="1:26" ht="16.5" customHeight="1">
+    <row r="558" spans="1:26" ht="16.5">
       <c r="A558" s="7"/>
       <c r="B558" s="7"/>
       <c r="C558" s="7"/>
@@ -44714,7 +44731,7 @@
       <c r="Y558" s="5"/>
       <c r="Z558" s="5"/>
     </row>
-    <row r="559" spans="1:26" ht="16.5" customHeight="1">
+    <row r="559" spans="1:26" ht="16.5">
       <c r="A559" s="7"/>
       <c r="B559" s="7"/>
       <c r="C559" s="7"/>
@@ -44742,7 +44759,7 @@
       <c r="Y559" s="5"/>
       <c r="Z559" s="5"/>
     </row>
-    <row r="560" spans="1:26" ht="16.5" customHeight="1">
+    <row r="560" spans="1:26" ht="16.5">
       <c r="A560" s="7"/>
       <c r="B560" s="7"/>
       <c r="C560" s="7"/>
@@ -44770,7 +44787,7 @@
       <c r="Y560" s="5"/>
       <c r="Z560" s="5"/>
     </row>
-    <row r="561" spans="1:26" ht="16.5" customHeight="1">
+    <row r="561" spans="1:26" ht="16.5">
       <c r="A561" s="7"/>
       <c r="B561" s="7"/>
       <c r="C561" s="7"/>
@@ -44798,7 +44815,7 @@
       <c r="Y561" s="5"/>
       <c r="Z561" s="5"/>
     </row>
-    <row r="562" spans="1:26" ht="16.5" customHeight="1">
+    <row r="562" spans="1:26" ht="16.5">
       <c r="A562" s="7"/>
       <c r="B562" s="7"/>
       <c r="C562" s="7"/>
@@ -44826,7 +44843,7 @@
       <c r="Y562" s="5"/>
       <c r="Z562" s="5"/>
     </row>
-    <row r="563" spans="1:26" ht="16.5" customHeight="1">
+    <row r="563" spans="1:26" ht="16.5">
       <c r="A563" s="7"/>
       <c r="B563" s="7"/>
       <c r="C563" s="7"/>
@@ -44854,7 +44871,7 @@
       <c r="Y563" s="5"/>
       <c r="Z563" s="5"/>
     </row>
-    <row r="564" spans="1:26" ht="16.5" customHeight="1">
+    <row r="564" spans="1:26" ht="16.5">
       <c r="A564" s="7"/>
       <c r="B564" s="7"/>
       <c r="C564" s="7"/>
@@ -44882,7 +44899,7 @@
       <c r="Y564" s="5"/>
       <c r="Z564" s="5"/>
     </row>
-    <row r="565" spans="1:26" ht="16.5" customHeight="1">
+    <row r="565" spans="1:26" ht="16.5">
       <c r="A565" s="7"/>
       <c r="B565" s="7"/>
       <c r="C565" s="7"/>
@@ -44910,7 +44927,7 @@
       <c r="Y565" s="5"/>
       <c r="Z565" s="5"/>
     </row>
-    <row r="566" spans="1:26" ht="16.5" customHeight="1">
+    <row r="566" spans="1:26" ht="16.5">
       <c r="A566" s="7"/>
       <c r="B566" s="7"/>
       <c r="C566" s="7"/>
@@ -44938,7 +44955,7 @@
       <c r="Y566" s="5"/>
       <c r="Z566" s="5"/>
     </row>
-    <row r="567" spans="1:26" ht="16.5" customHeight="1">
+    <row r="567" spans="1:26" ht="16.5">
       <c r="A567" s="7"/>
       <c r="B567" s="7"/>
       <c r="C567" s="7"/>
@@ -44966,7 +44983,7 @@
       <c r="Y567" s="5"/>
       <c r="Z567" s="5"/>
     </row>
-    <row r="568" spans="1:26" ht="16.5" customHeight="1">
+    <row r="568" spans="1:26" ht="16.5">
       <c r="A568" s="7"/>
       <c r="B568" s="7"/>
       <c r="C568" s="7"/>
@@ -44994,7 +45011,7 @@
       <c r="Y568" s="5"/>
       <c r="Z568" s="5"/>
     </row>
-    <row r="569" spans="1:26" ht="16.5" customHeight="1">
+    <row r="569" spans="1:26" ht="16.5">
       <c r="A569" s="7"/>
       <c r="B569" s="7"/>
       <c r="C569" s="7"/>
@@ -45022,7 +45039,7 @@
       <c r="Y569" s="5"/>
       <c r="Z569" s="5"/>
     </row>
-    <row r="570" spans="1:26" ht="16.5" customHeight="1">
+    <row r="570" spans="1:26" ht="16.5">
       <c r="A570" s="7"/>
       <c r="B570" s="7"/>
       <c r="C570" s="7"/>
@@ -45050,7 +45067,7 @@
       <c r="Y570" s="5"/>
       <c r="Z570" s="5"/>
     </row>
-    <row r="571" spans="1:26" ht="16.5" customHeight="1">
+    <row r="571" spans="1:26" ht="16.5">
       <c r="A571" s="7"/>
       <c r="B571" s="7"/>
       <c r="C571" s="7"/>
@@ -45078,7 +45095,7 @@
       <c r="Y571" s="5"/>
       <c r="Z571" s="5"/>
     </row>
-    <row r="572" spans="1:26" ht="16.5" customHeight="1">
+    <row r="572" spans="1:26" ht="16.5">
       <c r="A572" s="7"/>
       <c r="B572" s="7"/>
       <c r="C572" s="7"/>
@@ -45106,7 +45123,7 @@
       <c r="Y572" s="5"/>
       <c r="Z572" s="5"/>
     </row>
-    <row r="573" spans="1:26" ht="16.5" customHeight="1">
+    <row r="573" spans="1:26" ht="16.5">
       <c r="A573" s="7"/>
       <c r="B573" s="7"/>
       <c r="C573" s="7"/>
@@ -45134,7 +45151,7 @@
       <c r="Y573" s="5"/>
       <c r="Z573" s="5"/>
     </row>
-    <row r="574" spans="1:26" ht="16.5" customHeight="1">
+    <row r="574" spans="1:26" ht="16.5">
       <c r="A574" s="7"/>
       <c r="B574" s="7"/>
       <c r="C574" s="7"/>
@@ -45162,7 +45179,7 @@
       <c r="Y574" s="5"/>
       <c r="Z574" s="5"/>
     </row>
-    <row r="575" spans="1:26" ht="16.5" customHeight="1">
+    <row r="575" spans="1:26" ht="16.5">
       <c r="A575" s="7"/>
       <c r="B575" s="7"/>
       <c r="C575" s="7"/>
@@ -45190,7 +45207,7 @@
       <c r="Y575" s="5"/>
       <c r="Z575" s="5"/>
     </row>
-    <row r="576" spans="1:26" ht="16.5" customHeight="1">
+    <row r="576" spans="1:26" ht="16.5">
       <c r="A576" s="7"/>
       <c r="B576" s="7"/>
       <c r="C576" s="7"/>
@@ -45218,7 +45235,7 @@
       <c r="Y576" s="5"/>
       <c r="Z576" s="5"/>
     </row>
-    <row r="577" spans="1:26" ht="16.5" customHeight="1">
+    <row r="577" spans="1:26" ht="16.5">
       <c r="A577" s="7"/>
       <c r="B577" s="7"/>
       <c r="C577" s="7"/>
@@ -45246,7 +45263,7 @@
       <c r="Y577" s="5"/>
       <c r="Z577" s="5"/>
     </row>
-    <row r="578" spans="1:26" ht="16.5" customHeight="1">
+    <row r="578" spans="1:26" ht="16.5">
       <c r="A578" s="7"/>
       <c r="B578" s="7"/>
       <c r="C578" s="7"/>
@@ -45274,7 +45291,7 @@
       <c r="Y578" s="5"/>
       <c r="Z578" s="5"/>
     </row>
-    <row r="579" spans="1:26" ht="16.5" customHeight="1">
+    <row r="579" spans="1:26" ht="16.5">
       <c r="A579" s="7"/>
       <c r="B579" s="7"/>
       <c r="C579" s="7"/>
@@ -45302,7 +45319,7 @@
       <c r="Y579" s="5"/>
       <c r="Z579" s="5"/>
     </row>
-    <row r="580" spans="1:26" ht="16.5" customHeight="1">
+    <row r="580" spans="1:26" ht="16.5">
       <c r="A580" s="7"/>
       <c r="B580" s="7"/>
       <c r="C580" s="7"/>
@@ -45330,7 +45347,7 @@
       <c r="Y580" s="5"/>
       <c r="Z580" s="5"/>
     </row>
-    <row r="581" spans="1:26" ht="16.5" customHeight="1">
+    <row r="581" spans="1:26" ht="16.5">
       <c r="A581" s="7"/>
       <c r="B581" s="7"/>
       <c r="C581" s="7"/>
@@ -45358,7 +45375,7 @@
       <c r="Y581" s="5"/>
       <c r="Z581" s="5"/>
     </row>
-    <row r="582" spans="1:26" ht="16.5" customHeight="1">
+    <row r="582" spans="1:26" ht="16.5">
       <c r="A582" s="7"/>
       <c r="B582" s="7"/>
       <c r="C582" s="7"/>
@@ -45386,7 +45403,7 @@
       <c r="Y582" s="5"/>
       <c r="Z582" s="5"/>
     </row>
-    <row r="583" spans="1:26" ht="16.5" customHeight="1">
+    <row r="583" spans="1:26" ht="16.5">
       <c r="A583" s="7"/>
       <c r="B583" s="7"/>
       <c r="C583" s="7"/>
@@ -45414,7 +45431,7 @@
       <c r="Y583" s="5"/>
       <c r="Z583" s="5"/>
     </row>
-    <row r="584" spans="1:26" ht="16.5" customHeight="1">
+    <row r="584" spans="1:26" ht="16.5">
       <c r="A584" s="7"/>
       <c r="B584" s="7"/>
       <c r="C584" s="7"/>
@@ -45442,7 +45459,7 @@
       <c r="Y584" s="5"/>
       <c r="Z584" s="5"/>
     </row>
-    <row r="585" spans="1:26" ht="16.5" customHeight="1">
+    <row r="585" spans="1:26" ht="16.5">
       <c r="A585" s="7"/>
       <c r="B585" s="7"/>
       <c r="C585" s="7"/>
@@ -45470,7 +45487,7 @@
       <c r="Y585" s="5"/>
       <c r="Z585" s="5"/>
     </row>
-    <row r="586" spans="1:26" ht="16.5" customHeight="1">
+    <row r="586" spans="1:26" ht="16.5">
       <c r="A586" s="7"/>
       <c r="B586" s="7"/>
       <c r="C586" s="7"/>
@@ -45498,7 +45515,7 @@
       <c r="Y586" s="5"/>
       <c r="Z586" s="5"/>
     </row>
-    <row r="587" spans="1:26" ht="16.5" customHeight="1">
+    <row r="587" spans="1:26" ht="16.5">
       <c r="A587" s="7"/>
       <c r="B587" s="7"/>
       <c r="C587" s="7"/>
@@ -45526,7 +45543,7 @@
       <c r="Y587" s="5"/>
       <c r="Z587" s="5"/>
     </row>
-    <row r="588" spans="1:26" ht="16.5" customHeight="1">
+    <row r="588" spans="1:26" ht="16.5">
       <c r="A588" s="7"/>
       <c r="B588" s="7"/>
       <c r="C588" s="7"/>
@@ -45554,7 +45571,7 @@
       <c r="Y588" s="5"/>
       <c r="Z588" s="5"/>
     </row>
-    <row r="589" spans="1:26" ht="16.5" customHeight="1">
+    <row r="589" spans="1:26" ht="16.5">
       <c r="A589" s="7"/>
       <c r="B589" s="7"/>
       <c r="C589" s="7"/>
@@ -45582,7 +45599,7 @@
       <c r="Y589" s="5"/>
       <c r="Z589" s="5"/>
     </row>
-    <row r="590" spans="1:26" ht="16.5" customHeight="1">
+    <row r="590" spans="1:26" ht="16.5">
       <c r="A590" s="7"/>
       <c r="B590" s="7"/>
       <c r="C590" s="7"/>
@@ -45610,7 +45627,7 @@
       <c r="Y590" s="5"/>
       <c r="Z590" s="5"/>
     </row>
-    <row r="591" spans="1:26" ht="16.5" customHeight="1">
+    <row r="591" spans="1:26" ht="16.5">
       <c r="A591" s="7"/>
       <c r="B591" s="7"/>
       <c r="C591" s="7"/>
@@ -45638,7 +45655,7 @@
       <c r="Y591" s="5"/>
       <c r="Z591" s="5"/>
     </row>
-    <row r="592" spans="1:26" ht="16.5" customHeight="1">
+    <row r="592" spans="1:26" ht="16.5">
       <c r="A592" s="7"/>
       <c r="B592" s="7"/>
       <c r="C592" s="7"/>
@@ -45666,7 +45683,7 @@
       <c r="Y592" s="5"/>
       <c r="Z592" s="5"/>
     </row>
-    <row r="593" spans="1:26" ht="16.5" customHeight="1">
+    <row r="593" spans="1:26" ht="16.5">
       <c r="A593" s="7"/>
       <c r="B593" s="7"/>
       <c r="C593" s="7"/>
@@ -45694,7 +45711,7 @@
       <c r="Y593" s="5"/>
       <c r="Z593" s="5"/>
     </row>
-    <row r="594" spans="1:26" ht="16.5" customHeight="1">
+    <row r="594" spans="1:26" ht="16.5">
       <c r="A594" s="7"/>
       <c r="B594" s="7"/>
       <c r="C594" s="7"/>
@@ -45722,7 +45739,7 @@
       <c r="Y594" s="5"/>
       <c r="Z594" s="5"/>
     </row>
-    <row r="595" spans="1:26" ht="16.5" customHeight="1">
+    <row r="595" spans="1:26" ht="16.5">
       <c r="A595" s="7"/>
       <c r="B595" s="7"/>
       <c r="C595" s="7"/>
@@ -45750,7 +45767,7 @@
       <c r="Y595" s="5"/>
       <c r="Z595" s="5"/>
     </row>
-    <row r="596" spans="1:26" ht="16.5" customHeight="1">
+    <row r="596" spans="1:26" ht="16.5">
       <c r="A596" s="7"/>
       <c r="B596" s="7"/>
       <c r="C596" s="7"/>
@@ -45778,7 +45795,7 @@
       <c r="Y596" s="5"/>
       <c r="Z596" s="5"/>
     </row>
-    <row r="597" spans="1:26" ht="16.5" customHeight="1">
+    <row r="597" spans="1:26" ht="16.5">
       <c r="A597" s="7"/>
       <c r="B597" s="7"/>
       <c r="C597" s="7"/>
@@ -45806,7 +45823,7 @@
       <c r="Y597" s="5"/>
       <c r="Z597" s="5"/>
     </row>
-    <row r="598" spans="1:26" ht="16.5" customHeight="1">
+    <row r="598" spans="1:26" ht="16.5">
       <c r="A598" s="7"/>
       <c r="B598" s="7"/>
       <c r="C598" s="7"/>
@@ -45834,7 +45851,7 @@
       <c r="Y598" s="5"/>
       <c r="Z598" s="5"/>
     </row>
-    <row r="599" spans="1:26" ht="16.5" customHeight="1">
+    <row r="599" spans="1:26" ht="16.5">
       <c r="A599" s="7"/>
       <c r="B599" s="7"/>
       <c r="C599" s="7"/>
@@ -45862,7 +45879,7 @@
       <c r="Y599" s="5"/>
       <c r="Z599" s="5"/>
     </row>
-    <row r="600" spans="1:26" ht="16.5" customHeight="1">
+    <row r="600" spans="1:26" ht="16.5">
       <c r="A600" s="7"/>
       <c r="B600" s="7"/>
       <c r="C600" s="7"/>
@@ -45890,7 +45907,7 @@
       <c r="Y600" s="5"/>
       <c r="Z600" s="5"/>
     </row>
-    <row r="601" spans="1:26" ht="16.5" customHeight="1">
+    <row r="601" spans="1:26" ht="16.5">
       <c r="A601" s="7"/>
       <c r="B601" s="7"/>
       <c r="C601" s="7"/>
@@ -45918,7 +45935,7 @@
       <c r="Y601" s="5"/>
       <c r="Z601" s="5"/>
     </row>
-    <row r="602" spans="1:26" ht="16.5" customHeight="1">
+    <row r="602" spans="1:26" ht="16.5">
       <c r="A602" s="7"/>
       <c r="B602" s="7"/>
       <c r="C602" s="7"/>
@@ -45946,7 +45963,7 @@
       <c r="Y602" s="5"/>
       <c r="Z602" s="5"/>
     </row>
-    <row r="603" spans="1:26" ht="16.5" customHeight="1">
+    <row r="603" spans="1:26" ht="16.5">
       <c r="A603" s="7"/>
       <c r="B603" s="7"/>
       <c r="C603" s="7"/>
@@ -45974,7 +45991,7 @@
       <c r="Y603" s="5"/>
       <c r="Z603" s="5"/>
     </row>
-    <row r="604" spans="1:26" ht="16.5" customHeight="1">
+    <row r="604" spans="1:26" ht="16.5">
       <c r="A604" s="7"/>
       <c r="B604" s="7"/>
       <c r="C604" s="7"/>
@@ -46002,7 +46019,7 @@
       <c r="Y604" s="5"/>
       <c r="Z604" s="5"/>
     </row>
-    <row r="605" spans="1:26" ht="16.5" customHeight="1">
+    <row r="605" spans="1:26" ht="16.5">
       <c r="A605" s="7"/>
       <c r="B605" s="7"/>
       <c r="C605" s="7"/>
@@ -46030,7 +46047,7 @@
       <c r="Y605" s="5"/>
       <c r="Z605" s="5"/>
     </row>
-    <row r="606" spans="1:26" ht="16.5" customHeight="1">
+    <row r="606" spans="1:26" ht="16.5">
       <c r="A606" s="7"/>
       <c r="B606" s="7"/>
       <c r="C606" s="7"/>
@@ -46058,7 +46075,7 @@
       <c r="Y606" s="5"/>
       <c r="Z606" s="5"/>
     </row>
-    <row r="607" spans="1:26" ht="16.5" customHeight="1">
+    <row r="607" spans="1:26" ht="16.5">
       <c r="A607" s="7"/>
       <c r="B607" s="7"/>
       <c r="C607" s="7"/>
@@ -46086,7 +46103,7 @@
       <c r="Y607" s="5"/>
       <c r="Z607" s="5"/>
     </row>
-    <row r="608" spans="1:26" ht="16.5" customHeight="1">
+    <row r="608" spans="1:26" ht="16.5">
       <c r="A608" s="7"/>
       <c r="B608" s="7"/>
       <c r="C608" s="7"/>
@@ -46114,7 +46131,7 @@
       <c r="Y608" s="5"/>
       <c r="Z608" s="5"/>
     </row>
-    <row r="609" spans="1:26" ht="16.5" customHeight="1">
+    <row r="609" spans="1:26" ht="16.5">
       <c r="A609" s="7"/>
       <c r="B609" s="7"/>
       <c r="C609" s="7"/>
@@ -46142,7 +46159,7 @@
       <c r="Y609" s="5"/>
       <c r="Z609" s="5"/>
     </row>
-    <row r="610" spans="1:26" ht="16.5" customHeight="1">
+    <row r="610" spans="1:26" ht="16.5">
       <c r="A610" s="7"/>
       <c r="B610" s="7"/>
       <c r="C610" s="7"/>
@@ -46170,7 +46187,7 @@
       <c r="Y610" s="5"/>
       <c r="Z610" s="5"/>
     </row>
-    <row r="611" spans="1:26" ht="16.5" customHeight="1">
+    <row r="611" spans="1:26" ht="16.5">
       <c r="A611" s="7"/>
       <c r="B611" s="7"/>
       <c r="C611" s="7"/>
@@ -46198,7 +46215,7 @@
       <c r="Y611" s="5"/>
       <c r="Z611" s="5"/>
     </row>
-    <row r="612" spans="1:26" ht="16.5" customHeight="1">
+    <row r="612" spans="1:26" ht="16.5">
       <c r="A612" s="7"/>
       <c r="B612" s="7"/>
       <c r="C612" s="7"/>
@@ -46226,7 +46243,7 @@
       <c r="Y612" s="5"/>
       <c r="Z612" s="5"/>
     </row>
-    <row r="613" spans="1:26" ht="16.5" customHeight="1">
+    <row r="613" spans="1:26" ht="16.5">
       <c r="A613" s="7"/>
       <c r="B613" s="7"/>
       <c r="C613" s="7"/>
@@ -46254,7 +46271,7 @@
       <c r="Y613" s="5"/>
       <c r="Z613" s="5"/>
     </row>
-    <row r="614" spans="1:26" ht="16.5" customHeight="1">
+    <row r="614" spans="1:26" ht="16.5">
       <c r="A614" s="7"/>
       <c r="B614" s="7"/>
       <c r="C614" s="7"/>
@@ -46282,7 +46299,7 @@
       <c r="Y614" s="5"/>
       <c r="Z614" s="5"/>
     </row>
-    <row r="615" spans="1:26" ht="16.5" customHeight="1">
+    <row r="615" spans="1:26" ht="16.5">
       <c r="A615" s="7"/>
       <c r="B615" s="7"/>
       <c r="C615" s="7"/>
@@ -46310,7 +46327,7 @@
       <c r="Y615" s="5"/>
       <c r="Z615" s="5"/>
     </row>
-    <row r="616" spans="1:26" ht="16.5" customHeight="1">
+    <row r="616" spans="1:26" ht="16.5">
       <c r="A616" s="7"/>
       <c r="B616" s="7"/>
       <c r="C616" s="7"/>
@@ -46338,7 +46355,7 @@
       <c r="Y616" s="5"/>
       <c r="Z616" s="5"/>
     </row>
-    <row r="617" spans="1:26" ht="16.5" customHeight="1">
+    <row r="617" spans="1:26" ht="16.5">
       <c r="A617" s="7"/>
       <c r="B617" s="7"/>
       <c r="C617" s="7"/>
@@ -46366,7 +46383,7 @@
       <c r="Y617" s="5"/>
       <c r="Z617" s="5"/>
     </row>
-    <row r="618" spans="1:26" ht="16.5" customHeight="1">
+    <row r="618" spans="1:26" ht="16.5">
       <c r="A618" s="7"/>
       <c r="B618" s="7"/>
       <c r="C618" s="7"/>
@@ -46394,7 +46411,7 @@
       <c r="Y618" s="5"/>
       <c r="Z618" s="5"/>
     </row>
-    <row r="619" spans="1:26" ht="16.5" customHeight="1">
+    <row r="619" spans="1:26" ht="16.5">
       <c r="A619" s="7"/>
       <c r="B619" s="7"/>
       <c r="C619" s="7"/>
@@ -46422,7 +46439,7 @@
       <c r="Y619" s="5"/>
       <c r="Z619" s="5"/>
     </row>
-    <row r="620" spans="1:26" ht="16.5" customHeight="1">
+    <row r="620" spans="1:26" ht="16.5">
       <c r="A620" s="7"/>
       <c r="B620" s="7"/>
       <c r="C620" s="7"/>
@@ -46450,7 +46467,7 @@
       <c r="Y620" s="5"/>
       <c r="Z620" s="5"/>
     </row>
-    <row r="621" spans="1:26" ht="16.5" customHeight="1">
+    <row r="621" spans="1:26" ht="16.5">
       <c r="A621" s="7"/>
       <c r="B621" s="7"/>
       <c r="C621" s="7"/>
@@ -46478,7 +46495,7 @@
       <c r="Y621" s="5"/>
       <c r="Z621" s="5"/>
     </row>
-    <row r="622" spans="1:26" ht="16.5" customHeight="1">
+    <row r="622" spans="1:26" ht="16.5">
       <c r="A622" s="7"/>
       <c r="B622" s="7"/>
       <c r="C622" s="7"/>
@@ -46506,7 +46523,7 @@
       <c r="Y622" s="5"/>
       <c r="Z622" s="5"/>
     </row>
-    <row r="623" spans="1:26" ht="16.5" customHeight="1">
+    <row r="623" spans="1:26" ht="16.5">
       <c r="A623" s="7"/>
       <c r="B623" s="7"/>
       <c r="C623" s="7"/>
@@ -46534,7 +46551,7 @@
       <c r="Y623" s="5"/>
       <c r="Z623" s="5"/>
     </row>
-    <row r="624" spans="1:26" ht="16.5" customHeight="1">
+    <row r="624" spans="1:26" ht="16.5">
       <c r="A624" s="7"/>
       <c r="B624" s="7"/>
       <c r="C624" s="7"/>
@@ -46562,7 +46579,7 @@
       <c r="Y624" s="5"/>
       <c r="Z624" s="5"/>
     </row>
-    <row r="625" spans="1:26" ht="16.5" customHeight="1">
+    <row r="625" spans="1:26" ht="16.5">
       <c r="A625" s="7"/>
       <c r="B625" s="7"/>
       <c r="C625" s="7"/>
@@ -46590,7 +46607,7 @@
       <c r="Y625" s="5"/>
       <c r="Z625" s="5"/>
     </row>
-    <row r="626" spans="1:26" ht="16.5" customHeight="1">
+    <row r="626" spans="1:26" ht="16.5">
       <c r="A626" s="7"/>
       <c r="B626" s="7"/>
       <c r="C626" s="7"/>
@@ -46618,7 +46635,7 @@
       <c r="Y626" s="5"/>
       <c r="Z626" s="5"/>
     </row>
-    <row r="627" spans="1:26" ht="16.5" customHeight="1">
+    <row r="627" spans="1:26" ht="16.5">
       <c r="A627" s="7"/>
       <c r="B627" s="7"/>
       <c r="C627" s="7"/>
@@ -46646,7 +46663,7 @@
       <c r="Y627" s="5"/>
       <c r="Z627" s="5"/>
     </row>
-    <row r="628" spans="1:26" ht="16.5" customHeight="1">
+    <row r="628" spans="1:26" ht="16.5">
       <c r="A628" s="7"/>
       <c r="B628" s="7"/>
       <c r="C628" s="7"/>
@@ -46674,7 +46691,7 @@
       <c r="Y628" s="5"/>
       <c r="Z628" s="5"/>
     </row>
-    <row r="629" spans="1:26" ht="16.5" customHeight="1">
+    <row r="629" spans="1:26" ht="16.5">
       <c r="A629" s="7"/>
       <c r="B629" s="7"/>
       <c r="C629" s="7"/>
@@ -46702,7 +46719,7 @@
       <c r="Y629" s="5"/>
       <c r="Z629" s="5"/>
     </row>
-    <row r="630" spans="1:26" ht="16.5" customHeight="1">
+    <row r="630" spans="1:26" ht="16.5">
       <c r="A630" s="7"/>
       <c r="B630" s="7"/>
       <c r="C630" s="7"/>
@@ -46730,7 +46747,7 @@
       <c r="Y630" s="5"/>
       <c r="Z630" s="5"/>
     </row>
-    <row r="631" spans="1:26" ht="16.5" customHeight="1">
+    <row r="631" spans="1:26" ht="16.5">
       <c r="A631" s="7"/>
       <c r="B631" s="7"/>
       <c r="C631" s="7"/>
@@ -46758,7 +46775,7 @@
       <c r="Y631" s="5"/>
       <c r="Z631" s="5"/>
     </row>
-    <row r="632" spans="1:26" ht="16.5" customHeight="1">
+    <row r="632" spans="1:26" ht="16.5">
       <c r="A632" s="7"/>
       <c r="B632" s="7"/>
       <c r="C632" s="7"/>
@@ -46786,7 +46803,7 @@
       <c r="Y632" s="5"/>
       <c r="Z632" s="5"/>
     </row>
-    <row r="633" spans="1:26" ht="16.5" customHeight="1">
+    <row r="633" spans="1:26" ht="16.5">
       <c r="A633" s="7"/>
       <c r="B633" s="7"/>
       <c r="C633" s="7"/>
@@ -46814,7 +46831,7 @@
       <c r="Y633" s="5"/>
       <c r="Z633" s="5"/>
     </row>
-    <row r="634" spans="1:26" ht="16.5" customHeight="1">
+    <row r="634" spans="1:26" ht="16.5">
       <c r="A634" s="7"/>
       <c r="B634" s="7"/>
       <c r="C634" s="7"/>
@@ -46842,7 +46859,7 @@
       <c r="Y634" s="5"/>
       <c r="Z634" s="5"/>
     </row>
-    <row r="635" spans="1:26" ht="16.5" customHeight="1">
+    <row r="635" spans="1:26" ht="16.5">
       <c r="A635" s="7"/>
       <c r="B635" s="7"/>
       <c r="C635" s="7"/>
@@ -46870,7 +46887,7 @@
       <c r="Y635" s="5"/>
       <c r="Z635" s="5"/>
     </row>
-    <row r="636" spans="1:26" ht="16.5" customHeight="1">
+    <row r="636" spans="1:26" ht="16.5">
       <c r="A636" s="7"/>
       <c r="B636" s="7"/>
       <c r="C636" s="7"/>
@@ -46898,7 +46915,7 @@
       <c r="Y636" s="5"/>
       <c r="Z636" s="5"/>
     </row>
-    <row r="637" spans="1:26" ht="16.5" customHeight="1">
+    <row r="637" spans="1:26" ht="16.5">
       <c r="A637" s="7"/>
       <c r="B637" s="7"/>
       <c r="C637" s="7"/>
@@ -46926,7 +46943,7 @@
       <c r="Y637" s="5"/>
       <c r="Z637" s="5"/>
     </row>
-    <row r="638" spans="1:26" ht="16.5" customHeight="1">
+    <row r="638" spans="1:26" ht="16.5">
       <c r="A638" s="7"/>
       <c r="B638" s="7"/>
       <c r="C638" s="7"/>
@@ -46954,7 +46971,7 @@
       <c r="Y638" s="5"/>
       <c r="Z638" s="5"/>
     </row>
-    <row r="639" spans="1:26" ht="16.5" customHeight="1">
+    <row r="639" spans="1:26" ht="16.5">
       <c r="A639" s="7"/>
       <c r="B639" s="7"/>
       <c r="C639" s="7"/>
@@ -46982,7 +46999,7 @@
       <c r="Y639" s="5"/>
       <c r="Z639" s="5"/>
     </row>
-    <row r="640" spans="1:26" ht="16.5" customHeight="1">
+    <row r="640" spans="1:26" ht="16.5">
       <c r="A640" s="7"/>
       <c r="B640" s="7"/>
       <c r="C640" s="7"/>
@@ -47010,7 +47027,7 @@
       <c r="Y640" s="5"/>
       <c r="Z640" s="5"/>
     </row>
-    <row r="641" spans="1:26" ht="16.5" customHeight="1">
+    <row r="641" spans="1:26" ht="16.5">
       <c r="A641" s="7"/>
       <c r="B641" s="7"/>
       <c r="C641" s="7"/>
@@ -47038,7 +47055,7 @@
       <c r="Y641" s="5"/>
       <c r="Z641" s="5"/>
     </row>
-    <row r="642" spans="1:26" ht="16.5" customHeight="1">
+    <row r="642" spans="1:26" ht="16.5">
       <c r="A642" s="7"/>
       <c r="B642" s="7"/>
       <c r="C642" s="7"/>
@@ -47066,7 +47083,7 @@
       <c r="Y642" s="5"/>
       <c r="Z642" s="5"/>
     </row>
-    <row r="643" spans="1:26" ht="16.5" customHeight="1">
+    <row r="643" spans="1:26" ht="16.5">
       <c r="A643" s="7"/>
       <c r="B643" s="7"/>
       <c r="C643" s="7"/>
@@ -47094,7 +47111,7 @@
       <c r="Y643" s="5"/>
       <c r="Z643" s="5"/>
     </row>
-    <row r="644" spans="1:26" ht="16.5" customHeight="1">
+    <row r="644" spans="1:26" ht="16.5">
       <c r="A644" s="7"/>
       <c r="B644" s="7"/>
       <c r="C644" s="7"/>
@@ -47122,7 +47139,7 @@
       <c r="Y644" s="5"/>
       <c r="Z644" s="5"/>
     </row>
-    <row r="645" spans="1:26" ht="16.5" customHeight="1">
+    <row r="645" spans="1:26" ht="16.5">
       <c r="A645" s="7"/>
       <c r="B645" s="7"/>
       <c r="C645" s="7"/>
@@ -47150,7 +47167,7 @@
       <c r="Y645" s="5"/>
       <c r="Z645" s="5"/>
     </row>
-    <row r="646" spans="1:26" ht="16.5" customHeight="1">
+    <row r="646" spans="1:26" ht="16.5">
       <c r="A646" s="7"/>
       <c r="B646" s="7"/>
       <c r="C646" s="7"/>
@@ -47178,7 +47195,7 @@
       <c r="Y646" s="5"/>
       <c r="Z646" s="5"/>
     </row>
-    <row r="647" spans="1:26" ht="16.5" customHeight="1">
+    <row r="647" spans="1:26" ht="16.5">
       <c r="A647" s="7"/>
       <c r="B647" s="7"/>
       <c r="C647" s="7"/>
@@ -47206,7 +47223,7 @@
       <c r="Y647" s="5"/>
       <c r="Z647" s="5"/>
     </row>
-    <row r="648" spans="1:26" ht="16.5" customHeight="1">
+    <row r="648" spans="1:26" ht="16.5">
       <c r="A648" s="7"/>
       <c r="B648" s="7"/>
       <c r="C648" s="7"/>
@@ -47234,7 +47251,7 @@
       <c r="Y648" s="5"/>
       <c r="Z648" s="5"/>
     </row>
-    <row r="649" spans="1:26" ht="16.5" customHeight="1">
+    <row r="649" spans="1:26" ht="16.5">
       <c r="A649" s="7"/>
       <c r="B649" s="7"/>
       <c r="C649" s="7"/>
@@ -47262,7 +47279,7 @@
       <c r="Y649" s="5"/>
       <c r="Z649" s="5"/>
     </row>
-    <row r="650" spans="1:26" ht="16.5" customHeight="1">
+    <row r="650" spans="1:26" ht="16.5">
       <c r="A650" s="7"/>
       <c r="B650" s="7"/>
       <c r="C650" s="7"/>
@@ -47290,7 +47307,7 @@
       <c r="Y650" s="5"/>
       <c r="Z650" s="5"/>
     </row>
-    <row r="651" spans="1:26" ht="16.5" customHeight="1">
+    <row r="651" spans="1:26" ht="16.5">
       <c r="A651" s="7"/>
       <c r="B651" s="7"/>
       <c r="C651" s="7"/>
@@ -47318,7 +47335,7 @@
       <c r="Y651" s="5"/>
       <c r="Z651" s="5"/>
     </row>
-    <row r="652" spans="1:26" ht="16.5" customHeight="1">
+    <row r="652" spans="1:26" ht="16.5">
       <c r="A652" s="7"/>
       <c r="B652" s="7"/>
       <c r="C652" s="7"/>
@@ -47346,7 +47363,7 @@
       <c r="Y652" s="5"/>
       <c r="Z652" s="5"/>
     </row>
-    <row r="653" spans="1:26" ht="16.5" customHeight="1">
+    <row r="653" spans="1:26" ht="16.5">
       <c r="A653" s="7"/>
       <c r="B653" s="7"/>
       <c r="C653" s="7"/>
@@ -47374,7 +47391,7 @@
       <c r="Y653" s="5"/>
       <c r="Z653" s="5"/>
     </row>
-    <row r="654" spans="1:26" ht="16.5" customHeight="1">
+    <row r="654" spans="1:26" ht="16.5">
       <c r="A654" s="7"/>
       <c r="B654" s="7"/>
       <c r="C654" s="7"/>
@@ -47402,7 +47419,7 @@
       <c r="Y654" s="5"/>
       <c r="Z654" s="5"/>
     </row>
-    <row r="655" spans="1:26" ht="16.5" customHeight="1">
+    <row r="655" spans="1:26" ht="16.5">
       <c r="A655" s="7"/>
       <c r="B655" s="7"/>
       <c r="C655" s="7"/>
@@ -47430,7 +47447,7 @@
       <c r="Y655" s="5"/>
       <c r="Z655" s="5"/>
     </row>
-    <row r="656" spans="1:26" ht="16.5" customHeight="1">
+    <row r="656" spans="1:26" ht="16.5">
       <c r="A656" s="7"/>
       <c r="B656" s="7"/>
       <c r="C656" s="7"/>
@@ -47458,7 +47475,7 @@
       <c r="Y656" s="5"/>
       <c r="Z656" s="5"/>
     </row>
-    <row r="657" spans="1:26" ht="16.5" customHeight="1">
+    <row r="657" spans="1:26" ht="16.5">
       <c r="A657" s="7"/>
       <c r="B657" s="7"/>
       <c r="C657" s="7"/>
@@ -47486,7 +47503,7 @@
       <c r="Y657" s="5"/>
       <c r="Z657" s="5"/>
     </row>
-    <row r="658" spans="1:26" ht="16.5" customHeight="1">
+    <row r="658" spans="1:26" ht="16.5">
       <c r="A658" s="7"/>
       <c r="B658" s="7"/>
       <c r="C658" s="7"/>
@@ -47514,7 +47531,7 @@
       <c r="Y658" s="5"/>
       <c r="Z658" s="5"/>
     </row>
-    <row r="659" spans="1:26" ht="16.5" customHeight="1">
+    <row r="659" spans="1:26" ht="16.5">
       <c r="A659" s="7"/>
       <c r="B659" s="7"/>
       <c r="C659" s="7"/>
@@ -47542,7 +47559,7 @@
       <c r="Y659" s="5"/>
       <c r="Z659" s="5"/>
     </row>
-    <row r="660" spans="1:26" ht="16.5" customHeight="1">
+    <row r="660" spans="1:26" ht="16.5">
       <c r="A660" s="7"/>
       <c r="B660" s="7"/>
       <c r="C660" s="7"/>
@@ -47570,7 +47587,7 @@
       <c r="Y660" s="5"/>
       <c r="Z660" s="5"/>
     </row>
-    <row r="661" spans="1:26" ht="16.5" customHeight="1">
+    <row r="661" spans="1:26" ht="16.5">
       <c r="A661" s="7"/>
       <c r="B661" s="7"/>
       <c r="C661" s="7"/>
@@ -47598,7 +47615,7 @@
       <c r="Y661" s="5"/>
       <c r="Z661" s="5"/>
     </row>
-    <row r="662" spans="1:26" ht="16.5" customHeight="1">
+    <row r="662" spans="1:26" ht="16.5">
       <c r="A662" s="7"/>
       <c r="B662" s="7"/>
       <c r="C662" s="7"/>
@@ -47626,7 +47643,7 @@
       <c r="Y662" s="5"/>
       <c r="Z662" s="5"/>
     </row>
-    <row r="663" spans="1:26" ht="16.5" customHeight="1">
+    <row r="663" spans="1:26" ht="16.5">
       <c r="A663" s="7"/>
       <c r="B663" s="7"/>
       <c r="C663" s="7"/>
@@ -47654,7 +47671,7 @@
       <c r="Y663" s="5"/>
       <c r="Z663" s="5"/>
     </row>
-    <row r="664" spans="1:26" ht="16.5" customHeight="1">
+    <row r="664" spans="1:26" ht="16.5">
       <c r="A664" s="7"/>
       <c r="B664" s="7"/>
       <c r="C664" s="7"/>
@@ -47682,7 +47699,7 @@
       <c r="Y664" s="5"/>
       <c r="Z664" s="5"/>
     </row>
-    <row r="665" spans="1:26" ht="16.5" customHeight="1">
+    <row r="665" spans="1:26" ht="16.5">
       <c r="A665" s="7"/>
       <c r="B665" s="7"/>
       <c r="C665" s="7"/>
@@ -47710,7 +47727,7 @@
       <c r="Y665" s="5"/>
       <c r="Z665" s="5"/>
     </row>
-    <row r="666" spans="1:26" ht="16.5" customHeight="1">
+    <row r="666" spans="1:26" ht="16.5">
       <c r="A666" s="7"/>
       <c r="B666" s="7"/>
       <c r="C666" s="7"/>
@@ -47738,7 +47755,7 @@
       <c r="Y666" s="5"/>
       <c r="Z666" s="5"/>
     </row>
-    <row r="667" spans="1:26" ht="16.5" customHeight="1">
+    <row r="667" spans="1:26" ht="16.5">
       <c r="A667" s="7"/>
       <c r="B667" s="7"/>
       <c r="C667" s="7"/>
@@ -47766,7 +47783,7 @@
       <c r="Y667" s="5"/>
       <c r="Z667" s="5"/>
     </row>
-    <row r="668" spans="1:26" ht="16.5" customHeight="1">
+    <row r="668" spans="1:26" ht="16.5">
       <c r="A668" s="7"/>
       <c r="B668" s="7"/>
       <c r="C668" s="7"/>
@@ -47794,7 +47811,7 @@
       <c r="Y668" s="5"/>
       <c r="Z668" s="5"/>
     </row>
-    <row r="669" spans="1:26" ht="16.5" customHeight="1">
+    <row r="669" spans="1:26" ht="16.5">
       <c r="A669" s="7"/>
       <c r="B669" s="7"/>
       <c r="C669" s="7"/>
@@ -47822,7 +47839,7 @@
       <c r="Y669" s="5"/>
       <c r="Z669" s="5"/>
     </row>
-    <row r="670" spans="1:26" ht="16.5" customHeight="1">
+    <row r="670" spans="1:26" ht="16.5">
       <c r="A670" s="7"/>
       <c r="B670" s="7"/>
       <c r="C670" s="7"/>
@@ -47850,7 +47867,7 @@
       <c r="Y670" s="5"/>
       <c r="Z670" s="5"/>
     </row>
-    <row r="671" spans="1:26" ht="16.5" customHeight="1">
+    <row r="671" spans="1:26" ht="16.5">
       <c r="A671" s="7"/>
       <c r="B671" s="7"/>
       <c r="C671" s="7"/>
@@ -47878,7 +47895,7 @@
       <c r="Y671" s="5"/>
       <c r="Z671" s="5"/>
     </row>
-    <row r="672" spans="1:26" ht="16.5" customHeight="1">
+    <row r="672" spans="1:26" ht="16.5">
       <c r="A672" s="7"/>
       <c r="B672" s="7"/>
       <c r="C672" s="7"/>
@@ -47906,7 +47923,7 @@
       <c r="Y672" s="5"/>
       <c r="Z672" s="5"/>
     </row>
-    <row r="673" spans="1:26" ht="16.5" customHeight="1">
+    <row r="673" spans="1:26" ht="16.5">
       <c r="A673" s="7"/>
       <c r="B673" s="7"/>
       <c r="C673" s="7"/>
@@ -47934,7 +47951,7 @@
       <c r="Y673" s="5"/>
       <c r="Z673" s="5"/>
     </row>
-    <row r="674" spans="1:26" ht="16.5" customHeight="1">
+    <row r="674" spans="1:26" ht="16.5">
       <c r="A674" s="7"/>
       <c r="B674" s="7"/>
       <c r="C674" s="7"/>
@@ -47962,7 +47979,7 @@
       <c r="Y674" s="5"/>
       <c r="Z674" s="5"/>
     </row>
-    <row r="675" spans="1:26" ht="16.5" customHeight="1">
+    <row r="675" spans="1:26" ht="16.5">
       <c r="A675" s="7"/>
       <c r="B675" s="7"/>
       <c r="C675" s="7"/>
@@ -47990,7 +48007,7 @@
       <c r="Y675" s="5"/>
       <c r="Z675" s="5"/>
     </row>
-    <row r="676" spans="1:26" ht="16.5" customHeight="1">
+    <row r="676" spans="1:26" ht="16.5">
       <c r="A676" s="7"/>
       <c r="B676" s="7"/>
       <c r="C676" s="7"/>
@@ -48018,7 +48035,7 @@
       <c r="Y676" s="5"/>
       <c r="Z676" s="5"/>
     </row>
-    <row r="677" spans="1:26" ht="16.5" customHeight="1">
+    <row r="677" spans="1:26" ht="16.5">
       <c r="A677" s="7"/>
       <c r="B677" s="7"/>
       <c r="C677" s="7"/>
@@ -48046,7 +48063,7 @@
       <c r="Y677" s="5"/>
       <c r="Z677" s="5"/>
     </row>
-    <row r="678" spans="1:26" ht="16.5" customHeight="1">
+    <row r="678" spans="1:26" ht="16.5">
       <c r="A678" s="7"/>
       <c r="B678" s="7"/>
       <c r="C678" s="7"/>
@@ -48074,7 +48091,7 @@
       <c r="Y678" s="5"/>
       <c r="Z678" s="5"/>
     </row>
-    <row r="679" spans="1:26" ht="16.5" customHeight="1">
+    <row r="679" spans="1:26" ht="16.5">
       <c r="A679" s="7"/>
       <c r="B679" s="7"/>
       <c r="C679" s="7"/>
@@ -48102,7 +48119,7 @@
       <c r="Y679" s="5"/>
       <c r="Z679" s="5"/>
     </row>
-    <row r="680" spans="1:26" ht="16.5" customHeight="1">
+    <row r="680" spans="1:26" ht="16.5">
       <c r="A680" s="7"/>
       <c r="B680" s="7"/>
       <c r="C680" s="7"/>
@@ -48130,7 +48147,7 @@
       <c r="Y680" s="5"/>
       <c r="Z680" s="5"/>
     </row>
-    <row r="681" spans="1:26" ht="16.5" customHeight="1">
+    <row r="681" spans="1:26" ht="16.5">
       <c r="A681" s="7"/>
       <c r="B681" s="7"/>
       <c r="C681" s="7"/>
@@ -48158,7 +48175,7 @@
       <c r="Y681" s="5"/>
       <c r="Z681" s="5"/>
     </row>
-    <row r="682" spans="1:26" ht="16.5" customHeight="1">
+    <row r="682" spans="1:26" ht="16.5">
       <c r="A682" s="7"/>
       <c r="B682" s="7"/>
       <c r="C682" s="7"/>
@@ -48186,7 +48203,7 @@
       <c r="Y682" s="5"/>
       <c r="Z682" s="5"/>
     </row>
-    <row r="683" spans="1:26" ht="16.5" customHeight="1">
+    <row r="683" spans="1:26" ht="16.5">
       <c r="A683" s="7"/>
       <c r="B683" s="7"/>
       <c r="C683" s="7"/>
@@ -48214,7 +48231,7 @@
       <c r="Y683" s="5"/>
       <c r="Z683" s="5"/>
     </row>
-    <row r="684" spans="1:26" ht="16.5" customHeight="1">
+    <row r="684" spans="1:26" ht="16.5">
       <c r="A684" s="7"/>
       <c r="B684" s="7"/>
       <c r="C684" s="7"/>
@@ -48242,7 +48259,7 @@
       <c r="Y684" s="5"/>
       <c r="Z684" s="5"/>
     </row>
-    <row r="685" spans="1:26" ht="16.5" customHeight="1">
+    <row r="685" spans="1:26" ht="16.5">
       <c r="A685" s="7"/>
       <c r="B685" s="7"/>
       <c r="C685" s="7"/>
@@ -48270,7 +48287,7 @@
       <c r="Y685" s="5"/>
       <c r="Z685" s="5"/>
     </row>
-    <row r="686" spans="1:26" ht="16.5" customHeight="1">
+    <row r="686" spans="1:26" ht="16.5">
       <c r="A686" s="7"/>
       <c r="B686" s="7"/>
       <c r="C686" s="7"/>
@@ -48298,7 +48315,7 @@
       <c r="Y686" s="5"/>
       <c r="Z686" s="5"/>
     </row>
-    <row r="687" spans="1:26" ht="16.5" customHeight="1">
+    <row r="687" spans="1:26" ht="16.5">
       <c r="A687" s="7"/>
       <c r="B687" s="7"/>
       <c r="C687" s="7"/>
@@ -48326,7 +48343,7 @@
       <c r="Y687" s="5"/>
       <c r="Z687" s="5"/>
     </row>
-    <row r="688" spans="1:26" ht="16.5" customHeight="1">
+    <row r="688" spans="1:26" ht="16.5">
       <c r="A688" s="7"/>
       <c r="B688" s="7"/>
       <c r="C688" s="7"/>
@@ -48354,7 +48371,7 @@
       <c r="Y688" s="5"/>
       <c r="Z688" s="5"/>
     </row>
-    <row r="689" spans="1:26" ht="16.5" customHeight="1">
+    <row r="689" spans="1:26" ht="16.5">
       <c r="A689" s="7"/>
       <c r="B689" s="7"/>
       <c r="C689" s="7"/>
@@ -48382,7 +48399,7 @@
       <c r="Y689" s="5"/>
       <c r="Z689" s="5"/>
     </row>
-    <row r="690" spans="1:26" ht="16.5" customHeight="1">
+    <row r="690" spans="1:26" ht="16.5">
       <c r="A690" s="7"/>
       <c r="B690" s="7"/>
       <c r="C690" s="7"/>
@@ -48410,7 +48427,7 @@
       <c r="Y690" s="5"/>
       <c r="Z690" s="5"/>
     </row>
-    <row r="691" spans="1:26" ht="16.5" customHeight="1">
+    <row r="691" spans="1:26" ht="16.5">
       <c r="A691" s="7"/>
       <c r="B691" s="7"/>
       <c r="C691" s="7"/>
@@ -48438,7 +48455,7 @@
       <c r="Y691" s="5"/>
       <c r="Z691" s="5"/>
     </row>
-    <row r="692" spans="1:26" ht="16.5" customHeight="1">
+    <row r="692" spans="1:26" ht="16.5">
       <c r="A692" s="7"/>
       <c r="B692" s="7"/>
       <c r="C692" s="7"/>
@@ -48466,7 +48483,7 @@
       <c r="Y692" s="5"/>
       <c r="Z692" s="5"/>
     </row>
-    <row r="693" spans="1:26" ht="16.5" customHeight="1">
+    <row r="693" spans="1:26" ht="16.5">
       <c r="A693" s="7"/>
       <c r="B693" s="7"/>
       <c r="C693" s="7"/>
@@ -48494,7 +48511,7 @@
       <c r="Y693" s="5"/>
       <c r="Z693" s="5"/>
     </row>
-    <row r="694" spans="1:26" ht="16.5" customHeight="1">
+    <row r="694" spans="1:26" ht="16.5">
       <c r="A694" s="7"/>
       <c r="B694" s="7"/>
       <c r="C694" s="7"/>
@@ -48522,7 +48539,7 @@
       <c r="Y694" s="5"/>
       <c r="Z694" s="5"/>
     </row>
-    <row r="695" spans="1:26" ht="16.5" customHeight="1">
+    <row r="695" spans="1:26" ht="16.5">
       <c r="A695" s="7"/>
       <c r="B695" s="7"/>
       <c r="C695" s="7"/>
@@ -48550,7 +48567,7 @@
       <c r="Y695" s="5"/>
       <c r="Z695" s="5"/>
     </row>
-    <row r="696" spans="1:26" ht="16.5" customHeight="1">
+    <row r="696" spans="1:26" ht="16.5">
       <c r="A696" s="7"/>
       <c r="B696" s="7"/>
       <c r="C696" s="7"/>
@@ -48578,7 +48595,7 @@
       <c r="Y696" s="5"/>
       <c r="Z696" s="5"/>
     </row>
-    <row r="697" spans="1:26" ht="16.5" customHeight="1">
+    <row r="697" spans="1:26" ht="16.5">
       <c r="A697" s="7"/>
       <c r="B697" s="7"/>
       <c r="C697" s="7"/>
@@ -48606,7 +48623,7 @@
       <c r="Y697" s="5"/>
       <c r="Z697" s="5"/>
     </row>
-    <row r="698" spans="1:26" ht="16.5" customHeight="1">
+    <row r="698" spans="1:26" ht="16.5">
       <c r="A698" s="7"/>
       <c r="B698" s="7"/>
       <c r="C698" s="7"/>
@@ -48634,7 +48651,7 @@
       <c r="Y698" s="5"/>
       <c r="Z698" s="5"/>
     </row>
-    <row r="699" spans="1:26" ht="16.5" customHeight="1">
+    <row r="699" spans="1:26" ht="16.5">
       <c r="A699" s="7"/>
       <c r="B699" s="7"/>
       <c r="C699" s="7"/>
@@ -48662,7 +48679,7 @@
       <c r="Y699" s="5"/>
       <c r="Z699" s="5"/>
     </row>
-    <row r="700" spans="1:26" ht="16.5" customHeight="1">
+    <row r="700" spans="1:26" ht="16.5">
       <c r="A700" s="7"/>
       <c r="B700" s="7"/>
       <c r="C700" s="7"/>
@@ -48690,7 +48707,7 @@
       <c r="Y700" s="5"/>
       <c r="Z700" s="5"/>
     </row>
-    <row r="701" spans="1:26" ht="16.5" customHeight="1">
+    <row r="701" spans="1:26" ht="16.5">
       <c r="A701" s="7"/>
       <c r="B701" s="7"/>
       <c r="C701" s="7"/>
@@ -48718,7 +48735,7 @@
       <c r="Y701" s="5"/>
       <c r="Z701" s="5"/>
     </row>
-    <row r="702" spans="1:26" ht="16.5" customHeight="1">
+    <row r="702" spans="1:26" ht="16.5">
       <c r="A702" s="7"/>
       <c r="B702" s="7"/>
       <c r="C702" s="7"/>
@@ -48746,7 +48763,7 @@
       <c r="Y702" s="5"/>
       <c r="Z702" s="5"/>
     </row>
-    <row r="703" spans="1:26" ht="16.5" customHeight="1">
+    <row r="703" spans="1:26" ht="16.5">
       <c r="A703" s="7"/>
       <c r="B703" s="7"/>
       <c r="C703" s="7"/>
@@ -48774,7 +48791,7 @@
       <c r="Y703" s="5"/>
       <c r="Z703" s="5"/>
     </row>
-    <row r="704" spans="1:26" ht="16.5" customHeight="1">
+    <row r="704" spans="1:26" ht="16.5">
       <c r="A704" s="7"/>
       <c r="B704" s="7"/>
       <c r="C704" s="7"/>
@@ -48802,7 +48819,7 @@
       <c r="Y704" s="5"/>
       <c r="Z704" s="5"/>
     </row>
-    <row r="705" spans="1:26" ht="16.5" customHeight="1">
+    <row r="705" spans="1:26" ht="16.5">
       <c r="A705" s="7"/>
       <c r="B705" s="7"/>
       <c r="C705" s="7"/>
@@ -48830,7 +48847,7 @@
       <c r="Y705" s="5"/>
       <c r="Z705" s="5"/>
     </row>
-    <row r="706" spans="1:26" ht="16.5" customHeight="1">
+    <row r="706" spans="1:26" ht="16.5">
       <c r="A706" s="7"/>
       <c r="B706" s="7"/>
       <c r="C706" s="7"/>
@@ -48858,7 +48875,7 @@
       <c r="Y706" s="5"/>
       <c r="Z706" s="5"/>
     </row>
-    <row r="707" spans="1:26" ht="16.5" customHeight="1">
+    <row r="707" spans="1:26" ht="16.5">
       <c r="A707" s="7"/>
       <c r="B707" s="7"/>
       <c r="C707" s="7"/>
@@ -48886,7 +48903,7 @@
       <c r="Y707" s="5"/>
       <c r="Z707" s="5"/>
     </row>
-    <row r="708" spans="1:26" ht="16.5" customHeight="1">
+    <row r="708" spans="1:26" ht="16.5">
       <c r="A708" s="7"/>
       <c r="B708" s="7"/>
       <c r="C708" s="7"/>
@@ -48914,7 +48931,7 @@
       <c r="Y708" s="5"/>
       <c r="Z708" s="5"/>
     </row>
-    <row r="709" spans="1:26" ht="16.5" customHeight="1">
+    <row r="709" spans="1:26" ht="16.5">
       <c r="A709" s="7"/>
       <c r="B709" s="7"/>
       <c r="C709" s="7"/>
@@ -48942,7 +48959,7 @@
       <c r="Y709" s="5"/>
       <c r="Z709" s="5"/>
     </row>
-    <row r="710" spans="1:26" ht="16.5" customHeight="1">
+    <row r="710" spans="1:26" ht="16.5">
       <c r="A710" s="7"/>
       <c r="B710" s="7"/>
       <c r="C710" s="7"/>
@@ -48970,7 +48987,7 @@
       <c r="Y710" s="5"/>
       <c r="Z710" s="5"/>
     </row>
-    <row r="711" spans="1:26" ht="16.5" customHeight="1">
+    <row r="711" spans="1:26" ht="16.5">
       <c r="A711" s="7"/>
       <c r="B711" s="7"/>
       <c r="C711" s="7"/>
@@ -48998,7 +49015,7 @@
       <c r="Y711" s="5"/>
       <c r="Z711" s="5"/>
     </row>
-    <row r="712" spans="1:26" ht="16.5" customHeight="1">
+    <row r="712" spans="1:26" ht="16.5">
       <c r="A712" s="7"/>
       <c r="B712" s="7"/>
       <c r="C712" s="7"/>
@@ -49026,7 +49043,7 @@
       <c r="Y712" s="5"/>
       <c r="Z712" s="5"/>
     </row>
-    <row r="713" spans="1:26" ht="16.5" customHeight="1">
+    <row r="713" spans="1:26" ht="16.5">
       <c r="A713" s="7"/>
       <c r="B713" s="7"/>
       <c r="C713" s="7"/>
@@ -49054,7 +49071,7 @@
       <c r="Y713" s="5"/>
       <c r="Z713" s="5"/>
     </row>
-    <row r="714" spans="1:26" ht="16.5" customHeight="1">
+    <row r="714" spans="1:26" ht="16.5">
       <c r="A714" s="7"/>
       <c r="B714" s="7"/>
       <c r="C714" s="7"/>
@@ -49082,7 +49099,7 @@
       <c r="Y714" s="5"/>
       <c r="Z714" s="5"/>
     </row>
-    <row r="715" spans="1:26" ht="16.5" customHeight="1">
+    <row r="715" spans="1:26" ht="16.5">
       <c r="A715" s="7"/>
       <c r="B715" s="7"/>
       <c r="C715" s="7"/>
@@ -49110,7 +49127,7 @@
       <c r="Y715" s="5"/>
       <c r="Z715" s="5"/>
     </row>
-    <row r="716" spans="1:26" ht="16.5" customHeight="1">
+    <row r="716" spans="1:26" ht="16.5">
       <c r="A716" s="7"/>
       <c r="B716" s="7"/>
       <c r="C716" s="7"/>
@@ -49138,7 +49155,7 @@
       <c r="Y716" s="5"/>
       <c r="Z716" s="5"/>
     </row>
-    <row r="717" spans="1:26" ht="16.5" customHeight="1">
+    <row r="717" spans="1:26" ht="16.5">
       <c r="A717" s="7"/>
       <c r="B717" s="7"/>
       <c r="C717" s="7"/>
@@ -49166,7 +49183,7 @@
       <c r="Y717" s="5"/>
       <c r="Z717" s="5"/>
     </row>
-    <row r="718" spans="1:26" ht="16.5" customHeight="1">
+    <row r="718" spans="1:26" ht="16.5">
       <c r="A718" s="7"/>
       <c r="B718" s="7"/>
       <c r="C718" s="7"/>
@@ -49194,7 +49211,7 @@
       <c r="Y718" s="5"/>
       <c r="Z718" s="5"/>
     </row>
-    <row r="719" spans="1:26" ht="16.5" customHeight="1">
+    <row r="719" spans="1:26" ht="16.5">
       <c r="A719" s="7"/>
       <c r="B719" s="7"/>
       <c r="C719" s="7"/>
@@ -49222,7 +49239,7 @@
       <c r="Y719" s="5"/>
       <c r="Z719" s="5"/>
     </row>
-    <row r="720" spans="1:26" ht="16.5" customHeight="1">
+    <row r="720" spans="1:26" ht="16.5">
       <c r="A720" s="7"/>
       <c r="B720" s="7"/>
       <c r="C720" s="7"/>
@@ -49250,7 +49267,7 @@
       <c r="Y720" s="5"/>
       <c r="Z720" s="5"/>
     </row>
-    <row r="721" spans="1:26" ht="16.5" customHeight="1">
+    <row r="721" spans="1:26" ht="16.5">
       <c r="A721" s="7"/>
       <c r="B721" s="7"/>
       <c r="C721" s="7"/>
@@ -49278,7 +49295,7 @@
       <c r="Y721" s="5"/>
       <c r="Z721" s="5"/>
     </row>
-    <row r="722" spans="1:26" ht="16.5" customHeight="1">
+    <row r="722" spans="1:26" ht="16.5">
       <c r="A722" s="7"/>
       <c r="B722" s="7"/>
       <c r="C722" s="7"/>
@@ -49306,7 +49323,7 @@
       <c r="Y722" s="5"/>
       <c r="Z722" s="5"/>
     </row>
-    <row r="723" spans="1:26" ht="16.5" customHeight="1">
+    <row r="723" spans="1:26" ht="16.5">
       <c r="A723" s="7"/>
       <c r="B723" s="7"/>
       <c r="C723" s="7"/>
@@ -49334,7 +49351,7 @@
       <c r="Y723" s="5"/>
       <c r="Z723" s="5"/>
     </row>
-    <row r="724" spans="1:26" ht="16.5" customHeight="1">
+    <row r="724" spans="1:26" ht="16.5">
       <c r="A724" s="7"/>
       <c r="B724" s="7"/>
       <c r="C724" s="7"/>
@@ -49362,7 +49379,7 @@
       <c r="Y724" s="5"/>
       <c r="Z724" s="5"/>
     </row>
-    <row r="725" spans="1:26" ht="16.5" customHeight="1">
+    <row r="725" spans="1:26" ht="16.5">
       <c r="A725" s="7"/>
       <c r="B725" s="7"/>
       <c r="C725" s="7"/>
@@ -49390,7 +49407,7 @@
       <c r="Y725" s="5"/>
       <c r="Z725" s="5"/>
     </row>
-    <row r="726" spans="1:26" ht="16.5" customHeight="1">
+    <row r="726" spans="1:26" ht="16.5">
       <c r="A726" s="7"/>
       <c r="B726" s="7"/>
       <c r="C726" s="7"/>
@@ -49418,7 +49435,7 @@
       <c r="Y726" s="5"/>
       <c r="Z726" s="5"/>
     </row>
-    <row r="727" spans="1:26" ht="16.5" customHeight="1">
+    <row r="727" spans="1:26" ht="16.5">
       <c r="A727" s="7"/>
       <c r="B727" s="7"/>
       <c r="C727" s="7"/>
@@ -49446,7 +49463,7 @@
       <c r="Y727" s="5"/>
       <c r="Z727" s="5"/>
     </row>
-    <row r="728" spans="1:26" ht="16.5" customHeight="1">
+    <row r="728" spans="1:26" ht="16.5">
       <c r="A728" s="7"/>
       <c r="B728" s="7"/>
       <c r="C728" s="7"/>
@@ -49474,7 +49491,7 @@
       <c r="Y728" s="5"/>
       <c r="Z728" s="5"/>
     </row>
-    <row r="729" spans="1:26" ht="16.5" customHeight="1">
+    <row r="729" spans="1:26" ht="16.5">
       <c r="A729" s="7"/>
       <c r="B729" s="7"/>
       <c r="C729" s="7"/>
@@ -49502,7 +49519,7 @@
       <c r="Y729" s="5"/>
       <c r="Z729" s="5"/>
     </row>
-    <row r="730" spans="1:26" ht="16.5" customHeight="1">
+    <row r="730" spans="1:26" ht="16.5">
       <c r="A730" s="7"/>
       <c r="B730" s="7"/>
       <c r="C730" s="7"/>
@@ -49530,7 +49547,7 @@
       <c r="Y730" s="5"/>
       <c r="Z730" s="5"/>
     </row>
-    <row r="731" spans="1:26" ht="16.5" customHeight="1">
+    <row r="731" spans="1:26" ht="16.5">
       <c r="A731" s="7"/>
       <c r="B731" s="7"/>
       <c r="C731" s="7"/>
@@ -49558,7 +49575,7 @@
       <c r="Y731" s="5"/>
       <c r="Z731" s="5"/>
     </row>
-    <row r="732" spans="1:26" ht="16.5" customHeight="1">
+    <row r="732" spans="1:26" ht="16.5">
       <c r="A732" s="7"/>
       <c r="B732" s="7"/>
       <c r="C732" s="7"/>
@@ -49586,7 +49603,7 @@
       <c r="Y732" s="5"/>
       <c r="Z732" s="5"/>
     </row>
-    <row r="733" spans="1:26" ht="16.5" customHeight="1">
+    <row r="733" spans="1:26" ht="16.5">
       <c r="A733" s="7"/>
       <c r="B733" s="7"/>
       <c r="C733" s="7"/>
@@ -49614,7 +49631,7 @@
       <c r="Y733" s="5"/>
       <c r="Z733" s="5"/>
     </row>
-    <row r="734" spans="1:26" ht="16.5" customHeight="1">
+    <row r="734" spans="1:26" ht="16.5">
       <c r="A734" s="7"/>
       <c r="B734" s="7"/>
       <c r="C734" s="7"/>
@@ -49642,7 +49659,7 @@
       <c r="Y734" s="5"/>
       <c r="Z734" s="5"/>
     </row>
-    <row r="735" spans="1:26" ht="16.5" customHeight="1">
+    <row r="735" spans="1:26" ht="16.5">
       <c r="A735" s="7"/>
       <c r="B735" s="7"/>
       <c r="C735" s="7"/>
@@ -49670,7 +49687,7 @@
       <c r="Y735" s="5"/>
       <c r="Z735" s="5"/>
     </row>
-    <row r="736" spans="1:26" ht="16.5" customHeight="1">
+    <row r="736" spans="1:26" ht="16.5">
       <c r="A736" s="7"/>
       <c r="B736" s="7"/>
       <c r="C736" s="7"/>
@@ -49698,7 +49715,7 @@
       <c r="Y736" s="5"/>
       <c r="Z736" s="5"/>
     </row>
-    <row r="737" spans="1:26" ht="16.5" customHeight="1">
+    <row r="737" spans="1:26" ht="16.5">
       <c r="A737" s="7"/>
       <c r="B737" s="7"/>
       <c r="C737" s="7"/>
@@ -49726,7 +49743,7 @@
       <c r="Y737" s="5"/>
       <c r="Z737" s="5"/>
     </row>
-    <row r="738" spans="1:26" ht="16.5" customHeight="1">
+    <row r="738" spans="1:26" ht="16.5">
       <c r="A738" s="7"/>
       <c r="B738" s="7"/>
       <c r="C738" s="7"/>
@@ -49754,7 +49771,7 @@
       <c r="Y738" s="5"/>
       <c r="Z738" s="5"/>
     </row>
-    <row r="739" spans="1:26" ht="16.5" customHeight="1">
+    <row r="739" spans="1:26" ht="16.5">
       <c r="A739" s="7"/>
       <c r="B739" s="7"/>
       <c r="C739" s="7"/>
@@ -49782,7 +49799,7 @@
       <c r="Y739" s="5"/>
       <c r="Z739" s="5"/>
     </row>
-    <row r="740" spans="1:26" ht="16.5" customHeight="1">
+    <row r="740" spans="1:26" ht="16.5">
       <c r="A740" s="7"/>
       <c r="B740" s="7"/>
       <c r="C740" s="7"/>
@@ -49810,7 +49827,7 @@
       <c r="Y740" s="5"/>
       <c r="Z740" s="5"/>
     </row>
-    <row r="741" spans="1:26" ht="16.5" customHeight="1">
+    <row r="741" spans="1:26" ht="16.5">
       <c r="A741" s="7"/>
       <c r="B741" s="7"/>
       <c r="C741" s="7"/>
@@ -49838,7 +49855,7 @@
       <c r="Y741" s="5"/>
       <c r="Z741" s="5"/>
     </row>
-    <row r="742" spans="1:26" ht="16.5" customHeight="1">
+    <row r="742" spans="1:26" ht="16.5">
       <c r="A742" s="7"/>
       <c r="B742" s="7"/>
       <c r="C742" s="7"/>
@@ -49866,7 +49883,7 @@
       <c r="Y742" s="5"/>
       <c r="Z742" s="5"/>
     </row>
-    <row r="743" spans="1:26" ht="16.5" customHeight="1">
+    <row r="743" spans="1:26" ht="16.5">
       <c r="A743" s="7"/>
       <c r="B743" s="7"/>
       <c r="C743" s="7"/>
@@ -49894,7 +49911,7 @@
       <c r="Y743" s="5"/>
       <c r="Z743" s="5"/>
     </row>
-    <row r="744" spans="1:26" ht="16.5" customHeight="1">
+    <row r="744" spans="1:26" ht="16.5">
       <c r="A744" s="7"/>
       <c r="B744" s="7"/>
       <c r="C744" s="7"/>
@@ -49922,7 +49939,7 @@
       <c r="Y744" s="5"/>
       <c r="Z744" s="5"/>
     </row>
-    <row r="745" spans="1:26" ht="16.5" customHeight="1">
+    <row r="745" spans="1:26" ht="16.5">
       <c r="A745" s="7"/>
       <c r="B745" s="7"/>
       <c r="C745" s="7"/>
@@ -49950,7 +49967,7 @@
       <c r="Y745" s="5"/>
       <c r="Z745" s="5"/>
     </row>
-    <row r="746" spans="1:26" ht="16.5" customHeight="1">
+    <row r="746" spans="1:26" ht="16.5">
       <c r="A746" s="7"/>
       <c r="B746" s="7"/>
       <c r="C746" s="7"/>
@@ -49978,7 +49995,7 @@
       <c r="Y746" s="5"/>
       <c r="Z746" s="5"/>
     </row>
-    <row r="747" spans="1:26" ht="16.5" customHeight="1">
+    <row r="747" spans="1:26" ht="16.5">
       <c r="A747" s="7"/>
       <c r="B747" s="7"/>
       <c r="C747" s="7"/>
@@ -50006,7 +50023,7 @@
       <c r="Y747" s="5"/>
       <c r="Z747" s="5"/>
     </row>
-    <row r="748" spans="1:26" ht="16.5" customHeight="1">
+    <row r="748" spans="1:26" ht="16.5">
       <c r="A748" s="7"/>
       <c r="B748" s="7"/>
       <c r="C748" s="7"/>
@@ -50034,7 +50051,7 @@
       <c r="Y748" s="5"/>
       <c r="Z748" s="5"/>
     </row>
-    <row r="749" spans="1:26" ht="16.5" customHeight="1">
+    <row r="749" spans="1:26" ht="16.5">
       <c r="A749" s="7"/>
       <c r="B749" s="7"/>
       <c r="C749" s="7"/>
@@ -50062,7 +50079,7 @@
       <c r="Y749" s="5"/>
       <c r="Z749" s="5"/>
     </row>
-    <row r="750" spans="1:26" ht="16.5" customHeight="1">
+    <row r="750" spans="1:26" ht="16.5">
       <c r="A750" s="7"/>
       <c r="B750" s="7"/>
       <c r="C750" s="7"/>
@@ -50090,7 +50107,7 @@
       <c r="Y750" s="5"/>
       <c r="Z750" s="5"/>
     </row>
-    <row r="751" spans="1:26" ht="16.5" customHeight="1">
+    <row r="751" spans="1:26" ht="16.5">
       <c r="A751" s="7"/>
       <c r="B751" s="7"/>
       <c r="C751" s="7"/>
@@ -50118,7 +50135,7 @@
       <c r="Y751" s="5"/>
       <c r="Z751" s="5"/>
     </row>
-    <row r="752" spans="1:26" ht="16.5" customHeight="1">
+    <row r="752" spans="1:26" ht="16.5">
       <c r="A752" s="7"/>
       <c r="B752" s="7"/>
       <c r="C752" s="7"/>
@@ -50146,7 +50163,7 @@
       <c r="Y752" s="5"/>
       <c r="Z752" s="5"/>
     </row>
-    <row r="753" spans="1:26" ht="16.5" customHeight="1">
+    <row r="753" spans="1:26" ht="16.5">
       <c r="A753" s="7"/>
       <c r="B753" s="7"/>
       <c r="C753" s="7"/>
@@ -50174,7 +50191,7 @@
       <c r="Y753" s="5"/>
       <c r="Z753" s="5"/>
     </row>
-    <row r="754" spans="1:26" ht="16.5" customHeight="1">
+    <row r="754" spans="1:26" ht="16.5">
       <c r="A754" s="7"/>
       <c r="B754" s="7"/>
       <c r="C754" s="7"/>
@@ -50202,7 +50219,7 @@
       <c r="Y754" s="5"/>
       <c r="Z754" s="5"/>
     </row>
-    <row r="755" spans="1:26" ht="16.5" customHeight="1">
+    <row r="755" spans="1:26" ht="16.5">
       <c r="A755" s="7"/>
       <c r="B755" s="7"/>
       <c r="C755" s="7"/>
@@ -50230,7 +50247,7 @@
       <c r="Y755" s="5"/>
       <c r="Z755" s="5"/>
     </row>
-    <row r="756" spans="1:26" ht="16.5" customHeight="1">
+    <row r="756" spans="1:26" ht="16.5">
       <c r="A756" s="7"/>
       <c r="B756" s="7"/>
       <c r="C756" s="7"/>
@@ -50258,7 +50275,7 @@
       <c r="Y756" s="5"/>
       <c r="Z756" s="5"/>
     </row>
-    <row r="757" spans="1:26" ht="16.5" customHeight="1">
+    <row r="757" spans="1:26" ht="16.5">
       <c r="A757" s="7"/>
       <c r="B757" s="7"/>
       <c r="C757" s="7"/>
@@ -50286,7 +50303,7 @@
       <c r="Y757" s="5"/>
       <c r="Z757" s="5"/>
     </row>
-    <row r="758" spans="1:26" ht="16.5" customHeight="1">
+    <row r="758" spans="1:26" ht="16.5">
       <c r="A758" s="7"/>
       <c r="B758" s="7"/>
       <c r="C758" s="7"/>
@@ -50314,7 +50331,7 @@
       <c r="Y758" s="5"/>
       <c r="Z758" s="5"/>
     </row>
-    <row r="759" spans="1:26" ht="16.5" customHeight="1">
+    <row r="759" spans="1:26" ht="16.5">
       <c r="A759" s="7"/>
       <c r="B759" s="7"/>
       <c r="C759" s="7"/>
@@ -50342,7 +50359,7 @@
       <c r="Y759" s="5"/>
       <c r="Z759" s="5"/>
     </row>
-    <row r="760" spans="1:26" ht="16.5" customHeight="1">
+    <row r="760" spans="1:26" ht="16.5">
       <c r="A760" s="7"/>
       <c r="B760" s="7"/>
       <c r="C760" s="7"/>
@@ -50370,7 +50387,7 @@
       <c r="Y760" s="5"/>
       <c r="Z760" s="5"/>
     </row>
-    <row r="761" spans="1:26" ht="16.5" customHeight="1">
+    <row r="761" spans="1:26" ht="16.5">
       <c r="A761" s="7"/>
       <c r="B761" s="7"/>
       <c r="C761" s="7"/>
@@ -50398,7 +50415,7 @@
       <c r="Y761" s="5"/>
       <c r="Z761" s="5"/>
     </row>
-    <row r="762" spans="1:26" ht="16.5" customHeight="1">
+    <row r="762" spans="1:26" ht="16.5">
       <c r="A762" s="7"/>
       <c r="B762" s="7"/>
       <c r="C762" s="7"/>
@@ -50426,7 +50443,7 @@
       <c r="Y762" s="5"/>
       <c r="Z762" s="5"/>
     </row>
-    <row r="763" spans="1:26" ht="16.5" customHeight="1">
+    <row r="763" spans="1:26" ht="16.5">
       <c r="A763" s="7"/>
       <c r="B763" s="7"/>
       <c r="C763" s="7"/>
@@ -50454,7 +50471,7 @@
       <c r="Y763" s="5"/>
       <c r="Z763" s="5"/>
     </row>
-    <row r="764" spans="1:26" ht="16.5" customHeight="1">
+    <row r="764" spans="1:26" ht="16.5">
       <c r="A764" s="7"/>
       <c r="B764" s="7"/>
       <c r="C764" s="7"/>
@@ -50482,7 +50499,7 @@
       <c r="Y764" s="5"/>
       <c r="Z764" s="5"/>
     </row>
-    <row r="765" spans="1:26" ht="16.5" customHeight="1">
+    <row r="765" spans="1:26" ht="16.5">
       <c r="A765" s="7"/>
       <c r="B765" s="7"/>
       <c r="C765" s="7"/>
@@ -50510,7 +50527,7 @@
       <c r="Y765" s="5"/>
       <c r="Z765" s="5"/>
     </row>
-    <row r="766" spans="1:26" ht="16.5" customHeight="1">
+    <row r="766" spans="1:26" ht="16.5">
       <c r="A766" s="7"/>
       <c r="B766" s="7"/>
       <c r="C766" s="7"/>
@@ -50538,7 +50555,7 @@
       <c r="Y766" s="5"/>
       <c r="Z766" s="5"/>
     </row>
-    <row r="767" spans="1:26" ht="16.5" customHeight="1">
+    <row r="767" spans="1:26" ht="16.5">
       <c r="A767" s="7"/>
       <c r="B767" s="7"/>
       <c r="C767" s="7"/>
@@ -50566,7 +50583,7 @@
       <c r="Y767" s="5"/>
       <c r="Z767" s="5"/>
     </row>
-    <row r="768" spans="1:26" ht="16.5" customHeight="1">
+    <row r="768" spans="1:26" ht="16.5">
       <c r="A768" s="7"/>
       <c r="B768" s="7"/>
       <c r="C768" s="7"/>
@@ -50594,7 +50611,7 @@
       <c r="Y768" s="5"/>
       <c r="Z768" s="5"/>
     </row>
-    <row r="769" spans="1:26" ht="16.5" customHeight="1">
+    <row r="769" spans="1:26" ht="16.5">
       <c r="A769" s="7"/>
       <c r="B769" s="7"/>
       <c r="C769" s="7"/>
@@ -50622,7 +50639,7 @@
       <c r="Y769" s="5"/>
       <c r="Z769" s="5"/>
     </row>
-    <row r="770" spans="1:26" ht="16.5" customHeight="1">
+    <row r="770" spans="1:26" ht="16.5">
       <c r="A770" s="7"/>
       <c r="B770" s="7"/>
       <c r="C770" s="7"/>
@@ -50650,7 +50667,7 @@
       <c r="Y770" s="5"/>
       <c r="Z770" s="5"/>
     </row>
-    <row r="771" spans="1:26" ht="16.5" customHeight="1">
+    <row r="771" spans="1:26" ht="16.5">
       <c r="A771" s="7"/>
       <c r="B771" s="7"/>
       <c r="C771" s="7"/>
@@ -50678,7 +50695,7 @@
       <c r="Y771" s="5"/>
       <c r="Z771" s="5"/>
     </row>
-    <row r="772" spans="1:26" ht="16.5" customHeight="1">
+    <row r="772" spans="1:26" ht="16.5">
       <c r="A772" s="7"/>
       <c r="B772" s="7"/>
       <c r="C772" s="7"/>
@@ -50706,7 +50723,7 @@
       <c r="Y772" s="5"/>
       <c r="Z772" s="5"/>
     </row>
-    <row r="773" spans="1:26" ht="16.5" customHeight="1">
+    <row r="773" spans="1:26" ht="16.5">
       <c r="A773" s="7"/>
       <c r="B773" s="7"/>
       <c r="C773" s="7"/>
@@ -50734,7 +50751,7 @@
       <c r="Y773" s="5"/>
       <c r="Z773" s="5"/>
     </row>
-    <row r="774" spans="1:26" ht="16.5" customHeight="1">
+    <row r="774" spans="1:26" ht="16.5">
       <c r="A774" s="7"/>
       <c r="B774" s="7"/>
       <c r="C774" s="7"/>
@@ -50762,7 +50779,7 @@
       <c r="Y774" s="5"/>
       <c r="Z774" s="5"/>
     </row>
-    <row r="775" spans="1:26" ht="16.5" customHeight="1">
+    <row r="775" spans="1:26" ht="16.5">
       <c r="A775" s="7"/>
       <c r="B775" s="7"/>
       <c r="C775" s="7"/>
@@ -50790,7 +50807,7 @@
       <c r="Y775" s="5"/>
       <c r="Z775" s="5"/>
     </row>
-    <row r="776" spans="1:26" ht="16.5" customHeight="1">
+    <row r="776" spans="1:26" ht="16.5">
       <c r="A776" s="7"/>
       <c r="B776" s="7"/>
       <c r="C776" s="7"/>
@@ -50818,7 +50835,7 @@
       <c r="Y776" s="5"/>
       <c r="Z776" s="5"/>
     </row>
-    <row r="777" spans="1:26" ht="16.5" customHeight="1">
+    <row r="777" spans="1:26" ht="16.5">
       <c r="A777" s="7"/>
       <c r="B777" s="7"/>
       <c r="C777" s="7"/>
@@ -50846,7 +50863,7 @@
       <c r="Y777" s="5"/>
       <c r="Z777" s="5"/>
     </row>
-    <row r="778" spans="1:26" ht="16.5" customHeight="1">
+    <row r="778" spans="1:26" ht="16.5">
       <c r="A778" s="7"/>
       <c r="B778" s="7"/>
       <c r="C778" s="7"/>
@@ -50874,7 +50891,7 @@
       <c r="Y778" s="5"/>
       <c r="Z778" s="5"/>
     </row>
-    <row r="779" spans="1:26" ht="16.5" customHeight="1">
+    <row r="779" spans="1:26" ht="16.5">
       <c r="A779" s="7"/>
       <c r="B779" s="7"/>
       <c r="C779" s="7"/>
@@ -50902,7 +50919,7 @@
       <c r="Y779" s="5"/>
       <c r="Z779" s="5"/>
     </row>
-    <row r="780" spans="1:26" ht="16.5" customHeight="1">
+    <row r="780" spans="1:26" ht="16.5">
       <c r="A780" s="7"/>
       <c r="B780" s="7"/>
       <c r="C780" s="7"/>
@@ -50930,7 +50947,7 @@
       <c r="Y780" s="5"/>
       <c r="Z780" s="5"/>
     </row>
-    <row r="781" spans="1:26" ht="16.5" customHeight="1">
+    <row r="781" spans="1:26" ht="16.5">
       <c r="A781" s="7"/>
       <c r="B781" s="7"/>
       <c r="C781" s="7"/>
@@ -50958,7 +50975,7 @@
       <c r="Y781" s="5"/>
       <c r="Z781" s="5"/>
     </row>
-    <row r="782" spans="1:26" ht="16.5" customHeight="1">
+    <row r="782" spans="1:26" ht="16.5">
       <c r="A782" s="7"/>
       <c r="B782" s="7"/>
       <c r="C782" s="7"/>
@@ -50986,7 +51003,7 @@
       <c r="Y782" s="5"/>
       <c r="Z782" s="5"/>
     </row>
-    <row r="783" spans="1:26" ht="16.5" customHeight="1">
+    <row r="783" spans="1:26" ht="16.5">
       <c r="A783" s="7"/>
       <c r="B783" s="7"/>
       <c r="C783" s="7"/>
@@ -51014,7 +51031,7 @@
       <c r="Y783" s="5"/>
       <c r="Z783" s="5"/>
     </row>
-    <row r="784" spans="1:26" ht="16.5" customHeight="1">
+    <row r="784" spans="1:26" ht="16.5">
       <c r="A784" s="7"/>
       <c r="B784" s="7"/>
       <c r="C784" s="7"/>
@@ -51042,7 +51059,7 @@
       <c r="Y784" s="5"/>
       <c r="Z784" s="5"/>
     </row>
-    <row r="785" spans="1:26" ht="16.5" customHeight="1">
+    <row r="785" spans="1:26" ht="16.5">
       <c r="A785" s="7"/>
       <c r="B785" s="7"/>
       <c r="C785" s="7"/>
@@ -51070,7 +51087,7 @@
       <c r="Y785" s="5"/>
       <c r="Z785" s="5"/>
     </row>
-    <row r="786" spans="1:26" ht="16.5" customHeight="1">
+    <row r="786" spans="1:26" ht="16.5">
       <c r="A786" s="7"/>
       <c r="B786" s="7"/>
       <c r="C786" s="7"/>
@@ -51098,7 +51115,7 @@
       <c r="Y786" s="5"/>
       <c r="Z786" s="5"/>
     </row>
-    <row r="787" spans="1:26" ht="16.5" customHeight="1">
+    <row r="787" spans="1:26" ht="16.5">
       <c r="A787" s="7"/>
       <c r="B787" s="7"/>
       <c r="C787" s="7"/>
@@ -51126,7 +51143,7 @@
       <c r="Y787" s="5"/>
       <c r="Z787" s="5"/>
     </row>
-    <row r="788" spans="1:26" ht="16.5" customHeight="1">
+    <row r="788" spans="1:26" ht="16.5">
       <c r="A788" s="7"/>
       <c r="B788" s="7"/>
       <c r="C788" s="7"/>
@@ -51154,7 +51171,7 @@
       <c r="Y788" s="5"/>
       <c r="Z788" s="5"/>
     </row>
-    <row r="789" spans="1:26" ht="16.5" customHeight="1">
+    <row r="789" spans="1:26" ht="16.5">
       <c r="A789" s="7"/>
       <c r="B789" s="7"/>
       <c r="C789" s="7"/>
@@ -51182,7 +51199,7 @@
       <c r="Y789" s="5"/>
       <c r="Z789" s="5"/>
     </row>
-    <row r="790" spans="1:26" ht="16.5" customHeight="1">
+    <row r="790" spans="1:26" ht="16.5">
       <c r="A790" s="7"/>
       <c r="B790" s="7"/>
       <c r="C790" s="7"/>
@@ -51210,7 +51227,7 @@
       <c r="Y790" s="5"/>
       <c r="Z790" s="5"/>
     </row>
-    <row r="791" spans="1:26" ht="16.5" customHeight="1">
+    <row r="791" spans="1:26" ht="16.5">
       <c r="A791" s="7"/>
       <c r="B791" s="7"/>
       <c r="C791" s="7"/>
@@ -51238,7 +51255,7 @@
       <c r="Y791" s="5"/>
       <c r="Z791" s="5"/>
     </row>
-    <row r="792" spans="1:26" ht="16.5" customHeight="1">
+    <row r="792" spans="1:26" ht="16.5">
       <c r="A792" s="7"/>
       <c r="B792" s="7"/>
       <c r="C792" s="7"/>
@@ -51266,7 +51283,7 @@
       <c r="Y792" s="5"/>
       <c r="Z792" s="5"/>
     </row>
-    <row r="793" spans="1:26" ht="16.5" customHeight="1">
+    <row r="793" spans="1:26" ht="16.5">
       <c r="A793" s="7"/>
       <c r="B793" s="7"/>
       <c r="C793" s="7"/>
@@ -51294,7 +51311,7 @@
       <c r="Y793" s="5"/>
       <c r="Z793" s="5"/>
     </row>
-    <row r="794" spans="1:26" ht="16.5" customHeight="1">
+    <row r="794" spans="1:26" ht="16.5">
       <c r="A794" s="7"/>
       <c r="B794" s="7"/>
       <c r="C794" s="7"/>
@@ -51322,7 +51339,7 @@
       <c r="Y794" s="5"/>
       <c r="Z794" s="5"/>
     </row>
-    <row r="795" spans="1:26" ht="16.5" customHeight="1">
+    <row r="795" spans="1:26" ht="16.5">
       <c r="A795" s="7"/>
       <c r="B795" s="7"/>
       <c r="C795" s="7"/>
@@ -51350,7 +51367,7 @@
       <c r="Y795" s="5"/>
       <c r="Z795" s="5"/>
     </row>
-    <row r="796" spans="1:26" ht="16.5" customHeight="1">
+    <row r="796" spans="1:26" ht="16.5">
       <c r="A796" s="7"/>
       <c r="B796" s="7"/>
       <c r="C796" s="7"/>
@@ -51378,7 +51395,7 @@
       <c r="Y796" s="5"/>
       <c r="Z796" s="5"/>
     </row>
-    <row r="797" spans="1:26" ht="16.5" customHeight="1">
+    <row r="797" spans="1:26" ht="16.5">
       <c r="A797" s="7"/>
       <c r="B797" s="7"/>
       <c r="C797" s="7"/>
@@ -51406,7 +51423,7 @@
       <c r="Y797" s="5"/>
       <c r="Z797" s="5"/>
     </row>
-    <row r="798" spans="1:26" ht="16.5" customHeight="1">
+    <row r="798" spans="1:26" ht="16.5">
       <c r="A798" s="7"/>
       <c r="B798" s="7"/>
       <c r="C798" s="7"/>
@@ -51434,7 +51451,7 @@
       <c r="Y798" s="5"/>
       <c r="Z798" s="5"/>
     </row>
-    <row r="799" spans="1:26" ht="16.5" customHeight="1">
+    <row r="799" spans="1:26" ht="16.5">
       <c r="A799" s="7"/>
       <c r="B799" s="7"/>
       <c r="C799" s="7"/>
@@ -51462,7 +51479,7 @@
       <c r="Y799" s="5"/>
       <c r="Z799" s="5"/>
     </row>
-    <row r="800" spans="1:26" ht="16.5" customHeight="1">
+    <row r="800" spans="1:26" ht="16.5">
       <c r="A800" s="7"/>
       <c r="B800" s="7"/>
       <c r="C800" s="7"/>
@@ -51490,7 +51507,7 @@
       <c r="Y800" s="5"/>
       <c r="Z800" s="5"/>
     </row>
-    <row r="801" spans="1:26" ht="16.5" customHeight="1">
+    <row r="801" spans="1:26" ht="16.5">
       <c r="A801" s="7"/>
       <c r="B801" s="7"/>
       <c r="C801" s="7"/>
@@ -51518,7 +51535,7 @@
       <c r="Y801" s="5"/>
       <c r="Z801" s="5"/>
     </row>
-    <row r="802" spans="1:26" ht="16.5" customHeight="1">
+    <row r="802" spans="1:26" ht="16.5">
       <c r="A802" s="7"/>
       <c r="B802" s="7"/>
       <c r="C802" s="7"/>
@@ -51546,7 +51563,7 @@
       <c r="Y802" s="5"/>
       <c r="Z802" s="5"/>
     </row>
-    <row r="803" spans="1:26" ht="16.5" customHeight="1">
+    <row r="803" spans="1:26" ht="16.5">
       <c r="A803" s="7"/>
       <c r="B803" s="7"/>
       <c r="C803" s="7"/>
@@ -51574,7 +51591,7 @@
       <c r="Y803" s="5"/>
       <c r="Z803" s="5"/>
     </row>
-    <row r="804" spans="1:26" ht="16.5" customHeight="1">
+    <row r="804" spans="1:26" ht="16.5">
       <c r="A804" s="7"/>
       <c r="B804" s="7"/>
       <c r="C804" s="7"/>
@@ -51602,7 +51619,7 @@
       <c r="Y804" s="5"/>
       <c r="Z804" s="5"/>
     </row>
-    <row r="805" spans="1:26" ht="16.5" customHeight="1">
+    <row r="805" spans="1:26" ht="16.5">
       <c r="A805" s="7"/>
       <c r="B805" s="7"/>
       <c r="C805" s="7"/>
@@ -51630,7 +51647,7 @@
       <c r="Y805" s="5"/>
       <c r="Z805" s="5"/>
     </row>
-    <row r="806" spans="1:26" ht="16.5" customHeight="1">
+    <row r="806" spans="1:26" ht="16.5">
       <c r="A806" s="7"/>
       <c r="B806" s="7"/>
       <c r="C806" s="7"/>
@@ -51658,7 +51675,7 @@
       <c r="Y806" s="5"/>
       <c r="Z806" s="5"/>
     </row>
-    <row r="807" spans="1:26" ht="16.5" customHeight="1">
+    <row r="807" spans="1:26" ht="16.5">
       <c r="A807" s="7"/>
       <c r="B807" s="7"/>
       <c r="C807" s="7"/>
@@ -51686,7 +51703,7 @@
       <c r="Y807" s="5"/>
       <c r="Z807" s="5"/>
     </row>
-    <row r="808" spans="1:26" ht="16.5" customHeight="1">
+    <row r="808" spans="1:26" ht="16.5">
       <c r="A808" s="7"/>
       <c r="B808" s="7"/>
       <c r="C808" s="7"/>
@@ -51714,7 +51731,7 @@
       <c r="Y808" s="5"/>
       <c r="Z808" s="5"/>
     </row>
-    <row r="809" spans="1:26" ht="16.5" customHeight="1">
+    <row r="809" spans="1:26" ht="16.5">
       <c r="A809" s="7"/>
       <c r="B809" s="7"/>
       <c r="C809" s="7"/>
@@ -51742,7 +51759,7 @@
       <c r="Y809" s="5"/>
       <c r="Z809" s="5"/>
     </row>
-    <row r="810" spans="1:26" ht="16.5" customHeight="1">
+    <row r="810" spans="1:26" ht="16.5">
       <c r="A810" s="7"/>
       <c r="B810" s="7"/>
       <c r="C810" s="7"/>
@@ -51770,7 +51787,7 @@
       <c r="Y810" s="5"/>
       <c r="Z810" s="5"/>
     </row>
-    <row r="811" spans="1:26" ht="16.5" customHeight="1">
+    <row r="811" spans="1:26" ht="16.5">
       <c r="A811" s="7"/>
       <c r="B811" s="7"/>
       <c r="C811" s="7"/>
@@ -51798,7 +51815,7 @@
       <c r="Y811" s="5"/>
       <c r="Z811" s="5"/>
     </row>
-    <row r="812" spans="1:26" ht="16.5" customHeight="1">
+    <row r="812" spans="1:26" ht="16.5">
       <c r="A812" s="7"/>
       <c r="B812" s="7"/>
       <c r="C812" s="7"/>
@@ -51826,7 +51843,7 @@
       <c r="Y812" s="5"/>
       <c r="Z812" s="5"/>
     </row>
-    <row r="813" spans="1:26" ht="16.5" customHeight="1">
+    <row r="813" spans="1:26" ht="16.5">
       <c r="A813" s="7"/>
       <c r="B813" s="7"/>
       <c r="C813" s="7"/>
@@ -51854,7 +51871,7 @@
       <c r="Y813" s="5"/>
       <c r="Z813" s="5"/>
     </row>
-    <row r="814" spans="1:26" ht="16.5" customHeight="1">
+    <row r="814" spans="1:26" ht="16.5">
       <c r="A814" s="7"/>
       <c r="B814" s="7"/>
       <c r="C814" s="7"/>
@@ -51882,7 +51899,7 @@
       <c r="Y814" s="5"/>
       <c r="Z814" s="5"/>
     </row>
-    <row r="815" spans="1:26" ht="16.5" customHeight="1">
+    <row r="815" spans="1:26" ht="16.5">
       <c r="A815" s="7"/>
       <c r="B815" s="7"/>
       <c r="C815" s="7"/>
@@ -51910,7 +51927,7 @@
       <c r="Y815" s="5"/>
       <c r="Z815" s="5"/>
     </row>
-    <row r="816" spans="1:26" ht="16.5" customHeight="1">
+    <row r="816" spans="1:26" ht="16.5">
       <c r="A816" s="7"/>
       <c r="B816" s="7"/>
       <c r="C816" s="7"/>
@@ -51938,7 +51955,7 @@
       <c r="Y816" s="5"/>
       <c r="Z816" s="5"/>
     </row>
-    <row r="817" spans="1:26" ht="16.5" customHeight="1">
+    <row r="817" spans="1:26" ht="16.5">
       <c r="A817" s="7"/>
       <c r="B817" s="7"/>
       <c r="C817" s="7"/>
@@ -51966,7 +51983,7 @@
       <c r="Y817" s="5"/>
       <c r="Z817" s="5"/>
     </row>
-    <row r="818" spans="1:26" ht="16.5" customHeight="1">
+    <row r="818" spans="1:26" ht="16.5">
       <c r="A818" s="7"/>
       <c r="B818" s="7"/>
       <c r="C818" s="7"/>
@@ -51994,7 +52011,7 @@
       <c r="Y818" s="5"/>
       <c r="Z818" s="5"/>
     </row>
-    <row r="819" spans="1:26" ht="16.5" customHeight="1">
+    <row r="819" spans="1:26" ht="16.5">
       <c r="A819" s="7"/>
       <c r="B819" s="7"/>
       <c r="C819" s="7"/>
@@ -52022,7 +52039,7 @@
       <c r="Y819" s="5"/>
       <c r="Z819" s="5"/>
     </row>
-    <row r="820" spans="1:26" ht="16.5" customHeight="1">
+    <row r="820" spans="1:26" ht="16.5">
       <c r="A820" s="7"/>
       <c r="B820" s="7"/>
       <c r="C820" s="7"/>
@@ -52050,7 +52067,7 @@
       <c r="Y820" s="5"/>
       <c r="Z820" s="5"/>
     </row>
-    <row r="821" spans="1:26" ht="16.5" customHeight="1">
+    <row r="821" spans="1:26" ht="16.5">
       <c r="A821" s="7"/>
       <c r="B821" s="7"/>
       <c r="C821" s="7"/>
@@ -52078,7 +52095,7 @@
       <c r="Y821" s="5"/>
       <c r="Z821" s="5"/>
     </row>
-    <row r="822" spans="1:26" ht="16.5" customHeight="1">
+    <row r="822" spans="1:26" ht="16.5">
       <c r="A822" s="7"/>
       <c r="B822" s="7"/>
       <c r="C822" s="7"/>
@@ -52106,7 +52123,7 @@
       <c r="Y822" s="5"/>
       <c r="Z822" s="5"/>
     </row>
-    <row r="823" spans="1:26" ht="16.5" customHeight="1">
+    <row r="823" spans="1:26" ht="16.5">
       <c r="A823" s="7"/>
       <c r="B823" s="7"/>
       <c r="C823" s="7"/>
@@ -52134,7 +52151,7 @@
       <c r="Y823" s="5"/>
       <c r="Z823" s="5"/>
     </row>
-    <row r="824" spans="1:26" ht="16.5" customHeight="1">
+    <row r="824" spans="1:26" ht="16.5">
       <c r="A824" s="7"/>
       <c r="B824" s="7"/>
       <c r="C824" s="7"/>
@@ -52162,7 +52179,7 @@
       <c r="Y824" s="5"/>
       <c r="Z824" s="5"/>
     </row>
-    <row r="825" spans="1:26" ht="16.5" customHeight="1">
+    <row r="825" spans="1:26" ht="16.5">
       <c r="A825" s="7"/>
       <c r="B825" s="7"/>
       <c r="C825" s="7"/>
@@ -52190,7 +52207,7 @@
       <c r="Y825" s="5"/>
       <c r="Z825" s="5"/>
     </row>
-    <row r="826" spans="1:26" ht="16.5" customHeight="1">
+    <row r="826" spans="1:26" ht="16.5">
       <c r="A826" s="7"/>
       <c r="B826" s="7"/>
       <c r="C826" s="7"/>
@@ -52218,7 +52235,7 @@
       <c r="Y826" s="5"/>
       <c r="Z826" s="5"/>
     </row>
-    <row r="827" spans="1:26" ht="16.5" customHeight="1">
+    <row r="827" spans="1:26" ht="16.5">
       <c r="A827" s="7"/>
       <c r="B827" s="7"/>
       <c r="C827" s="7"/>
@@ -52246,7 +52263,7 @@
       <c r="Y827" s="5"/>
       <c r="Z827" s="5"/>
     </row>
-    <row r="828" spans="1:26" ht="16.5" customHeight="1">
+    <row r="828" spans="1:26" ht="16.5">
       <c r="A828" s="7"/>
       <c r="B828" s="7"/>
       <c r="C828" s="7"/>
@@ -52274,7 +52291,7 @@
       <c r="Y828" s="5"/>
       <c r="Z828" s="5"/>
     </row>
-    <row r="829" spans="1:26" ht="16.5" customHeight="1">
+    <row r="829" spans="1:26" ht="16.5">
       <c r="A829" s="7"/>
       <c r="B829" s="7"/>
       <c r="C829" s="7"/>
@@ -52302,7 +52319,7 @@
       <c r="Y829" s="5"/>
       <c r="Z829" s="5"/>
     </row>
-    <row r="830" spans="1:26" ht="16.5" customHeight="1">
+    <row r="830" spans="1:26" ht="16.5">
       <c r="A830" s="7"/>
       <c r="B830" s="7"/>
       <c r="C830" s="7"/>
@@ -52330,7 +52347,7 @@
       <c r="Y830" s="5"/>
       <c r="Z830" s="5"/>
     </row>
-    <row r="831" spans="1:26" ht="16.5" customHeight="1">
+    <row r="831" spans="1:26" ht="16.5">
       <c r="A831" s="7"/>
       <c r="B831" s="7"/>
       <c r="C831" s="7"/>
@@ -52358,7 +52375,7 @@
       <c r="Y831" s="5"/>
       <c r="Z831" s="5"/>
     </row>
-    <row r="832" spans="1:26" ht="16.5" customHeight="1">
+    <row r="832" spans="1:26" ht="16.5">
       <c r="A832" s="7"/>
       <c r="B832" s="7"/>
       <c r="C832" s="7"/>
@@ -52386,7 +52403,7 @@
       <c r="Y832" s="5"/>
       <c r="Z832" s="5"/>
     </row>
-    <row r="833" spans="1:26" ht="16.5" customHeight="1">
+    <row r="833" spans="1:26" ht="16.5">
       <c r="A833" s="7"/>
       <c r="B833" s="7"/>
       <c r="C833" s="7"/>
@@ -52414,7 +52431,7 @@
       <c r="Y833" s="5"/>
       <c r="Z833" s="5"/>
     </row>
-    <row r="834" spans="1:26" ht="16.5" customHeight="1">
+    <row r="834" spans="1:26" ht="16.5">
       <c r="A834" s="7"/>
       <c r="B834" s="7"/>
       <c r="C834" s="7"/>
@@ -52442,7 +52459,7 @@
       <c r="Y834" s="5"/>
       <c r="Z834" s="5"/>
     </row>
-    <row r="835" spans="1:26" ht="16.5" customHeight="1">
+    <row r="835" spans="1:26" ht="16.5">
       <c r="A835" s="7"/>
       <c r="B835" s="7"/>
       <c r="C835" s="7"/>
@@ -52470,7 +52487,7 @@
       <c r="Y835" s="5"/>
       <c r="Z835" s="5"/>
     </row>
-    <row r="836" spans="1:26" ht="16.5" customHeight="1">
+    <row r="836" spans="1:26" ht="16.5">
       <c r="A836" s="7"/>
       <c r="B836" s="7"/>
       <c r="C836" s="7"/>
@@ -52498,7 +52515,7 @@
       <c r="Y836" s="5"/>
       <c r="Z836" s="5"/>
     </row>
-    <row r="837" spans="1:26" ht="16.5" customHeight="1">
+    <row r="837" spans="1:26" ht="16.5">
       <c r="A837" s="7"/>
       <c r="B837" s="7"/>
       <c r="C837" s="7"/>
@@ -52526,7 +52543,7 @@
       <c r="Y837" s="5"/>
       <c r="Z837" s="5"/>
     </row>
-    <row r="838" spans="1:26" ht="16.5" customHeight="1">
+    <row r="838" spans="1:26" ht="16.5">
       <c r="A838" s="7"/>
       <c r="B838" s="7"/>
       <c r="C838" s="7"/>
@@ -52554,7 +52571,7 @@
       <c r="Y838" s="5"/>
       <c r="Z838" s="5"/>
     </row>
-    <row r="839" spans="1:26" ht="16.5" customHeight="1">
+    <row r="839" spans="1:26" ht="16.5">
       <c r="A839" s="7"/>
       <c r="B839" s="7"/>
       <c r="C839" s="7"/>
@@ -52582,7 +52599,7 @@
       <c r="Y839" s="5"/>
       <c r="Z839" s="5"/>
     </row>
-    <row r="840" spans="1:26" ht="16.5" customHeight="1">
+    <row r="840" spans="1:26" ht="16.5">
       <c r="A840" s="7"/>
       <c r="B840" s="7"/>
       <c r="C840" s="7"/>
@@ -52610,7 +52627,7 @@
       <c r="Y840" s="5"/>
       <c r="Z840" s="5"/>
     </row>
-    <row r="841" spans="1:26" ht="16.5" customHeight="1">
+    <row r="841" spans="1:26" ht="16.5">
       <c r="A841" s="7"/>
       <c r="B841" s="7"/>
       <c r="C841" s="7"/>
@@ -52638,7 +52655,7 @@
       <c r="Y841" s="5"/>
       <c r="Z841" s="5"/>
     </row>
-    <row r="842" spans="1:26" ht="16.5" customHeight="1">
+    <row r="842" spans="1:26" ht="16.5">
       <c r="A842" s="7"/>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
@@ -52666,7 +52683,7 @@
       <c r="Y842" s="5"/>
       <c r="Z842" s="5"/>
     </row>
-    <row r="843" spans="1:26" ht="16.5" customHeight="1">
+    <row r="843" spans="1:26" ht="16.5">
       <c r="A843" s="7"/>
       <c r="B843" s="7"/>
       <c r="C843" s="7"/>
@@ -52694,7 +52711,7 @@
       <c r="Y843" s="5"/>
       <c r="Z843" s="5"/>
     </row>
-    <row r="844" spans="1:26" ht="16.5" customHeight="1">
+    <row r="844" spans="1:26" ht="16.5">
       <c r="A844" s="7"/>
       <c r="B844" s="7"/>
       <c r="C844" s="7"/>
@@ -52722,7 +52739,7 @@
       <c r="Y844" s="5"/>
       <c r="Z844" s="5"/>
     </row>
-    <row r="845" spans="1:26" ht="16.5" customHeight="1">
+    <row r="845" spans="1:26" ht="16.5">
       <c r="A845" s="7"/>
       <c r="B845" s="7"/>
       <c r="C845" s="7"/>
@@ -52750,7 +52767,7 @@
       <c r="Y845" s="5"/>
       <c r="Z845" s="5"/>
     </row>
-    <row r="846" spans="1:26" ht="16.5" customHeight="1">
+    <row r="846" spans="1:26" ht="16.5">
       <c r="A846" s="7"/>
       <c r="B846" s="7"/>
       <c r="C846" s="7"/>
@@ -52778,7 +52795,7 @@
       <c r="Y846" s="5"/>
       <c r="Z846" s="5"/>
     </row>
-    <row r="847" spans="1:26" ht="16.5" customHeight="1">
+    <row r="847" spans="1:26" ht="16.5">
       <c r="A847" s="7"/>
       <c r="B847" s="7"/>
       <c r="C847" s="7"/>
@@ -52806,7 +52823,7 @@
       <c r="Y847" s="5"/>
       <c r="Z847" s="5"/>
     </row>
-    <row r="848" spans="1:26" ht="16.5" customHeight="1">
+    <row r="848" spans="1:26" ht="16.5">
       <c r="A848" s="7"/>
       <c r="B848" s="7"/>
       <c r="C848" s="7"/>
@@ -52834,7 +52851,7 @@
       <c r="Y848" s="5"/>
       <c r="Z848" s="5"/>
     </row>
-    <row r="849" spans="1:26" ht="16.5" customHeight="1">
+    <row r="849" spans="1:26" ht="16.5">
       <c r="A849" s="7"/>
       <c r="B849" s="7"/>
       <c r="C849" s="7"/>
@@ -52862,7 +52879,7 @@
       <c r="Y849" s="5"/>
       <c r="Z849" s="5"/>
     </row>
-    <row r="850" spans="1:26" ht="16.5" customHeight="1">
+    <row r="850" spans="1:26" ht="16.5">
       <c r="A850" s="7"/>
       <c r="B850" s="7"/>
       <c r="C850" s="7"/>
@@ -52890,7 +52907,7 @@
       <c r="Y850" s="5"/>
       <c r="Z850" s="5"/>
     </row>
-    <row r="851" spans="1:26" ht="16.5" customHeight="1">
+    <row r="851" spans="1:26" ht="16.5">
       <c r="A851" s="7"/>
       <c r="B851" s="7"/>
       <c r="C851" s="7"/>
@@ -52918,7 +52935,7 @@
       <c r="Y851" s="5"/>
       <c r="Z851" s="5"/>
     </row>
-    <row r="852" spans="1:26" ht="16.5" customHeight="1">
+    <row r="852" spans="1:26" ht="16.5">
       <c r="A852" s="7"/>
       <c r="B852" s="7"/>
       <c r="C852" s="7"/>
@@ -52946,7 +52963,7 @@
       <c r="Y852" s="5"/>
       <c r="Z852" s="5"/>
     </row>
-    <row r="853" spans="1:26" ht="16.5" customHeight="1">
+    <row r="853" spans="1:26" ht="16.5">
       <c r="A853" s="7"/>
       <c r="B853" s="7"/>
       <c r="C853" s="7"/>
@@ -52974,7 +52991,7 @@
       <c r="Y853" s="5"/>
       <c r="Z853" s="5"/>
     </row>
-    <row r="854" spans="1:26" ht="16.5" customHeight="1">
+    <row r="854" spans="1:26" ht="16.5">
       <c r="A854" s="7"/>
       <c r="B854" s="7"/>
       <c r="C854" s="7"/>
@@ -53002,7 +53019,7 @@
       <c r="Y854" s="5"/>
       <c r="Z854" s="5"/>
     </row>
-    <row r="855" spans="1:26" ht="16.5" customHeight="1">
+    <row r="855" spans="1:26" ht="16.5">
       <c r="A855" s="7"/>
       <c r="B855" s="7"/>
       <c r="C855" s="7"/>
@@ -53030,7 +53047,7 @@
       <c r="Y855" s="5"/>
       <c r="Z855" s="5"/>
     </row>
-    <row r="856" spans="1:26" ht="16.5" customHeight="1">
+    <row r="856" spans="1:26" ht="16.5">
       <c r="A856" s="7"/>
       <c r="B856" s="7"/>
       <c r="C856" s="7"/>
@@ -53058,7 +53075,7 @@
       <c r="Y856" s="5"/>
       <c r="Z856" s="5"/>
     </row>
-    <row r="857" spans="1:26" ht="16.5" customHeight="1">
+    <row r="857" spans="1:26" ht="16.5">
       <c r="A857" s="7"/>
       <c r="B857" s="7"/>
       <c r="C857" s="7"/>
@@ -53086,7 +53103,7 @@
       <c r="Y857" s="5"/>
       <c r="Z857" s="5"/>
     </row>
-    <row r="858" spans="1:26" ht="16.5" customHeight="1">
+    <row r="858" spans="1:26" ht="16.5">
       <c r="A858" s="7"/>
       <c r="B858" s="7"/>
       <c r="C858" s="7"/>
@@ -53114,7 +53131,7 @@
       <c r="Y858" s="5"/>
       <c r="Z858" s="5"/>
     </row>
-    <row r="859" spans="1:26" ht="16.5" customHeight="1">
+    <row r="859" spans="1:26" ht="16.5">
       <c r="A859" s="7"/>
       <c r="B859" s="7"/>
       <c r="C859" s="7"/>
@@ -53142,7 +53159,7 @@
       <c r="Y859" s="5"/>
       <c r="Z859" s="5"/>
     </row>
-    <row r="860" spans="1:26" ht="16.5" customHeight="1">
+    <row r="860" spans="1:26" ht="16.5">
       <c r="A860" s="7"/>
       <c r="B860" s="7"/>
       <c r="C860" s="7"/>
@@ -53170,7 +53187,7 @@
       <c r="Y860" s="5"/>
       <c r="Z860" s="5"/>
     </row>
-    <row r="861" spans="1:26" ht="16.5" customHeight="1">
+    <row r="861" spans="1:26" ht="16.5">
       <c r="A861" s="7"/>
       <c r="B861" s="7"/>
       <c r="C861" s="7"/>
@@ -53198,7 +53215,7 @@
       <c r="Y861" s="5"/>
       <c r="Z861" s="5"/>
     </row>
-    <row r="862" spans="1:26" ht="16.5" customHeight="1">
+    <row r="862" spans="1:26" ht="16.5">
       <c r="A862" s="7"/>
       <c r="B862" s="7"/>
       <c r="C862" s="7"/>
@@ -53226,7 +53243,7 @@
       <c r="Y862" s="5"/>
       <c r="Z862" s="5"/>
     </row>
-    <row r="863" spans="1:26" ht="16.5" customHeight="1">
+    <row r="863" spans="1:26" ht="16.5">
       <c r="A863" s="7"/>
       <c r="B863" s="7"/>
       <c r="C863" s="7"/>
@@ -53254,7 +53271,7 @@
       <c r="Y863" s="5"/>
       <c r="Z863" s="5"/>
     </row>
-    <row r="864" spans="1:26" ht="16.5" customHeight="1">
+    <row r="864" spans="1:26" ht="16.5">
       <c r="A864" s="7"/>
       <c r="B864" s="7"/>
       <c r="C864" s="7"/>
@@ -53282,7 +53299,7 @@
       <c r="Y864" s="5"/>
       <c r="Z864" s="5"/>
     </row>
-    <row r="865" spans="1:26" ht="16.5" customHeight="1">
+    <row r="865" spans="1:26" ht="16.5">
       <c r="A865" s="7"/>
       <c r="B865" s="7"/>
       <c r="C865" s="7"/>
@@ -53310,7 +53327,7 @@
       <c r="Y865" s="5"/>
       <c r="Z865" s="5"/>
     </row>
-    <row r="866" spans="1:26" ht="16.5" customHeight="1">
+    <row r="866" spans="1:26" ht="16.5">
       <c r="A866" s="7"/>
       <c r="B866" s="7"/>
       <c r="C866" s="7"/>
@@ -53338,7 +53355,7 @@
       <c r="Y866" s="5"/>
       <c r="Z866" s="5"/>
     </row>
-    <row r="867" spans="1:26" ht="16.5" customHeight="1">
+    <row r="867" spans="1:26" ht="16.5">
       <c r="A867" s="7"/>
       <c r="B867" s="7"/>
       <c r="C867" s="7"/>
@@ -53366,7 +53383,7 @@
       <c r="Y867" s="5"/>
       <c r="Z867" s="5"/>
     </row>
-    <row r="868" spans="1:26" ht="16.5" customHeight="1">
+    <row r="868" spans="1:26" ht="16.5">
       <c r="A868" s="7"/>
       <c r="B868" s="7"/>
       <c r="C868" s="7"/>
@@ -53394,7 +53411,7 @@
       <c r="Y868" s="5"/>
       <c r="Z868" s="5"/>
     </row>
-    <row r="869" spans="1:26" ht="16.5" customHeight="1">
+    <row r="869" spans="1:26" ht="16.5">
       <c r="A869" s="7"/>
       <c r="B869" s="7"/>
       <c r="C869" s="7"/>
@@ -53422,7 +53439,7 @@
       <c r="Y869" s="5"/>
       <c r="Z869" s="5"/>
     </row>
-    <row r="870" spans="1:26" ht="16.5" customHeight="1">
+    <row r="870" spans="1:26" ht="16.5">
       <c r="A870" s="7"/>
       <c r="B870" s="7"/>
       <c r="C870" s="7"/>
@@ -53450,7 +53467,7 @@
       <c r="Y870" s="5"/>
       <c r="Z870" s="5"/>
     </row>
-    <row r="871" spans="1:26" ht="16.5" customHeight="1">
+    <row r="871" spans="1:26" ht="16.5">
       <c r="A871" s="7"/>
       <c r="B871" s="7"/>
       <c r="C871" s="7"/>
@@ -53478,7 +53495,7 @@
       <c r="Y871" s="5"/>
       <c r="Z871" s="5"/>
     </row>
-    <row r="872" spans="1:26" ht="16.5" customHeight="1">
+    <row r="872" spans="1:26" ht="16.5">
       <c r="A872" s="7"/>
       <c r="B872" s="7"/>
       <c r="C872" s="7"/>
@@ -53506,7 +53523,7 @@
       <c r="Y872" s="5"/>
       <c r="Z872" s="5"/>
     </row>
-    <row r="873" spans="1:26" ht="16.5" customHeight="1">
+    <row r="873" spans="1:26" ht="16.5">
       <c r="A873" s="7"/>
       <c r="B873" s="7"/>
       <c r="C873" s="7"/>
@@ -53534,7 +53551,7 @@
       <c r="Y873" s="5"/>
       <c r="Z873" s="5"/>
     </row>
-    <row r="874" spans="1:26" ht="16.5" customHeight="1">
+    <row r="874" spans="1:26" ht="16.5">
       <c r="A874" s="7"/>
       <c r="B874" s="7"/>
       <c r="C874" s="7"/>
@@ -53562,7 +53579,7 @@
       <c r="Y874" s="5"/>
       <c r="Z874" s="5"/>
     </row>
-    <row r="875" spans="1:26" ht="16.5" customHeight="1">
+    <row r="875" spans="1:26" ht="16.5">
       <c r="A875" s="7"/>
       <c r="B875" s="7"/>
       <c r="C875" s="7"/>
@@ -53590,7 +53607,7 @@
       <c r="Y875" s="5"/>
       <c r="Z875" s="5"/>
     </row>
-    <row r="876" spans="1:26" ht="16.5" customHeight="1">
+    <row r="876" spans="1:26" ht="16.5">
       <c r="A876" s="7"/>
       <c r="B876" s="7"/>
       <c r="C876" s="7"/>
@@ -53618,7 +53635,7 @@
       <c r="Y876" s="5"/>
       <c r="Z876" s="5"/>
     </row>
-    <row r="877" spans="1:26" ht="16.5" customHeight="1">
+    <row r="877" spans="1:26" ht="16.5">
       <c r="A877" s="7"/>
       <c r="B877" s="7"/>
       <c r="C877" s="7"/>
@@ -53646,7 +53663,7 @@
       <c r="Y877" s="5"/>
       <c r="Z877" s="5"/>
     </row>
-    <row r="878" spans="1:26" ht="16.5" customHeight="1">
+    <row r="878" spans="1:26" ht="16.5">
       <c r="A878" s="7"/>
       <c r="B878" s="7"/>
       <c r="C878" s="7"/>
@@ -53674,7 +53691,7 @@
       <c r="Y878" s="5"/>
       <c r="Z878" s="5"/>
     </row>
-    <row r="879" spans="1:26" ht="16.5" customHeight="1">
+    <row r="879" spans="1:26" ht="16.5">
       <c r="A879" s="7"/>
       <c r="B879" s="7"/>
       <c r="C879" s="7"/>
@@ -53702,7 +53719,7 @@
       <c r="Y879" s="5"/>
       <c r="Z879" s="5"/>
     </row>
-    <row r="880" spans="1:26" ht="16.5" customHeight="1">
+    <row r="880" spans="1:26" ht="16.5">
       <c r="A880" s="7"/>
       <c r="B880" s="7"/>
       <c r="C880" s="7"/>
@@ -53730,7 +53747,7 @@
       <c r="Y880" s="5"/>
       <c r="Z880" s="5"/>
     </row>
-    <row r="881" spans="1:26" ht="16.5" customHeight="1">
+    <row r="881" spans="1:26" ht="16.5">
       <c r="A881" s="7"/>
       <c r="B881" s="7"/>
       <c r="C881" s="7"/>
@@ -53758,7 +53775,7 @@
       <c r="Y881" s="5"/>
       <c r="Z881" s="5"/>
     </row>
-    <row r="882" spans="1:26" ht="16.5" customHeight="1">
+    <row r="882" spans="1:26" ht="16.5">
       <c r="A882" s="7"/>
       <c r="B882" s="7"/>
       <c r="C882" s="7"/>
@@ -53786,7 +53803,7 @@
       <c r="Y882" s="5"/>
       <c r="Z882" s="5"/>
     </row>
-    <row r="883" spans="1:26" ht="16.5" customHeight="1">
+    <row r="883" spans="1:26" ht="16.5">
       <c r="A883" s="7"/>
       <c r="B883" s="7"/>
       <c r="C883" s="7"/>
@@ -53814,7 +53831,7 @@
       <c r="Y883" s="5"/>
       <c r="Z883" s="5"/>
     </row>
-    <row r="884" spans="1:26" ht="16.5" customHeight="1">
+    <row r="884" spans="1:26" ht="16.5">
       <c r="A884" s="7"/>
       <c r="B884" s="7"/>
       <c r="C884" s="7"/>
@@ -53842,7 +53859,7 @@
       <c r="Y884" s="5"/>
       <c r="Z884" s="5"/>
     </row>
-    <row r="885" spans="1:26" ht="16.5" customHeight="1">
+    <row r="885" spans="1:26" ht="16.5">
       <c r="A885" s="7"/>
       <c r="B885" s="7"/>
       <c r="C885" s="7"/>
@@ -53870,7 +53887,7 @@
       <c r="Y885" s="5"/>
       <c r="Z885" s="5"/>
     </row>
-    <row r="886" spans="1:26" ht="16.5" customHeight="1">
+    <row r="886" spans="1:26" ht="16.5">
       <c r="A886" s="7"/>
       <c r="B886" s="7"/>
       <c r="C886" s="7"/>
@@ -53898,7 +53915,7 @@
       <c r="Y886" s="5"/>
       <c r="Z886" s="5"/>
     </row>
-    <row r="887" spans="1:26" ht="16.5" customHeight="1">
+    <row r="887" spans="1:26" ht="16.5">
       <c r="A887" s="7"/>
       <c r="B887" s="7"/>
       <c r="C887" s="7"/>
@@ -53926,7 +53943,7 @@
       <c r="Y887" s="5"/>
       <c r="Z887" s="5"/>
     </row>
-    <row r="888" spans="1:26" ht="16.5" customHeight="1">
+    <row r="888" spans="1:26" ht="16.5">
       <c r="A888" s="7"/>
       <c r="B888" s="7"/>
       <c r="C888" s="7"/>
@@ -53954,7 +53971,7 @@
       <c r="Y888" s="5"/>
       <c r="Z888" s="5"/>
     </row>
-    <row r="889" spans="1:26" ht="16.5" customHeight="1">
+    <row r="889" spans="1:26" ht="16.5">
       <c r="A889" s="7"/>
       <c r="B889" s="7"/>
       <c r="C889" s="7"/>
@@ -53982,7 +53999,7 @@
       <c r="Y889" s="5"/>
       <c r="Z889" s="5"/>
     </row>
-    <row r="890" spans="1:26" ht="16.5" customHeight="1">
+    <row r="890" spans="1:26" ht="16.5">
       <c r="A890" s="7"/>
       <c r="B890" s="7"/>
       <c r="C890" s="7"/>
@@ -54010,7 +54027,7 @@
       <c r="Y890" s="5"/>
       <c r="Z890" s="5"/>
     </row>
-    <row r="891" spans="1:26" ht="16.5" customHeight="1">
+    <row r="891" spans="1:26" ht="16.5">
       <c r="A891" s="7"/>
       <c r="B891" s="7"/>
       <c r="C891" s="7"/>
@@ -54038,7 +54055,7 @@
       <c r="Y891" s="5"/>
       <c r="Z891" s="5"/>
     </row>
-    <row r="892" spans="1:26" ht="16.5" customHeight="1">
+    <row r="892" spans="1:26" ht="16.5">
       <c r="A892" s="7"/>
       <c r="B892" s="7"/>
       <c r="C892" s="7"/>
@@ -54066,7 +54083,7 @@
       <c r="Y892" s="5"/>
       <c r="Z892" s="5"/>
     </row>
-    <row r="893" spans="1:26" ht="16.5" customHeight="1">
+    <row r="893" spans="1:26" ht="16.5">
       <c r="A893" s="7"/>
       <c r="B893" s="7"/>
       <c r="C893" s="7"/>
@@ -54094,7 +54111,7 @@
       <c r="Y893" s="5"/>
       <c r="Z893" s="5"/>
     </row>
-    <row r="894" spans="1:26" ht="16.5" customHeight="1">
+    <row r="894" spans="1:26" ht="16.5">
       <c r="A894" s="7"/>
       <c r="B894" s="7"/>
       <c r="C894" s="7"/>
@@ -54122,7 +54139,7 @@
       <c r="Y894" s="5"/>
       <c r="Z894" s="5"/>
     </row>
-    <row r="895" spans="1:26" ht="16.5" customHeight="1">
+    <row r="895" spans="1:26" ht="16.5">
       <c r="A895" s="7"/>
       <c r="B895" s="7"/>
       <c r="C895" s="7"/>
@@ -54150,7 +54167,7 @@
       <c r="Y895" s="5"/>
       <c r="Z895" s="5"/>
     </row>
-    <row r="896" spans="1:26" ht="16.5" customHeight="1">
+    <row r="896" spans="1:26" ht="16.5">
       <c r="A896" s="7"/>
       <c r="B896" s="7"/>
       <c r="C896" s="7"/>
@@ -54178,7 +54195,7 @@
       <c r="Y896" s="5"/>
       <c r="Z896" s="5"/>
     </row>
-    <row r="897" spans="1:26" ht="16.5" customHeight="1">
+    <row r="897" spans="1:26" ht="16.5">
       <c r="A897" s="7"/>
       <c r="B897" s="7"/>
       <c r="C897" s="7"/>
@@ -54206,7 +54223,7 @@
       <c r="Y897" s="5"/>
       <c r="Z897" s="5"/>
     </row>
-    <row r="898" spans="1:26" ht="16.5" customHeight="1">
+    <row r="898" spans="1:26" ht="16.5">
       <c r="A898" s="7"/>
       <c r="B898" s="7"/>
       <c r="C898" s="7"/>
@@ -54234,7 +54251,7 @@
       <c r="Y898" s="5"/>
       <c r="Z898" s="5"/>
     </row>
-    <row r="899" spans="1:26" ht="16.5" customHeight="1">
+    <row r="899" spans="1:26" ht="16.5">
       <c r="A899" s="7"/>
       <c r="B899" s="7"/>
       <c r="C899" s="7"/>
@@ -54262,7 +54279,7 @@
       <c r="Y899" s="5"/>
       <c r="Z899" s="5"/>
     </row>
-    <row r="900" spans="1:26" ht="16.5" customHeight="1">
+    <row r="900" spans="1:26" ht="16.5">
       <c r="A900" s="7"/>
       <c r="B900" s="7"/>
       <c r="C900" s="7"/>
@@ -54290,7 +54307,7 @@
       <c r="Y900" s="5"/>
       <c r="Z900" s="5"/>
     </row>
-    <row r="901" spans="1:26" ht="16.5" customHeight="1">
+    <row r="901" spans="1:26" ht="16.5">
       <c r="A901" s="7"/>
       <c r="B901" s="7"/>
       <c r="C901" s="7"/>
@@ -54318,7 +54335,7 @@
       <c r="Y901" s="5"/>
       <c r="Z901" s="5"/>
     </row>
-    <row r="902" spans="1:26" ht="16.5" customHeight="1">
+    <row r="902" spans="1:26" ht="16.5">
       <c r="A902" s="7"/>
       <c r="B902" s="7"/>
       <c r="C902" s="7"/>
@@ -54346,7 +54363,7 @@
       <c r="Y902" s="5"/>
       <c r="Z902" s="5"/>
     </row>
-    <row r="903" spans="1:26" ht="16.5" customHeight="1">
+    <row r="903" spans="1:26" ht="16.5">
       <c r="A903" s="7"/>
       <c r="B903" s="7"/>
       <c r="C903" s="7"/>
@@ -54374,7 +54391,7 @@
       <c r="Y903" s="5"/>
       <c r="Z903" s="5"/>
     </row>
-    <row r="904" spans="1:26" ht="16.5" customHeight="1">
+    <row r="904" spans="1:26" ht="16.5">
       <c r="A904" s="7"/>
       <c r="B904" s="7"/>
       <c r="C904" s="7"/>
@@ -54402,7 +54419,7 @@
       <c r="Y904" s="5"/>
       <c r="Z904" s="5"/>
     </row>
-    <row r="905" spans="1:26" ht="16.5" customHeight="1">
+    <row r="905" spans="1:26" ht="16.5">
       <c r="A905" s="7"/>
       <c r="B905" s="7"/>
       <c r="C905" s="7"/>
@@ -54430,7 +54447,7 @@
       <c r="Y905" s="5"/>
       <c r="Z905" s="5"/>
     </row>
-    <row r="906" spans="1:26" ht="16.5" customHeight="1">
+    <row r="906" spans="1:26" ht="16.5">
       <c r="A906" s="7"/>
       <c r="B906" s="7"/>
       <c r="C906" s="7"/>
@@ -54458,7 +54475,7 @@
       <c r="Y906" s="5"/>
       <c r="Z906" s="5"/>
     </row>
-    <row r="907" spans="1:26" ht="16.5" customHeight="1">
+    <row r="907" spans="1:26" ht="16.5">
       <c r="A907" s="7"/>
       <c r="B907" s="7"/>
       <c r="C907" s="7"/>
@@ -54486,7 +54503,7 @@
       <c r="Y907" s="5"/>
       <c r="Z907" s="5"/>
     </row>
-    <row r="908" spans="1:26" ht="16.5" customHeight="1">
+    <row r="908" spans="1:26" ht="16.5">
       <c r="A908" s="7"/>
       <c r="B908" s="7"/>
       <c r="C908" s="7"/>
@@ -54514,7 +54531,7 @@
       <c r="Y908" s="5"/>
       <c r="Z908" s="5"/>
     </row>
-    <row r="909" spans="1:26" ht="16.5" customHeight="1">
+    <row r="909" spans="1:26" ht="16.5">
       <c r="A909" s="7"/>
       <c r="B909" s="7"/>
       <c r="C909" s="7"/>
@@ -54542,7 +54559,7 @@
       <c r="Y909" s="5"/>
       <c r="Z909" s="5"/>
     </row>
-    <row r="910" spans="1:26" ht="16.5" customHeight="1">
+    <row r="910" spans="1:26" ht="16.5">
       <c r="A910" s="7"/>
       <c r="B910" s="7"/>
       <c r="C910" s="7"/>
@@ -54570,7 +54587,7 @@
       <c r="Y910" s="5"/>
       <c r="Z910" s="5"/>
     </row>
-    <row r="911" spans="1:26" ht="16.5" customHeight="1">
+    <row r="911" spans="1:26" ht="16.5">
       <c r="A911" s="7"/>
       <c r="B911" s="7"/>
       <c r="C911" s="7"/>
@@ -54598,7 +54615,7 @@
       <c r="Y911" s="5"/>
       <c r="Z911" s="5"/>
     </row>
-    <row r="912" spans="1:26" ht="16.5" customHeight="1">
+    <row r="912" spans="1:26" ht="16.5">
       <c r="A912" s="7"/>
       <c r="B912" s="7"/>
       <c r="C912" s="7"/>
@@ -54626,7 +54643,7 @@
       <c r="Y912" s="5"/>
       <c r="Z912" s="5"/>
     </row>
-    <row r="913" spans="1:26" ht="16.5" customHeight="1">
+    <row r="913" spans="1:26" ht="16.5">
       <c r="A913" s="7"/>
       <c r="B913" s="7"/>
       <c r="C913" s="7"/>
@@ -54654,7 +54671,7 @@
       <c r="Y913" s="5"/>
       <c r="Z913" s="5"/>
     </row>
-    <row r="914" spans="1:26" ht="16.5" customHeight="1">
+    <row r="914" spans="1:26" ht="16.5">
       <c r="A914" s="7"/>
       <c r="B914" s="7"/>
       <c r="C914" s="7"/>
@@ -54682,7 +54699,7 @@
       <c r="Y914" s="5"/>
       <c r="Z914" s="5"/>
     </row>
-    <row r="915" spans="1:26" ht="16.5" customHeight="1">
+    <row r="915" spans="1:26" ht="16.5">
       <c r="A915" s="7"/>
       <c r="B915" s="7"/>
       <c r="C915" s="7"/>
@@ -54710,7 +54727,7 @@
       <c r="Y915" s="5"/>
       <c r="Z915" s="5"/>
     </row>
-    <row r="916" spans="1:26" ht="16.5" customHeight="1">
+    <row r="916" spans="1:26" ht="16.5">
       <c r="A916" s="7"/>
       <c r="B916" s="7"/>
       <c r="C916" s="7"/>
@@ -54738,7 +54755,7 @@
       <c r="Y916" s="5"/>
       <c r="Z916" s="5"/>
     </row>
-    <row r="917" spans="1:26" ht="16.5" customHeight="1">
+    <row r="917" spans="1:26" ht="16.5">
       <c r="A917" s="7"/>
       <c r="B917" s="7"/>
       <c r="C917" s="7"/>
@@ -54766,7 +54783,7 @@
       <c r="Y917" s="5"/>
       <c r="Z917" s="5"/>
     </row>
-    <row r="918" spans="1:26" ht="16.5" customHeight="1">
+    <row r="918" spans="1:26" ht="16.5">
       <c r="A918" s="7"/>
       <c r="B918" s="7"/>
       <c r="C918" s="7"/>
@@ -54794,7 +54811,7 @@
       <c r="Y918" s="5"/>
       <c r="Z918" s="5"/>
     </row>
-    <row r="919" spans="1:26" ht="16.5" customHeight="1">
+    <row r="919" spans="1:26" ht="16.5">
       <c r="A919" s="7"/>
       <c r="B919" s="7"/>
       <c r="C919" s="7"/>
@@ -54822,7 +54839,7 @@
       <c r="Y919" s="5"/>
       <c r="Z919" s="5"/>
     </row>
-    <row r="920" spans="1:26" ht="16.5" customHeight="1">
+    <row r="920" spans="1:26" ht="16.5">
       <c r="A920" s="7"/>
       <c r="B920" s="7"/>
       <c r="C920" s="7"/>
@@ -54850,7 +54867,7 @@
       <c r="Y920" s="5"/>
       <c r="Z920" s="5"/>
     </row>
-    <row r="921" spans="1:26" ht="16.5" customHeight="1">
+    <row r="921" spans="1:26" ht="16.5">
       <c r="A921" s="7"/>
       <c r="B921" s="7"/>
       <c r="C921" s="7"/>
@@ -54878,7 +54895,7 @@
       <c r="Y921" s="5"/>
       <c r="Z921" s="5"/>
     </row>
-    <row r="922" spans="1:26" ht="16.5" customHeight="1">
+    <row r="922" spans="1:26" ht="16.5">
       <c r="A922" s="7"/>
       <c r="B922" s="7"/>
       <c r="C922" s="7"/>
@@ -54906,7 +54923,7 @@
       <c r="Y922" s="5"/>
       <c r="Z922" s="5"/>
     </row>
-    <row r="923" spans="1:26" ht="16.5" customHeight="1">
+    <row r="923" spans="1:26" ht="16.5">
       <c r="A923" s="7"/>
       <c r="B923" s="7"/>
       <c r="C923" s="7"/>
@@ -54934,7 +54951,7 @@
       <c r="Y923" s="5"/>
       <c r="Z923" s="5"/>
     </row>
-    <row r="924" spans="1:26" ht="16.5" customHeight="1">
+    <row r="924" spans="1:26" ht="16.5">
       <c r="A924" s="7"/>
       <c r="B924" s="7"/>
       <c r="C924" s="7"/>
@@ -54962,7 +54979,7 @@
       <c r="Y924" s="5"/>
       <c r="Z924" s="5"/>
     </row>
-    <row r="925" spans="1:26" ht="16.5" customHeight="1">
+    <row r="925" spans="1:26" ht="16.5">
       <c r="A925" s="7"/>
       <c r="B925" s="7"/>
       <c r="C925" s="7"/>
@@ -54990,7 +55007,7 @@
       <c r="Y925" s="5"/>
       <c r="Z925" s="5"/>
     </row>
-    <row r="926" spans="1:26" ht="16.5" customHeight="1">
+    <row r="926" spans="1:26" ht="16.5">
       <c r="A926" s="7"/>
       <c r="B926" s="7"/>
       <c r="C926" s="7"/>
@@ -55018,7 +55035,7 @@
       <c r="Y926" s="5"/>
       <c r="Z926" s="5"/>
     </row>
-    <row r="927" spans="1:26" ht="16.5" customHeight="1">
+    <row r="927" spans="1:26" ht="16.5">
       <c r="A927" s="7"/>
       <c r="B927" s="7"/>
       <c r="C927" s="7"/>
@@ -55046,7 +55063,7 @@
       <c r="Y927" s="5"/>
       <c r="Z927" s="5"/>
     </row>
-    <row r="928" spans="1:26" ht="16.5" customHeight="1">
+    <row r="928" spans="1:26" ht="16.5">
       <c r="A928" s="7"/>
       <c r="B928" s="7"/>
       <c r="C928" s="7"/>
@@ -55074,7 +55091,7 @@
       <c r="Y928" s="5"/>
       <c r="Z928" s="5"/>
     </row>
-    <row r="929" spans="1:26" ht="16.5" customHeight="1">
+    <row r="929" spans="1:26" ht="16.5">
       <c r="A929" s="7"/>
       <c r="B929" s="7"/>
       <c r="C929" s="7"/>
@@ -55102,7 +55119,7 @@
       <c r="Y929" s="5"/>
       <c r="Z929" s="5"/>
     </row>
-    <row r="930" spans="1:26" ht="16.5" customHeight="1">
+    <row r="930" spans="1:26" ht="16.5">
       <c r="A930" s="7"/>
       <c r="B930" s="7"/>
       <c r="C930" s="7"/>
@@ -55130,7 +55147,7 @@
       <c r="Y930" s="5"/>
       <c r="Z930" s="5"/>
     </row>
-    <row r="931" spans="1:26" ht="16.5" customHeight="1">
+    <row r="931" spans="1:26" ht="16.5">
       <c r="A931" s="7"/>
       <c r="B931" s="7"/>
       <c r="C931" s="7"/>
@@ -55158,7 +55175,7 @@
       <c r="Y931" s="5"/>
       <c r="Z931" s="5"/>
     </row>
-    <row r="932" spans="1:26" ht="16.5" customHeight="1">
+    <row r="932" spans="1:26" ht="16.5">
       <c r="A932" s="7"/>
       <c r="B932" s="7"/>
       <c r="C932" s="7"/>
@@ -55186,7 +55203,7 @@
       <c r="Y932" s="5"/>
       <c r="Z932" s="5"/>
     </row>
-    <row r="933" spans="1:26" ht="16.5" customHeight="1">
+    <row r="933" spans="1:26" ht="16.5">
       <c r="A933" s="7"/>
       <c r="B933" s="7"/>
       <c r="C933" s="7"/>
@@ -55214,7 +55231,7 @@
       <c r="Y933" s="5"/>
       <c r="Z933" s="5"/>
     </row>
-    <row r="934" spans="1:26" ht="16.5" customHeight="1">
+    <row r="934" spans="1:26" ht="16.5">
       <c r="A934" s="7"/>
       <c r="B934" s="7"/>
       <c r="C934" s="7"/>
@@ -55242,7 +55259,7 @@
       <c r="Y934" s="5"/>
       <c r="Z934" s="5"/>
     </row>
-    <row r="935" spans="1:26" ht="16.5" customHeight="1">
+    <row r="935" spans="1:26" ht="16.5">
       <c r="A935" s="7"/>
       <c r="B935" s="7"/>
       <c r="C935" s="7"/>
@@ -55270,7 +55287,7 @@
       <c r="Y935" s="5"/>
       <c r="Z935" s="5"/>
     </row>
-    <row r="936" spans="1:26" ht="16.5" customHeight="1">
+    <row r="936" spans="1:26" ht="16.5">
       <c r="A936" s="7"/>
       <c r="B936" s="7"/>
       <c r="C936" s="7"/>
@@ -55298,7 +55315,7 @@
       <c r="Y936" s="5"/>
       <c r="Z936" s="5"/>
     </row>
-    <row r="937" spans="1:26" ht="16.5" customHeight="1">
+    <row r="937" spans="1:26" ht="16.5">
       <c r="A937" s="7"/>
       <c r="B937" s="7"/>
       <c r="C937" s="7"/>
@@ -55326,7 +55343,7 @@
       <c r="Y937" s="5"/>
       <c r="Z937" s="5"/>
     </row>
-    <row r="938" spans="1:26" ht="16.5" customHeight="1">
+    <row r="938" spans="1:26" ht="16.5">
       <c r="A938" s="7"/>
       <c r="B938" s="7"/>
       <c r="C938" s="7"/>
@@ -55354,7 +55371,7 @@
       <c r="Y938" s="5"/>
       <c r="Z938" s="5"/>
     </row>
-    <row r="939" spans="1:26" ht="16.5" customHeight="1">
+    <row r="939" spans="1:26" ht="16.5">
       <c r="A939" s="7"/>
       <c r="B939" s="7"/>
       <c r="C939" s="7"/>
@@ -55382,7 +55399,7 @@
       <c r="Y939" s="5"/>
       <c r="Z939" s="5"/>
     </row>
-    <row r="940" spans="1:26" ht="16.5" customHeight="1">
+    <row r="940" spans="1:26" ht="16.5">
       <c r="A940" s="7"/>
       <c r="B940" s="7"/>
       <c r="C940" s="7"/>
@@ -55410,7 +55427,7 @@
       <c r="Y940" s="5"/>
       <c r="Z940" s="5"/>
     </row>
-    <row r="941" spans="1:26" ht="16.5" customHeight="1">
+    <row r="941" spans="1:26" ht="16.5">
       <c r="A941" s="7"/>
       <c r="B941" s="7"/>
       <c r="C941" s="7"/>
@@ -55438,7 +55455,7 @@
       <c r="Y941" s="5"/>
       <c r="Z941" s="5"/>
     </row>
-    <row r="942" spans="1:26" ht="16.5" customHeight="1">
+    <row r="942" spans="1:26" ht="16.5">
       <c r="A942" s="7"/>
       <c r="B942" s="7"/>
       <c r="C942" s="7"/>
@@ -55466,7 +55483,7 @@
       <c r="Y942" s="5"/>
       <c r="Z942" s="5"/>
     </row>
-    <row r="943" spans="1:26" ht="16.5" customHeight="1">
+    <row r="943" spans="1:26" ht="16.5">
       <c r="A943" s="7"/>
       <c r="B943" s="7"/>
       <c r="C943" s="7"/>
@@ -55494,7 +55511,7 @@
       <c r="Y943" s="5"/>
       <c r="Z943" s="5"/>
     </row>
-    <row r="944" spans="1:26" ht="16.5" customHeight="1">
+    <row r="944" spans="1:26" ht="16.5">
       <c r="A944" s="7"/>
       <c r="B944" s="7"/>
       <c r="C944" s="7"/>
@@ -55522,7 +55539,7 @@
       <c r="Y944" s="5"/>
       <c r="Z944" s="5"/>
     </row>
-    <row r="945" spans="1:26" ht="16.5" customHeight="1">
+    <row r="945" spans="1:26" ht="16.5">
       <c r="A945" s="7"/>
       <c r="B945" s="7"/>
       <c r="C945" s="7"/>
@@ -55550,7 +55567,7 @@
       <c r="Y945" s="5"/>
       <c r="Z945" s="5"/>
     </row>
-    <row r="946" spans="1:26" ht="16.5" customHeight="1">
+    <row r="946" spans="1:26" ht="16.5">
       <c r="A946" s="7"/>
       <c r="B946" s="7"/>
       <c r="C946" s="7"/>
@@ -55578,7 +55595,7 @@
       <c r="Y946" s="5"/>
       <c r="Z946" s="5"/>
     </row>
-    <row r="947" spans="1:26" ht="16.5" customHeight="1">
+    <row r="947" spans="1:26" ht="16.5">
       <c r="A947" s="7"/>
       <c r="B947" s="7"/>
       <c r="C947" s="7"/>
@@ -55606,7 +55623,7 @@
       <c r="Y947" s="5"/>
       <c r="Z947" s="5"/>
     </row>
-    <row r="948" spans="1:26" ht="16.5" customHeight="1">
+    <row r="948" spans="1:26" ht="16.5">
       <c r="A948" s="7"/>
       <c r="B948" s="7"/>
       <c r="C948" s="7"/>
@@ -55634,7 +55651,7 @@
       <c r="Y948" s="5"/>
       <c r="Z948" s="5"/>
     </row>
-    <row r="949" spans="1:26" ht="16.5" customHeight="1">
+    <row r="949" spans="1:26" ht="16.5">
       <c r="A949" s="7"/>
       <c r="B949" s="7"/>
       <c r="C949" s="7"/>
@@ -55662,7 +55679,7 @@
       <c r="Y949" s="5"/>
       <c r="Z949" s="5"/>
     </row>
-    <row r="950" spans="1:26" ht="16.5" customHeight="1">
+    <row r="950" spans="1:26" ht="16.5">
       <c r="A950" s="7"/>
       <c r="B950" s="7"/>
       <c r="C950" s="7"/>
@@ -55690,7 +55707,7 @@
       <c r="Y950" s="5"/>
       <c r="Z950" s="5"/>
     </row>
-    <row r="951" spans="1:26" ht="16.5" customHeight="1">
+    <row r="951" spans="1:26" ht="16.5">
       <c r="A951" s="7"/>
       <c r="B951" s="7"/>
       <c r="C951" s="7"/>
@@ -55718,7 +55735,7 @@
       <c r="Y951" s="5"/>
       <c r="Z951" s="5"/>
     </row>
-    <row r="952" spans="1:26" ht="16.5" customHeight="1">
+    <row r="952" spans="1:26" ht="16.5">
       <c r="A952" s="7"/>
       <c r="B952" s="7"/>
       <c r="C952" s="7"/>
@@ -55746,7 +55763,7 @@
       <c r="Y952" s="5"/>
       <c r="Z952" s="5"/>
     </row>
-    <row r="953" spans="1:26" ht="16.5" customHeight="1">
+    <row r="953" spans="1:26" ht="16.5">
       <c r="A953" s="7"/>
       <c r="B953" s="7"/>
       <c r="C953" s="7"/>
@@ -55774,7 +55791,7 @@
       <c r="Y953" s="5"/>
       <c r="Z953" s="5"/>
     </row>
-    <row r="954" spans="1:26" ht="16.5" customHeight="1">
+    <row r="954" spans="1:26" ht="16.5">
       <c r="A954" s="7"/>
       <c r="B954" s="7"/>
       <c r="C954" s="7"/>
@@ -55802,7 +55819,7 @@
       <c r="Y954" s="5"/>
       <c r="Z954" s="5"/>
     </row>
-    <row r="955" spans="1:26" ht="16.5" customHeight="1">
+    <row r="955" spans="1:26" ht="16.5">
       <c r="A955" s="7"/>
       <c r="B955" s="7"/>
       <c r="C955" s="7"/>
@@ -55830,7 +55847,7 @@
       <c r="Y955" s="5"/>
       <c r="Z955" s="5"/>
     </row>
-    <row r="956" spans="1:26" ht="16.5" customHeight="1">
+    <row r="956" spans="1:26" ht="16.5">
       <c r="A956" s="7"/>
       <c r="B956" s="7"/>
       <c r="C956" s="7"/>
@@ -55858,7 +55875,7 @@
       <c r="Y956" s="5"/>
       <c r="Z956" s="5"/>
     </row>
-    <row r="957" spans="1:26" ht="16.5" customHeight="1">
+    <row r="957" spans="1:26" ht="16.5">
       <c r="A957" s="7"/>
       <c r="B957" s="7"/>
       <c r="C957" s="7"/>
@@ -55886,7 +55903,7 @@
       <c r="Y957" s="5"/>
       <c r="Z957" s="5"/>
     </row>
-    <row r="958" spans="1:26" ht="16.5" customHeight="1">
+    <row r="958" spans="1:26" ht="16.5">
       <c r="A958" s="7"/>
       <c r="B958" s="7"/>
       <c r="C958" s="7"/>
@@ -55914,7 +55931,7 @@
       <c r="Y958" s="5"/>
       <c r="Z958" s="5"/>
     </row>
-    <row r="959" spans="1:26" ht="16.5" customHeight="1">
+    <row r="959" spans="1:26" ht="16.5">
       <c r="A959" s="7"/>
       <c r="B959" s="7"/>
       <c r="C959" s="7"/>
@@ -55942,7 +55959,7 @@
       <c r="Y959" s="5"/>
       <c r="Z959" s="5"/>
     </row>
-    <row r="960" spans="1:26" ht="16.5" customHeight="1">
+    <row r="960" spans="1:26" ht="16.5">
       <c r="A960" s="7"/>
       <c r="B960" s="7"/>
       <c r="C960" s="7"/>
@@ -55970,7 +55987,7 @@
       <c r="Y960" s="5"/>
       <c r="Z960" s="5"/>
     </row>
-    <row r="961" spans="1:26" ht="16.5" customHeight="1">
+    <row r="961" spans="1:26" ht="16.5">
       <c r="A961" s="7"/>
       <c r="B961" s="7"/>
       <c r="C961" s="7"/>
@@ -55998,7 +56015,7 @@
       <c r="Y961" s="5"/>
       <c r="Z961" s="5"/>
     </row>
-    <row r="962" spans="1:26" ht="16.5" customHeight="1">
+    <row r="962" spans="1:26" ht="16.5">
       <c r="A962" s="7"/>
       <c r="B962" s="7"/>
       <c r="C962" s="7"/>
@@ -56026,7 +56043,7 @@
       <c r="Y962" s="5"/>
       <c r="Z962" s="5"/>
     </row>
-    <row r="963" spans="1:26" ht="16.5" customHeight="1">
+    <row r="963" spans="1:26" ht="16.5">
       <c r="A963" s="7"/>
       <c r="B963" s="7"/>
       <c r="C963" s="7"/>
@@ -56054,7 +56071,7 @@
       <c r="Y963" s="5"/>
       <c r="Z963" s="5"/>
     </row>
-    <row r="964" spans="1:26" ht="16.5" customHeight="1">
+    <row r="964" spans="1:26" ht="16.5">
       <c r="A964" s="7"/>
       <c r="B964" s="7"/>
       <c r="C964" s="7"/>
@@ -56082,7 +56099,7 @@
       <c r="Y964" s="5"/>
       <c r="Z964" s="5"/>
     </row>
-    <row r="965" spans="1:26" ht="16.5" customHeight="1">
+    <row r="965" spans="1:26" ht="16.5">
       <c r="A965" s="7"/>
       <c r="B965" s="7"/>
       <c r="C965" s="7"/>
@@ -56110,7 +56127,7 @@
       <c r="Y965" s="5"/>
       <c r="Z965" s="5"/>
     </row>
-    <row r="966" spans="1:26" ht="16.5" customHeight="1">
+    <row r="966" spans="1:26" ht="16.5">
       <c r="A966" s="7"/>
       <c r="B966" s="7"/>
       <c r="C966" s="7"/>
@@ -56138,7 +56155,7 @@
       <c r="Y966" s="5"/>
       <c r="Z966" s="5"/>
     </row>
-    <row r="967" spans="1:26" ht="16.5" customHeight="1">
+    <row r="967" spans="1:26" ht="16.5">
       <c r="A967" s="7"/>
       <c r="B967" s="7"/>
       <c r="C967" s="7"/>
@@ -56166,7 +56183,7 @@
       <c r="Y967" s="5"/>
       <c r="Z967" s="5"/>
     </row>
-    <row r="968" spans="1:26" ht="16.5" customHeight="1">
+    <row r="968" spans="1:26" ht="16.5">
       <c r="A968" s="7"/>
       <c r="B968" s="7"/>
       <c r="C968" s="7"/>
@@ -56194,7 +56211,7 @@
       <c r="Y968" s="5"/>
       <c r="Z968" s="5"/>
     </row>
-    <row r="969" spans="1:26" ht="16.5" customHeight="1">
+    <row r="969" spans="1:26" ht="16.5">
       <c r="A969" s="7"/>
       <c r="B969" s="7"/>
       <c r="C969" s="7"/>
@@ -56222,7 +56239,7 @@
       <c r="Y969" s="5"/>
       <c r="Z969" s="5"/>
     </row>
-    <row r="970" spans="1:26" ht="16.5" customHeight="1">
+    <row r="970" spans="1:26" ht="16.5">
       <c r="A970" s="7"/>
       <c r="B970" s="7"/>
       <c r="C970" s="7"/>
@@ -56250,7 +56267,7 @@
       <c r="Y970" s="5"/>
       <c r="Z970" s="5"/>
     </row>
-    <row r="971" spans="1:26" ht="16.5" customHeight="1">
+    <row r="971" spans="1:26" ht="16.5">
       <c r="A971" s="7"/>
       <c r="B971" s="7"/>
       <c r="C971" s="7"/>
@@ -56278,7 +56295,7 @@
       <c r="Y971" s="5"/>
       <c r="Z971" s="5"/>
     </row>
-    <row r="972" spans="1:26" ht="16.5" customHeight="1">
+    <row r="972" spans="1:26" ht="16.5">
       <c r="A972" s="7"/>
       <c r="B972" s="7"/>
       <c r="C972" s="7"/>
@@ -56306,7 +56323,7 @@
       <c r="Y972" s="5"/>
       <c r="Z972" s="5"/>
     </row>
-    <row r="973" spans="1:26" ht="16.5" customHeight="1">
+    <row r="973" spans="1:26" ht="16.5">
       <c r="A973" s="7"/>
       <c r="B973" s="7"/>
       <c r="C973" s="7"/>
@@ -56334,7 +56351,7 @@
       <c r="Y973" s="5"/>
       <c r="Z973" s="5"/>
     </row>
-    <row r="974" spans="1:26" ht="16.5" customHeight="1">
+    <row r="974" spans="1:26" ht="16.5">
       <c r="A974" s="7"/>
       <c r="B974" s="7"/>
       <c r="C974" s="7"/>
@@ -56362,7 +56379,7 @@
       <c r="Y974" s="5"/>
       <c r="Z974" s="5"/>
     </row>
-    <row r="975" spans="1:26" ht="16.5" customHeight="1">
+    <row r="975" spans="1:26" ht="16.5">
       <c r="A975" s="7"/>
       <c r="B975" s="7"/>
       <c r="C975" s="7"/>
@@ -56390,7 +56407,7 @@
       <c r="Y975" s="5"/>
       <c r="Z975" s="5"/>
     </row>
-    <row r="976" spans="1:26" ht="16.5" customHeight="1">
+    <row r="976" spans="1:26" ht="16.5">
       <c r="A976" s="7"/>
       <c r="B976" s="7"/>
       <c r="C976" s="7"/>
@@ -56418,7 +56435,7 @@
       <c r="Y976" s="5"/>
       <c r="Z976" s="5"/>
     </row>
-    <row r="977" spans="1:26" ht="16.5" customHeight="1">
+    <row r="977" spans="1:26" ht="16.5">
       <c r="A977" s="7"/>
       <c r="B977" s="7"/>
       <c r="C977" s="7"/>
@@ -56446,7 +56463,7 @@
       <c r="Y977" s="5"/>
       <c r="Z977" s="5"/>
     </row>
-    <row r="978" spans="1:26" ht="16.5" customHeight="1">
+    <row r="978" spans="1:26" ht="16.5">
       <c r="A978" s="7"/>
       <c r="B978" s="7"/>
       <c r="C978" s="7"/>
@@ -56474,7 +56491,7 @@
       <c r="Y978" s="5"/>
       <c r="Z978" s="5"/>
     </row>
-    <row r="979" spans="1:26" ht="16.5" customHeight="1">
+    <row r="979" spans="1:26" ht="16.5">
       <c r="A979" s="7"/>
       <c r="B979" s="7"/>
       <c r="C979" s="7"/>
@@ -56502,7 +56519,7 @@
       <c r="Y979" s="5"/>
       <c r="Z979" s="5"/>
     </row>
-    <row r="980" spans="1:26" ht="16.5" customHeight="1">
+    <row r="980" spans="1:26" ht="16.5">
       <c r="A980" s="7"/>
       <c r="B980" s="7"/>
       <c r="C980" s="7"/>
@@ -56530,7 +56547,7 @@
       <c r="Y980" s="5"/>
       <c r="Z980" s="5"/>
     </row>
-    <row r="981" spans="1:26" ht="16.5" customHeight="1">
+    <row r="981" spans="1:26" ht="16.5">
       <c r="A981" s="7"/>
       <c r="B981" s="7"/>
       <c r="C981" s="7"/>
@@ -56558,7 +56575,7 @@
       <c r="Y981" s="5"/>
       <c r="Z981" s="5"/>
     </row>
-    <row r="982" spans="1:26" ht="16.5" customHeight="1">
+    <row r="982" spans="1:26" ht="16.5">
       <c r="A982" s="7"/>
       <c r="B982" s="7"/>
       <c r="C982" s="7"/>
@@ -56586,7 +56603,7 @@
       <c r="Y982" s="5"/>
       <c r="Z982" s="5"/>
     </row>
-    <row r="983" spans="1:26" ht="16.5" customHeight="1">
+    <row r="983" spans="1:26" ht="16.5">
       <c r="A983" s="7"/>
       <c r="B983" s="7"/>
       <c r="C983" s="7"/>
@@ -56614,7 +56631,7 @@
       <c r="Y983" s="5"/>
       <c r="Z983" s="5"/>
     </row>
-    <row r="984" spans="1:26" ht="16.5" customHeight="1">
+    <row r="984" spans="1:26" ht="16.5">
       <c r="A984" s="7"/>
       <c r="B984" s="7"/>
       <c r="C984" s="7"/>
@@ -56642,7 +56659,7 @@
       <c r="Y984" s="5"/>
       <c r="Z984" s="5"/>
     </row>
-    <row r="985" spans="1:26" ht="16.5" customHeight="1">
+    <row r="985" spans="1:26" ht="16.5">
       <c r="A985" s="7"/>
       <c r="B985" s="7"/>
       <c r="C985" s="7"/>
@@ -56670,7 +56687,7 @@
       <c r="Y985" s="5"/>
       <c r="Z985" s="5"/>
     </row>
-    <row r="986" spans="1:26" ht="16.5" customHeight="1">
+    <row r="986" spans="1:26" ht="16.5">
       <c r="A986" s="7"/>
       <c r="B986" s="7"/>
       <c r="C986" s="7"/>
@@ -56698,7 +56715,7 @@
       <c r="Y986" s="5"/>
       <c r="Z986" s="5"/>
     </row>
-    <row r="987" spans="1:26" ht="16.5" customHeight="1">
+    <row r="987" spans="1:26" ht="16.5">
       <c r="A987" s="7"/>
       <c r="B987" s="7"/>
       <c r="C987" s="7"/>
@@ -56726,7 +56743,7 @@
       <c r="Y987" s="5"/>
       <c r="Z987" s="5"/>
     </row>
-    <row r="988" spans="1:26" ht="16.5" customHeight="1">
+    <row r="988" spans="1:26" ht="16.5">
       <c r="A988" s="7"/>
       <c r="B988" s="7"/>
       <c r="C988" s="7"/>
@@ -56754,7 +56771,7 @@
       <c r="Y988" s="5"/>
       <c r="Z988" s="5"/>
     </row>
-    <row r="989" spans="1:26" ht="16.5" customHeight="1">
+    <row r="989" spans="1:26" ht="16.5">
       <c r="A989" s="7"/>
       <c r="B989" s="7"/>
       <c r="C989" s="7"/>
@@ -56782,7 +56799,7 @@
       <c r="Y989" s="5"/>
       <c r="Z989" s="5"/>
     </row>
-    <row r="990" spans="1:26" ht="16.5" customHeight="1">
+    <row r="990" spans="1:26" ht="16.5">
       <c r="A990" s="7"/>
       <c r="B990" s="7"/>
       <c r="C990" s="7"/>
@@ -56810,7 +56827,7 @@
       <c r="Y990" s="5"/>
       <c r="Z990" s="5"/>
     </row>
-    <row r="991" spans="1:26" ht="16.5" customHeight="1">
+    <row r="991" spans="1:26" ht="16.5">
       <c r="A991" s="7"/>
       <c r="B991" s="7"/>
       <c r="C991" s="7"/>
@@ -56838,7 +56855,7 @@
       <c r="Y991" s="5"/>
       <c r="Z991" s="5"/>
     </row>
-    <row r="992" spans="1:26" ht="16.5" customHeight="1">
+    <row r="992" spans="1:26" ht="16.5">
       <c r="A992" s="7"/>
       <c r="B992" s="7"/>
       <c r="C992" s="7"/>
@@ -56866,7 +56883,7 @@
       <c r="Y992" s="5"/>
       <c r="Z992" s="5"/>
     </row>
-    <row r="993" spans="1:26" ht="16.5" customHeight="1">
+    <row r="993" spans="1:26" ht="16.5">
       <c r="A993" s="7"/>
       <c r="B993" s="7"/>
       <c r="C993" s="7"/>
@@ -56894,7 +56911,7 @@
       <c r="Y993" s="5"/>
       <c r="Z993" s="5"/>
     </row>
-    <row r="994" spans="1:26" ht="16.5" customHeight="1">
+    <row r="994" spans="1:26" ht="16.5">
       <c r="A994" s="7"/>
       <c r="B994" s="7"/>
       <c r="C994" s="7"/>
@@ -56922,7 +56939,7 @@
       <c r="Y994" s="5"/>
       <c r="Z994" s="5"/>
     </row>
-    <row r="995" spans="1:26" ht="16.5" customHeight="1">
+    <row r="995" spans="1:26" ht="16.5">
       <c r="A995" s="7"/>
       <c r="B995" s="7"/>
       <c r="C995" s="7"/>
@@ -56950,7 +56967,7 @@
       <c r="Y995" s="5"/>
       <c r="Z995" s="5"/>
     </row>
-    <row r="996" spans="1:26" ht="16.5" customHeight="1">
+    <row r="996" spans="1:26" ht="16.5">
       <c r="A996" s="7"/>
       <c r="B996" s="7"/>
       <c r="C996" s="7"/>
@@ -56978,7 +56995,7 @@
       <c r="Y996" s="5"/>
       <c r="Z996" s="5"/>
     </row>
-    <row r="997" spans="1:26" ht="16.5" customHeight="1">
+    <row r="997" spans="1:26" ht="16.5">
       <c r="A997" s="7"/>
       <c r="B997" s="7"/>
       <c r="C997" s="7"/>
@@ -57006,7 +57023,7 @@
       <c r="Y997" s="5"/>
       <c r="Z997" s="5"/>
     </row>
-    <row r="998" spans="1:26" ht="16.5" customHeight="1">
+    <row r="998" spans="1:26" ht="16.5">
       <c r="A998" s="7"/>
       <c r="B998" s="7"/>
       <c r="C998" s="7"/>
@@ -57034,7 +57051,7 @@
       <c r="Y998" s="5"/>
       <c r="Z998" s="5"/>
     </row>
-    <row r="999" spans="1:26" ht="16.5" customHeight="1">
+    <row r="999" spans="1:26" ht="16.5">
       <c r="A999" s="7"/>
       <c r="B999" s="7"/>
       <c r="C999" s="7"/>
@@ -57062,7 +57079,7 @@
       <c r="Y999" s="5"/>
       <c r="Z999" s="5"/>
     </row>
-    <row r="1000" spans="1:26" ht="16.5" customHeight="1">
+    <row r="1000" spans="1:26" ht="16.5">
       <c r="A1000" s="7"/>
       <c r="B1000" s="7"/>
       <c r="C1000" s="7"/>
@@ -57098,7 +57115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -57115,16 +57132,16 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>31</v>
+      <c r="D1" s="8" t="s">
+        <v>26</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>32</v>
+      <c r="E1" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -58140,7 +58157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58153,44 +58170,44 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
@@ -58198,13 +58215,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D25C7AE-6DB8-41EF-AB6E-41523D712C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE0312F-086D-4552-8BCF-01F348CCDCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="4875" windowWidth="17310" windowHeight="9795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,8 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -69,8 +58,92 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>jwl55</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{89F4C14C-C56B-4FAF-AAE3-92599164F05A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1 : Text
+2 : Image
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{0AB67B95-93B7-4817-ACF0-4C6AA5FE335C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>정지될</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>지점에서</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Break </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">작성
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="65">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -222,25 +295,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>평온한 마을인 라노스마을
-해가 높이 떠올랐고, 바람은 따뜻했다.
-나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>마을 사람들이 특별히 따돌리진 않았다
-하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.
-나는 그게 더 편했다.
-누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>그날 아침도 평범했다,
-언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.
-모두가 자신만의 하루를 살고 있던 평범한 날이였다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>하지만 나는 이상한 기척을 순간 느꼈다…</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -249,38 +303,229 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>멀리서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보이는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>흙먼지와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>짐승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>울음소리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑작스러운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>비명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>마을 입구 쪽이였다.
-사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.</t>
+    <t>그리고 얼마 지나지 않아 마을은 완전히 제 모습이 아니게 되었다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>그리고 그 잠깐의 고요함은 오래가지 않았다.
-사람들이 비명을 지르며 도망치기 시작했다.
-창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.
-그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.</t>
+    <t>"또…. 나만…."</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>거칠게 짖는 괴수들,
-날이 빠진 무기를 들고도 거침없이 웃는 산적들.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>평온한 마을인 라노스마을\n
+해가 높이 떠올랐고, 바람은 따뜻했다.\n
+나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.</t>
   </si>
   <si>
-    <t>그것은 단순한 약탈이 아니었다.
-말살에 가까웠다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>마을 사람들이 특별히 따돌리진 않았다\n
+하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.\n
+나는 그게 더 편했다.\n
+누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..</t>
   </si>
   <si>
-    <t>소년은 그 광경을 멍하니 바라보고만 있었다.
-누군가의 비명이 들려왔다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>그날 아침도 평범했다,\n
+언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.\n
+모두가 자신만의 하루를 살고 있던 평범한 날이였다.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>마을 입구 쪽이였다.\n
+사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.</t>
+  </si>
+  <si>
+    <t>그리고 그 잠깐의 고요함은 오래가지 않았다.\n
+사람들이 비명을 지르며 도망치기 시작했다.\n
+창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.\n
+그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.</t>
+  </si>
+  <si>
+    <t>거칠게 짖는 괴수들,\n
+날이 빠진 무기를 들고도 거침없이 웃는 산적들.</t>
+  </si>
+  <si>
+    <t>그것은 단순한 약탈이 아니었다.\n
+말살에 가까웠다…</t>
+  </si>
+  <si>
+    <t>나는 그 광경을 멍하니 바라보고만 있었다.\n
+누군가의 비명이 들려왔다.</t>
+  </si>
+  <si>
+    <t>마치… 이 모든 장면을 어디선가 본 것처럼 \n
+기억도, 감정도, 이 상황을 처음 겪는 상황이 아닌거 같았다.</t>
+  </si>
+  <si>
+    <t>나는 무너진 담벼락 옆에 주저앉아 숨을 내쉬었다.\n
+손에는 작은 흠집만 남았고, 주변은 적막뿐이였다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그의 눈동자는 텅 비어 있었다.\n
+</t>
+  </si>
+  <si>
+    <t>모두가 흩어졌고, 쓰러지고, 불탔다.\n
+그리고 남겨진 자는, 또다시 나 혼자였다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -288,7 +533,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +564,29 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
@@ -399,7 +667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -440,6 +708,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -28824,7 +29098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -28894,8 +29168,8 @@
         <f t="shared" ref="D2:D22" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>48</v>
+      <c r="E2" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>42</v>
@@ -28921,7 +29195,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="90">
+    <row r="3" spans="1:26" ht="75">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -28935,8 +29209,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_2</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>49</v>
+      <c r="E3" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>42</v>
@@ -28962,7 +29236,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="75">
+    <row r="4" spans="1:26" ht="60">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -28976,8 +29250,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_3</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>50</v>
+      <c r="E4" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>42</v>
@@ -29018,7 +29292,7 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>42</v>
@@ -29059,7 +29333,7 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>42</v>
@@ -29099,8 +29373,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>53</v>
+      <c r="E7" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>42</v>
@@ -29126,7 +29400,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="45">
+    <row r="8" spans="1:26" ht="30">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -29140,8 +29414,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_7</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>54</v>
+      <c r="E8" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>42</v>
@@ -29167,7 +29441,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="90">
+    <row r="9" spans="1:26" ht="75">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -29181,8 +29455,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_8</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>55</v>
+      <c r="E9" s="15" t="s">
+        <v>57</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>42</v>
@@ -29222,8 +29496,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_9</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>56</v>
+      <c r="E10" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>47</v>
@@ -29263,8 +29537,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_10</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>57</v>
+      <c r="E11" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>42</v>
@@ -29304,8 +29578,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>58</v>
+      <c r="E12" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>42</v>
@@ -29331,7 +29605,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" ht="16.5">
+    <row r="13" spans="1:26" ht="30">
       <c r="A13" s="7">
         <v>1</v>
       </c>
@@ -29345,8 +29619,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>59</v>
+      <c r="E13" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>42</v>
@@ -29386,7 +29660,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="F14" s="5" t="s">
         <v>42</v>
       </c>
@@ -29411,7 +29687,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="16.5">
+    <row r="15" spans="1:26" ht="33">
       <c r="A15" s="7">
         <v>1</v>
       </c>
@@ -29425,7 +29701,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_14</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="F15" s="5" t="s">
         <v>42</v>
       </c>
@@ -29450,7 +29728,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" ht="16.5">
+    <row r="16" spans="1:26" ht="33">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -29464,7 +29742,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_15</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="F16" s="5" t="s">
         <v>42</v>
       </c>
@@ -29503,7 +29783,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_16</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="F17" s="5" t="s">
         <v>42</v>
       </c>
@@ -29528,7 +29810,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="16.5">
+    <row r="18" spans="1:26" ht="33">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -29542,7 +29824,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_17</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="F18" s="5" t="s">
         <v>42</v>
       </c>
@@ -57111,6 +57395,7 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D25C7AE-6DB8-41EF-AB6E-41523D712C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2D25C7AE-6DB8-41EF-AB6E-41523D712C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8111B971-3272-4478-B261-DBB2B1F9F5FA}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="4875" windowWidth="17310" windowHeight="9795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26070" yWindow="2145" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -222,65 +222,2944 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>평온한 마을인 라노스마을
-해가 높이 떠올랐고, 바람은 따뜻했다.
-나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.</t>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>마을 사람들이 특별히 따돌리진 않았다
-하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.
-나는 그게 더 편했다.
-누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평온한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라노스마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+해가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠올랐고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조용한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변함없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살아가고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>그날 아침도 평범했다,
-언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.
-모두가 자신만의 하루를 살고 있던 평범한 날이였다.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특별히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따돌리진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당신을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시선에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어딘가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어려운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거리감이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>편했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누구와도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엮이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누군가를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잃는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테니까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>..\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>하지만 나는 이상한 기척을 순간 느꼈다…</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아침도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평범했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>언제나처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우물가에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>길었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>식사를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자신만의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하루를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평범한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날이였다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>"뭐지….?"</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기척을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>느꼈다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,</t>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.?"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>마을 입구 쪽이였다.
-사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멀리서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보이는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흙먼지와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>울음소리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갑작스러운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>그리고 그 잠깐의 고요함은 오래가지 않았다.
-사람들이 비명을 지르며 도망치기 시작했다.
-창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.
-그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쪽이였다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당황한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표정으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그쪽을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>거칠게 짖는 괴수들,
-날이 빠진 무기를 들고도 거침없이 웃는 산적들.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잠깐의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고요함은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오래가지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비명을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지르며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도망치기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시작했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>창백한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얼굴이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달려오는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허둥지둥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챙기는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뒤를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>망토를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뒤집어쓴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이들과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기괴한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형체들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나타났다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>그것은 단순한 약탈이 아니었다.
-말살에 가까웠다…</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거칠게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짖는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>괴수들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빠진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들고도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거침없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>웃는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>산적들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>소년은 그 광경을 멍하니 바라보고만 있었다.
-누군가의 비명이 들려왔다.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그것은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단순한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약탈이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말살에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가까웠다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소년은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>광경을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멍하니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바라보고만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누군가의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비명이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들려왔다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -288,7 +3167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,6 +3202,34 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -399,7 +3306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -436,10 +3343,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,9 +3862,7 @@
       <c r="F7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="G7" s="6"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -28880,7 +31791,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" ht="60">
+    <row r="2" spans="1:26" ht="66">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -28894,8 +31805,8 @@
         <f t="shared" ref="D2:D22" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>48</v>
+      <c r="E2" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>42</v>
@@ -28921,7 +31832,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="90">
+    <row r="3" spans="1:26" ht="82.5">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -28935,8 +31846,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_2</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>49</v>
+      <c r="E3" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>42</v>
@@ -28962,7 +31873,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="75">
+    <row r="4" spans="1:26" ht="66">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -28976,8 +31887,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_3</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>50</v>
+      <c r="E4" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>42</v>
@@ -29017,8 +31928,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_4</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>51</v>
+      <c r="E5" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>42</v>
@@ -29058,8 +31969,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>52</v>
+      <c r="E6" s="16" t="s">
+        <v>53</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>42</v>
@@ -29085,7 +31996,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="30">
+    <row r="7" spans="1:26" ht="33">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -29099,8 +32010,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>53</v>
+      <c r="E7" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>42</v>
@@ -29126,7 +32037,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="45">
+    <row r="8" spans="1:26" ht="49.5">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -29140,8 +32051,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_7</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>54</v>
+      <c r="E8" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>42</v>
@@ -29167,7 +32078,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="90">
+    <row r="9" spans="1:26" ht="82.5">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -29181,8 +32092,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_8</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>55</v>
+      <c r="E9" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>42</v>
@@ -29208,7 +32119,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="30">
+    <row r="10" spans="1:26" ht="33">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -29222,8 +32133,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_9</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>56</v>
+      <c r="E10" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>47</v>
@@ -29249,7 +32160,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="30">
+    <row r="11" spans="1:26" ht="33">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -29263,8 +32174,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_10</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>57</v>
+      <c r="E11" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>42</v>
@@ -29290,7 +32201,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" ht="30">
+    <row r="12" spans="1:26" ht="33">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -29304,8 +32215,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>58</v>
+      <c r="E12" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>42</v>
@@ -29345,8 +32256,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>59</v>
+      <c r="E13" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>42</v>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyh\Desktop\주환\Unity\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2D25C7AE-6DB8-41EF-AB6E-41523D712C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8111B971-3272-4478-B261-DBB2B1F9F5FA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3218750-F7B9-4D1C-BC92-1242F2398569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26070" yWindow="2145" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -115,12 +115,6 @@
   </si>
   <si>
     <t>MainScript_1_1_3</t>
-  </si>
-  <si>
-    <t>MainScript_1_1_4</t>
-  </si>
-  <si>
-    <t>MainScene_1_1_4</t>
   </si>
   <si>
     <t>MainScript_1_1_5</t>
@@ -199,1419 +193,70 @@
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_1_8</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScene_1_1_8</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_9</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>MainScript_1_1_10</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>평온한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마을인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>라노스마을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-해가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>높이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>떠올랐고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바람은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따뜻했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조용한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>속에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오늘도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변함없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>숨을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>죽이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>살아가고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>MainScript_1_1_11</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>특별히</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따돌리진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않았다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당신을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>향한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시선에는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어딘가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설명하기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어려운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>거리감이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>편했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누구와도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>엮이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않으면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누군가를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잃는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테니까</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>..\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>평온한 마을인 라노스마을
+해가 높이 떠올랐고, 바람은 따뜻했다.
+나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그날</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아침도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>평범했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>언제나처럼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우물가에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>물을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>길었고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>남은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>식사를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정리했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모두가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자신만의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하루를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>살고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있던</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>평범한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날이였다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>마을 사람들이 특별히 따돌리진 않았다
+하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.
+나는 그게 더 편했다.
+누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이상한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기척을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>느꼈다</t>
-    </r>
+    <t>그날 아침도 평범했다,
+언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.
+모두가 자신만의 하루를 살고 있던 평범한 날이였다.</t>
+  </si>
+  <si>
+    <t>하지만 나는 이상한 기척을 순간 느꼈다…</t>
+  </si>
+  <si>
+    <t>"뭐지….?"</t>
+  </si>
+  <si>
+    <t>멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,</t>
+  </si>
+  <si>
+    <t>마을 입구 쪽이였다.
+사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.</t>
+  </si>
+  <si>
+    <t>그리고 그 잠깐의 고요함은 오래가지 않았다.
+사람들이 비명을 지르며 도망치기 시작했다.
+창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.
+그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.</t>
+  </si>
+  <si>
+    <t>거칠게 짖는 괴수들,
+날이 빠진 무기를 들고도 거침없이 웃는 산적들.</t>
+  </si>
+  <si>
+    <t>그것은 단순한 약탈이 아니었다.
+말살에 가까웠다…</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1620,1374 +265,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뭐지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.?"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>멀리서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보이는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>흙먼지와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>짐승</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>울음소리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>갑작스러운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쪽이였다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>둘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당황한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표정으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그쪽을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바라보고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그리고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잠깐의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고요함은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오래가지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않았다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비명을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지르며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>도망치기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시작했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>창백한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>얼굴이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>달려오는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>허둥지둥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>짐을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>챙기는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>노인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그들의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뒤를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>망토를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뒤집어쓴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이들과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기괴한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>형체들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나타났다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>거칠게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>짖는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>괴수들</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빠진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무기를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>들고도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>거침없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>웃는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>산적들</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그것은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단순한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>약탈이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아니었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>말살에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가까웠다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소년은</t>
+      <t>나는</t>
     </r>
     <r>
       <rPr>
@@ -3097,7 +375,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.\n
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -3105,10 +383,10 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
+        <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>누군가의</t>
+      <t>마치…</t>
     </r>
     <r>
       <rPr>
@@ -3116,7 +394,6 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3125,53 +402,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
+        <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>비명이</t>
+      <t>이 모든 장면을 어디선가 본 것처럼.
+기억도, 감정도, 이 상황을 처음 겪는 사람의 것과는 달랐다.</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>들려왔다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3229,7 +485,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="3"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3308,50 +564,50 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3574,7 +830,7 @@
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
     <col min="2" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.85546875" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
@@ -3657,7 +913,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -3738,18 +994,10 @@
         <v>14</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="3"/>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="3"/>
@@ -3782,7 +1030,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -3821,7 +1069,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -3860,7 +1108,7 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="3"/>
@@ -3899,7 +1147,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -3938,7 +1186,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -3976,7 +1224,9 @@
         <v>MainScene_1_1_9</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -4013,6 +1263,9 @@
         <v>MainScene_1_1_10</v>
       </c>
       <c r="E11" s="3"/>
+      <c r="F11" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -31727,7 +28980,7 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -31743,7 +28996,7 @@
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" customWidth="1"/>
-    <col min="5" max="5" width="56.7109375" customWidth="1"/>
+    <col min="5" max="5" width="58.42578125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="26" width="8.7109375" customWidth="1"/>
@@ -31760,16 +29013,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -31805,11 +29058,11 @@
         <f t="shared" ref="D2:D22" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>49</v>
+      <c r="E2" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -31846,11 +29099,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_2</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>50</v>
+      <c r="E3" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -31887,11 +29140,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_3</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>51</v>
+      <c r="E4" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -31928,11 +29181,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_4</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>52</v>
+      <c r="E5" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -31969,11 +29222,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>53</v>
+      <c r="E6" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -32010,11 +29263,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>54</v>
+      <c r="E7" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -32051,11 +29304,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_7</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>55</v>
+      <c r="E8" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -32092,11 +29345,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_8</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>56</v>
+      <c r="E9" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -32133,11 +29386,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_9</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>57</v>
+      <c r="E10" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -32174,11 +29427,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_10</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>58</v>
+      <c r="E11" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -32201,7 +29454,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" ht="33">
+    <row r="12" spans="1:26" ht="66">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -32215,11 +29468,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>59</v>
+      <c r="E12" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -32256,11 +29509,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>48</v>
-      </c>
+      <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -32297,9 +29548,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
       </c>
-      <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -32338,7 +29588,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -32377,7 +29627,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -32416,7 +29666,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -32455,7 +29705,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -32494,7 +29744,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -32533,7 +29783,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -32572,7 +29822,7 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -32611,7 +29861,7 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -60019,7 +57269,7 @@
       <c r="Z1000" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -60030,11 +57280,11 @@
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -60043,16 +57293,16 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
@@ -61061,7 +58311,7 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -61081,58 +58331,58 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1"/>
@@ -62132,7 +59382,7 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyh\Desktop\주환\Unity\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3218750-F7B9-4D1C-BC92-1242F2398569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,12 +38,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -70,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -214,47 +213,90 @@
     <t>MainScript_1_1_11</t>
   </si>
   <si>
-    <t>평온한 마을인 라노스마을
+    <t xml:space="preserve">평온한 마을인 라노스마을
 해가 높이 떠올랐고, 바람은 따뜻했다.
-나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.</t>
+나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>마을 사람들이 특별히 따돌리진 않았다
+    <t xml:space="preserve">마을 사람들이 특별히 따돌리진 않았다
 하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.
 나는 그게 더 편했다.
-누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..</t>
+누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>그날 아침도 평범했다,
+    <t xml:space="preserve">그날 아침도 평범했다,
 언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.
-모두가 자신만의 하루를 살고 있던 평범한 날이였다.</t>
+모두가 자신만의 하루를 살고 있던 평범한 날이였다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>하지만 나는 이상한 기척을 순간 느꼈다…</t>
+    <t xml:space="preserve">하지만 나는 이상한 기척을 순간 느꼈다…
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"뭐지….?"</t>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>뭐지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">….?"
+</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,</t>
+    <t xml:space="preserve">멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>마을 입구 쪽이였다.
-사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.</t>
+    <t xml:space="preserve">마을 입구 쪽이였다.
+사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>그리고 그 잠깐의 고요함은 오래가지 않았다.
+    <t xml:space="preserve">그리고 그 잠깐의 고요함은 오래가지 않았다.
 사람들이 비명을 지르며 도망치기 시작했다.
 창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.
-그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.</t>
+그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>거칠게 짖는 괴수들,
-날이 빠진 무기를 들고도 거침없이 웃는 산적들.</t>
+    <t xml:space="preserve">거칠게 짖는 괴수들,
+날이 빠진 무기를 들고도 거침없이 웃는 산적들.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>그것은 단순한 약탈이 아니었다.
-말살에 가까웠다…</t>
+    <t xml:space="preserve">그것은 단순한 약탈이 아니었다.
+말살에 가까웠다…
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -405,16 +447,25 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>이 모든 장면을 어디선가 본 것처럼.
-기억도, 감정도, 이 상황을 처음 겪는 사람의 것과는 달랐다.</t>
+      <t xml:space="preserve">이 모든 장면을 어디선가 본 것처럼.
+기억도, 감정도, 이 상황을 처음 겪는 사람의 것과는 달랐다.
+</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -562,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -600,9 +651,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -824,7 +872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -28988,7 +29036,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -29044,7 +29092,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" ht="66">
+    <row r="2" spans="1:26" ht="75">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -29064,7 +29112,9 @@
       <c r="F2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -29085,7 +29135,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="82.5">
+    <row r="3" spans="1:26" ht="90">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -29105,7 +29155,9 @@
       <c r="F3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -29126,7 +29178,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="66">
+    <row r="4" spans="1:26" ht="60">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -29146,7 +29198,9 @@
       <c r="F4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -29167,7 +29221,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" spans="1:26" ht="16.5">
+    <row r="5" spans="1:26" ht="30">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -29181,13 +29235,15 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_4</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -29208,7 +29264,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" spans="1:26" ht="16.5">
+    <row r="6" spans="1:26" ht="30">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -29222,13 +29278,15 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -29249,7 +29307,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="33">
+    <row r="7" spans="1:26" ht="30">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -29269,7 +29327,9 @@
       <c r="F7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -29290,7 +29350,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="49.5">
+    <row r="8" spans="1:26" ht="45">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -29310,7 +29370,9 @@
       <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -29331,7 +29393,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="82.5">
+    <row r="9" spans="1:26" ht="90">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -29351,7 +29413,9 @@
       <c r="F9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -29372,7 +29436,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="33">
+    <row r="10" spans="1:26" ht="45">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -29392,7 +29456,9 @@
       <c r="F10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -29413,7 +29479,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="33">
+    <row r="11" spans="1:26" ht="45">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -29433,7 +29499,9 @@
       <c r="F11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -29468,13 +29536,15 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>56</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -57276,7 +57346,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58318,7 +58388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195" activeTab="1"/>
+    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -460,6 +460,27 @@
   <si>
     <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_12</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_13</t>
+  </si>
+  <si>
+    <t>monster_002</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 모험으로 떠난다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_14</t>
   </si>
 </sst>
 </file>
@@ -956,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D11" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D14" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
@@ -1198,9 +1219,13 @@
         <v>19</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -1336,12 +1361,23 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="4">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_11</v>
+      </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -1364,12 +1400,23 @@
       <c r="Z12" s="3"/>
     </row>
     <row r="13" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="4">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_12</v>
+      </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -1392,12 +1439,23 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="4">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_13</v>
+      </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -29579,9 +29637,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="F13" s="5" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -29617,6 +29677,9 @@
       <c r="D14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
@@ -29660,7 +29723,9 @@
       <c r="F15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195"/>
+    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195" activeTab="1"/>
+    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_FF4B7E40354D6F4EED092ADC9272D2B65D97BDCA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C700B4-B184-46E4-9838-C6117054E12C}"/>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="405" windowWidth="15330" windowHeight="15195"/>
+    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,12 +39,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -486,7 +487,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -893,7 +894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1219,13 +1220,9 @@
         <v>19</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="H8" s="5"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="J8" s="5"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -29094,7 +29091,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -29600,9 +29597,7 @@
       <c r="F12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -29684,7 +29679,9 @@
       <c r="F14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -29723,9 +29720,7 @@
       <c r="F15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
@@ -57411,7 +57406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58453,7 +58448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_FF4B7E40354D6F4EED092ADC9272D2B65D97BDCA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C700B4-B184-46E4-9838-C6117054E12C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,18 +38,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>======
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -193,10 +193,6 @@
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_1_9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -481,13 +477,60 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MainScript_1_1_14</t>
+    <t>MainScript_1_1_4</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_9</t>
+  </si>
+  <si>
+    <t>MainScript_2_1 테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_2  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_3  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_4  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_5  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_6  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_7  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_8  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_9  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_10  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_11  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -894,7 +937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -978,12 +1021,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D14" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D25" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1100,7 +1143,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1139,7 +1182,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1178,7 +1221,7 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="3"/>
@@ -1217,7 +1260,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="5"/>
@@ -1256,7 +1299,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -1295,7 +1338,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1334,7 +1377,7 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1373,7 +1416,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -1412,7 +1455,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -1451,7 +1494,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -1475,12 +1518,24 @@
       <c r="Z14" s="3"/>
     </row>
     <row r="15" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3"/>
+      <c r="A15" s="4">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_1</v>
+      </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3" t="str">
+        <f>Main_Script_Master_Main!D15</f>
+        <v>MainScript_1_2_1</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -1503,12 +1558,24 @@
       <c r="Z15" s="3"/>
     </row>
     <row r="16" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3"/>
+      <c r="A16" s="4">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_2</v>
+      </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3" t="str">
+        <f>Main_Script_Master_Main!D16</f>
+        <v>MainScript_1_2_2</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -1531,12 +1598,24 @@
       <c r="Z16" s="3"/>
     </row>
     <row r="17" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3"/>
+      <c r="A17" s="4">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_3</v>
+      </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3" t="str">
+        <f>Main_Script_Master_Main!D17</f>
+        <v>MainScript_1_2_3</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1559,12 +1638,24 @@
       <c r="Z17" s="3"/>
     </row>
     <row r="18" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="3"/>
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_4</v>
+      </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3" t="str">
+        <f>Main_Script_Master_Main!D18</f>
+        <v>MainScript_1_2_4</v>
+      </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1587,12 +1678,24 @@
       <c r="Z18" s="3"/>
     </row>
     <row r="19" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="3"/>
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_5</v>
+      </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="str">
+        <f>Main_Script_Master_Main!D19</f>
+        <v>MainScript_1_2_5</v>
+      </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -1615,12 +1718,24 @@
       <c r="Z19" s="3"/>
     </row>
     <row r="20" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="3"/>
+      <c r="A20" s="4">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_6</v>
+      </c>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3" t="str">
+        <f>Main_Script_Master_Main!D20</f>
+        <v>MainScript_1_2_6</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -1643,12 +1758,24 @@
       <c r="Z20" s="3"/>
     </row>
     <row r="21" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="3"/>
+      <c r="A21" s="4">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_7</v>
+      </c>
       <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3" t="str">
+        <f>Main_Script_Master_Main!D21</f>
+        <v>MainScript_1_2_7</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1671,12 +1798,24 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="3"/>
+      <c r="A22" s="4">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_8</v>
+      </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3" t="str">
+        <f>Main_Script_Master_Main!D22</f>
+        <v>MainScript_1_2_8</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -1699,12 +1838,24 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="3"/>
+      <c r="A23" s="4">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4">
+        <v>9</v>
+      </c>
+      <c r="D23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_9</v>
+      </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="str">
+        <f>Main_Script_Master_Main!D23</f>
+        <v>MainScript_1_2_9</v>
+      </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -1727,12 +1878,24 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="3"/>
+      <c r="A24" s="4">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_10</v>
+      </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="str">
+        <f>Main_Script_Master_Main!D24</f>
+        <v>MainScript_1_2_10</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -1755,12 +1918,24 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="3"/>
+      <c r="A25" s="4">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_11</v>
+      </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="str">
+        <f>Main_Script_Master_Main!D25</f>
+        <v>MainScript_1_2_11</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -29091,8 +29266,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -29158,17 +29333,17 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D22" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D25" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -29205,13 +29380,13 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -29248,13 +29423,13 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -29291,13 +29466,13 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -29334,13 +29509,13 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -29377,13 +29552,13 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -29420,13 +29595,13 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -29463,13 +29638,13 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -29506,13 +29681,13 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -29549,13 +29724,13 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -29592,7 +29767,7 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>40</v>
@@ -29633,10 +29808,10 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -29674,13 +29849,13 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -29707,16 +29882,18 @@
         <v>1</v>
       </c>
       <c r="B15" s="7">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7">
         <v>1</v>
       </c>
-      <c r="C15" s="7">
-        <v>14</v>
+      <c r="D15" s="5" t="str">
+        <f>CONCATENATE("MainScript_",A15,"_",B15,"_",C15)</f>
+        <v>MainScript_1_2_1</v>
       </c>
-      <c r="D15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_1_14</v>
+      <c r="E15" s="5" t="s">
+        <v>65</v>
       </c>
-      <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
         <v>40</v>
       </c>
@@ -29746,16 +29923,18 @@
         <v>1</v>
       </c>
       <c r="B16" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="7">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_1_15</v>
+        <v>MainScript_1_2_2</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="F16" s="5" t="s">
         <v>40</v>
       </c>
@@ -29785,16 +29964,18 @@
         <v>1</v>
       </c>
       <c r="B17" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="7">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_1_16</v>
+        <v>MainScript_1_2_3</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="F17" s="5" t="s">
         <v>40</v>
       </c>
@@ -29824,16 +30005,18 @@
         <v>1</v>
       </c>
       <c r="B18" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="7">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_1_17</v>
+        <v>MainScript_1_2_4</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="F18" s="5" t="s">
         <v>40</v>
       </c>
@@ -29863,16 +30046,18 @@
         <v>1</v>
       </c>
       <c r="B19" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="7">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_1_18</v>
+        <v>MainScript_1_2_5</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="F19" s="5" t="s">
         <v>40</v>
       </c>
@@ -29902,16 +30087,18 @@
         <v>1</v>
       </c>
       <c r="B20" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_1_19</v>
+        <v>MainScript_1_2_6</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
       </c>
@@ -29941,16 +30128,18 @@
         <v>1</v>
       </c>
       <c r="B21" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="7">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_1_20</v>
+        <v>MainScript_1_2_7</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
       </c>
@@ -29980,16 +30169,18 @@
         <v>1</v>
       </c>
       <c r="B22" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="7">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D22" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_1_21</v>
+        <f>CONCATENATE("MainScript_",A22,"_",B22,"_",C22)</f>
+        <v>MainScript_1_2_8</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
       </c>
@@ -30015,12 +30206,25 @@
       <c r="Z22" s="5"/>
     </row>
     <row r="23" spans="1:26" ht="16.5">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2</v>
+      </c>
+      <c r="C23" s="7">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_9</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -30043,12 +30247,25 @@
       <c r="Z23" s="5"/>
     </row>
     <row r="24" spans="1:26" ht="16.5">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="7">
+        <v>2</v>
+      </c>
+      <c r="C24" s="7">
+        <v>10</v>
+      </c>
+      <c r="D24" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_10</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -30071,12 +30288,25 @@
       <c r="Z24" s="5"/>
     </row>
     <row r="25" spans="1:26" ht="16.5">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7">
+        <v>2</v>
+      </c>
+      <c r="C25" s="7">
+        <v>11</v>
+      </c>
+      <c r="D25" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_11</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -57370,34 +57600,6 @@
       <c r="Y999" s="5"/>
       <c r="Z999" s="5"/>
     </row>
-    <row r="1000" spans="1:26" ht="16.5">
-      <c r="A1000" s="7"/>
-      <c r="B1000" s="7"/>
-      <c r="C1000" s="7"/>
-      <c r="D1000" s="5"/>
-      <c r="E1000" s="5"/>
-      <c r="F1000" s="5"/>
-      <c r="G1000" s="5"/>
-      <c r="H1000" s="5"/>
-      <c r="I1000" s="5"/>
-      <c r="J1000" s="5"/>
-      <c r="K1000" s="5"/>
-      <c r="L1000" s="5"/>
-      <c r="M1000" s="5"/>
-      <c r="N1000" s="5"/>
-      <c r="O1000" s="5"/>
-      <c r="P1000" s="5"/>
-      <c r="Q1000" s="5"/>
-      <c r="R1000" s="5"/>
-      <c r="S1000" s="5"/>
-      <c r="T1000" s="5"/>
-      <c r="U1000" s="5"/>
-      <c r="V1000" s="5"/>
-      <c r="W1000" s="5"/>
-      <c r="X1000" s="5"/>
-      <c r="Y1000" s="5"/>
-      <c r="Z1000" s="5"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -57406,7 +57608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58448,7 +58650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -1458,7 +1458,9 @@
         <v>59</v>
       </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085"/>
+    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -451,10 +451,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>null</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -470,10 +466,6 @@
   </si>
   <si>
     <t>monster_002</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음 모험으로 떠난다</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -507,10 +499,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MainScript_2_7  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_2_8  테스트 입니다</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -524,6 +512,145 @@
   </si>
   <si>
     <t>MainScript_2_11  테스트 입니다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 모험으로 떠난다(전투 승리)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>전투</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>패배</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>양심없네</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>혹시 몰라서 남겨둠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_14</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_15</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_16</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_17</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지역으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>넘어간다</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEXTWIN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEXTLOSE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1021,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D25" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D18" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
@@ -1143,7 +1270,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1338,7 +1465,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1455,11 +1582,11 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1496,7 +1623,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -1524,19 +1651,17 @@
         <v>1</v>
       </c>
       <c r="B15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>MainScene_1_2_1</v>
+        <v>MainScene_1_1_14</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="str">
-        <f>Main_Script_Master_Main!D15</f>
-        <v>MainScript_1_2_1</v>
+      <c r="F15" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -1564,19 +1689,17 @@
         <v>1</v>
       </c>
       <c r="B16" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>MainScene_1_2_2</v>
+        <v>MainScene_1_1_15</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="str">
-        <f>Main_Script_Master_Main!D16</f>
-        <v>MainScript_1_2_2</v>
+      <c r="F16" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -1604,19 +1727,17 @@
         <v>1</v>
       </c>
       <c r="B17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>MainScene_1_2_3</v>
+        <v>MainScene_1_1_16</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="str">
-        <f>Main_Script_Master_Main!D17</f>
-        <v>MainScript_1_2_3</v>
+      <c r="F17" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -1644,19 +1765,17 @@
         <v>1</v>
       </c>
       <c r="B18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="4">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D18" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>MainScene_1_2_4</v>
+        <v>MainScene_1_1_17</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="str">
-        <f>Main_Script_Master_Main!D18</f>
-        <v>MainScript_1_2_4</v>
+      <c r="F18" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -1687,16 +1806,16 @@
         <v>2</v>
       </c>
       <c r="C19" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_5</v>
+        <f t="shared" ref="D19:D29" si="1">CONCATENATE("MainScene_",A19,"_",B19,"_",C19)</f>
+        <v>MainScene_1_2_1</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="str">
-        <f>Main_Script_Master_Main!D19</f>
-        <v>MainScript_1_2_5</v>
+        <f>Main_Script_Master_Main!D20</f>
+        <v>MainScript_1_2_1</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -1727,16 +1846,16 @@
         <v>2</v>
       </c>
       <c r="C20" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_6</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_2</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="str">
-        <f>Main_Script_Master_Main!D20</f>
-        <v>MainScript_1_2_6</v>
+        <f>Main_Script_Master_Main!D21</f>
+        <v>MainScript_1_2_2</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1767,16 +1886,16 @@
         <v>2</v>
       </c>
       <c r="C21" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_7</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_3</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="str">
-        <f>Main_Script_Master_Main!D21</f>
-        <v>MainScript_1_2_7</v>
+        <f>Main_Script_Master_Main!D22</f>
+        <v>MainScript_1_2_3</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -1807,16 +1926,16 @@
         <v>2</v>
       </c>
       <c r="C22" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_8</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_4</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="str">
-        <f>Main_Script_Master_Main!D22</f>
-        <v>MainScript_1_2_8</v>
+        <f>Main_Script_Master_Main!D23</f>
+        <v>MainScript_1_2_4</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1847,16 +1966,16 @@
         <v>2</v>
       </c>
       <c r="C23" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_9</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_5</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="str">
-        <f>Main_Script_Master_Main!D23</f>
-        <v>MainScript_1_2_9</v>
+        <f>Main_Script_Master_Main!D24</f>
+        <v>MainScript_1_2_5</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1887,16 +2006,16 @@
         <v>2</v>
       </c>
       <c r="C24" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_10</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_6</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="str">
-        <f>Main_Script_Master_Main!D24</f>
-        <v>MainScript_1_2_10</v>
+        <f>Main_Script_Master_Main!D25</f>
+        <v>MainScript_1_2_6</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1927,16 +2046,16 @@
         <v>2</v>
       </c>
       <c r="C25" s="4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_11</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_7</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="str">
-        <f>Main_Script_Master_Main!D25</f>
-        <v>MainScript_1_2_11</v>
+        <f>Main_Script_Master_Main!D26</f>
+        <v>MainScript_1_2_7</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1960,12 +2079,24 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="3"/>
+      <c r="A26" s="4">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_8</v>
+      </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3" t="str">
+        <f>Main_Script_Master_Main!D27</f>
+        <v>MainScript_1_2_8</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -1988,12 +2119,24 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="3"/>
+      <c r="A27" s="4">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4">
+        <v>9</v>
+      </c>
+      <c r="D27" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_9</v>
+      </c>
       <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="str">
+        <f>Main_Script_Master_Main!D28</f>
+        <v>MainScript_1_2_9</v>
+      </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -2016,12 +2159,24 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="3"/>
+      <c r="A28" s="4">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_10</v>
+      </c>
       <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3" t="str">
+        <f>Main_Script_Master_Main!D29</f>
+        <v>MainScript_1_2_10</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -2044,12 +2199,24 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="3"/>
+      <c r="A29" s="4">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_11</v>
+      </c>
       <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3" t="str">
+        <f>Main_Script_Master_Main!D30</f>
+        <v>MainScript_1_2_11</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -29279,7 +29446,9 @@
     <col min="5" max="5" width="58.42578125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="26" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="59.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5">
@@ -29304,8 +29473,12 @@
       <c r="G1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -29335,7 +29508,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D25" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="13" t="s">
@@ -29344,9 +29517,7 @@
       <c r="F2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -29387,9 +29558,7 @@
       <c r="F3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -29430,9 +29599,7 @@
       <c r="F4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -29473,9 +29640,7 @@
       <c r="F5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -29516,9 +29681,7 @@
       <c r="F6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -29559,9 +29722,7 @@
       <c r="F7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -29602,9 +29763,7 @@
       <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -29645,9 +29804,7 @@
       <c r="F9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -29688,9 +29845,7 @@
       <c r="F10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -29731,9 +29886,7 @@
       <c r="F11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -29810,14 +29963,20 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="H13" s="5" t="str">
+        <f>VLOOKUP(D14,D14,1,FALSE)</f>
+        <v>MainScript_1_1_13</v>
+      </c>
+      <c r="I13" s="5" t="str">
+        <f>VLOOKUP(D16,D16,1,FALSE)</f>
+        <v>MainScript_1_1_15</v>
+      </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -29851,13 +30010,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -29884,23 +30040,24 @@
         <v>1</v>
       </c>
       <c r="B15" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D15" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A15,"_",B15,"_",C15)</f>
-        <v>MainScript_1_2_1</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_1_14</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>65</v>
+      <c r="E15" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -29925,20 +30082,20 @@
         <v>1</v>
       </c>
       <c r="B16" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_2</v>
+        <v>MainScript_1_1_15</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>66</v>
+      <c r="E16" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -29966,22 +30123,24 @@
         <v>1</v>
       </c>
       <c r="B17" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_3</v>
+        <v>MainScript_1_1_16</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>67</v>
+      <c r="E17" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
@@ -30007,22 +30166,21 @@
         <v>1</v>
       </c>
       <c r="B18" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="7">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_4</v>
+        <v>MainScript_1_1_17</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>68</v>
+      <c r="E18" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
-      <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
@@ -30048,20 +30206,20 @@
         <v>1</v>
       </c>
       <c r="B19" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_5</v>
+        <v>MainScript_1_1_18</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>69</v>
+      <c r="E19" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -30092,14 +30250,14 @@
         <v>2</v>
       </c>
       <c r="C20" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_2_6</v>
+        <f t="shared" ref="D20:D30" si="1">CONCATENATE("MainScript_",A20,"_",B20,"_",C20)</f>
+        <v>MainScript_1_2_1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -30133,14 +30291,14 @@
         <v>2</v>
       </c>
       <c r="C21" s="7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_2_7</v>
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
@@ -30174,14 +30332,14 @@
         <v>2</v>
       </c>
       <c r="C22" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D22" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A22,"_",B22,"_",C22)</f>
-        <v>MainScript_1_2_8</v>
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_3</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
@@ -30215,14 +30373,14 @@
         <v>2</v>
       </c>
       <c r="C23" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D23" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_2_9</v>
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>40</v>
@@ -30256,14 +30414,14 @@
         <v>2</v>
       </c>
       <c r="C24" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D24" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_2_10</v>
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_5</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -30297,14 +30455,14 @@
         <v>2</v>
       </c>
       <c r="C25" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D25" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_2_11</v>
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_6</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>40</v>
@@ -30331,15 +30489,34 @@
       <c r="Z25" s="5"/>
     </row>
     <row r="26" spans="1:26" ht="16.5">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7">
+        <v>2</v>
+      </c>
+      <c r="C26" s="7">
+        <v>7</v>
+      </c>
+      <c r="D26" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_7</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="H26" s="5" t="str">
+        <f>VLOOKUP(D27,D27,1,FALSE)</f>
+        <v>MainScript_1_2_8</v>
+      </c>
+      <c r="I26" s="5" t="str">
+        <f>VLOOKUP(D29,D29,1,FALSE)</f>
+        <v>MainScript_1_2_10</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -30359,12 +30536,25 @@
       <c r="Z26" s="5"/>
     </row>
     <row r="27" spans="1:26" ht="16.5">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2</v>
+      </c>
+      <c r="C27" s="7">
+        <v>8</v>
+      </c>
+      <c r="D27" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_8</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -30387,13 +30577,28 @@
       <c r="Z27" s="5"/>
     </row>
     <row r="28" spans="1:26" ht="16.5">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7">
+        <v>2</v>
+      </c>
+      <c r="C28" s="7">
+        <v>9</v>
+      </c>
+      <c r="D28" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_9</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -30415,12 +30620,25 @@
       <c r="Z28" s="5"/>
     </row>
     <row r="29" spans="1:26" ht="16.5">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7">
+        <v>2</v>
+      </c>
+      <c r="C29" s="7">
+        <v>10</v>
+      </c>
+      <c r="D29" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_10</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
@@ -30443,13 +30661,28 @@
       <c r="Z29" s="5"/>
     </row>
     <row r="30" spans="1:26" ht="16.5">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7">
+        <v>2</v>
+      </c>
+      <c r="C30" s="7">
+        <v>11</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_11</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A747C2-96F7-40CA-829B-02C93A08934F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3120" windowWidth="31020" windowHeight="11085" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,19 +18,8 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -38,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -70,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="101">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -208,61 +198,6 @@
   </si>
   <si>
     <t>MainScript_1_1_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">평온한 마을인 라노스마을
-해가 높이 떠올랐고, 바람은 따뜻했다.
-나는 그 조용한 일상 속에서 오늘도 변함없이 숨을 죽이며 살아가고 있었다.
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">마을 사람들이 특별히 따돌리진 않았다
-하지만 당신을 향한 시선에는 어딘가 설명하기 어려운 거리감이 배어 있었다.
-나는 그게 더 편했다.
-누구와도 엮이지 않으면, 누군가를 잃는 일도 없을 테니까..
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그날 아침도 평범했다,
-언제나처럼 우물가에서 물을 길었고, 남은 식사를 정리했다.
-모두가 자신만의 하루를 살고 있던 평범한 날이였다.
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">하지만 나는 이상한 기척을 순간 느꼈다…
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>뭐지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">….?"
-</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,
@@ -451,123 +386,16 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Break</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BATTLE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_1_1_12</t>
   </si>
   <si>
     <t>MainScript_1_1_13</t>
   </si>
   <si>
-    <t>monster_002</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_1_1_4</t>
   </si>
   <si>
     <t>MainScript_1_1_9</t>
-  </si>
-  <si>
-    <t>MainScript_2_1 테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_2  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_3  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_4  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_5  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_6  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_8  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_9  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_10  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_2_11  테스트 입니다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음 모험으로 떠난다(전투 승리)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>전투</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>패배</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>양심없네</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>지지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>혹시 몰라서 남겨둠</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_14</t>
@@ -582,19 +410,24 @@
     <t>MainScript_1_1_17</t>
   </si>
   <si>
-    <t>TEXT</t>
+    <t>NEXTWIN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEXTLOSE</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>다음</t>
+      <t>평온한</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -608,14 +441,15 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>지역으로</t>
+      <t>마을인</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -629,36 +463,2456 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>넘어간다</t>
+      <t>라노스마을_x000D_
+해가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>높이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>떠올랐고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>바람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>따뜻했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">._x000D_
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조용한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오늘도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변함없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>숨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>죽이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>살아가고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">._x000D_
+</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>NEXTWIN</t>
+    <r>
+      <t>마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사람들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>특별히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>따돌리진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>않았다_x000D_
+하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>당신을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>향한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시선에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>어딘가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설명하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>어려운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>거리감이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>배어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">._x000D_
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>편했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">._x000D_
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>누구와도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>엮이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>누군가를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>잃는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>없을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>테니까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.._x000D_
+</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>NEXTLOSE</t>
+    <r>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아침도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평범했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,_x000D_
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>언제나처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우물가에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>길었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>남은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>식사를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정리했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">._x000D_
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모두가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자신만의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하루를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>살고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평범한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>날이였다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">._x000D_
+</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>BATTLE</t>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>뭐지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">….?"_x000D_
+</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Break</t>
+    <r>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이상한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기척을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>순간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>느꼈다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">…_x000D_
+</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Break</t>
+    <t>그리고 얼마 지나지 않아 마을은 그 기능을 완전히 잃었다.
+모두가 흩어졌고, 쓰러졌고, 불타고 있었다.
+그리고 남겨진 자는, 또다시 그 혼자였다.
+소년은 무너진 담벼락 옆에 주저앉아 숨을 내쉬었다.
+손에는 작은 흠집만 남았고, 주변은 적막뿐이였다.
+"또…. 나만.."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"이번에도 살아남았네… 왜… 도대체 왜…"</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>알</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>없겠지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>."
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>네가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>살아남았는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반복되는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일엔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이유가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>빛은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>멈추었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>천천히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>낮고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부드러운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>목소리로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>말했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소년의 눈동자가 흔들렸다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>멈추면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>또</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하나의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반복으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>끝나겠지
+하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>네가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>걸어간다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>끝은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>달라질</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>그때였다. 시야 가장자리에, 느릿하게 퍼지는 빛이 있었다.
+"….저게…. 뭐지…?"
+불에 탄 공기 속에서, 그 빛은 아무 말도 없이 다가왔다.
+낯설고 설명할 수 없지만, 이상하게 시선을 뗄 수 없었다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 아무 말 없이 그 빛을 바라보았다.
+나는 천천히 일어났고
+푸른 위습은 앞서 나아가듯 떠올랐다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 그 뒤를 따랐다. 
+그리고 그렇게, 이야기는 움직이기 시작했다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMAGE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_18</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_19</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_20</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_21</t>
+  </si>
+  <si>
+    <t>C1E1_town</t>
+  </si>
+  <si>
+    <t>불타던 마을은 잿더미가 되어 있었다.
+붉게 달아올랐던 불길도 꺼졌고
+연기만이 바람을 따라 흘러가고 있었다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무너진 가게 앞
+진흙투성이가 된 거리 한복판에서 목소리가 들렸다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>"생존자다…!"
+아직 누군가 살아 있었다.
+나는 조심스레 다가갔고 
+그곳에는 벽돌 더미에 깔린 어린 소년이 있었다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 소년이랑 눈이 마주쳤고 
+나는 손을 소년에게 뻗었다.
+하지만 아이는 눈을 크게 뜨고 움찔거렸다.
+본능적으로 나를 두려워하는 눈빛이였다…
+나는 손을 거두고 
+"…괜찮아."
+라고 작은 목소리로 중얼거렸다…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽돌을 옆으로 치운다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무시하고 옆으로 지나간다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_1</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_2</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_3</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_4</t>
+  </si>
+  <si>
+    <t>나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
+하지만 그 소년은 숨이 점점 거칠어 지다가 
+결국 숨이 끊어져 버렸다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 천천히 일어났다
+"나는… 또 살아남았고.."
+"넌… 결국 이렇게 떠나는 구나…."
+"왜…. 왜 매번 이렇게 되는거지…."</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>손바닥에는 진흙과 피가 묻어 있었지만. 
+그 손은 어디에도 닦지 않았다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>고개를 들어 폐허 너머를 바라봤다.
+이제 이 마을엔 더 머물 이유도.. 머물 자리도 없었다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene_1_2_5</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_8</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_9</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_7</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +2983,19 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -805,7 +3072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -849,6 +3116,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,7 +3343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1148,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D18" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D31" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
@@ -1270,7 +3549,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1465,7 +3744,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1582,12 +3861,10 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="H13" s="5"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1623,7 +3900,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -1661,7 +3938,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -1699,7 +3976,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -1737,7 +4014,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -1775,7 +4052,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -1803,19 +4080,18 @@
         <v>1</v>
       </c>
       <c r="B19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D19" s="3" t="str">
-        <f t="shared" ref="D19:D29" si="1">CONCATENATE("MainScene_",A19,"_",B19,"_",C19)</f>
-        <v>MainScene_1_2_1</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_18</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="3" t="str">
-        <f>Main_Script_Master_Main!D20</f>
-        <v>MainScript_1_2_1</v>
+      <c r="F19" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -1843,19 +4119,18 @@
         <v>1</v>
       </c>
       <c r="B20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_2</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_19</v>
       </c>
       <c r="E20" s="3"/>
-      <c r="F20" s="3" t="str">
-        <f>Main_Script_Master_Main!D21</f>
-        <v>MainScript_1_2_2</v>
+      <c r="F20" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1883,19 +4158,18 @@
         <v>1</v>
       </c>
       <c r="B21" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_3</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_20</v>
       </c>
       <c r="E21" s="3"/>
-      <c r="F21" s="3" t="str">
-        <f>Main_Script_Master_Main!D22</f>
-        <v>MainScript_1_2_3</v>
+      <c r="F21" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -1923,19 +4197,18 @@
         <v>1</v>
       </c>
       <c r="B22" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="4">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_4</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_21</v>
       </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="3" t="str">
-        <f>Main_Script_Master_Main!D23</f>
-        <v>MainScript_1_2_4</v>
+      <c r="F22" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1966,16 +4239,15 @@
         <v>2</v>
       </c>
       <c r="C23" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_5</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_1</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3" t="str">
-        <f>Main_Script_Master_Main!D24</f>
-        <v>MainScript_1_2_5</v>
+      <c r="F23" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -2006,16 +4278,15 @@
         <v>2</v>
       </c>
       <c r="C24" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_6</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_2</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3" t="str">
-        <f>Main_Script_Master_Main!D25</f>
-        <v>MainScript_1_2_6</v>
+      <c r="F24" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -2046,16 +4317,15 @@
         <v>2</v>
       </c>
       <c r="C25" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D25" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_7</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_3</v>
       </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3" t="str">
-        <f>Main_Script_Master_Main!D26</f>
-        <v>MainScript_1_2_7</v>
+      <c r="F25" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -2086,20 +4356,23 @@
         <v>2</v>
       </c>
       <c r="C26" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_8</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_4</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="3" t="str">
-        <f>Main_Script_Master_Main!D27</f>
-        <v>MainScript_1_2_8</v>
+      <c r="F26" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -2126,16 +4399,15 @@
         <v>2</v>
       </c>
       <c r="C27" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_9</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_5</v>
       </c>
       <c r="E27" s="3"/>
-      <c r="F27" s="3" t="str">
-        <f>Main_Script_Master_Main!D28</f>
-        <v>MainScript_1_2_9</v>
+      <c r="F27" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -2166,16 +4438,15 @@
         <v>2</v>
       </c>
       <c r="C28" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D28" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_10</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_6</v>
       </c>
       <c r="E28" s="3"/>
-      <c r="F28" s="3" t="str">
-        <f>Main_Script_Master_Main!D29</f>
-        <v>MainScript_1_2_10</v>
+      <c r="F28" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -2206,16 +4477,15 @@
         <v>2</v>
       </c>
       <c r="C29" s="4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_11</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_7</v>
       </c>
       <c r="E29" s="3"/>
-      <c r="F29" s="3" t="str">
-        <f>Main_Script_Master_Main!D30</f>
-        <v>MainScript_1_2_11</v>
+      <c r="F29" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -2239,12 +4509,23 @@
       <c r="Z29" s="3"/>
     </row>
     <row r="30" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3"/>
+      <c r="A30" s="4">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4">
+        <v>8</v>
+      </c>
+      <c r="D30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_8</v>
+      </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -2267,10 +4548,19 @@
       <c r="Z30" s="3"/>
     </row>
     <row r="31" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="3"/>
+      <c r="A31" s="4">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScene_1_2_9</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -29435,7 +31725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -29474,10 +31764,10 @@
         <v>39</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -29497,7 +31787,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" ht="75">
+    <row r="2" spans="1:26" ht="16.5">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -29508,14 +31798,14 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D20" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>45</v>
+      <c r="E2" s="19" t="s">
+        <v>80</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>40</v>
+      <c r="F2" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -29538,7 +31828,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="90">
+    <row r="3" spans="1:26" ht="75">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -29553,7 +31843,7 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>40</v>
@@ -29579,7 +31869,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="60">
+    <row r="4" spans="1:26" ht="90">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -29594,7 +31884,7 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>40</v>
@@ -29620,7 +31910,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="60">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -29635,7 +31925,7 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>40</v>
@@ -29675,8 +31965,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_5</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>49</v>
+      <c r="E6" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>40</v>
@@ -29716,8 +32006,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>50</v>
+      <c r="E7" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>40</v>
@@ -29743,7 +32033,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="45">
+    <row r="8" spans="1:26" ht="30">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -29758,7 +32048,7 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>40</v>
@@ -29784,7 +32074,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="90">
+    <row r="9" spans="1:26" ht="45">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -29799,7 +32089,7 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>40</v>
@@ -29825,7 +32115,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="45">
+    <row r="10" spans="1:26" ht="90">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -29840,10 +32130,10 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -29881,10 +32171,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -29907,7 +32197,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" ht="66">
+    <row r="12" spans="1:26" ht="45">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -29921,8 +32211,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_11</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>55</v>
+      <c r="E12" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>40</v>
@@ -29948,7 +32238,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" ht="16.5">
+    <row r="13" spans="1:26" ht="66">
       <c r="A13" s="7">
         <v>1</v>
       </c>
@@ -29962,21 +32252,15 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>60</v>
+      <c r="E13" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="5" t="str">
-        <f>VLOOKUP(D14,D14,1,FALSE)</f>
-        <v>MainScript_1_1_13</v>
-      </c>
-      <c r="I13" s="5" t="str">
-        <f>VLOOKUP(D16,D16,1,FALSE)</f>
-        <v>MainScript_1_1_15</v>
-      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -29995,7 +32279,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="16.5">
+    <row r="14" spans="1:26" ht="99">
       <c r="A14" s="7">
         <v>1</v>
       </c>
@@ -30009,8 +32293,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>73</v>
+      <c r="E14" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
@@ -30050,14 +32334,12 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -30077,7 +32359,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" ht="16.5">
+    <row r="16" spans="1:26" ht="60">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -30092,10 +32374,10 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -30118,7 +32400,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="16.5">
+    <row r="17" spans="1:26" ht="30">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -30133,14 +32415,12 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
@@ -30161,7 +32441,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="16.5">
+    <row r="18" spans="1:26" ht="45">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -30175,11 +32455,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_17</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>77</v>
+      <c r="E18" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -30216,10 +32496,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -30242,22 +32522,22 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="16.5">
+    <row r="20" spans="1:26" ht="30">
       <c r="A20" s="7">
         <v>1</v>
       </c>
       <c r="B20" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="7">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D20" s="5" t="str">
-        <f t="shared" ref="D20:D30" si="1">CONCATENATE("MainScript_",A20,"_",B20,"_",C20)</f>
-        <v>MainScript_1_2_1</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_1_19</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>63</v>
+      <c r="E20" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -30283,22 +32563,22 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="16.5">
+    <row r="21" spans="1:26" ht="49.5">
       <c r="A21" s="7">
         <v>1</v>
       </c>
       <c r="B21" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_2</v>
+        <f>CONCATENATE("MainScript_",A21,"_",B21,"_",C21)</f>
+        <v>MainScript_1_1_20</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>64</v>
+      <c r="E21" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
@@ -30324,22 +32604,22 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" ht="16.5">
+    <row r="22" spans="1:26" ht="33">
       <c r="A22" s="7">
         <v>1</v>
       </c>
       <c r="B22" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="7">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_3</v>
+        <f>CONCATENATE("MainScript_",A22,"_",B22,"_",C22)</f>
+        <v>MainScript_1_1_21</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>65</v>
+      <c r="E22" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
@@ -30365,7 +32645,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="16.5">
+    <row r="23" spans="1:26" ht="49.5">
       <c r="A23" s="7">
         <v>1</v>
       </c>
@@ -30373,14 +32653,14 @@
         <v>2</v>
       </c>
       <c r="C23" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_4</v>
+        <f t="shared" ref="D23:D34" si="1">CONCATENATE("MainScript_",A23,"_",B23,"_",C23)</f>
+        <v>MainScript_1_2_1</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>66</v>
+      <c r="E23" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>40</v>
@@ -30406,7 +32686,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" ht="16.5">
+    <row r="24" spans="1:26" ht="33">
       <c r="A24" s="7">
         <v>1</v>
       </c>
@@ -30414,14 +32694,14 @@
         <v>2</v>
       </c>
       <c r="C24" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_5</v>
+        <v>MainScript_1_2_2</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>67</v>
+      <c r="E24" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -30447,7 +32727,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" spans="1:26" ht="16.5">
+    <row r="25" spans="1:26" ht="66">
       <c r="A25" s="7">
         <v>1</v>
       </c>
@@ -30455,14 +32735,14 @@
         <v>2</v>
       </c>
       <c r="C25" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_6</v>
+        <v>MainScript_1_2_3</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>68</v>
+      <c r="E25" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>40</v>
@@ -30488,7 +32768,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="16.5">
+    <row r="26" spans="1:26" ht="115.5">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -30496,27 +32776,21 @@
         <v>2</v>
       </c>
       <c r="C26" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_7</v>
+        <v>MainScript_1_2_4</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>60</v>
+      <c r="E26" s="16" t="s">
+        <v>84</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="5" t="str">
-        <f>VLOOKUP(D27,D27,1,FALSE)</f>
-        <v>MainScript_1_2_8</v>
-      </c>
-      <c r="I26" s="5" t="str">
-        <f>VLOOKUP(D29,D29,1,FALSE)</f>
-        <v>MainScript_1_2_10</v>
-      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -30543,14 +32817,14 @@
         <v>2</v>
       </c>
       <c r="C27" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D27" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_8</v>
+        <v>MainScript_1_2_5</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>40</v>
@@ -30576,7 +32850,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="16.5">
+    <row r="28" spans="1:26" ht="49.5">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -30584,21 +32858,19 @@
         <v>2</v>
       </c>
       <c r="C28" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_9</v>
+        <v>MainScript_1_2_6</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>70</v>
+      <c r="E28" s="16" t="s">
+        <v>91</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -30619,7 +32891,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="16.5">
+    <row r="29" spans="1:26" ht="66">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -30627,14 +32899,14 @@
         <v>2</v>
       </c>
       <c r="C29" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D29" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_10</v>
+        <v>MainScript_1_2_7</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>71</v>
+      <c r="E29" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>40</v>
@@ -30660,7 +32932,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="16.5">
+    <row r="30" spans="1:26" ht="33">
       <c r="A30" s="7">
         <v>1</v>
       </c>
@@ -30668,21 +32940,19 @@
         <v>2</v>
       </c>
       <c r="C30" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D30" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_2_11</v>
+        <v>MainScript_1_2_8</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>72</v>
+      <c r="E30" s="16" t="s">
+        <v>93</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -30703,13 +32973,26 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="16.5">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+    <row r="31" spans="1:26" ht="33">
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7">
+        <v>2</v>
+      </c>
+      <c r="C31" s="7">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_9</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -30732,12 +33015,25 @@
       <c r="Z31" s="5"/>
     </row>
     <row r="32" spans="1:26" ht="16.5">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7">
+        <v>2</v>
+      </c>
+      <c r="C32" s="7">
+        <v>10</v>
+      </c>
+      <c r="D32" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_10</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -30760,10 +33056,19 @@
       <c r="Z32" s="5"/>
     </row>
     <row r="33" spans="1:26" ht="16.5">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="5"/>
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7">
+        <v>11</v>
+      </c>
+      <c r="D33" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_11</v>
+      </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -30788,10 +33093,19 @@
       <c r="Z33" s="5"/>
     </row>
     <row r="34" spans="1:26" ht="16.5">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="5"/>
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_2_12</v>
+      </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -57843,7 +60157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -58885,7 +61199,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A747C2-96F7-40CA-829B-02C93A08934F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA89D03-F830-484E-B206-5C93EE1817D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,17 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -60,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2907,6 +2916,29 @@
     <t>MainScript_1_2_7</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>TEST</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>MainScene_1_2_4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">STR*10 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene_1_2_6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene_1_2_7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -4359,7 +4391,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("MainScene_",A26,"_",B26,"_",C26)</f>
         <v>MainScene_1_2_4</v>
       </c>
       <c r="E26" s="3"/>
@@ -31807,9 +31839,15 @@
       <c r="F2" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -32624,7 +32662,9 @@
       <c r="F22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -60187,7 +60227,21 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A2" s="3"/>
+      <c r="A2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
       <c r="A3" s="3"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA89D03-F830-484E-B206-5C93EE1817D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE972BC-EDE0-4624-B966-55E15AC09E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2904,9 +2904,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MainScene_1_2_5</t>
-  </si>
-  <si>
     <t>MainScript_1_2_8</t>
   </si>
   <si>
@@ -2937,6 +2934,10 @@
   </si>
   <si>
     <t>MainScene_1_2_7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -4402,9 +4403,7 @@
       <c r="H26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -4478,7 +4477,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -4517,7 +4516,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4556,7 +4555,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -31840,13 +31839,13 @@
         <v>75</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32663,7 +32662,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -32869,7 +32868,9 @@
       <c r="F27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -33074,7 +33075,9 @@
       <c r="F32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -60228,19 +60231,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE972BC-EDE0-4624-B966-55E15AC09E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{BDE972BC-EDE0-4624-B966-55E15AC09E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766FC18B-E045-4B19-A6D6-9EEB0FAEB703}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2843,16 +2843,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>나는 소년이랑 눈이 마주쳤고 
-나는 손을 소년에게 뻗었다.
-하지만 아이는 눈을 크게 뜨고 움찔거렸다.
-본능적으로 나를 두려워하는 눈빛이였다…
-나는 손을 거두고 
-"…괜찮아."
-라고 작은 목소리로 중얼거렸다…</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>벽돌을 옆으로 치운다.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2900,18 +2890,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MainScript_1_2_6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_1_2_8</t>
   </si>
   <si>
     <t>MainScript_1_2_9</t>
-  </si>
-  <si>
-    <t>MainScript_1_2_7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TEST</t>
@@ -2939,6 +2921,167 @@
   <si>
     <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 소년이랑 눈이 마주쳤고 
+나는 손을 소년에게 뻗었다.
+하지만 아이는 눈을 크게 뜨고 움찔거렸다.
+본능적으로 나를 두려워하는 눈빛이였다…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거두고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+"…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>괜찮아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목소리로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중얼거렸다…</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_6</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_7</t>
   </si>
 </sst>
 </file>
@@ -4280,7 +4423,7 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -4319,7 +4462,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -4358,7 +4501,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -4397,12 +4540,9 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -4438,10 +4578,12 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -4477,7 +4619,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -4516,7 +4658,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4555,7 +4697,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -4593,7 +4735,9 @@
         <v>MainScene_1_2_9</v>
       </c>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -31839,13 +31983,13 @@
         <v>75</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32662,7 +32806,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -32807,7 +32951,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="115.5">
+    <row r="26" spans="1:26" ht="66">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -32822,7 +32966,7 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>40</v>
@@ -32848,7 +32992,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="16.5">
+    <row r="27" spans="1:26" ht="49.5">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -32862,14 +33006,11 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_5</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>85</v>
+      <c r="E27" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -32891,7 +33032,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="49.5">
+    <row r="28" spans="1:26" ht="16.5">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -32905,13 +33046,15 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_6</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>91</v>
+      <c r="E28" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -32932,7 +33075,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="66">
+    <row r="29" spans="1:26" ht="49.5">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -32947,7 +33090,7 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>40</v>
@@ -32973,7 +33116,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="33">
+    <row r="30" spans="1:26" ht="66">
       <c r="A30" s="7">
         <v>1</v>
       </c>
@@ -32988,7 +33131,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
@@ -33029,7 +33172,7 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>40</v>
@@ -33055,7 +33198,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="16.5">
+    <row r="32" spans="1:26" ht="33">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -33069,14 +33212,14 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_10</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>86</v>
+      <c r="E32" s="16" t="s">
+        <v>93</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -33112,7 +33255,9 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_11</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -60231,19 +60376,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE972BC-EDE0-4624-B966-55E15AC09E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="34995" windowHeight="15345" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,12 +36,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -1920,16 +1919,123 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>그리고 얼마 지나지 않아 마을은 그 기능을 완전히 잃었다.
-모두가 흩어졌고, 쓰러졌고, 불타고 있었다.
-그리고 남겨진 자는, 또다시 그 혼자였다.
-소년은 무너진 담벼락 옆에 주저앉아 숨을 내쉬었다.
-손에는 작은 흠집만 남았고, 주변은 적막뿐이였다.
-"또…. 나만.."</t>
+    <t>IMAGE</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>"이번에도 살아남았네… 왜… 도대체 왜…"</t>
+    <t>MainScript_1_1_18</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_19</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_20</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_21</t>
+  </si>
+  <si>
+    <t>C1E1_town</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_1</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_2</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_3</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_4</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_8</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_9</t>
+  </si>
+  <si>
+    <t>TEST</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">벽돌을 옆으로 치운다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"생존자다…!"
+아직 누군가 살아 있었다.
+나는 조심스레 다가갔고 
+그곳에는 벽돌 더미에 깔린 어린 소년이 있었다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무너진 가게 앞
+진흙투성이가 된 거리 한복판에서 목소리가 들렸다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">불타던 마을은 잿더미가 되어 있었다.
+붉게 달아올랐던 불길도 꺼졌고
+연기만이 바람을 따라 흘러가고 있었다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 그 뒤를 따랐다. 
+그리고 그렇게, 이야기는 움직이기 시작했다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
+하지만 그 소년은 숨이 점점 거칠어 지다가 
+결국 숨이 끊어져 버렸다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 천천히 일어났다
+"나는… 또 살아남았고.."
+"넌… 결국 이렇게 떠나는 구나…."
+"왜…. 왜 매번 이렇게 되는거지…."
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">손바닥에는 진흙과 피가 묻어 있었지만. 
+그 손은 어디에도 닦지 않았다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">고개를 들어 폐허 너머를 바라봤다.
+이제 이 마을엔 더 머물 이유도.. 머물 자리도 없었다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무시하고 옆으로 지나간다.
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2259,692 +2365,88 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>."</t>
+      <t xml:space="preserve">."
+</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사람은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>아니고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"
+    <t xml:space="preserve">소년의 눈동자가 흔들렸다.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>빛은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>멈추었고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>천천히</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>아주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>낮고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>부드러운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>목소리로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>말했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>소년의 눈동자가 흔들렸다.</t>
+    <t xml:space="preserve">"지금 멈추면, 이건 또 하나의 반복으로 끝나겠지
+하지만 네가 걸어간다면 끝은 달라질 수도 있어."
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>지금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>멈추면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>또</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>하나의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>반복으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>끝나겠지
-하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>네가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>걸어간다면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>끝은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>달라질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>수도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>있어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>."</t>
-    </r>
+    <t xml:space="preserve">나는 아무 말 없이 그 빛을 바라보았다.
+나는 천천히 일어났고
+푸른 위습은 앞서 나아가듯 떠올랐다.
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>그때였다. 시야 가장자리에, 느릿하게 퍼지는 빛이 있었다.
-"….저게…. 뭐지…?"
-불에 탄 공기 속에서, 그 빛은 아무 말도 없이 다가왔다.
-낯설고 설명할 수 없지만, 이상하게 시선을 뗄 수 없었다.</t>
+    <t xml:space="preserve">"사람은 아니고"
+빛은 멈추었고 천천히 아주 낮고 부드러운 목소리로 말했다.
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>나는 아무 말 없이 그 빛을 바라보았다.
-나는 천천히 일어났고
-푸른 위습은 앞서 나아가듯 떠올랐다.</t>
+    <t xml:space="preserve">그때였다. 시야 가장자리에, 느릿하게 퍼지는 빛이 있었다.
+"….저게…. 뭐지…?"
+불에 탄 공기 속에서, 그 빛은 아무 말도 없이 다가왔다.
+낯설고 설명할 수 없지만, 이상하게 시선을 뗄 수 없었다.
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>나는 그 뒤를 따랐다. 
-그리고 그렇게, 이야기는 움직이기 시작했다.</t>
+    <t xml:space="preserve">"이번에도 살아남았네… 왜… 도대체 왜…"
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>IMAGE</t>
+    <t xml:space="preserve">그리고 얼마 지나지 않아 마을은 그 기능을 완전히 잃었다.
+모두가 흩어졌고, 쓰러졌고, 불타고 있었다.
+그리고 남겨진 자는, 또다시 그 혼자였다.
+소년은 무너진 담벼락 옆에 주저앉아 숨을 내쉬었다.
+손에는 작은 흠집만 남았고, 주변은 적막뿐이였다.
+"또…. 나만.."
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_1_18</t>
-  </si>
-  <si>
-    <t>MainScript_1_1_19</t>
-  </si>
-  <si>
-    <t>MainScript_1_1_20</t>
-  </si>
-  <si>
-    <t>MainScript_1_1_21</t>
-  </si>
-  <si>
-    <t>C1E1_town</t>
-  </si>
-  <si>
-    <t>불타던 마을은 잿더미가 되어 있었다.
-붉게 달아올랐던 불길도 꺼졌고
-연기만이 바람을 따라 흘러가고 있었다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>무너진 가게 앞
-진흙투성이가 된 거리 한복판에서 목소리가 들렸다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>"생존자다…!"
-아직 누군가 살아 있었다.
-나는 조심스레 다가갔고 
-그곳에는 벽돌 더미에 깔린 어린 소년이 있었다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 소년이랑 눈이 마주쳤고 
-나는 손을 소년에게 뻗었다.
-하지만 아이는 눈을 크게 뜨고 움찔거렸다.
-본능적으로 나를 두려워하는 눈빛이였다…
-나는 손을 거두고 
-"…괜찮아."
-라고 작은 목소리로 중얼거렸다…</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>벽돌을 옆으로 치운다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>무시하고 옆으로 지나간다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_2_1</t>
-  </si>
-  <si>
-    <t>MainScript_1_2_2</t>
-  </si>
-  <si>
-    <t>MainScript_1_2_3</t>
-  </si>
-  <si>
-    <t>MainScript_1_2_4</t>
-  </si>
-  <si>
-    <t>나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
-하지만 그 소년은 숨이 점점 거칠어 지다가 
-결국 숨이 끊어져 버렸다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 천천히 일어났다
-"나는… 또 살아남았고.."
-"넌… 결국 이렇게 떠나는 구나…."
-"왜…. 왜 매번 이렇게 되는거지…."</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>손바닥에는 진흙과 피가 묻어 있었지만. 
-그 손은 어디에도 닦지 않았다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>고개를 들어 폐허 너머를 바라봤다.
-이제 이 마을엔 더 머물 이유도.. 머물 자리도 없었다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_2_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_2_6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_2_8</t>
-  </si>
-  <si>
-    <t>MainScript_1_2_9</t>
-  </si>
-  <si>
-    <t>MainScript_1_2_7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEST</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break</t>
   </si>
   <si>
     <t>MainScene_1_2_4</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">STR*10 </t>
+    <t>MainScript_1_2_7</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 소년이랑 눈이 마주쳤고 
+나는 손을 소년에게 뻗었다.
+하지만 아이는 눈을 크게 뜨고 움찔거렸다.
+본능적으로 나를 두려워하는 눈빛이였다…
+나는 손을 거두고 
+"…괜찮아."
+라고 작은 목소리로 중얼거렸다…
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MainScene_1_2_6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScene_1_2_7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break</t>
+    <t xml:space="preserve">STR*10 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -3376,7 +2878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4124,7 +3626,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -4163,7 +3665,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -4202,7 +3704,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -4241,7 +3743,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -4280,7 +3782,7 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -4319,7 +3821,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -4358,7 +3860,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -4397,11 +3899,11 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -4438,7 +3940,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -4477,7 +3979,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -4516,7 +4018,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4555,7 +4057,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -4593,7 +4095,9 @@
         <v>MainScene_1_2_9</v>
       </c>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -4647,7 +4151,6 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -31756,7 +31259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -31833,19 +31336,19 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32316,7 +31819,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="99">
+    <row r="14" spans="1:26" ht="115.5">
       <c r="A14" s="7">
         <v>1</v>
       </c>
@@ -32331,7 +31834,7 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
@@ -32356,7 +31859,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="16.5">
+    <row r="15" spans="1:26" ht="30">
       <c r="A15" s="7">
         <v>1</v>
       </c>
@@ -32371,7 +31874,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>40</v>
@@ -32396,7 +31899,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" ht="60">
+    <row r="16" spans="1:26" ht="75">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -32411,7 +31914,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>40</v>
@@ -32437,7 +31940,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="30">
+    <row r="17" spans="1:26" ht="45">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -32452,7 +31955,7 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>40</v>
@@ -32478,7 +31981,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="45">
+    <row r="18" spans="1:26" ht="60">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -32493,7 +31996,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>40</v>
@@ -32518,7 +32021,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="16.5">
+    <row r="19" spans="1:26" ht="30">
       <c r="A19" s="7">
         <v>1</v>
       </c>
@@ -32533,7 +32036,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>40</v>
@@ -32559,7 +32062,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="30">
+    <row r="20" spans="1:26" ht="45">
       <c r="A20" s="7">
         <v>1</v>
       </c>
@@ -32574,7 +32077,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -32600,7 +32103,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="49.5">
+    <row r="21" spans="1:26" ht="66">
       <c r="A21" s="7">
         <v>1</v>
       </c>
@@ -32615,7 +32118,7 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
@@ -32641,7 +32144,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" ht="33">
+    <row r="22" spans="1:26" ht="49.5">
       <c r="A22" s="7">
         <v>1</v>
       </c>
@@ -32656,13 +32159,13 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -32684,7 +32187,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="49.5">
+    <row r="23" spans="1:26" ht="66">
       <c r="A23" s="7">
         <v>1</v>
       </c>
@@ -32699,7 +32202,7 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>40</v>
@@ -32725,7 +32228,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" ht="33">
+    <row r="24" spans="1:26" ht="49.5">
       <c r="A24" s="7">
         <v>1</v>
       </c>
@@ -32740,7 +32243,7 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -32766,7 +32269,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" spans="1:26" ht="66">
+    <row r="25" spans="1:26" ht="82.5">
       <c r="A25" s="7">
         <v>1</v>
       </c>
@@ -32781,7 +32284,7 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>40</v>
@@ -32807,7 +32310,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="115.5">
+    <row r="26" spans="1:26" ht="132">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -32822,7 +32325,7 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>40</v>
@@ -32848,7 +32351,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="16.5">
+    <row r="27" spans="1:26" ht="33">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -32862,14 +32365,14 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_5</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>85</v>
+      <c r="E27" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -32891,7 +32394,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="49.5">
+    <row r="28" spans="1:26" ht="66">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -32906,7 +32409,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
@@ -32932,7 +32435,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="66">
+    <row r="29" spans="1:26" ht="82.5">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -32947,7 +32450,7 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>40</v>
@@ -32973,7 +32476,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="33">
+    <row r="30" spans="1:26" ht="49.5">
       <c r="A30" s="7">
         <v>1</v>
       </c>
@@ -32988,7 +32491,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
@@ -33014,7 +32517,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="33">
+    <row r="31" spans="1:26" ht="49.5">
       <c r="A31" s="7">
         <v>1</v>
       </c>
@@ -33029,7 +32532,7 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>40</v>
@@ -33055,7 +32558,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="16.5">
+    <row r="32" spans="1:26" ht="33">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -33069,14 +32572,14 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_10</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>86</v>
+      <c r="E32" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -60200,15 +59703,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -60231,19 +59734,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -61256,7 +60759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3FFFB7-43EC-488B-845A-2ADFCF770309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="34995" windowHeight="15345" activeTab="1"/>
+    <workbookView xWindow="3870" yWindow="900" windowWidth="16770" windowHeight="13260" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,17 +18,8 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -36,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -68,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2007,13 +1999,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
-하지만 그 소년은 숨이 점점 거칠어 지다가 
-결국 숨이 끊어져 버렸다.
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">나는 천천히 일어났다
 "나는… 또 살아남았고.."
 "넌… 결국 이렇게 떠나는 구나…."
@@ -2030,11 +2015,6 @@
   <si>
     <t xml:space="preserve">고개를 들어 폐허 너머를 바라봤다.
 이제 이 마을엔 더 머물 이유도.. 머물 자리도 없었다.
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">무시하고 옆으로 지나간다.
 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2425,28 +2405,48 @@
     <t>MainScript_1_2_7</t>
   </si>
   <si>
-    <t>MainScript_1_2_6</t>
+    <t xml:space="preserve">STR*10 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_2_10</t>
+  </si>
+  <si>
+    <t>무시하고 옆으로 지나간다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">나는 소년이랑 눈이 마주쳤고 
 나는 손을 소년에게 뻗었다.
 하지만 아이는 눈을 크게 뜨고 움찔거렸다.
 본능적으로 나를 두려워하는 눈빛이였다…
-나는 손을 거두고 
-"…괜찮아."
-라고 작은 목소리로 중얼거렸다…
 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">STR*10 </t>
+    <t xml:space="preserve">나는 손을 거두고 
+"…괜찮아."
+라고 작은 목소리로 중얼거렸다…
+나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
+하지만 그 소년은 숨이 점점 거칠어 지다가 
+결국 숨이 끊어져 버렸다.
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"어차피 죽을 목숨이였어…"
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -2878,7 +2878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -31259,7 +31259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -31834,7 +31834,7 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
@@ -31874,7 +31874,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>40</v>
@@ -31914,7 +31914,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>40</v>
@@ -31955,7 +31955,7 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>40</v>
@@ -31996,7 +31996,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>40</v>
@@ -32036,7 +32036,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>40</v>
@@ -32077,7 +32077,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -32118,7 +32118,7 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
@@ -32310,7 +32310,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="132">
+    <row r="26" spans="1:26" ht="99">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -32325,7 +32325,7 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>40</v>
@@ -32394,7 +32394,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="66">
+    <row r="28" spans="1:26" ht="115.5">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -32409,7 +32409,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
@@ -32450,7 +32450,7 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>40</v>
@@ -32491,7 +32491,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
@@ -32532,7 +32532,7 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>40</v>
@@ -32558,7 +32558,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="33">
+    <row r="32" spans="1:26" ht="16.5">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -32573,7 +32573,7 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>40</v>
@@ -32601,7 +32601,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="16.5">
+    <row r="33" spans="1:26" ht="33">
       <c r="A33" s="7">
         <v>1</v>
       </c>
@@ -32615,7 +32615,9 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_2_11</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="16" t="s">
+        <v>107</v>
+      </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -59703,7 +59705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -59734,19 +59736,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -60759,7 +60761,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3FFFB7-43EC-488B-845A-2ADFCF770309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="900" windowWidth="16770" windowHeight="13260" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="900" windowWidth="16770" windowHeight="13260"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
@@ -28,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="113">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -1956,13 +1955,6 @@
     <t>MainScript_1_2_9</t>
   </si>
   <si>
-    <t>TEST</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break</t>
-  </si>
-  <si>
     <t>Break</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2409,10 +2401,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MainScript_1_2_7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_1_2_10</t>
   </si>
   <si>
@@ -2442,11 +2430,39 @@
 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>다음 이야기로</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_1_1_22</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_5</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_6</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_11</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -2607,7 +2623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2663,6 +2679,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2878,7 +2897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2887,7 +2906,7 @@
     <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.85546875" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -3660,7 +3679,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("MainScene_",A20,"_",B20,"_",C20)</f>
         <v>MainScene_1_1_19</v>
       </c>
       <c r="E20" s="3"/>
@@ -3699,7 +3718,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("MainScene_",A21,"_",B21,"_",C21)</f>
         <v>MainScene_1_1_20</v>
       </c>
       <c r="E21" s="3"/>
@@ -3738,15 +3757,17 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("MainScene_",A22,"_",B22,"_",C22)</f>
         <v>MainScene_1_1_21</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -3771,21 +3792,18 @@
         <v>1</v>
       </c>
       <c r="B23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_1</v>
+        <f>CONCATENATE("MainScene_",A23,"_",B23,"_",C23)</f>
+        <v>MainScene_1_1_22</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>72</v>
+      <c r="F23" s="5" t="s">
+        <v>107</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -3813,15 +3831,15 @@
         <v>2</v>
       </c>
       <c r="C24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_2</v>
+        <f>CONCATENATE("MainScene_",A24,"_",B24,"_",C24)</f>
+        <v>MainScene_1_2_1</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -3852,15 +3870,15 @@
         <v>2</v>
       </c>
       <c r="C25" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_3</v>
+        <f>CONCATENATE("MainScene_",A25,"_",B25,"_",C25)</f>
+        <v>MainScene_1_2_2</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -3891,20 +3909,18 @@
         <v>2</v>
       </c>
       <c r="C26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3" t="str">
         <f>CONCATENATE("MainScene_",A26,"_",B26,"_",C26)</f>
-        <v>MainScene_1_2_4</v>
+        <v>MainScene_1_2_3</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -3932,18 +3948,20 @@
         <v>2</v>
       </c>
       <c r="C27" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_5</v>
+        <f>CONCATENATE("MainScene_",A27,"_",B27,"_",C27)</f>
+        <v>MainScene_1_2_4</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -3971,15 +3989,15 @@
         <v>2</v>
       </c>
       <c r="C28" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_6</v>
+        <f>CONCATENATE("MainScene_",A28,"_",B28,"_",C28)</f>
+        <v>MainScene_1_2_5</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -4010,15 +4028,15 @@
         <v>2</v>
       </c>
       <c r="C29" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_7</v>
+        <f>CONCATENATE("MainScene_",A29,"_",B29,"_",C29)</f>
+        <v>MainScene_1_2_6</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4049,15 +4067,15 @@
         <v>2</v>
       </c>
       <c r="C30" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_8</v>
+        <f>CONCATENATE("MainScene_",A30,"_",B30,"_",C30)</f>
+        <v>MainScene_1_2_7</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -4088,15 +4106,15 @@
         <v>2</v>
       </c>
       <c r="C31" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScene_1_2_9</v>
+        <f>CONCATENATE("MainScene_",A31,"_",B31,"_",C31)</f>
+        <v>MainScene_1_2_8</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -4120,12 +4138,23 @@
       <c r="Z31" s="3"/>
     </row>
     <row r="32" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="3"/>
+      <c r="A32" s="4">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="str">
+        <f>CONCATENATE("MainScene_",A32,"_",B32,"_",C32)</f>
+        <v>MainScene_1_2_9</v>
+      </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -4148,13 +4177,27 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
+      <c r="A33" s="4">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2</v>
+      </c>
+      <c r="C33" s="4">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="str">
+        <f>CONCATENATE("MainScene_",A33,"_",B33,"_",C33)</f>
+        <v>MainScene_1_2_10</v>
+      </c>
       <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -4175,12 +4218,23 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="3"/>
+      <c r="A34" s="4">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="str">
+        <f>CONCATENATE("MainScene_",A34,"_",B34,"_",C34)</f>
+        <v>MainScene_1_2_11</v>
+      </c>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -31259,7 +31313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -31267,7 +31321,7 @@
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" customWidth="1"/>
-    <col min="5" max="5" width="58.42578125" customWidth="1"/>
+    <col min="5" max="5" width="58.42578125" style="20" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
@@ -31341,15 +31395,9 @@
       <c r="F2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -31834,7 +31882,7 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
@@ -31874,7 +31922,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>40</v>
@@ -31914,7 +31962,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>40</v>
@@ -31955,7 +32003,7 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>40</v>
@@ -31996,7 +32044,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>40</v>
@@ -32036,7 +32084,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>40</v>
@@ -32077,7 +32125,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -32118,7 +32166,7 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
@@ -32159,14 +32207,12 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -32187,27 +32233,29 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="66">
+    <row r="23" spans="1:26" ht="16.5">
       <c r="A23" s="7">
         <v>1</v>
       </c>
       <c r="B23" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D23" s="5" t="str">
-        <f t="shared" ref="D23:D34" si="1">CONCATENATE("MainScript_",A23,"_",B23,"_",C23)</f>
-        <v>MainScript_1_2_1</v>
+        <f t="shared" ref="D23" si="1">CONCATENATE("MainScript_",A23,"_",B23,"_",C23)</f>
+        <v>MainScript_1_1_22</v>
       </c>
-      <c r="E23" s="16" t="s">
-        <v>86</v>
+      <c r="E23" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -32228,7 +32276,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" ht="49.5">
+    <row r="24" spans="1:26" ht="66">
       <c r="A24" s="7">
         <v>1</v>
       </c>
@@ -32236,14 +32284,14 @@
         <v>2</v>
       </c>
       <c r="C24" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_2</v>
+        <f>CONCATENATE("MainScript_",A23,"_",B24,"_",C24)</f>
+        <v>MainScript_1_2_1</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -32269,7 +32317,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" spans="1:26" ht="82.5">
+    <row r="25" spans="1:26" ht="49.5">
       <c r="A25" s="7">
         <v>1</v>
       </c>
@@ -32277,14 +32325,14 @@
         <v>2</v>
       </c>
       <c r="C25" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_3</v>
+        <f>CONCATENATE("MainScript_",A24,"_",B25,"_",C25)</f>
+        <v>MainScript_1_2_2</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>40</v>
@@ -32310,7 +32358,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="99">
+    <row r="26" spans="1:26" ht="82.5">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -32318,14 +32366,14 @@
         <v>2</v>
       </c>
       <c r="C26" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_4</v>
+        <f>CONCATENATE("MainScript_",A25,"_",B26,"_",C26)</f>
+        <v>MainScript_1_2_3</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>40</v>
@@ -32351,7 +32399,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="33">
+    <row r="27" spans="1:26" ht="99">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -32359,21 +32407,19 @@
         <v>2</v>
       </c>
       <c r="C27" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_5</v>
+        <f>CONCATENATE("MainScript_",A26,"_",B27,"_",C27)</f>
+        <v>MainScript_1_2_4</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -32394,7 +32440,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="115.5">
+    <row r="28" spans="1:26" ht="33">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -32402,19 +32448,21 @@
         <v>2</v>
       </c>
       <c r="C28" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_6</v>
+        <f>CONCATENATE("MainScript_",A27,"_",B28,"_",C28)</f>
+        <v>MainScript_1_2_5</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -32435,7 +32483,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="82.5">
+    <row r="29" spans="1:26" ht="115.5">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -32443,14 +32491,14 @@
         <v>2</v>
       </c>
       <c r="C29" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_7</v>
+        <f>CONCATENATE("MainScript_",A28,"_",B29,"_",C29)</f>
+        <v>MainScript_1_2_6</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>40</v>
@@ -32476,7 +32524,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="49.5">
+    <row r="30" spans="1:26" ht="82.5">
       <c r="A30" s="7">
         <v>1</v>
       </c>
@@ -32484,14 +32532,14 @@
         <v>2</v>
       </c>
       <c r="C30" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_8</v>
+        <f>CONCATENATE("MainScript_",A29,"_",B30,"_",C30)</f>
+        <v>MainScript_1_2_7</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
@@ -32525,14 +32573,14 @@
         <v>2</v>
       </c>
       <c r="C31" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_9</v>
+        <f>CONCATENATE("MainScript_",A30,"_",B31,"_",C31)</f>
+        <v>MainScript_1_2_8</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>40</v>
@@ -32558,7 +32606,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="16.5">
+    <row r="32" spans="1:26" ht="49.5">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -32566,21 +32614,19 @@
         <v>2</v>
       </c>
       <c r="C32" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_10</v>
+        <f>CONCATENATE("MainScript_",A31,"_",B32,"_",C32)</f>
+        <v>MainScript_1_2_9</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -32601,7 +32647,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="33">
+    <row r="33" spans="1:26" ht="16.5">
       <c r="A33" s="7">
         <v>1</v>
       </c>
@@ -32609,17 +32655,21 @@
         <v>2</v>
       </c>
       <c r="C33" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_11</v>
+        <f>CONCATENATE("MainScript_",A32,"_",B33,"_",C33)</f>
+        <v>MainScript_1_2_10</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -32640,7 +32690,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="1:26" ht="16.5">
+    <row r="34" spans="1:26" ht="33">
       <c r="A34" s="7">
         <v>1</v>
       </c>
@@ -32648,14 +32698,18 @@
         <v>2</v>
       </c>
       <c r="C34" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D34" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_2_12</v>
+        <f>CONCATENATE("MainScript_",A33,"_",B34,"_",C34)</f>
+        <v>MainScript_1_2_11</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="E34" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -32679,12 +32733,25 @@
     </row>
     <row r="35" spans="1:26" ht="16.5">
       <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="B35" s="7">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7">
+        <v>12</v>
+      </c>
+      <c r="D35" s="5" t="str">
+        <f>CONCATENATE("MainScript_",A34,"_",B35,"_",C35)</f>
+        <v>MainScript_1_2_12</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -59705,7 +59772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -59736,19 +59803,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -60761,7 +60828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504FFEAE-1D06-4830-AE1D-A9F3A4D77EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="900" windowWidth="16770" windowHeight="13260"/>
+    <workbookView xWindow="15" yWindow="0" windowWidth="16770" windowHeight="13260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
@@ -27,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -58,8 +59,57 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>jwl55</author>
+  </authors>
+  <commentList>
+    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{2E7B0A27-7510-4B72-B75A-D33C73DC1308}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{4C8CCA33-BC42-4747-98EB-82D5A3DC7378}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jwl55:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="137">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -182,15 +232,11 @@
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScript_1_1_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_10</t>
@@ -201,13 +247,13 @@
   <si>
     <t xml:space="preserve">멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">마을 입구 쪽이였다.
 사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">그리고 그 잠깐의 고요함은 오래가지 않았다.
@@ -215,19 +261,19 @@
 창백한 얼굴이 달려오는 아이, 허둥지둥 짐을 챙기는 노인.
 그들의 뒤를 따라, 망토를 뒤집어쓴 이들과 기괴한 형체들이 나타났다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">거칠게 짖는 괴수들,
 날이 빠진 무기를 들고도 거침없이 웃는 산적들.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">그것은 단순한 약탈이 아니었다.
 말살에 가까웠다…
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -382,7 +428,7 @@
 기억도, 감정도, 이 상황을 처음 겪는 사람의 것과는 달랐다.
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_12</t>
@@ -410,11 +456,11 @@
   </si>
   <si>
     <t>NEXTWIN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>NEXTLOSE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -808,7 +854,7 @@
       <t xml:space="preserve">._x000D_
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1379,7 +1425,7 @@
       <t xml:space="preserve">.._x000D_
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1751,7 +1797,7 @@
       <t xml:space="preserve">._x000D_
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1779,7 +1825,7 @@
       <t xml:space="preserve">….?"_x000D_
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1907,11 +1953,11 @@
       <t xml:space="preserve">…_x000D_
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>IMAGE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_18</t>
@@ -1941,12 +1987,8 @@
     <t>MainScript_1_2_4</t>
   </si>
   <si>
-    <t>MainScript_1_2_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScript_1_2_6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_2_8</t>
@@ -1956,12 +1998,12 @@
   </si>
   <si>
     <t>Break</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">벽돌을 옆으로 치운다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">"생존자다…!"
@@ -1969,26 +2011,26 @@
 나는 조심스레 다가갔고 
 그곳에는 벽돌 더미에 깔린 어린 소년이 있었다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">무너진 가게 앞
 진흙투성이가 된 거리 한복판에서 목소리가 들렸다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">불타던 마을은 잿더미가 되어 있었다.
 붉게 달아올랐던 불길도 꺼졌고
 연기만이 바람을 따라 흘러가고 있었다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">나는 그 뒤를 따랐다. 
 그리고 그렇게, 이야기는 움직이기 시작했다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">나는 천천히 일어났다
@@ -1996,19 +2038,19 @@
 "넌… 결국 이렇게 떠나는 구나…."
 "왜…. 왜 매번 이렇게 되는거지…."
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">손바닥에는 진흙과 피가 묻어 있었지만. 
 그 손은 어디에도 닦지 않았다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">고개를 들어 폐허 너머를 바라봤다.
 이제 이 마을엔 더 머물 이유도.. 머물 자리도 없었다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2340,31 +2382,31 @@
       <t xml:space="preserve">."
 </t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">소년의 눈동자가 흔들렸다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">"지금 멈추면, 이건 또 하나의 반복으로 끝나겠지
 하지만 네가 걸어간다면 끝은 달라질 수도 있어."
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">나는 아무 말 없이 그 빛을 바라보았다.
 나는 천천히 일어났고
 푸른 위습은 앞서 나아가듯 떠올랐다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">"사람은 아니고"
 빛은 멈추었고 천천히 아주 낮고 부드러운 목소리로 말했다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">그때였다. 시야 가장자리에, 느릿하게 퍼지는 빛이 있었다.
@@ -2372,12 +2414,12 @@
 불에 탄 공기 속에서, 그 빛은 아무 말도 없이 다가왔다.
 낯설고 설명할 수 없지만, 이상하게 시선을 뗄 수 없었다.
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">"이번에도 살아남았네… 왜… 도대체 왜…"
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">그리고 얼마 지나지 않아 마을은 그 기능을 완전히 잃었다.
@@ -2387,25 +2429,25 @@
 손에는 작은 흠집만 남았고, 주변은 적막뿐이였다.
 "또…. 나만.."
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScene_1_2_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_2_7</t>
   </si>
   <si>
     <t xml:space="preserve">STR*10 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_2_10</t>
   </si>
   <si>
     <t>무시하고 옆으로 지나간다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">나는 소년이랑 눈이 마주쳤고 
@@ -2413,30 +2455,20 @@
 하지만 아이는 눈을 크게 뜨고 움찔거렸다.
 본능적으로 나를 두려워하는 눈빛이였다…
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">나는 손을 거두고 
-"…괜찮아."
-라고 작은 목소리로 중얼거렸다…
-나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
-하지만 그 소년은 숨이 점점 거칠어 지다가 
-결국 숨이 끊어져 버렸다.
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">"어차피 죽을 목숨이였어…"
 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>다음 이야기로</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MainScript_1_1_22</t>
@@ -2452,22 +2484,122 @@
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Break</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene_1_2_8</t>
+  </si>
+  <si>
+    <t>나는 천천히 걸음을 옮겼고
+푸른 위습은 그 옆을 따라왔다.
+두 존재는 그렇게, 죽음이 남긴 마을을 등지고 나아가고 있었다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1E1_house</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1E1_danger</t>
+  </si>
+  <si>
+    <t>C1E1_meeting_wisp</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_1</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_23</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_24</t>
+  </si>
+  <si>
+    <t>MainScript_1_1_25</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_12</t>
+  </si>
+  <si>
+    <t>C1E2_child_under_the_rubble</t>
+  </si>
+  <si>
+    <t>C1E2_extension</t>
+  </si>
+  <si>
+    <t>C1E2_sighting</t>
+  </si>
+  <si>
+    <t>C1E2_journey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 손을 거두고 
+"…괜찮아."
+라고 작은 목소리로 중얼거렸다…
+나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 그 소년은 숨이 점점 거칠어 지다가 
+결국 숨이 끊어져 버렸다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1E2_finally</t>
+  </si>
+  <si>
+    <t>C1E2_rescue</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_13</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_14</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_15</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_16</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_17</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_18</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_19</t>
+  </si>
+  <si>
+    <t>MainScene_1_2_16</t>
+  </si>
+  <si>
+    <t>MainScene_1_2_18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2548,6 +2680,19 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2623,65 +2768,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2897,7 +3045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2981,12 +3129,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D31" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -3103,7 +3251,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -3298,7 +3446,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -3337,7 +3485,7 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -3376,7 +3524,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -3415,7 +3563,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5"/>
@@ -3454,7 +3602,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -3492,7 +3640,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -3530,7 +3678,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -3568,7 +3716,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -3606,7 +3754,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -3645,7 +3793,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -3679,12 +3827,12 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A20,"_",B20,"_",C20)</f>
+        <f t="shared" ref="D20:E35" si="1">CONCATENATE("MainScene_",A20,"_",B20,"_",C20)</f>
         <v>MainScene_1_1_19</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -3718,12 +3866,12 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A21,"_",B21,"_",C21)</f>
+        <f t="shared" si="1"/>
         <v>MainScene_1_1_20</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -3757,17 +3905,15 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A22,"_",B22,"_",C22)</f>
+        <f t="shared" si="1"/>
         <v>MainScene_1_1_21</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
-        <v>107</v>
-      </c>
+      <c r="H22" s="5"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -3798,11 +3944,11 @@
         <v>22</v>
       </c>
       <c r="D23" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A23,"_",B23,"_",C23)</f>
+        <f t="shared" si="1"/>
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -3831,15 +3977,15 @@
         <v>2</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A24,"_",B24,"_",C24)</f>
-        <v>MainScene_1_2_1</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_23</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -3870,15 +4016,15 @@
         <v>2</v>
       </c>
       <c r="C25" s="4">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A25,"_",B25,"_",C25)</f>
-        <v>MainScene_1_2_2</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_24</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -3909,15 +4055,15 @@
         <v>2</v>
       </c>
       <c r="C26" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A26,"_",B26,"_",C26)</f>
-        <v>MainScene_1_2_3</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_25</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -3948,20 +4094,18 @@
         <v>2</v>
       </c>
       <c r="C27" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A27,"_",B27,"_",C27)</f>
-        <v>MainScene_1_2_4</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_1</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -3989,15 +4133,15 @@
         <v>2</v>
       </c>
       <c r="C28" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A28,"_",B28,"_",C28)</f>
-        <v>MainScene_1_2_5</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_2</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -4028,15 +4172,15 @@
         <v>2</v>
       </c>
       <c r="C29" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A29,"_",B29,"_",C29)</f>
-        <v>MainScene_1_2_6</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_3</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4067,15 +4211,15 @@
         <v>2</v>
       </c>
       <c r="C30" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A30,"_",B30,"_",C30)</f>
-        <v>MainScene_1_2_7</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_4</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -4106,15 +4250,15 @@
         <v>2</v>
       </c>
       <c r="C31" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A31,"_",B31,"_",C31)</f>
-        <v>MainScene_1_2_8</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_5</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -4145,21 +4289,29 @@
         <v>2</v>
       </c>
       <c r="C32" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D32" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A32,"_",B32,"_",C32)</f>
-        <v>MainScene_1_2_9</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_6</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
+      <c r="H32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -4184,20 +4336,18 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A33,"_",B33,"_",C33)</f>
-        <v>MainScene_1_2_10</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_7</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -4225,15 +4375,15 @@
         <v>2</v>
       </c>
       <c r="C34" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="str">
-        <f>CONCATENATE("MainScene_",A34,"_",B34,"_",C34)</f>
-        <v>MainScene_1_2_11</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_8</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -4257,12 +4407,23 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="3"/>
+      <c r="A35" s="4">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4">
+        <v>2</v>
+      </c>
+      <c r="C35" s="4">
+        <v>9</v>
+      </c>
+      <c r="D35" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_9</v>
+      </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -4285,12 +4446,23 @@
       <c r="Z35" s="3"/>
     </row>
     <row r="36" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="3"/>
+      <c r="A36" s="4">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4">
+        <v>10</v>
+      </c>
+      <c r="D36" s="3" t="str">
+        <f t="shared" ref="D36:E45" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <v>MainScene_1_2_10</v>
+      </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4313,12 +4485,23 @@
       <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="3"/>
+      <c r="A37" s="4">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4">
+        <v>2</v>
+      </c>
+      <c r="C37" s="4">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_11</v>
+      </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -4341,12 +4524,23 @@
       <c r="Z37" s="3"/>
     </row>
     <row r="38" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="3"/>
+      <c r="A38" s="4">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4">
+        <v>2</v>
+      </c>
+      <c r="C38" s="4">
+        <v>12</v>
+      </c>
+      <c r="D38" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_12</v>
+      </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -4369,12 +4563,23 @@
       <c r="Z38" s="3"/>
     </row>
     <row r="39" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="3"/>
+      <c r="A39" s="4">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4">
+        <v>2</v>
+      </c>
+      <c r="C39" s="4">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_13</v>
+      </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4397,12 +4602,25 @@
       <c r="Z39" s="3"/>
     </row>
     <row r="40" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="A40" s="4">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4">
+        <v>2</v>
+      </c>
+      <c r="C40" s="4">
+        <v>14</v>
+      </c>
+      <c r="D40" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_14</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -4425,12 +4643,23 @@
       <c r="Z40" s="3"/>
     </row>
     <row r="41" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="3"/>
+      <c r="A41" s="4">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4">
+        <v>2</v>
+      </c>
+      <c r="C41" s="4">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_15</v>
+      </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4453,12 +4682,23 @@
       <c r="Z41" s="3"/>
     </row>
     <row r="42" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="4">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4">
+        <v>2</v>
+      </c>
+      <c r="C42" s="4">
+        <v>16</v>
+      </c>
+      <c r="D42" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_16</v>
+      </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -4481,12 +4721,23 @@
       <c r="Z42" s="3"/>
     </row>
     <row r="43" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="4">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4">
+        <v>2</v>
+      </c>
+      <c r="C43" s="4">
+        <v>17</v>
+      </c>
+      <c r="D43" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_17</v>
+      </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -4509,12 +4760,23 @@
       <c r="Z43" s="3"/>
     </row>
     <row r="44" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="3"/>
+      <c r="A44" s="4">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44" s="4">
+        <v>18</v>
+      </c>
+      <c r="D44" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_18</v>
+      </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -4537,12 +4799,23 @@
       <c r="Z44" s="3"/>
     </row>
     <row r="45" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="3"/>
+      <c r="A45" s="4">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4">
+        <v>2</v>
+      </c>
+      <c r="C45" s="4">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_2_19</v>
+      </c>
       <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -31305,7 +31578,7 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -31313,15 +31586,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z999"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z1009"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" customWidth="1"/>
-    <col min="5" max="5" width="58.42578125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="65.5703125" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
@@ -31352,10 +31625,10 @@
         <v>39</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -31386,14 +31659,14 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D20" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D45" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -31431,7 +31704,7 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>40</v>
@@ -31472,12 +31745,14 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -31498,7 +31773,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" spans="1:26" ht="60">
+    <row r="5" spans="1:26" ht="16.5">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -31513,10 +31788,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>40</v>
+      <c r="F5" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -31539,7 +31814,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" spans="1:26" ht="30">
+    <row r="6" spans="1:26" ht="60">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -31554,7 +31829,7 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>40</v>
@@ -31594,7 +31869,7 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_6</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -31635,8 +31910,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_7</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>45</v>
+      <c r="E8" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>40</v>
@@ -31662,7 +31937,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="45">
+    <row r="9" spans="1:26" ht="30">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -31677,7 +31952,7 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>40</v>
@@ -31703,7 +31978,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="90">
+    <row r="10" spans="1:26" ht="45">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -31718,7 +31993,7 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>40</v>
@@ -31744,7 +32019,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="45">
+    <row r="11" spans="1:26" ht="90">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -31759,10 +32034,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -31800,10 +32075,10 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -31826,7 +32101,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" ht="66">
+    <row r="13" spans="1:26" ht="45">
       <c r="A13" s="7">
         <v>1</v>
       </c>
@@ -31840,8 +32115,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_12</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>50</v>
+      <c r="E13" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>40</v>
@@ -31867,7 +32142,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="115.5">
+    <row r="14" spans="1:26" ht="66">
       <c r="A14" s="7">
         <v>1</v>
       </c>
@@ -31881,11 +32156,14 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_13</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>96</v>
+      <c r="E14" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -31907,7 +32185,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="30">
+    <row r="15" spans="1:26" ht="16.5">
       <c r="A15" s="7">
         <v>1</v>
       </c>
@@ -31921,13 +32199,14 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_14</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>95</v>
+      <c r="E15" s="21" t="s">
+        <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -31947,7 +32226,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" ht="75">
+    <row r="16" spans="1:26" ht="115.5">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -31961,13 +32240,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_15</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="16" t="s">
         <v>94</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
@@ -31988,7 +32266,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="45">
+    <row r="17" spans="1:26" ht="30">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -32008,8 +32286,9 @@
       <c r="F17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="G17" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -32029,7 +32308,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="60">
+    <row r="18" spans="1:26" ht="16.5">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -32043,13 +32322,13 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_1_17</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>89</v>
+      <c r="E18" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="G18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -32069,7 +32348,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="30">
+    <row r="19" spans="1:26" ht="75">
       <c r="A19" s="7">
         <v>1</v>
       </c>
@@ -32084,7 +32363,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>40</v>
@@ -32151,7 +32430,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="66">
+    <row r="21" spans="1:26" ht="60">
       <c r="A21" s="7">
         <v>1</v>
       </c>
@@ -32162,16 +32441,15 @@
         <v>20</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A21,"_",B21,"_",C21)</f>
+        <f t="shared" si="0"/>
         <v>MainScript_1_1_20</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>92</v>
+      <c r="E21" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -32192,7 +32470,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" ht="49.5">
+    <row r="22" spans="1:26" ht="30">
       <c r="A22" s="7">
         <v>1</v>
       </c>
@@ -32203,11 +32481,11 @@
         <v>21</v>
       </c>
       <c r="D22" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A22,"_",B22,"_",C22)</f>
+        <f t="shared" si="0"/>
         <v>MainScript_1_1_21</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>85</v>
+      <c r="E22" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
@@ -32233,7 +32511,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="16.5">
+    <row r="23" spans="1:26" ht="45">
       <c r="A23" s="7">
         <v>1</v>
       </c>
@@ -32244,18 +32522,16 @@
         <v>22</v>
       </c>
       <c r="D23" s="5" t="str">
-        <f t="shared" ref="D23" si="1">CONCATENATE("MainScript_",A23,"_",B23,"_",C23)</f>
+        <f t="shared" si="0"/>
         <v>MainScript_1_1_22</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>105</v>
+      <c r="E23" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -32281,17 +32557,17 @@
         <v>1</v>
       </c>
       <c r="B24" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="7">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D24" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A23,"_",B24,"_",C24)</f>
-        <v>MainScript_1_2_1</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -32322,14 +32598,14 @@
         <v>1</v>
       </c>
       <c r="B25" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="7">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A24,"_",B25,"_",C25)</f>
-        <v>MainScript_1_2_2</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>83</v>
@@ -32358,27 +32634,29 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="82.5">
+    <row r="26" spans="1:26" ht="16.5">
       <c r="A26" s="7">
         <v>1</v>
       </c>
       <c r="B26" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A25,"_",B26,"_",C26)</f>
-        <v>MainScript_1_2_3</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_1_25</v>
       </c>
-      <c r="E26" s="16" t="s">
-        <v>82</v>
+      <c r="E26" s="18" t="s">
+        <v>102</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
-      <c r="G26" s="5"/>
+      <c r="G26" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -32399,7 +32677,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="99">
+    <row r="27" spans="1:26" ht="66">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -32407,14 +32685,14 @@
         <v>2</v>
       </c>
       <c r="C27" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A26,"_",B27,"_",C27)</f>
-        <v>MainScript_1_2_4</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_1</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>40</v>
@@ -32440,7 +32718,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="33">
+    <row r="28" spans="1:26" ht="49.5">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -32448,11 +32726,11 @@
         <v>2</v>
       </c>
       <c r="C28" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A27,"_",B28,"_",C28)</f>
-        <v>MainScript_1_2_5</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_2</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>81</v>
@@ -32461,7 +32739,7 @@
         <v>40</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -32483,7 +32761,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="115.5">
+    <row r="29" spans="1:26" ht="16.5">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -32491,17 +32769,17 @@
         <v>2</v>
       </c>
       <c r="C29" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A28,"_",B29,"_",C29)</f>
-        <v>MainScript_1_2_6</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -32532,19 +32810,21 @@
         <v>2</v>
       </c>
       <c r="C30" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A29,"_",B30,"_",C30)</f>
-        <v>MainScript_1_2_7</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -32565,7 +32845,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="49.5">
+    <row r="31" spans="1:26" ht="16.5">
       <c r="A31" s="7">
         <v>1</v>
       </c>
@@ -32573,17 +32853,17 @@
         <v>2</v>
       </c>
       <c r="C31" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A30,"_",B31,"_",C31)</f>
-        <v>MainScript_1_2_8</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -32606,7 +32886,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="49.5">
+    <row r="32" spans="1:26" ht="99">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -32614,19 +32894,21 @@
         <v>2</v>
       </c>
       <c r="C32" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D32" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A31,"_",B32,"_",C32)</f>
-        <v>MainScript_1_2_9</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -32647,7 +32929,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="16.5">
+    <row r="33" spans="1:26" ht="33">
       <c r="A33" s="7">
         <v>1</v>
       </c>
@@ -32655,21 +32937,19 @@
         <v>2</v>
       </c>
       <c r="C33" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A32,"_",B33,"_",C33)</f>
-        <v>MainScript_1_2_10</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -32690,7 +32970,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="1:26" ht="33">
+    <row r="34" spans="1:26" ht="16.5">
       <c r="A34" s="7">
         <v>1</v>
       </c>
@@ -32698,17 +32978,17 @@
         <v>2</v>
       </c>
       <c r="C34" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D34" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A33,"_",B34,"_",C34)</f>
-        <v>MainScript_1_2_11</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -32731,26 +33011,28 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" spans="1:26" ht="16.5">
-      <c r="A35" s="7"/>
+    <row r="35" spans="1:26" ht="99">
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
       <c r="B35" s="7">
         <v>2</v>
       </c>
       <c r="C35" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="5" t="str">
-        <f>CONCATENATE("MainScript_",A34,"_",B35,"_",C35)</f>
-        <v>MainScript_1_2_12</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_9</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>105</v>
+      <c r="E35" s="16" t="s">
+        <v>124</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -32773,12 +33055,25 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="1:26" ht="16.5">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>10</v>
+      </c>
+      <c r="D36" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_10</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -32800,14 +33095,29 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="16.5">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+    <row r="37" spans="1:26" ht="33">
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="7">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>11</v>
+      </c>
+      <c r="D37" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_11</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -32829,12 +33139,25 @@
       <c r="Z37" s="5"/>
     </row>
     <row r="38" spans="1:26" ht="16.5">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>12</v>
+      </c>
+      <c r="D38" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_12</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -32856,14 +33179,29 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" spans="1:26" ht="16.5">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+    <row r="39" spans="1:26" ht="82.5">
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>13</v>
+      </c>
+      <c r="D39" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_13</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
@@ -32884,13 +33222,26 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" spans="1:26" ht="16.5">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+    <row r="40" spans="1:26" ht="49.5">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="7">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7">
+        <v>14</v>
+      </c>
+      <c r="D40" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_14</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -32913,13 +33264,28 @@
       <c r="Z40" s="5"/>
     </row>
     <row r="41" spans="1:26" ht="16.5">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7">
+        <v>15</v>
+      </c>
+      <c r="D41" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_15</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -32940,14 +33306,26 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" spans="1:26" ht="16.5">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+    <row r="42" spans="1:26" ht="33">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="7">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>16</v>
+      </c>
+      <c r="D42" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_16</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -32969,13 +33347,25 @@
       <c r="Z42" s="5"/>
     </row>
     <row r="43" spans="1:26" ht="16.5">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="7">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>17</v>
+      </c>
+      <c r="D43" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_17</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -32996,13 +33386,26 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" spans="1:26" ht="16.5">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+    <row r="44" spans="1:26" ht="49.5">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="7">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>18</v>
+      </c>
+      <c r="D44" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_18</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -33024,13 +33427,26 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" spans="1:26" ht="16.5">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+    <row r="45" spans="1:26" ht="49.5">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="7">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>19</v>
+      </c>
+      <c r="D45" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_2_19</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -59764,15 +60180,271 @@
       <c r="Y999" s="5"/>
       <c r="Z999" s="5"/>
     </row>
+    <row r="1000" spans="1:26" ht="16.5">
+      <c r="A1000" s="7"/>
+      <c r="B1000" s="7"/>
+      <c r="C1000" s="7"/>
+      <c r="D1000" s="5"/>
+      <c r="E1000" s="5"/>
+      <c r="F1000" s="5"/>
+      <c r="G1000" s="5"/>
+      <c r="H1000" s="5"/>
+      <c r="I1000" s="5"/>
+      <c r="J1000" s="5"/>
+      <c r="K1000" s="5"/>
+      <c r="L1000" s="5"/>
+      <c r="M1000" s="5"/>
+      <c r="N1000" s="5"/>
+      <c r="O1000" s="5"/>
+      <c r="P1000" s="5"/>
+      <c r="Q1000" s="5"/>
+      <c r="R1000" s="5"/>
+      <c r="S1000" s="5"/>
+      <c r="T1000" s="5"/>
+      <c r="U1000" s="5"/>
+      <c r="V1000" s="5"/>
+      <c r="W1000" s="5"/>
+      <c r="X1000" s="5"/>
+      <c r="Y1000" s="5"/>
+      <c r="Z1000" s="5"/>
+    </row>
+    <row r="1001" spans="1:26" ht="16.5">
+      <c r="A1001" s="7"/>
+      <c r="B1001" s="7"/>
+      <c r="C1001" s="7"/>
+      <c r="D1001" s="5"/>
+      <c r="E1001" s="5"/>
+      <c r="F1001" s="5"/>
+      <c r="G1001" s="5"/>
+      <c r="H1001" s="5"/>
+      <c r="I1001" s="5"/>
+      <c r="J1001" s="5"/>
+      <c r="K1001" s="5"/>
+      <c r="L1001" s="5"/>
+      <c r="M1001" s="5"/>
+      <c r="N1001" s="5"/>
+      <c r="O1001" s="5"/>
+      <c r="P1001" s="5"/>
+      <c r="Q1001" s="5"/>
+      <c r="R1001" s="5"/>
+      <c r="S1001" s="5"/>
+      <c r="T1001" s="5"/>
+      <c r="U1001" s="5"/>
+      <c r="V1001" s="5"/>
+      <c r="W1001" s="5"/>
+      <c r="X1001" s="5"/>
+      <c r="Y1001" s="5"/>
+      <c r="Z1001" s="5"/>
+    </row>
+    <row r="1002" spans="1:26" ht="16.5">
+      <c r="A1002" s="7"/>
+      <c r="B1002" s="7"/>
+      <c r="C1002" s="7"/>
+      <c r="D1002" s="5"/>
+      <c r="E1002" s="5"/>
+      <c r="F1002" s="5"/>
+      <c r="G1002" s="5"/>
+      <c r="H1002" s="5"/>
+      <c r="I1002" s="5"/>
+      <c r="J1002" s="5"/>
+      <c r="K1002" s="5"/>
+      <c r="L1002" s="5"/>
+      <c r="M1002" s="5"/>
+      <c r="N1002" s="5"/>
+      <c r="O1002" s="5"/>
+      <c r="P1002" s="5"/>
+      <c r="Q1002" s="5"/>
+      <c r="R1002" s="5"/>
+      <c r="S1002" s="5"/>
+      <c r="T1002" s="5"/>
+      <c r="U1002" s="5"/>
+      <c r="V1002" s="5"/>
+      <c r="W1002" s="5"/>
+      <c r="X1002" s="5"/>
+      <c r="Y1002" s="5"/>
+      <c r="Z1002" s="5"/>
+    </row>
+    <row r="1003" spans="1:26" ht="16.5">
+      <c r="A1003" s="7"/>
+      <c r="B1003" s="7"/>
+      <c r="C1003" s="7"/>
+      <c r="D1003" s="5"/>
+      <c r="E1003" s="5"/>
+      <c r="F1003" s="5"/>
+      <c r="G1003" s="5"/>
+      <c r="H1003" s="5"/>
+      <c r="I1003" s="5"/>
+      <c r="J1003" s="5"/>
+      <c r="K1003" s="5"/>
+      <c r="L1003" s="5"/>
+      <c r="M1003" s="5"/>
+      <c r="N1003" s="5"/>
+      <c r="O1003" s="5"/>
+      <c r="P1003" s="5"/>
+      <c r="Q1003" s="5"/>
+      <c r="R1003" s="5"/>
+      <c r="S1003" s="5"/>
+      <c r="T1003" s="5"/>
+      <c r="U1003" s="5"/>
+      <c r="V1003" s="5"/>
+      <c r="W1003" s="5"/>
+      <c r="X1003" s="5"/>
+      <c r="Y1003" s="5"/>
+      <c r="Z1003" s="5"/>
+    </row>
+    <row r="1004" spans="1:26" ht="16.5">
+      <c r="A1004" s="7"/>
+      <c r="B1004" s="7"/>
+      <c r="C1004" s="7"/>
+      <c r="D1004" s="5"/>
+      <c r="E1004" s="5"/>
+      <c r="F1004" s="5"/>
+      <c r="G1004" s="5"/>
+      <c r="H1004" s="5"/>
+      <c r="I1004" s="5"/>
+      <c r="J1004" s="5"/>
+      <c r="K1004" s="5"/>
+      <c r="L1004" s="5"/>
+      <c r="M1004" s="5"/>
+      <c r="N1004" s="5"/>
+      <c r="O1004" s="5"/>
+      <c r="P1004" s="5"/>
+      <c r="Q1004" s="5"/>
+      <c r="R1004" s="5"/>
+      <c r="S1004" s="5"/>
+      <c r="T1004" s="5"/>
+      <c r="U1004" s="5"/>
+      <c r="V1004" s="5"/>
+      <c r="W1004" s="5"/>
+      <c r="X1004" s="5"/>
+      <c r="Y1004" s="5"/>
+      <c r="Z1004" s="5"/>
+    </row>
+    <row r="1005" spans="1:26" ht="16.5">
+      <c r="A1005" s="7"/>
+      <c r="B1005" s="7"/>
+      <c r="C1005" s="7"/>
+      <c r="D1005" s="5"/>
+      <c r="E1005" s="5"/>
+      <c r="F1005" s="5"/>
+      <c r="G1005" s="5"/>
+      <c r="H1005" s="5"/>
+      <c r="I1005" s="5"/>
+      <c r="J1005" s="5"/>
+      <c r="K1005" s="5"/>
+      <c r="L1005" s="5"/>
+      <c r="M1005" s="5"/>
+      <c r="N1005" s="5"/>
+      <c r="O1005" s="5"/>
+      <c r="P1005" s="5"/>
+      <c r="Q1005" s="5"/>
+      <c r="R1005" s="5"/>
+      <c r="S1005" s="5"/>
+      <c r="T1005" s="5"/>
+      <c r="U1005" s="5"/>
+      <c r="V1005" s="5"/>
+      <c r="W1005" s="5"/>
+      <c r="X1005" s="5"/>
+      <c r="Y1005" s="5"/>
+      <c r="Z1005" s="5"/>
+    </row>
+    <row r="1006" spans="1:26" ht="16.5">
+      <c r="A1006" s="7"/>
+      <c r="B1006" s="7"/>
+      <c r="C1006" s="7"/>
+      <c r="D1006" s="5"/>
+      <c r="E1006" s="5"/>
+      <c r="F1006" s="5"/>
+      <c r="G1006" s="5"/>
+      <c r="H1006" s="5"/>
+      <c r="I1006" s="5"/>
+      <c r="J1006" s="5"/>
+      <c r="K1006" s="5"/>
+      <c r="L1006" s="5"/>
+      <c r="M1006" s="5"/>
+      <c r="N1006" s="5"/>
+      <c r="O1006" s="5"/>
+      <c r="P1006" s="5"/>
+      <c r="Q1006" s="5"/>
+      <c r="R1006" s="5"/>
+      <c r="S1006" s="5"/>
+      <c r="T1006" s="5"/>
+      <c r="U1006" s="5"/>
+      <c r="V1006" s="5"/>
+      <c r="W1006" s="5"/>
+      <c r="X1006" s="5"/>
+      <c r="Y1006" s="5"/>
+      <c r="Z1006" s="5"/>
+    </row>
+    <row r="1007" spans="1:26" ht="16.5">
+      <c r="A1007" s="7"/>
+      <c r="B1007" s="7"/>
+      <c r="C1007" s="7"/>
+      <c r="D1007" s="5"/>
+      <c r="E1007" s="5"/>
+      <c r="F1007" s="5"/>
+      <c r="G1007" s="5"/>
+      <c r="H1007" s="5"/>
+      <c r="I1007" s="5"/>
+      <c r="J1007" s="5"/>
+      <c r="K1007" s="5"/>
+      <c r="L1007" s="5"/>
+      <c r="M1007" s="5"/>
+      <c r="N1007" s="5"/>
+      <c r="O1007" s="5"/>
+      <c r="P1007" s="5"/>
+      <c r="Q1007" s="5"/>
+      <c r="R1007" s="5"/>
+      <c r="S1007" s="5"/>
+      <c r="T1007" s="5"/>
+      <c r="U1007" s="5"/>
+      <c r="V1007" s="5"/>
+      <c r="W1007" s="5"/>
+      <c r="X1007" s="5"/>
+      <c r="Y1007" s="5"/>
+      <c r="Z1007" s="5"/>
+    </row>
+    <row r="1008" spans="1:26" ht="16.5">
+      <c r="A1008" s="7"/>
+      <c r="B1008" s="7"/>
+      <c r="C1008" s="7"/>
+      <c r="D1008" s="5"/>
+      <c r="E1008" s="5"/>
+      <c r="F1008" s="5"/>
+      <c r="G1008" s="5"/>
+      <c r="H1008" s="5"/>
+      <c r="I1008" s="5"/>
+      <c r="J1008" s="5"/>
+      <c r="K1008" s="5"/>
+      <c r="L1008" s="5"/>
+      <c r="M1008" s="5"/>
+      <c r="N1008" s="5"/>
+      <c r="O1008" s="5"/>
+      <c r="P1008" s="5"/>
+      <c r="Q1008" s="5"/>
+      <c r="R1008" s="5"/>
+      <c r="S1008" s="5"/>
+      <c r="T1008" s="5"/>
+      <c r="U1008" s="5"/>
+      <c r="V1008" s="5"/>
+      <c r="W1008" s="5"/>
+      <c r="X1008" s="5"/>
+      <c r="Y1008" s="5"/>
+      <c r="Z1008" s="5"/>
+    </row>
+    <row r="1009" spans="5:5" ht="16.5">
+      <c r="E1009" s="5"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -59803,19 +60475,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -60821,14 +61493,14 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -61892,7 +62564,7 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504FFEAE-1D06-4830-AE1D-A9F3A4D77EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CDDA3F-565E-4858-BFA2-A4A82F879335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="0" windowWidth="16770" windowHeight="13260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40290" yWindow="1470" windowWidth="16770" windowHeight="13260" firstSheet="1" activeTab="2" xr2:uid="{2D37D46F-FF3D-47B1-BBBE-027E6665CAAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="144">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2582,6 +2583,38 @@
   <si>
     <t>MainScene_1_2_18</t>
   </si>
+  <si>
+    <t>갑자기 나뭇잎 사이로 괴물이 튀어나왔다
+더 이상 인간이라고 부르기 어려운 형체였다..</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 본능적으로 뒤로 물러섰다.
+"…젠장…"</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기…
+손에 쥘 만한 무엇이든
+나는 주변을 둘러보다가 땅에 떨어진 무기를 발견했다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>검</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>활</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>단검</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>지팡이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3827,7 +3860,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f t="shared" ref="D20:E35" si="1">CONCATENATE("MainScene_",A20,"_",B20,"_",C20)</f>
+        <f t="shared" ref="D20:D35" si="1">CONCATENATE("MainScene_",A20,"_",B20,"_",C20)</f>
         <v>MainScene_1_1_19</v>
       </c>
       <c r="E20" s="3"/>
@@ -4456,7 +4489,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" ref="D36:E45" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <f t="shared" ref="D36:D45" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
@@ -31659,7 +31692,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D45" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D59" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
@@ -32019,7 +32052,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="90">
+    <row r="11" spans="1:26" ht="75">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -33468,12 +33501,23 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" ht="16.5">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
+    <row r="46" spans="1:26" ht="33">
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="7">
+        <v>3</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_1</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>137</v>
+      </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -33496,12 +33540,23 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" ht="16.5">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
+    <row r="47" spans="1:26" ht="33">
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="7">
+        <v>3</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2</v>
+      </c>
+      <c r="D47" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_2</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>138</v>
+      </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -33524,12 +33579,23 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" spans="1:26" ht="16.5">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
+    <row r="48" spans="1:26" ht="49.5">
+      <c r="A48" s="7">
+        <v>1</v>
+      </c>
+      <c r="B48" s="7">
+        <v>3</v>
+      </c>
+      <c r="C48" s="7">
+        <v>3</v>
+      </c>
+      <c r="D48" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_3</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>139</v>
+      </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -33553,11 +33619,22 @@
       <c r="Z48" s="5"/>
     </row>
     <row r="49" spans="1:26" ht="16.5">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
+      <c r="A49" s="7">
+        <v>1</v>
+      </c>
+      <c r="B49" s="7">
+        <v>3</v>
+      </c>
+      <c r="C49" s="7">
+        <v>4</v>
+      </c>
+      <c r="D49" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_4</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>140</v>
+      </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -33581,11 +33658,22 @@
       <c r="Z49" s="5"/>
     </row>
     <row r="50" spans="1:26" ht="16.5">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
+      <c r="A50" s="7">
+        <v>1</v>
+      </c>
+      <c r="B50" s="7">
+        <v>3</v>
+      </c>
+      <c r="C50" s="7">
+        <v>5</v>
+      </c>
+      <c r="D50" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_5</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -33609,11 +33697,22 @@
       <c r="Z50" s="5"/>
     </row>
     <row r="51" spans="1:26" ht="16.5">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
+      <c r="A51" s="7">
+        <v>1</v>
+      </c>
+      <c r="B51" s="7">
+        <v>3</v>
+      </c>
+      <c r="C51" s="7">
+        <v>6</v>
+      </c>
+      <c r="D51" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_6</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>142</v>
+      </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -33637,11 +33736,22 @@
       <c r="Z51" s="5"/>
     </row>
     <row r="52" spans="1:26" ht="16.5">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
+      <c r="A52" s="7">
+        <v>1</v>
+      </c>
+      <c r="B52" s="7">
+        <v>3</v>
+      </c>
+      <c r="C52" s="7">
+        <v>7</v>
+      </c>
+      <c r="D52" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_7</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>143</v>
+      </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -33665,10 +33775,19 @@
       <c r="Z52" s="5"/>
     </row>
     <row r="53" spans="1:26" ht="16.5">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="5"/>
+      <c r="A53" s="7">
+        <v>1</v>
+      </c>
+      <c r="B53" s="7">
+        <v>3</v>
+      </c>
+      <c r="C53" s="7">
+        <v>8</v>
+      </c>
+      <c r="D53" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_8</v>
+      </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -33693,10 +33812,19 @@
       <c r="Z53" s="5"/>
     </row>
     <row r="54" spans="1:26" ht="16.5">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="5"/>
+      <c r="A54" s="7">
+        <v>1</v>
+      </c>
+      <c r="B54" s="7">
+        <v>3</v>
+      </c>
+      <c r="C54" s="7">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_9</v>
+      </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -33721,10 +33849,19 @@
       <c r="Z54" s="5"/>
     </row>
     <row r="55" spans="1:26" ht="16.5">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="5"/>
+      <c r="A55" s="7">
+        <v>1</v>
+      </c>
+      <c r="B55" s="7">
+        <v>3</v>
+      </c>
+      <c r="C55" s="7">
+        <v>10</v>
+      </c>
+      <c r="D55" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_10</v>
+      </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -33749,10 +33886,19 @@
       <c r="Z55" s="5"/>
     </row>
     <row r="56" spans="1:26" ht="16.5">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="5"/>
+      <c r="A56" s="7">
+        <v>1</v>
+      </c>
+      <c r="B56" s="7">
+        <v>3</v>
+      </c>
+      <c r="C56" s="7">
+        <v>11</v>
+      </c>
+      <c r="D56" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_11</v>
+      </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -33777,10 +33923,19 @@
       <c r="Z56" s="5"/>
     </row>
     <row r="57" spans="1:26" ht="16.5">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="5"/>
+      <c r="A57" s="7">
+        <v>1</v>
+      </c>
+      <c r="B57" s="7">
+        <v>3</v>
+      </c>
+      <c r="C57" s="7">
+        <v>12</v>
+      </c>
+      <c r="D57" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_12</v>
+      </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -33805,10 +33960,19 @@
       <c r="Z57" s="5"/>
     </row>
     <row r="58" spans="1:26" ht="16.5">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="5"/>
+      <c r="A58" s="7">
+        <v>1</v>
+      </c>
+      <c r="B58" s="7">
+        <v>3</v>
+      </c>
+      <c r="C58" s="7">
+        <v>13</v>
+      </c>
+      <c r="D58" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_13</v>
+      </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -33833,10 +33997,19 @@
       <c r="Z58" s="5"/>
     </row>
     <row r="59" spans="1:26" ht="16.5">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="5"/>
+      <c r="A59" s="7">
+        <v>1</v>
+      </c>
+      <c r="B59" s="7">
+        <v>3</v>
+      </c>
+      <c r="C59" s="7">
+        <v>14</v>
+      </c>
+      <c r="D59" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_3_14</v>
+      </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -5,13 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CDDA3F-565E-4858-BFA2-A4A82F879335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FA85A-21DF-4DFD-9157-9ED3521385AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="40290" yWindow="1470" windowWidth="16770" windowHeight="13260" firstSheet="1" activeTab="2" xr2:uid="{2D37D46F-FF3D-47B1-BBBE-027E6665CAAC}"/>
+    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -19,8 +18,19 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -110,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="151">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2615,6 +2625,42 @@
     <t>지팡이</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>monster_001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 본능적으로 몸을 틀면서
+땅에 떨어진 무기를 주웠다.
+괴물과 싸움을 시작했다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴물은 쓰러졌고 나는 한동안 그 자리에 서서
+괴물의 시체를 바라보았다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>위습은 조용히 빛을 뿜어냈고
+나는 말했다.
+"….지금까지는 그저 흘러갔지만,
+이젠 내가 움직여야겠네.."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금까지의 삶은 버티는 것이었다.
+하지만 이제는 다르다.
+무언가를 향해 걸어가야 한다는 걸, 그는 알았다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>처음으로, 그가 앞으로 나아갔다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2801,7 +2847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2863,6 +2909,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -33774,7 +33823,7 @@
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
     </row>
-    <row r="53" spans="1:26" ht="16.5">
+    <row r="53" spans="1:26" ht="49.5">
       <c r="A53" s="7">
         <v>1</v>
       </c>
@@ -33788,8 +33837,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_8</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="E53" s="22" t="s">
+        <v>146</v>
+      </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -33825,8 +33875,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_9</v>
       </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="E54" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -33848,7 +33902,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" spans="1:26" ht="16.5">
+    <row r="55" spans="1:26" ht="33">
       <c r="A55" s="7">
         <v>1</v>
       </c>
@@ -33862,7 +33916,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_10</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="16" t="s">
+        <v>147</v>
+      </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -33885,7 +33941,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" spans="1:26" ht="16.5">
+    <row r="56" spans="1:26" ht="66">
       <c r="A56" s="7">
         <v>1</v>
       </c>
@@ -33899,7 +33955,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_11</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="16" t="s">
+        <v>148</v>
+      </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -33922,7 +33980,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="16.5">
+    <row r="57" spans="1:26" ht="49.5">
       <c r="A57" s="7">
         <v>1</v>
       </c>
@@ -33936,7 +33994,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_12</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="16" t="s">
+        <v>149</v>
+      </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -33973,7 +34033,9 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_13</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -34001,17 +34063,15 @@
         <v>1</v>
       </c>
       <c r="B59" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" s="7">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D59" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_14</v>
+        <v>MainScript_1_4_1</v>
       </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
@@ -34034,8 +34094,12 @@
       <c r="Z59" s="5"/>
     </row>
     <row r="60" spans="1:26" ht="16.5">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="7">
+        <v>1</v>
+      </c>
+      <c r="B60" s="7">
+        <v>4</v>
+      </c>
       <c r="C60" s="7"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FA85A-21DF-4DFD-9157-9ED3521385AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B94886-643D-43D1-A1FA-C3370A3C2000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29970" yWindow="1170" windowWidth="17310" windowHeight="11580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FA85A-21DF-4DFD-9157-9ED3521385AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,12 +38,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -71,12 +70,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>jwl55</author>
   </authors>
   <commentList>
-    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{2E7B0A27-7510-4B72-B75A-D33C73DC1308}">
+    <comment ref="E33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{4C8CCA33-BC42-4747-98EB-82D5A3DC7378}">
+    <comment ref="E41" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2665,7 +2664,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="15">
     <font>
       <sz val="11"/>
@@ -3127,7 +3126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3211,8 +3210,8 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
-        <v>MainScene_1_1_1</v>
+        <f>CONCATENATE(E12,A2,"_",B2,"_",C2)</f>
+        <v>1_1_1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
@@ -3250,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScene_",A3,"_",B3,"_",C3)</f>
         <v>MainScene_1_1_2</v>
       </c>
       <c r="E3" s="3"/>
@@ -31668,7 +31667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1009"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
@@ -60681,7 +60680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -61737,7 +61736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995"/>
+    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="151">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2501,9 +2501,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>MainScene_1_2_8</t>
-  </si>
-  <si>
     <t>나는 천천히 걸음을 옮겼고
 푸른 위습은 그 옆을 따라왔다.
 두 존재는 그렇게, 죽음이 남긴 마을을 등지고 나아가고 있었다.</t>
@@ -2587,9 +2584,6 @@
     <t>MainScript_1_2_19</t>
   </si>
   <si>
-    <t>MainScene_1_2_16</t>
-  </si>
-  <si>
     <t>MainScene_1_2_18</t>
   </si>
   <si>
@@ -2658,6 +2652,14 @@
   </si>
   <si>
     <t>처음으로, 그가 앞으로 나아갔다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3210,12 +3212,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f>CONCATENATE(E12,A2,"_",B2,"_",C2)</f>
-        <v>1_1_1</v>
+        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -3249,7 +3251,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="str">
-        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScene_",A3,"_",B3,"_",C3)</f>
+        <f t="shared" si="0"/>
         <v>MainScene_1_1_2</v>
       </c>
       <c r="E3" s="3"/>
@@ -4066,7 +4068,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -4105,7 +4107,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -4144,7 +4146,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -4384,15 +4386,11 @@
       <c r="H32" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>110</v>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>129</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>135</v>
-      </c>
+      <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -4620,7 +4618,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -4659,7 +4657,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -4697,10 +4695,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4739,7 +4737,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
@@ -4778,7 +4776,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -4817,7 +4815,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -4856,7 +4854,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
@@ -4895,7 +4893,7 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
@@ -31750,8 +31748,12 @@
         <v>65</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="H2" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -31831,9 +31833,7 @@
       <c r="F4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -31869,7 +31869,7 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -32281,7 +32281,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>65</v>
@@ -32367,9 +32367,7 @@
       <c r="F17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -32404,7 +32402,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>65</v>
@@ -32819,9 +32817,7 @@
       <c r="F28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -32857,7 +32853,7 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>65</v>
@@ -32903,9 +32899,7 @@
       <c r="F30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -32941,7 +32935,7 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>65</v>
@@ -32987,9 +32981,7 @@
       <c r="F32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -33066,7 +33058,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>65</v>
@@ -33107,14 +33099,12 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -33150,7 +33140,7 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>65</v>
@@ -33191,14 +33181,12 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -33234,7 +33222,7 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>65</v>
@@ -33280,9 +33268,7 @@
       <c r="F39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
@@ -33364,9 +33350,7 @@
       <c r="F41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -33442,7 +33426,7 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>65</v>
@@ -33523,7 +33507,7 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>40</v>
@@ -33564,7 +33548,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -33603,7 +33587,7 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -33642,7 +33626,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -33681,7 +33665,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -33720,7 +33704,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -33759,7 +33743,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -33798,7 +33782,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -33837,7 +33821,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -33875,10 +33859,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -33916,7 +33900,7 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -33955,7 +33939,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -33994,7 +33978,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -34033,7 +34017,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995" activeTab="1"/>
+    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="151">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -32243,9 +32243,7 @@
       <c r="F14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -33512,7 +33510,9 @@
       <c r="F45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G45" s="5"/>
+      <c r="G45" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -33550,7 +33550,9 @@
       <c r="E46" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -33589,7 +33591,9 @@
       <c r="E47" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -33628,7 +33632,9 @@
       <c r="E48" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -33667,7 +33673,9 @@
       <c r="E49" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -33706,7 +33714,9 @@
       <c r="E50" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -33745,7 +33755,9 @@
       <c r="E51" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -33784,7 +33796,9 @@
       <c r="E52" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -33822,6 +33836,9 @@
       </c>
       <c r="E53" s="22" t="s">
         <v>144</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -3212,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D19" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D26" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
@@ -3910,7 +3910,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="str">
-        <f t="shared" ref="D20:D35" si="1">CONCATENATE("MainScene_",A20,"_",B20,"_",C20)</f>
+        <f t="shared" si="0"/>
         <v>MainScene_1_1_19</v>
       </c>
       <c r="E20" s="3"/>
@@ -3949,7 +3949,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>MainScene_1_1_20</v>
       </c>
       <c r="E21" s="3"/>
@@ -3988,7 +3988,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>MainScene_1_1_21</v>
       </c>
       <c r="E22" s="3"/>
@@ -4027,7 +4027,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
@@ -4057,14 +4057,14 @@
         <v>1</v>
       </c>
       <c r="B24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="4">
         <v>23</v>
       </c>
       <c r="D24" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_23</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_23</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
@@ -4096,14 +4096,14 @@
         <v>1</v>
       </c>
       <c r="B25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="4">
         <v>24</v>
       </c>
       <c r="D25" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_24</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_24</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
@@ -4135,14 +4135,14 @@
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="4">
         <v>25</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_25</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_25</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
@@ -4180,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D27:D35" si="1">CONCATENATE("MainScene_",A27,"_",B27,"_",C27)</f>
         <v>MainScene_1_2_1</v>
       </c>
       <c r="E27" s="3"/>
@@ -32690,7 +32690,9 @@
       <c r="F25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="5"/>
+      <c r="G25" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
@@ -32730,9 +32732,6 @@
       </c>
       <c r="F26" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E018F27-95B1-4CB7-879E-D02FB6F8DC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8670" yWindow="1710" windowWidth="20130" windowHeight="13995"/>
+    <workbookView xWindow="10560" yWindow="1770" windowWidth="16770" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -17,19 +18,8 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -38,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -70,12 +60,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>jwl55</author>
   </authors>
   <commentList>
-    <comment ref="E33" authorId="0" shapeId="0">
+    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -90,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E41" authorId="0" shapeId="0">
+    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -119,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="195">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2011,11 +2001,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">벽돌을 옆으로 치운다.
-</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">"생존자다…!"
 아직 누군가 살아 있었다.
 나는 조심스레 다가갔고 
@@ -2460,14 +2445,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">나는 소년이랑 눈이 마주쳤고 
-나는 손을 소년에게 뻗었다.
-하지만 아이는 눈을 크게 뜨고 움찔거렸다.
-본능적으로 나를 두려워하는 눈빛이였다…
-</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">"어차피 죽을 목숨이였어…"
 </t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -2587,11 +2564,6 @@
     <t>MainScene_1_2_18</t>
   </si>
   <si>
-    <t>갑자기 나뭇잎 사이로 괴물이 튀어나왔다
-더 이상 인간이라고 부르기 어려운 형체였다..</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>나는 본능적으로 뒤로 물러섰다.
 "…젠장…"</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -2608,10 +2580,6 @@
   </si>
   <si>
     <t>활</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>단검</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -2662,11 +2630,190 @@
     <t>null</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">나는 소년이랑 눈이 마주쳤고 
+나는 손을 소년에게 뻗었다.
+하지만 아이는 눈을 크게 뜨고 움찔거렸다.
+본능적으로 나를 두려워하는 눈빛이였다…
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽돌을 옆으로 치운다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 나뭇잎 사이로 괴물이 튀어나왔다
+더 이상 인간이라고 부르기 어려운 형체였다..</t>
+  </si>
+  <si>
+    <t>C1E3_monster</t>
+  </si>
+  <si>
+    <t>C1E3_monster_died</t>
+  </si>
+  <si>
+    <t>C1E4_go_out</t>
+  </si>
+  <si>
+    <t>나는 위습에게 말을 걸었다.
+"이젠 말 좀 해줄레?"
+위습은 천천히 말을 해왔다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"네가 머문 곳은 언제나 무너졌다..
+그건 우연이 아니었어."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 표정이 굳어졌다.
+"그러니까… 그 모든게 나 때문이라고 말하고 싶은거야?"</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"아니 너는 단지, 감추어진 진실의 중심에 있었을 뿐이야."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"무슨 진실?"</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"이 세계는 오래전부터 틀어져 있었어.
+누군가는 그 틀을 지키기 위해.
+누군가는 그 틀을 부수기 위해 움직여왔지."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 위습을 노려보았다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"그래서 난 뭐지? 그 틀을 부수는 도구라도 된다는 거냐?"</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"…..그건 너 자신이 선택해야 해."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>위습은 천천히 앞으로 떠올랐고 바람은 고요했다.
+"하지만 기억해. 무너진 자리에는 반드시 무언가 숨겨져있어.
+그건, 너만이 찾을 수 있는 것들이야 
+그리고 그 조각들은…
+한 방향으로 향하고 있어."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 한참을 멈춰 서서 생각했다.
+내가 걸어온 모든 폐허, 그 속에서 반복되어온 '끝'
+이번에도… 결국 혼자 남았다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>"…이젠 더 이상, 우연이라고는 생각 안 해."</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 마지막으로 뒤를 돌아보았고
+그리고 아주 천천히, 그리고 확실하게 걸음을 옮겼고
+위습은 그 앞길을 비춰주듯이 내 앞을 비춰줬다.
+소리 없이 묵묵히</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1E4_travel</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_1</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_2</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_3</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_4</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_5</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_6</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_7</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_8</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_9</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_11</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_12</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_13</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_14</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_1</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_2</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_3</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_4</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_5</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_6</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_7</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_8</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_9</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_10</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_11</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_12</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_13</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_14</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_15</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="15">
     <font>
       <sz val="11"/>
@@ -2848,7 +2995,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2913,6 +3060,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3128,7 +3281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3217,7 +3370,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -4031,7 +4184,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -4068,7 +4221,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -4107,7 +4260,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -4146,7 +4299,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -4341,7 +4494,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -4380,15 +4533,15 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4423,7 +4576,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -4535,12 +4688,12 @@
         <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" ref="D36:D45" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <f t="shared" ref="D36:D74" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -4579,7 +4732,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -4618,7 +4771,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -4657,7 +4810,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -4695,10 +4848,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4737,7 +4890,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
@@ -4776,7 +4929,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -4815,7 +4968,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -4854,7 +5007,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
@@ -4893,7 +5046,7 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
@@ -4917,12 +5070,23 @@
       <c r="Z45" s="3"/>
     </row>
     <row r="46" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="3"/>
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="7">
+        <v>3</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_1</v>
+      </c>
       <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -4945,12 +5109,23 @@
       <c r="Z46" s="3"/>
     </row>
     <row r="47" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="3"/>
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="7">
+        <v>3</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_2</v>
+      </c>
       <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>168</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -4973,12 +5148,23 @@
       <c r="Z47" s="3"/>
     </row>
     <row r="48" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="3"/>
+      <c r="A48" s="7">
+        <v>1</v>
+      </c>
+      <c r="B48" s="7">
+        <v>3</v>
+      </c>
+      <c r="C48" s="7">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_3</v>
+      </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+      <c r="F48" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -5001,12 +5187,23 @@
       <c r="Z48" s="3"/>
     </row>
     <row r="49" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="3"/>
+      <c r="A49" s="7">
+        <v>1</v>
+      </c>
+      <c r="B49" s="7">
+        <v>3</v>
+      </c>
+      <c r="C49" s="7">
+        <v>4</v>
+      </c>
+      <c r="D49" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_4</v>
+      </c>
       <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -5029,12 +5226,23 @@
       <c r="Z49" s="3"/>
     </row>
     <row r="50" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="3"/>
+      <c r="A50" s="7">
+        <v>1</v>
+      </c>
+      <c r="B50" s="7">
+        <v>3</v>
+      </c>
+      <c r="C50" s="7">
+        <v>5</v>
+      </c>
+      <c r="D50" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_5</v>
+      </c>
       <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -5057,12 +5265,23 @@
       <c r="Z50" s="3"/>
     </row>
     <row r="51" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="3"/>
+      <c r="A51" s="7">
+        <v>1</v>
+      </c>
+      <c r="B51" s="7">
+        <v>3</v>
+      </c>
+      <c r="C51" s="7">
+        <v>6</v>
+      </c>
+      <c r="D51" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_6</v>
+      </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -5085,12 +5304,23 @@
       <c r="Z51" s="3"/>
     </row>
     <row r="52" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="3"/>
+      <c r="A52" s="7">
+        <v>1</v>
+      </c>
+      <c r="B52" s="7">
+        <v>3</v>
+      </c>
+      <c r="C52" s="7">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_7</v>
+      </c>
       <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -5113,12 +5343,23 @@
       <c r="Z52" s="3"/>
     </row>
     <row r="53" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="3"/>
+      <c r="A53" s="7">
+        <v>1</v>
+      </c>
+      <c r="B53" s="7">
+        <v>3</v>
+      </c>
+      <c r="C53" s="7">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_8</v>
+      </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -5141,12 +5382,23 @@
       <c r="Z53" s="3"/>
     </row>
     <row r="54" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="3"/>
+      <c r="A54" s="7">
+        <v>1</v>
+      </c>
+      <c r="B54" s="7">
+        <v>3</v>
+      </c>
+      <c r="C54" s="7">
+        <v>9</v>
+      </c>
+      <c r="D54" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_9</v>
+      </c>
       <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -5169,10 +5421,19 @@
       <c r="Z54" s="3"/>
     </row>
     <row r="55" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="3"/>
+      <c r="A55" s="7">
+        <v>1</v>
+      </c>
+      <c r="B55" s="7">
+        <v>3</v>
+      </c>
+      <c r="C55" s="7">
+        <v>10</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_10</v>
+      </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -5197,12 +5458,23 @@
       <c r="Z55" s="3"/>
     </row>
     <row r="56" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="3"/>
+      <c r="A56" s="7">
+        <v>1</v>
+      </c>
+      <c r="B56" s="7">
+        <v>3</v>
+      </c>
+      <c r="C56" s="7">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_11</v>
+      </c>
       <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -5225,12 +5497,23 @@
       <c r="Z56" s="3"/>
     </row>
     <row r="57" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="3"/>
+      <c r="A57" s="7">
+        <v>1</v>
+      </c>
+      <c r="B57" s="7">
+        <v>3</v>
+      </c>
+      <c r="C57" s="7">
+        <v>12</v>
+      </c>
+      <c r="D57" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_12</v>
+      </c>
       <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -5253,12 +5536,23 @@
       <c r="Z57" s="3"/>
     </row>
     <row r="58" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="3"/>
+      <c r="A58" s="7">
+        <v>1</v>
+      </c>
+      <c r="B58" s="7">
+        <v>3</v>
+      </c>
+      <c r="C58" s="7">
+        <v>13</v>
+      </c>
+      <c r="D58" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_13</v>
+      </c>
       <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -5281,12 +5575,23 @@
       <c r="Z58" s="3"/>
     </row>
     <row r="59" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="3"/>
+      <c r="A59" s="7">
+        <v>1</v>
+      </c>
+      <c r="B59" s="7">
+        <v>3</v>
+      </c>
+      <c r="C59" s="7">
+        <v>14</v>
+      </c>
+      <c r="D59" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_3_14</v>
+      </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -5309,12 +5614,23 @@
       <c r="Z59" s="3"/>
     </row>
     <row r="60" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="3"/>
+      <c r="A60" s="7">
+        <v>1</v>
+      </c>
+      <c r="B60" s="7">
+        <v>4</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_1</v>
+      </c>
       <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -5337,12 +5653,23 @@
       <c r="Z60" s="3"/>
     </row>
     <row r="61" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="3"/>
+      <c r="A61" s="7">
+        <v>1</v>
+      </c>
+      <c r="B61" s="7">
+        <v>4</v>
+      </c>
+      <c r="C61" s="7">
+        <v>2</v>
+      </c>
+      <c r="D61" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_2</v>
+      </c>
       <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -5365,12 +5692,23 @@
       <c r="Z61" s="3"/>
     </row>
     <row r="62" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="3"/>
+      <c r="A62" s="7">
+        <v>1</v>
+      </c>
+      <c r="B62" s="7">
+        <v>4</v>
+      </c>
+      <c r="C62" s="7">
+        <v>3</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_3</v>
+      </c>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -5393,12 +5731,23 @@
       <c r="Z62" s="3"/>
     </row>
     <row r="63" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="3"/>
+      <c r="A63" s="7">
+        <v>1</v>
+      </c>
+      <c r="B63" s="7">
+        <v>4</v>
+      </c>
+      <c r="C63" s="7">
+        <v>4</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_4</v>
+      </c>
       <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -5421,12 +5770,23 @@
       <c r="Z63" s="3"/>
     </row>
     <row r="64" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="3"/>
+      <c r="A64" s="7">
+        <v>1</v>
+      </c>
+      <c r="B64" s="7">
+        <v>4</v>
+      </c>
+      <c r="C64" s="7">
+        <v>5</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_5</v>
+      </c>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -5449,12 +5809,23 @@
       <c r="Z64" s="3"/>
     </row>
     <row r="65" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="3"/>
+      <c r="A65" s="7">
+        <v>1</v>
+      </c>
+      <c r="B65" s="7">
+        <v>4</v>
+      </c>
+      <c r="C65" s="7">
+        <v>6</v>
+      </c>
+      <c r="D65" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_6</v>
+      </c>
       <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -5477,12 +5848,23 @@
       <c r="Z65" s="3"/>
     </row>
     <row r="66" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="3"/>
+      <c r="A66" s="7">
+        <v>1</v>
+      </c>
+      <c r="B66" s="7">
+        <v>4</v>
+      </c>
+      <c r="C66" s="7">
+        <v>7</v>
+      </c>
+      <c r="D66" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_7</v>
+      </c>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -5505,12 +5887,23 @@
       <c r="Z66" s="3"/>
     </row>
     <row r="67" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="3"/>
+      <c r="A67" s="7">
+        <v>1</v>
+      </c>
+      <c r="B67" s="7">
+        <v>4</v>
+      </c>
+      <c r="C67" s="7">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_8</v>
+      </c>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
@@ -5533,12 +5926,23 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="3"/>
+      <c r="A68" s="7">
+        <v>1</v>
+      </c>
+      <c r="B68" s="7">
+        <v>4</v>
+      </c>
+      <c r="C68" s="7">
+        <v>9</v>
+      </c>
+      <c r="D68" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_9</v>
+      </c>
       <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -5561,12 +5965,23 @@
       <c r="Z68" s="3"/>
     </row>
     <row r="69" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="3"/>
+      <c r="A69" s="7">
+        <v>1</v>
+      </c>
+      <c r="B69" s="7">
+        <v>4</v>
+      </c>
+      <c r="C69" s="7">
+        <v>10</v>
+      </c>
+      <c r="D69" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_10</v>
+      </c>
       <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -5589,12 +6004,23 @@
       <c r="Z69" s="3"/>
     </row>
     <row r="70" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="3"/>
+      <c r="A70" s="7">
+        <v>1</v>
+      </c>
+      <c r="B70" s="7">
+        <v>4</v>
+      </c>
+      <c r="C70" s="7">
+        <v>11</v>
+      </c>
+      <c r="D70" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_11</v>
+      </c>
       <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -5617,12 +6043,23 @@
       <c r="Z70" s="3"/>
     </row>
     <row r="71" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="3"/>
+      <c r="A71" s="7">
+        <v>1</v>
+      </c>
+      <c r="B71" s="7">
+        <v>4</v>
+      </c>
+      <c r="C71" s="7">
+        <v>12</v>
+      </c>
+      <c r="D71" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_12</v>
+      </c>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -5645,12 +6082,23 @@
       <c r="Z71" s="3"/>
     </row>
     <row r="72" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="3"/>
+      <c r="A72" s="7">
+        <v>1</v>
+      </c>
+      <c r="B72" s="7">
+        <v>4</v>
+      </c>
+      <c r="C72" s="7">
+        <v>13</v>
+      </c>
+      <c r="D72" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_13</v>
+      </c>
       <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -5673,12 +6121,23 @@
       <c r="Z72" s="3"/>
     </row>
     <row r="73" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="3"/>
+      <c r="A73" s="7">
+        <v>1</v>
+      </c>
+      <c r="B73" s="7">
+        <v>4</v>
+      </c>
+      <c r="C73" s="7">
+        <v>14</v>
+      </c>
+      <c r="D73" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_14</v>
+      </c>
       <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -5701,12 +6160,23 @@
       <c r="Z73" s="3"/>
     </row>
     <row r="74" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="3"/>
+      <c r="A74" s="7">
+        <v>1</v>
+      </c>
+      <c r="B74" s="7">
+        <v>4</v>
+      </c>
+      <c r="C74" s="7">
+        <v>15</v>
+      </c>
+      <c r="D74" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_4_15</v>
+      </c>
       <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
@@ -31665,8 +32135,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1009"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z1011"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -31675,7 +32145,7 @@
     <col min="4" max="4" width="32.28515625" customWidth="1"/>
     <col min="5" max="5" width="65.5703125" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="59.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="26" width="8.7109375" customWidth="1"/>
@@ -31738,7 +32208,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D59" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D65" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
@@ -31749,10 +32219,10 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -31833,7 +32303,9 @@
       <c r="F4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -31869,7 +32341,7 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -32243,7 +32715,9 @@
       <c r="F14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -32279,7 +32753,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>65</v>
@@ -32320,7 +32794,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>40</v>
@@ -32360,12 +32834,14 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -32400,7 +32876,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>65</v>
@@ -32440,7 +32916,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>40</v>
@@ -32481,7 +32957,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -32522,7 +32998,7 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>40</v>
@@ -32562,7 +33038,7 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>40</v>
@@ -32603,7 +33079,7 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>40</v>
@@ -32644,7 +33120,7 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -32685,13 +33161,13 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>109</v>
+      <c r="G25" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -32728,10 +33204,10 @@
         <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -32768,7 +33244,7 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>40</v>
@@ -32809,7 +33285,7 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
@@ -32850,7 +33326,7 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>65</v>
@@ -32891,12 +33367,14 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -32932,7 +33410,7 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>65</v>
@@ -32958,7 +33436,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="99">
+    <row r="32" spans="1:26" ht="82.5">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -32973,7 +33451,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>40</v>
@@ -32999,7 +33477,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="33">
+    <row r="33" spans="1:26" ht="16.5">
       <c r="A33" s="7">
         <v>1</v>
       </c>
@@ -33014,12 +33492,14 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G33" s="5"/>
+      <c r="G33" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -33055,7 +33535,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>65</v>
@@ -33096,12 +33576,14 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="5"/>
+      <c r="G35" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -33137,7 +33619,7 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>65</v>
@@ -33178,12 +33660,14 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G37" s="5"/>
+      <c r="G37" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -33219,7 +33703,7 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>65</v>
@@ -33260,7 +33744,7 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>40</v>
@@ -33301,7 +33785,7 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>40</v>
@@ -33342,12 +33826,14 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G41" s="5"/>
+      <c r="G41" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -33383,10 +33869,13 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>78</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -33423,7 +33912,7 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>65</v>
@@ -33463,7 +33952,7 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>40</v>
@@ -33504,7 +33993,7 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>40</v>
@@ -33532,7 +34021,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" ht="33">
+    <row r="46" spans="1:26" ht="16.5">
       <c r="A46" s="7">
         <v>1</v>
       </c>
@@ -33547,10 +34036,10 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -33588,7 +34077,7 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>40</v>
@@ -33614,7 +34103,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" spans="1:26" ht="49.5">
+    <row r="48" spans="1:26" ht="33">
       <c r="A48" s="7">
         <v>1</v>
       </c>
@@ -33629,7 +34118,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>40</v>
@@ -33655,7 +34144,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" spans="1:26" ht="16.5">
+    <row r="49" spans="1:26" ht="49.5">
       <c r="A49" s="7">
         <v>1</v>
       </c>
@@ -33669,8 +34158,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_4</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>138</v>
+      <c r="E49" s="16" t="s">
+        <v>134</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>40</v>
@@ -33711,7 +34200,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>40</v>
@@ -33752,7 +34241,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>40</v>
@@ -33793,7 +34282,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>40</v>
@@ -33834,7 +34323,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>40</v>
@@ -33875,10 +34364,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -33901,7 +34390,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" spans="1:26" ht="33">
+    <row r="55" spans="1:26" ht="16.5">
       <c r="A55" s="7">
         <v>1</v>
       </c>
@@ -33911,14 +34400,13 @@
       <c r="C55" s="7">
         <v>10</v>
       </c>
-      <c r="D55" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>MainScript_1_3_10</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="F55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -33940,7 +34428,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" spans="1:26" ht="66">
+    <row r="56" spans="1:26" ht="33">
       <c r="A56" s="7">
         <v>1</v>
       </c>
@@ -33955,9 +34443,11 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="F56" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -33979,7 +34469,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="49.5">
+    <row r="57" spans="1:26" ht="66">
       <c r="A57" s="7">
         <v>1</v>
       </c>
@@ -33994,9 +34484,11 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F57" s="5"/>
+        <v>142</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -34018,7 +34510,7 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58" spans="1:26" ht="16.5">
+    <row r="58" spans="1:26" ht="49.5">
       <c r="A58" s="7">
         <v>1</v>
       </c>
@@ -34032,10 +34524,12 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_3_13</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F58" s="5"/>
+      <c r="E58" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -34062,16 +34556,24 @@
         <v>1</v>
       </c>
       <c r="B59" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D59" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_1</v>
-      </c>
-      <c r="G59" s="5"/>
+        <v>MainScript_1_3_14</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -34099,10 +34601,19 @@
       <c r="B60" s="7">
         <v>4</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="C60" s="7">
+        <v>1</v>
+      </c>
+      <c r="D60" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_1</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -34124,13 +34635,26 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61" spans="1:26" ht="16.5">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+    <row r="61" spans="1:26" ht="45">
+      <c r="A61" s="7">
+        <v>1</v>
+      </c>
+      <c r="B61" s="7">
+        <v>4</v>
+      </c>
+      <c r="C61" s="7">
+        <v>2</v>
+      </c>
+      <c r="D61" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_2</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -34152,13 +34676,26 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" spans="1:26" ht="16.5">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+    <row r="62" spans="1:26" ht="33">
+      <c r="A62" s="7">
+        <v>1</v>
+      </c>
+      <c r="B62" s="7">
+        <v>4</v>
+      </c>
+      <c r="C62" s="7">
+        <v>3</v>
+      </c>
+      <c r="D62" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_3</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -34180,13 +34717,26 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" spans="1:26" ht="16.5">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+    <row r="63" spans="1:26" ht="33">
+      <c r="A63" s="7">
+        <v>1</v>
+      </c>
+      <c r="B63" s="7">
+        <v>4</v>
+      </c>
+      <c r="C63" s="7">
+        <v>4</v>
+      </c>
+      <c r="D63" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_4</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -34209,12 +34759,25 @@
       <c r="Z63" s="5"/>
     </row>
     <row r="64" spans="1:26" ht="16.5">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="A64" s="7">
+        <v>1</v>
+      </c>
+      <c r="B64" s="7">
+        <v>4</v>
+      </c>
+      <c r="C64" s="7">
+        <v>5</v>
+      </c>
+      <c r="D64" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_5</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -34237,13 +34800,28 @@
       <c r="Z64" s="5"/>
     </row>
     <row r="65" spans="1:26" ht="16.5">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="A65" s="7">
+        <v>1</v>
+      </c>
+      <c r="B65" s="7">
+        <v>4</v>
+      </c>
+      <c r="C65" s="7">
+        <v>6</v>
+      </c>
+      <c r="D65" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_6</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -34264,13 +34842,26 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66" spans="1:26" ht="16.5">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
+    <row r="66" spans="1:26" ht="49.5">
+      <c r="A66" s="7">
+        <v>1</v>
+      </c>
+      <c r="B66" s="7">
+        <v>4</v>
+      </c>
+      <c r="C66" s="7">
+        <v>7</v>
+      </c>
+      <c r="D66" s="5" t="str">
+        <f t="shared" ref="D66:D74" si="1">CONCATENATE("MainScript_",A66,"_",B66,"_",C66)</f>
+        <v>MainScript_1_4_7</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
@@ -34293,12 +34884,25 @@
       <c r="Z66" s="5"/>
     </row>
     <row r="67" spans="1:26" ht="16.5">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="7">
+        <v>1</v>
+      </c>
+      <c r="B67" s="7">
+        <v>4</v>
+      </c>
+      <c r="C67" s="7">
+        <v>8</v>
+      </c>
+      <c r="D67" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_8</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
@@ -34321,12 +34925,25 @@
       <c r="Z67" s="5"/>
     </row>
     <row r="68" spans="1:26" ht="16.5">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="A68" s="7">
+        <v>1</v>
+      </c>
+      <c r="B68" s="7">
+        <v>4</v>
+      </c>
+      <c r="C68" s="7">
+        <v>9</v>
+      </c>
+      <c r="D68" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_9</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -34349,12 +34966,25 @@
       <c r="Z68" s="5"/>
     </row>
     <row r="69" spans="1:26" ht="16.5">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="7">
+        <v>1</v>
+      </c>
+      <c r="B69" s="7">
+        <v>4</v>
+      </c>
+      <c r="C69" s="7">
+        <v>10</v>
+      </c>
+      <c r="D69" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_10</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -34376,13 +35006,26 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" spans="1:26" ht="16.5">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
+    <row r="70" spans="1:26" ht="82.5">
+      <c r="A70" s="7">
+        <v>1</v>
+      </c>
+      <c r="B70" s="7">
+        <v>4</v>
+      </c>
+      <c r="C70" s="7">
+        <v>11</v>
+      </c>
+      <c r="D70" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_11</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
@@ -34404,13 +35047,26 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71" spans="1:26" ht="16.5">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+    <row r="71" spans="1:26" ht="66">
+      <c r="A71" s="7">
+        <v>1</v>
+      </c>
+      <c r="B71" s="7">
+        <v>4</v>
+      </c>
+      <c r="C71" s="7">
+        <v>12</v>
+      </c>
+      <c r="D71" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_12</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -34433,13 +35089,28 @@
       <c r="Z71" s="5"/>
     </row>
     <row r="72" spans="1:26" ht="16.5">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="A72" s="7">
+        <v>1</v>
+      </c>
+      <c r="B72" s="7">
+        <v>4</v>
+      </c>
+      <c r="C72" s="7">
+        <v>13</v>
+      </c>
+      <c r="D72" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_13</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -34461,12 +35132,25 @@
       <c r="Z72" s="5"/>
     </row>
     <row r="73" spans="1:26" ht="16.5">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+      <c r="A73" s="7">
+        <v>1</v>
+      </c>
+      <c r="B73" s="7">
+        <v>4</v>
+      </c>
+      <c r="C73" s="7">
+        <v>14</v>
+      </c>
+      <c r="D73" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_14</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -34488,14 +35172,29 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" spans="1:26" ht="16.5">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
+    <row r="74" spans="1:26" ht="66">
+      <c r="A74" s="7">
+        <v>1</v>
+      </c>
+      <c r="B74" s="7">
+        <v>4</v>
+      </c>
+      <c r="C74" s="7">
+        <v>15</v>
+      </c>
+      <c r="D74" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_4_15</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -60668,8 +61367,64 @@
       <c r="Y1008" s="5"/>
       <c r="Z1008" s="5"/>
     </row>
-    <row r="1009" spans="5:5" ht="16.5">
+    <row r="1009" spans="1:26" ht="16.5">
+      <c r="A1009" s="7"/>
+      <c r="B1009" s="7"/>
+      <c r="C1009" s="7"/>
+      <c r="D1009" s="5"/>
       <c r="E1009" s="5"/>
+      <c r="F1009" s="5"/>
+      <c r="G1009" s="5"/>
+      <c r="H1009" s="5"/>
+      <c r="I1009" s="5"/>
+      <c r="J1009" s="5"/>
+      <c r="K1009" s="5"/>
+      <c r="L1009" s="5"/>
+      <c r="M1009" s="5"/>
+      <c r="N1009" s="5"/>
+      <c r="O1009" s="5"/>
+      <c r="P1009" s="5"/>
+      <c r="Q1009" s="5"/>
+      <c r="R1009" s="5"/>
+      <c r="S1009" s="5"/>
+      <c r="T1009" s="5"/>
+      <c r="U1009" s="5"/>
+      <c r="V1009" s="5"/>
+      <c r="W1009" s="5"/>
+      <c r="X1009" s="5"/>
+      <c r="Y1009" s="5"/>
+      <c r="Z1009" s="5"/>
+    </row>
+    <row r="1010" spans="1:26" ht="16.5">
+      <c r="A1010" s="7"/>
+      <c r="B1010" s="7"/>
+      <c r="C1010" s="7"/>
+      <c r="D1010" s="5"/>
+      <c r="E1010" s="5"/>
+      <c r="F1010" s="5"/>
+      <c r="G1010" s="5"/>
+      <c r="H1010" s="5"/>
+      <c r="I1010" s="5"/>
+      <c r="J1010" s="5"/>
+      <c r="K1010" s="5"/>
+      <c r="L1010" s="5"/>
+      <c r="M1010" s="5"/>
+      <c r="N1010" s="5"/>
+      <c r="O1010" s="5"/>
+      <c r="P1010" s="5"/>
+      <c r="Q1010" s="5"/>
+      <c r="R1010" s="5"/>
+      <c r="S1010" s="5"/>
+      <c r="T1010" s="5"/>
+      <c r="U1010" s="5"/>
+      <c r="V1010" s="5"/>
+      <c r="W1010" s="5"/>
+      <c r="X1010" s="5"/>
+      <c r="Y1010" s="5"/>
+      <c r="Z1010" s="5"/>
+    </row>
+    <row r="1011" spans="1:26" ht="16.5">
+      <c r="E1011" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -60680,7 +61435,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -60711,19 +61466,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -61736,7 +62491,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA72C7D-9AE8-49F0-B94B-2284A4C03C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4EA90D-5A19-41F6-ABA7-D58CE978191F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,17 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -194,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="203">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2662,10 +2671,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Battle</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>나는 본능적으로 몸을 틀면서
 땅에 떨어진 무기를 주웠다.
 괴물과 싸움을 시작했다.</t>
@@ -2962,6 +2967,13 @@
   <si>
     <t>Weapon_002</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLE</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Effect_001","Effect_002","Effect_004"]</t>
   </si>
 </sst>
 </file>
@@ -3453,7 +3465,7 @@
     <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.85546875" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.85546875" style="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -3535,7 +3547,9 @@
       <c r="F2" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>202</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -5209,7 +5223,7 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3"/>
@@ -5248,7 +5262,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5287,7 +5301,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5326,26 +5340,26 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J48" s="3" t="s">
+      <c r="K48" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="M48" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -5376,10 +5390,10 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G49" s="19" t="s">
         <v>18</v>
@@ -5419,13 +5433,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -5462,13 +5476,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -5506,7 +5520,7 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="3"/>
@@ -5545,7 +5559,7 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="3"/>
@@ -5584,7 +5598,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -5623,7 +5637,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -5662,7 +5676,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -5701,7 +5715,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -5740,7 +5754,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -5779,7 +5793,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -5818,7 +5832,7 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3"/>
@@ -5857,7 +5871,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -5896,7 +5910,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -5935,7 +5949,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -5974,7 +5988,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -6013,7 +6027,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -6052,7 +6066,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -6091,7 +6105,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6130,7 +6144,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6169,7 +6183,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6208,7 +6222,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6247,7 +6261,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6286,7 +6300,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6325,7 +6339,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -32369,10 +32383,10 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -33553,7 +33567,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>39</v>
@@ -33594,7 +33608,7 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>39</v>
@@ -34128,7 +34142,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>64</v>
@@ -34169,7 +34183,7 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>39</v>
@@ -34415,7 +34429,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>39</v>
@@ -34459,7 +34473,7 @@
         <v>134</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -34497,7 +34511,7 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>64</v>
@@ -34538,7 +34552,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>39</v>
@@ -34579,7 +34593,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>39</v>
@@ -34620,7 +34634,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>39</v>
@@ -34661,7 +34675,7 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>39</v>
@@ -34704,7 +34718,7 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>64</v>
@@ -34745,7 +34759,7 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>39</v>
@@ -34786,7 +34800,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>39</v>
@@ -34827,7 +34841,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>39</v>
@@ -34868,7 +34882,7 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>39</v>
@@ -34909,7 +34923,7 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>39</v>
@@ -34950,7 +34964,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>39</v>
@@ -34991,7 +35005,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>39</v>
@@ -35032,7 +35046,7 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>39</v>
@@ -35073,7 +35087,7 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>39</v>
@@ -35114,7 +35128,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>39</v>
@@ -35155,7 +35169,7 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>39</v>
@@ -35196,7 +35210,7 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>39</v>
@@ -35237,7 +35251,7 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>64</v>
@@ -35278,7 +35292,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>39</v>
@@ -62604,7 +62618,7 @@
         <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>29</v>
@@ -62621,7 +62635,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>32</v>
@@ -62638,7 +62652,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>35</v>
@@ -62649,13 +62663,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -62663,7 +62677,7 @@
     </row>
     <row r="5" spans="1:5" ht="16.5" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>36</v>
@@ -62672,7 +62686,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -62680,7 +62694,7 @@
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>36</v>
@@ -62689,7 +62703,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4EA90D-5A19-41F6-ABA7-D58CE978191F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B789E0F-9147-4818-8C7B-5B829AC98BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="204">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2975,6 +2975,9 @@
   <si>
     <t>["Effect_001","Effect_002","Effect_004"]</t>
   </si>
+  <si>
+    <t>CLAER</t>
+  </si>
 </sst>
 </file>
 
@@ -32465,7 +32468,7 @@
         <v>60</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>39</v>
+        <v>203</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B789E0F-9147-4818-8C7B-5B829AC98BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C1A1FC-BE3B-481A-8A2B-8FDAA431845D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,8 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -74,136 +65,15 @@
     <author>jwl55</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{7FE15EEB-C944-4C6D-8906-C77EBD1DF50C}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7FE15EEB-C944-4C6D-8906-C77EBD1DF50C}">
       <text/>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{004086C3-6F3A-4A37-8D6D-69D1540EB090}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">1: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>아이템</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">획득
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">2: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>소울</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t xml:space="preserve">획득
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">3: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>체력</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> +-</t>
-        </r>
-      </text>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="203">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -289,22 +159,13 @@
     <t>Effect_Description</t>
   </si>
   <si>
-    <t>Effect_Type</t>
-  </si>
-  <si>
     <t>Effect_Value</t>
-  </si>
-  <si>
-    <t>Effect_1</t>
   </si>
   <si>
     <t>Soul +100</t>
   </si>
   <si>
     <t>100</t>
-  </si>
-  <si>
-    <t>Effect_2</t>
   </si>
   <si>
     <t>체력 -10</t>
@@ -2978,12 +2839,20 @@
   <si>
     <t>CLAER</t>
   </si>
+  <si>
+    <t>Effect_ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Index</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3076,23 +2945,8 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3103,6 +2957,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD8D8D8"/>
         <bgColor rgb="FFD8D8D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3166,7 +3026,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3245,6 +3105,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3548,10 +3412,10 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -3667,7 +3531,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="3"/>
@@ -3862,7 +3726,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="3"/>
@@ -3901,7 +3765,7 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="3"/>
@@ -3940,7 +3804,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="3"/>
@@ -3979,7 +3843,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -4018,7 +3882,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="3"/>
@@ -4056,7 +3920,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="3"/>
@@ -4094,7 +3958,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="3"/>
@@ -4132,7 +3996,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="3"/>
@@ -4170,7 +4034,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="3"/>
@@ -4209,7 +4073,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="3"/>
@@ -4248,7 +4112,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="3"/>
@@ -4287,7 +4151,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="3"/>
@@ -4326,7 +4190,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -4364,7 +4228,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -4401,7 +4265,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -4440,7 +4304,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="3"/>
@@ -4479,7 +4343,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -4518,7 +4382,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -4557,7 +4421,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -4596,7 +4460,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -4635,7 +4499,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -4674,15 +4538,15 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -4717,7 +4581,7 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3"/>
@@ -4756,7 +4620,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -4795,7 +4659,7 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -4834,7 +4698,7 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -4873,7 +4737,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -4912,7 +4776,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -4951,7 +4815,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -4989,10 +4853,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -5031,7 +4895,7 @@
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -5070,7 +4934,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -5109,7 +4973,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -5148,7 +5012,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -5187,7 +5051,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -5226,7 +5090,7 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3"/>
@@ -5265,7 +5129,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5304,7 +5168,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5343,26 +5207,26 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -5393,10 +5257,10 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G49" s="19" t="s">
         <v>18</v>
@@ -5436,13 +5300,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -5479,13 +5343,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G51" s="26" t="s">
         <v>191</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>194</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -5523,7 +5387,7 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="3"/>
@@ -5562,7 +5426,7 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="3"/>
@@ -5601,7 +5465,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -5640,7 +5504,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -5679,7 +5543,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -5718,7 +5582,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -5757,7 +5621,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -5796,7 +5660,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -5835,7 +5699,7 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3"/>
@@ -5874,7 +5738,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -5913,7 +5777,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -5952,7 +5816,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -5991,7 +5855,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -6030,7 +5894,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -6069,7 +5933,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -6108,7 +5972,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6147,7 +6011,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6186,7 +6050,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6225,7 +6089,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6264,7 +6128,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6303,7 +6167,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6342,7 +6206,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -32335,16 +32199,16 @@
         <v>21</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -32379,17 +32243,17 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32424,10 +32288,10 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -32465,10 +32329,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -32506,10 +32370,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -32547,10 +32411,10 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -32588,10 +32452,10 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -32629,10 +32493,10 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -32670,10 +32534,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -32711,10 +32575,10 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -32752,10 +32616,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -32793,10 +32657,10 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -32834,10 +32698,10 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -32875,10 +32739,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -32916,10 +32780,10 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -32957,10 +32821,10 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -32997,10 +32861,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -33037,10 +32901,10 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G18" s="5"/>
       <c r="I18" s="5"/>
@@ -33077,10 +32941,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -33118,10 +32982,10 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -33159,10 +33023,10 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -33199,10 +33063,10 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -33240,10 +33104,10 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -33281,10 +33145,10 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -33322,13 +33186,13 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -33365,10 +33229,10 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -33406,10 +33270,10 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -33447,10 +33311,10 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -33488,10 +33352,10 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -33529,10 +33393,10 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -33570,10 +33434,10 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -33611,10 +33475,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -33652,10 +33516,10 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -33693,10 +33557,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -33734,10 +33598,10 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -33775,10 +33639,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -33816,10 +33680,10 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -33857,10 +33721,10 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -33898,10 +33762,10 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -33939,10 +33803,10 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -33980,10 +33844,10 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G41" s="19"/>
       <c r="H41" s="5"/>
@@ -34021,10 +33885,10 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -34061,10 +33925,10 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -34102,13 +33966,13 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -34145,10 +34009,10 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -34186,10 +34050,10 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -34227,10 +34091,10 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -34268,10 +34132,10 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -34309,10 +34173,10 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -34350,10 +34214,10 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -34391,10 +34255,10 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -34432,10 +34296,10 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -34473,10 +34337,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -34514,10 +34378,10 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -34555,10 +34419,10 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -34596,10 +34460,10 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -34637,10 +34501,10 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -34678,13 +34542,13 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -34721,10 +34585,10 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -34762,10 +34626,10 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -34803,10 +34667,10 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -34844,10 +34708,10 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -34885,10 +34749,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -34926,10 +34790,10 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -34967,10 +34831,10 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -35008,10 +34872,10 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -35049,10 +34913,10 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -35090,10 +34954,10 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -35131,10 +34995,10 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -35172,10 +35036,10 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -35213,10 +35077,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -35254,10 +35118,10 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -35295,13 +35159,13 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -61573,19 +61437,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -62599,129 +62463,159 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E1000"/>
+  <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="27" width="8.7109375" customWidth="1"/>
+    <col min="1" max="2" width="14.42578125" style="29"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="28" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A1" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A2" s="29">
+        <v>2</v>
+      </c>
+      <c r="B2" s="29">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <f>CONCATENATE("Effect_",A2,"_",B2)</f>
+        <v>Effect_2_1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A3" s="29">
+        <v>3</v>
+      </c>
+      <c r="B3" s="29">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <f t="shared" ref="C3:C6" si="0">CONCATENATE("Effect_",A3,"_",B3)</f>
+        <v>Effect_3_2</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A4" s="29">
+        <v>1</v>
+      </c>
+      <c r="B4" s="29">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Effect_1_3</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="6">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A5" s="29">
+        <v>1</v>
+      </c>
+      <c r="B5" s="29">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Effect_1_4</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A6" s="29">
+        <v>1</v>
+      </c>
+      <c r="B6" s="29">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Effect_1_5</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="E6" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:5" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.5" customHeight="1">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" customHeight="1">
+      <c r="E8" s="25"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" customHeight="1">
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:6" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:6" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:6" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:6" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:6" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C1A1FC-BE3B-481A-8A2B-8FDAA431845D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FDAF4C-DBE6-49BB-98FD-A4B3EC82F17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,19 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -2834,9 +2845,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>["Effect_001","Effect_002","Effect_004"]</t>
-  </si>
-  <si>
     <t>CLAER</t>
   </si>
   <si>
@@ -2845,6 +2853,10 @@
   </si>
   <si>
     <t>Effect_Index</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_001|Effect_002|Effect_004|</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3415,7 +3427,7 @@
         <v>106</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -32332,7 +32344,7 @@
         <v>57</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -62476,10 +62488,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1">
       <c r="A1" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>201</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>202</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>26</v>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FDAF4C-DBE6-49BB-98FD-A4B3EC82F17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E08312-D051-42D8-A2E4-BC5B5C0E0487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-2910" yWindow="1830" windowWidth="31020" windowHeight="11085" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
     <author>jwl55</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7FE15EEB-C944-4C6D-8906-C77EBD1DF50C}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{7FE15EEB-C944-4C6D-8906-C77EBD1DF50C}">
       <text/>
     </comment>
   </commentList>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="214">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -171,21 +171,6 @@
   </si>
   <si>
     <t>Effect_Value</t>
-  </si>
-  <si>
-    <t>Soul +100</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>체력 -10</t>
-  </si>
-  <si>
-    <t>-10</t>
-  </si>
-  <si>
-    <t>아이템 획득</t>
   </si>
   <si>
     <t>displayType</t>
@@ -2764,17 +2749,50 @@
     <t>MainScene_1_3_8</t>
   </si>
   <si>
-    <t>Weapon_003</t>
-  </si>
-  <si>
     <t>Effect_4</t>
   </si>
   <si>
     <t>Effect_5</t>
   </si>
   <si>
+    <t>EffectItem_Code</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soul</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLE</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLAER</t>
+  </si>
+  <si>
+    <t>Effect_001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_002</t>
+  </si>
+  <si>
+    <t>Effect_003</t>
+  </si>
+  <si>
     <r>
-      <t>검</t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
     </r>
     <r>
       <rPr>
@@ -2790,74 +2808,73 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
         <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>아이템</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>획득</t>
+      <t>설정</t>
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>EffectItem_Code</t>
+    <t>소울 추가/감소</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Soul</t>
+    <t>아이템 추가/제거</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>HP</t>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_003","Code":"Weapon_005","Value":1}]</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_004","Code":"Weapon_005","Value":1}]</t>
   </si>
   <si>
-    <t>Weapon_002</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_005","Code":"Weapon_005","Value":1}]</t>
   </si>
   <si>
-    <t>BATTLE</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_006","Code":"Weapon_005","Value":1}]</t>
   </si>
   <si>
-    <t>CLAER</t>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_007","Code":"Weapon_005","Value":1}]</t>
   </si>
   <si>
-    <t>Effect_ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_008","Code":"Weapon_005","Value":1}]</t>
   </si>
   <si>
-    <t>Effect_Index</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_009","Code":"Weapon_005","Value":1}]</t>
   </si>
   <si>
-    <t>Effect_001|Effect_002|Effect_004|</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0010","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0011","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0012","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0013","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0014","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0015","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0016","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0017","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0018","Code":"Weapon_005","Value":1}]</t>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0019","Code":"Weapon_005","Value":1}]</t>
   </si>
 </sst>
 </file>
@@ -2958,7 +2975,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2969,12 +2986,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD8D8D8"/>
         <bgColor rgb="FFD8D8D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3117,10 +3128,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3408,7 +3417,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" ht="16.5" customHeight="1">
+    <row r="2" spans="1:26" ht="16.5">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3424,10 +3433,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -3506,7 +3512,9 @@
       <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="16" t="s">
+        <v>197</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="3"/>
       <c r="J4" s="5"/>
@@ -3543,7 +3551,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="3"/>
@@ -3738,7 +3746,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="3"/>
@@ -3777,7 +3785,7 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="3"/>
@@ -3816,7 +3824,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="3"/>
@@ -3855,7 +3863,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3894,7 +3902,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="3"/>
@@ -3932,7 +3940,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="3"/>
@@ -3970,7 +3978,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="3"/>
@@ -4008,7 +4016,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="3"/>
@@ -4046,7 +4054,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="3"/>
@@ -4085,7 +4093,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="3"/>
@@ -4124,7 +4132,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="3"/>
@@ -4163,7 +4171,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="3"/>
@@ -4202,7 +4210,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -4240,7 +4248,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -4277,7 +4285,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -4316,7 +4324,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="3"/>
@@ -4355,7 +4363,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -4394,7 +4402,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -4433,7 +4441,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -4472,7 +4480,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -4511,7 +4519,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -4550,15 +4558,15 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -4593,7 +4601,7 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3"/>
@@ -4632,7 +4640,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -4671,7 +4679,7 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -4710,7 +4718,7 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -4749,7 +4757,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -4788,7 +4796,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -4827,7 +4835,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -4865,10 +4873,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -4907,7 +4915,7 @@
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -4946,7 +4954,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -4985,7 +4993,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -5024,7 +5032,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -5063,7 +5071,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -5102,7 +5110,7 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3"/>
@@ -5141,7 +5149,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5180,7 +5188,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5219,26 +5227,26 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -5269,10 +5277,10 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G49" s="19" t="s">
         <v>18</v>
@@ -5312,13 +5320,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -5355,13 +5363,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -5399,7 +5407,7 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="3"/>
@@ -5438,7 +5446,7 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="3"/>
@@ -5477,7 +5485,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -5555,7 +5563,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -5594,7 +5602,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -5633,7 +5641,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -5672,7 +5680,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -5711,7 +5719,7 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3"/>
@@ -5750,7 +5758,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -5789,7 +5797,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -5828,7 +5836,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -5867,7 +5875,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -5906,7 +5914,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -5945,7 +5953,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -5984,7 +5992,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6023,7 +6031,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6062,7 +6070,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6101,7 +6109,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6140,7 +6148,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6179,7 +6187,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6218,7 +6226,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -32211,16 +32219,16 @@
         <v>21</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -32255,17 +32263,17 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32300,10 +32308,10 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -32341,10 +32349,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -32382,10 +32390,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -32423,10 +32431,10 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -32464,10 +32472,10 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -32505,10 +32513,10 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -32546,10 +32554,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -32587,10 +32595,10 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -32628,10 +32636,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -32669,10 +32677,10 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -32710,10 +32718,10 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -32751,10 +32759,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -32792,10 +32800,10 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -32833,10 +32841,10 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -32873,10 +32881,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -32913,10 +32921,10 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G18" s="5"/>
       <c r="I18" s="5"/>
@@ -32953,10 +32961,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -32994,10 +33002,10 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -33035,10 +33043,10 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -33075,10 +33083,10 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -33116,10 +33124,10 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -33157,10 +33165,10 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -33198,13 +33206,13 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -33241,10 +33249,10 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -33282,10 +33290,10 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -33323,10 +33331,10 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -33364,10 +33372,10 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -33405,10 +33413,10 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -33446,10 +33454,10 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -33487,10 +33495,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -33528,10 +33536,10 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -33569,10 +33577,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -33610,10 +33618,10 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -33651,10 +33659,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -33692,10 +33700,10 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -33733,10 +33741,10 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -33774,10 +33782,10 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -33815,10 +33823,10 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -33856,10 +33864,10 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E41" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="G41" s="19"/>
       <c r="H41" s="5"/>
@@ -33897,10 +33905,10 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -33937,10 +33945,10 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -33978,13 +33986,13 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -34021,10 +34029,10 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -34062,10 +34070,10 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -34103,10 +34111,10 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -34144,10 +34152,10 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -34185,10 +34193,10 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -34226,10 +34234,10 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -34267,10 +34275,10 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -34308,10 +34316,10 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -34349,10 +34357,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -34390,10 +34398,10 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -34431,10 +34439,10 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -34472,10 +34480,10 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -34513,10 +34521,10 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -34554,13 +34562,13 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -34597,10 +34605,10 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -34638,10 +34646,10 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -34679,10 +34687,10 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -34720,10 +34728,10 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -34761,10 +34769,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -34802,10 +34810,10 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -34843,10 +34851,10 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -34884,10 +34892,10 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -34925,10 +34933,10 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -34966,10 +34974,10 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -35007,10 +35015,10 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -35048,10 +35056,10 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -35089,10 +35097,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -35130,10 +35138,10 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -35171,13 +35179,13 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -61449,19 +61457,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -62475,159 +62483,90 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="14.42578125" style="29"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="28" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>201</v>
+    <row r="1" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A2" s="29">
-        <v>2</v>
-      </c>
-      <c r="B2" s="29">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <f>CONCATENATE("Effect_",A2,"_",B2)</f>
-        <v>Effect_2_1</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A3" s="29">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <f t="shared" ref="C3:C6" si="0">CONCATENATE("Effect_",A3,"_",B3)</f>
-        <v>Effect_3_2</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A4" s="29">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Effect_1_3</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="B4" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A5" s="29">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Effect_1_4</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A6" s="29">
-        <v>1</v>
-      </c>
-      <c r="B6" s="29">
-        <v>5</v>
-      </c>
-      <c r="C6" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Effect_1_5</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.5" customHeight="1">
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1">
-      <c r="E8" s="25"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" customHeight="1">
-      <c r="E9" s="25"/>
-    </row>
-    <row r="10" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1"/>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" customHeight="1">
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" customHeight="1">
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:4" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -63615,7 +63554,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E08312-D051-42D8-A2E4-BC5B5C0E0487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45901735-0554-411D-83F4-7D7EC152AF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2910" yWindow="1830" windowWidth="31020" windowHeight="11085" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -84,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="209">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -138,9 +136,6 @@
   </si>
   <si>
     <t>MainScript_1_1_7</t>
-  </si>
-  <si>
-    <t>Effect_3</t>
   </si>
   <si>
     <t>MainScript_1_1_8</t>
@@ -2749,12 +2744,6 @@
     <t>MainScene_1_3_8</t>
   </si>
   <si>
-    <t>Effect_4</t>
-  </si>
-  <si>
-    <t>Effect_5</t>
-  </si>
-  <si>
     <t>EffectItem_Code</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -2829,52 +2818,56 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_004","Code":"Weapon_005","Value":1}]</t>
+    <t>상인을 만났다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_005","Code":"Weapon_005","Value":1}]</t>
+    <t>거래를 한다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_006","Code":"Weapon_005","Value":1}]</t>
+    <t>그냥 간다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_007","Code":"Weapon_005","Value":1}]</t>
+    <t>다음 스토리로 넘어감</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_008","Code":"Weapon_005","Value":1}]</t>
+    <t>MERCHANT</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_009","Code":"Weapon_005","Value":1}]</t>
+    <t>MainScript_1_5_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0010","Code":"Weapon_005","Value":1}]</t>
+    <t>MainScript_1_5_2</t>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0011","Code":"Weapon_005","Value":1}]</t>
+    <t>MainScript_1_5_3</t>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0012","Code":"Weapon_005","Value":1}]</t>
+    <t>MainScript_1_5_4</t>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0013","Code":"Weapon_005","Value":1}]</t>
+    <t>MainScript_1_5_5</t>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0014","Code":"Weapon_005","Value":1}]</t>
+    <t>{"ID":"Effect_003","Code":"Weapon_001","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0015","Code":"Weapon_005","Value":1}]</t>
+    <t>{"ID":"Effect_003","Code":"Weapon_002","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0016","Code":"Weapon_005","Value":1}]</t>
+    <t>{"ID":"Effect_003","Code":"Weapon_004","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0017","Code":"Weapon_005","Value":1}]</t>
-  </si>
-  <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0018","Code":"Weapon_005","Value":1}]</t>
-  </si>
-  <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_0019","Code":"Weapon_005","Value":1}]</t>
+    <t>General</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3433,7 +3426,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -3513,7 +3506,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="3"/>
@@ -3551,7 +3544,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="3"/>
@@ -3707,7 +3700,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="3"/>
@@ -3746,7 +3739,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="3"/>
@@ -3785,7 +3778,7 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="3"/>
@@ -3824,7 +3817,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="3"/>
@@ -3863,7 +3856,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3902,7 +3895,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="3"/>
@@ -3940,7 +3933,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="3"/>
@@ -3978,7 +3971,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="3"/>
@@ -4016,7 +4009,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="3"/>
@@ -4054,7 +4047,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="3"/>
@@ -4093,7 +4086,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="3"/>
@@ -4132,7 +4125,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="3"/>
@@ -4171,7 +4164,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="3"/>
@@ -4210,7 +4203,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -4248,7 +4241,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -4285,7 +4278,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -4324,7 +4317,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="3"/>
@@ -4363,7 +4356,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -4402,7 +4395,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -4441,7 +4434,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -4480,7 +4473,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -4519,7 +4512,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -4558,15 +4551,15 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -4601,7 +4594,7 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3"/>
@@ -4640,7 +4633,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -4679,7 +4672,7 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -4713,12 +4706,12 @@
         <v>10</v>
       </c>
       <c r="D35" s="3" t="str">
-        <f t="shared" ref="D35:D73" si="2">CONCATENATE("MainScene_",A35,"_",B35,"_",C35)</f>
+        <f t="shared" ref="D35:D78" si="2">CONCATENATE("MainScene_",A35,"_",B35,"_",C35)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -4757,7 +4750,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -4796,7 +4789,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -4835,7 +4828,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -4873,10 +4866,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -4915,7 +4908,7 @@
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -4954,7 +4947,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -4993,7 +4986,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -5032,7 +5025,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -5071,7 +5064,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -5110,7 +5103,7 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3"/>
@@ -5149,7 +5142,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5188,7 +5181,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5227,26 +5220,26 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J48" s="3" t="s">
+      <c r="K48" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="M48" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -5277,13 +5270,13 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -5320,13 +5313,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -5363,13 +5356,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -5407,7 +5400,7 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="3"/>
@@ -5446,7 +5439,7 @@
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="3"/>
@@ -5485,7 +5478,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -5524,7 +5517,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -5563,7 +5556,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -5602,7 +5595,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -5641,7 +5634,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -5680,7 +5673,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -5719,7 +5712,7 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3"/>
@@ -5758,7 +5751,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -5797,7 +5790,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -5836,7 +5829,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -5875,7 +5868,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -5914,7 +5907,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -5953,7 +5946,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -5992,7 +5985,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6031,7 +6024,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6070,7 +6063,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6109,7 +6102,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6148,7 +6141,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6187,7 +6180,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6226,7 +6219,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -6250,16 +6243,31 @@
       <c r="Z73" s="3"/>
     </row>
     <row r="74" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="3"/>
+      <c r="A74" s="4">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4">
+        <v>5</v>
+      </c>
+      <c r="C74" s="4">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_1</v>
+      </c>
       <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G74" s="5"/>
-      <c r="H74" s="3"/>
+      <c r="H74" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
@@ -6278,12 +6286,26 @@
       <c r="Z74" s="3"/>
     </row>
     <row r="75" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
+      <c r="A75" s="4">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4">
+        <v>5</v>
+      </c>
+      <c r="C75" s="4">
+        <v>2</v>
+      </c>
+      <c r="D75" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_2</v>
+      </c>
+      <c r="E75" s="3" t="str">
+        <f>D77</f>
+        <v>MainScene_1_5_4</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
@@ -6306,12 +6328,26 @@
       <c r="Z75" s="3"/>
     </row>
     <row r="76" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
+      <c r="A76" s="4">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4">
+        <v>5</v>
+      </c>
+      <c r="C76" s="4">
+        <v>3</v>
+      </c>
+      <c r="D76" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_3</v>
+      </c>
+      <c r="E76" s="3" t="str">
+        <f>D78</f>
+        <v>MainScene_1_5_5</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="G76" s="5"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
@@ -6334,12 +6370,23 @@
       <c r="Z76" s="3"/>
     </row>
     <row r="77" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="3"/>
+      <c r="A77" s="4">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4">
+        <v>5</v>
+      </c>
+      <c r="C77" s="4">
+        <v>4</v>
+      </c>
+      <c r="D77" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_4</v>
+      </c>
       <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
@@ -6362,12 +6409,23 @@
       <c r="Z77" s="3"/>
     </row>
     <row r="78" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="3"/>
+      <c r="A78" s="4">
+        <v>1</v>
+      </c>
+      <c r="B78" s="4">
+        <v>5</v>
+      </c>
+      <c r="C78" s="4">
+        <v>5</v>
+      </c>
+      <c r="D78" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_5</v>
+      </c>
       <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="G78" s="5"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
@@ -32213,22 +32271,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>21</v>
-      </c>
       <c r="F1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>30</v>
-      </c>
       <c r="H1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
@@ -32263,17 +32321,17 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32308,10 +32366,10 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -32349,10 +32407,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -32390,10 +32448,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -32431,10 +32489,10 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -32472,10 +32530,10 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -32513,10 +32571,10 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -32554,10 +32612,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -32595,10 +32653,10 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -32636,10 +32694,10 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -32677,10 +32735,10 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -32718,10 +32776,10 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -32759,10 +32817,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -32800,10 +32858,10 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -32841,10 +32899,10 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -32881,10 +32939,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -32921,10 +32979,10 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="5"/>
       <c r="I18" s="5"/>
@@ -32961,10 +33019,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -33002,10 +33060,10 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -33043,10 +33101,10 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -33083,10 +33141,10 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -33124,10 +33182,10 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -33165,10 +33223,10 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -33206,13 +33264,13 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -33249,10 +33307,10 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -33290,10 +33348,10 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -33331,10 +33389,10 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -33372,10 +33430,10 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -33413,10 +33471,10 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -33454,10 +33512,10 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -33495,10 +33553,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -33536,10 +33594,10 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -33577,10 +33635,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -33618,10 +33676,10 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -33659,10 +33717,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -33700,10 +33758,10 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -33741,10 +33799,10 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -33782,10 +33840,10 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -33823,10 +33881,10 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -33864,10 +33922,10 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G41" s="19"/>
       <c r="H41" s="5"/>
@@ -33905,10 +33963,10 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -33945,10 +34003,10 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -33986,13 +34044,13 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -34029,10 +34087,10 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -34070,10 +34128,10 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -34111,10 +34169,10 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -34152,10 +34210,10 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -34193,10 +34251,10 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -34234,10 +34292,10 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -34275,10 +34333,10 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -34316,10 +34374,10 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -34357,10 +34415,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -34398,10 +34456,10 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -34439,10 +34497,10 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -34480,10 +34538,10 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -34521,10 +34579,10 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -34562,13 +34620,13 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -34605,10 +34663,10 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -34646,10 +34704,10 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -34687,10 +34745,10 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -34728,10 +34786,10 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -34769,10 +34827,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -34810,10 +34868,10 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -34847,14 +34905,14 @@
         <v>7</v>
       </c>
       <c r="D65" s="5" t="str">
-        <f t="shared" ref="D65:D73" si="1">CONCATENATE("MainScript_",A65,"_",B65,"_",C65)</f>
+        <f t="shared" ref="D65:D78" si="1">CONCATENATE("MainScript_",A65,"_",B65,"_",C65)</f>
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -34892,10 +34950,10 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -34933,10 +34991,10 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -34974,10 +35032,10 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -35015,10 +35073,10 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -35056,10 +35114,10 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -35097,10 +35155,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -35138,10 +35196,10 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -35179,13 +35237,13 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -35208,12 +35266,25 @@
       <c r="Z73" s="5"/>
     </row>
     <row r="74" spans="1:26" ht="16.5">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="A74" s="7">
+        <v>1</v>
+      </c>
+      <c r="B74" s="7">
+        <v>5</v>
+      </c>
+      <c r="C74" s="7">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_1</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -35236,12 +35307,25 @@
       <c r="Z74" s="5"/>
     </row>
     <row r="75" spans="1:26" ht="16.5">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="A75" s="7">
+        <v>1</v>
+      </c>
+      <c r="B75" s="7">
+        <v>5</v>
+      </c>
+      <c r="C75" s="7">
+        <v>2</v>
+      </c>
+      <c r="D75" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_2</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -35264,12 +35348,25 @@
       <c r="Z75" s="5"/>
     </row>
     <row r="76" spans="1:26" ht="16.5">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="A76" s="7">
+        <v>1</v>
+      </c>
+      <c r="B76" s="7">
+        <v>5</v>
+      </c>
+      <c r="C76" s="7">
+        <v>3</v>
+      </c>
+      <c r="D76" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_3</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -35292,12 +35389,25 @@
       <c r="Z76" s="5"/>
     </row>
     <row r="77" spans="1:26" ht="16.5">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
+      <c r="A77" s="7">
+        <v>1</v>
+      </c>
+      <c r="B77" s="7">
+        <v>5</v>
+      </c>
+      <c r="C77" s="7">
+        <v>4</v>
+      </c>
+      <c r="D77" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_4</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -35320,13 +35430,28 @@
       <c r="Z77" s="5"/>
     </row>
     <row r="78" spans="1:26" ht="16.5">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="A78" s="7">
+        <v>1</v>
+      </c>
+      <c r="B78" s="7">
+        <v>5</v>
+      </c>
+      <c r="C78" s="7">
+        <v>5</v>
+      </c>
+      <c r="D78" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_5</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -61443,33 +61568,33 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -62495,48 +62620,48 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>193</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>196</v>
       </c>
       <c r="C4" s="6"/>
     </row>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45901735-0554-411D-83F4-7D7EC152AF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CFCE14-71EA-4ABE-9A0F-DE6D5CD54FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
+    <author>김태경</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -56,6 +57,554 @@
 ID#AAABhyQcozI
 jwl55    (2025-04-15 04:47:48)
 현재 챕터를 뜻한다</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{6512A511-CF81-436A-A15B-2C8EC299DB64}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>김태경</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이거</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>비워두면</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>자기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>마음대로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> bool</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>값을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>채워버려서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>임시로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">넣었음
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I50" authorId="1" shapeId="0" xr:uid="{2BB6490E-5AE8-4A30-9445-766D9F60E0A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>김태경</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>여기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>안넣은</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이유가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>선택지에서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>해당</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>코드로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>넘어가는데</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>아이템</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>넣고</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>나서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>바로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>해당</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>씬으로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">보내버림
+</t>
         </r>
       </text>
     </comment>
@@ -82,7 +631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="215">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2409,10 +2958,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Break</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>나는 천천히 걸음을 옮겼고
 푸른 위습은 그 옆을 따라왔다.
 두 존재는 그렇게, 죽음이 남긴 마을을 등지고 나아가고 있었다.</t>
@@ -2854,19 +3399,43 @@
     <t>MainScript_1_5_5</t>
   </si>
   <si>
-    <t>{"ID":"Effect_003","Code":"Weapon_001","Value":1}]</t>
+    <t>General</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{"ID":"Effect_003","Code":"Weapon_002","Value":1}]</t>
+    <t>MainScript_1_1_25</t>
+  </si>
+  <si>
+    <t>MainScript_1_2_20</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_15</t>
+  </si>
+  <si>
+    <t>MainScript_1_4_16</t>
+  </si>
+  <si>
+    <t>MainScript_1_3_5</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{"ID":"Effect_003","Code":"Weapon_004","Value":1}]</t>
+    <t>[{"ID":"Effect_001","Value":100}]</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>General</t>
+    <t>[{"ID":"Effect_003","Code":"Weapon_004","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_003","Code":"Weapon_001","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"ID":"Effect_002","Code":"Weapon_003","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene_1_1_1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2874,7 +3443,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2966,6 +3535,34 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3338,7 +3935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z999"/>
+  <dimension ref="A1:Z1003"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -3421,19 +4018,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D25" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D26" si="0">CONCATENATE("MainScene_",A2,"_",B2,"_",C2)</f>
         <v>MainScene_1_1_1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -3506,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="3"/>
@@ -3702,7 +4305,9 @@
       <c r="F9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -4278,7 +4883,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -4317,10 +4922,12 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G25" s="5"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="5" t="s">
+        <v>205</v>
+      </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -4345,18 +4952,18 @@
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="str">
-        <f t="shared" ref="D26:D34" si="1">CONCATENATE("MainScene_",A26,"_",B26,"_",C26)</f>
-        <v>MainScene_1_2_1</v>
+        <f t="shared" si="0"/>
+        <v>MainScene_1_1_25</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
-        <v>61</v>
+      <c r="F26" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -4387,15 +4994,15 @@
         <v>2</v>
       </c>
       <c r="C27" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScene_1_2_2</v>
+        <f t="shared" ref="D27:D35" si="1">CONCATENATE("MainScene_",A27,"_",B27,"_",C27)</f>
+        <v>MainScene_1_2_1</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -4426,15 +5033,15 @@
         <v>2</v>
       </c>
       <c r="C28" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_3</v>
+        <v>MainScene_1_2_2</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -4465,15 +5072,15 @@
         <v>2</v>
       </c>
       <c r="C29" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_4</v>
+        <v>MainScene_1_2_3</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -4504,15 +5111,15 @@
         <v>2</v>
       </c>
       <c r="C30" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_5</v>
+        <v>MainScene_1_2_4</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -4543,24 +5150,20 @@
         <v>2</v>
       </c>
       <c r="C31" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_6</v>
+        <v>MainScene_1_2_5</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3" t="s">
-        <v>114</v>
-      </c>
+      <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -4586,20 +5189,24 @@
         <v>2</v>
       </c>
       <c r="C32" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_7</v>
+        <v>MainScene_1_2_6</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -4625,15 +5232,15 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_8</v>
+        <v>MainScene_1_2_7</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -4664,15 +5271,15 @@
         <v>2</v>
       </c>
       <c r="C34" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>MainScene_1_2_9</v>
+        <v>MainScene_1_2_8</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -4703,15 +5310,15 @@
         <v>2</v>
       </c>
       <c r="C35" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="3" t="str">
-        <f t="shared" ref="D35:D78" si="2">CONCATENATE("MainScene_",A35,"_",B35,"_",C35)</f>
-        <v>MainScene_1_2_10</v>
+        <f t="shared" si="1"/>
+        <v>MainScene_1_2_9</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -4742,15 +5349,15 @@
         <v>2</v>
       </c>
       <c r="C36" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>MainScene_1_2_11</v>
+        <f t="shared" ref="D36:D82" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -4781,15 +5388,15 @@
         <v>2</v>
       </c>
       <c r="C37" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_12</v>
+        <v>MainScene_1_2_11</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -4820,15 +5427,15 @@
         <v>2</v>
       </c>
       <c r="C38" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_13</v>
+        <v>MainScene_1_2_12</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -4859,17 +5466,15 @@
         <v>2</v>
       </c>
       <c r="C39" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_14</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>MainScene_1_2_13</v>
+      </c>
+      <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -4900,15 +5505,17 @@
         <v>2</v>
       </c>
       <c r="C40" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D40" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_15</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>MainScene_1_2_14</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="F40" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -4939,15 +5546,15 @@
         <v>2</v>
       </c>
       <c r="C41" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_16</v>
+        <v>MainScene_1_2_15</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -4978,15 +5585,15 @@
         <v>2</v>
       </c>
       <c r="C42" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_17</v>
+        <v>MainScene_1_2_16</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -5017,15 +5624,15 @@
         <v>2</v>
       </c>
       <c r="C43" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_18</v>
+        <v>MainScene_1_2_17</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -5056,15 +5663,15 @@
         <v>2</v>
       </c>
       <c r="C44" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D44" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_2_19</v>
+        <v>MainScene_1_2_18</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -5088,25 +5695,27 @@
       <c r="Z44" s="3"/>
     </row>
     <row r="45" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A45" s="7">
+      <c r="A45" s="4">
         <v>1</v>
       </c>
-      <c r="B45" s="7">
-        <v>3</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1</v>
+      <c r="B45" s="4">
+        <v>2</v>
+      </c>
+      <c r="C45" s="4">
+        <v>19</v>
       </c>
       <c r="D45" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_1</v>
+        <v>MainScene_1_2_19</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="G45" s="5"/>
-      <c r="H45" s="3"/>
+      <c r="H45" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -5127,22 +5736,22 @@
       <c r="Z45" s="3"/>
     </row>
     <row r="46" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A46" s="7">
+      <c r="A46" s="4">
         <v>1</v>
       </c>
-      <c r="B46" s="7">
-        <v>3</v>
-      </c>
-      <c r="C46" s="7">
+      <c r="B46" s="4">
         <v>2</v>
+      </c>
+      <c r="C46" s="4">
+        <v>20</v>
       </c>
       <c r="D46" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_2</v>
+        <v>MainScene_1_2_20</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5173,15 +5782,15 @@
         <v>3</v>
       </c>
       <c r="C47" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_3</v>
+        <v>MainScene_1_3_1</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5212,35 +5821,25 @@
         <v>3</v>
       </c>
       <c r="C48" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_4</v>
+        <v>MainScene_1_3_2</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
@@ -5263,20 +5862,18 @@
         <v>3</v>
       </c>
       <c r="C49" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>MainScene_1_3_3</v>
+      </c>
+      <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>205</v>
+        <v>154</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -5306,27 +5903,28 @@
         <v>3</v>
       </c>
       <c r="C50" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_6</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>MainScene_1_3_4</v>
+      </c>
+      <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G50" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -5349,23 +5947,22 @@
         <v>3</v>
       </c>
       <c r="C51" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D51" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_7</v>
+        <v>MainScene_1_3_5</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
@@ -5392,23 +5989,25 @@
         <v>3</v>
       </c>
       <c r="C52" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_8</v>
-      </c>
-      <c r="E52" s="3"/>
+        <v>MainScene_1_3_6</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="F52" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G52" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>213</v>
+      </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
       <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
@@ -5431,23 +6030,26 @@
         <v>3</v>
       </c>
       <c r="C53" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_9</v>
-      </c>
-      <c r="E53" s="3"/>
+        <v>MainScene_1_3_7</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="F53" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G53" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>211</v>
+      </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
@@ -5470,15 +6072,15 @@
         <v>3</v>
       </c>
       <c r="C54" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D54" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_10</v>
+        <v>MainScene_1_3_8</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -5509,15 +6111,15 @@
         <v>3</v>
       </c>
       <c r="C55" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D55" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_11</v>
+        <v>MainScene_1_3_9</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -5548,15 +6150,15 @@
         <v>3</v>
       </c>
       <c r="C56" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D56" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_12</v>
+        <v>MainScene_1_3_10</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -5587,15 +6189,15 @@
         <v>3</v>
       </c>
       <c r="C57" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D57" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_13</v>
+        <v>MainScene_1_3_11</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -5626,15 +6228,15 @@
         <v>3</v>
       </c>
       <c r="C58" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D58" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_3_14</v>
+        <v>MainScene_1_3_12</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -5662,18 +6264,18 @@
         <v>1</v>
       </c>
       <c r="B59" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D59" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_1</v>
+        <v>MainScene_1_3_13</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -5701,21 +6303,23 @@
         <v>1</v>
       </c>
       <c r="B60" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D60" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_2</v>
+        <v>MainScene_1_3_14</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G60" s="5"/>
-      <c r="H60" s="3"/>
+      <c r="H60" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -5740,18 +6344,18 @@
         <v>1</v>
       </c>
       <c r="B61" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D61" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_3</v>
+        <v>MainScene_1_3_15</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -5782,15 +6386,15 @@
         <v>4</v>
       </c>
       <c r="C62" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_4</v>
+        <v>MainScene_1_4_1</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -5821,15 +6425,15 @@
         <v>4</v>
       </c>
       <c r="C63" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D63" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_5</v>
+        <v>MainScene_1_4_2</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -5860,15 +6464,15 @@
         <v>4</v>
       </c>
       <c r="C64" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D64" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_6</v>
+        <v>MainScene_1_4_3</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -5899,15 +6503,15 @@
         <v>4</v>
       </c>
       <c r="C65" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D65" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_7</v>
+        <v>MainScene_1_4_4</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -5938,15 +6542,15 @@
         <v>4</v>
       </c>
       <c r="C66" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D66" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_8</v>
+        <v>MainScene_1_4_5</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -5977,15 +6581,15 @@
         <v>4</v>
       </c>
       <c r="C67" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D67" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_9</v>
+        <v>MainScene_1_4_6</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6016,15 +6620,15 @@
         <v>4</v>
       </c>
       <c r="C68" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D68" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_10</v>
+        <v>MainScene_1_4_7</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6055,15 +6659,15 @@
         <v>4</v>
       </c>
       <c r="C69" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D69" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_11</v>
+        <v>MainScene_1_4_8</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6094,15 +6698,15 @@
         <v>4</v>
       </c>
       <c r="C70" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_12</v>
+        <v>MainScene_1_4_9</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6133,15 +6737,15 @@
         <v>4</v>
       </c>
       <c r="C71" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D71" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_13</v>
+        <v>MainScene_1_4_10</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6172,15 +6776,15 @@
         <v>4</v>
       </c>
       <c r="C72" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D72" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_14</v>
+        <v>MainScene_1_4_11</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6211,15 +6815,15 @@
         <v>4</v>
       </c>
       <c r="C73" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D73" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_4_15</v>
+        <v>MainScene_1_4_12</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -6243,31 +6847,27 @@
       <c r="Z73" s="3"/>
     </row>
     <row r="74" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A74" s="4">
+      <c r="A74" s="7">
         <v>1</v>
       </c>
-      <c r="B74" s="4">
-        <v>5</v>
-      </c>
-      <c r="C74" s="4">
-        <v>1</v>
+      <c r="B74" s="7">
+        <v>4</v>
+      </c>
+      <c r="C74" s="7">
+        <v>13</v>
       </c>
       <c r="D74" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_5_1</v>
+        <v>MainScene_1_4_13</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="G74" s="5"/>
-      <c r="H74" s="3" t="s">
-        <v>201</v>
-      </c>
+      <c r="H74" s="3"/>
       <c r="I74" s="3"/>
-      <c r="J74" s="3" t="s">
-        <v>202</v>
-      </c>
+      <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
@@ -6286,25 +6886,22 @@
       <c r="Z74" s="3"/>
     </row>
     <row r="75" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A75" s="4">
+      <c r="A75" s="7">
         <v>1</v>
       </c>
-      <c r="B75" s="4">
-        <v>5</v>
-      </c>
-      <c r="C75" s="4">
-        <v>2</v>
+      <c r="B75" s="7">
+        <v>4</v>
+      </c>
+      <c r="C75" s="7">
+        <v>14</v>
       </c>
       <c r="D75" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_5_2</v>
-      </c>
-      <c r="E75" s="3" t="str">
-        <f>D77</f>
-        <v>MainScene_1_5_4</v>
-      </c>
+        <v>MainScene_1_4_14</v>
+      </c>
+      <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
@@ -6328,28 +6925,27 @@
       <c r="Z75" s="3"/>
     </row>
     <row r="76" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A76" s="4">
+      <c r="A76" s="7">
         <v>1</v>
       </c>
-      <c r="B76" s="4">
-        <v>5</v>
-      </c>
-      <c r="C76" s="4">
-        <v>3</v>
+      <c r="B76" s="7">
+        <v>4</v>
+      </c>
+      <c r="C76" s="7">
+        <v>15</v>
       </c>
       <c r="D76" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_5_3</v>
-      </c>
-      <c r="E76" s="3" t="str">
-        <f>D78</f>
-        <v>MainScene_1_5_5</v>
-      </c>
+        <v>MainScene_1_4_15</v>
+      </c>
+      <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="G76" s="5"/>
-      <c r="H76" s="3"/>
+      <c r="H76" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
@@ -6370,22 +6966,22 @@
       <c r="Z76" s="3"/>
     </row>
     <row r="77" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A77" s="4">
+      <c r="A77" s="7">
         <v>1</v>
       </c>
-      <c r="B77" s="4">
-        <v>5</v>
-      </c>
-      <c r="C77" s="4">
+      <c r="B77" s="7">
         <v>4</v>
+      </c>
+      <c r="C77" s="7">
+        <v>16</v>
       </c>
       <c r="D77" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_5_4</v>
+        <v>MainScene_1_4_16</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
@@ -6416,20 +7012,24 @@
         <v>5</v>
       </c>
       <c r="C78" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>MainScene_1_5_5</v>
+        <v>MainScene_1_5_1</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G78" s="5"/>
-      <c r="H78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
@@ -6448,12 +7048,26 @@
       <c r="Z78" s="3"/>
     </row>
     <row r="79" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
+      <c r="A79" s="4">
+        <v>1</v>
+      </c>
+      <c r="B79" s="4">
+        <v>5</v>
+      </c>
+      <c r="C79" s="4">
+        <v>2</v>
+      </c>
+      <c r="D79" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_2</v>
+      </c>
+      <c r="E79" s="3" t="str">
+        <f>D81</f>
+        <v>MainScene_1_5_4</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G79" s="5"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -6476,12 +7090,26 @@
       <c r="Z79" s="3"/>
     </row>
     <row r="80" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
+      <c r="A80" s="4">
+        <v>1</v>
+      </c>
+      <c r="B80" s="4">
+        <v>5</v>
+      </c>
+      <c r="C80" s="4">
+        <v>3</v>
+      </c>
+      <c r="D80" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_3</v>
+      </c>
+      <c r="E80" s="3" t="str">
+        <f>D82</f>
+        <v>MainScene_1_5_5</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G80" s="5"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
@@ -6504,12 +7132,23 @@
       <c r="Z80" s="3"/>
     </row>
     <row r="81" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="3"/>
+      <c r="A81" s="4">
+        <v>1</v>
+      </c>
+      <c r="B81" s="4">
+        <v>5</v>
+      </c>
+      <c r="C81" s="4">
+        <v>4</v>
+      </c>
+      <c r="D81" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_4</v>
+      </c>
       <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="G81" s="5"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
@@ -6532,12 +7171,23 @@
       <c r="Z81" s="3"/>
     </row>
     <row r="82" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="3"/>
+      <c r="A82" s="4">
+        <v>1</v>
+      </c>
+      <c r="B82" s="4">
+        <v>5</v>
+      </c>
+      <c r="C82" s="4">
+        <v>5</v>
+      </c>
+      <c r="D82" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_1_5_5</v>
+      </c>
       <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G82" s="5"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
@@ -32235,6 +32885,118 @@
       <c r="Y999" s="3"/>
       <c r="Z999" s="3"/>
     </row>
+    <row r="1000" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1000" s="4"/>
+      <c r="B1000" s="4"/>
+      <c r="C1000" s="4"/>
+      <c r="D1000" s="3"/>
+      <c r="E1000" s="3"/>
+      <c r="F1000" s="3"/>
+      <c r="G1000" s="5"/>
+      <c r="H1000" s="3"/>
+      <c r="I1000" s="3"/>
+      <c r="J1000" s="3"/>
+      <c r="K1000" s="3"/>
+      <c r="L1000" s="3"/>
+      <c r="M1000" s="3"/>
+      <c r="N1000" s="3"/>
+      <c r="O1000" s="3"/>
+      <c r="P1000" s="3"/>
+      <c r="Q1000" s="3"/>
+      <c r="R1000" s="3"/>
+      <c r="S1000" s="3"/>
+      <c r="T1000" s="3"/>
+      <c r="U1000" s="3"/>
+      <c r="V1000" s="3"/>
+      <c r="W1000" s="3"/>
+      <c r="X1000" s="3"/>
+      <c r="Y1000" s="3"/>
+      <c r="Z1000" s="3"/>
+    </row>
+    <row r="1001" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1001" s="4"/>
+      <c r="B1001" s="4"/>
+      <c r="C1001" s="4"/>
+      <c r="D1001" s="3"/>
+      <c r="E1001" s="3"/>
+      <c r="F1001" s="3"/>
+      <c r="G1001" s="5"/>
+      <c r="H1001" s="3"/>
+      <c r="I1001" s="3"/>
+      <c r="J1001" s="3"/>
+      <c r="K1001" s="3"/>
+      <c r="L1001" s="3"/>
+      <c r="M1001" s="3"/>
+      <c r="N1001" s="3"/>
+      <c r="O1001" s="3"/>
+      <c r="P1001" s="3"/>
+      <c r="Q1001" s="3"/>
+      <c r="R1001" s="3"/>
+      <c r="S1001" s="3"/>
+      <c r="T1001" s="3"/>
+      <c r="U1001" s="3"/>
+      <c r="V1001" s="3"/>
+      <c r="W1001" s="3"/>
+      <c r="X1001" s="3"/>
+      <c r="Y1001" s="3"/>
+      <c r="Z1001" s="3"/>
+    </row>
+    <row r="1002" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1002" s="4"/>
+      <c r="B1002" s="4"/>
+      <c r="C1002" s="4"/>
+      <c r="D1002" s="3"/>
+      <c r="E1002" s="3"/>
+      <c r="F1002" s="3"/>
+      <c r="G1002" s="5"/>
+      <c r="H1002" s="3"/>
+      <c r="I1002" s="3"/>
+      <c r="J1002" s="3"/>
+      <c r="K1002" s="3"/>
+      <c r="L1002" s="3"/>
+      <c r="M1002" s="3"/>
+      <c r="N1002" s="3"/>
+      <c r="O1002" s="3"/>
+      <c r="P1002" s="3"/>
+      <c r="Q1002" s="3"/>
+      <c r="R1002" s="3"/>
+      <c r="S1002" s="3"/>
+      <c r="T1002" s="3"/>
+      <c r="U1002" s="3"/>
+      <c r="V1002" s="3"/>
+      <c r="W1002" s="3"/>
+      <c r="X1002" s="3"/>
+      <c r="Y1002" s="3"/>
+      <c r="Z1002" s="3"/>
+    </row>
+    <row r="1003" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1003" s="4"/>
+      <c r="B1003" s="4"/>
+      <c r="C1003" s="4"/>
+      <c r="D1003" s="3"/>
+      <c r="E1003" s="3"/>
+      <c r="F1003" s="3"/>
+      <c r="G1003" s="5"/>
+      <c r="H1003" s="3"/>
+      <c r="I1003" s="3"/>
+      <c r="J1003" s="3"/>
+      <c r="K1003" s="3"/>
+      <c r="L1003" s="3"/>
+      <c r="M1003" s="3"/>
+      <c r="N1003" s="3"/>
+      <c r="O1003" s="3"/>
+      <c r="P1003" s="3"/>
+      <c r="Q1003" s="3"/>
+      <c r="R1003" s="3"/>
+      <c r="S1003" s="3"/>
+      <c r="T1003" s="3"/>
+      <c r="U1003" s="3"/>
+      <c r="V1003" s="3"/>
+      <c r="W1003" s="3"/>
+      <c r="X1003" s="3"/>
+      <c r="Y1003" s="3"/>
+      <c r="Z1003" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -32245,7 +33007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z1010"/>
+  <dimension ref="A1:Z1014"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -32317,7 +33079,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2:D64" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
+        <f t="shared" ref="D2:D67" si="0">CONCATENATE("MainScript_",A2,"_",B2,"_",C2)</f>
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
@@ -32328,10 +33090,10 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -32410,7 +33172,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -32448,7 +33210,7 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>55</v>
@@ -32858,7 +33620,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>55</v>
@@ -32979,7 +33741,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>55</v>
@@ -33269,9 +34031,7 @@
       <c r="F25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="19" t="s">
-        <v>95</v>
-      </c>
+      <c r="G25" s="19"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
@@ -33292,27 +34052,29 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="66">
+    <row r="26" spans="1:26" ht="16.5">
       <c r="A26" s="7">
         <v>1</v>
       </c>
       <c r="B26" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_1</v>
+        <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="5"/>
+      <c r="G26" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -33333,7 +34095,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="49.5">
+    <row r="27" spans="1:26" ht="66">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -33341,14 +34103,14 @@
         <v>2</v>
       </c>
       <c r="C27" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_2</v>
+        <v>MainScript_1_2_1</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>30</v>
@@ -33374,7 +34136,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="16.5">
+    <row r="28" spans="1:26" ht="49.5">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -33382,17 +34144,17 @@
         <v>2</v>
       </c>
       <c r="C28" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_3</v>
+        <v>MainScript_1_2_2</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -33415,7 +34177,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="82.5">
+    <row r="29" spans="1:26" ht="16.5">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -33423,17 +34185,17 @@
         <v>2</v>
       </c>
       <c r="C29" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_4</v>
+        <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -33456,7 +34218,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="16.5">
+    <row r="30" spans="1:26" ht="82.5">
       <c r="A30" s="7">
         <v>1</v>
       </c>
@@ -33464,17 +34226,17 @@
         <v>2</v>
       </c>
       <c r="C30" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_5</v>
+        <v>MainScript_1_2_4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -33497,7 +34259,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="82.5">
+    <row r="31" spans="1:26" ht="16.5">
       <c r="A31" s="7">
         <v>1</v>
       </c>
@@ -33505,17 +34267,17 @@
         <v>2</v>
       </c>
       <c r="C31" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_6</v>
+        <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -33538,7 +34300,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="16.5">
+    <row r="32" spans="1:26" ht="82.5">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -33546,14 +34308,14 @@
         <v>2</v>
       </c>
       <c r="C32" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_7</v>
+        <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
@@ -33587,17 +34349,17 @@
         <v>2</v>
       </c>
       <c r="C33" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_8</v>
+        <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -33620,7 +34382,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="1:26" ht="99">
+    <row r="34" spans="1:26" ht="16.5">
       <c r="A34" s="7">
         <v>1</v>
       </c>
@@ -33628,17 +34390,17 @@
         <v>2</v>
       </c>
       <c r="C34" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_9</v>
+        <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -33661,7 +34423,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" spans="1:26" ht="16.5">
+    <row r="35" spans="1:26" ht="99">
       <c r="A35" s="7">
         <v>1</v>
       </c>
@@ -33669,17 +34431,17 @@
         <v>2</v>
       </c>
       <c r="C35" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_10</v>
+        <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -33702,7 +34464,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" spans="1:26" ht="33">
+    <row r="36" spans="1:26" ht="16.5">
       <c r="A36" s="7">
         <v>1</v>
       </c>
@@ -33710,17 +34472,17 @@
         <v>2</v>
       </c>
       <c r="C36" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_11</v>
+        <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>109</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -33743,7 +34505,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="16.5">
+    <row r="37" spans="1:26" ht="33">
       <c r="A37" s="7">
         <v>1</v>
       </c>
@@ -33751,17 +34513,17 @@
         <v>2</v>
       </c>
       <c r="C37" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_12</v>
+        <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -33784,7 +34546,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" spans="1:26" ht="82.5">
+    <row r="38" spans="1:26" ht="16.5">
       <c r="A38" s="7">
         <v>1</v>
       </c>
@@ -33792,17 +34554,17 @@
         <v>2</v>
       </c>
       <c r="C38" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_13</v>
+        <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -33825,7 +34587,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" spans="1:26" ht="49.5">
+    <row r="39" spans="1:26" ht="82.5">
       <c r="A39" s="7">
         <v>1</v>
       </c>
@@ -33833,14 +34595,14 @@
         <v>2</v>
       </c>
       <c r="C39" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_14</v>
+        <v>MainScript_1_2_13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>30</v>
@@ -33866,7 +34628,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" spans="1:26" ht="16.5">
+    <row r="40" spans="1:26" ht="49.5">
       <c r="A40" s="7">
         <v>1</v>
       </c>
@@ -33874,14 +34636,14 @@
         <v>2</v>
       </c>
       <c r="C40" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D40" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_15</v>
+        <v>MainScript_1_2_14</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
@@ -33907,7 +34669,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" spans="1:26" ht="33">
+    <row r="41" spans="1:26" ht="16.5">
       <c r="A41" s="7">
         <v>1</v>
       </c>
@@ -33915,19 +34677,19 @@
         <v>2</v>
       </c>
       <c r="C41" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_16</v>
+        <v>MainScript_1_2_15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -33948,7 +34710,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" spans="1:26" ht="16.5">
+    <row r="42" spans="1:26" ht="33">
       <c r="A42" s="7">
         <v>1</v>
       </c>
@@ -33956,18 +34718,19 @@
         <v>2</v>
       </c>
       <c r="C42" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_17</v>
+        <v>MainScript_1_2_16</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>55</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G42" s="19"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -33988,7 +34751,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43" spans="1:26" ht="49.5">
+    <row r="43" spans="1:26" ht="16.5">
       <c r="A43" s="7">
         <v>1</v>
       </c>
@@ -33996,19 +34759,18 @@
         <v>2</v>
       </c>
       <c r="C43" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_18</v>
+        <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" s="5"/>
+        <v>55</v>
+      </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -34037,21 +34799,19 @@
         <v>2</v>
       </c>
       <c r="C44" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D44" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_2_19</v>
+        <v>MainScript_1_2_18</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -34072,25 +34832,25 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" spans="1:26" ht="16.5">
+    <row r="45" spans="1:26" ht="49.5">
       <c r="A45" s="7">
         <v>1</v>
       </c>
       <c r="B45" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" s="7">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D45" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_1</v>
+        <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -34113,27 +34873,29 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" ht="33">
+    <row r="46" spans="1:26" ht="16.5">
       <c r="A46" s="7">
         <v>1</v>
       </c>
       <c r="B46" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" s="7">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D46" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_2</v>
+        <v>MainScript_1_2_20</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G46" s="5"/>
+      <c r="G46" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -34154,7 +34916,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" ht="33">
+    <row r="47" spans="1:26" ht="16.5">
       <c r="A47" s="7">
         <v>1</v>
       </c>
@@ -34162,17 +34924,17 @@
         <v>3</v>
       </c>
       <c r="C47" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_3</v>
+        <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -34195,7 +34957,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" spans="1:26" ht="49.5">
+    <row r="48" spans="1:26" ht="33">
       <c r="A48" s="7">
         <v>1</v>
       </c>
@@ -34203,14 +34965,14 @@
         <v>3</v>
       </c>
       <c r="C48" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_4</v>
+        <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>30</v>
@@ -34236,7 +34998,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" spans="1:26" ht="16.5">
+    <row r="49" spans="1:26" ht="33">
       <c r="A49" s="7">
         <v>1</v>
       </c>
@@ -34244,14 +35006,14 @@
         <v>3</v>
       </c>
       <c r="C49" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_5</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>122</v>
+        <v>MainScript_1_3_3</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>119</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -34277,7 +35039,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" spans="1:26" ht="16.5">
+    <row r="50" spans="1:26" ht="49.5">
       <c r="A50" s="7">
         <v>1</v>
       </c>
@@ -34285,14 +35047,14 @@
         <v>3</v>
       </c>
       <c r="C50" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_6</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>123</v>
+        <v>MainScript_1_3_4</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -34326,14 +35088,14 @@
         <v>3</v>
       </c>
       <c r="C51" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D51" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_7</v>
+        <v>MainScript_1_3_5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>30</v>
@@ -34359,7 +35121,7 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
     </row>
-    <row r="52" spans="1:26" ht="49.5">
+    <row r="52" spans="1:26" ht="16.5">
       <c r="A52" s="7">
         <v>1</v>
       </c>
@@ -34367,14 +35129,14 @@
         <v>3</v>
       </c>
       <c r="C52" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_8</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>126</v>
+        <v>MainScript_1_3_6</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>30</v>
@@ -34408,17 +35170,17 @@
         <v>3</v>
       </c>
       <c r="C53" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_9</v>
+        <v>MainScript_1_3_7</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -34441,7 +35203,7 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54" spans="1:26" ht="16.5">
+    <row r="54" spans="1:26" ht="49.5">
       <c r="A54" s="7">
         <v>1</v>
       </c>
@@ -34449,17 +35211,17 @@
         <v>3</v>
       </c>
       <c r="C54" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D54" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_10</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>137</v>
+        <v>MainScript_1_3_8</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -34482,7 +35244,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" spans="1:26" ht="33">
+    <row r="55" spans="1:26" ht="16.5">
       <c r="A55" s="7">
         <v>1</v>
       </c>
@@ -34490,17 +35252,17 @@
         <v>3</v>
       </c>
       <c r="C55" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D55" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_11</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>127</v>
+        <v>MainScript_1_3_9</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -34523,7 +35285,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" spans="1:26" ht="66">
+    <row r="56" spans="1:26" ht="16.5">
       <c r="A56" s="7">
         <v>1</v>
       </c>
@@ -34531,17 +35293,17 @@
         <v>3</v>
       </c>
       <c r="C56" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D56" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_12</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>128</v>
+        <v>MainScript_1_3_10</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -34564,7 +35326,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="49.5">
+    <row r="57" spans="1:26" ht="33">
       <c r="A57" s="7">
         <v>1</v>
       </c>
@@ -34572,14 +35334,14 @@
         <v>3</v>
       </c>
       <c r="C57" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D57" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_13</v>
+        <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -34605,7 +35367,7 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58" spans="1:26" ht="16.5">
+    <row r="58" spans="1:26" ht="66">
       <c r="A58" s="7">
         <v>1</v>
       </c>
@@ -34613,21 +35375,19 @@
         <v>3</v>
       </c>
       <c r="C58" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D58" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_3_14</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>130</v>
+        <v>MainScript_1_3_12</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>127</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -34648,25 +35408,25 @@
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
     </row>
-    <row r="59" spans="1:26" ht="16.5">
+    <row r="59" spans="1:26" ht="49.5">
       <c r="A59" s="7">
         <v>1</v>
       </c>
       <c r="B59" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D59" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_1</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>138</v>
+        <v>MainScript_1_3_13</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>128</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -34689,22 +35449,22 @@
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
     </row>
-    <row r="60" spans="1:26" ht="45">
+    <row r="60" spans="1:26" ht="16.5">
       <c r="A60" s="7">
         <v>1</v>
       </c>
       <c r="B60" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D60" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_2</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>139</v>
+        <v>MainScript_1_3_14</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>30</v>
@@ -34730,27 +35490,29 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61" spans="1:26" ht="33">
+    <row r="61" spans="1:26" ht="16.5">
       <c r="A61" s="7">
         <v>1</v>
       </c>
       <c r="B61" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D61" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_3</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>140</v>
+        <v>MainScript_1_3_15</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G61" s="5"/>
+      <c r="G61" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -34771,7 +35533,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" spans="1:26" ht="33">
+    <row r="62" spans="1:26" ht="16.5">
       <c r="A62" s="7">
         <v>1</v>
       </c>
@@ -34779,17 +35541,17 @@
         <v>4</v>
       </c>
       <c r="C62" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_4</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>141</v>
+        <v>MainScript_1_4_1</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>137</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -34812,7 +35574,7 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" spans="1:26" ht="16.5">
+    <row r="63" spans="1:26" ht="45">
       <c r="A63" s="7">
         <v>1</v>
       </c>
@@ -34820,14 +35582,14 @@
         <v>4</v>
       </c>
       <c r="C63" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D63" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_5</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>142</v>
+        <v>MainScript_1_4_2</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>138</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -34853,7 +35615,7 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64" spans="1:26" ht="16.5">
+    <row r="64" spans="1:26" ht="33">
       <c r="A64" s="7">
         <v>1</v>
       </c>
@@ -34861,14 +35623,14 @@
         <v>4</v>
       </c>
       <c r="C64" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D64" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>MainScript_1_4_6</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>143</v>
+        <v>MainScript_1_4_3</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>139</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -34894,7 +35656,7 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65" spans="1:26" ht="49.5">
+    <row r="65" spans="1:26" ht="33">
       <c r="A65" s="7">
         <v>1</v>
       </c>
@@ -34902,14 +35664,14 @@
         <v>4</v>
       </c>
       <c r="C65" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D65" s="5" t="str">
-        <f t="shared" ref="D65:D78" si="1">CONCATENATE("MainScript_",A65,"_",B65,"_",C65)</f>
-        <v>MainScript_1_4_7</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -34943,14 +35705,14 @@
         <v>4</v>
       </c>
       <c r="C66" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D66" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_4_8</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>145</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_5</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>30</v>
@@ -34984,14 +35746,14 @@
         <v>4</v>
       </c>
       <c r="C67" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D67" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_4_9</v>
+        <f t="shared" si="0"/>
+        <v>MainScript_1_4_6</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -35017,7 +35779,7 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68" spans="1:26" ht="16.5">
+    <row r="68" spans="1:26" ht="49.5">
       <c r="A68" s="7">
         <v>1</v>
       </c>
@@ -35025,14 +35787,14 @@
         <v>4</v>
       </c>
       <c r="C68" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D68" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>MainScript_1_4_10</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>147</v>
+        <f t="shared" ref="D68:D82" si="1">CONCATENATE("MainScript_",A68,"_",B68,"_",C68)</f>
+        <v>MainScript_1_4_7</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>143</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -35058,7 +35820,7 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69" spans="1:26" ht="82.5">
+    <row r="69" spans="1:26" ht="16.5">
       <c r="A69" s="7">
         <v>1</v>
       </c>
@@ -35066,14 +35828,14 @@
         <v>4</v>
       </c>
       <c r="C69" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D69" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_4_11</v>
+        <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -35099,7 +35861,7 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" spans="1:26" ht="66">
+    <row r="70" spans="1:26" ht="16.5">
       <c r="A70" s="7">
         <v>1</v>
       </c>
@@ -35107,14 +35869,14 @@
         <v>4</v>
       </c>
       <c r="C70" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_4_12</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>149</v>
+        <v>MainScript_1_4_9</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -35148,14 +35910,14 @@
         <v>4</v>
       </c>
       <c r="C71" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D71" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_4_13</v>
+        <v>MainScript_1_4_10</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -35181,7 +35943,7 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
     </row>
-    <row r="72" spans="1:26" ht="16.5">
+    <row r="72" spans="1:26" ht="82.5">
       <c r="A72" s="7">
         <v>1</v>
       </c>
@@ -35189,17 +35951,17 @@
         <v>4</v>
       </c>
       <c r="C72" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D72" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_4_14</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>152</v>
+        <v>MainScript_1_4_11</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>147</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -35230,21 +35992,19 @@
         <v>4</v>
       </c>
       <c r="C73" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D73" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_4_15</v>
+        <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -35270,17 +36030,17 @@
         <v>1</v>
       </c>
       <c r="B74" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" s="7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D74" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_5_1</v>
+        <v>MainScript_1_4_13</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>30</v>
@@ -35311,20 +36071,20 @@
         <v>1</v>
       </c>
       <c r="B75" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D75" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_5_2</v>
+        <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -35347,22 +36107,22 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" spans="1:26" ht="16.5">
+    <row r="76" spans="1:26" ht="66">
       <c r="A76" s="7">
         <v>1</v>
       </c>
       <c r="B76" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D76" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_5_3</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>197</v>
+        <v>MainScript_1_4_15</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -35393,22 +36153,24 @@
         <v>1</v>
       </c>
       <c r="B77" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D77" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_5_4</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>208</v>
+        <v>MainScript_1_4_16</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>197</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G77" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -35437,21 +36199,19 @@
         <v>5</v>
       </c>
       <c r="C78" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>MainScript_1_5_5</v>
+        <v>MainScript_1_5_1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -35473,12 +36233,25 @@
       <c r="Z78" s="5"/>
     </row>
     <row r="79" spans="1:26" ht="16.5">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="A79" s="7">
+        <v>1</v>
+      </c>
+      <c r="B79" s="7">
+        <v>5</v>
+      </c>
+      <c r="C79" s="7">
+        <v>2</v>
+      </c>
+      <c r="D79" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_2</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
@@ -35501,12 +36274,25 @@
       <c r="Z79" s="5"/>
     </row>
     <row r="80" spans="1:26" ht="16.5">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
+      <c r="A80" s="7">
+        <v>1</v>
+      </c>
+      <c r="B80" s="7">
+        <v>5</v>
+      </c>
+      <c r="C80" s="7">
+        <v>3</v>
+      </c>
+      <c r="D80" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_3</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
@@ -35529,12 +36315,25 @@
       <c r="Z80" s="5"/>
     </row>
     <row r="81" spans="1:26" ht="16.5">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
+      <c r="A81" s="7">
+        <v>1</v>
+      </c>
+      <c r="B81" s="7">
+        <v>5</v>
+      </c>
+      <c r="C81" s="7">
+        <v>4</v>
+      </c>
+      <c r="D81" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_4</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>198</v>
+      </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -35557,13 +36356,28 @@
       <c r="Z81" s="5"/>
     </row>
     <row r="82" spans="1:26" ht="16.5">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
+      <c r="A82" s="7">
+        <v>1</v>
+      </c>
+      <c r="B82" s="7">
+        <v>5</v>
+      </c>
+      <c r="C82" s="7">
+        <v>5</v>
+      </c>
+      <c r="D82" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_1_5_5</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -61541,7 +62355,119 @@
       <c r="Z1009" s="5"/>
     </row>
     <row r="1010" spans="1:26" ht="16.5">
+      <c r="A1010" s="7"/>
+      <c r="B1010" s="7"/>
+      <c r="C1010" s="7"/>
+      <c r="D1010" s="5"/>
       <c r="E1010" s="5"/>
+      <c r="F1010" s="5"/>
+      <c r="G1010" s="5"/>
+      <c r="H1010" s="5"/>
+      <c r="I1010" s="5"/>
+      <c r="J1010" s="5"/>
+      <c r="K1010" s="5"/>
+      <c r="L1010" s="5"/>
+      <c r="M1010" s="5"/>
+      <c r="N1010" s="5"/>
+      <c r="O1010" s="5"/>
+      <c r="P1010" s="5"/>
+      <c r="Q1010" s="5"/>
+      <c r="R1010" s="5"/>
+      <c r="S1010" s="5"/>
+      <c r="T1010" s="5"/>
+      <c r="U1010" s="5"/>
+      <c r="V1010" s="5"/>
+      <c r="W1010" s="5"/>
+      <c r="X1010" s="5"/>
+      <c r="Y1010" s="5"/>
+      <c r="Z1010" s="5"/>
+    </row>
+    <row r="1011" spans="1:26" ht="16.5">
+      <c r="A1011" s="7"/>
+      <c r="B1011" s="7"/>
+      <c r="C1011" s="7"/>
+      <c r="D1011" s="5"/>
+      <c r="E1011" s="5"/>
+      <c r="F1011" s="5"/>
+      <c r="G1011" s="5"/>
+      <c r="H1011" s="5"/>
+      <c r="I1011" s="5"/>
+      <c r="J1011" s="5"/>
+      <c r="K1011" s="5"/>
+      <c r="L1011" s="5"/>
+      <c r="M1011" s="5"/>
+      <c r="N1011" s="5"/>
+      <c r="O1011" s="5"/>
+      <c r="P1011" s="5"/>
+      <c r="Q1011" s="5"/>
+      <c r="R1011" s="5"/>
+      <c r="S1011" s="5"/>
+      <c r="T1011" s="5"/>
+      <c r="U1011" s="5"/>
+      <c r="V1011" s="5"/>
+      <c r="W1011" s="5"/>
+      <c r="X1011" s="5"/>
+      <c r="Y1011" s="5"/>
+      <c r="Z1011" s="5"/>
+    </row>
+    <row r="1012" spans="1:26" ht="16.5">
+      <c r="A1012" s="7"/>
+      <c r="B1012" s="7"/>
+      <c r="C1012" s="7"/>
+      <c r="D1012" s="5"/>
+      <c r="E1012" s="5"/>
+      <c r="F1012" s="5"/>
+      <c r="G1012" s="5"/>
+      <c r="H1012" s="5"/>
+      <c r="I1012" s="5"/>
+      <c r="J1012" s="5"/>
+      <c r="K1012" s="5"/>
+      <c r="L1012" s="5"/>
+      <c r="M1012" s="5"/>
+      <c r="N1012" s="5"/>
+      <c r="O1012" s="5"/>
+      <c r="P1012" s="5"/>
+      <c r="Q1012" s="5"/>
+      <c r="R1012" s="5"/>
+      <c r="S1012" s="5"/>
+      <c r="T1012" s="5"/>
+      <c r="U1012" s="5"/>
+      <c r="V1012" s="5"/>
+      <c r="W1012" s="5"/>
+      <c r="X1012" s="5"/>
+      <c r="Y1012" s="5"/>
+      <c r="Z1012" s="5"/>
+    </row>
+    <row r="1013" spans="1:26" ht="16.5">
+      <c r="A1013" s="7"/>
+      <c r="B1013" s="7"/>
+      <c r="C1013" s="7"/>
+      <c r="D1013" s="5"/>
+      <c r="E1013" s="5"/>
+      <c r="F1013" s="5"/>
+      <c r="G1013" s="5"/>
+      <c r="H1013" s="5"/>
+      <c r="I1013" s="5"/>
+      <c r="J1013" s="5"/>
+      <c r="K1013" s="5"/>
+      <c r="L1013" s="5"/>
+      <c r="M1013" s="5"/>
+      <c r="N1013" s="5"/>
+      <c r="O1013" s="5"/>
+      <c r="P1013" s="5"/>
+      <c r="Q1013" s="5"/>
+      <c r="R1013" s="5"/>
+      <c r="S1013" s="5"/>
+      <c r="T1013" s="5"/>
+      <c r="U1013" s="5"/>
+      <c r="V1013" s="5"/>
+      <c r="W1013" s="5"/>
+      <c r="X1013" s="5"/>
+      <c r="Y1013" s="5"/>
+      <c r="Z1013" s="5"/>
+    </row>
+    <row r="1014" spans="1:26" ht="16.5">
+      <c r="E1014" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -62626,7 +63552,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>27</v>
@@ -62634,34 +63560,34 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C4" s="6"/>
     </row>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CFCE14-71EA-4ABE-9A0F-DE6D5CD54FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99648650-137A-446B-9750-6AC2C79BBC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,8 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -631,7 +622,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="212">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2872,11 +2863,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">소년의 눈동자가 흔들렸다.
-</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">"지금 멈추면, 이건 또 하나의 반복으로 끝나겠지
 하지만 네가 걸어간다면 끝은 달라질 수도 있어."
 </t>
@@ -2952,10 +2938,6 @@
   </si>
   <si>
     <t>MainScript_1_2_11</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>나는 천천히 걸음을 옮겼고
@@ -3359,10 +3341,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100},{"ID":"Effect_002","Value":-1},{"ID":"Effect_003","Code":"Weapon_005","Value":1}]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>상인을 만났다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3419,10 +3397,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_001","Value":100}]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"ID":"Effect_003","Code":"Weapon_004","Value":1}]</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3436,6 +3410,11 @@
   </si>
   <si>
     <t>MainScene_1_1_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 눈동자가 흔들렸다.
+</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4023,19 +4002,19 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -4108,9 +4087,7 @@
       <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>193</v>
-      </c>
+      <c r="G4" s="16"/>
       <c r="H4" s="5"/>
       <c r="I4" s="3"/>
       <c r="J4" s="5"/>
@@ -4305,9 +4282,7 @@
       <c r="F9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>210</v>
-      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -4846,7 +4821,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -4883,7 +4858,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -4922,11 +4897,11 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -4963,7 +4938,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -5158,7 +5133,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3"/>
@@ -5197,15 +5172,15 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -5240,7 +5215,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -5357,7 +5332,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -5396,7 +5371,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -5435,7 +5410,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -5474,7 +5449,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -5512,10 +5487,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -5554,7 +5529,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -5593,7 +5568,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -5632,7 +5607,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -5671,7 +5646,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -5710,11 +5685,11 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -5751,7 +5726,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5790,7 +5765,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5829,11 +5804,9 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>210</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="G48" s="5"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
@@ -5870,11 +5843,9 @@
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>210</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G49" s="5"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -5911,19 +5882,17 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="L50" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -5954,13 +5923,13 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H51" s="3"/>
       <c r="J51" s="3"/>
@@ -5996,13 +5965,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -6037,13 +6006,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -6080,7 +6049,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -6119,7 +6088,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -6158,7 +6127,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -6197,7 +6166,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -6236,7 +6205,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -6275,7 +6244,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -6314,11 +6283,11 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -6355,7 +6324,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -6394,7 +6363,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -6433,7 +6402,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -6472,7 +6441,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -6511,7 +6480,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -6550,7 +6519,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -6589,7 +6558,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6628,7 +6597,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6667,7 +6636,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6706,7 +6675,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6745,7 +6714,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6784,7 +6753,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6823,7 +6792,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -6862,7 +6831,7 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="3"/>
@@ -6901,7 +6870,7 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
@@ -6940,11 +6909,11 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -6981,7 +6950,7 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
@@ -7020,15 +6989,15 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -7066,7 +7035,7 @@
         <v>MainScene_1_5_4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="3"/>
@@ -7108,7 +7077,7 @@
         <v>MainScene_1_5_5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="3"/>
@@ -7147,7 +7116,7 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="3"/>
@@ -7186,7 +7155,7 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="3"/>
@@ -33090,10 +33059,10 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -33172,7 +33141,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -33210,7 +33179,7 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>55</v>
@@ -33377,7 +33346,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -33582,7 +33551,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -33620,7 +33589,7 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>55</v>
@@ -33661,7 +33630,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>30</v>
@@ -33701,10 +33670,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -33741,7 +33710,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>55</v>
@@ -33781,7 +33750,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>30</v>
@@ -33822,7 +33791,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>30</v>
@@ -33866,7 +33835,7 @@
         <v>76</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -33903,7 +33872,7 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>30</v>
@@ -33944,7 +33913,7 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>30</v>
@@ -33985,7 +33954,7 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>30</v>
@@ -34029,7 +33998,7 @@
         <v>72</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="5"/>
@@ -34067,7 +34036,7 @@
         <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>30</v>
@@ -34154,7 +34123,7 @@
         <v>70</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -34192,7 +34161,7 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>55</v>
@@ -34236,7 +34205,7 @@
         <v>69</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -34274,7 +34243,7 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>55</v>
@@ -34315,7 +34284,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
@@ -34356,10 +34325,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -34397,7 +34366,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>55</v>
@@ -34438,10 +34407,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -34479,7 +34448,7 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>55</v>
@@ -34520,10 +34489,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -34561,7 +34530,7 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>55</v>
@@ -34684,7 +34653,7 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>30</v>
@@ -34725,12 +34694,12 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G42" s="19"/>
+        <v>184</v>
+      </c>
+      <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -34766,7 +34735,7 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>55</v>
@@ -34847,7 +34816,7 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>30</v>
@@ -34888,7 +34857,7 @@
         <v>MainScript_1_2_20</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>30</v>
@@ -34931,7 +34900,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>55</v>
@@ -34972,7 +34941,7 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>30</v>
@@ -35013,7 +34982,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -35054,7 +35023,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -35095,7 +35064,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>30</v>
@@ -35136,7 +35105,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>30</v>
@@ -35177,7 +35146,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>30</v>
@@ -35218,7 +35187,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>30</v>
@@ -35259,10 +35228,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -35300,7 +35269,7 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>55</v>
@@ -35341,7 +35310,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -35382,7 +35351,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>30</v>
@@ -35423,7 +35392,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>30</v>
@@ -35464,7 +35433,7 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>30</v>
@@ -35505,7 +35474,7 @@
         <v>MainScript_1_3_15</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>30</v>
@@ -35548,7 +35517,7 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>55</v>
@@ -35589,7 +35558,7 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -35630,7 +35599,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -35671,7 +35640,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -35712,10 +35681,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -35753,7 +35722,7 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -35794,7 +35763,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -35835,7 +35804,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -35876,7 +35845,7 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -35917,7 +35886,7 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -35958,7 +35927,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -35999,7 +35968,7 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>30</v>
@@ -36040,10 +36009,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -36081,7 +36050,7 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>55</v>
@@ -36122,7 +36091,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -36163,7 +36132,7 @@
         <v>MainScript_1_4_16</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>30</v>
@@ -36206,7 +36175,7 @@
         <v>MainScript_1_5_1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>30</v>
@@ -36247,7 +36216,7 @@
         <v>MainScript_1_5_2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>30</v>
@@ -36288,7 +36257,7 @@
         <v>MainScript_1_5_3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>30</v>
@@ -36329,10 +36298,10 @@
         <v>MainScript_1_5_4</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -36370,7 +36339,7 @@
         <v>MainScript_1_5_5</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>30</v>
@@ -62508,19 +62477,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -63552,7 +63521,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>27</v>
@@ -63560,34 +63529,34 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>190</v>
-      </c>
       <c r="C3" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C4" s="6"/>
     </row>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99648650-137A-446B-9750-6AC2C79BBC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD2B1DB-C872-4B3D-A9F7-C6DD54CF1628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="2490" yWindow="1470" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,17 @@
     <sheet name="Main_SuccessRate_Master_Main" sheetId="3" r:id="rId3"/>
     <sheet name="Story_Effect_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="d4gLGIA0SBWCPd3pZpVE5bQwybvzM8L5KBikCItZ3vw="/>
     </ext>
@@ -622,7 +631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="238">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -3417,6 +3426,89 @@
 </t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>MainScript_2_1_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_1_3</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_4</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_5</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_6</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScript_2_1_7</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_8</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_9</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_10</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_11</t>
+  </si>
+  <si>
+    <t>MainScript_2_1_12</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_2</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_3</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_4</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_5</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_6</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_7</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_8</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_9</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_10</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_11</t>
+  </si>
+  <si>
+    <t>2챕터 메인스토리 진행 테스트 1_12</t>
+  </si>
+  <si>
+    <t>Chapter_Index</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChapterBreack</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -5327,7 +5419,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" ref="D36:D82" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <f t="shared" ref="D36:D94" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
@@ -7179,12 +7271,23 @@
       <c r="Z82" s="3"/>
     </row>
     <row r="83" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="3"/>
+      <c r="A83" s="4">
+        <v>2</v>
+      </c>
+      <c r="B83" s="4">
+        <v>1</v>
+      </c>
+      <c r="C83" s="4">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_1</v>
+      </c>
       <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
@@ -7207,12 +7310,23 @@
       <c r="Z83" s="3"/>
     </row>
     <row r="84" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="3"/>
+      <c r="A84" s="4">
+        <v>2</v>
+      </c>
+      <c r="B84" s="4">
+        <v>1</v>
+      </c>
+      <c r="C84" s="4">
+        <v>2</v>
+      </c>
+      <c r="D84" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_2</v>
+      </c>
       <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G84" s="5"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
@@ -7235,12 +7349,23 @@
       <c r="Z84" s="3"/>
     </row>
     <row r="85" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="3"/>
+      <c r="A85" s="4">
+        <v>2</v>
+      </c>
+      <c r="B85" s="4">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_3</v>
+      </c>
       <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
@@ -7263,12 +7388,23 @@
       <c r="Z85" s="3"/>
     </row>
     <row r="86" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="3"/>
+      <c r="A86" s="4">
+        <v>2</v>
+      </c>
+      <c r="B86" s="4">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4">
+        <v>4</v>
+      </c>
+      <c r="D86" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_4</v>
+      </c>
       <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G86" s="5"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
@@ -7291,12 +7427,23 @@
       <c r="Z86" s="3"/>
     </row>
     <row r="87" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="3"/>
+      <c r="A87" s="4">
+        <v>2</v>
+      </c>
+      <c r="B87" s="4">
+        <v>1</v>
+      </c>
+      <c r="C87" s="4">
+        <v>5</v>
+      </c>
+      <c r="D87" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_5</v>
+      </c>
       <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G87" s="5"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
@@ -7319,12 +7466,23 @@
       <c r="Z87" s="3"/>
     </row>
     <row r="88" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="3"/>
+      <c r="A88" s="4">
+        <v>2</v>
+      </c>
+      <c r="B88" s="4">
+        <v>1</v>
+      </c>
+      <c r="C88" s="4">
+        <v>6</v>
+      </c>
+      <c r="D88" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_6</v>
+      </c>
       <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
@@ -7347,12 +7505,23 @@
       <c r="Z88" s="3"/>
     </row>
     <row r="89" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="3"/>
+      <c r="A89" s="4">
+        <v>2</v>
+      </c>
+      <c r="B89" s="4">
+        <v>1</v>
+      </c>
+      <c r="C89" s="4">
+        <v>7</v>
+      </c>
+      <c r="D89" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_7</v>
+      </c>
       <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="G89" s="5"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
@@ -7375,12 +7544,23 @@
       <c r="Z89" s="3"/>
     </row>
     <row r="90" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="3"/>
+      <c r="A90" s="4">
+        <v>2</v>
+      </c>
+      <c r="B90" s="4">
+        <v>1</v>
+      </c>
+      <c r="C90" s="4">
+        <v>8</v>
+      </c>
+      <c r="D90" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_8</v>
+      </c>
       <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="G90" s="5"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
@@ -7403,12 +7583,23 @@
       <c r="Z90" s="3"/>
     </row>
     <row r="91" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="3"/>
+      <c r="A91" s="4">
+        <v>2</v>
+      </c>
+      <c r="B91" s="4">
+        <v>1</v>
+      </c>
+      <c r="C91" s="4">
+        <v>9</v>
+      </c>
+      <c r="D91" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_9</v>
+      </c>
       <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
+      <c r="F91" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="G91" s="5"/>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
@@ -7431,12 +7622,23 @@
       <c r="Z91" s="3"/>
     </row>
     <row r="92" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="3"/>
+      <c r="A92" s="4">
+        <v>2</v>
+      </c>
+      <c r="B92" s="4">
+        <v>1</v>
+      </c>
+      <c r="C92" s="4">
+        <v>10</v>
+      </c>
+      <c r="D92" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_10</v>
+      </c>
       <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="G92" s="5"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
@@ -7459,12 +7661,23 @@
       <c r="Z92" s="3"/>
     </row>
     <row r="93" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="3"/>
+      <c r="A93" s="4">
+        <v>2</v>
+      </c>
+      <c r="B93" s="4">
+        <v>1</v>
+      </c>
+      <c r="C93" s="4">
+        <v>11</v>
+      </c>
+      <c r="D93" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_11</v>
+      </c>
       <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G93" s="5"/>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
@@ -7487,12 +7700,23 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="3"/>
+      <c r="A94" s="4">
+        <v>2</v>
+      </c>
+      <c r="B94" s="4">
+        <v>1</v>
+      </c>
+      <c r="C94" s="4">
+        <v>12</v>
+      </c>
+      <c r="D94" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MainScene_2_1_12</v>
+      </c>
       <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="G94" s="5"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
@@ -32993,7 +33217,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="9" t="s">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -33013,13 +33237,15 @@
       <c r="G1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -33058,13 +33284,12 @@
         <v>55</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -35759,7 +35984,7 @@
         <v>7</v>
       </c>
       <c r="D68" s="5" t="str">
-        <f t="shared" ref="D68:D82" si="1">CONCATENATE("MainScript_",A68,"_",B68,"_",C68)</f>
+        <f t="shared" ref="D68:D94" si="1">CONCATENATE("MainScript_",A68,"_",B68,"_",C68)</f>
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
@@ -36347,7 +36572,9 @@
       <c r="G82" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H82" s="5"/>
+      <c r="H82" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
@@ -36368,12 +36595,25 @@
       <c r="Z82" s="5"/>
     </row>
     <row r="83" spans="1:26" ht="16.5">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
+      <c r="A83" s="7">
+        <v>2</v>
+      </c>
+      <c r="B83" s="7">
+        <v>1</v>
+      </c>
+      <c r="C83" s="7">
+        <v>1</v>
+      </c>
+      <c r="D83" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_1</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -36396,12 +36636,25 @@
       <c r="Z83" s="5"/>
     </row>
     <row r="84" spans="1:26" ht="16.5">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
+      <c r="A84" s="7">
+        <v>2</v>
+      </c>
+      <c r="B84" s="7">
+        <v>1</v>
+      </c>
+      <c r="C84" s="7">
+        <v>2</v>
+      </c>
+      <c r="D84" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_2</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -36424,12 +36677,25 @@
       <c r="Z84" s="5"/>
     </row>
     <row r="85" spans="1:26" ht="16.5">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
+      <c r="A85" s="7">
+        <v>2</v>
+      </c>
+      <c r="B85" s="7">
+        <v>1</v>
+      </c>
+      <c r="C85" s="7">
+        <v>3</v>
+      </c>
+      <c r="D85" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_3</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -36452,12 +36718,25 @@
       <c r="Z85" s="5"/>
     </row>
     <row r="86" spans="1:26" ht="16.5">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="A86" s="7">
+        <v>2</v>
+      </c>
+      <c r="B86" s="7">
+        <v>1</v>
+      </c>
+      <c r="C86" s="7">
+        <v>4</v>
+      </c>
+      <c r="D86" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_4</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -36480,12 +36759,25 @@
       <c r="Z86" s="5"/>
     </row>
     <row r="87" spans="1:26" ht="16.5">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
+      <c r="A87" s="7">
+        <v>2</v>
+      </c>
+      <c r="B87" s="7">
+        <v>1</v>
+      </c>
+      <c r="C87" s="7">
+        <v>5</v>
+      </c>
+      <c r="D87" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_5</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -36508,12 +36800,25 @@
       <c r="Z87" s="5"/>
     </row>
     <row r="88" spans="1:26" ht="16.5">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
+      <c r="A88" s="7">
+        <v>2</v>
+      </c>
+      <c r="B88" s="7">
+        <v>1</v>
+      </c>
+      <c r="C88" s="7">
+        <v>6</v>
+      </c>
+      <c r="D88" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_6</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -36536,12 +36841,25 @@
       <c r="Z88" s="5"/>
     </row>
     <row r="89" spans="1:26" ht="16.5">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="A89" s="7">
+        <v>2</v>
+      </c>
+      <c r="B89" s="7">
+        <v>1</v>
+      </c>
+      <c r="C89" s="7">
+        <v>7</v>
+      </c>
+      <c r="D89" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_7</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -36564,12 +36882,25 @@
       <c r="Z89" s="5"/>
     </row>
     <row r="90" spans="1:26" ht="16.5">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
+      <c r="A90" s="7">
+        <v>2</v>
+      </c>
+      <c r="B90" s="7">
+        <v>1</v>
+      </c>
+      <c r="C90" s="7">
+        <v>8</v>
+      </c>
+      <c r="D90" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_8</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -36592,12 +36923,25 @@
       <c r="Z90" s="5"/>
     </row>
     <row r="91" spans="1:26" ht="16.5">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
+      <c r="A91" s="7">
+        <v>2</v>
+      </c>
+      <c r="B91" s="7">
+        <v>1</v>
+      </c>
+      <c r="C91" s="7">
+        <v>9</v>
+      </c>
+      <c r="D91" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_9</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -36620,12 +36964,25 @@
       <c r="Z91" s="5"/>
     </row>
     <row r="92" spans="1:26" ht="16.5">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
+      <c r="A92" s="7">
+        <v>2</v>
+      </c>
+      <c r="B92" s="7">
+        <v>1</v>
+      </c>
+      <c r="C92" s="7">
+        <v>10</v>
+      </c>
+      <c r="D92" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_10</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -36648,12 +37005,25 @@
       <c r="Z92" s="5"/>
     </row>
     <row r="93" spans="1:26" ht="16.5">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
+      <c r="A93" s="7">
+        <v>2</v>
+      </c>
+      <c r="B93" s="7">
+        <v>1</v>
+      </c>
+      <c r="C93" s="7">
+        <v>11</v>
+      </c>
+      <c r="D93" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_11</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -36676,13 +37046,28 @@
       <c r="Z93" s="5"/>
     </row>
     <row r="94" spans="1:26" ht="16.5">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
+      <c r="A94" s="7">
+        <v>2</v>
+      </c>
+      <c r="B94" s="7">
+        <v>1</v>
+      </c>
+      <c r="C94" s="7">
+        <v>12</v>
+      </c>
+      <c r="D94" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>MainScript_2_1_12</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD2B1DB-C872-4B3D-A9F7-C6DD54CF1628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E2E7C4-1148-49C0-AB35-D60F26E5ECB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="1470" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="3180" yWindow="2160" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="238">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -3465,49 +3465,62 @@
     <t>MainScript_2_1_12</t>
   </si>
   <si>
-    <t>2챕터 메인스토리 진행 테스트 1_1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_2</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_3</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_4</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_5</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_6</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_7</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_8</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_9</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_10</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_11</t>
-  </si>
-  <si>
-    <t>2챕터 메인스토리 진행 테스트 1_12</t>
-  </si>
-  <si>
     <t>Chapter_Index</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ChapterBreack</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_1
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_2
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_12
+</t>
   </si>
 </sst>
 </file>
@@ -33217,7 +33230,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="9" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -33238,7 +33251,7 @@
         <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>48</v>
@@ -36594,7 +36607,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83" spans="1:26" ht="16.5">
+    <row r="83" spans="1:26" ht="33">
       <c r="A83" s="7">
         <v>2</v>
       </c>
@@ -36608,8 +36621,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_1</v>
       </c>
-      <c r="E83" s="5" t="s">
-        <v>224</v>
+      <c r="E83" s="16" t="s">
+        <v>226</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>30</v>
@@ -36635,7 +36648,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84" spans="1:26" ht="16.5">
+    <row r="84" spans="1:26" ht="33">
       <c r="A84" s="7">
         <v>2</v>
       </c>
@@ -36649,8 +36662,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_2</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>225</v>
+      <c r="E84" s="16" t="s">
+        <v>227</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>30</v>
@@ -36676,7 +36689,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85" spans="1:26" ht="16.5">
+    <row r="85" spans="1:26" ht="33">
       <c r="A85" s="7">
         <v>2</v>
       </c>
@@ -36690,8 +36703,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_3</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>226</v>
+      <c r="E85" s="16" t="s">
+        <v>228</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>30</v>
@@ -36717,7 +36730,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86" spans="1:26" ht="16.5">
+    <row r="86" spans="1:26" ht="33">
       <c r="A86" s="7">
         <v>2</v>
       </c>
@@ -36731,8 +36744,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_4</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>227</v>
+      <c r="E86" s="16" t="s">
+        <v>229</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>30</v>
@@ -36758,7 +36771,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87" spans="1:26" ht="16.5">
+    <row r="87" spans="1:26" ht="33">
       <c r="A87" s="7">
         <v>2</v>
       </c>
@@ -36772,8 +36785,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_5</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>228</v>
+      <c r="E87" s="16" t="s">
+        <v>230</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>30</v>
@@ -36799,7 +36812,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88" spans="1:26" ht="16.5">
+    <row r="88" spans="1:26" ht="33">
       <c r="A88" s="7">
         <v>2</v>
       </c>
@@ -36813,8 +36826,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_6</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>229</v>
+      <c r="E88" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>30</v>
@@ -36840,7 +36853,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89" spans="1:26" ht="16.5">
+    <row r="89" spans="1:26" ht="33">
       <c r="A89" s="7">
         <v>2</v>
       </c>
@@ -36854,8 +36867,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_7</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>230</v>
+      <c r="E89" s="16" t="s">
+        <v>232</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>30</v>
@@ -36881,7 +36894,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90" spans="1:26" ht="16.5">
+    <row r="90" spans="1:26" ht="33">
       <c r="A90" s="7">
         <v>2</v>
       </c>
@@ -36895,8 +36908,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_8</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>231</v>
+      <c r="E90" s="16" t="s">
+        <v>233</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>30</v>
@@ -36922,7 +36935,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91" spans="1:26" ht="16.5">
+    <row r="91" spans="1:26" ht="33">
       <c r="A91" s="7">
         <v>2</v>
       </c>
@@ -36936,8 +36949,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_9</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>232</v>
+      <c r="E91" s="16" t="s">
+        <v>234</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>30</v>
@@ -36963,7 +36976,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92" spans="1:26" ht="16.5">
+    <row r="92" spans="1:26" ht="33">
       <c r="A92" s="7">
         <v>2</v>
       </c>
@@ -36977,8 +36990,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_10</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>233</v>
+      <c r="E92" s="16" t="s">
+        <v>235</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>30</v>
@@ -37004,7 +37017,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93" spans="1:26" ht="16.5">
+    <row r="93" spans="1:26" ht="33">
       <c r="A93" s="7">
         <v>2</v>
       </c>
@@ -37018,8 +37031,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_11</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>234</v>
+      <c r="E93" s="16" t="s">
+        <v>236</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>30</v>
@@ -37045,7 +37058,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94" spans="1:26" ht="16.5">
+    <row r="94" spans="1:26" ht="33">
       <c r="A94" s="7">
         <v>2</v>
       </c>
@@ -37059,8 +37072,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_12</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>235</v>
+      <c r="E94" s="16" t="s">
+        <v>237</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>30</v>
@@ -37068,7 +37081,9 @@
       <c r="G94" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H94" s="5"/>
+      <c r="H94" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E2E7C4-1148-49C0-AB35-D60F26E5ECB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6466A4-4502-4981-AA59-A34E0F85E69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="2160" windowWidth="34995" windowHeight="15345" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="238">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -36500,8 +36500,12 @@
       <c r="F80" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
+      <c r="G80" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6466A4-4502-4981-AA59-A34E0F85E69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E24AD8B-333C-40F7-AE5D-C2B50EA8B99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="690" yWindow="2670" windowWidth="35085" windowHeight="18210" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="238">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2989,19 +2989,6 @@
     <t>C1E2_journey</t>
   </si>
   <si>
-    <t xml:space="preserve">나는 손을 거두고 
-"…괜찮아."
-라고 작은 목소리로 중얼거렸다…
-나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
-</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>하지만 그 소년은 숨이 점점 거칠어 지다가 
-결국 숨이 끊어져 버렸다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>C1E2_finally</t>
   </si>
   <si>
@@ -3032,17 +3019,6 @@
     <t>MainScene_1_2_18</t>
   </si>
   <si>
-    <t>나는 본능적으로 뒤로 물러섰다.
-"…젠장…"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기…
-손에 쥘 만한 무엇이든
-나는 주변을 둘러보다가 땅에 떨어진 무기를 발견했다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>검</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3056,17 +3032,6 @@
   </si>
   <si>
     <t>monster_001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 본능적으로 몸을 틀면서
-땅에 떨어진 무기를 주웠다.
-괴물과 싸움을 시작했다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>괴물은 쓰러졌고 나는 한동안 그 자리에 서서
-괴물의 시체를 바라보았다.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -3118,73 +3083,6 @@
   </si>
   <si>
     <t>C1E4_go_out</t>
-  </si>
-  <si>
-    <t>나는 위습에게 말을 걸었다.
-"이젠 말 좀 해줄레?"
-위습은 천천히 말을 해왔다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"네가 머문 곳은 언제나 무너졌다..
-그건 우연이 아니었어."</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 표정이 굳어졌다.
-"그러니까… 그 모든게 나 때문이라고 말하고 싶은거야?"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"아니 너는 단지, 감추어진 진실의 중심에 있었을 뿐이야."</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"무슨 진실?"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"이 세계는 오래전부터 틀어져 있었어.
-누군가는 그 틀을 지키기 위해.
-누군가는 그 틀을 부수기 위해 움직여왔지."</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 위습을 노려보았다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"그래서 난 뭐지? 그 틀을 부수는 도구라도 된다는 거냐?"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"…..그건 너 자신이 선택해야 해."</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>위습은 천천히 앞으로 떠올랐고 바람은 고요했다.
-"하지만 기억해. 무너진 자리에는 반드시 무언가 숨겨져있어.
-그건, 너만이 찾을 수 있는 것들이야 
-그리고 그 조각들은…
-한 방향으로 향하고 있어."</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 한참을 멈춰 서서 생각했다.
-내가 걸어온 모든 폐허, 그 속에서 반복되어온 '끝'
-이번에도… 결국 혼자 남았다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>"…이젠 더 이상, 우연이라고는 생각 안 해."</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 마지막으로 뒤를 돌아보았고
-그리고 아주 천천히, 그리고 확실하게 걸음을 옮겼고
-위습은 그 앞길을 비춰주듯이 내 앞을 비춰줬다.
-소리 없이 묵묵히</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>C1E4_travel</t>
@@ -3414,10 +3312,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>[{"ID":"Effect_002","Code":"Weapon_003","Value":1}]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>MainScene_1_1_1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3519,8 +3413,372 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">2챕터 메인스토리 진행 테스트 1_12
+    <t>[{"ID":"Effect_003","Code":"Weapon_002","Value":1}]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 스토리로 넘어간다
 </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 손을 거두고 
+"…괜찮아."
+라고 작은 목소리로 중얼거렸다…
+나는 재빠르게 그를 살릴려고 벽돌을 치웠다..
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">하지만 그 소년은 숨이 점점 거칠어 지다가 
+결국 숨이 끊어져 버렸다.
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 본능적으로 뒤로 물러섰다.
+"…젠장…"
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">무기…
+손에 쥘 만한 무엇이든
+나는 주변을 둘러보다가 땅에 떨어진 무기를 발견했다.
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 본능적으로 몸을 틀면서
+땅에 떨어진 무기를 주웠다.
+괴물과 싸움을 시작했다.
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">괴물은 쓰러졌고 나는 한동안 그 자리에 서서
+괴물의 시체를 바라보았다.
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위습에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>걸었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이젠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해줄레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위습은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천천히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해왔다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"네가 머문 곳은 언제나 무너졌다..
+그건 우연이 아니었어."
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 표정이 굳어졌다.
+"그러니까… 그 모든게 나 때문이라고 말하고 싶은거야?"
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"아니 너는 단지, 감추어진 진실의 중심에 있었을 뿐이야."
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"무슨 진실?"
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"이 세계는 오래전부터 틀어져 있었어.
+누군가는 그 틀을 지키기 위해.
+누군가는 그 틀을 부수기 위해 움직여왔지."
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 위습을 노려보았다.
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"그래서 난 뭐지? 그 틀을 부수는 도구라도 된다는 거냐?"
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"…..그건 너 자신이 선택해야 해."
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">위습은 천천히 앞으로 떠올랐고 바람은 고요했다.
+"하지만 기억해. 무너진 자리에는 반드시 무언가 숨겨져있어.
+그건, 너만이 찾을 수 있는 것들이야 
+그리고 그 조각들은…
+한 방향으로 향하고 있어."
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 한참을 멈춰 서서 생각했다.
+내가 걸어온 모든 폐허, 그 속에서 반복되어온 '끝'
+이번에도… 결국 혼자 남았다.
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"…이젠 더 이상, 우연이라고는 생각 안 해."
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나는 마지막으로 뒤를 돌아보았고
+그리고 아주 천천히, 그리고 확실하게 걸음을 옮겼고
+위습은 그 앞길을 비춰주듯이 내 앞을 비춰줬다.
+소리 없이 묵묵히
+</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4111,15 +4369,15 @@
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -5006,7 +5264,7 @@
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -5043,7 +5301,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -5285,7 +5543,7 @@
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -5554,7 +5812,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -5592,10 +5850,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -5634,7 +5892,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -5673,7 +5931,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -5712,7 +5970,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -5751,7 +6009,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -5790,11 +6048,11 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -5831,7 +6089,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -5870,7 +6128,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -5909,7 +6167,7 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3"/>
@@ -5948,7 +6206,7 @@
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="3"/>
@@ -5987,17 +6245,17 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="3" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -6028,13 +6286,13 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H51" s="3"/>
       <c r="J51" s="3"/>
@@ -6070,13 +6328,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -6111,13 +6369,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -6154,7 +6412,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -6193,7 +6451,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -6232,7 +6490,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -6271,7 +6529,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -6310,7 +6568,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -6349,7 +6607,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -6388,11 +6646,11 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -6429,7 +6687,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -6468,7 +6726,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -6507,7 +6765,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -6546,7 +6804,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -6585,7 +6843,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -6624,7 +6882,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -6663,7 +6921,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -6702,7 +6960,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -6741,7 +6999,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -6780,7 +7038,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -6819,7 +7077,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -6858,7 +7116,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -6897,7 +7155,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -6936,7 +7194,7 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="3"/>
@@ -6975,7 +7233,7 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
@@ -7014,11 +7272,11 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="3" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -7055,7 +7313,7 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
@@ -7094,15 +7352,15 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="3" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -7140,7 +7398,7 @@
         <v>MainScene_1_5_4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="3"/>
@@ -7182,7 +7440,7 @@
         <v>MainScene_1_5_5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="3"/>
@@ -7221,7 +7479,7 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="3"/>
@@ -7260,7 +7518,7 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="3"/>
@@ -7299,7 +7557,7 @@
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="3"/>
@@ -7338,7 +7596,7 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="3"/>
@@ -7377,7 +7635,7 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="3"/>
@@ -7416,7 +7674,7 @@
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="3"/>
@@ -7455,7 +7713,7 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="3"/>
@@ -7494,7 +7752,7 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="3"/>
@@ -7533,7 +7791,7 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="3"/>
@@ -7572,7 +7830,7 @@
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="3"/>
@@ -7611,7 +7869,7 @@
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="3"/>
@@ -7650,7 +7908,7 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="3"/>
@@ -7689,10 +7947,12 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="G93" s="5"/>
-      <c r="H93" s="3"/>
+      <c r="H93" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -7728,7 +7988,7 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="3"/>
@@ -33230,7 +33490,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="9" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -33251,7 +33511,7 @@
         <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>48</v>
@@ -33298,10 +33558,10 @@
       </c>
       <c r="G2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -33379,7 +33639,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -33584,7 +33844,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -33789,7 +34049,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -33911,7 +34171,7 @@
         <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -34073,7 +34333,7 @@
         <v>76</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -34110,7 +34370,7 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>30</v>
@@ -34236,7 +34496,7 @@
         <v>72</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="5"/>
@@ -34274,7 +34534,7 @@
         <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>30</v>
@@ -34361,7 +34621,7 @@
         <v>70</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -34443,7 +34703,7 @@
         <v>69</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -34522,7 +34782,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
@@ -34563,10 +34823,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -34604,7 +34864,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>55</v>
@@ -34630,7 +34890,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" spans="1:26" ht="99">
+    <row r="35" spans="1:26" ht="82.5">
       <c r="A35" s="7">
         <v>1</v>
       </c>
@@ -34645,10 +34905,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>105</v>
+        <v>219</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -34686,7 +34946,7 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>55</v>
@@ -34712,7 +34972,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="33">
+    <row r="37" spans="1:26" ht="49.5">
       <c r="A37" s="7">
         <v>1</v>
       </c>
@@ -34727,10 +34987,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>106</v>
+        <v>220</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -34935,7 +35195,7 @@
         <v>88</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -35095,7 +35355,7 @@
         <v>MainScript_1_2_20</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>30</v>
@@ -35138,7 +35398,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>55</v>
@@ -35179,7 +35439,7 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>30</v>
@@ -35205,7 +35465,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" spans="1:26" ht="33">
+    <row r="49" spans="1:26" ht="49.5">
       <c r="A49" s="7">
         <v>1</v>
       </c>
@@ -35220,7 +35480,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -35246,7 +35506,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" spans="1:26" ht="49.5">
+    <row r="50" spans="1:26" ht="66">
       <c r="A50" s="7">
         <v>1</v>
       </c>
@@ -35261,7 +35521,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -35302,7 +35562,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>30</v>
@@ -35343,7 +35603,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>30</v>
@@ -35384,7 +35644,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>30</v>
@@ -35410,7 +35670,7 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54" spans="1:26" ht="49.5">
+    <row r="54" spans="1:26" ht="66">
       <c r="A54" s="7">
         <v>1</v>
       </c>
@@ -35425,7 +35685,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>123</v>
+        <v>223</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>30</v>
@@ -35466,10 +35726,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -35507,7 +35767,7 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>55</v>
@@ -35533,7 +35793,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="33">
+    <row r="57" spans="1:26" ht="49.5">
       <c r="A57" s="7">
         <v>1</v>
       </c>
@@ -35548,7 +35808,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -35589,7 +35849,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>30</v>
@@ -35630,7 +35890,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>30</v>
@@ -35671,7 +35931,7 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>30</v>
@@ -35712,7 +35972,7 @@
         <v>MainScript_1_3_15</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>30</v>
@@ -35755,7 +36015,7 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>55</v>
@@ -35781,7 +36041,7 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" spans="1:26" ht="45">
+    <row r="63" spans="1:26" ht="66">
       <c r="A63" s="7">
         <v>1</v>
       </c>
@@ -35796,7 +36056,7 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -35822,7 +36082,7 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64" spans="1:26" ht="33">
+    <row r="64" spans="1:26" ht="49.5">
       <c r="A64" s="7">
         <v>1</v>
       </c>
@@ -35837,7 +36097,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -35863,7 +36123,7 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65" spans="1:26" ht="33">
+    <row r="65" spans="1:26" ht="49.5">
       <c r="A65" s="7">
         <v>1</v>
       </c>
@@ -35878,7 +36138,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>138</v>
+        <v>227</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -35904,7 +36164,7 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66" spans="1:26" ht="16.5">
+    <row r="66" spans="1:26" ht="33">
       <c r="A66" s="7">
         <v>1</v>
       </c>
@@ -35918,11 +36178,11 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_4_5</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>139</v>
+      <c r="E66" s="16" t="s">
+        <v>228</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -35945,7 +36205,7 @@
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
     </row>
-    <row r="67" spans="1:26" ht="16.5">
+    <row r="67" spans="1:26" ht="33">
       <c r="A67" s="7">
         <v>1</v>
       </c>
@@ -35959,8 +36219,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_4_6</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>140</v>
+      <c r="E67" s="16" t="s">
+        <v>229</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -35986,7 +36246,7 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68" spans="1:26" ht="49.5">
+    <row r="68" spans="1:26" ht="66">
       <c r="A68" s="7">
         <v>1</v>
       </c>
@@ -36001,7 +36261,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -36027,7 +36287,7 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69" spans="1:26" ht="16.5">
+    <row r="69" spans="1:26" ht="33">
       <c r="A69" s="7">
         <v>1</v>
       </c>
@@ -36042,7 +36302,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -36068,7 +36328,7 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" spans="1:26" ht="16.5">
+    <row r="70" spans="1:26" ht="33">
       <c r="A70" s="7">
         <v>1</v>
       </c>
@@ -36082,8 +36342,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_4_9</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>143</v>
+      <c r="E70" s="16" t="s">
+        <v>232</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -36109,7 +36369,7 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71" spans="1:26" ht="16.5">
+    <row r="71" spans="1:26" ht="33">
       <c r="A71" s="7">
         <v>1</v>
       </c>
@@ -36123,8 +36383,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_4_10</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>144</v>
+      <c r="E71" s="16" t="s">
+        <v>233</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -36150,7 +36410,7 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
     </row>
-    <row r="72" spans="1:26" ht="82.5">
+    <row r="72" spans="1:26" ht="99">
       <c r="A72" s="7">
         <v>1</v>
       </c>
@@ -36165,7 +36425,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -36191,7 +36451,7 @@
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
     </row>
-    <row r="73" spans="1:26" ht="66">
+    <row r="73" spans="1:26" ht="82.5">
       <c r="A73" s="7">
         <v>1</v>
       </c>
@@ -36206,7 +36466,7 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>30</v>
@@ -36232,7 +36492,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" spans="1:26" ht="16.5">
+    <row r="74" spans="1:26" ht="33">
       <c r="A74" s="7">
         <v>1</v>
       </c>
@@ -36246,11 +36506,11 @@
         <f t="shared" si="1"/>
         <v>MainScript_1_4_13</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>147</v>
+      <c r="E74" s="16" t="s">
+        <v>236</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -36288,7 +36548,7 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>55</v>
@@ -36314,7 +36574,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" spans="1:26" ht="66">
+    <row r="76" spans="1:26" ht="82.5">
       <c r="A76" s="7">
         <v>1</v>
       </c>
@@ -36329,7 +36589,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>148</v>
+        <v>237</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -36370,7 +36630,7 @@
         <v>MainScript_1_4_16</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>30</v>
@@ -36413,7 +36673,7 @@
         <v>MainScript_1_5_1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>30</v>
@@ -36454,7 +36714,7 @@
         <v>MainScript_1_5_2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>30</v>
@@ -36495,7 +36755,7 @@
         <v>MainScript_1_5_3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>30</v>
@@ -36540,10 +36800,10 @@
         <v>MainScript_1_5_4</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -36581,7 +36841,7 @@
         <v>MainScript_1_5_5</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>30</v>
@@ -36626,7 +36886,7 @@
         <v>MainScript_2_1_1</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>30</v>
@@ -36667,7 +36927,7 @@
         <v>MainScript_2_1_2</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>30</v>
@@ -36708,7 +36968,7 @@
         <v>MainScript_2_1_3</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>30</v>
@@ -36749,7 +37009,7 @@
         <v>MainScript_2_1_4</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>30</v>
@@ -36790,7 +37050,7 @@
         <v>MainScript_2_1_5</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>30</v>
@@ -36831,7 +37091,7 @@
         <v>MainScript_2_1_6</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>30</v>
@@ -36872,7 +37132,7 @@
         <v>MainScript_2_1_7</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>30</v>
@@ -36913,7 +37173,7 @@
         <v>MainScript_2_1_8</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>30</v>
@@ -36954,7 +37214,7 @@
         <v>MainScript_2_1_9</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>30</v>
@@ -36995,7 +37255,7 @@
         <v>MainScript_2_1_10</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>30</v>
@@ -37036,7 +37296,7 @@
         <v>MainScript_2_1_11</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>30</v>
@@ -37077,7 +37337,7 @@
         <v>MainScript_2_1_12</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>30</v>
@@ -63925,7 +64185,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>27</v>
@@ -63933,34 +64193,34 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C4" s="6"/>
     </row>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60ade03816ecf377/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{1AC8DCC3-BAE6-4225-9F25-1268A604BEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88422E6-1AB1-41CD-A7F4-75067BFC177B}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{E8CAFB78-27A3-4419-9B02-080EB16180A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3718117B-38D2-407D-962A-736685815190}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="6936" yWindow="4032" windowWidth="22200" windowHeight="11988" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -952,971 +952,6 @@
   </si>
   <si>
     <t>NEXTLOSE</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>평온한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>마을인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>라노스마을_x000D_
-해가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>높이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>떠올랐고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>바람은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>따뜻했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">._x000D_
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>조용한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>속에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>오늘도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>변함없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>숨을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>죽이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>살아가고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">._x000D_
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>마을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사람들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>특별히</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>따돌리진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>않았다_x000D_
-하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>당신을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>향한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시선에는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>어딘가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>설명하기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>어려운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>거리감이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>배어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">._x000D_
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>그게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>편했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">._x000D_
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>누구와도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>엮이지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>않으면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>누군가를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>잃는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>없을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>테니까</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.._x000D_
-</t>
-    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2881,12 +1916,6 @@
     <t xml:space="preserve">나는 아무 말 없이 그 빛을 바라보았다.
 나는 천천히 일어났고
 푸른 위습은 앞서 나아가듯 떠올랐다.
-</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">"사람은 아니고"
-빛은 멈추었고 천천히 아주 낮고 부드러운 목소리로 말했다.
 </t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -4030,11 +3059,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>그러던 중 숲에서 자라난 무성한 나무들 사이에서 괴물이 튀어나왔다
-더 이상 인간이라고 부르기 어려운 형체였다..</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>C1E3_monster</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -4526,6 +3550,1136 @@
     <t>C1E4_travel</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수도에서 떨어진 변방의 평온한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시골마을인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라노스마을
+해가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠올랐고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조용한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변함없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살아가고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불빛이 날아다녀..?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빛은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멈추었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천천히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낮고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부드러운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목소리로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마을밖 숲에서 걷는 도중 자라난 무성한 나무들 사이에 사람을 닮은 검은 형체가 기어다니고 있었다.
+조심스럽게 다가가서 확인해보았지만 그것은 더 이상 인간이라고 부르기 어려운 형체였다..</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특별히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따돌리진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았다
+하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당신을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시선에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어딘가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어려운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거리감이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그러나 나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그것이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>편했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누구와도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엮이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누군가를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잃는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테니까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">..
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -4833,10 +4987,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4854,10 +5008,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5146,19 +5296,19 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -5810,7 +5960,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="3"/>
@@ -5849,7 +5999,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="3"/>
@@ -5888,7 +6038,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="3"/>
@@ -5927,7 +6077,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5965,7 +6115,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -6002,7 +6152,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -6041,11 +6191,11 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -6082,7 +6232,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -6121,7 +6271,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -6160,7 +6310,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -6199,7 +6349,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -6238,7 +6388,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -6277,7 +6427,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3"/>
@@ -6316,15 +6466,15 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -6359,7 +6509,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -6398,7 +6548,7 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -6437,7 +6587,7 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -6476,7 +6626,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -6515,7 +6665,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -6554,7 +6704,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -6593,7 +6743,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -6631,10 +6781,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -6673,7 +6823,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -6712,7 +6862,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -6751,7 +6901,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -6790,7 +6940,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -6829,11 +6979,11 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -6870,7 +7020,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -6909,7 +7059,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -6948,7 +7098,7 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3"/>
@@ -6987,7 +7137,7 @@
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="3"/>
@@ -7026,17 +7176,17 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -7067,13 +7217,13 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3"/>
       <c r="J51" s="3"/>
@@ -7109,13 +7259,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -7150,13 +7300,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -7193,7 +7343,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -7232,7 +7382,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -7271,7 +7421,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -7310,7 +7460,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -7349,7 +7499,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -7388,7 +7538,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -7427,11 +7577,11 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -7468,7 +7618,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -7507,7 +7657,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -7546,7 +7696,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -7585,7 +7735,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -7624,7 +7774,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -7663,7 +7813,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -7702,7 +7852,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -7741,7 +7891,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -7780,7 +7930,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -7819,7 +7969,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -7858,7 +8008,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -7897,7 +8047,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -7936,7 +8086,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -7975,7 +8125,7 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="3"/>
@@ -8014,7 +8164,7 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
@@ -8053,11 +8203,11 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -8094,7 +8244,7 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
@@ -8133,15 +8283,15 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -8179,7 +8329,7 @@
         <v>MainScene_1_5_4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="3"/>
@@ -8221,7 +8371,7 @@
         <v>MainScene_1_5_5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="3"/>
@@ -8260,7 +8410,7 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="3"/>
@@ -8299,7 +8449,7 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="3"/>
@@ -8338,7 +8488,7 @@
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="3"/>
@@ -8377,7 +8527,7 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="3"/>
@@ -8416,7 +8566,7 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="3"/>
@@ -8455,7 +8605,7 @@
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="3"/>
@@ -8494,7 +8644,7 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="3"/>
@@ -8533,7 +8683,7 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="3"/>
@@ -8572,7 +8722,7 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="3"/>
@@ -8611,7 +8761,7 @@
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="3"/>
@@ -8650,7 +8800,7 @@
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="3"/>
@@ -8689,7 +8839,7 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="3"/>
@@ -8728,11 +8878,11 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
@@ -8769,7 +8919,7 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="3"/>
@@ -34271,7 +34421,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="17.399999999999999">
       <c r="A1" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -34292,7 +34442,7 @@
         <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>48</v>
@@ -34332,17 +34482,17 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -34361,7 +34511,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="72">
+    <row r="3" spans="1:26" ht="87">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -34376,7 +34526,7 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>30</v>
@@ -34402,7 +34552,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="86.4">
+    <row r="4" spans="1:26" ht="104.4">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -34417,10 +34567,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -34458,10 +34608,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -34499,7 +34649,7 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>30</v>
@@ -34540,7 +34690,7 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>30</v>
@@ -34581,7 +34731,7 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>30</v>
@@ -34625,7 +34775,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -34830,7 +34980,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -34868,10 +35018,10 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -34909,7 +35059,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>30</v>
@@ -34949,10 +35099,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -34989,7 +35139,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>30</v>
@@ -35029,10 +35179,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -35055,7 +35205,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="43.2">
+    <row r="20" spans="1:26" ht="52.2">
       <c r="A20" s="7">
         <v>1</v>
       </c>
@@ -35070,7 +35220,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>30</v>
@@ -35111,10 +35261,10 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -35151,7 +35301,7 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>30</v>
@@ -35192,7 +35342,7 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>30</v>
@@ -35233,7 +35383,7 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>30</v>
@@ -35274,10 +35424,10 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="5"/>
@@ -35315,13 +35465,13 @@
         <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -35358,7 +35508,7 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>30</v>
@@ -35399,10 +35549,10 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -35440,10 +35590,10 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -35481,10 +35631,10 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -35522,10 +35672,10 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -35563,7 +35713,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
@@ -35604,10 +35754,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -35645,10 +35795,10 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -35686,10 +35836,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -35727,10 +35877,10 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -35768,10 +35918,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -35809,10 +35959,10 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -35850,7 +36000,7 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>30</v>
@@ -35891,7 +36041,7 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
@@ -35932,7 +36082,7 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>30</v>
@@ -35973,10 +36123,10 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -36014,10 +36164,10 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -36054,7 +36204,7 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>30</v>
@@ -36095,7 +36245,7 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>30</v>
@@ -36136,13 +36286,13 @@
         <v>MainScript_1_2_20</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -36164,7 +36314,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" ht="34.799999999999997">
+    <row r="47" spans="1:26" ht="69.599999999999994">
       <c r="A47" s="7">
         <v>1</v>
       </c>
@@ -36179,7 +36329,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>30</v>
@@ -36220,10 +36370,10 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -36261,7 +36411,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -36302,7 +36452,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -36343,7 +36493,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>30</v>
@@ -36384,7 +36534,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>30</v>
@@ -36425,7 +36575,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>30</v>
@@ -36466,7 +36616,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>30</v>
@@ -36507,10 +36657,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -36548,10 +36698,10 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -36589,7 +36739,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -36630,7 +36780,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>30</v>
@@ -36671,7 +36821,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>30</v>
@@ -36712,7 +36862,7 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>30</v>
@@ -36753,13 +36903,13 @@
         <v>MainScript_1_3_15</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -36795,8 +36945,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_4_1</v>
       </c>
-      <c r="E62" s="29" t="s">
-        <v>220</v>
+      <c r="E62" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>30</v>
@@ -36836,8 +36986,8 @@
         <f t="shared" si="0"/>
         <v>MainScript_1_4_2</v>
       </c>
-      <c r="E63" s="30" t="s">
-        <v>221</v>
+      <c r="E63" s="29" t="s">
+        <v>217</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -36878,7 +37028,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -36919,7 +37069,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -36960,10 +37110,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -37001,7 +37151,7 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -37042,7 +37192,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -37083,7 +37233,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -37124,7 +37274,7 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -37165,7 +37315,7 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -37206,7 +37356,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -37247,10 +37397,10 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -37288,10 +37438,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -37329,10 +37479,10 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -37370,7 +37520,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -37411,13 +37561,13 @@
         <v>MainScript_1_4_16</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -37454,7 +37604,7 @@
         <v>MainScript_1_5_1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>30</v>
@@ -37495,7 +37645,7 @@
         <v>MainScript_1_5_2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>30</v>
@@ -37536,16 +37686,16 @@
         <v>MainScript_1_5_3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -37581,10 +37731,10 @@
         <v>MainScript_1_5_4</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -37622,16 +37772,16 @@
         <v>MainScript_1_5_5</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -37667,7 +37817,7 @@
         <v>MainScript_2_1_1</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>30</v>
@@ -37708,7 +37858,7 @@
         <v>MainScript_2_1_2</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>30</v>
@@ -37749,7 +37899,7 @@
         <v>MainScript_2_1_3</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>30</v>
@@ -37790,7 +37940,7 @@
         <v>MainScript_2_1_4</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>30</v>
@@ -37831,7 +37981,7 @@
         <v>MainScript_2_1_5</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>30</v>
@@ -37872,7 +38022,7 @@
         <v>MainScript_2_1_6</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>30</v>
@@ -37913,7 +38063,7 @@
         <v>MainScript_2_1_7</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>30</v>
@@ -37954,7 +38104,7 @@
         <v>MainScript_2_1_8</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>30</v>
@@ -37995,7 +38145,7 @@
         <v>MainScript_2_1_9</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>30</v>
@@ -38036,7 +38186,7 @@
         <v>MainScript_2_1_10</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>30</v>
@@ -38077,7 +38227,7 @@
         <v>MainScript_2_1_11</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>30</v>
@@ -38118,16 +38268,16 @@
         <v>MainScript_2_1_12</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -63922,19 +64072,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -64966,7 +65116,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>27</v>
@@ -64974,34 +65124,34 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>157</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>160</v>
       </c>
       <c r="C4" s="6"/>
     </row>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60ade03816ecf377/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{E8CAFB78-27A3-4419-9B02-080EB16180A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3718117B-38D2-407D-962A-736685815190}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E130E280-0607-452A-9E79-C841259C9BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6936" yWindow="4032" windowWidth="22200" windowHeight="11988" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="4695" yWindow="2010" windowWidth="24255" windowHeight="18210" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="237">
   <si>
     <t>Chapter_Index</t>
   </si>
@@ -2404,11 +2404,6 @@
   </si>
   <si>
     <t>[{"ID":"Effect_003","Code":"Weapon_002","Value":1}]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">다음 스토리로 넘어간다
-</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -5209,21 +5204,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1003"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.44140625" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="20.44140625" customWidth="1"/>
-    <col min="14" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" customWidth="1"/>
+    <col min="14" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
@@ -5280,7 +5275,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" ht="17.399999999999999">
+    <row r="2" spans="1:26" ht="16.5">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -6621,7 +6616,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" ref="D36:D94" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <f t="shared" ref="D36:D95" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
@@ -34405,21 +34400,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1014"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" customWidth="1"/>
-    <col min="5" max="5" width="65.5546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
+    <col min="5" max="5" width="65.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="59.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="59.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="17.399999999999999">
+    <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="9" t="s">
         <v>190</v>
       </c>
@@ -34467,7 +34462,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" ht="17.399999999999999">
+    <row r="2" spans="1:26" ht="16.5">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -34511,7 +34506,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="87">
+    <row r="3" spans="1:26" ht="82.5">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -34526,7 +34521,7 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>30</v>
@@ -34552,7 +34547,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" spans="1:26" ht="104.4">
+    <row r="4" spans="1:26" ht="99">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -34567,7 +34562,7 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>151</v>
@@ -34593,7 +34588,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" spans="1:26" ht="17.399999999999999">
+    <row r="5" spans="1:26" ht="16.5">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -34634,7 +34629,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" spans="1:26" ht="57.6">
+    <row r="6" spans="1:26" ht="60">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -34675,7 +34670,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="28.8">
+    <row r="7" spans="1:26" ht="30">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -34716,7 +34711,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="28.8">
+    <row r="8" spans="1:26" ht="30">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -34757,7 +34752,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="28.8">
+    <row r="9" spans="1:26" ht="30">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -34798,7 +34793,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" ht="43.2">
+    <row r="10" spans="1:26" ht="45">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -34839,7 +34834,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="72">
+    <row r="11" spans="1:26" ht="75">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -34880,7 +34875,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" ht="43.2">
+    <row r="12" spans="1:26" ht="45">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -34921,7 +34916,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" ht="43.2">
+    <row r="13" spans="1:26" ht="45">
       <c r="A13" s="7">
         <v>1</v>
       </c>
@@ -34962,7 +34957,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="69.599999999999994">
+    <row r="14" spans="1:26" ht="66">
       <c r="A14" s="7">
         <v>1</v>
       </c>
@@ -35003,7 +34998,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="17.399999999999999">
+    <row r="15" spans="1:26" ht="16.5">
       <c r="A15" s="7">
         <v>1</v>
       </c>
@@ -35044,7 +35039,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" ht="121.8">
+    <row r="16" spans="1:26" ht="115.5">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -35084,7 +35079,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="28.8">
+    <row r="17" spans="1:26" ht="30">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -35124,7 +35119,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="69.599999999999994">
+    <row r="18" spans="1:26" ht="66">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -35139,7 +35134,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>30</v>
@@ -35164,7 +35159,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="17.399999999999999">
+    <row r="19" spans="1:26" ht="16.5">
       <c r="A19" s="7">
         <v>1</v>
       </c>
@@ -35179,7 +35174,7 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>53</v>
@@ -35205,7 +35200,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="52.2">
+    <row r="20" spans="1:26" ht="49.5">
       <c r="A20" s="7">
         <v>1</v>
       </c>
@@ -35220,7 +35215,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>30</v>
@@ -35246,7 +35241,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="57.6">
+    <row r="21" spans="1:26" ht="60">
       <c r="A21" s="7">
         <v>1</v>
       </c>
@@ -35286,7 +35281,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" ht="28.8">
+    <row r="22" spans="1:26" ht="30">
       <c r="A22" s="7">
         <v>1</v>
       </c>
@@ -35327,7 +35322,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="43.2">
+    <row r="23" spans="1:26" ht="45">
       <c r="A23" s="7">
         <v>1</v>
       </c>
@@ -35368,7 +35363,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" ht="69.599999999999994">
+    <row r="24" spans="1:26" ht="66">
       <c r="A24" s="7">
         <v>1</v>
       </c>
@@ -35409,7 +35404,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" spans="1:26" ht="52.2">
+    <row r="25" spans="1:26" ht="49.5">
       <c r="A25" s="7">
         <v>1</v>
       </c>
@@ -35450,7 +35445,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="17.399999999999999">
+    <row r="26" spans="1:26" ht="16.5">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -35493,7 +35488,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="69.599999999999994">
+    <row r="27" spans="1:26" ht="66">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -35534,7 +35529,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="52.2">
+    <row r="28" spans="1:26" ht="49.5">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -35575,7 +35570,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="17.399999999999999">
+    <row r="29" spans="1:26" ht="16.5">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -35616,7 +35611,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="87">
+    <row r="30" spans="1:26" ht="82.5">
       <c r="A30" s="7">
         <v>1</v>
       </c>
@@ -35657,7 +35652,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="17.399999999999999">
+    <row r="31" spans="1:26" ht="16.5">
       <c r="A31" s="7">
         <v>1</v>
       </c>
@@ -35672,7 +35667,7 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>53</v>
@@ -35698,7 +35693,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="87">
+    <row r="32" spans="1:26" ht="82.5">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -35739,7 +35734,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="17.399999999999999">
+    <row r="33" spans="1:26" ht="16.5">
       <c r="A33" s="7">
         <v>1</v>
       </c>
@@ -35780,7 +35775,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="1:26" ht="17.399999999999999">
+    <row r="34" spans="1:26" ht="16.5">
       <c r="A34" s="7">
         <v>1</v>
       </c>
@@ -35795,7 +35790,7 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>53</v>
@@ -35821,7 +35816,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" spans="1:26" ht="87">
+    <row r="35" spans="1:26" ht="82.5">
       <c r="A35" s="7">
         <v>1</v>
       </c>
@@ -35836,7 +35831,7 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>151</v>
@@ -35862,7 +35857,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" spans="1:26" ht="17.399999999999999">
+    <row r="36" spans="1:26" ht="16.5">
       <c r="A36" s="7">
         <v>1</v>
       </c>
@@ -35877,7 +35872,7 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>53</v>
@@ -35903,7 +35898,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="52.2">
+    <row r="37" spans="1:26" ht="49.5">
       <c r="A37" s="7">
         <v>1</v>
       </c>
@@ -35918,7 +35913,7 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>151</v>
@@ -35944,7 +35939,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" spans="1:26" ht="17.399999999999999">
+    <row r="38" spans="1:26" ht="16.5">
       <c r="A38" s="7">
         <v>1</v>
       </c>
@@ -35959,7 +35954,7 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>53</v>
@@ -35985,7 +35980,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" spans="1:26" ht="87">
+    <row r="39" spans="1:26" ht="82.5">
       <c r="A39" s="7">
         <v>1</v>
       </c>
@@ -36026,7 +36021,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" spans="1:26" ht="52.2">
+    <row r="40" spans="1:26" ht="49.5">
       <c r="A40" s="7">
         <v>1</v>
       </c>
@@ -36067,7 +36062,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" spans="1:26" ht="17.399999999999999">
+    <row r="41" spans="1:26" ht="16.5">
       <c r="A41" s="7">
         <v>1</v>
       </c>
@@ -36108,7 +36103,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" spans="1:26" ht="34.799999999999997">
+    <row r="42" spans="1:26" ht="33">
       <c r="A42" s="7">
         <v>1</v>
       </c>
@@ -36149,7 +36144,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43" spans="1:26" ht="17.399999999999999">
+    <row r="43" spans="1:26" ht="16.5">
       <c r="A43" s="7">
         <v>1</v>
       </c>
@@ -36189,7 +36184,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" spans="1:26" ht="52.2">
+    <row r="44" spans="1:26" ht="49.5">
       <c r="A44" s="7">
         <v>1</v>
       </c>
@@ -36230,7 +36225,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" spans="1:26" ht="52.2">
+    <row r="45" spans="1:26" ht="49.5">
       <c r="A45" s="7">
         <v>1</v>
       </c>
@@ -36271,7 +36266,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" ht="17.399999999999999">
+    <row r="46" spans="1:26" ht="16.5">
       <c r="A46" s="7">
         <v>1</v>
       </c>
@@ -36314,7 +36309,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" ht="69.599999999999994">
+    <row r="47" spans="1:26" ht="66">
       <c r="A47" s="7">
         <v>1</v>
       </c>
@@ -36329,7 +36324,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>30</v>
@@ -36355,7 +36350,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" spans="1:26" ht="17.399999999999999">
+    <row r="48" spans="1:26" ht="16.5">
       <c r="A48" s="7">
         <v>1</v>
       </c>
@@ -36370,7 +36365,7 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>53</v>
@@ -36396,7 +36391,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" spans="1:26" ht="52.2">
+    <row r="49" spans="1:26" ht="49.5">
       <c r="A49" s="7">
         <v>1</v>
       </c>
@@ -36411,7 +36406,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -36437,7 +36432,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" spans="1:26" ht="69.599999999999994">
+    <row r="50" spans="1:26" ht="66">
       <c r="A50" s="7">
         <v>1</v>
       </c>
@@ -36452,7 +36447,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -36478,7 +36473,7 @@
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
     </row>
-    <row r="51" spans="1:26" ht="17.399999999999999">
+    <row r="51" spans="1:26" ht="16.5">
       <c r="A51" s="7">
         <v>1</v>
       </c>
@@ -36519,7 +36514,7 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
     </row>
-    <row r="52" spans="1:26" ht="17.399999999999999">
+    <row r="52" spans="1:26" ht="16.5">
       <c r="A52" s="7">
         <v>1</v>
       </c>
@@ -36560,7 +36555,7 @@
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
     </row>
-    <row r="53" spans="1:26" ht="17.399999999999999">
+    <row r="53" spans="1:26" ht="16.5">
       <c r="A53" s="7">
         <v>1</v>
       </c>
@@ -36601,7 +36596,7 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54" spans="1:26" ht="69.599999999999994">
+    <row r="54" spans="1:26" ht="66">
       <c r="A54" s="7">
         <v>1</v>
       </c>
@@ -36616,7 +36611,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>30</v>
@@ -36642,7 +36637,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" spans="1:26" ht="17.399999999999999">
+    <row r="55" spans="1:26" ht="16.5">
       <c r="A55" s="7">
         <v>1</v>
       </c>
@@ -36683,7 +36678,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" spans="1:26" ht="17.399999999999999">
+    <row r="56" spans="1:26" ht="16.5">
       <c r="A56" s="7">
         <v>1</v>
       </c>
@@ -36698,7 +36693,7 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>53</v>
@@ -36724,7 +36719,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="52.2">
+    <row r="57" spans="1:26" ht="49.5">
       <c r="A57" s="7">
         <v>1</v>
       </c>
@@ -36739,7 +36734,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -36765,7 +36760,7 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58" spans="1:26" ht="69.599999999999994">
+    <row r="58" spans="1:26" ht="66">
       <c r="A58" s="7">
         <v>1</v>
       </c>
@@ -36806,7 +36801,7 @@
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
     </row>
-    <row r="59" spans="1:26" ht="52.2">
+    <row r="59" spans="1:26" ht="49.5">
       <c r="A59" s="7">
         <v>1</v>
       </c>
@@ -36847,7 +36842,7 @@
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
     </row>
-    <row r="60" spans="1:26" ht="17.399999999999999">
+    <row r="60" spans="1:26" ht="16.5">
       <c r="A60" s="7">
         <v>1</v>
       </c>
@@ -36888,7 +36883,7 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61" spans="1:26" ht="17.399999999999999">
+    <row r="61" spans="1:26" ht="16.5">
       <c r="A61" s="7">
         <v>1</v>
       </c>
@@ -36931,7 +36926,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" spans="1:26" ht="52.2">
+    <row r="62" spans="1:26" ht="49.5">
       <c r="A62" s="7">
         <v>1</v>
       </c>
@@ -36946,7 +36941,7 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>30</v>
@@ -36972,7 +36967,7 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" spans="1:26" ht="34.799999999999997">
+    <row r="63" spans="1:26" ht="33">
       <c r="A63" s="7">
         <v>1</v>
       </c>
@@ -36987,7 +36982,7 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -37013,7 +37008,7 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64" spans="1:26" ht="34.799999999999997">
+    <row r="64" spans="1:26" ht="33">
       <c r="A64" s="7">
         <v>1</v>
       </c>
@@ -37028,7 +37023,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -37054,7 +37049,7 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65" spans="1:26" ht="17.399999999999999">
+    <row r="65" spans="1:26" ht="16.5">
       <c r="A65" s="7">
         <v>1</v>
       </c>
@@ -37069,7 +37064,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -37095,7 +37090,7 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66" spans="1:26" ht="17.399999999999999">
+    <row r="66" spans="1:26" ht="16.5">
       <c r="A66" s="7">
         <v>1</v>
       </c>
@@ -37110,7 +37105,7 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>151</v>
@@ -37136,7 +37131,7 @@
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
     </row>
-    <row r="67" spans="1:26" ht="69.599999999999994">
+    <row r="67" spans="1:26" ht="66">
       <c r="A67" s="7">
         <v>1</v>
       </c>
@@ -37151,7 +37146,7 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -37177,7 +37172,7 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68" spans="1:26" ht="17.399999999999999">
+    <row r="68" spans="1:26" ht="16.5">
       <c r="A68" s="7">
         <v>1</v>
       </c>
@@ -37192,7 +37187,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -37218,7 +37213,7 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69" spans="1:26" ht="17.399999999999999">
+    <row r="69" spans="1:26" ht="16.5">
       <c r="A69" s="7">
         <v>1</v>
       </c>
@@ -37233,7 +37228,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -37259,7 +37254,7 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" spans="1:26" ht="17.399999999999999">
+    <row r="70" spans="1:26" ht="16.5">
       <c r="A70" s="7">
         <v>1</v>
       </c>
@@ -37274,7 +37269,7 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -37300,7 +37295,7 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71" spans="1:26" ht="87">
+    <row r="71" spans="1:26" ht="82.5">
       <c r="A71" s="7">
         <v>1</v>
       </c>
@@ -37315,7 +37310,7 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -37341,7 +37336,7 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
     </row>
-    <row r="72" spans="1:26" ht="69.599999999999994">
+    <row r="72" spans="1:26" ht="66">
       <c r="A72" s="7">
         <v>1</v>
       </c>
@@ -37356,7 +37351,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -37382,7 +37377,7 @@
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
     </row>
-    <row r="73" spans="1:26" ht="17.399999999999999">
+    <row r="73" spans="1:26" ht="16.5">
       <c r="A73" s="7">
         <v>1</v>
       </c>
@@ -37397,7 +37392,7 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>53</v>
@@ -37423,7 +37418,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" spans="1:26" ht="34.799999999999997">
+    <row r="74" spans="1:26" ht="33">
       <c r="A74" s="7">
         <v>1</v>
       </c>
@@ -37438,7 +37433,7 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>151</v>
@@ -37464,7 +37459,7 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75" spans="1:26" ht="17.399999999999999">
+    <row r="75" spans="1:26" ht="16.5">
       <c r="A75" s="7">
         <v>1</v>
       </c>
@@ -37479,7 +37474,7 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>53</v>
@@ -37505,7 +37500,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" spans="1:26" ht="87">
+    <row r="76" spans="1:26" ht="82.5">
       <c r="A76" s="7">
         <v>1</v>
       </c>
@@ -37520,7 +37515,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -37546,7 +37541,7 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
     </row>
-    <row r="77" spans="1:26" ht="17.399999999999999">
+    <row r="77" spans="1:26" ht="16.5">
       <c r="A77" s="7">
         <v>1</v>
       </c>
@@ -37589,7 +37584,7 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
     </row>
-    <row r="78" spans="1:26" ht="17.399999999999999">
+    <row r="78" spans="1:26" ht="16.5">
       <c r="A78" s="7">
         <v>1</v>
       </c>
@@ -37630,7 +37625,7 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
     </row>
-    <row r="79" spans="1:26" ht="17.399999999999999">
+    <row r="79" spans="1:26" ht="16.5">
       <c r="A79" s="7">
         <v>1</v>
       </c>
@@ -37671,7 +37666,7 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
     </row>
-    <row r="80" spans="1:26" ht="17.399999999999999">
+    <row r="80" spans="1:26" ht="16.5">
       <c r="A80" s="7">
         <v>1</v>
       </c>
@@ -37716,7 +37711,7 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
     </row>
-    <row r="81" spans="1:26" ht="17.399999999999999">
+    <row r="81" spans="1:26" ht="16.5">
       <c r="A81" s="7">
         <v>1</v>
       </c>
@@ -37757,7 +37752,7 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
     </row>
-    <row r="82" spans="1:26" ht="17.399999999999999">
+    <row r="82" spans="1:26" ht="16.5">
       <c r="A82" s="7">
         <v>1</v>
       </c>
@@ -37802,7 +37797,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83" spans="1:26" ht="34.799999999999997">
+    <row r="83" spans="1:26" ht="33">
       <c r="A83" s="7">
         <v>2</v>
       </c>
@@ -37843,7 +37838,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84" spans="1:26" ht="34.799999999999997">
+    <row r="84" spans="1:26" ht="33">
       <c r="A84" s="7">
         <v>2</v>
       </c>
@@ -37884,7 +37879,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85" spans="1:26" ht="34.799999999999997">
+    <row r="85" spans="1:26" ht="33">
       <c r="A85" s="7">
         <v>2</v>
       </c>
@@ -37925,7 +37920,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86" spans="1:26" ht="34.799999999999997">
+    <row r="86" spans="1:26" ht="33">
       <c r="A86" s="7">
         <v>2</v>
       </c>
@@ -37966,7 +37961,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87" spans="1:26" ht="34.799999999999997">
+    <row r="87" spans="1:26" ht="33">
       <c r="A87" s="7">
         <v>2</v>
       </c>
@@ -38007,7 +38002,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88" spans="1:26" ht="34.799999999999997">
+    <row r="88" spans="1:26" ht="33">
       <c r="A88" s="7">
         <v>2</v>
       </c>
@@ -38048,7 +38043,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89" spans="1:26" ht="34.799999999999997">
+    <row r="89" spans="1:26" ht="33">
       <c r="A89" s="7">
         <v>2</v>
       </c>
@@ -38089,7 +38084,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90" spans="1:26" ht="34.799999999999997">
+    <row r="90" spans="1:26" ht="33">
       <c r="A90" s="7">
         <v>2</v>
       </c>
@@ -38130,7 +38125,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91" spans="1:26" ht="34.799999999999997">
+    <row r="91" spans="1:26" ht="33">
       <c r="A91" s="7">
         <v>2</v>
       </c>
@@ -38171,7 +38166,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92" spans="1:26" ht="34.799999999999997">
+    <row r="92" spans="1:26" ht="33">
       <c r="A92" s="7">
         <v>2</v>
       </c>
@@ -38212,7 +38207,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93" spans="1:26" ht="34.799999999999997">
+    <row r="93" spans="1:26" ht="33">
       <c r="A93" s="7">
         <v>2</v>
       </c>
@@ -38253,7 +38248,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94" spans="1:26" ht="34.799999999999997">
+    <row r="94" spans="1:26" ht="16.5">
       <c r="A94" s="7">
         <v>2</v>
       </c>
@@ -38267,8 +38262,8 @@
         <f t="shared" si="1"/>
         <v>MainScript_2_1_12</v>
       </c>
-      <c r="E94" s="16" t="s">
-        <v>204</v>
+      <c r="E94" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>30</v>
@@ -38298,7 +38293,7 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
     </row>
-    <row r="95" spans="1:26" ht="17.399999999999999">
+    <row r="95" spans="1:26" ht="16.5">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -38326,7 +38321,7 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
     </row>
-    <row r="96" spans="1:26" ht="17.399999999999999">
+    <row r="96" spans="1:26" ht="16.5">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -38354,7 +38349,7 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
     </row>
-    <row r="97" spans="1:26" ht="17.399999999999999">
+    <row r="97" spans="1:26" ht="16.5">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -38382,7 +38377,7 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
     </row>
-    <row r="98" spans="1:26" ht="17.399999999999999">
+    <row r="98" spans="1:26" ht="16.5">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -38410,7 +38405,7 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
     </row>
-    <row r="99" spans="1:26" ht="17.399999999999999">
+    <row r="99" spans="1:26" ht="16.5">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -38438,7 +38433,7 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
     </row>
-    <row r="100" spans="1:26" ht="17.399999999999999">
+    <row r="100" spans="1:26" ht="16.5">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -38466,7 +38461,7 @@
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
     </row>
-    <row r="101" spans="1:26" ht="17.399999999999999">
+    <row r="101" spans="1:26" ht="16.5">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -38494,7 +38489,7 @@
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
     </row>
-    <row r="102" spans="1:26" ht="17.399999999999999">
+    <row r="102" spans="1:26" ht="16.5">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -38522,7 +38517,7 @@
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
     </row>
-    <row r="103" spans="1:26" ht="17.399999999999999">
+    <row r="103" spans="1:26" ht="16.5">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -38550,7 +38545,7 @@
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
     </row>
-    <row r="104" spans="1:26" ht="17.399999999999999">
+    <row r="104" spans="1:26" ht="16.5">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -38578,7 +38573,7 @@
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
     </row>
-    <row r="105" spans="1:26" ht="17.399999999999999">
+    <row r="105" spans="1:26" ht="16.5">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -38606,7 +38601,7 @@
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
     </row>
-    <row r="106" spans="1:26" ht="17.399999999999999">
+    <row r="106" spans="1:26" ht="16.5">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -38634,7 +38629,7 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
     </row>
-    <row r="107" spans="1:26" ht="17.399999999999999">
+    <row r="107" spans="1:26" ht="16.5">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -38662,7 +38657,7 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
     </row>
-    <row r="108" spans="1:26" ht="17.399999999999999">
+    <row r="108" spans="1:26" ht="16.5">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -38690,7 +38685,7 @@
       <c r="Y108" s="5"/>
       <c r="Z108" s="5"/>
     </row>
-    <row r="109" spans="1:26" ht="17.399999999999999">
+    <row r="109" spans="1:26" ht="16.5">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -38718,7 +38713,7 @@
       <c r="Y109" s="5"/>
       <c r="Z109" s="5"/>
     </row>
-    <row r="110" spans="1:26" ht="17.399999999999999">
+    <row r="110" spans="1:26" ht="16.5">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -38746,7 +38741,7 @@
       <c r="Y110" s="5"/>
       <c r="Z110" s="5"/>
     </row>
-    <row r="111" spans="1:26" ht="17.399999999999999">
+    <row r="111" spans="1:26" ht="16.5">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -38774,7 +38769,7 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
     </row>
-    <row r="112" spans="1:26" ht="17.399999999999999">
+    <row r="112" spans="1:26" ht="16.5">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -38802,7 +38797,7 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
     </row>
-    <row r="113" spans="1:26" ht="17.399999999999999">
+    <row r="113" spans="1:26" ht="16.5">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -38830,7 +38825,7 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
     </row>
-    <row r="114" spans="1:26" ht="17.399999999999999">
+    <row r="114" spans="1:26" ht="16.5">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -38858,7 +38853,7 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
     </row>
-    <row r="115" spans="1:26" ht="17.399999999999999">
+    <row r="115" spans="1:26" ht="16.5">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -38886,7 +38881,7 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
     </row>
-    <row r="116" spans="1:26" ht="17.399999999999999">
+    <row r="116" spans="1:26" ht="16.5">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -38914,7 +38909,7 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117" spans="1:26" ht="17.399999999999999">
+    <row r="117" spans="1:26" ht="16.5">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -38942,7 +38937,7 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118" spans="1:26" ht="17.399999999999999">
+    <row r="118" spans="1:26" ht="16.5">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -38970,7 +38965,7 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119" spans="1:26" ht="17.399999999999999">
+    <row r="119" spans="1:26" ht="16.5">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -38998,7 +38993,7 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120" spans="1:26" ht="17.399999999999999">
+    <row r="120" spans="1:26" ht="16.5">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -39026,7 +39021,7 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
     </row>
-    <row r="121" spans="1:26" ht="17.399999999999999">
+    <row r="121" spans="1:26" ht="16.5">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -39054,7 +39049,7 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
     </row>
-    <row r="122" spans="1:26" ht="17.399999999999999">
+    <row r="122" spans="1:26" ht="16.5">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -39082,7 +39077,7 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
     </row>
-    <row r="123" spans="1:26" ht="17.399999999999999">
+    <row r="123" spans="1:26" ht="16.5">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -39110,7 +39105,7 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
-    <row r="124" spans="1:26" ht="17.399999999999999">
+    <row r="124" spans="1:26" ht="16.5">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -39138,7 +39133,7 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
-    <row r="125" spans="1:26" ht="17.399999999999999">
+    <row r="125" spans="1:26" ht="16.5">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -39166,7 +39161,7 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
     </row>
-    <row r="126" spans="1:26" ht="17.399999999999999">
+    <row r="126" spans="1:26" ht="16.5">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -39194,7 +39189,7 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
     </row>
-    <row r="127" spans="1:26" ht="17.399999999999999">
+    <row r="127" spans="1:26" ht="16.5">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -39222,7 +39217,7 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128" spans="1:26" ht="17.399999999999999">
+    <row r="128" spans="1:26" ht="16.5">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -39250,7 +39245,7 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129" spans="1:26" ht="17.399999999999999">
+    <row r="129" spans="1:26" ht="16.5">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -39278,7 +39273,7 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130" spans="1:26" ht="17.399999999999999">
+    <row r="130" spans="1:26" ht="16.5">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -39306,7 +39301,7 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131" spans="1:26" ht="17.399999999999999">
+    <row r="131" spans="1:26" ht="16.5">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -39334,7 +39329,7 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132" spans="1:26" ht="17.399999999999999">
+    <row r="132" spans="1:26" ht="16.5">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -39362,7 +39357,7 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133" spans="1:26" ht="17.399999999999999">
+    <row r="133" spans="1:26" ht="16.5">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -39390,7 +39385,7 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134" spans="1:26" ht="17.399999999999999">
+    <row r="134" spans="1:26" ht="16.5">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -39418,7 +39413,7 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135" spans="1:26" ht="17.399999999999999">
+    <row r="135" spans="1:26" ht="16.5">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -39446,7 +39441,7 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136" spans="1:26" ht="17.399999999999999">
+    <row r="136" spans="1:26" ht="16.5">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -39474,7 +39469,7 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137" spans="1:26" ht="17.399999999999999">
+    <row r="137" spans="1:26" ht="16.5">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -39502,7 +39497,7 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138" spans="1:26" ht="17.399999999999999">
+    <row r="138" spans="1:26" ht="16.5">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -39530,7 +39525,7 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139" spans="1:26" ht="17.399999999999999">
+    <row r="139" spans="1:26" ht="16.5">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -39558,7 +39553,7 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140" spans="1:26" ht="17.399999999999999">
+    <row r="140" spans="1:26" ht="16.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -39586,7 +39581,7 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141" spans="1:26" ht="17.399999999999999">
+    <row r="141" spans="1:26" ht="16.5">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -39614,7 +39609,7 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142" spans="1:26" ht="17.399999999999999">
+    <row r="142" spans="1:26" ht="16.5">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -39642,7 +39637,7 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143" spans="1:26" ht="17.399999999999999">
+    <row r="143" spans="1:26" ht="16.5">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -39670,7 +39665,7 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144" spans="1:26" ht="17.399999999999999">
+    <row r="144" spans="1:26" ht="16.5">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -39698,7 +39693,7 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145" spans="1:26" ht="17.399999999999999">
+    <row r="145" spans="1:26" ht="16.5">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -39726,7 +39721,7 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146" spans="1:26" ht="17.399999999999999">
+    <row r="146" spans="1:26" ht="16.5">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -39754,7 +39749,7 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
     </row>
-    <row r="147" spans="1:26" ht="17.399999999999999">
+    <row r="147" spans="1:26" ht="16.5">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -39782,7 +39777,7 @@
       <c r="Y147" s="5"/>
       <c r="Z147" s="5"/>
     </row>
-    <row r="148" spans="1:26" ht="17.399999999999999">
+    <row r="148" spans="1:26" ht="16.5">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -39810,7 +39805,7 @@
       <c r="Y148" s="5"/>
       <c r="Z148" s="5"/>
     </row>
-    <row r="149" spans="1:26" ht="17.399999999999999">
+    <row r="149" spans="1:26" ht="16.5">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -39838,7 +39833,7 @@
       <c r="Y149" s="5"/>
       <c r="Z149" s="5"/>
     </row>
-    <row r="150" spans="1:26" ht="17.399999999999999">
+    <row r="150" spans="1:26" ht="16.5">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -39866,7 +39861,7 @@
       <c r="Y150" s="5"/>
       <c r="Z150" s="5"/>
     </row>
-    <row r="151" spans="1:26" ht="17.399999999999999">
+    <row r="151" spans="1:26" ht="16.5">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -39894,7 +39889,7 @@
       <c r="Y151" s="5"/>
       <c r="Z151" s="5"/>
     </row>
-    <row r="152" spans="1:26" ht="17.399999999999999">
+    <row r="152" spans="1:26" ht="16.5">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -39922,7 +39917,7 @@
       <c r="Y152" s="5"/>
       <c r="Z152" s="5"/>
     </row>
-    <row r="153" spans="1:26" ht="17.399999999999999">
+    <row r="153" spans="1:26" ht="16.5">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -39950,7 +39945,7 @@
       <c r="Y153" s="5"/>
       <c r="Z153" s="5"/>
     </row>
-    <row r="154" spans="1:26" ht="17.399999999999999">
+    <row r="154" spans="1:26" ht="16.5">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -39978,7 +39973,7 @@
       <c r="Y154" s="5"/>
       <c r="Z154" s="5"/>
     </row>
-    <row r="155" spans="1:26" ht="17.399999999999999">
+    <row r="155" spans="1:26" ht="16.5">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -40006,7 +40001,7 @@
       <c r="Y155" s="5"/>
       <c r="Z155" s="5"/>
     </row>
-    <row r="156" spans="1:26" ht="17.399999999999999">
+    <row r="156" spans="1:26" ht="16.5">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -40034,7 +40029,7 @@
       <c r="Y156" s="5"/>
       <c r="Z156" s="5"/>
     </row>
-    <row r="157" spans="1:26" ht="17.399999999999999">
+    <row r="157" spans="1:26" ht="16.5">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -40062,7 +40057,7 @@
       <c r="Y157" s="5"/>
       <c r="Z157" s="5"/>
     </row>
-    <row r="158" spans="1:26" ht="17.399999999999999">
+    <row r="158" spans="1:26" ht="16.5">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -40090,7 +40085,7 @@
       <c r="Y158" s="5"/>
       <c r="Z158" s="5"/>
     </row>
-    <row r="159" spans="1:26" ht="17.399999999999999">
+    <row r="159" spans="1:26" ht="16.5">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -40118,7 +40113,7 @@
       <c r="Y159" s="5"/>
       <c r="Z159" s="5"/>
     </row>
-    <row r="160" spans="1:26" ht="17.399999999999999">
+    <row r="160" spans="1:26" ht="16.5">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -40146,7 +40141,7 @@
       <c r="Y160" s="5"/>
       <c r="Z160" s="5"/>
     </row>
-    <row r="161" spans="1:26" ht="17.399999999999999">
+    <row r="161" spans="1:26" ht="16.5">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -40174,7 +40169,7 @@
       <c r="Y161" s="5"/>
       <c r="Z161" s="5"/>
     </row>
-    <row r="162" spans="1:26" ht="17.399999999999999">
+    <row r="162" spans="1:26" ht="16.5">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -40202,7 +40197,7 @@
       <c r="Y162" s="5"/>
       <c r="Z162" s="5"/>
     </row>
-    <row r="163" spans="1:26" ht="17.399999999999999">
+    <row r="163" spans="1:26" ht="16.5">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -40230,7 +40225,7 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
     </row>
-    <row r="164" spans="1:26" ht="17.399999999999999">
+    <row r="164" spans="1:26" ht="16.5">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -40258,7 +40253,7 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165" spans="1:26" ht="17.399999999999999">
+    <row r="165" spans="1:26" ht="16.5">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -40286,7 +40281,7 @@
       <c r="Y165" s="5"/>
       <c r="Z165" s="5"/>
     </row>
-    <row r="166" spans="1:26" ht="17.399999999999999">
+    <row r="166" spans="1:26" ht="16.5">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -40314,7 +40309,7 @@
       <c r="Y166" s="5"/>
       <c r="Z166" s="5"/>
     </row>
-    <row r="167" spans="1:26" ht="17.399999999999999">
+    <row r="167" spans="1:26" ht="16.5">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -40342,7 +40337,7 @@
       <c r="Y167" s="5"/>
       <c r="Z167" s="5"/>
     </row>
-    <row r="168" spans="1:26" ht="17.399999999999999">
+    <row r="168" spans="1:26" ht="16.5">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -40370,7 +40365,7 @@
       <c r="Y168" s="5"/>
       <c r="Z168" s="5"/>
     </row>
-    <row r="169" spans="1:26" ht="17.399999999999999">
+    <row r="169" spans="1:26" ht="16.5">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -40398,7 +40393,7 @@
       <c r="Y169" s="5"/>
       <c r="Z169" s="5"/>
     </row>
-    <row r="170" spans="1:26" ht="17.399999999999999">
+    <row r="170" spans="1:26" ht="16.5">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -40426,7 +40421,7 @@
       <c r="Y170" s="5"/>
       <c r="Z170" s="5"/>
     </row>
-    <row r="171" spans="1:26" ht="17.399999999999999">
+    <row r="171" spans="1:26" ht="16.5">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -40454,7 +40449,7 @@
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
     </row>
-    <row r="172" spans="1:26" ht="17.399999999999999">
+    <row r="172" spans="1:26" ht="16.5">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -40482,7 +40477,7 @@
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
     </row>
-    <row r="173" spans="1:26" ht="17.399999999999999">
+    <row r="173" spans="1:26" ht="16.5">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -40510,7 +40505,7 @@
       <c r="Y173" s="5"/>
       <c r="Z173" s="5"/>
     </row>
-    <row r="174" spans="1:26" ht="17.399999999999999">
+    <row r="174" spans="1:26" ht="16.5">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -40538,7 +40533,7 @@
       <c r="Y174" s="5"/>
       <c r="Z174" s="5"/>
     </row>
-    <row r="175" spans="1:26" ht="17.399999999999999">
+    <row r="175" spans="1:26" ht="16.5">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -40566,7 +40561,7 @@
       <c r="Y175" s="5"/>
       <c r="Z175" s="5"/>
     </row>
-    <row r="176" spans="1:26" ht="17.399999999999999">
+    <row r="176" spans="1:26" ht="16.5">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -40594,7 +40589,7 @@
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
     </row>
-    <row r="177" spans="1:26" ht="17.399999999999999">
+    <row r="177" spans="1:26" ht="16.5">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -40622,7 +40617,7 @@
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
     </row>
-    <row r="178" spans="1:26" ht="17.399999999999999">
+    <row r="178" spans="1:26" ht="16.5">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -40650,7 +40645,7 @@
       <c r="Y178" s="5"/>
       <c r="Z178" s="5"/>
     </row>
-    <row r="179" spans="1:26" ht="17.399999999999999">
+    <row r="179" spans="1:26" ht="16.5">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -40678,7 +40673,7 @@
       <c r="Y179" s="5"/>
       <c r="Z179" s="5"/>
     </row>
-    <row r="180" spans="1:26" ht="17.399999999999999">
+    <row r="180" spans="1:26" ht="16.5">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -40706,7 +40701,7 @@
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
     </row>
-    <row r="181" spans="1:26" ht="17.399999999999999">
+    <row r="181" spans="1:26" ht="16.5">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -40734,7 +40729,7 @@
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
     </row>
-    <row r="182" spans="1:26" ht="17.399999999999999">
+    <row r="182" spans="1:26" ht="16.5">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -40762,7 +40757,7 @@
       <c r="Y182" s="5"/>
       <c r="Z182" s="5"/>
     </row>
-    <row r="183" spans="1:26" ht="17.399999999999999">
+    <row r="183" spans="1:26" ht="16.5">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -40790,7 +40785,7 @@
       <c r="Y183" s="5"/>
       <c r="Z183" s="5"/>
     </row>
-    <row r="184" spans="1:26" ht="17.399999999999999">
+    <row r="184" spans="1:26" ht="16.5">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -40818,7 +40813,7 @@
       <c r="Y184" s="5"/>
       <c r="Z184" s="5"/>
     </row>
-    <row r="185" spans="1:26" ht="17.399999999999999">
+    <row r="185" spans="1:26" ht="16.5">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -40846,7 +40841,7 @@
       <c r="Y185" s="5"/>
       <c r="Z185" s="5"/>
     </row>
-    <row r="186" spans="1:26" ht="17.399999999999999">
+    <row r="186" spans="1:26" ht="16.5">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -40874,7 +40869,7 @@
       <c r="Y186" s="5"/>
       <c r="Z186" s="5"/>
     </row>
-    <row r="187" spans="1:26" ht="17.399999999999999">
+    <row r="187" spans="1:26" ht="16.5">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -40902,7 +40897,7 @@
       <c r="Y187" s="5"/>
       <c r="Z187" s="5"/>
     </row>
-    <row r="188" spans="1:26" ht="17.399999999999999">
+    <row r="188" spans="1:26" ht="16.5">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -40930,7 +40925,7 @@
       <c r="Y188" s="5"/>
       <c r="Z188" s="5"/>
     </row>
-    <row r="189" spans="1:26" ht="17.399999999999999">
+    <row r="189" spans="1:26" ht="16.5">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -40958,7 +40953,7 @@
       <c r="Y189" s="5"/>
       <c r="Z189" s="5"/>
     </row>
-    <row r="190" spans="1:26" ht="17.399999999999999">
+    <row r="190" spans="1:26" ht="16.5">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -40986,7 +40981,7 @@
       <c r="Y190" s="5"/>
       <c r="Z190" s="5"/>
     </row>
-    <row r="191" spans="1:26" ht="17.399999999999999">
+    <row r="191" spans="1:26" ht="16.5">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -41014,7 +41009,7 @@
       <c r="Y191" s="5"/>
       <c r="Z191" s="5"/>
     </row>
-    <row r="192" spans="1:26" ht="17.399999999999999">
+    <row r="192" spans="1:26" ht="16.5">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -41042,7 +41037,7 @@
       <c r="Y192" s="5"/>
       <c r="Z192" s="5"/>
     </row>
-    <row r="193" spans="1:26" ht="17.399999999999999">
+    <row r="193" spans="1:26" ht="16.5">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -41070,7 +41065,7 @@
       <c r="Y193" s="5"/>
       <c r="Z193" s="5"/>
     </row>
-    <row r="194" spans="1:26" ht="17.399999999999999">
+    <row r="194" spans="1:26" ht="16.5">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -41098,7 +41093,7 @@
       <c r="Y194" s="5"/>
       <c r="Z194" s="5"/>
     </row>
-    <row r="195" spans="1:26" ht="17.399999999999999">
+    <row r="195" spans="1:26" ht="16.5">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -41126,7 +41121,7 @@
       <c r="Y195" s="5"/>
       <c r="Z195" s="5"/>
     </row>
-    <row r="196" spans="1:26" ht="17.399999999999999">
+    <row r="196" spans="1:26" ht="16.5">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -41154,7 +41149,7 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
     </row>
-    <row r="197" spans="1:26" ht="17.399999999999999">
+    <row r="197" spans="1:26" ht="16.5">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -41182,7 +41177,7 @@
       <c r="Y197" s="5"/>
       <c r="Z197" s="5"/>
     </row>
-    <row r="198" spans="1:26" ht="17.399999999999999">
+    <row r="198" spans="1:26" ht="16.5">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -41210,7 +41205,7 @@
       <c r="Y198" s="5"/>
       <c r="Z198" s="5"/>
     </row>
-    <row r="199" spans="1:26" ht="17.399999999999999">
+    <row r="199" spans="1:26" ht="16.5">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -41238,7 +41233,7 @@
       <c r="Y199" s="5"/>
       <c r="Z199" s="5"/>
     </row>
-    <row r="200" spans="1:26" ht="17.399999999999999">
+    <row r="200" spans="1:26" ht="16.5">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -41266,7 +41261,7 @@
       <c r="Y200" s="5"/>
       <c r="Z200" s="5"/>
     </row>
-    <row r="201" spans="1:26" ht="17.399999999999999">
+    <row r="201" spans="1:26" ht="16.5">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -41294,7 +41289,7 @@
       <c r="Y201" s="5"/>
       <c r="Z201" s="5"/>
     </row>
-    <row r="202" spans="1:26" ht="17.399999999999999">
+    <row r="202" spans="1:26" ht="16.5">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -41322,7 +41317,7 @@
       <c r="Y202" s="5"/>
       <c r="Z202" s="5"/>
     </row>
-    <row r="203" spans="1:26" ht="17.399999999999999">
+    <row r="203" spans="1:26" ht="16.5">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -41350,7 +41345,7 @@
       <c r="Y203" s="5"/>
       <c r="Z203" s="5"/>
     </row>
-    <row r="204" spans="1:26" ht="17.399999999999999">
+    <row r="204" spans="1:26" ht="16.5">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -41378,7 +41373,7 @@
       <c r="Y204" s="5"/>
       <c r="Z204" s="5"/>
     </row>
-    <row r="205" spans="1:26" ht="17.399999999999999">
+    <row r="205" spans="1:26" ht="16.5">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -41406,7 +41401,7 @@
       <c r="Y205" s="5"/>
       <c r="Z205" s="5"/>
     </row>
-    <row r="206" spans="1:26" ht="17.399999999999999">
+    <row r="206" spans="1:26" ht="16.5">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -41434,7 +41429,7 @@
       <c r="Y206" s="5"/>
       <c r="Z206" s="5"/>
     </row>
-    <row r="207" spans="1:26" ht="17.399999999999999">
+    <row r="207" spans="1:26" ht="16.5">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -41462,7 +41457,7 @@
       <c r="Y207" s="5"/>
       <c r="Z207" s="5"/>
     </row>
-    <row r="208" spans="1:26" ht="17.399999999999999">
+    <row r="208" spans="1:26" ht="16.5">
       <c r="A208" s="7"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -41490,7 +41485,7 @@
       <c r="Y208" s="5"/>
       <c r="Z208" s="5"/>
     </row>
-    <row r="209" spans="1:26" ht="17.399999999999999">
+    <row r="209" spans="1:26" ht="16.5">
       <c r="A209" s="7"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
@@ -41518,7 +41513,7 @@
       <c r="Y209" s="5"/>
       <c r="Z209" s="5"/>
     </row>
-    <row r="210" spans="1:26" ht="17.399999999999999">
+    <row r="210" spans="1:26" ht="16.5">
       <c r="A210" s="7"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
@@ -41546,7 +41541,7 @@
       <c r="Y210" s="5"/>
       <c r="Z210" s="5"/>
     </row>
-    <row r="211" spans="1:26" ht="17.399999999999999">
+    <row r="211" spans="1:26" ht="16.5">
       <c r="A211" s="7"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
@@ -41574,7 +41569,7 @@
       <c r="Y211" s="5"/>
       <c r="Z211" s="5"/>
     </row>
-    <row r="212" spans="1:26" ht="17.399999999999999">
+    <row r="212" spans="1:26" ht="16.5">
       <c r="A212" s="7"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
@@ -41602,7 +41597,7 @@
       <c r="Y212" s="5"/>
       <c r="Z212" s="5"/>
     </row>
-    <row r="213" spans="1:26" ht="17.399999999999999">
+    <row r="213" spans="1:26" ht="16.5">
       <c r="A213" s="7"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
@@ -41630,7 +41625,7 @@
       <c r="Y213" s="5"/>
       <c r="Z213" s="5"/>
     </row>
-    <row r="214" spans="1:26" ht="17.399999999999999">
+    <row r="214" spans="1:26" ht="16.5">
       <c r="A214" s="7"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
@@ -41658,7 +41653,7 @@
       <c r="Y214" s="5"/>
       <c r="Z214" s="5"/>
     </row>
-    <row r="215" spans="1:26" ht="17.399999999999999">
+    <row r="215" spans="1:26" ht="16.5">
       <c r="A215" s="7"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
@@ -41686,7 +41681,7 @@
       <c r="Y215" s="5"/>
       <c r="Z215" s="5"/>
     </row>
-    <row r="216" spans="1:26" ht="17.399999999999999">
+    <row r="216" spans="1:26" ht="16.5">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
@@ -41714,7 +41709,7 @@
       <c r="Y216" s="5"/>
       <c r="Z216" s="5"/>
     </row>
-    <row r="217" spans="1:26" ht="17.399999999999999">
+    <row r="217" spans="1:26" ht="16.5">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -41742,7 +41737,7 @@
       <c r="Y217" s="5"/>
       <c r="Z217" s="5"/>
     </row>
-    <row r="218" spans="1:26" ht="17.399999999999999">
+    <row r="218" spans="1:26" ht="16.5">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
@@ -41770,7 +41765,7 @@
       <c r="Y218" s="5"/>
       <c r="Z218" s="5"/>
     </row>
-    <row r="219" spans="1:26" ht="17.399999999999999">
+    <row r="219" spans="1:26" ht="16.5">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
@@ -41798,7 +41793,7 @@
       <c r="Y219" s="5"/>
       <c r="Z219" s="5"/>
     </row>
-    <row r="220" spans="1:26" ht="17.399999999999999">
+    <row r="220" spans="1:26" ht="16.5">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -41826,7 +41821,7 @@
       <c r="Y220" s="5"/>
       <c r="Z220" s="5"/>
     </row>
-    <row r="221" spans="1:26" ht="17.399999999999999">
+    <row r="221" spans="1:26" ht="16.5">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -41854,7 +41849,7 @@
       <c r="Y221" s="5"/>
       <c r="Z221" s="5"/>
     </row>
-    <row r="222" spans="1:26" ht="17.399999999999999">
+    <row r="222" spans="1:26" ht="16.5">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -41882,7 +41877,7 @@
       <c r="Y222" s="5"/>
       <c r="Z222" s="5"/>
     </row>
-    <row r="223" spans="1:26" ht="17.399999999999999">
+    <row r="223" spans="1:26" ht="16.5">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -41910,7 +41905,7 @@
       <c r="Y223" s="5"/>
       <c r="Z223" s="5"/>
     </row>
-    <row r="224" spans="1:26" ht="17.399999999999999">
+    <row r="224" spans="1:26" ht="16.5">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -41938,7 +41933,7 @@
       <c r="Y224" s="5"/>
       <c r="Z224" s="5"/>
     </row>
-    <row r="225" spans="1:26" ht="17.399999999999999">
+    <row r="225" spans="1:26" ht="16.5">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -41966,7 +41961,7 @@
       <c r="Y225" s="5"/>
       <c r="Z225" s="5"/>
     </row>
-    <row r="226" spans="1:26" ht="17.399999999999999">
+    <row r="226" spans="1:26" ht="16.5">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -41994,7 +41989,7 @@
       <c r="Y226" s="5"/>
       <c r="Z226" s="5"/>
     </row>
-    <row r="227" spans="1:26" ht="17.399999999999999">
+    <row r="227" spans="1:26" ht="16.5">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -42022,7 +42017,7 @@
       <c r="Y227" s="5"/>
       <c r="Z227" s="5"/>
     </row>
-    <row r="228" spans="1:26" ht="17.399999999999999">
+    <row r="228" spans="1:26" ht="16.5">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -42050,7 +42045,7 @@
       <c r="Y228" s="5"/>
       <c r="Z228" s="5"/>
     </row>
-    <row r="229" spans="1:26" ht="17.399999999999999">
+    <row r="229" spans="1:26" ht="16.5">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -42078,7 +42073,7 @@
       <c r="Y229" s="5"/>
       <c r="Z229" s="5"/>
     </row>
-    <row r="230" spans="1:26" ht="17.399999999999999">
+    <row r="230" spans="1:26" ht="16.5">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -42106,7 +42101,7 @@
       <c r="Y230" s="5"/>
       <c r="Z230" s="5"/>
     </row>
-    <row r="231" spans="1:26" ht="17.399999999999999">
+    <row r="231" spans="1:26" ht="16.5">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -42134,7 +42129,7 @@
       <c r="Y231" s="5"/>
       <c r="Z231" s="5"/>
     </row>
-    <row r="232" spans="1:26" ht="17.399999999999999">
+    <row r="232" spans="1:26" ht="16.5">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -42162,7 +42157,7 @@
       <c r="Y232" s="5"/>
       <c r="Z232" s="5"/>
     </row>
-    <row r="233" spans="1:26" ht="17.399999999999999">
+    <row r="233" spans="1:26" ht="16.5">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -42190,7 +42185,7 @@
       <c r="Y233" s="5"/>
       <c r="Z233" s="5"/>
     </row>
-    <row r="234" spans="1:26" ht="17.399999999999999">
+    <row r="234" spans="1:26" ht="16.5">
       <c r="A234" s="7"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
@@ -42218,7 +42213,7 @@
       <c r="Y234" s="5"/>
       <c r="Z234" s="5"/>
     </row>
-    <row r="235" spans="1:26" ht="17.399999999999999">
+    <row r="235" spans="1:26" ht="16.5">
       <c r="A235" s="7"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
@@ -42246,7 +42241,7 @@
       <c r="Y235" s="5"/>
       <c r="Z235" s="5"/>
     </row>
-    <row r="236" spans="1:26" ht="17.399999999999999">
+    <row r="236" spans="1:26" ht="16.5">
       <c r="A236" s="7"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
@@ -42274,7 +42269,7 @@
       <c r="Y236" s="5"/>
       <c r="Z236" s="5"/>
     </row>
-    <row r="237" spans="1:26" ht="17.399999999999999">
+    <row r="237" spans="1:26" ht="16.5">
       <c r="A237" s="7"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
@@ -42302,7 +42297,7 @@
       <c r="Y237" s="5"/>
       <c r="Z237" s="5"/>
     </row>
-    <row r="238" spans="1:26" ht="17.399999999999999">
+    <row r="238" spans="1:26" ht="16.5">
       <c r="A238" s="7"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
@@ -42330,7 +42325,7 @@
       <c r="Y238" s="5"/>
       <c r="Z238" s="5"/>
     </row>
-    <row r="239" spans="1:26" ht="17.399999999999999">
+    <row r="239" spans="1:26" ht="16.5">
       <c r="A239" s="7"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
@@ -42358,7 +42353,7 @@
       <c r="Y239" s="5"/>
       <c r="Z239" s="5"/>
     </row>
-    <row r="240" spans="1:26" ht="17.399999999999999">
+    <row r="240" spans="1:26" ht="16.5">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
@@ -42386,7 +42381,7 @@
       <c r="Y240" s="5"/>
       <c r="Z240" s="5"/>
     </row>
-    <row r="241" spans="1:26" ht="17.399999999999999">
+    <row r="241" spans="1:26" ht="16.5">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -42414,7 +42409,7 @@
       <c r="Y241" s="5"/>
       <c r="Z241" s="5"/>
     </row>
-    <row r="242" spans="1:26" ht="17.399999999999999">
+    <row r="242" spans="1:26" ht="16.5">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
@@ -42442,7 +42437,7 @@
       <c r="Y242" s="5"/>
       <c r="Z242" s="5"/>
     </row>
-    <row r="243" spans="1:26" ht="17.399999999999999">
+    <row r="243" spans="1:26" ht="16.5">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
@@ -42470,7 +42465,7 @@
       <c r="Y243" s="5"/>
       <c r="Z243" s="5"/>
     </row>
-    <row r="244" spans="1:26" ht="17.399999999999999">
+    <row r="244" spans="1:26" ht="16.5">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
@@ -42498,7 +42493,7 @@
       <c r="Y244" s="5"/>
       <c r="Z244" s="5"/>
     </row>
-    <row r="245" spans="1:26" ht="17.399999999999999">
+    <row r="245" spans="1:26" ht="16.5">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -42526,7 +42521,7 @@
       <c r="Y245" s="5"/>
       <c r="Z245" s="5"/>
     </row>
-    <row r="246" spans="1:26" ht="17.399999999999999">
+    <row r="246" spans="1:26" ht="16.5">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
@@ -42554,7 +42549,7 @@
       <c r="Y246" s="5"/>
       <c r="Z246" s="5"/>
     </row>
-    <row r="247" spans="1:26" ht="17.399999999999999">
+    <row r="247" spans="1:26" ht="16.5">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
@@ -42582,7 +42577,7 @@
       <c r="Y247" s="5"/>
       <c r="Z247" s="5"/>
     </row>
-    <row r="248" spans="1:26" ht="17.399999999999999">
+    <row r="248" spans="1:26" ht="16.5">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
@@ -42610,7 +42605,7 @@
       <c r="Y248" s="5"/>
       <c r="Z248" s="5"/>
     </row>
-    <row r="249" spans="1:26" ht="17.399999999999999">
+    <row r="249" spans="1:26" ht="16.5">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
@@ -42638,7 +42633,7 @@
       <c r="Y249" s="5"/>
       <c r="Z249" s="5"/>
     </row>
-    <row r="250" spans="1:26" ht="17.399999999999999">
+    <row r="250" spans="1:26" ht="16.5">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
@@ -42666,7 +42661,7 @@
       <c r="Y250" s="5"/>
       <c r="Z250" s="5"/>
     </row>
-    <row r="251" spans="1:26" ht="17.399999999999999">
+    <row r="251" spans="1:26" ht="16.5">
       <c r="A251" s="7"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
@@ -42694,7 +42689,7 @@
       <c r="Y251" s="5"/>
       <c r="Z251" s="5"/>
     </row>
-    <row r="252" spans="1:26" ht="17.399999999999999">
+    <row r="252" spans="1:26" ht="16.5">
       <c r="A252" s="7"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
@@ -42722,7 +42717,7 @@
       <c r="Y252" s="5"/>
       <c r="Z252" s="5"/>
     </row>
-    <row r="253" spans="1:26" ht="17.399999999999999">
+    <row r="253" spans="1:26" ht="16.5">
       <c r="A253" s="7"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
@@ -42750,7 +42745,7 @@
       <c r="Y253" s="5"/>
       <c r="Z253" s="5"/>
     </row>
-    <row r="254" spans="1:26" ht="17.399999999999999">
+    <row r="254" spans="1:26" ht="16.5">
       <c r="A254" s="7"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
@@ -42778,7 +42773,7 @@
       <c r="Y254" s="5"/>
       <c r="Z254" s="5"/>
     </row>
-    <row r="255" spans="1:26" ht="17.399999999999999">
+    <row r="255" spans="1:26" ht="16.5">
       <c r="A255" s="7"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
@@ -42806,7 +42801,7 @@
       <c r="Y255" s="5"/>
       <c r="Z255" s="5"/>
     </row>
-    <row r="256" spans="1:26" ht="17.399999999999999">
+    <row r="256" spans="1:26" ht="16.5">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
@@ -42834,7 +42829,7 @@
       <c r="Y256" s="5"/>
       <c r="Z256" s="5"/>
     </row>
-    <row r="257" spans="1:26" ht="17.399999999999999">
+    <row r="257" spans="1:26" ht="16.5">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
@@ -42862,7 +42857,7 @@
       <c r="Y257" s="5"/>
       <c r="Z257" s="5"/>
     </row>
-    <row r="258" spans="1:26" ht="17.399999999999999">
+    <row r="258" spans="1:26" ht="16.5">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
@@ -42890,7 +42885,7 @@
       <c r="Y258" s="5"/>
       <c r="Z258" s="5"/>
     </row>
-    <row r="259" spans="1:26" ht="17.399999999999999">
+    <row r="259" spans="1:26" ht="16.5">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
@@ -42918,7 +42913,7 @@
       <c r="Y259" s="5"/>
       <c r="Z259" s="5"/>
     </row>
-    <row r="260" spans="1:26" ht="17.399999999999999">
+    <row r="260" spans="1:26" ht="16.5">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
@@ -42946,7 +42941,7 @@
       <c r="Y260" s="5"/>
       <c r="Z260" s="5"/>
     </row>
-    <row r="261" spans="1:26" ht="17.399999999999999">
+    <row r="261" spans="1:26" ht="16.5">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
@@ -42974,7 +42969,7 @@
       <c r="Y261" s="5"/>
       <c r="Z261" s="5"/>
     </row>
-    <row r="262" spans="1:26" ht="17.399999999999999">
+    <row r="262" spans="1:26" ht="16.5">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
@@ -43002,7 +42997,7 @@
       <c r="Y262" s="5"/>
       <c r="Z262" s="5"/>
     </row>
-    <row r="263" spans="1:26" ht="17.399999999999999">
+    <row r="263" spans="1:26" ht="16.5">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
@@ -43030,7 +43025,7 @@
       <c r="Y263" s="5"/>
       <c r="Z263" s="5"/>
     </row>
-    <row r="264" spans="1:26" ht="17.399999999999999">
+    <row r="264" spans="1:26" ht="16.5">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
@@ -43058,7 +43053,7 @@
       <c r="Y264" s="5"/>
       <c r="Z264" s="5"/>
     </row>
-    <row r="265" spans="1:26" ht="17.399999999999999">
+    <row r="265" spans="1:26" ht="16.5">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
@@ -43086,7 +43081,7 @@
       <c r="Y265" s="5"/>
       <c r="Z265" s="5"/>
     </row>
-    <row r="266" spans="1:26" ht="17.399999999999999">
+    <row r="266" spans="1:26" ht="16.5">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
@@ -43114,7 +43109,7 @@
       <c r="Y266" s="5"/>
       <c r="Z266" s="5"/>
     </row>
-    <row r="267" spans="1:26" ht="17.399999999999999">
+    <row r="267" spans="1:26" ht="16.5">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
@@ -43142,7 +43137,7 @@
       <c r="Y267" s="5"/>
       <c r="Z267" s="5"/>
     </row>
-    <row r="268" spans="1:26" ht="17.399999999999999">
+    <row r="268" spans="1:26" ht="16.5">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
@@ -43170,7 +43165,7 @@
       <c r="Y268" s="5"/>
       <c r="Z268" s="5"/>
     </row>
-    <row r="269" spans="1:26" ht="17.399999999999999">
+    <row r="269" spans="1:26" ht="16.5">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
@@ -43198,7 +43193,7 @@
       <c r="Y269" s="5"/>
       <c r="Z269" s="5"/>
     </row>
-    <row r="270" spans="1:26" ht="17.399999999999999">
+    <row r="270" spans="1:26" ht="16.5">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
@@ -43226,7 +43221,7 @@
       <c r="Y270" s="5"/>
       <c r="Z270" s="5"/>
     </row>
-    <row r="271" spans="1:26" ht="17.399999999999999">
+    <row r="271" spans="1:26" ht="16.5">
       <c r="A271" s="7"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
@@ -43254,7 +43249,7 @@
       <c r="Y271" s="5"/>
       <c r="Z271" s="5"/>
     </row>
-    <row r="272" spans="1:26" ht="17.399999999999999">
+    <row r="272" spans="1:26" ht="16.5">
       <c r="A272" s="7"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
@@ -43282,7 +43277,7 @@
       <c r="Y272" s="5"/>
       <c r="Z272" s="5"/>
     </row>
-    <row r="273" spans="1:26" ht="17.399999999999999">
+    <row r="273" spans="1:26" ht="16.5">
       <c r="A273" s="7"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
@@ -43310,7 +43305,7 @@
       <c r="Y273" s="5"/>
       <c r="Z273" s="5"/>
     </row>
-    <row r="274" spans="1:26" ht="17.399999999999999">
+    <row r="274" spans="1:26" ht="16.5">
       <c r="A274" s="7"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
@@ -43338,7 +43333,7 @@
       <c r="Y274" s="5"/>
       <c r="Z274" s="5"/>
     </row>
-    <row r="275" spans="1:26" ht="17.399999999999999">
+    <row r="275" spans="1:26" ht="16.5">
       <c r="A275" s="7"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
@@ -43366,7 +43361,7 @@
       <c r="Y275" s="5"/>
       <c r="Z275" s="5"/>
     </row>
-    <row r="276" spans="1:26" ht="17.399999999999999">
+    <row r="276" spans="1:26" ht="16.5">
       <c r="A276" s="7"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
@@ -43394,7 +43389,7 @@
       <c r="Y276" s="5"/>
       <c r="Z276" s="5"/>
     </row>
-    <row r="277" spans="1:26" ht="17.399999999999999">
+    <row r="277" spans="1:26" ht="16.5">
       <c r="A277" s="7"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
@@ -43422,7 +43417,7 @@
       <c r="Y277" s="5"/>
       <c r="Z277" s="5"/>
     </row>
-    <row r="278" spans="1:26" ht="17.399999999999999">
+    <row r="278" spans="1:26" ht="16.5">
       <c r="A278" s="7"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
@@ -43450,7 +43445,7 @@
       <c r="Y278" s="5"/>
       <c r="Z278" s="5"/>
     </row>
-    <row r="279" spans="1:26" ht="17.399999999999999">
+    <row r="279" spans="1:26" ht="16.5">
       <c r="A279" s="7"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
@@ -43478,7 +43473,7 @@
       <c r="Y279" s="5"/>
       <c r="Z279" s="5"/>
     </row>
-    <row r="280" spans="1:26" ht="17.399999999999999">
+    <row r="280" spans="1:26" ht="16.5">
       <c r="A280" s="7"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
@@ -43506,7 +43501,7 @@
       <c r="Y280" s="5"/>
       <c r="Z280" s="5"/>
     </row>
-    <row r="281" spans="1:26" ht="17.399999999999999">
+    <row r="281" spans="1:26" ht="16.5">
       <c r="A281" s="7"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
@@ -43534,7 +43529,7 @@
       <c r="Y281" s="5"/>
       <c r="Z281" s="5"/>
     </row>
-    <row r="282" spans="1:26" ht="17.399999999999999">
+    <row r="282" spans="1:26" ht="16.5">
       <c r="A282" s="7"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
@@ -43562,7 +43557,7 @@
       <c r="Y282" s="5"/>
       <c r="Z282" s="5"/>
     </row>
-    <row r="283" spans="1:26" ht="17.399999999999999">
+    <row r="283" spans="1:26" ht="16.5">
       <c r="A283" s="7"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
@@ -43590,7 +43585,7 @@
       <c r="Y283" s="5"/>
       <c r="Z283" s="5"/>
     </row>
-    <row r="284" spans="1:26" ht="17.399999999999999">
+    <row r="284" spans="1:26" ht="16.5">
       <c r="A284" s="7"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
@@ -43618,7 +43613,7 @@
       <c r="Y284" s="5"/>
       <c r="Z284" s="5"/>
     </row>
-    <row r="285" spans="1:26" ht="17.399999999999999">
+    <row r="285" spans="1:26" ht="16.5">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
@@ -43646,7 +43641,7 @@
       <c r="Y285" s="5"/>
       <c r="Z285" s="5"/>
     </row>
-    <row r="286" spans="1:26" ht="17.399999999999999">
+    <row r="286" spans="1:26" ht="16.5">
       <c r="A286" s="7"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
@@ -43674,7 +43669,7 @@
       <c r="Y286" s="5"/>
       <c r="Z286" s="5"/>
     </row>
-    <row r="287" spans="1:26" ht="17.399999999999999">
+    <row r="287" spans="1:26" ht="16.5">
       <c r="A287" s="7"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
@@ -43702,7 +43697,7 @@
       <c r="Y287" s="5"/>
       <c r="Z287" s="5"/>
     </row>
-    <row r="288" spans="1:26" ht="17.399999999999999">
+    <row r="288" spans="1:26" ht="16.5">
       <c r="A288" s="7"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
@@ -43730,7 +43725,7 @@
       <c r="Y288" s="5"/>
       <c r="Z288" s="5"/>
     </row>
-    <row r="289" spans="1:26" ht="17.399999999999999">
+    <row r="289" spans="1:26" ht="16.5">
       <c r="A289" s="7"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
@@ -43758,7 +43753,7 @@
       <c r="Y289" s="5"/>
       <c r="Z289" s="5"/>
     </row>
-    <row r="290" spans="1:26" ht="17.399999999999999">
+    <row r="290" spans="1:26" ht="16.5">
       <c r="A290" s="7"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
@@ -43786,7 +43781,7 @@
       <c r="Y290" s="5"/>
       <c r="Z290" s="5"/>
     </row>
-    <row r="291" spans="1:26" ht="17.399999999999999">
+    <row r="291" spans="1:26" ht="16.5">
       <c r="A291" s="7"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
@@ -43814,7 +43809,7 @@
       <c r="Y291" s="5"/>
       <c r="Z291" s="5"/>
     </row>
-    <row r="292" spans="1:26" ht="17.399999999999999">
+    <row r="292" spans="1:26" ht="16.5">
       <c r="A292" s="7"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
@@ -43842,7 +43837,7 @@
       <c r="Y292" s="5"/>
       <c r="Z292" s="5"/>
     </row>
-    <row r="293" spans="1:26" ht="17.399999999999999">
+    <row r="293" spans="1:26" ht="16.5">
       <c r="A293" s="7"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
@@ -43870,7 +43865,7 @@
       <c r="Y293" s="5"/>
       <c r="Z293" s="5"/>
     </row>
-    <row r="294" spans="1:26" ht="17.399999999999999">
+    <row r="294" spans="1:26" ht="16.5">
       <c r="A294" s="7"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
@@ -43898,7 +43893,7 @@
       <c r="Y294" s="5"/>
       <c r="Z294" s="5"/>
     </row>
-    <row r="295" spans="1:26" ht="17.399999999999999">
+    <row r="295" spans="1:26" ht="16.5">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
@@ -43926,7 +43921,7 @@
       <c r="Y295" s="5"/>
       <c r="Z295" s="5"/>
     </row>
-    <row r="296" spans="1:26" ht="17.399999999999999">
+    <row r="296" spans="1:26" ht="16.5">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
@@ -43954,7 +43949,7 @@
       <c r="Y296" s="5"/>
       <c r="Z296" s="5"/>
     </row>
-    <row r="297" spans="1:26" ht="17.399999999999999">
+    <row r="297" spans="1:26" ht="16.5">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
@@ -43982,7 +43977,7 @@
       <c r="Y297" s="5"/>
       <c r="Z297" s="5"/>
     </row>
-    <row r="298" spans="1:26" ht="17.399999999999999">
+    <row r="298" spans="1:26" ht="16.5">
       <c r="A298" s="7"/>
       <c r="B298" s="7"/>
       <c r="C298" s="7"/>
@@ -44010,7 +44005,7 @@
       <c r="Y298" s="5"/>
       <c r="Z298" s="5"/>
     </row>
-    <row r="299" spans="1:26" ht="17.399999999999999">
+    <row r="299" spans="1:26" ht="16.5">
       <c r="A299" s="7"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
@@ -44038,7 +44033,7 @@
       <c r="Y299" s="5"/>
       <c r="Z299" s="5"/>
     </row>
-    <row r="300" spans="1:26" ht="17.399999999999999">
+    <row r="300" spans="1:26" ht="16.5">
       <c r="A300" s="7"/>
       <c r="B300" s="7"/>
       <c r="C300" s="7"/>
@@ -44066,7 +44061,7 @@
       <c r="Y300" s="5"/>
       <c r="Z300" s="5"/>
     </row>
-    <row r="301" spans="1:26" ht="17.399999999999999">
+    <row r="301" spans="1:26" ht="16.5">
       <c r="A301" s="7"/>
       <c r="B301" s="7"/>
       <c r="C301" s="7"/>
@@ -44094,7 +44089,7 @@
       <c r="Y301" s="5"/>
       <c r="Z301" s="5"/>
     </row>
-    <row r="302" spans="1:26" ht="17.399999999999999">
+    <row r="302" spans="1:26" ht="16.5">
       <c r="A302" s="7"/>
       <c r="B302" s="7"/>
       <c r="C302" s="7"/>
@@ -44122,7 +44117,7 @@
       <c r="Y302" s="5"/>
       <c r="Z302" s="5"/>
     </row>
-    <row r="303" spans="1:26" ht="17.399999999999999">
+    <row r="303" spans="1:26" ht="16.5">
       <c r="A303" s="7"/>
       <c r="B303" s="7"/>
       <c r="C303" s="7"/>
@@ -44150,7 +44145,7 @@
       <c r="Y303" s="5"/>
       <c r="Z303" s="5"/>
     </row>
-    <row r="304" spans="1:26" ht="17.399999999999999">
+    <row r="304" spans="1:26" ht="16.5">
       <c r="A304" s="7"/>
       <c r="B304" s="7"/>
       <c r="C304" s="7"/>
@@ -44178,7 +44173,7 @@
       <c r="Y304" s="5"/>
       <c r="Z304" s="5"/>
     </row>
-    <row r="305" spans="1:26" ht="17.399999999999999">
+    <row r="305" spans="1:26" ht="16.5">
       <c r="A305" s="7"/>
       <c r="B305" s="7"/>
       <c r="C305" s="7"/>
@@ -44206,7 +44201,7 @@
       <c r="Y305" s="5"/>
       <c r="Z305" s="5"/>
     </row>
-    <row r="306" spans="1:26" ht="17.399999999999999">
+    <row r="306" spans="1:26" ht="16.5">
       <c r="A306" s="7"/>
       <c r="B306" s="7"/>
       <c r="C306" s="7"/>
@@ -44234,7 +44229,7 @@
       <c r="Y306" s="5"/>
       <c r="Z306" s="5"/>
     </row>
-    <row r="307" spans="1:26" ht="17.399999999999999">
+    <row r="307" spans="1:26" ht="16.5">
       <c r="A307" s="7"/>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
@@ -44262,7 +44257,7 @@
       <c r="Y307" s="5"/>
       <c r="Z307" s="5"/>
     </row>
-    <row r="308" spans="1:26" ht="17.399999999999999">
+    <row r="308" spans="1:26" ht="16.5">
       <c r="A308" s="7"/>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
@@ -44290,7 +44285,7 @@
       <c r="Y308" s="5"/>
       <c r="Z308" s="5"/>
     </row>
-    <row r="309" spans="1:26" ht="17.399999999999999">
+    <row r="309" spans="1:26" ht="16.5">
       <c r="A309" s="7"/>
       <c r="B309" s="7"/>
       <c r="C309" s="7"/>
@@ -44318,7 +44313,7 @@
       <c r="Y309" s="5"/>
       <c r="Z309" s="5"/>
     </row>
-    <row r="310" spans="1:26" ht="17.399999999999999">
+    <row r="310" spans="1:26" ht="16.5">
       <c r="A310" s="7"/>
       <c r="B310" s="7"/>
       <c r="C310" s="7"/>
@@ -44346,7 +44341,7 @@
       <c r="Y310" s="5"/>
       <c r="Z310" s="5"/>
     </row>
-    <row r="311" spans="1:26" ht="17.399999999999999">
+    <row r="311" spans="1:26" ht="16.5">
       <c r="A311" s="7"/>
       <c r="B311" s="7"/>
       <c r="C311" s="7"/>
@@ -44374,7 +44369,7 @@
       <c r="Y311" s="5"/>
       <c r="Z311" s="5"/>
     </row>
-    <row r="312" spans="1:26" ht="17.399999999999999">
+    <row r="312" spans="1:26" ht="16.5">
       <c r="A312" s="7"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
@@ -44402,7 +44397,7 @@
       <c r="Y312" s="5"/>
       <c r="Z312" s="5"/>
     </row>
-    <row r="313" spans="1:26" ht="17.399999999999999">
+    <row r="313" spans="1:26" ht="16.5">
       <c r="A313" s="7"/>
       <c r="B313" s="7"/>
       <c r="C313" s="7"/>
@@ -44430,7 +44425,7 @@
       <c r="Y313" s="5"/>
       <c r="Z313" s="5"/>
     </row>
-    <row r="314" spans="1:26" ht="17.399999999999999">
+    <row r="314" spans="1:26" ht="16.5">
       <c r="A314" s="7"/>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
@@ -44458,7 +44453,7 @@
       <c r="Y314" s="5"/>
       <c r="Z314" s="5"/>
     </row>
-    <row r="315" spans="1:26" ht="17.399999999999999">
+    <row r="315" spans="1:26" ht="16.5">
       <c r="A315" s="7"/>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
@@ -44486,7 +44481,7 @@
       <c r="Y315" s="5"/>
       <c r="Z315" s="5"/>
     </row>
-    <row r="316" spans="1:26" ht="17.399999999999999">
+    <row r="316" spans="1:26" ht="16.5">
       <c r="A316" s="7"/>
       <c r="B316" s="7"/>
       <c r="C316" s="7"/>
@@ -44514,7 +44509,7 @@
       <c r="Y316" s="5"/>
       <c r="Z316" s="5"/>
     </row>
-    <row r="317" spans="1:26" ht="17.399999999999999">
+    <row r="317" spans="1:26" ht="16.5">
       <c r="A317" s="7"/>
       <c r="B317" s="7"/>
       <c r="C317" s="7"/>
@@ -44542,7 +44537,7 @@
       <c r="Y317" s="5"/>
       <c r="Z317" s="5"/>
     </row>
-    <row r="318" spans="1:26" ht="17.399999999999999">
+    <row r="318" spans="1:26" ht="16.5">
       <c r="A318" s="7"/>
       <c r="B318" s="7"/>
       <c r="C318" s="7"/>
@@ -44570,7 +44565,7 @@
       <c r="Y318" s="5"/>
       <c r="Z318" s="5"/>
     </row>
-    <row r="319" spans="1:26" ht="17.399999999999999">
+    <row r="319" spans="1:26" ht="16.5">
       <c r="A319" s="7"/>
       <c r="B319" s="7"/>
       <c r="C319" s="7"/>
@@ -44598,7 +44593,7 @@
       <c r="Y319" s="5"/>
       <c r="Z319" s="5"/>
     </row>
-    <row r="320" spans="1:26" ht="17.399999999999999">
+    <row r="320" spans="1:26" ht="16.5">
       <c r="A320" s="7"/>
       <c r="B320" s="7"/>
       <c r="C320" s="7"/>
@@ -44626,7 +44621,7 @@
       <c r="Y320" s="5"/>
       <c r="Z320" s="5"/>
     </row>
-    <row r="321" spans="1:26" ht="17.399999999999999">
+    <row r="321" spans="1:26" ht="16.5">
       <c r="A321" s="7"/>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
@@ -44654,7 +44649,7 @@
       <c r="Y321" s="5"/>
       <c r="Z321" s="5"/>
     </row>
-    <row r="322" spans="1:26" ht="17.399999999999999">
+    <row r="322" spans="1:26" ht="16.5">
       <c r="A322" s="7"/>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
@@ -44682,7 +44677,7 @@
       <c r="Y322" s="5"/>
       <c r="Z322" s="5"/>
     </row>
-    <row r="323" spans="1:26" ht="17.399999999999999">
+    <row r="323" spans="1:26" ht="16.5">
       <c r="A323" s="7"/>
       <c r="B323" s="7"/>
       <c r="C323" s="7"/>
@@ -44710,7 +44705,7 @@
       <c r="Y323" s="5"/>
       <c r="Z323" s="5"/>
     </row>
-    <row r="324" spans="1:26" ht="17.399999999999999">
+    <row r="324" spans="1:26" ht="16.5">
       <c r="A324" s="7"/>
       <c r="B324" s="7"/>
       <c r="C324" s="7"/>
@@ -44738,7 +44733,7 @@
       <c r="Y324" s="5"/>
       <c r="Z324" s="5"/>
     </row>
-    <row r="325" spans="1:26" ht="17.399999999999999">
+    <row r="325" spans="1:26" ht="16.5">
       <c r="A325" s="7"/>
       <c r="B325" s="7"/>
       <c r="C325" s="7"/>
@@ -44766,7 +44761,7 @@
       <c r="Y325" s="5"/>
       <c r="Z325" s="5"/>
     </row>
-    <row r="326" spans="1:26" ht="17.399999999999999">
+    <row r="326" spans="1:26" ht="16.5">
       <c r="A326" s="7"/>
       <c r="B326" s="7"/>
       <c r="C326" s="7"/>
@@ -44794,7 +44789,7 @@
       <c r="Y326" s="5"/>
       <c r="Z326" s="5"/>
     </row>
-    <row r="327" spans="1:26" ht="17.399999999999999">
+    <row r="327" spans="1:26" ht="16.5">
       <c r="A327" s="7"/>
       <c r="B327" s="7"/>
       <c r="C327" s="7"/>
@@ -44822,7 +44817,7 @@
       <c r="Y327" s="5"/>
       <c r="Z327" s="5"/>
     </row>
-    <row r="328" spans="1:26" ht="17.399999999999999">
+    <row r="328" spans="1:26" ht="16.5">
       <c r="A328" s="7"/>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
@@ -44850,7 +44845,7 @@
       <c r="Y328" s="5"/>
       <c r="Z328" s="5"/>
     </row>
-    <row r="329" spans="1:26" ht="17.399999999999999">
+    <row r="329" spans="1:26" ht="16.5">
       <c r="A329" s="7"/>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
@@ -44878,7 +44873,7 @@
       <c r="Y329" s="5"/>
       <c r="Z329" s="5"/>
     </row>
-    <row r="330" spans="1:26" ht="17.399999999999999">
+    <row r="330" spans="1:26" ht="16.5">
       <c r="A330" s="7"/>
       <c r="B330" s="7"/>
       <c r="C330" s="7"/>
@@ -44906,7 +44901,7 @@
       <c r="Y330" s="5"/>
       <c r="Z330" s="5"/>
     </row>
-    <row r="331" spans="1:26" ht="17.399999999999999">
+    <row r="331" spans="1:26" ht="16.5">
       <c r="A331" s="7"/>
       <c r="B331" s="7"/>
       <c r="C331" s="7"/>
@@ -44934,7 +44929,7 @@
       <c r="Y331" s="5"/>
       <c r="Z331" s="5"/>
     </row>
-    <row r="332" spans="1:26" ht="17.399999999999999">
+    <row r="332" spans="1:26" ht="16.5">
       <c r="A332" s="7"/>
       <c r="B332" s="7"/>
       <c r="C332" s="7"/>
@@ -44962,7 +44957,7 @@
       <c r="Y332" s="5"/>
       <c r="Z332" s="5"/>
     </row>
-    <row r="333" spans="1:26" ht="17.399999999999999">
+    <row r="333" spans="1:26" ht="16.5">
       <c r="A333" s="7"/>
       <c r="B333" s="7"/>
       <c r="C333" s="7"/>
@@ -44990,7 +44985,7 @@
       <c r="Y333" s="5"/>
       <c r="Z333" s="5"/>
     </row>
-    <row r="334" spans="1:26" ht="17.399999999999999">
+    <row r="334" spans="1:26" ht="16.5">
       <c r="A334" s="7"/>
       <c r="B334" s="7"/>
       <c r="C334" s="7"/>
@@ -45018,7 +45013,7 @@
       <c r="Y334" s="5"/>
       <c r="Z334" s="5"/>
     </row>
-    <row r="335" spans="1:26" ht="17.399999999999999">
+    <row r="335" spans="1:26" ht="16.5">
       <c r="A335" s="7"/>
       <c r="B335" s="7"/>
       <c r="C335" s="7"/>
@@ -45046,7 +45041,7 @@
       <c r="Y335" s="5"/>
       <c r="Z335" s="5"/>
     </row>
-    <row r="336" spans="1:26" ht="17.399999999999999">
+    <row r="336" spans="1:26" ht="16.5">
       <c r="A336" s="7"/>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
@@ -45074,7 +45069,7 @@
       <c r="Y336" s="5"/>
       <c r="Z336" s="5"/>
     </row>
-    <row r="337" spans="1:26" ht="17.399999999999999">
+    <row r="337" spans="1:26" ht="16.5">
       <c r="A337" s="7"/>
       <c r="B337" s="7"/>
       <c r="C337" s="7"/>
@@ -45102,7 +45097,7 @@
       <c r="Y337" s="5"/>
       <c r="Z337" s="5"/>
     </row>
-    <row r="338" spans="1:26" ht="17.399999999999999">
+    <row r="338" spans="1:26" ht="16.5">
       <c r="A338" s="7"/>
       <c r="B338" s="7"/>
       <c r="C338" s="7"/>
@@ -45130,7 +45125,7 @@
       <c r="Y338" s="5"/>
       <c r="Z338" s="5"/>
     </row>
-    <row r="339" spans="1:26" ht="17.399999999999999">
+    <row r="339" spans="1:26" ht="16.5">
       <c r="A339" s="7"/>
       <c r="B339" s="7"/>
       <c r="C339" s="7"/>
@@ -45158,7 +45153,7 @@
       <c r="Y339" s="5"/>
       <c r="Z339" s="5"/>
     </row>
-    <row r="340" spans="1:26" ht="17.399999999999999">
+    <row r="340" spans="1:26" ht="16.5">
       <c r="A340" s="7"/>
       <c r="B340" s="7"/>
       <c r="C340" s="7"/>
@@ -45186,7 +45181,7 @@
       <c r="Y340" s="5"/>
       <c r="Z340" s="5"/>
     </row>
-    <row r="341" spans="1:26" ht="17.399999999999999">
+    <row r="341" spans="1:26" ht="16.5">
       <c r="A341" s="7"/>
       <c r="B341" s="7"/>
       <c r="C341" s="7"/>
@@ -45214,7 +45209,7 @@
       <c r="Y341" s="5"/>
       <c r="Z341" s="5"/>
     </row>
-    <row r="342" spans="1:26" ht="17.399999999999999">
+    <row r="342" spans="1:26" ht="16.5">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
       <c r="C342" s="7"/>
@@ -45242,7 +45237,7 @@
       <c r="Y342" s="5"/>
       <c r="Z342" s="5"/>
     </row>
-    <row r="343" spans="1:26" ht="17.399999999999999">
+    <row r="343" spans="1:26" ht="16.5">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
       <c r="C343" s="7"/>
@@ -45270,7 +45265,7 @@
       <c r="Y343" s="5"/>
       <c r="Z343" s="5"/>
     </row>
-    <row r="344" spans="1:26" ht="17.399999999999999">
+    <row r="344" spans="1:26" ht="16.5">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
       <c r="C344" s="7"/>
@@ -45298,7 +45293,7 @@
       <c r="Y344" s="5"/>
       <c r="Z344" s="5"/>
     </row>
-    <row r="345" spans="1:26" ht="17.399999999999999">
+    <row r="345" spans="1:26" ht="16.5">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
       <c r="C345" s="7"/>
@@ -45326,7 +45321,7 @@
       <c r="Y345" s="5"/>
       <c r="Z345" s="5"/>
     </row>
-    <row r="346" spans="1:26" ht="17.399999999999999">
+    <row r="346" spans="1:26" ht="16.5">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
       <c r="C346" s="7"/>
@@ -45354,7 +45349,7 @@
       <c r="Y346" s="5"/>
       <c r="Z346" s="5"/>
     </row>
-    <row r="347" spans="1:26" ht="17.399999999999999">
+    <row r="347" spans="1:26" ht="16.5">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="7"/>
@@ -45382,7 +45377,7 @@
       <c r="Y347" s="5"/>
       <c r="Z347" s="5"/>
     </row>
-    <row r="348" spans="1:26" ht="17.399999999999999">
+    <row r="348" spans="1:26" ht="16.5">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="7"/>
@@ -45410,7 +45405,7 @@
       <c r="Y348" s="5"/>
       <c r="Z348" s="5"/>
     </row>
-    <row r="349" spans="1:26" ht="17.399999999999999">
+    <row r="349" spans="1:26" ht="16.5">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="7"/>
@@ -45438,7 +45433,7 @@
       <c r="Y349" s="5"/>
       <c r="Z349" s="5"/>
     </row>
-    <row r="350" spans="1:26" ht="17.399999999999999">
+    <row r="350" spans="1:26" ht="16.5">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="7"/>
@@ -45466,7 +45461,7 @@
       <c r="Y350" s="5"/>
       <c r="Z350" s="5"/>
     </row>
-    <row r="351" spans="1:26" ht="17.399999999999999">
+    <row r="351" spans="1:26" ht="16.5">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="7"/>
@@ -45494,7 +45489,7 @@
       <c r="Y351" s="5"/>
       <c r="Z351" s="5"/>
     </row>
-    <row r="352" spans="1:26" ht="17.399999999999999">
+    <row r="352" spans="1:26" ht="16.5">
       <c r="A352" s="7"/>
       <c r="B352" s="7"/>
       <c r="C352" s="7"/>
@@ -45522,7 +45517,7 @@
       <c r="Y352" s="5"/>
       <c r="Z352" s="5"/>
     </row>
-    <row r="353" spans="1:26" ht="17.399999999999999">
+    <row r="353" spans="1:26" ht="16.5">
       <c r="A353" s="7"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
@@ -45550,7 +45545,7 @@
       <c r="Y353" s="5"/>
       <c r="Z353" s="5"/>
     </row>
-    <row r="354" spans="1:26" ht="17.399999999999999">
+    <row r="354" spans="1:26" ht="16.5">
       <c r="A354" s="7"/>
       <c r="B354" s="7"/>
       <c r="C354" s="7"/>
@@ -45578,7 +45573,7 @@
       <c r="Y354" s="5"/>
       <c r="Z354" s="5"/>
     </row>
-    <row r="355" spans="1:26" ht="17.399999999999999">
+    <row r="355" spans="1:26" ht="16.5">
       <c r="A355" s="7"/>
       <c r="B355" s="7"/>
       <c r="C355" s="7"/>
@@ -45606,7 +45601,7 @@
       <c r="Y355" s="5"/>
       <c r="Z355" s="5"/>
     </row>
-    <row r="356" spans="1:26" ht="17.399999999999999">
+    <row r="356" spans="1:26" ht="16.5">
       <c r="A356" s="7"/>
       <c r="B356" s="7"/>
       <c r="C356" s="7"/>
@@ -45634,7 +45629,7 @@
       <c r="Y356" s="5"/>
       <c r="Z356" s="5"/>
     </row>
-    <row r="357" spans="1:26" ht="17.399999999999999">
+    <row r="357" spans="1:26" ht="16.5">
       <c r="A357" s="7"/>
       <c r="B357" s="7"/>
       <c r="C357" s="7"/>
@@ -45662,7 +45657,7 @@
       <c r="Y357" s="5"/>
       <c r="Z357" s="5"/>
     </row>
-    <row r="358" spans="1:26" ht="17.399999999999999">
+    <row r="358" spans="1:26" ht="16.5">
       <c r="A358" s="7"/>
       <c r="B358" s="7"/>
       <c r="C358" s="7"/>
@@ -45690,7 +45685,7 @@
       <c r="Y358" s="5"/>
       <c r="Z358" s="5"/>
     </row>
-    <row r="359" spans="1:26" ht="17.399999999999999">
+    <row r="359" spans="1:26" ht="16.5">
       <c r="A359" s="7"/>
       <c r="B359" s="7"/>
       <c r="C359" s="7"/>
@@ -45718,7 +45713,7 @@
       <c r="Y359" s="5"/>
       <c r="Z359" s="5"/>
     </row>
-    <row r="360" spans="1:26" ht="17.399999999999999">
+    <row r="360" spans="1:26" ht="16.5">
       <c r="A360" s="7"/>
       <c r="B360" s="7"/>
       <c r="C360" s="7"/>
@@ -45746,7 +45741,7 @@
       <c r="Y360" s="5"/>
       <c r="Z360" s="5"/>
     </row>
-    <row r="361" spans="1:26" ht="17.399999999999999">
+    <row r="361" spans="1:26" ht="16.5">
       <c r="A361" s="7"/>
       <c r="B361" s="7"/>
       <c r="C361" s="7"/>
@@ -45774,7 +45769,7 @@
       <c r="Y361" s="5"/>
       <c r="Z361" s="5"/>
     </row>
-    <row r="362" spans="1:26" ht="17.399999999999999">
+    <row r="362" spans="1:26" ht="16.5">
       <c r="A362" s="7"/>
       <c r="B362" s="7"/>
       <c r="C362" s="7"/>
@@ -45802,7 +45797,7 @@
       <c r="Y362" s="5"/>
       <c r="Z362" s="5"/>
     </row>
-    <row r="363" spans="1:26" ht="17.399999999999999">
+    <row r="363" spans="1:26" ht="16.5">
       <c r="A363" s="7"/>
       <c r="B363" s="7"/>
       <c r="C363" s="7"/>
@@ -45830,7 +45825,7 @@
       <c r="Y363" s="5"/>
       <c r="Z363" s="5"/>
     </row>
-    <row r="364" spans="1:26" ht="17.399999999999999">
+    <row r="364" spans="1:26" ht="16.5">
       <c r="A364" s="7"/>
       <c r="B364" s="7"/>
       <c r="C364" s="7"/>
@@ -45858,7 +45853,7 @@
       <c r="Y364" s="5"/>
       <c r="Z364" s="5"/>
     </row>
-    <row r="365" spans="1:26" ht="17.399999999999999">
+    <row r="365" spans="1:26" ht="16.5">
       <c r="A365" s="7"/>
       <c r="B365" s="7"/>
       <c r="C365" s="7"/>
@@ -45886,7 +45881,7 @@
       <c r="Y365" s="5"/>
       <c r="Z365" s="5"/>
     </row>
-    <row r="366" spans="1:26" ht="17.399999999999999">
+    <row r="366" spans="1:26" ht="16.5">
       <c r="A366" s="7"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
@@ -45914,7 +45909,7 @@
       <c r="Y366" s="5"/>
       <c r="Z366" s="5"/>
     </row>
-    <row r="367" spans="1:26" ht="17.399999999999999">
+    <row r="367" spans="1:26" ht="16.5">
       <c r="A367" s="7"/>
       <c r="B367" s="7"/>
       <c r="C367" s="7"/>
@@ -45942,7 +45937,7 @@
       <c r="Y367" s="5"/>
       <c r="Z367" s="5"/>
     </row>
-    <row r="368" spans="1:26" ht="17.399999999999999">
+    <row r="368" spans="1:26" ht="16.5">
       <c r="A368" s="7"/>
       <c r="B368" s="7"/>
       <c r="C368" s="7"/>
@@ -45970,7 +45965,7 @@
       <c r="Y368" s="5"/>
       <c r="Z368" s="5"/>
     </row>
-    <row r="369" spans="1:26" ht="17.399999999999999">
+    <row r="369" spans="1:26" ht="16.5">
       <c r="A369" s="7"/>
       <c r="B369" s="7"/>
       <c r="C369" s="7"/>
@@ -45998,7 +45993,7 @@
       <c r="Y369" s="5"/>
       <c r="Z369" s="5"/>
     </row>
-    <row r="370" spans="1:26" ht="17.399999999999999">
+    <row r="370" spans="1:26" ht="16.5">
       <c r="A370" s="7"/>
       <c r="B370" s="7"/>
       <c r="C370" s="7"/>
@@ -46026,7 +46021,7 @@
       <c r="Y370" s="5"/>
       <c r="Z370" s="5"/>
     </row>
-    <row r="371" spans="1:26" ht="17.399999999999999">
+    <row r="371" spans="1:26" ht="16.5">
       <c r="A371" s="7"/>
       <c r="B371" s="7"/>
       <c r="C371" s="7"/>
@@ -46054,7 +46049,7 @@
       <c r="Y371" s="5"/>
       <c r="Z371" s="5"/>
     </row>
-    <row r="372" spans="1:26" ht="17.399999999999999">
+    <row r="372" spans="1:26" ht="16.5">
       <c r="A372" s="7"/>
       <c r="B372" s="7"/>
       <c r="C372" s="7"/>
@@ -46082,7 +46077,7 @@
       <c r="Y372" s="5"/>
       <c r="Z372" s="5"/>
     </row>
-    <row r="373" spans="1:26" ht="17.399999999999999">
+    <row r="373" spans="1:26" ht="16.5">
       <c r="A373" s="7"/>
       <c r="B373" s="7"/>
       <c r="C373" s="7"/>
@@ -46110,7 +46105,7 @@
       <c r="Y373" s="5"/>
       <c r="Z373" s="5"/>
     </row>
-    <row r="374" spans="1:26" ht="17.399999999999999">
+    <row r="374" spans="1:26" ht="16.5">
       <c r="A374" s="7"/>
       <c r="B374" s="7"/>
       <c r="C374" s="7"/>
@@ -46138,7 +46133,7 @@
       <c r="Y374" s="5"/>
       <c r="Z374" s="5"/>
     </row>
-    <row r="375" spans="1:26" ht="17.399999999999999">
+    <row r="375" spans="1:26" ht="16.5">
       <c r="A375" s="7"/>
       <c r="B375" s="7"/>
       <c r="C375" s="7"/>
@@ -46166,7 +46161,7 @@
       <c r="Y375" s="5"/>
       <c r="Z375" s="5"/>
     </row>
-    <row r="376" spans="1:26" ht="17.399999999999999">
+    <row r="376" spans="1:26" ht="16.5">
       <c r="A376" s="7"/>
       <c r="B376" s="7"/>
       <c r="C376" s="7"/>
@@ -46194,7 +46189,7 @@
       <c r="Y376" s="5"/>
       <c r="Z376" s="5"/>
     </row>
-    <row r="377" spans="1:26" ht="17.399999999999999">
+    <row r="377" spans="1:26" ht="16.5">
       <c r="A377" s="7"/>
       <c r="B377" s="7"/>
       <c r="C377" s="7"/>
@@ -46222,7 +46217,7 @@
       <c r="Y377" s="5"/>
       <c r="Z377" s="5"/>
     </row>
-    <row r="378" spans="1:26" ht="17.399999999999999">
+    <row r="378" spans="1:26" ht="16.5">
       <c r="A378" s="7"/>
       <c r="B378" s="7"/>
       <c r="C378" s="7"/>
@@ -46250,7 +46245,7 @@
       <c r="Y378" s="5"/>
       <c r="Z378" s="5"/>
     </row>
-    <row r="379" spans="1:26" ht="17.399999999999999">
+    <row r="379" spans="1:26" ht="16.5">
       <c r="A379" s="7"/>
       <c r="B379" s="7"/>
       <c r="C379" s="7"/>
@@ -46278,7 +46273,7 @@
       <c r="Y379" s="5"/>
       <c r="Z379" s="5"/>
     </row>
-    <row r="380" spans="1:26" ht="17.399999999999999">
+    <row r="380" spans="1:26" ht="16.5">
       <c r="A380" s="7"/>
       <c r="B380" s="7"/>
       <c r="C380" s="7"/>
@@ -46306,7 +46301,7 @@
       <c r="Y380" s="5"/>
       <c r="Z380" s="5"/>
     </row>
-    <row r="381" spans="1:26" ht="17.399999999999999">
+    <row r="381" spans="1:26" ht="16.5">
       <c r="A381" s="7"/>
       <c r="B381" s="7"/>
       <c r="C381" s="7"/>
@@ -46334,7 +46329,7 @@
       <c r="Y381" s="5"/>
       <c r="Z381" s="5"/>
     </row>
-    <row r="382" spans="1:26" ht="17.399999999999999">
+    <row r="382" spans="1:26" ht="16.5">
       <c r="A382" s="7"/>
       <c r="B382" s="7"/>
       <c r="C382" s="7"/>
@@ -46362,7 +46357,7 @@
       <c r="Y382" s="5"/>
       <c r="Z382" s="5"/>
     </row>
-    <row r="383" spans="1:26" ht="17.399999999999999">
+    <row r="383" spans="1:26" ht="16.5">
       <c r="A383" s="7"/>
       <c r="B383" s="7"/>
       <c r="C383" s="7"/>
@@ -46390,7 +46385,7 @@
       <c r="Y383" s="5"/>
       <c r="Z383" s="5"/>
     </row>
-    <row r="384" spans="1:26" ht="17.399999999999999">
+    <row r="384" spans="1:26" ht="16.5">
       <c r="A384" s="7"/>
       <c r="B384" s="7"/>
       <c r="C384" s="7"/>
@@ -46418,7 +46413,7 @@
       <c r="Y384" s="5"/>
       <c r="Z384" s="5"/>
     </row>
-    <row r="385" spans="1:26" ht="17.399999999999999">
+    <row r="385" spans="1:26" ht="16.5">
       <c r="A385" s="7"/>
       <c r="B385" s="7"/>
       <c r="C385" s="7"/>
@@ -46446,7 +46441,7 @@
       <c r="Y385" s="5"/>
       <c r="Z385" s="5"/>
     </row>
-    <row r="386" spans="1:26" ht="17.399999999999999">
+    <row r="386" spans="1:26" ht="16.5">
       <c r="A386" s="7"/>
       <c r="B386" s="7"/>
       <c r="C386" s="7"/>
@@ -46474,7 +46469,7 @@
       <c r="Y386" s="5"/>
       <c r="Z386" s="5"/>
     </row>
-    <row r="387" spans="1:26" ht="17.399999999999999">
+    <row r="387" spans="1:26" ht="16.5">
       <c r="A387" s="7"/>
       <c r="B387" s="7"/>
       <c r="C387" s="7"/>
@@ -46502,7 +46497,7 @@
       <c r="Y387" s="5"/>
       <c r="Z387" s="5"/>
     </row>
-    <row r="388" spans="1:26" ht="17.399999999999999">
+    <row r="388" spans="1:26" ht="16.5">
       <c r="A388" s="7"/>
       <c r="B388" s="7"/>
       <c r="C388" s="7"/>
@@ -46530,7 +46525,7 @@
       <c r="Y388" s="5"/>
       <c r="Z388" s="5"/>
     </row>
-    <row r="389" spans="1:26" ht="17.399999999999999">
+    <row r="389" spans="1:26" ht="16.5">
       <c r="A389" s="7"/>
       <c r="B389" s="7"/>
       <c r="C389" s="7"/>
@@ -46558,7 +46553,7 @@
       <c r="Y389" s="5"/>
       <c r="Z389" s="5"/>
     </row>
-    <row r="390" spans="1:26" ht="17.399999999999999">
+    <row r="390" spans="1:26" ht="16.5">
       <c r="A390" s="7"/>
       <c r="B390" s="7"/>
       <c r="C390" s="7"/>
@@ -46586,7 +46581,7 @@
       <c r="Y390" s="5"/>
       <c r="Z390" s="5"/>
     </row>
-    <row r="391" spans="1:26" ht="17.399999999999999">
+    <row r="391" spans="1:26" ht="16.5">
       <c r="A391" s="7"/>
       <c r="B391" s="7"/>
       <c r="C391" s="7"/>
@@ -46614,7 +46609,7 @@
       <c r="Y391" s="5"/>
       <c r="Z391" s="5"/>
     </row>
-    <row r="392" spans="1:26" ht="17.399999999999999">
+    <row r="392" spans="1:26" ht="16.5">
       <c r="A392" s="7"/>
       <c r="B392" s="7"/>
       <c r="C392" s="7"/>
@@ -46642,7 +46637,7 @@
       <c r="Y392" s="5"/>
       <c r="Z392" s="5"/>
     </row>
-    <row r="393" spans="1:26" ht="17.399999999999999">
+    <row r="393" spans="1:26" ht="16.5">
       <c r="A393" s="7"/>
       <c r="B393" s="7"/>
       <c r="C393" s="7"/>
@@ -46670,7 +46665,7 @@
       <c r="Y393" s="5"/>
       <c r="Z393" s="5"/>
     </row>
-    <row r="394" spans="1:26" ht="17.399999999999999">
+    <row r="394" spans="1:26" ht="16.5">
       <c r="A394" s="7"/>
       <c r="B394" s="7"/>
       <c r="C394" s="7"/>
@@ -46698,7 +46693,7 @@
       <c r="Y394" s="5"/>
       <c r="Z394" s="5"/>
     </row>
-    <row r="395" spans="1:26" ht="17.399999999999999">
+    <row r="395" spans="1:26" ht="16.5">
       <c r="A395" s="7"/>
       <c r="B395" s="7"/>
       <c r="C395" s="7"/>
@@ -46726,7 +46721,7 @@
       <c r="Y395" s="5"/>
       <c r="Z395" s="5"/>
     </row>
-    <row r="396" spans="1:26" ht="17.399999999999999">
+    <row r="396" spans="1:26" ht="16.5">
       <c r="A396" s="7"/>
       <c r="B396" s="7"/>
       <c r="C396" s="7"/>
@@ -46754,7 +46749,7 @@
       <c r="Y396" s="5"/>
       <c r="Z396" s="5"/>
     </row>
-    <row r="397" spans="1:26" ht="17.399999999999999">
+    <row r="397" spans="1:26" ht="16.5">
       <c r="A397" s="7"/>
       <c r="B397" s="7"/>
       <c r="C397" s="7"/>
@@ -46782,7 +46777,7 @@
       <c r="Y397" s="5"/>
       <c r="Z397" s="5"/>
     </row>
-    <row r="398" spans="1:26" ht="17.399999999999999">
+    <row r="398" spans="1:26" ht="16.5">
       <c r="A398" s="7"/>
       <c r="B398" s="7"/>
       <c r="C398" s="7"/>
@@ -46810,7 +46805,7 @@
       <c r="Y398" s="5"/>
       <c r="Z398" s="5"/>
     </row>
-    <row r="399" spans="1:26" ht="17.399999999999999">
+    <row r="399" spans="1:26" ht="16.5">
       <c r="A399" s="7"/>
       <c r="B399" s="7"/>
       <c r="C399" s="7"/>
@@ -46838,7 +46833,7 @@
       <c r="Y399" s="5"/>
       <c r="Z399" s="5"/>
     </row>
-    <row r="400" spans="1:26" ht="17.399999999999999">
+    <row r="400" spans="1:26" ht="16.5">
       <c r="A400" s="7"/>
       <c r="B400" s="7"/>
       <c r="C400" s="7"/>
@@ -46866,7 +46861,7 @@
       <c r="Y400" s="5"/>
       <c r="Z400" s="5"/>
     </row>
-    <row r="401" spans="1:26" ht="17.399999999999999">
+    <row r="401" spans="1:26" ht="16.5">
       <c r="A401" s="7"/>
       <c r="B401" s="7"/>
       <c r="C401" s="7"/>
@@ -46894,7 +46889,7 @@
       <c r="Y401" s="5"/>
       <c r="Z401" s="5"/>
     </row>
-    <row r="402" spans="1:26" ht="17.399999999999999">
+    <row r="402" spans="1:26" ht="16.5">
       <c r="A402" s="7"/>
       <c r="B402" s="7"/>
       <c r="C402" s="7"/>
@@ -46922,7 +46917,7 @@
       <c r="Y402" s="5"/>
       <c r="Z402" s="5"/>
     </row>
-    <row r="403" spans="1:26" ht="17.399999999999999">
+    <row r="403" spans="1:26" ht="16.5">
       <c r="A403" s="7"/>
       <c r="B403" s="7"/>
       <c r="C403" s="7"/>
@@ -46950,7 +46945,7 @@
       <c r="Y403" s="5"/>
       <c r="Z403" s="5"/>
     </row>
-    <row r="404" spans="1:26" ht="17.399999999999999">
+    <row r="404" spans="1:26" ht="16.5">
       <c r="A404" s="7"/>
       <c r="B404" s="7"/>
       <c r="C404" s="7"/>
@@ -46978,7 +46973,7 @@
       <c r="Y404" s="5"/>
       <c r="Z404" s="5"/>
     </row>
-    <row r="405" spans="1:26" ht="17.399999999999999">
+    <row r="405" spans="1:26" ht="16.5">
       <c r="A405" s="7"/>
       <c r="B405" s="7"/>
       <c r="C405" s="7"/>
@@ -47006,7 +47001,7 @@
       <c r="Y405" s="5"/>
       <c r="Z405" s="5"/>
     </row>
-    <row r="406" spans="1:26" ht="17.399999999999999">
+    <row r="406" spans="1:26" ht="16.5">
       <c r="A406" s="7"/>
       <c r="B406" s="7"/>
       <c r="C406" s="7"/>
@@ -47034,7 +47029,7 @@
       <c r="Y406" s="5"/>
       <c r="Z406" s="5"/>
     </row>
-    <row r="407" spans="1:26" ht="17.399999999999999">
+    <row r="407" spans="1:26" ht="16.5">
       <c r="A407" s="7"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
@@ -47062,7 +47057,7 @@
       <c r="Y407" s="5"/>
       <c r="Z407" s="5"/>
     </row>
-    <row r="408" spans="1:26" ht="17.399999999999999">
+    <row r="408" spans="1:26" ht="16.5">
       <c r="A408" s="7"/>
       <c r="B408" s="7"/>
       <c r="C408" s="7"/>
@@ -47090,7 +47085,7 @@
       <c r="Y408" s="5"/>
       <c r="Z408" s="5"/>
     </row>
-    <row r="409" spans="1:26" ht="17.399999999999999">
+    <row r="409" spans="1:26" ht="16.5">
       <c r="A409" s="7"/>
       <c r="B409" s="7"/>
       <c r="C409" s="7"/>
@@ -47118,7 +47113,7 @@
       <c r="Y409" s="5"/>
       <c r="Z409" s="5"/>
     </row>
-    <row r="410" spans="1:26" ht="17.399999999999999">
+    <row r="410" spans="1:26" ht="16.5">
       <c r="A410" s="7"/>
       <c r="B410" s="7"/>
       <c r="C410" s="7"/>
@@ -47146,7 +47141,7 @@
       <c r="Y410" s="5"/>
       <c r="Z410" s="5"/>
     </row>
-    <row r="411" spans="1:26" ht="17.399999999999999">
+    <row r="411" spans="1:26" ht="16.5">
       <c r="A411" s="7"/>
       <c r="B411" s="7"/>
       <c r="C411" s="7"/>
@@ -47174,7 +47169,7 @@
       <c r="Y411" s="5"/>
       <c r="Z411" s="5"/>
     </row>
-    <row r="412" spans="1:26" ht="17.399999999999999">
+    <row r="412" spans="1:26" ht="16.5">
       <c r="A412" s="7"/>
       <c r="B412" s="7"/>
       <c r="C412" s="7"/>
@@ -47202,7 +47197,7 @@
       <c r="Y412" s="5"/>
       <c r="Z412" s="5"/>
     </row>
-    <row r="413" spans="1:26" ht="17.399999999999999">
+    <row r="413" spans="1:26" ht="16.5">
       <c r="A413" s="7"/>
       <c r="B413" s="7"/>
       <c r="C413" s="7"/>
@@ -47230,7 +47225,7 @@
       <c r="Y413" s="5"/>
       <c r="Z413" s="5"/>
     </row>
-    <row r="414" spans="1:26" ht="17.399999999999999">
+    <row r="414" spans="1:26" ht="16.5">
       <c r="A414" s="7"/>
       <c r="B414" s="7"/>
       <c r="C414" s="7"/>
@@ -47258,7 +47253,7 @@
       <c r="Y414" s="5"/>
       <c r="Z414" s="5"/>
     </row>
-    <row r="415" spans="1:26" ht="17.399999999999999">
+    <row r="415" spans="1:26" ht="16.5">
       <c r="A415" s="7"/>
       <c r="B415" s="7"/>
       <c r="C415" s="7"/>
@@ -47286,7 +47281,7 @@
       <c r="Y415" s="5"/>
       <c r="Z415" s="5"/>
     </row>
-    <row r="416" spans="1:26" ht="17.399999999999999">
+    <row r="416" spans="1:26" ht="16.5">
       <c r="A416" s="7"/>
       <c r="B416" s="7"/>
       <c r="C416" s="7"/>
@@ -47314,7 +47309,7 @@
       <c r="Y416" s="5"/>
       <c r="Z416" s="5"/>
     </row>
-    <row r="417" spans="1:26" ht="17.399999999999999">
+    <row r="417" spans="1:26" ht="16.5">
       <c r="A417" s="7"/>
       <c r="B417" s="7"/>
       <c r="C417" s="7"/>
@@ -47342,7 +47337,7 @@
       <c r="Y417" s="5"/>
       <c r="Z417" s="5"/>
     </row>
-    <row r="418" spans="1:26" ht="17.399999999999999">
+    <row r="418" spans="1:26" ht="16.5">
       <c r="A418" s="7"/>
       <c r="B418" s="7"/>
       <c r="C418" s="7"/>
@@ -47370,7 +47365,7 @@
       <c r="Y418" s="5"/>
       <c r="Z418" s="5"/>
     </row>
-    <row r="419" spans="1:26" ht="17.399999999999999">
+    <row r="419" spans="1:26" ht="16.5">
       <c r="A419" s="7"/>
       <c r="B419" s="7"/>
       <c r="C419" s="7"/>
@@ -47398,7 +47393,7 @@
       <c r="Y419" s="5"/>
       <c r="Z419" s="5"/>
     </row>
-    <row r="420" spans="1:26" ht="17.399999999999999">
+    <row r="420" spans="1:26" ht="16.5">
       <c r="A420" s="7"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
@@ -47426,7 +47421,7 @@
       <c r="Y420" s="5"/>
       <c r="Z420" s="5"/>
     </row>
-    <row r="421" spans="1:26" ht="17.399999999999999">
+    <row r="421" spans="1:26" ht="16.5">
       <c r="A421" s="7"/>
       <c r="B421" s="7"/>
       <c r="C421" s="7"/>
@@ -47454,7 +47449,7 @@
       <c r="Y421" s="5"/>
       <c r="Z421" s="5"/>
     </row>
-    <row r="422" spans="1:26" ht="17.399999999999999">
+    <row r="422" spans="1:26" ht="16.5">
       <c r="A422" s="7"/>
       <c r="B422" s="7"/>
       <c r="C422" s="7"/>
@@ -47482,7 +47477,7 @@
       <c r="Y422" s="5"/>
       <c r="Z422" s="5"/>
     </row>
-    <row r="423" spans="1:26" ht="17.399999999999999">
+    <row r="423" spans="1:26" ht="16.5">
       <c r="A423" s="7"/>
       <c r="B423" s="7"/>
       <c r="C423" s="7"/>
@@ -47510,7 +47505,7 @@
       <c r="Y423" s="5"/>
       <c r="Z423" s="5"/>
     </row>
-    <row r="424" spans="1:26" ht="17.399999999999999">
+    <row r="424" spans="1:26" ht="16.5">
       <c r="A424" s="7"/>
       <c r="B424" s="7"/>
       <c r="C424" s="7"/>
@@ -47538,7 +47533,7 @@
       <c r="Y424" s="5"/>
       <c r="Z424" s="5"/>
     </row>
-    <row r="425" spans="1:26" ht="17.399999999999999">
+    <row r="425" spans="1:26" ht="16.5">
       <c r="A425" s="7"/>
       <c r="B425" s="7"/>
       <c r="C425" s="7"/>
@@ -47566,7 +47561,7 @@
       <c r="Y425" s="5"/>
       <c r="Z425" s="5"/>
     </row>
-    <row r="426" spans="1:26" ht="17.399999999999999">
+    <row r="426" spans="1:26" ht="16.5">
       <c r="A426" s="7"/>
       <c r="B426" s="7"/>
       <c r="C426" s="7"/>
@@ -47594,7 +47589,7 @@
       <c r="Y426" s="5"/>
       <c r="Z426" s="5"/>
     </row>
-    <row r="427" spans="1:26" ht="17.399999999999999">
+    <row r="427" spans="1:26" ht="16.5">
       <c r="A427" s="7"/>
       <c r="B427" s="7"/>
       <c r="C427" s="7"/>
@@ -47622,7 +47617,7 @@
       <c r="Y427" s="5"/>
       <c r="Z427" s="5"/>
     </row>
-    <row r="428" spans="1:26" ht="17.399999999999999">
+    <row r="428" spans="1:26" ht="16.5">
       <c r="A428" s="7"/>
       <c r="B428" s="7"/>
       <c r="C428" s="7"/>
@@ -47650,7 +47645,7 @@
       <c r="Y428" s="5"/>
       <c r="Z428" s="5"/>
     </row>
-    <row r="429" spans="1:26" ht="17.399999999999999">
+    <row r="429" spans="1:26" ht="16.5">
       <c r="A429" s="7"/>
       <c r="B429" s="7"/>
       <c r="C429" s="7"/>
@@ -47678,7 +47673,7 @@
       <c r="Y429" s="5"/>
       <c r="Z429" s="5"/>
     </row>
-    <row r="430" spans="1:26" ht="17.399999999999999">
+    <row r="430" spans="1:26" ht="16.5">
       <c r="A430" s="7"/>
       <c r="B430" s="7"/>
       <c r="C430" s="7"/>
@@ -47706,7 +47701,7 @@
       <c r="Y430" s="5"/>
       <c r="Z430" s="5"/>
     </row>
-    <row r="431" spans="1:26" ht="17.399999999999999">
+    <row r="431" spans="1:26" ht="16.5">
       <c r="A431" s="7"/>
       <c r="B431" s="7"/>
       <c r="C431" s="7"/>
@@ -47734,7 +47729,7 @@
       <c r="Y431" s="5"/>
       <c r="Z431" s="5"/>
     </row>
-    <row r="432" spans="1:26" ht="17.399999999999999">
+    <row r="432" spans="1:26" ht="16.5">
       <c r="A432" s="7"/>
       <c r="B432" s="7"/>
       <c r="C432" s="7"/>
@@ -47762,7 +47757,7 @@
       <c r="Y432" s="5"/>
       <c r="Z432" s="5"/>
     </row>
-    <row r="433" spans="1:26" ht="17.399999999999999">
+    <row r="433" spans="1:26" ht="16.5">
       <c r="A433" s="7"/>
       <c r="B433" s="7"/>
       <c r="C433" s="7"/>
@@ -47790,7 +47785,7 @@
       <c r="Y433" s="5"/>
       <c r="Z433" s="5"/>
     </row>
-    <row r="434" spans="1:26" ht="17.399999999999999">
+    <row r="434" spans="1:26" ht="16.5">
       <c r="A434" s="7"/>
       <c r="B434" s="7"/>
       <c r="C434" s="7"/>
@@ -47818,7 +47813,7 @@
       <c r="Y434" s="5"/>
       <c r="Z434" s="5"/>
     </row>
-    <row r="435" spans="1:26" ht="17.399999999999999">
+    <row r="435" spans="1:26" ht="16.5">
       <c r="A435" s="7"/>
       <c r="B435" s="7"/>
       <c r="C435" s="7"/>
@@ -47846,7 +47841,7 @@
       <c r="Y435" s="5"/>
       <c r="Z435" s="5"/>
     </row>
-    <row r="436" spans="1:26" ht="17.399999999999999">
+    <row r="436" spans="1:26" ht="16.5">
       <c r="A436" s="7"/>
       <c r="B436" s="7"/>
       <c r="C436" s="7"/>
@@ -47874,7 +47869,7 @@
       <c r="Y436" s="5"/>
       <c r="Z436" s="5"/>
     </row>
-    <row r="437" spans="1:26" ht="17.399999999999999">
+    <row r="437" spans="1:26" ht="16.5">
       <c r="A437" s="7"/>
       <c r="B437" s="7"/>
       <c r="C437" s="7"/>
@@ -47902,7 +47897,7 @@
       <c r="Y437" s="5"/>
       <c r="Z437" s="5"/>
     </row>
-    <row r="438" spans="1:26" ht="17.399999999999999">
+    <row r="438" spans="1:26" ht="16.5">
       <c r="A438" s="7"/>
       <c r="B438" s="7"/>
       <c r="C438" s="7"/>
@@ -47930,7 +47925,7 @@
       <c r="Y438" s="5"/>
       <c r="Z438" s="5"/>
     </row>
-    <row r="439" spans="1:26" ht="17.399999999999999">
+    <row r="439" spans="1:26" ht="16.5">
       <c r="A439" s="7"/>
       <c r="B439" s="7"/>
       <c r="C439" s="7"/>
@@ -47958,7 +47953,7 @@
       <c r="Y439" s="5"/>
       <c r="Z439" s="5"/>
     </row>
-    <row r="440" spans="1:26" ht="17.399999999999999">
+    <row r="440" spans="1:26" ht="16.5">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
       <c r="C440" s="7"/>
@@ -47986,7 +47981,7 @@
       <c r="Y440" s="5"/>
       <c r="Z440" s="5"/>
     </row>
-    <row r="441" spans="1:26" ht="17.399999999999999">
+    <row r="441" spans="1:26" ht="16.5">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
       <c r="C441" s="7"/>
@@ -48014,7 +48009,7 @@
       <c r="Y441" s="5"/>
       <c r="Z441" s="5"/>
     </row>
-    <row r="442" spans="1:26" ht="17.399999999999999">
+    <row r="442" spans="1:26" ht="16.5">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
       <c r="C442" s="7"/>
@@ -48042,7 +48037,7 @@
       <c r="Y442" s="5"/>
       <c r="Z442" s="5"/>
     </row>
-    <row r="443" spans="1:26" ht="17.399999999999999">
+    <row r="443" spans="1:26" ht="16.5">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
       <c r="C443" s="7"/>
@@ -48070,7 +48065,7 @@
       <c r="Y443" s="5"/>
       <c r="Z443" s="5"/>
     </row>
-    <row r="444" spans="1:26" ht="17.399999999999999">
+    <row r="444" spans="1:26" ht="16.5">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
       <c r="C444" s="7"/>
@@ -48098,7 +48093,7 @@
       <c r="Y444" s="5"/>
       <c r="Z444" s="5"/>
     </row>
-    <row r="445" spans="1:26" ht="17.399999999999999">
+    <row r="445" spans="1:26" ht="16.5">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
       <c r="C445" s="7"/>
@@ -48126,7 +48121,7 @@
       <c r="Y445" s="5"/>
       <c r="Z445" s="5"/>
     </row>
-    <row r="446" spans="1:26" ht="17.399999999999999">
+    <row r="446" spans="1:26" ht="16.5">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
       <c r="C446" s="7"/>
@@ -48154,7 +48149,7 @@
       <c r="Y446" s="5"/>
       <c r="Z446" s="5"/>
     </row>
-    <row r="447" spans="1:26" ht="17.399999999999999">
+    <row r="447" spans="1:26" ht="16.5">
       <c r="A447" s="7"/>
       <c r="B447" s="7"/>
       <c r="C447" s="7"/>
@@ -48182,7 +48177,7 @@
       <c r="Y447" s="5"/>
       <c r="Z447" s="5"/>
     </row>
-    <row r="448" spans="1:26" ht="17.399999999999999">
+    <row r="448" spans="1:26" ht="16.5">
       <c r="A448" s="7"/>
       <c r="B448" s="7"/>
       <c r="C448" s="7"/>
@@ -48210,7 +48205,7 @@
       <c r="Y448" s="5"/>
       <c r="Z448" s="5"/>
     </row>
-    <row r="449" spans="1:26" ht="17.399999999999999">
+    <row r="449" spans="1:26" ht="16.5">
       <c r="A449" s="7"/>
       <c r="B449" s="7"/>
       <c r="C449" s="7"/>
@@ -48238,7 +48233,7 @@
       <c r="Y449" s="5"/>
       <c r="Z449" s="5"/>
     </row>
-    <row r="450" spans="1:26" ht="17.399999999999999">
+    <row r="450" spans="1:26" ht="16.5">
       <c r="A450" s="7"/>
       <c r="B450" s="7"/>
       <c r="C450" s="7"/>
@@ -48266,7 +48261,7 @@
       <c r="Y450" s="5"/>
       <c r="Z450" s="5"/>
     </row>
-    <row r="451" spans="1:26" ht="17.399999999999999">
+    <row r="451" spans="1:26" ht="16.5">
       <c r="A451" s="7"/>
       <c r="B451" s="7"/>
       <c r="C451" s="7"/>
@@ -48294,7 +48289,7 @@
       <c r="Y451" s="5"/>
       <c r="Z451" s="5"/>
     </row>
-    <row r="452" spans="1:26" ht="17.399999999999999">
+    <row r="452" spans="1:26" ht="16.5">
       <c r="A452" s="7"/>
       <c r="B452" s="7"/>
       <c r="C452" s="7"/>
@@ -48322,7 +48317,7 @@
       <c r="Y452" s="5"/>
       <c r="Z452" s="5"/>
     </row>
-    <row r="453" spans="1:26" ht="17.399999999999999">
+    <row r="453" spans="1:26" ht="16.5">
       <c r="A453" s="7"/>
       <c r="B453" s="7"/>
       <c r="C453" s="7"/>
@@ -48350,7 +48345,7 @@
       <c r="Y453" s="5"/>
       <c r="Z453" s="5"/>
     </row>
-    <row r="454" spans="1:26" ht="17.399999999999999">
+    <row r="454" spans="1:26" ht="16.5">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="7"/>
@@ -48378,7 +48373,7 @@
       <c r="Y454" s="5"/>
       <c r="Z454" s="5"/>
     </row>
-    <row r="455" spans="1:26" ht="17.399999999999999">
+    <row r="455" spans="1:26" ht="16.5">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="7"/>
@@ -48406,7 +48401,7 @@
       <c r="Y455" s="5"/>
       <c r="Z455" s="5"/>
     </row>
-    <row r="456" spans="1:26" ht="17.399999999999999">
+    <row r="456" spans="1:26" ht="16.5">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="7"/>
@@ -48434,7 +48429,7 @@
       <c r="Y456" s="5"/>
       <c r="Z456" s="5"/>
     </row>
-    <row r="457" spans="1:26" ht="17.399999999999999">
+    <row r="457" spans="1:26" ht="16.5">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="7"/>
@@ -48462,7 +48457,7 @@
       <c r="Y457" s="5"/>
       <c r="Z457" s="5"/>
     </row>
-    <row r="458" spans="1:26" ht="17.399999999999999">
+    <row r="458" spans="1:26" ht="16.5">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="7"/>
@@ -48490,7 +48485,7 @@
       <c r="Y458" s="5"/>
       <c r="Z458" s="5"/>
     </row>
-    <row r="459" spans="1:26" ht="17.399999999999999">
+    <row r="459" spans="1:26" ht="16.5">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="7"/>
@@ -48518,7 +48513,7 @@
       <c r="Y459" s="5"/>
       <c r="Z459" s="5"/>
     </row>
-    <row r="460" spans="1:26" ht="17.399999999999999">
+    <row r="460" spans="1:26" ht="16.5">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="7"/>
@@ -48546,7 +48541,7 @@
       <c r="Y460" s="5"/>
       <c r="Z460" s="5"/>
     </row>
-    <row r="461" spans="1:26" ht="17.399999999999999">
+    <row r="461" spans="1:26" ht="16.5">
       <c r="A461" s="7"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
@@ -48574,7 +48569,7 @@
       <c r="Y461" s="5"/>
       <c r="Z461" s="5"/>
     </row>
-    <row r="462" spans="1:26" ht="17.399999999999999">
+    <row r="462" spans="1:26" ht="16.5">
       <c r="A462" s="7"/>
       <c r="B462" s="7"/>
       <c r="C462" s="7"/>
@@ -48602,7 +48597,7 @@
       <c r="Y462" s="5"/>
       <c r="Z462" s="5"/>
     </row>
-    <row r="463" spans="1:26" ht="17.399999999999999">
+    <row r="463" spans="1:26" ht="16.5">
       <c r="A463" s="7"/>
       <c r="B463" s="7"/>
       <c r="C463" s="7"/>
@@ -48630,7 +48625,7 @@
       <c r="Y463" s="5"/>
       <c r="Z463" s="5"/>
     </row>
-    <row r="464" spans="1:26" ht="17.399999999999999">
+    <row r="464" spans="1:26" ht="16.5">
       <c r="A464" s="7"/>
       <c r="B464" s="7"/>
       <c r="C464" s="7"/>
@@ -48658,7 +48653,7 @@
       <c r="Y464" s="5"/>
       <c r="Z464" s="5"/>
     </row>
-    <row r="465" spans="1:26" ht="17.399999999999999">
+    <row r="465" spans="1:26" ht="16.5">
       <c r="A465" s="7"/>
       <c r="B465" s="7"/>
       <c r="C465" s="7"/>
@@ -48686,7 +48681,7 @@
       <c r="Y465" s="5"/>
       <c r="Z465" s="5"/>
     </row>
-    <row r="466" spans="1:26" ht="17.399999999999999">
+    <row r="466" spans="1:26" ht="16.5">
       <c r="A466" s="7"/>
       <c r="B466" s="7"/>
       <c r="C466" s="7"/>
@@ -48714,7 +48709,7 @@
       <c r="Y466" s="5"/>
       <c r="Z466" s="5"/>
     </row>
-    <row r="467" spans="1:26" ht="17.399999999999999">
+    <row r="467" spans="1:26" ht="16.5">
       <c r="A467" s="7"/>
       <c r="B467" s="7"/>
       <c r="C467" s="7"/>
@@ -48742,7 +48737,7 @@
       <c r="Y467" s="5"/>
       <c r="Z467" s="5"/>
     </row>
-    <row r="468" spans="1:26" ht="17.399999999999999">
+    <row r="468" spans="1:26" ht="16.5">
       <c r="A468" s="7"/>
       <c r="B468" s="7"/>
       <c r="C468" s="7"/>
@@ -48770,7 +48765,7 @@
       <c r="Y468" s="5"/>
       <c r="Z468" s="5"/>
     </row>
-    <row r="469" spans="1:26" ht="17.399999999999999">
+    <row r="469" spans="1:26" ht="16.5">
       <c r="A469" s="7"/>
       <c r="B469" s="7"/>
       <c r="C469" s="7"/>
@@ -48798,7 +48793,7 @@
       <c r="Y469" s="5"/>
       <c r="Z469" s="5"/>
     </row>
-    <row r="470" spans="1:26" ht="17.399999999999999">
+    <row r="470" spans="1:26" ht="16.5">
       <c r="A470" s="7"/>
       <c r="B470" s="7"/>
       <c r="C470" s="7"/>
@@ -48826,7 +48821,7 @@
       <c r="Y470" s="5"/>
       <c r="Z470" s="5"/>
     </row>
-    <row r="471" spans="1:26" ht="17.399999999999999">
+    <row r="471" spans="1:26" ht="16.5">
       <c r="A471" s="7"/>
       <c r="B471" s="7"/>
       <c r="C471" s="7"/>
@@ -48854,7 +48849,7 @@
       <c r="Y471" s="5"/>
       <c r="Z471" s="5"/>
     </row>
-    <row r="472" spans="1:26" ht="17.399999999999999">
+    <row r="472" spans="1:26" ht="16.5">
       <c r="A472" s="7"/>
       <c r="B472" s="7"/>
       <c r="C472" s="7"/>
@@ -48882,7 +48877,7 @@
       <c r="Y472" s="5"/>
       <c r="Z472" s="5"/>
     </row>
-    <row r="473" spans="1:26" ht="17.399999999999999">
+    <row r="473" spans="1:26" ht="16.5">
       <c r="A473" s="7"/>
       <c r="B473" s="7"/>
       <c r="C473" s="7"/>
@@ -48910,7 +48905,7 @@
       <c r="Y473" s="5"/>
       <c r="Z473" s="5"/>
     </row>
-    <row r="474" spans="1:26" ht="17.399999999999999">
+    <row r="474" spans="1:26" ht="16.5">
       <c r="A474" s="7"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
@@ -48938,7 +48933,7 @@
       <c r="Y474" s="5"/>
       <c r="Z474" s="5"/>
     </row>
-    <row r="475" spans="1:26" ht="17.399999999999999">
+    <row r="475" spans="1:26" ht="16.5">
       <c r="A475" s="7"/>
       <c r="B475" s="7"/>
       <c r="C475" s="7"/>
@@ -48966,7 +48961,7 @@
       <c r="Y475" s="5"/>
       <c r="Z475" s="5"/>
     </row>
-    <row r="476" spans="1:26" ht="17.399999999999999">
+    <row r="476" spans="1:26" ht="16.5">
       <c r="A476" s="7"/>
       <c r="B476" s="7"/>
       <c r="C476" s="7"/>
@@ -48994,7 +48989,7 @@
       <c r="Y476" s="5"/>
       <c r="Z476" s="5"/>
     </row>
-    <row r="477" spans="1:26" ht="17.399999999999999">
+    <row r="477" spans="1:26" ht="16.5">
       <c r="A477" s="7"/>
       <c r="B477" s="7"/>
       <c r="C477" s="7"/>
@@ -49022,7 +49017,7 @@
       <c r="Y477" s="5"/>
       <c r="Z477" s="5"/>
     </row>
-    <row r="478" spans="1:26" ht="17.399999999999999">
+    <row r="478" spans="1:26" ht="16.5">
       <c r="A478" s="7"/>
       <c r="B478" s="7"/>
       <c r="C478" s="7"/>
@@ -49050,7 +49045,7 @@
       <c r="Y478" s="5"/>
       <c r="Z478" s="5"/>
     </row>
-    <row r="479" spans="1:26" ht="17.399999999999999">
+    <row r="479" spans="1:26" ht="16.5">
       <c r="A479" s="7"/>
       <c r="B479" s="7"/>
       <c r="C479" s="7"/>
@@ -49078,7 +49073,7 @@
       <c r="Y479" s="5"/>
       <c r="Z479" s="5"/>
     </row>
-    <row r="480" spans="1:26" ht="17.399999999999999">
+    <row r="480" spans="1:26" ht="16.5">
       <c r="A480" s="7"/>
       <c r="B480" s="7"/>
       <c r="C480" s="7"/>
@@ -49106,7 +49101,7 @@
       <c r="Y480" s="5"/>
       <c r="Z480" s="5"/>
     </row>
-    <row r="481" spans="1:26" ht="17.399999999999999">
+    <row r="481" spans="1:26" ht="16.5">
       <c r="A481" s="7"/>
       <c r="B481" s="7"/>
       <c r="C481" s="7"/>
@@ -49134,7 +49129,7 @@
       <c r="Y481" s="5"/>
       <c r="Z481" s="5"/>
     </row>
-    <row r="482" spans="1:26" ht="17.399999999999999">
+    <row r="482" spans="1:26" ht="16.5">
       <c r="A482" s="7"/>
       <c r="B482" s="7"/>
       <c r="C482" s="7"/>
@@ -49162,7 +49157,7 @@
       <c r="Y482" s="5"/>
       <c r="Z482" s="5"/>
     </row>
-    <row r="483" spans="1:26" ht="17.399999999999999">
+    <row r="483" spans="1:26" ht="16.5">
       <c r="A483" s="7"/>
       <c r="B483" s="7"/>
       <c r="C483" s="7"/>
@@ -49190,7 +49185,7 @@
       <c r="Y483" s="5"/>
       <c r="Z483" s="5"/>
     </row>
-    <row r="484" spans="1:26" ht="17.399999999999999">
+    <row r="484" spans="1:26" ht="16.5">
       <c r="A484" s="7"/>
       <c r="B484" s="7"/>
       <c r="C484" s="7"/>
@@ -49218,7 +49213,7 @@
       <c r="Y484" s="5"/>
       <c r="Z484" s="5"/>
     </row>
-    <row r="485" spans="1:26" ht="17.399999999999999">
+    <row r="485" spans="1:26" ht="16.5">
       <c r="A485" s="7"/>
       <c r="B485" s="7"/>
       <c r="C485" s="7"/>
@@ -49246,7 +49241,7 @@
       <c r="Y485" s="5"/>
       <c r="Z485" s="5"/>
     </row>
-    <row r="486" spans="1:26" ht="17.399999999999999">
+    <row r="486" spans="1:26" ht="16.5">
       <c r="A486" s="7"/>
       <c r="B486" s="7"/>
       <c r="C486" s="7"/>
@@ -49274,7 +49269,7 @@
       <c r="Y486" s="5"/>
       <c r="Z486" s="5"/>
     </row>
-    <row r="487" spans="1:26" ht="17.399999999999999">
+    <row r="487" spans="1:26" ht="16.5">
       <c r="A487" s="7"/>
       <c r="B487" s="7"/>
       <c r="C487" s="7"/>
@@ -49302,7 +49297,7 @@
       <c r="Y487" s="5"/>
       <c r="Z487" s="5"/>
     </row>
-    <row r="488" spans="1:26" ht="17.399999999999999">
+    <row r="488" spans="1:26" ht="16.5">
       <c r="A488" s="7"/>
       <c r="B488" s="7"/>
       <c r="C488" s="7"/>
@@ -49330,7 +49325,7 @@
       <c r="Y488" s="5"/>
       <c r="Z488" s="5"/>
     </row>
-    <row r="489" spans="1:26" ht="17.399999999999999">
+    <row r="489" spans="1:26" ht="16.5">
       <c r="A489" s="7"/>
       <c r="B489" s="7"/>
       <c r="C489" s="7"/>
@@ -49358,7 +49353,7 @@
       <c r="Y489" s="5"/>
       <c r="Z489" s="5"/>
     </row>
-    <row r="490" spans="1:26" ht="17.399999999999999">
+    <row r="490" spans="1:26" ht="16.5">
       <c r="A490" s="7"/>
       <c r="B490" s="7"/>
       <c r="C490" s="7"/>
@@ -49386,7 +49381,7 @@
       <c r="Y490" s="5"/>
       <c r="Z490" s="5"/>
     </row>
-    <row r="491" spans="1:26" ht="17.399999999999999">
+    <row r="491" spans="1:26" ht="16.5">
       <c r="A491" s="7"/>
       <c r="B491" s="7"/>
       <c r="C491" s="7"/>
@@ -49414,7 +49409,7 @@
       <c r="Y491" s="5"/>
       <c r="Z491" s="5"/>
     </row>
-    <row r="492" spans="1:26" ht="17.399999999999999">
+    <row r="492" spans="1:26" ht="16.5">
       <c r="A492" s="7"/>
       <c r="B492" s="7"/>
       <c r="C492" s="7"/>
@@ -49442,7 +49437,7 @@
       <c r="Y492" s="5"/>
       <c r="Z492" s="5"/>
     </row>
-    <row r="493" spans="1:26" ht="17.399999999999999">
+    <row r="493" spans="1:26" ht="16.5">
       <c r="A493" s="7"/>
       <c r="B493" s="7"/>
       <c r="C493" s="7"/>
@@ -49470,7 +49465,7 @@
       <c r="Y493" s="5"/>
       <c r="Z493" s="5"/>
     </row>
-    <row r="494" spans="1:26" ht="17.399999999999999">
+    <row r="494" spans="1:26" ht="16.5">
       <c r="A494" s="7"/>
       <c r="B494" s="7"/>
       <c r="C494" s="7"/>
@@ -49498,7 +49493,7 @@
       <c r="Y494" s="5"/>
       <c r="Z494" s="5"/>
     </row>
-    <row r="495" spans="1:26" ht="17.399999999999999">
+    <row r="495" spans="1:26" ht="16.5">
       <c r="A495" s="7"/>
       <c r="B495" s="7"/>
       <c r="C495" s="7"/>
@@ -49526,7 +49521,7 @@
       <c r="Y495" s="5"/>
       <c r="Z495" s="5"/>
     </row>
-    <row r="496" spans="1:26" ht="17.399999999999999">
+    <row r="496" spans="1:26" ht="16.5">
       <c r="A496" s="7"/>
       <c r="B496" s="7"/>
       <c r="C496" s="7"/>
@@ -49554,7 +49549,7 @@
       <c r="Y496" s="5"/>
       <c r="Z496" s="5"/>
     </row>
-    <row r="497" spans="1:26" ht="17.399999999999999">
+    <row r="497" spans="1:26" ht="16.5">
       <c r="A497" s="7"/>
       <c r="B497" s="7"/>
       <c r="C497" s="7"/>
@@ -49582,7 +49577,7 @@
       <c r="Y497" s="5"/>
       <c r="Z497" s="5"/>
     </row>
-    <row r="498" spans="1:26" ht="17.399999999999999">
+    <row r="498" spans="1:26" ht="16.5">
       <c r="A498" s="7"/>
       <c r="B498" s="7"/>
       <c r="C498" s="7"/>
@@ -49610,7 +49605,7 @@
       <c r="Y498" s="5"/>
       <c r="Z498" s="5"/>
     </row>
-    <row r="499" spans="1:26" ht="17.399999999999999">
+    <row r="499" spans="1:26" ht="16.5">
       <c r="A499" s="7"/>
       <c r="B499" s="7"/>
       <c r="C499" s="7"/>
@@ -49638,7 +49633,7 @@
       <c r="Y499" s="5"/>
       <c r="Z499" s="5"/>
     </row>
-    <row r="500" spans="1:26" ht="17.399999999999999">
+    <row r="500" spans="1:26" ht="16.5">
       <c r="A500" s="7"/>
       <c r="B500" s="7"/>
       <c r="C500" s="7"/>
@@ -49666,7 +49661,7 @@
       <c r="Y500" s="5"/>
       <c r="Z500" s="5"/>
     </row>
-    <row r="501" spans="1:26" ht="17.399999999999999">
+    <row r="501" spans="1:26" ht="16.5">
       <c r="A501" s="7"/>
       <c r="B501" s="7"/>
       <c r="C501" s="7"/>
@@ -49694,7 +49689,7 @@
       <c r="Y501" s="5"/>
       <c r="Z501" s="5"/>
     </row>
-    <row r="502" spans="1:26" ht="17.399999999999999">
+    <row r="502" spans="1:26" ht="16.5">
       <c r="A502" s="7"/>
       <c r="B502" s="7"/>
       <c r="C502" s="7"/>
@@ -49722,7 +49717,7 @@
       <c r="Y502" s="5"/>
       <c r="Z502" s="5"/>
     </row>
-    <row r="503" spans="1:26" ht="17.399999999999999">
+    <row r="503" spans="1:26" ht="16.5">
       <c r="A503" s="7"/>
       <c r="B503" s="7"/>
       <c r="C503" s="7"/>
@@ -49750,7 +49745,7 @@
       <c r="Y503" s="5"/>
       <c r="Z503" s="5"/>
     </row>
-    <row r="504" spans="1:26" ht="17.399999999999999">
+    <row r="504" spans="1:26" ht="16.5">
       <c r="A504" s="7"/>
       <c r="B504" s="7"/>
       <c r="C504" s="7"/>
@@ -49778,7 +49773,7 @@
       <c r="Y504" s="5"/>
       <c r="Z504" s="5"/>
     </row>
-    <row r="505" spans="1:26" ht="17.399999999999999">
+    <row r="505" spans="1:26" ht="16.5">
       <c r="A505" s="7"/>
       <c r="B505" s="7"/>
       <c r="C505" s="7"/>
@@ -49806,7 +49801,7 @@
       <c r="Y505" s="5"/>
       <c r="Z505" s="5"/>
     </row>
-    <row r="506" spans="1:26" ht="17.399999999999999">
+    <row r="506" spans="1:26" ht="16.5">
       <c r="A506" s="7"/>
       <c r="B506" s="7"/>
       <c r="C506" s="7"/>
@@ -49834,7 +49829,7 @@
       <c r="Y506" s="5"/>
       <c r="Z506" s="5"/>
     </row>
-    <row r="507" spans="1:26" ht="17.399999999999999">
+    <row r="507" spans="1:26" ht="16.5">
       <c r="A507" s="7"/>
       <c r="B507" s="7"/>
       <c r="C507" s="7"/>
@@ -49862,7 +49857,7 @@
       <c r="Y507" s="5"/>
       <c r="Z507" s="5"/>
     </row>
-    <row r="508" spans="1:26" ht="17.399999999999999">
+    <row r="508" spans="1:26" ht="16.5">
       <c r="A508" s="7"/>
       <c r="B508" s="7"/>
       <c r="C508" s="7"/>
@@ -49890,7 +49885,7 @@
       <c r="Y508" s="5"/>
       <c r="Z508" s="5"/>
     </row>
-    <row r="509" spans="1:26" ht="17.399999999999999">
+    <row r="509" spans="1:26" ht="16.5">
       <c r="A509" s="7"/>
       <c r="B509" s="7"/>
       <c r="C509" s="7"/>
@@ -49918,7 +49913,7 @@
       <c r="Y509" s="5"/>
       <c r="Z509" s="5"/>
     </row>
-    <row r="510" spans="1:26" ht="17.399999999999999">
+    <row r="510" spans="1:26" ht="16.5">
       <c r="A510" s="7"/>
       <c r="B510" s="7"/>
       <c r="C510" s="7"/>
@@ -49946,7 +49941,7 @@
       <c r="Y510" s="5"/>
       <c r="Z510" s="5"/>
     </row>
-    <row r="511" spans="1:26" ht="17.399999999999999">
+    <row r="511" spans="1:26" ht="16.5">
       <c r="A511" s="7"/>
       <c r="B511" s="7"/>
       <c r="C511" s="7"/>
@@ -49974,7 +49969,7 @@
       <c r="Y511" s="5"/>
       <c r="Z511" s="5"/>
     </row>
-    <row r="512" spans="1:26" ht="17.399999999999999">
+    <row r="512" spans="1:26" ht="16.5">
       <c r="A512" s="7"/>
       <c r="B512" s="7"/>
       <c r="C512" s="7"/>
@@ -50002,7 +49997,7 @@
       <c r="Y512" s="5"/>
       <c r="Z512" s="5"/>
     </row>
-    <row r="513" spans="1:26" ht="17.399999999999999">
+    <row r="513" spans="1:26" ht="16.5">
       <c r="A513" s="7"/>
       <c r="B513" s="7"/>
       <c r="C513" s="7"/>
@@ -50030,7 +50025,7 @@
       <c r="Y513" s="5"/>
       <c r="Z513" s="5"/>
     </row>
-    <row r="514" spans="1:26" ht="17.399999999999999">
+    <row r="514" spans="1:26" ht="16.5">
       <c r="A514" s="7"/>
       <c r="B514" s="7"/>
       <c r="C514" s="7"/>
@@ -50058,7 +50053,7 @@
       <c r="Y514" s="5"/>
       <c r="Z514" s="5"/>
     </row>
-    <row r="515" spans="1:26" ht="17.399999999999999">
+    <row r="515" spans="1:26" ht="16.5">
       <c r="A515" s="7"/>
       <c r="B515" s="7"/>
       <c r="C515" s="7"/>
@@ -50086,7 +50081,7 @@
       <c r="Y515" s="5"/>
       <c r="Z515" s="5"/>
     </row>
-    <row r="516" spans="1:26" ht="17.399999999999999">
+    <row r="516" spans="1:26" ht="16.5">
       <c r="A516" s="7"/>
       <c r="B516" s="7"/>
       <c r="C516" s="7"/>
@@ -50114,7 +50109,7 @@
       <c r="Y516" s="5"/>
       <c r="Z516" s="5"/>
     </row>
-    <row r="517" spans="1:26" ht="17.399999999999999">
+    <row r="517" spans="1:26" ht="16.5">
       <c r="A517" s="7"/>
       <c r="B517" s="7"/>
       <c r="C517" s="7"/>
@@ -50142,7 +50137,7 @@
       <c r="Y517" s="5"/>
       <c r="Z517" s="5"/>
     </row>
-    <row r="518" spans="1:26" ht="17.399999999999999">
+    <row r="518" spans="1:26" ht="16.5">
       <c r="A518" s="7"/>
       <c r="B518" s="7"/>
       <c r="C518" s="7"/>
@@ -50170,7 +50165,7 @@
       <c r="Y518" s="5"/>
       <c r="Z518" s="5"/>
     </row>
-    <row r="519" spans="1:26" ht="17.399999999999999">
+    <row r="519" spans="1:26" ht="16.5">
       <c r="A519" s="7"/>
       <c r="B519" s="7"/>
       <c r="C519" s="7"/>
@@ -50198,7 +50193,7 @@
       <c r="Y519" s="5"/>
       <c r="Z519" s="5"/>
     </row>
-    <row r="520" spans="1:26" ht="17.399999999999999">
+    <row r="520" spans="1:26" ht="16.5">
       <c r="A520" s="7"/>
       <c r="B520" s="7"/>
       <c r="C520" s="7"/>
@@ -50226,7 +50221,7 @@
       <c r="Y520" s="5"/>
       <c r="Z520" s="5"/>
     </row>
-    <row r="521" spans="1:26" ht="17.399999999999999">
+    <row r="521" spans="1:26" ht="16.5">
       <c r="A521" s="7"/>
       <c r="B521" s="7"/>
       <c r="C521" s="7"/>
@@ -50254,7 +50249,7 @@
       <c r="Y521" s="5"/>
       <c r="Z521" s="5"/>
     </row>
-    <row r="522" spans="1:26" ht="17.399999999999999">
+    <row r="522" spans="1:26" ht="16.5">
       <c r="A522" s="7"/>
       <c r="B522" s="7"/>
       <c r="C522" s="7"/>
@@ -50282,7 +50277,7 @@
       <c r="Y522" s="5"/>
       <c r="Z522" s="5"/>
     </row>
-    <row r="523" spans="1:26" ht="17.399999999999999">
+    <row r="523" spans="1:26" ht="16.5">
       <c r="A523" s="7"/>
       <c r="B523" s="7"/>
       <c r="C523" s="7"/>
@@ -50310,7 +50305,7 @@
       <c r="Y523" s="5"/>
       <c r="Z523" s="5"/>
     </row>
-    <row r="524" spans="1:26" ht="17.399999999999999">
+    <row r="524" spans="1:26" ht="16.5">
       <c r="A524" s="7"/>
       <c r="B524" s="7"/>
       <c r="C524" s="7"/>
@@ -50338,7 +50333,7 @@
       <c r="Y524" s="5"/>
       <c r="Z524" s="5"/>
     </row>
-    <row r="525" spans="1:26" ht="17.399999999999999">
+    <row r="525" spans="1:26" ht="16.5">
       <c r="A525" s="7"/>
       <c r="B525" s="7"/>
       <c r="C525" s="7"/>
@@ -50366,7 +50361,7 @@
       <c r="Y525" s="5"/>
       <c r="Z525" s="5"/>
     </row>
-    <row r="526" spans="1:26" ht="17.399999999999999">
+    <row r="526" spans="1:26" ht="16.5">
       <c r="A526" s="7"/>
       <c r="B526" s="7"/>
       <c r="C526" s="7"/>
@@ -50394,7 +50389,7 @@
       <c r="Y526" s="5"/>
       <c r="Z526" s="5"/>
     </row>
-    <row r="527" spans="1:26" ht="17.399999999999999">
+    <row r="527" spans="1:26" ht="16.5">
       <c r="A527" s="7"/>
       <c r="B527" s="7"/>
       <c r="C527" s="7"/>
@@ -50422,7 +50417,7 @@
       <c r="Y527" s="5"/>
       <c r="Z527" s="5"/>
     </row>
-    <row r="528" spans="1:26" ht="17.399999999999999">
+    <row r="528" spans="1:26" ht="16.5">
       <c r="A528" s="7"/>
       <c r="B528" s="7"/>
       <c r="C528" s="7"/>
@@ -50450,7 +50445,7 @@
       <c r="Y528" s="5"/>
       <c r="Z528" s="5"/>
     </row>
-    <row r="529" spans="1:26" ht="17.399999999999999">
+    <row r="529" spans="1:26" ht="16.5">
       <c r="A529" s="7"/>
       <c r="B529" s="7"/>
       <c r="C529" s="7"/>
@@ -50478,7 +50473,7 @@
       <c r="Y529" s="5"/>
       <c r="Z529" s="5"/>
     </row>
-    <row r="530" spans="1:26" ht="17.399999999999999">
+    <row r="530" spans="1:26" ht="16.5">
       <c r="A530" s="7"/>
       <c r="B530" s="7"/>
       <c r="C530" s="7"/>
@@ -50506,7 +50501,7 @@
       <c r="Y530" s="5"/>
       <c r="Z530" s="5"/>
     </row>
-    <row r="531" spans="1:26" ht="17.399999999999999">
+    <row r="531" spans="1:26" ht="16.5">
       <c r="A531" s="7"/>
       <c r="B531" s="7"/>
       <c r="C531" s="7"/>
@@ -50534,7 +50529,7 @@
       <c r="Y531" s="5"/>
       <c r="Z531" s="5"/>
     </row>
-    <row r="532" spans="1:26" ht="17.399999999999999">
+    <row r="532" spans="1:26" ht="16.5">
       <c r="A532" s="7"/>
       <c r="B532" s="7"/>
       <c r="C532" s="7"/>
@@ -50562,7 +50557,7 @@
       <c r="Y532" s="5"/>
       <c r="Z532" s="5"/>
     </row>
-    <row r="533" spans="1:26" ht="17.399999999999999">
+    <row r="533" spans="1:26" ht="16.5">
       <c r="A533" s="7"/>
       <c r="B533" s="7"/>
       <c r="C533" s="7"/>
@@ -50590,7 +50585,7 @@
       <c r="Y533" s="5"/>
       <c r="Z533" s="5"/>
     </row>
-    <row r="534" spans="1:26" ht="17.399999999999999">
+    <row r="534" spans="1:26" ht="16.5">
       <c r="A534" s="7"/>
       <c r="B534" s="7"/>
       <c r="C534" s="7"/>
@@ -50618,7 +50613,7 @@
       <c r="Y534" s="5"/>
       <c r="Z534" s="5"/>
     </row>
-    <row r="535" spans="1:26" ht="17.399999999999999">
+    <row r="535" spans="1:26" ht="16.5">
       <c r="A535" s="7"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
@@ -50646,7 +50641,7 @@
       <c r="Y535" s="5"/>
       <c r="Z535" s="5"/>
     </row>
-    <row r="536" spans="1:26" ht="17.399999999999999">
+    <row r="536" spans="1:26" ht="16.5">
       <c r="A536" s="7"/>
       <c r="B536" s="7"/>
       <c r="C536" s="7"/>
@@ -50674,7 +50669,7 @@
       <c r="Y536" s="5"/>
       <c r="Z536" s="5"/>
     </row>
-    <row r="537" spans="1:26" ht="17.399999999999999">
+    <row r="537" spans="1:26" ht="16.5">
       <c r="A537" s="7"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
@@ -50702,7 +50697,7 @@
       <c r="Y537" s="5"/>
       <c r="Z537" s="5"/>
     </row>
-    <row r="538" spans="1:26" ht="17.399999999999999">
+    <row r="538" spans="1:26" ht="16.5">
       <c r="A538" s="7"/>
       <c r="B538" s="7"/>
       <c r="C538" s="7"/>
@@ -50730,7 +50725,7 @@
       <c r="Y538" s="5"/>
       <c r="Z538" s="5"/>
     </row>
-    <row r="539" spans="1:26" ht="17.399999999999999">
+    <row r="539" spans="1:26" ht="16.5">
       <c r="A539" s="7"/>
       <c r="B539" s="7"/>
       <c r="C539" s="7"/>
@@ -50758,7 +50753,7 @@
       <c r="Y539" s="5"/>
       <c r="Z539" s="5"/>
     </row>
-    <row r="540" spans="1:26" ht="17.399999999999999">
+    <row r="540" spans="1:26" ht="16.5">
       <c r="A540" s="7"/>
       <c r="B540" s="7"/>
       <c r="C540" s="7"/>
@@ -50786,7 +50781,7 @@
       <c r="Y540" s="5"/>
       <c r="Z540" s="5"/>
     </row>
-    <row r="541" spans="1:26" ht="17.399999999999999">
+    <row r="541" spans="1:26" ht="16.5">
       <c r="A541" s="7"/>
       <c r="B541" s="7"/>
       <c r="C541" s="7"/>
@@ -50814,7 +50809,7 @@
       <c r="Y541" s="5"/>
       <c r="Z541" s="5"/>
     </row>
-    <row r="542" spans="1:26" ht="17.399999999999999">
+    <row r="542" spans="1:26" ht="16.5">
       <c r="A542" s="7"/>
       <c r="B542" s="7"/>
       <c r="C542" s="7"/>
@@ -50842,7 +50837,7 @@
       <c r="Y542" s="5"/>
       <c r="Z542" s="5"/>
     </row>
-    <row r="543" spans="1:26" ht="17.399999999999999">
+    <row r="543" spans="1:26" ht="16.5">
       <c r="A543" s="7"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
@@ -50870,7 +50865,7 @@
       <c r="Y543" s="5"/>
       <c r="Z543" s="5"/>
     </row>
-    <row r="544" spans="1:26" ht="17.399999999999999">
+    <row r="544" spans="1:26" ht="16.5">
       <c r="A544" s="7"/>
       <c r="B544" s="7"/>
       <c r="C544" s="7"/>
@@ -50898,7 +50893,7 @@
       <c r="Y544" s="5"/>
       <c r="Z544" s="5"/>
     </row>
-    <row r="545" spans="1:26" ht="17.399999999999999">
+    <row r="545" spans="1:26" ht="16.5">
       <c r="A545" s="7"/>
       <c r="B545" s="7"/>
       <c r="C545" s="7"/>
@@ -50926,7 +50921,7 @@
       <c r="Y545" s="5"/>
       <c r="Z545" s="5"/>
     </row>
-    <row r="546" spans="1:26" ht="17.399999999999999">
+    <row r="546" spans="1:26" ht="16.5">
       <c r="A546" s="7"/>
       <c r="B546" s="7"/>
       <c r="C546" s="7"/>
@@ -50954,7 +50949,7 @@
       <c r="Y546" s="5"/>
       <c r="Z546" s="5"/>
     </row>
-    <row r="547" spans="1:26" ht="17.399999999999999">
+    <row r="547" spans="1:26" ht="16.5">
       <c r="A547" s="7"/>
       <c r="B547" s="7"/>
       <c r="C547" s="7"/>
@@ -50982,7 +50977,7 @@
       <c r="Y547" s="5"/>
       <c r="Z547" s="5"/>
     </row>
-    <row r="548" spans="1:26" ht="17.399999999999999">
+    <row r="548" spans="1:26" ht="16.5">
       <c r="A548" s="7"/>
       <c r="B548" s="7"/>
       <c r="C548" s="7"/>
@@ -51010,7 +51005,7 @@
       <c r="Y548" s="5"/>
       <c r="Z548" s="5"/>
     </row>
-    <row r="549" spans="1:26" ht="17.399999999999999">
+    <row r="549" spans="1:26" ht="16.5">
       <c r="A549" s="7"/>
       <c r="B549" s="7"/>
       <c r="C549" s="7"/>
@@ -51038,7 +51033,7 @@
       <c r="Y549" s="5"/>
       <c r="Z549" s="5"/>
     </row>
-    <row r="550" spans="1:26" ht="17.399999999999999">
+    <row r="550" spans="1:26" ht="16.5">
       <c r="A550" s="7"/>
       <c r="B550" s="7"/>
       <c r="C550" s="7"/>
@@ -51066,7 +51061,7 @@
       <c r="Y550" s="5"/>
       <c r="Z550" s="5"/>
     </row>
-    <row r="551" spans="1:26" ht="17.399999999999999">
+    <row r="551" spans="1:26" ht="16.5">
       <c r="A551" s="7"/>
       <c r="B551" s="7"/>
       <c r="C551" s="7"/>
@@ -51094,7 +51089,7 @@
       <c r="Y551" s="5"/>
       <c r="Z551" s="5"/>
     </row>
-    <row r="552" spans="1:26" ht="17.399999999999999">
+    <row r="552" spans="1:26" ht="16.5">
       <c r="A552" s="7"/>
       <c r="B552" s="7"/>
       <c r="C552" s="7"/>
@@ -51122,7 +51117,7 @@
       <c r="Y552" s="5"/>
       <c r="Z552" s="5"/>
     </row>
-    <row r="553" spans="1:26" ht="17.399999999999999">
+    <row r="553" spans="1:26" ht="16.5">
       <c r="A553" s="7"/>
       <c r="B553" s="7"/>
       <c r="C553" s="7"/>
@@ -51150,7 +51145,7 @@
       <c r="Y553" s="5"/>
       <c r="Z553" s="5"/>
     </row>
-    <row r="554" spans="1:26" ht="17.399999999999999">
+    <row r="554" spans="1:26" ht="16.5">
       <c r="A554" s="7"/>
       <c r="B554" s="7"/>
       <c r="C554" s="7"/>
@@ -51178,7 +51173,7 @@
       <c r="Y554" s="5"/>
       <c r="Z554" s="5"/>
     </row>
-    <row r="555" spans="1:26" ht="17.399999999999999">
+    <row r="555" spans="1:26" ht="16.5">
       <c r="A555" s="7"/>
       <c r="B555" s="7"/>
       <c r="C555" s="7"/>
@@ -51206,7 +51201,7 @@
       <c r="Y555" s="5"/>
       <c r="Z555" s="5"/>
     </row>
-    <row r="556" spans="1:26" ht="17.399999999999999">
+    <row r="556" spans="1:26" ht="16.5">
       <c r="A556" s="7"/>
       <c r="B556" s="7"/>
       <c r="C556" s="7"/>
@@ -51234,7 +51229,7 @@
       <c r="Y556" s="5"/>
       <c r="Z556" s="5"/>
     </row>
-    <row r="557" spans="1:26" ht="17.399999999999999">
+    <row r="557" spans="1:26" ht="16.5">
       <c r="A557" s="7"/>
       <c r="B557" s="7"/>
       <c r="C557" s="7"/>
@@ -51262,7 +51257,7 @@
       <c r="Y557" s="5"/>
       <c r="Z557" s="5"/>
     </row>
-    <row r="558" spans="1:26" ht="17.399999999999999">
+    <row r="558" spans="1:26" ht="16.5">
       <c r="A558" s="7"/>
       <c r="B558" s="7"/>
       <c r="C558" s="7"/>
@@ -51290,7 +51285,7 @@
       <c r="Y558" s="5"/>
       <c r="Z558" s="5"/>
     </row>
-    <row r="559" spans="1:26" ht="17.399999999999999">
+    <row r="559" spans="1:26" ht="16.5">
       <c r="A559" s="7"/>
       <c r="B559" s="7"/>
       <c r="C559" s="7"/>
@@ -51318,7 +51313,7 @@
       <c r="Y559" s="5"/>
       <c r="Z559" s="5"/>
     </row>
-    <row r="560" spans="1:26" ht="17.399999999999999">
+    <row r="560" spans="1:26" ht="16.5">
       <c r="A560" s="7"/>
       <c r="B560" s="7"/>
       <c r="C560" s="7"/>
@@ -51346,7 +51341,7 @@
       <c r="Y560" s="5"/>
       <c r="Z560" s="5"/>
     </row>
-    <row r="561" spans="1:26" ht="17.399999999999999">
+    <row r="561" spans="1:26" ht="16.5">
       <c r="A561" s="7"/>
       <c r="B561" s="7"/>
       <c r="C561" s="7"/>
@@ -51374,7 +51369,7 @@
       <c r="Y561" s="5"/>
       <c r="Z561" s="5"/>
     </row>
-    <row r="562" spans="1:26" ht="17.399999999999999">
+    <row r="562" spans="1:26" ht="16.5">
       <c r="A562" s="7"/>
       <c r="B562" s="7"/>
       <c r="C562" s="7"/>
@@ -51402,7 +51397,7 @@
       <c r="Y562" s="5"/>
       <c r="Z562" s="5"/>
     </row>
-    <row r="563" spans="1:26" ht="17.399999999999999">
+    <row r="563" spans="1:26" ht="16.5">
       <c r="A563" s="7"/>
       <c r="B563" s="7"/>
       <c r="C563" s="7"/>
@@ -51430,7 +51425,7 @@
       <c r="Y563" s="5"/>
       <c r="Z563" s="5"/>
     </row>
-    <row r="564" spans="1:26" ht="17.399999999999999">
+    <row r="564" spans="1:26" ht="16.5">
       <c r="A564" s="7"/>
       <c r="B564" s="7"/>
       <c r="C564" s="7"/>
@@ -51458,7 +51453,7 @@
       <c r="Y564" s="5"/>
       <c r="Z564" s="5"/>
     </row>
-    <row r="565" spans="1:26" ht="17.399999999999999">
+    <row r="565" spans="1:26" ht="16.5">
       <c r="A565" s="7"/>
       <c r="B565" s="7"/>
       <c r="C565" s="7"/>
@@ -51486,7 +51481,7 @@
       <c r="Y565" s="5"/>
       <c r="Z565" s="5"/>
     </row>
-    <row r="566" spans="1:26" ht="17.399999999999999">
+    <row r="566" spans="1:26" ht="16.5">
       <c r="A566" s="7"/>
       <c r="B566" s="7"/>
       <c r="C566" s="7"/>
@@ -51514,7 +51509,7 @@
       <c r="Y566" s="5"/>
       <c r="Z566" s="5"/>
     </row>
-    <row r="567" spans="1:26" ht="17.399999999999999">
+    <row r="567" spans="1:26" ht="16.5">
       <c r="A567" s="7"/>
       <c r="B567" s="7"/>
       <c r="C567" s="7"/>
@@ -51542,7 +51537,7 @@
       <c r="Y567" s="5"/>
       <c r="Z567" s="5"/>
     </row>
-    <row r="568" spans="1:26" ht="17.399999999999999">
+    <row r="568" spans="1:26" ht="16.5">
       <c r="A568" s="7"/>
       <c r="B568" s="7"/>
       <c r="C568" s="7"/>
@@ -51570,7 +51565,7 @@
       <c r="Y568" s="5"/>
       <c r="Z568" s="5"/>
     </row>
-    <row r="569" spans="1:26" ht="17.399999999999999">
+    <row r="569" spans="1:26" ht="16.5">
       <c r="A569" s="7"/>
       <c r="B569" s="7"/>
       <c r="C569" s="7"/>
@@ -51598,7 +51593,7 @@
       <c r="Y569" s="5"/>
       <c r="Z569" s="5"/>
     </row>
-    <row r="570" spans="1:26" ht="17.399999999999999">
+    <row r="570" spans="1:26" ht="16.5">
       <c r="A570" s="7"/>
       <c r="B570" s="7"/>
       <c r="C570" s="7"/>
@@ -51626,7 +51621,7 @@
       <c r="Y570" s="5"/>
       <c r="Z570" s="5"/>
     </row>
-    <row r="571" spans="1:26" ht="17.399999999999999">
+    <row r="571" spans="1:26" ht="16.5">
       <c r="A571" s="7"/>
       <c r="B571" s="7"/>
       <c r="C571" s="7"/>
@@ -51654,7 +51649,7 @@
       <c r="Y571" s="5"/>
       <c r="Z571" s="5"/>
     </row>
-    <row r="572" spans="1:26" ht="17.399999999999999">
+    <row r="572" spans="1:26" ht="16.5">
       <c r="A572" s="7"/>
       <c r="B572" s="7"/>
       <c r="C572" s="7"/>
@@ -51682,7 +51677,7 @@
       <c r="Y572" s="5"/>
       <c r="Z572" s="5"/>
     </row>
-    <row r="573" spans="1:26" ht="17.399999999999999">
+    <row r="573" spans="1:26" ht="16.5">
       <c r="A573" s="7"/>
       <c r="B573" s="7"/>
       <c r="C573" s="7"/>
@@ -51710,7 +51705,7 @@
       <c r="Y573" s="5"/>
       <c r="Z573" s="5"/>
     </row>
-    <row r="574" spans="1:26" ht="17.399999999999999">
+    <row r="574" spans="1:26" ht="16.5">
       <c r="A574" s="7"/>
       <c r="B574" s="7"/>
       <c r="C574" s="7"/>
@@ -51738,7 +51733,7 @@
       <c r="Y574" s="5"/>
       <c r="Z574" s="5"/>
     </row>
-    <row r="575" spans="1:26" ht="17.399999999999999">
+    <row r="575" spans="1:26" ht="16.5">
       <c r="A575" s="7"/>
       <c r="B575" s="7"/>
       <c r="C575" s="7"/>
@@ -51766,7 +51761,7 @@
       <c r="Y575" s="5"/>
       <c r="Z575" s="5"/>
     </row>
-    <row r="576" spans="1:26" ht="17.399999999999999">
+    <row r="576" spans="1:26" ht="16.5">
       <c r="A576" s="7"/>
       <c r="B576" s="7"/>
       <c r="C576" s="7"/>
@@ -51794,7 +51789,7 @@
       <c r="Y576" s="5"/>
       <c r="Z576" s="5"/>
     </row>
-    <row r="577" spans="1:26" ht="17.399999999999999">
+    <row r="577" spans="1:26" ht="16.5">
       <c r="A577" s="7"/>
       <c r="B577" s="7"/>
       <c r="C577" s="7"/>
@@ -51822,7 +51817,7 @@
       <c r="Y577" s="5"/>
       <c r="Z577" s="5"/>
     </row>
-    <row r="578" spans="1:26" ht="17.399999999999999">
+    <row r="578" spans="1:26" ht="16.5">
       <c r="A578" s="7"/>
       <c r="B578" s="7"/>
       <c r="C578" s="7"/>
@@ -51850,7 +51845,7 @@
       <c r="Y578" s="5"/>
       <c r="Z578" s="5"/>
     </row>
-    <row r="579" spans="1:26" ht="17.399999999999999">
+    <row r="579" spans="1:26" ht="16.5">
       <c r="A579" s="7"/>
       <c r="B579" s="7"/>
       <c r="C579" s="7"/>
@@ -51878,7 +51873,7 @@
       <c r="Y579" s="5"/>
       <c r="Z579" s="5"/>
     </row>
-    <row r="580" spans="1:26" ht="17.399999999999999">
+    <row r="580" spans="1:26" ht="16.5">
       <c r="A580" s="7"/>
       <c r="B580" s="7"/>
       <c r="C580" s="7"/>
@@ -51906,7 +51901,7 @@
       <c r="Y580" s="5"/>
       <c r="Z580" s="5"/>
     </row>
-    <row r="581" spans="1:26" ht="17.399999999999999">
+    <row r="581" spans="1:26" ht="16.5">
       <c r="A581" s="7"/>
       <c r="B581" s="7"/>
       <c r="C581" s="7"/>
@@ -51934,7 +51929,7 @@
       <c r="Y581" s="5"/>
       <c r="Z581" s="5"/>
     </row>
-    <row r="582" spans="1:26" ht="17.399999999999999">
+    <row r="582" spans="1:26" ht="16.5">
       <c r="A582" s="7"/>
       <c r="B582" s="7"/>
       <c r="C582" s="7"/>
@@ -51962,7 +51957,7 @@
       <c r="Y582" s="5"/>
       <c r="Z582" s="5"/>
     </row>
-    <row r="583" spans="1:26" ht="17.399999999999999">
+    <row r="583" spans="1:26" ht="16.5">
       <c r="A583" s="7"/>
       <c r="B583" s="7"/>
       <c r="C583" s="7"/>
@@ -51990,7 +51985,7 @@
       <c r="Y583" s="5"/>
       <c r="Z583" s="5"/>
     </row>
-    <row r="584" spans="1:26" ht="17.399999999999999">
+    <row r="584" spans="1:26" ht="16.5">
       <c r="A584" s="7"/>
       <c r="B584" s="7"/>
       <c r="C584" s="7"/>
@@ -52018,7 +52013,7 @@
       <c r="Y584" s="5"/>
       <c r="Z584" s="5"/>
     </row>
-    <row r="585" spans="1:26" ht="17.399999999999999">
+    <row r="585" spans="1:26" ht="16.5">
       <c r="A585" s="7"/>
       <c r="B585" s="7"/>
       <c r="C585" s="7"/>
@@ -52046,7 +52041,7 @@
       <c r="Y585" s="5"/>
       <c r="Z585" s="5"/>
     </row>
-    <row r="586" spans="1:26" ht="17.399999999999999">
+    <row r="586" spans="1:26" ht="16.5">
       <c r="A586" s="7"/>
       <c r="B586" s="7"/>
       <c r="C586" s="7"/>
@@ -52074,7 +52069,7 @@
       <c r="Y586" s="5"/>
       <c r="Z586" s="5"/>
     </row>
-    <row r="587" spans="1:26" ht="17.399999999999999">
+    <row r="587" spans="1:26" ht="16.5">
       <c r="A587" s="7"/>
       <c r="B587" s="7"/>
       <c r="C587" s="7"/>
@@ -52102,7 +52097,7 @@
       <c r="Y587" s="5"/>
       <c r="Z587" s="5"/>
     </row>
-    <row r="588" spans="1:26" ht="17.399999999999999">
+    <row r="588" spans="1:26" ht="16.5">
       <c r="A588" s="7"/>
       <c r="B588" s="7"/>
       <c r="C588" s="7"/>
@@ -52130,7 +52125,7 @@
       <c r="Y588" s="5"/>
       <c r="Z588" s="5"/>
     </row>
-    <row r="589" spans="1:26" ht="17.399999999999999">
+    <row r="589" spans="1:26" ht="16.5">
       <c r="A589" s="7"/>
       <c r="B589" s="7"/>
       <c r="C589" s="7"/>
@@ -52158,7 +52153,7 @@
       <c r="Y589" s="5"/>
       <c r="Z589" s="5"/>
     </row>
-    <row r="590" spans="1:26" ht="17.399999999999999">
+    <row r="590" spans="1:26" ht="16.5">
       <c r="A590" s="7"/>
       <c r="B590" s="7"/>
       <c r="C590" s="7"/>
@@ -52186,7 +52181,7 @@
       <c r="Y590" s="5"/>
       <c r="Z590" s="5"/>
     </row>
-    <row r="591" spans="1:26" ht="17.399999999999999">
+    <row r="591" spans="1:26" ht="16.5">
       <c r="A591" s="7"/>
       <c r="B591" s="7"/>
       <c r="C591" s="7"/>
@@ -52214,7 +52209,7 @@
       <c r="Y591" s="5"/>
       <c r="Z591" s="5"/>
     </row>
-    <row r="592" spans="1:26" ht="17.399999999999999">
+    <row r="592" spans="1:26" ht="16.5">
       <c r="A592" s="7"/>
       <c r="B592" s="7"/>
       <c r="C592" s="7"/>
@@ -52242,7 +52237,7 @@
       <c r="Y592" s="5"/>
       <c r="Z592" s="5"/>
     </row>
-    <row r="593" spans="1:26" ht="17.399999999999999">
+    <row r="593" spans="1:26" ht="16.5">
       <c r="A593" s="7"/>
       <c r="B593" s="7"/>
       <c r="C593" s="7"/>
@@ -52270,7 +52265,7 @@
       <c r="Y593" s="5"/>
       <c r="Z593" s="5"/>
     </row>
-    <row r="594" spans="1:26" ht="17.399999999999999">
+    <row r="594" spans="1:26" ht="16.5">
       <c r="A594" s="7"/>
       <c r="B594" s="7"/>
       <c r="C594" s="7"/>
@@ -52298,7 +52293,7 @@
       <c r="Y594" s="5"/>
       <c r="Z594" s="5"/>
     </row>
-    <row r="595" spans="1:26" ht="17.399999999999999">
+    <row r="595" spans="1:26" ht="16.5">
       <c r="A595" s="7"/>
       <c r="B595" s="7"/>
       <c r="C595" s="7"/>
@@ -52326,7 +52321,7 @@
       <c r="Y595" s="5"/>
       <c r="Z595" s="5"/>
     </row>
-    <row r="596" spans="1:26" ht="17.399999999999999">
+    <row r="596" spans="1:26" ht="16.5">
       <c r="A596" s="7"/>
       <c r="B596" s="7"/>
       <c r="C596" s="7"/>
@@ -52354,7 +52349,7 @@
       <c r="Y596" s="5"/>
       <c r="Z596" s="5"/>
     </row>
-    <row r="597" spans="1:26" ht="17.399999999999999">
+    <row r="597" spans="1:26" ht="16.5">
       <c r="A597" s="7"/>
       <c r="B597" s="7"/>
       <c r="C597" s="7"/>
@@ -52382,7 +52377,7 @@
       <c r="Y597" s="5"/>
       <c r="Z597" s="5"/>
     </row>
-    <row r="598" spans="1:26" ht="17.399999999999999">
+    <row r="598" spans="1:26" ht="16.5">
       <c r="A598" s="7"/>
       <c r="B598" s="7"/>
       <c r="C598" s="7"/>
@@ -52410,7 +52405,7 @@
       <c r="Y598" s="5"/>
       <c r="Z598" s="5"/>
     </row>
-    <row r="599" spans="1:26" ht="17.399999999999999">
+    <row r="599" spans="1:26" ht="16.5">
       <c r="A599" s="7"/>
       <c r="B599" s="7"/>
       <c r="C599" s="7"/>
@@ -52438,7 +52433,7 @@
       <c r="Y599" s="5"/>
       <c r="Z599" s="5"/>
     </row>
-    <row r="600" spans="1:26" ht="17.399999999999999">
+    <row r="600" spans="1:26" ht="16.5">
       <c r="A600" s="7"/>
       <c r="B600" s="7"/>
       <c r="C600" s="7"/>
@@ -52466,7 +52461,7 @@
       <c r="Y600" s="5"/>
       <c r="Z600" s="5"/>
     </row>
-    <row r="601" spans="1:26" ht="17.399999999999999">
+    <row r="601" spans="1:26" ht="16.5">
       <c r="A601" s="7"/>
       <c r="B601" s="7"/>
       <c r="C601" s="7"/>
@@ -52494,7 +52489,7 @@
       <c r="Y601" s="5"/>
       <c r="Z601" s="5"/>
     </row>
-    <row r="602" spans="1:26" ht="17.399999999999999">
+    <row r="602" spans="1:26" ht="16.5">
       <c r="A602" s="7"/>
       <c r="B602" s="7"/>
       <c r="C602" s="7"/>
@@ -52522,7 +52517,7 @@
       <c r="Y602" s="5"/>
       <c r="Z602" s="5"/>
     </row>
-    <row r="603" spans="1:26" ht="17.399999999999999">
+    <row r="603" spans="1:26" ht="16.5">
       <c r="A603" s="7"/>
       <c r="B603" s="7"/>
       <c r="C603" s="7"/>
@@ -52550,7 +52545,7 @@
       <c r="Y603" s="5"/>
       <c r="Z603" s="5"/>
     </row>
-    <row r="604" spans="1:26" ht="17.399999999999999">
+    <row r="604" spans="1:26" ht="16.5">
       <c r="A604" s="7"/>
       <c r="B604" s="7"/>
       <c r="C604" s="7"/>
@@ -52578,7 +52573,7 @@
       <c r="Y604" s="5"/>
       <c r="Z604" s="5"/>
     </row>
-    <row r="605" spans="1:26" ht="17.399999999999999">
+    <row r="605" spans="1:26" ht="16.5">
       <c r="A605" s="7"/>
       <c r="B605" s="7"/>
       <c r="C605" s="7"/>
@@ -52606,7 +52601,7 @@
       <c r="Y605" s="5"/>
       <c r="Z605" s="5"/>
     </row>
-    <row r="606" spans="1:26" ht="17.399999999999999">
+    <row r="606" spans="1:26" ht="16.5">
       <c r="A606" s="7"/>
       <c r="B606" s="7"/>
       <c r="C606" s="7"/>
@@ -52634,7 +52629,7 @@
       <c r="Y606" s="5"/>
       <c r="Z606" s="5"/>
     </row>
-    <row r="607" spans="1:26" ht="17.399999999999999">
+    <row r="607" spans="1:26" ht="16.5">
       <c r="A607" s="7"/>
       <c r="B607" s="7"/>
       <c r="C607" s="7"/>
@@ -52662,7 +52657,7 @@
       <c r="Y607" s="5"/>
       <c r="Z607" s="5"/>
     </row>
-    <row r="608" spans="1:26" ht="17.399999999999999">
+    <row r="608" spans="1:26" ht="16.5">
       <c r="A608" s="7"/>
       <c r="B608" s="7"/>
       <c r="C608" s="7"/>
@@ -52690,7 +52685,7 @@
       <c r="Y608" s="5"/>
       <c r="Z608" s="5"/>
     </row>
-    <row r="609" spans="1:26" ht="17.399999999999999">
+    <row r="609" spans="1:26" ht="16.5">
       <c r="A609" s="7"/>
       <c r="B609" s="7"/>
       <c r="C609" s="7"/>
@@ -52718,7 +52713,7 @@
       <c r="Y609" s="5"/>
       <c r="Z609" s="5"/>
     </row>
-    <row r="610" spans="1:26" ht="17.399999999999999">
+    <row r="610" spans="1:26" ht="16.5">
       <c r="A610" s="7"/>
       <c r="B610" s="7"/>
       <c r="C610" s="7"/>
@@ -52746,7 +52741,7 @@
       <c r="Y610" s="5"/>
       <c r="Z610" s="5"/>
     </row>
-    <row r="611" spans="1:26" ht="17.399999999999999">
+    <row r="611" spans="1:26" ht="16.5">
       <c r="A611" s="7"/>
       <c r="B611" s="7"/>
       <c r="C611" s="7"/>
@@ -52774,7 +52769,7 @@
       <c r="Y611" s="5"/>
       <c r="Z611" s="5"/>
     </row>
-    <row r="612" spans="1:26" ht="17.399999999999999">
+    <row r="612" spans="1:26" ht="16.5">
       <c r="A612" s="7"/>
       <c r="B612" s="7"/>
       <c r="C612" s="7"/>
@@ -52802,7 +52797,7 @@
       <c r="Y612" s="5"/>
       <c r="Z612" s="5"/>
     </row>
-    <row r="613" spans="1:26" ht="17.399999999999999">
+    <row r="613" spans="1:26" ht="16.5">
       <c r="A613" s="7"/>
       <c r="B613" s="7"/>
       <c r="C613" s="7"/>
@@ -52830,7 +52825,7 @@
       <c r="Y613" s="5"/>
       <c r="Z613" s="5"/>
     </row>
-    <row r="614" spans="1:26" ht="17.399999999999999">
+    <row r="614" spans="1:26" ht="16.5">
       <c r="A614" s="7"/>
       <c r="B614" s="7"/>
       <c r="C614" s="7"/>
@@ -52858,7 +52853,7 @@
       <c r="Y614" s="5"/>
       <c r="Z614" s="5"/>
     </row>
-    <row r="615" spans="1:26" ht="17.399999999999999">
+    <row r="615" spans="1:26" ht="16.5">
       <c r="A615" s="7"/>
       <c r="B615" s="7"/>
       <c r="C615" s="7"/>
@@ -52886,7 +52881,7 @@
       <c r="Y615" s="5"/>
       <c r="Z615" s="5"/>
     </row>
-    <row r="616" spans="1:26" ht="17.399999999999999">
+    <row r="616" spans="1:26" ht="16.5">
       <c r="A616" s="7"/>
       <c r="B616" s="7"/>
       <c r="C616" s="7"/>
@@ -52914,7 +52909,7 @@
       <c r="Y616" s="5"/>
       <c r="Z616" s="5"/>
     </row>
-    <row r="617" spans="1:26" ht="17.399999999999999">
+    <row r="617" spans="1:26" ht="16.5">
       <c r="A617" s="7"/>
       <c r="B617" s="7"/>
       <c r="C617" s="7"/>
@@ -52942,7 +52937,7 @@
       <c r="Y617" s="5"/>
       <c r="Z617" s="5"/>
     </row>
-    <row r="618" spans="1:26" ht="17.399999999999999">
+    <row r="618" spans="1:26" ht="16.5">
       <c r="A618" s="7"/>
       <c r="B618" s="7"/>
       <c r="C618" s="7"/>
@@ -52970,7 +52965,7 @@
       <c r="Y618" s="5"/>
       <c r="Z618" s="5"/>
     </row>
-    <row r="619" spans="1:26" ht="17.399999999999999">
+    <row r="619" spans="1:26" ht="16.5">
       <c r="A619" s="7"/>
       <c r="B619" s="7"/>
       <c r="C619" s="7"/>
@@ -52998,7 +52993,7 @@
       <c r="Y619" s="5"/>
       <c r="Z619" s="5"/>
     </row>
-    <row r="620" spans="1:26" ht="17.399999999999999">
+    <row r="620" spans="1:26" ht="16.5">
       <c r="A620" s="7"/>
       <c r="B620" s="7"/>
       <c r="C620" s="7"/>
@@ -53026,7 +53021,7 @@
       <c r="Y620" s="5"/>
       <c r="Z620" s="5"/>
     </row>
-    <row r="621" spans="1:26" ht="17.399999999999999">
+    <row r="621" spans="1:26" ht="16.5">
       <c r="A621" s="7"/>
       <c r="B621" s="7"/>
       <c r="C621" s="7"/>
@@ -53054,7 +53049,7 @@
       <c r="Y621" s="5"/>
       <c r="Z621" s="5"/>
     </row>
-    <row r="622" spans="1:26" ht="17.399999999999999">
+    <row r="622" spans="1:26" ht="16.5">
       <c r="A622" s="7"/>
       <c r="B622" s="7"/>
       <c r="C622" s="7"/>
@@ -53082,7 +53077,7 @@
       <c r="Y622" s="5"/>
       <c r="Z622" s="5"/>
     </row>
-    <row r="623" spans="1:26" ht="17.399999999999999">
+    <row r="623" spans="1:26" ht="16.5">
       <c r="A623" s="7"/>
       <c r="B623" s="7"/>
       <c r="C623" s="7"/>
@@ -53110,7 +53105,7 @@
       <c r="Y623" s="5"/>
       <c r="Z623" s="5"/>
     </row>
-    <row r="624" spans="1:26" ht="17.399999999999999">
+    <row r="624" spans="1:26" ht="16.5">
       <c r="A624" s="7"/>
       <c r="B624" s="7"/>
       <c r="C624" s="7"/>
@@ -53138,7 +53133,7 @@
       <c r="Y624" s="5"/>
       <c r="Z624" s="5"/>
     </row>
-    <row r="625" spans="1:26" ht="17.399999999999999">
+    <row r="625" spans="1:26" ht="16.5">
       <c r="A625" s="7"/>
       <c r="B625" s="7"/>
       <c r="C625" s="7"/>
@@ -53166,7 +53161,7 @@
       <c r="Y625" s="5"/>
       <c r="Z625" s="5"/>
     </row>
-    <row r="626" spans="1:26" ht="17.399999999999999">
+    <row r="626" spans="1:26" ht="16.5">
       <c r="A626" s="7"/>
       <c r="B626" s="7"/>
       <c r="C626" s="7"/>
@@ -53194,7 +53189,7 @@
       <c r="Y626" s="5"/>
       <c r="Z626" s="5"/>
     </row>
-    <row r="627" spans="1:26" ht="17.399999999999999">
+    <row r="627" spans="1:26" ht="16.5">
       <c r="A627" s="7"/>
       <c r="B627" s="7"/>
       <c r="C627" s="7"/>
@@ -53222,7 +53217,7 @@
       <c r="Y627" s="5"/>
       <c r="Z627" s="5"/>
     </row>
-    <row r="628" spans="1:26" ht="17.399999999999999">
+    <row r="628" spans="1:26" ht="16.5">
       <c r="A628" s="7"/>
       <c r="B628" s="7"/>
       <c r="C628" s="7"/>
@@ -53250,7 +53245,7 @@
       <c r="Y628" s="5"/>
       <c r="Z628" s="5"/>
     </row>
-    <row r="629" spans="1:26" ht="17.399999999999999">
+    <row r="629" spans="1:26" ht="16.5">
       <c r="A629" s="7"/>
       <c r="B629" s="7"/>
       <c r="C629" s="7"/>
@@ -53278,7 +53273,7 @@
       <c r="Y629" s="5"/>
       <c r="Z629" s="5"/>
     </row>
-    <row r="630" spans="1:26" ht="17.399999999999999">
+    <row r="630" spans="1:26" ht="16.5">
       <c r="A630" s="7"/>
       <c r="B630" s="7"/>
       <c r="C630" s="7"/>
@@ -53306,7 +53301,7 @@
       <c r="Y630" s="5"/>
       <c r="Z630" s="5"/>
     </row>
-    <row r="631" spans="1:26" ht="17.399999999999999">
+    <row r="631" spans="1:26" ht="16.5">
       <c r="A631" s="7"/>
       <c r="B631" s="7"/>
       <c r="C631" s="7"/>
@@ -53334,7 +53329,7 @@
       <c r="Y631" s="5"/>
       <c r="Z631" s="5"/>
     </row>
-    <row r="632" spans="1:26" ht="17.399999999999999">
+    <row r="632" spans="1:26" ht="16.5">
       <c r="A632" s="7"/>
       <c r="B632" s="7"/>
       <c r="C632" s="7"/>
@@ -53362,7 +53357,7 @@
       <c r="Y632" s="5"/>
       <c r="Z632" s="5"/>
     </row>
-    <row r="633" spans="1:26" ht="17.399999999999999">
+    <row r="633" spans="1:26" ht="16.5">
       <c r="A633" s="7"/>
       <c r="B633" s="7"/>
       <c r="C633" s="7"/>
@@ -53390,7 +53385,7 @@
       <c r="Y633" s="5"/>
       <c r="Z633" s="5"/>
     </row>
-    <row r="634" spans="1:26" ht="17.399999999999999">
+    <row r="634" spans="1:26" ht="16.5">
       <c r="A634" s="7"/>
       <c r="B634" s="7"/>
       <c r="C634" s="7"/>
@@ -53418,7 +53413,7 @@
       <c r="Y634" s="5"/>
       <c r="Z634" s="5"/>
     </row>
-    <row r="635" spans="1:26" ht="17.399999999999999">
+    <row r="635" spans="1:26" ht="16.5">
       <c r="A635" s="7"/>
       <c r="B635" s="7"/>
       <c r="C635" s="7"/>
@@ -53446,7 +53441,7 @@
       <c r="Y635" s="5"/>
       <c r="Z635" s="5"/>
     </row>
-    <row r="636" spans="1:26" ht="17.399999999999999">
+    <row r="636" spans="1:26" ht="16.5">
       <c r="A636" s="7"/>
       <c r="B636" s="7"/>
       <c r="C636" s="7"/>
@@ -53474,7 +53469,7 @@
       <c r="Y636" s="5"/>
       <c r="Z636" s="5"/>
     </row>
-    <row r="637" spans="1:26" ht="17.399999999999999">
+    <row r="637" spans="1:26" ht="16.5">
       <c r="A637" s="7"/>
       <c r="B637" s="7"/>
       <c r="C637" s="7"/>
@@ -53502,7 +53497,7 @@
       <c r="Y637" s="5"/>
       <c r="Z637" s="5"/>
     </row>
-    <row r="638" spans="1:26" ht="17.399999999999999">
+    <row r="638" spans="1:26" ht="16.5">
       <c r="A638" s="7"/>
       <c r="B638" s="7"/>
       <c r="C638" s="7"/>
@@ -53530,7 +53525,7 @@
       <c r="Y638" s="5"/>
       <c r="Z638" s="5"/>
     </row>
-    <row r="639" spans="1:26" ht="17.399999999999999">
+    <row r="639" spans="1:26" ht="16.5">
       <c r="A639" s="7"/>
       <c r="B639" s="7"/>
       <c r="C639" s="7"/>
@@ -53558,7 +53553,7 @@
       <c r="Y639" s="5"/>
       <c r="Z639" s="5"/>
     </row>
-    <row r="640" spans="1:26" ht="17.399999999999999">
+    <row r="640" spans="1:26" ht="16.5">
       <c r="A640" s="7"/>
       <c r="B640" s="7"/>
       <c r="C640" s="7"/>
@@ -53586,7 +53581,7 @@
       <c r="Y640" s="5"/>
       <c r="Z640" s="5"/>
     </row>
-    <row r="641" spans="1:26" ht="17.399999999999999">
+    <row r="641" spans="1:26" ht="16.5">
       <c r="A641" s="7"/>
       <c r="B641" s="7"/>
       <c r="C641" s="7"/>
@@ -53614,7 +53609,7 @@
       <c r="Y641" s="5"/>
       <c r="Z641" s="5"/>
     </row>
-    <row r="642" spans="1:26" ht="17.399999999999999">
+    <row r="642" spans="1:26" ht="16.5">
       <c r="A642" s="7"/>
       <c r="B642" s="7"/>
       <c r="C642" s="7"/>
@@ -53642,7 +53637,7 @@
       <c r="Y642" s="5"/>
       <c r="Z642" s="5"/>
     </row>
-    <row r="643" spans="1:26" ht="17.399999999999999">
+    <row r="643" spans="1:26" ht="16.5">
       <c r="A643" s="7"/>
       <c r="B643" s="7"/>
       <c r="C643" s="7"/>
@@ -53670,7 +53665,7 @@
       <c r="Y643" s="5"/>
       <c r="Z643" s="5"/>
     </row>
-    <row r="644" spans="1:26" ht="17.399999999999999">
+    <row r="644" spans="1:26" ht="16.5">
       <c r="A644" s="7"/>
       <c r="B644" s="7"/>
       <c r="C644" s="7"/>
@@ -53698,7 +53693,7 @@
       <c r="Y644" s="5"/>
       <c r="Z644" s="5"/>
     </row>
-    <row r="645" spans="1:26" ht="17.399999999999999">
+    <row r="645" spans="1:26" ht="16.5">
       <c r="A645" s="7"/>
       <c r="B645" s="7"/>
       <c r="C645" s="7"/>
@@ -53726,7 +53721,7 @@
       <c r="Y645" s="5"/>
       <c r="Z645" s="5"/>
     </row>
-    <row r="646" spans="1:26" ht="17.399999999999999">
+    <row r="646" spans="1:26" ht="16.5">
       <c r="A646" s="7"/>
       <c r="B646" s="7"/>
       <c r="C646" s="7"/>
@@ -53754,7 +53749,7 @@
       <c r="Y646" s="5"/>
       <c r="Z646" s="5"/>
     </row>
-    <row r="647" spans="1:26" ht="17.399999999999999">
+    <row r="647" spans="1:26" ht="16.5">
       <c r="A647" s="7"/>
       <c r="B647" s="7"/>
       <c r="C647" s="7"/>
@@ -53782,7 +53777,7 @@
       <c r="Y647" s="5"/>
       <c r="Z647" s="5"/>
     </row>
-    <row r="648" spans="1:26" ht="17.399999999999999">
+    <row r="648" spans="1:26" ht="16.5">
       <c r="A648" s="7"/>
       <c r="B648" s="7"/>
       <c r="C648" s="7"/>
@@ -53810,7 +53805,7 @@
       <c r="Y648" s="5"/>
       <c r="Z648" s="5"/>
     </row>
-    <row r="649" spans="1:26" ht="17.399999999999999">
+    <row r="649" spans="1:26" ht="16.5">
       <c r="A649" s="7"/>
       <c r="B649" s="7"/>
       <c r="C649" s="7"/>
@@ -53838,7 +53833,7 @@
       <c r="Y649" s="5"/>
       <c r="Z649" s="5"/>
     </row>
-    <row r="650" spans="1:26" ht="17.399999999999999">
+    <row r="650" spans="1:26" ht="16.5">
       <c r="A650" s="7"/>
       <c r="B650" s="7"/>
       <c r="C650" s="7"/>
@@ -53866,7 +53861,7 @@
       <c r="Y650" s="5"/>
       <c r="Z650" s="5"/>
     </row>
-    <row r="651" spans="1:26" ht="17.399999999999999">
+    <row r="651" spans="1:26" ht="16.5">
       <c r="A651" s="7"/>
       <c r="B651" s="7"/>
       <c r="C651" s="7"/>
@@ -53894,7 +53889,7 @@
       <c r="Y651" s="5"/>
       <c r="Z651" s="5"/>
     </row>
-    <row r="652" spans="1:26" ht="17.399999999999999">
+    <row r="652" spans="1:26" ht="16.5">
       <c r="A652" s="7"/>
       <c r="B652" s="7"/>
       <c r="C652" s="7"/>
@@ -53922,7 +53917,7 @@
       <c r="Y652" s="5"/>
       <c r="Z652" s="5"/>
     </row>
-    <row r="653" spans="1:26" ht="17.399999999999999">
+    <row r="653" spans="1:26" ht="16.5">
       <c r="A653" s="7"/>
       <c r="B653" s="7"/>
       <c r="C653" s="7"/>
@@ -53950,7 +53945,7 @@
       <c r="Y653" s="5"/>
       <c r="Z653" s="5"/>
     </row>
-    <row r="654" spans="1:26" ht="17.399999999999999">
+    <row r="654" spans="1:26" ht="16.5">
       <c r="A654" s="7"/>
       <c r="B654" s="7"/>
       <c r="C654" s="7"/>
@@ -53978,7 +53973,7 @@
       <c r="Y654" s="5"/>
       <c r="Z654" s="5"/>
     </row>
-    <row r="655" spans="1:26" ht="17.399999999999999">
+    <row r="655" spans="1:26" ht="16.5">
       <c r="A655" s="7"/>
       <c r="B655" s="7"/>
       <c r="C655" s="7"/>
@@ -54006,7 +54001,7 @@
       <c r="Y655" s="5"/>
       <c r="Z655" s="5"/>
     </row>
-    <row r="656" spans="1:26" ht="17.399999999999999">
+    <row r="656" spans="1:26" ht="16.5">
       <c r="A656" s="7"/>
       <c r="B656" s="7"/>
       <c r="C656" s="7"/>
@@ -54034,7 +54029,7 @@
       <c r="Y656" s="5"/>
       <c r="Z656" s="5"/>
     </row>
-    <row r="657" spans="1:26" ht="17.399999999999999">
+    <row r="657" spans="1:26" ht="16.5">
       <c r="A657" s="7"/>
       <c r="B657" s="7"/>
       <c r="C657" s="7"/>
@@ -54062,7 +54057,7 @@
       <c r="Y657" s="5"/>
       <c r="Z657" s="5"/>
     </row>
-    <row r="658" spans="1:26" ht="17.399999999999999">
+    <row r="658" spans="1:26" ht="16.5">
       <c r="A658" s="7"/>
       <c r="B658" s="7"/>
       <c r="C658" s="7"/>
@@ -54090,7 +54085,7 @@
       <c r="Y658" s="5"/>
       <c r="Z658" s="5"/>
     </row>
-    <row r="659" spans="1:26" ht="17.399999999999999">
+    <row r="659" spans="1:26" ht="16.5">
       <c r="A659" s="7"/>
       <c r="B659" s="7"/>
       <c r="C659" s="7"/>
@@ -54118,7 +54113,7 @@
       <c r="Y659" s="5"/>
       <c r="Z659" s="5"/>
     </row>
-    <row r="660" spans="1:26" ht="17.399999999999999">
+    <row r="660" spans="1:26" ht="16.5">
       <c r="A660" s="7"/>
       <c r="B660" s="7"/>
       <c r="C660" s="7"/>
@@ -54146,7 +54141,7 @@
       <c r="Y660" s="5"/>
       <c r="Z660" s="5"/>
     </row>
-    <row r="661" spans="1:26" ht="17.399999999999999">
+    <row r="661" spans="1:26" ht="16.5">
       <c r="A661" s="7"/>
       <c r="B661" s="7"/>
       <c r="C661" s="7"/>
@@ -54174,7 +54169,7 @@
       <c r="Y661" s="5"/>
       <c r="Z661" s="5"/>
     </row>
-    <row r="662" spans="1:26" ht="17.399999999999999">
+    <row r="662" spans="1:26" ht="16.5">
       <c r="A662" s="7"/>
       <c r="B662" s="7"/>
       <c r="C662" s="7"/>
@@ -54202,7 +54197,7 @@
       <c r="Y662" s="5"/>
       <c r="Z662" s="5"/>
     </row>
-    <row r="663" spans="1:26" ht="17.399999999999999">
+    <row r="663" spans="1:26" ht="16.5">
       <c r="A663" s="7"/>
       <c r="B663" s="7"/>
       <c r="C663" s="7"/>
@@ -54230,7 +54225,7 @@
       <c r="Y663" s="5"/>
       <c r="Z663" s="5"/>
     </row>
-    <row r="664" spans="1:26" ht="17.399999999999999">
+    <row r="664" spans="1:26" ht="16.5">
       <c r="A664" s="7"/>
       <c r="B664" s="7"/>
       <c r="C664" s="7"/>
@@ -54258,7 +54253,7 @@
       <c r="Y664" s="5"/>
       <c r="Z664" s="5"/>
     </row>
-    <row r="665" spans="1:26" ht="17.399999999999999">
+    <row r="665" spans="1:26" ht="16.5">
       <c r="A665" s="7"/>
       <c r="B665" s="7"/>
       <c r="C665" s="7"/>
@@ -54286,7 +54281,7 @@
       <c r="Y665" s="5"/>
       <c r="Z665" s="5"/>
     </row>
-    <row r="666" spans="1:26" ht="17.399999999999999">
+    <row r="666" spans="1:26" ht="16.5">
       <c r="A666" s="7"/>
       <c r="B666" s="7"/>
       <c r="C666" s="7"/>
@@ -54314,7 +54309,7 @@
       <c r="Y666" s="5"/>
       <c r="Z666" s="5"/>
     </row>
-    <row r="667" spans="1:26" ht="17.399999999999999">
+    <row r="667" spans="1:26" ht="16.5">
       <c r="A667" s="7"/>
       <c r="B667" s="7"/>
       <c r="C667" s="7"/>
@@ -54342,7 +54337,7 @@
       <c r="Y667" s="5"/>
       <c r="Z667" s="5"/>
     </row>
-    <row r="668" spans="1:26" ht="17.399999999999999">
+    <row r="668" spans="1:26" ht="16.5">
       <c r="A668" s="7"/>
       <c r="B668" s="7"/>
       <c r="C668" s="7"/>
@@ -54370,7 +54365,7 @@
       <c r="Y668" s="5"/>
       <c r="Z668" s="5"/>
     </row>
-    <row r="669" spans="1:26" ht="17.399999999999999">
+    <row r="669" spans="1:26" ht="16.5">
       <c r="A669" s="7"/>
       <c r="B669" s="7"/>
       <c r="C669" s="7"/>
@@ -54398,7 +54393,7 @@
       <c r="Y669" s="5"/>
       <c r="Z669" s="5"/>
     </row>
-    <row r="670" spans="1:26" ht="17.399999999999999">
+    <row r="670" spans="1:26" ht="16.5">
       <c r="A670" s="7"/>
       <c r="B670" s="7"/>
       <c r="C670" s="7"/>
@@ -54426,7 +54421,7 @@
       <c r="Y670" s="5"/>
       <c r="Z670" s="5"/>
     </row>
-    <row r="671" spans="1:26" ht="17.399999999999999">
+    <row r="671" spans="1:26" ht="16.5">
       <c r="A671" s="7"/>
       <c r="B671" s="7"/>
       <c r="C671" s="7"/>
@@ -54454,7 +54449,7 @@
       <c r="Y671" s="5"/>
       <c r="Z671" s="5"/>
     </row>
-    <row r="672" spans="1:26" ht="17.399999999999999">
+    <row r="672" spans="1:26" ht="16.5">
       <c r="A672" s="7"/>
       <c r="B672" s="7"/>
       <c r="C672" s="7"/>
@@ -54482,7 +54477,7 @@
       <c r="Y672" s="5"/>
       <c r="Z672" s="5"/>
     </row>
-    <row r="673" spans="1:26" ht="17.399999999999999">
+    <row r="673" spans="1:26" ht="16.5">
       <c r="A673" s="7"/>
       <c r="B673" s="7"/>
       <c r="C673" s="7"/>
@@ -54510,7 +54505,7 @@
       <c r="Y673" s="5"/>
       <c r="Z673" s="5"/>
     </row>
-    <row r="674" spans="1:26" ht="17.399999999999999">
+    <row r="674" spans="1:26" ht="16.5">
       <c r="A674" s="7"/>
       <c r="B674" s="7"/>
       <c r="C674" s="7"/>
@@ -54538,7 +54533,7 @@
       <c r="Y674" s="5"/>
       <c r="Z674" s="5"/>
     </row>
-    <row r="675" spans="1:26" ht="17.399999999999999">
+    <row r="675" spans="1:26" ht="16.5">
       <c r="A675" s="7"/>
       <c r="B675" s="7"/>
       <c r="C675" s="7"/>
@@ -54566,7 +54561,7 @@
       <c r="Y675" s="5"/>
       <c r="Z675" s="5"/>
     </row>
-    <row r="676" spans="1:26" ht="17.399999999999999">
+    <row r="676" spans="1:26" ht="16.5">
       <c r="A676" s="7"/>
       <c r="B676" s="7"/>
       <c r="C676" s="7"/>
@@ -54594,7 +54589,7 @@
       <c r="Y676" s="5"/>
       <c r="Z676" s="5"/>
     </row>
-    <row r="677" spans="1:26" ht="17.399999999999999">
+    <row r="677" spans="1:26" ht="16.5">
       <c r="A677" s="7"/>
       <c r="B677" s="7"/>
       <c r="C677" s="7"/>
@@ -54622,7 +54617,7 @@
       <c r="Y677" s="5"/>
       <c r="Z677" s="5"/>
     </row>
-    <row r="678" spans="1:26" ht="17.399999999999999">
+    <row r="678" spans="1:26" ht="16.5">
       <c r="A678" s="7"/>
       <c r="B678" s="7"/>
       <c r="C678" s="7"/>
@@ -54650,7 +54645,7 @@
       <c r="Y678" s="5"/>
       <c r="Z678" s="5"/>
     </row>
-    <row r="679" spans="1:26" ht="17.399999999999999">
+    <row r="679" spans="1:26" ht="16.5">
       <c r="A679" s="7"/>
       <c r="B679" s="7"/>
       <c r="C679" s="7"/>
@@ -54678,7 +54673,7 @@
       <c r="Y679" s="5"/>
       <c r="Z679" s="5"/>
     </row>
-    <row r="680" spans="1:26" ht="17.399999999999999">
+    <row r="680" spans="1:26" ht="16.5">
       <c r="A680" s="7"/>
       <c r="B680" s="7"/>
       <c r="C680" s="7"/>
@@ -54706,7 +54701,7 @@
       <c r="Y680" s="5"/>
       <c r="Z680" s="5"/>
     </row>
-    <row r="681" spans="1:26" ht="17.399999999999999">
+    <row r="681" spans="1:26" ht="16.5">
       <c r="A681" s="7"/>
       <c r="B681" s="7"/>
       <c r="C681" s="7"/>
@@ -54734,7 +54729,7 @@
       <c r="Y681" s="5"/>
       <c r="Z681" s="5"/>
     </row>
-    <row r="682" spans="1:26" ht="17.399999999999999">
+    <row r="682" spans="1:26" ht="16.5">
       <c r="A682" s="7"/>
       <c r="B682" s="7"/>
       <c r="C682" s="7"/>
@@ -54762,7 +54757,7 @@
       <c r="Y682" s="5"/>
       <c r="Z682" s="5"/>
     </row>
-    <row r="683" spans="1:26" ht="17.399999999999999">
+    <row r="683" spans="1:26" ht="16.5">
       <c r="A683" s="7"/>
       <c r="B683" s="7"/>
       <c r="C683" s="7"/>
@@ -54790,7 +54785,7 @@
       <c r="Y683" s="5"/>
       <c r="Z683" s="5"/>
     </row>
-    <row r="684" spans="1:26" ht="17.399999999999999">
+    <row r="684" spans="1:26" ht="16.5">
       <c r="A684" s="7"/>
       <c r="B684" s="7"/>
       <c r="C684" s="7"/>
@@ -54818,7 +54813,7 @@
       <c r="Y684" s="5"/>
       <c r="Z684" s="5"/>
     </row>
-    <row r="685" spans="1:26" ht="17.399999999999999">
+    <row r="685" spans="1:26" ht="16.5">
       <c r="A685" s="7"/>
       <c r="B685" s="7"/>
       <c r="C685" s="7"/>
@@ -54846,7 +54841,7 @@
       <c r="Y685" s="5"/>
       <c r="Z685" s="5"/>
     </row>
-    <row r="686" spans="1:26" ht="17.399999999999999">
+    <row r="686" spans="1:26" ht="16.5">
       <c r="A686" s="7"/>
       <c r="B686" s="7"/>
       <c r="C686" s="7"/>
@@ -54874,7 +54869,7 @@
       <c r="Y686" s="5"/>
       <c r="Z686" s="5"/>
     </row>
-    <row r="687" spans="1:26" ht="17.399999999999999">
+    <row r="687" spans="1:26" ht="16.5">
       <c r="A687" s="7"/>
       <c r="B687" s="7"/>
       <c r="C687" s="7"/>
@@ -54902,7 +54897,7 @@
       <c r="Y687" s="5"/>
       <c r="Z687" s="5"/>
     </row>
-    <row r="688" spans="1:26" ht="17.399999999999999">
+    <row r="688" spans="1:26" ht="16.5">
       <c r="A688" s="7"/>
       <c r="B688" s="7"/>
       <c r="C688" s="7"/>
@@ -54930,7 +54925,7 @@
       <c r="Y688" s="5"/>
       <c r="Z688" s="5"/>
     </row>
-    <row r="689" spans="1:26" ht="17.399999999999999">
+    <row r="689" spans="1:26" ht="16.5">
       <c r="A689" s="7"/>
       <c r="B689" s="7"/>
       <c r="C689" s="7"/>
@@ -54958,7 +54953,7 @@
       <c r="Y689" s="5"/>
       <c r="Z689" s="5"/>
     </row>
-    <row r="690" spans="1:26" ht="17.399999999999999">
+    <row r="690" spans="1:26" ht="16.5">
       <c r="A690" s="7"/>
       <c r="B690" s="7"/>
       <c r="C690" s="7"/>
@@ -54986,7 +54981,7 @@
       <c r="Y690" s="5"/>
       <c r="Z690" s="5"/>
     </row>
-    <row r="691" spans="1:26" ht="17.399999999999999">
+    <row r="691" spans="1:26" ht="16.5">
       <c r="A691" s="7"/>
       <c r="B691" s="7"/>
       <c r="C691" s="7"/>
@@ -55014,7 +55009,7 @@
       <c r="Y691" s="5"/>
       <c r="Z691" s="5"/>
     </row>
-    <row r="692" spans="1:26" ht="17.399999999999999">
+    <row r="692" spans="1:26" ht="16.5">
       <c r="A692" s="7"/>
       <c r="B692" s="7"/>
       <c r="C692" s="7"/>
@@ -55042,7 +55037,7 @@
       <c r="Y692" s="5"/>
       <c r="Z692" s="5"/>
     </row>
-    <row r="693" spans="1:26" ht="17.399999999999999">
+    <row r="693" spans="1:26" ht="16.5">
       <c r="A693" s="7"/>
       <c r="B693" s="7"/>
       <c r="C693" s="7"/>
@@ -55070,7 +55065,7 @@
       <c r="Y693" s="5"/>
       <c r="Z693" s="5"/>
     </row>
-    <row r="694" spans="1:26" ht="17.399999999999999">
+    <row r="694" spans="1:26" ht="16.5">
       <c r="A694" s="7"/>
       <c r="B694" s="7"/>
       <c r="C694" s="7"/>
@@ -55098,7 +55093,7 @@
       <c r="Y694" s="5"/>
       <c r="Z694" s="5"/>
     </row>
-    <row r="695" spans="1:26" ht="17.399999999999999">
+    <row r="695" spans="1:26" ht="16.5">
       <c r="A695" s="7"/>
       <c r="B695" s="7"/>
       <c r="C695" s="7"/>
@@ -55126,7 +55121,7 @@
       <c r="Y695" s="5"/>
       <c r="Z695" s="5"/>
     </row>
-    <row r="696" spans="1:26" ht="17.399999999999999">
+    <row r="696" spans="1:26" ht="16.5">
       <c r="A696" s="7"/>
       <c r="B696" s="7"/>
       <c r="C696" s="7"/>
@@ -55154,7 +55149,7 @@
       <c r="Y696" s="5"/>
       <c r="Z696" s="5"/>
     </row>
-    <row r="697" spans="1:26" ht="17.399999999999999">
+    <row r="697" spans="1:26" ht="16.5">
       <c r="A697" s="7"/>
       <c r="B697" s="7"/>
       <c r="C697" s="7"/>
@@ -55182,7 +55177,7 @@
       <c r="Y697" s="5"/>
       <c r="Z697" s="5"/>
     </row>
-    <row r="698" spans="1:26" ht="17.399999999999999">
+    <row r="698" spans="1:26" ht="16.5">
       <c r="A698" s="7"/>
       <c r="B698" s="7"/>
       <c r="C698" s="7"/>
@@ -55210,7 +55205,7 @@
       <c r="Y698" s="5"/>
       <c r="Z698" s="5"/>
     </row>
-    <row r="699" spans="1:26" ht="17.399999999999999">
+    <row r="699" spans="1:26" ht="16.5">
       <c r="A699" s="7"/>
       <c r="B699" s="7"/>
       <c r="C699" s="7"/>
@@ -55238,7 +55233,7 @@
       <c r="Y699" s="5"/>
       <c r="Z699" s="5"/>
     </row>
-    <row r="700" spans="1:26" ht="17.399999999999999">
+    <row r="700" spans="1:26" ht="16.5">
       <c r="A700" s="7"/>
       <c r="B700" s="7"/>
       <c r="C700" s="7"/>
@@ -55266,7 +55261,7 @@
       <c r="Y700" s="5"/>
       <c r="Z700" s="5"/>
     </row>
-    <row r="701" spans="1:26" ht="17.399999999999999">
+    <row r="701" spans="1:26" ht="16.5">
       <c r="A701" s="7"/>
       <c r="B701" s="7"/>
       <c r="C701" s="7"/>
@@ -55294,7 +55289,7 @@
       <c r="Y701" s="5"/>
       <c r="Z701" s="5"/>
     </row>
-    <row r="702" spans="1:26" ht="17.399999999999999">
+    <row r="702" spans="1:26" ht="16.5">
       <c r="A702" s="7"/>
       <c r="B702" s="7"/>
       <c r="C702" s="7"/>
@@ -55322,7 +55317,7 @@
       <c r="Y702" s="5"/>
       <c r="Z702" s="5"/>
     </row>
-    <row r="703" spans="1:26" ht="17.399999999999999">
+    <row r="703" spans="1:26" ht="16.5">
       <c r="A703" s="7"/>
       <c r="B703" s="7"/>
       <c r="C703" s="7"/>
@@ -55350,7 +55345,7 @@
       <c r="Y703" s="5"/>
       <c r="Z703" s="5"/>
     </row>
-    <row r="704" spans="1:26" ht="17.399999999999999">
+    <row r="704" spans="1:26" ht="16.5">
       <c r="A704" s="7"/>
       <c r="B704" s="7"/>
       <c r="C704" s="7"/>
@@ -55378,7 +55373,7 @@
       <c r="Y704" s="5"/>
       <c r="Z704" s="5"/>
     </row>
-    <row r="705" spans="1:26" ht="17.399999999999999">
+    <row r="705" spans="1:26" ht="16.5">
       <c r="A705" s="7"/>
       <c r="B705" s="7"/>
       <c r="C705" s="7"/>
@@ -55406,7 +55401,7 @@
       <c r="Y705" s="5"/>
       <c r="Z705" s="5"/>
     </row>
-    <row r="706" spans="1:26" ht="17.399999999999999">
+    <row r="706" spans="1:26" ht="16.5">
       <c r="A706" s="7"/>
       <c r="B706" s="7"/>
       <c r="C706" s="7"/>
@@ -55434,7 +55429,7 @@
       <c r="Y706" s="5"/>
       <c r="Z706" s="5"/>
     </row>
-    <row r="707" spans="1:26" ht="17.399999999999999">
+    <row r="707" spans="1:26" ht="16.5">
       <c r="A707" s="7"/>
       <c r="B707" s="7"/>
       <c r="C707" s="7"/>
@@ -55462,7 +55457,7 @@
       <c r="Y707" s="5"/>
       <c r="Z707" s="5"/>
     </row>
-    <row r="708" spans="1:26" ht="17.399999999999999">
+    <row r="708" spans="1:26" ht="16.5">
       <c r="A708" s="7"/>
       <c r="B708" s="7"/>
       <c r="C708" s="7"/>
@@ -55490,7 +55485,7 @@
       <c r="Y708" s="5"/>
       <c r="Z708" s="5"/>
     </row>
-    <row r="709" spans="1:26" ht="17.399999999999999">
+    <row r="709" spans="1:26" ht="16.5">
       <c r="A709" s="7"/>
       <c r="B709" s="7"/>
       <c r="C709" s="7"/>
@@ -55518,7 +55513,7 @@
       <c r="Y709" s="5"/>
       <c r="Z709" s="5"/>
     </row>
-    <row r="710" spans="1:26" ht="17.399999999999999">
+    <row r="710" spans="1:26" ht="16.5">
       <c r="A710" s="7"/>
       <c r="B710" s="7"/>
       <c r="C710" s="7"/>
@@ -55546,7 +55541,7 @@
       <c r="Y710" s="5"/>
       <c r="Z710" s="5"/>
     </row>
-    <row r="711" spans="1:26" ht="17.399999999999999">
+    <row r="711" spans="1:26" ht="16.5">
       <c r="A711" s="7"/>
       <c r="B711" s="7"/>
       <c r="C711" s="7"/>
@@ -55574,7 +55569,7 @@
       <c r="Y711" s="5"/>
       <c r="Z711" s="5"/>
     </row>
-    <row r="712" spans="1:26" ht="17.399999999999999">
+    <row r="712" spans="1:26" ht="16.5">
       <c r="A712" s="7"/>
       <c r="B712" s="7"/>
       <c r="C712" s="7"/>
@@ -55602,7 +55597,7 @@
       <c r="Y712" s="5"/>
       <c r="Z712" s="5"/>
     </row>
-    <row r="713" spans="1:26" ht="17.399999999999999">
+    <row r="713" spans="1:26" ht="16.5">
       <c r="A713" s="7"/>
       <c r="B713" s="7"/>
       <c r="C713" s="7"/>
@@ -55630,7 +55625,7 @@
       <c r="Y713" s="5"/>
       <c r="Z713" s="5"/>
     </row>
-    <row r="714" spans="1:26" ht="17.399999999999999">
+    <row r="714" spans="1:26" ht="16.5">
       <c r="A714" s="7"/>
       <c r="B714" s="7"/>
       <c r="C714" s="7"/>
@@ -55658,7 +55653,7 @@
       <c r="Y714" s="5"/>
       <c r="Z714" s="5"/>
     </row>
-    <row r="715" spans="1:26" ht="17.399999999999999">
+    <row r="715" spans="1:26" ht="16.5">
       <c r="A715" s="7"/>
       <c r="B715" s="7"/>
       <c r="C715" s="7"/>
@@ -55686,7 +55681,7 @@
       <c r="Y715" s="5"/>
       <c r="Z715" s="5"/>
     </row>
-    <row r="716" spans="1:26" ht="17.399999999999999">
+    <row r="716" spans="1:26" ht="16.5">
       <c r="A716" s="7"/>
       <c r="B716" s="7"/>
       <c r="C716" s="7"/>
@@ -55714,7 +55709,7 @@
       <c r="Y716" s="5"/>
       <c r="Z716" s="5"/>
     </row>
-    <row r="717" spans="1:26" ht="17.399999999999999">
+    <row r="717" spans="1:26" ht="16.5">
       <c r="A717" s="7"/>
       <c r="B717" s="7"/>
       <c r="C717" s="7"/>
@@ -55742,7 +55737,7 @@
       <c r="Y717" s="5"/>
       <c r="Z717" s="5"/>
     </row>
-    <row r="718" spans="1:26" ht="17.399999999999999">
+    <row r="718" spans="1:26" ht="16.5">
       <c r="A718" s="7"/>
       <c r="B718" s="7"/>
       <c r="C718" s="7"/>
@@ -55770,7 +55765,7 @@
       <c r="Y718" s="5"/>
       <c r="Z718" s="5"/>
     </row>
-    <row r="719" spans="1:26" ht="17.399999999999999">
+    <row r="719" spans="1:26" ht="16.5">
       <c r="A719" s="7"/>
       <c r="B719" s="7"/>
       <c r="C719" s="7"/>
@@ -55798,7 +55793,7 @@
       <c r="Y719" s="5"/>
       <c r="Z719" s="5"/>
     </row>
-    <row r="720" spans="1:26" ht="17.399999999999999">
+    <row r="720" spans="1:26" ht="16.5">
       <c r="A720" s="7"/>
       <c r="B720" s="7"/>
       <c r="C720" s="7"/>
@@ -55826,7 +55821,7 @@
       <c r="Y720" s="5"/>
       <c r="Z720" s="5"/>
     </row>
-    <row r="721" spans="1:26" ht="17.399999999999999">
+    <row r="721" spans="1:26" ht="16.5">
       <c r="A721" s="7"/>
       <c r="B721" s="7"/>
       <c r="C721" s="7"/>
@@ -55854,7 +55849,7 @@
       <c r="Y721" s="5"/>
       <c r="Z721" s="5"/>
     </row>
-    <row r="722" spans="1:26" ht="17.399999999999999">
+    <row r="722" spans="1:26" ht="16.5">
       <c r="A722" s="7"/>
       <c r="B722" s="7"/>
       <c r="C722" s="7"/>
@@ -55882,7 +55877,7 @@
       <c r="Y722" s="5"/>
       <c r="Z722" s="5"/>
     </row>
-    <row r="723" spans="1:26" ht="17.399999999999999">
+    <row r="723" spans="1:26" ht="16.5">
       <c r="A723" s="7"/>
       <c r="B723" s="7"/>
       <c r="C723" s="7"/>
@@ -55910,7 +55905,7 @@
       <c r="Y723" s="5"/>
       <c r="Z723" s="5"/>
     </row>
-    <row r="724" spans="1:26" ht="17.399999999999999">
+    <row r="724" spans="1:26" ht="16.5">
       <c r="A724" s="7"/>
       <c r="B724" s="7"/>
       <c r="C724" s="7"/>
@@ -55938,7 +55933,7 @@
       <c r="Y724" s="5"/>
       <c r="Z724" s="5"/>
     </row>
-    <row r="725" spans="1:26" ht="17.399999999999999">
+    <row r="725" spans="1:26" ht="16.5">
       <c r="A725" s="7"/>
       <c r="B725" s="7"/>
       <c r="C725" s="7"/>
@@ -55966,7 +55961,7 @@
       <c r="Y725" s="5"/>
       <c r="Z725" s="5"/>
     </row>
-    <row r="726" spans="1:26" ht="17.399999999999999">
+    <row r="726" spans="1:26" ht="16.5">
       <c r="A726" s="7"/>
       <c r="B726" s="7"/>
       <c r="C726" s="7"/>
@@ -55994,7 +55989,7 @@
       <c r="Y726" s="5"/>
       <c r="Z726" s="5"/>
     </row>
-    <row r="727" spans="1:26" ht="17.399999999999999">
+    <row r="727" spans="1:26" ht="16.5">
       <c r="A727" s="7"/>
       <c r="B727" s="7"/>
       <c r="C727" s="7"/>
@@ -56022,7 +56017,7 @@
       <c r="Y727" s="5"/>
       <c r="Z727" s="5"/>
     </row>
-    <row r="728" spans="1:26" ht="17.399999999999999">
+    <row r="728" spans="1:26" ht="16.5">
       <c r="A728" s="7"/>
       <c r="B728" s="7"/>
       <c r="C728" s="7"/>
@@ -56050,7 +56045,7 @@
       <c r="Y728" s="5"/>
       <c r="Z728" s="5"/>
     </row>
-    <row r="729" spans="1:26" ht="17.399999999999999">
+    <row r="729" spans="1:26" ht="16.5">
       <c r="A729" s="7"/>
       <c r="B729" s="7"/>
       <c r="C729" s="7"/>
@@ -56078,7 +56073,7 @@
       <c r="Y729" s="5"/>
       <c r="Z729" s="5"/>
     </row>
-    <row r="730" spans="1:26" ht="17.399999999999999">
+    <row r="730" spans="1:26" ht="16.5">
       <c r="A730" s="7"/>
       <c r="B730" s="7"/>
       <c r="C730" s="7"/>
@@ -56106,7 +56101,7 @@
       <c r="Y730" s="5"/>
       <c r="Z730" s="5"/>
     </row>
-    <row r="731" spans="1:26" ht="17.399999999999999">
+    <row r="731" spans="1:26" ht="16.5">
       <c r="A731" s="7"/>
       <c r="B731" s="7"/>
       <c r="C731" s="7"/>
@@ -56134,7 +56129,7 @@
       <c r="Y731" s="5"/>
       <c r="Z731" s="5"/>
     </row>
-    <row r="732" spans="1:26" ht="17.399999999999999">
+    <row r="732" spans="1:26" ht="16.5">
       <c r="A732" s="7"/>
       <c r="B732" s="7"/>
       <c r="C732" s="7"/>
@@ -56162,7 +56157,7 @@
       <c r="Y732" s="5"/>
       <c r="Z732" s="5"/>
     </row>
-    <row r="733" spans="1:26" ht="17.399999999999999">
+    <row r="733" spans="1:26" ht="16.5">
       <c r="A733" s="7"/>
       <c r="B733" s="7"/>
       <c r="C733" s="7"/>
@@ -56190,7 +56185,7 @@
       <c r="Y733" s="5"/>
       <c r="Z733" s="5"/>
     </row>
-    <row r="734" spans="1:26" ht="17.399999999999999">
+    <row r="734" spans="1:26" ht="16.5">
       <c r="A734" s="7"/>
       <c r="B734" s="7"/>
       <c r="C734" s="7"/>
@@ -56218,7 +56213,7 @@
       <c r="Y734" s="5"/>
       <c r="Z734" s="5"/>
     </row>
-    <row r="735" spans="1:26" ht="17.399999999999999">
+    <row r="735" spans="1:26" ht="16.5">
       <c r="A735" s="7"/>
       <c r="B735" s="7"/>
       <c r="C735" s="7"/>
@@ -56246,7 +56241,7 @@
       <c r="Y735" s="5"/>
       <c r="Z735" s="5"/>
     </row>
-    <row r="736" spans="1:26" ht="17.399999999999999">
+    <row r="736" spans="1:26" ht="16.5">
       <c r="A736" s="7"/>
       <c r="B736" s="7"/>
       <c r="C736" s="7"/>
@@ -56274,7 +56269,7 @@
       <c r="Y736" s="5"/>
       <c r="Z736" s="5"/>
     </row>
-    <row r="737" spans="1:26" ht="17.399999999999999">
+    <row r="737" spans="1:26" ht="16.5">
       <c r="A737" s="7"/>
       <c r="B737" s="7"/>
       <c r="C737" s="7"/>
@@ -56302,7 +56297,7 @@
       <c r="Y737" s="5"/>
       <c r="Z737" s="5"/>
     </row>
-    <row r="738" spans="1:26" ht="17.399999999999999">
+    <row r="738" spans="1:26" ht="16.5">
       <c r="A738" s="7"/>
       <c r="B738" s="7"/>
       <c r="C738" s="7"/>
@@ -56330,7 +56325,7 @@
       <c r="Y738" s="5"/>
       <c r="Z738" s="5"/>
     </row>
-    <row r="739" spans="1:26" ht="17.399999999999999">
+    <row r="739" spans="1:26" ht="16.5">
       <c r="A739" s="7"/>
       <c r="B739" s="7"/>
       <c r="C739" s="7"/>
@@ -56358,7 +56353,7 @@
       <c r="Y739" s="5"/>
       <c r="Z739" s="5"/>
     </row>
-    <row r="740" spans="1:26" ht="17.399999999999999">
+    <row r="740" spans="1:26" ht="16.5">
       <c r="A740" s="7"/>
       <c r="B740" s="7"/>
       <c r="C740" s="7"/>
@@ -56386,7 +56381,7 @@
       <c r="Y740" s="5"/>
       <c r="Z740" s="5"/>
     </row>
-    <row r="741" spans="1:26" ht="17.399999999999999">
+    <row r="741" spans="1:26" ht="16.5">
       <c r="A741" s="7"/>
       <c r="B741" s="7"/>
       <c r="C741" s="7"/>
@@ -56414,7 +56409,7 @@
       <c r="Y741" s="5"/>
       <c r="Z741" s="5"/>
     </row>
-    <row r="742" spans="1:26" ht="17.399999999999999">
+    <row r="742" spans="1:26" ht="16.5">
       <c r="A742" s="7"/>
       <c r="B742" s="7"/>
       <c r="C742" s="7"/>
@@ -56442,7 +56437,7 @@
       <c r="Y742" s="5"/>
       <c r="Z742" s="5"/>
     </row>
-    <row r="743" spans="1:26" ht="17.399999999999999">
+    <row r="743" spans="1:26" ht="16.5">
       <c r="A743" s="7"/>
       <c r="B743" s="7"/>
       <c r="C743" s="7"/>
@@ -56470,7 +56465,7 @@
       <c r="Y743" s="5"/>
       <c r="Z743" s="5"/>
     </row>
-    <row r="744" spans="1:26" ht="17.399999999999999">
+    <row r="744" spans="1:26" ht="16.5">
       <c r="A744" s="7"/>
       <c r="B744" s="7"/>
       <c r="C744" s="7"/>
@@ -56498,7 +56493,7 @@
       <c r="Y744" s="5"/>
       <c r="Z744" s="5"/>
     </row>
-    <row r="745" spans="1:26" ht="17.399999999999999">
+    <row r="745" spans="1:26" ht="16.5">
       <c r="A745" s="7"/>
       <c r="B745" s="7"/>
       <c r="C745" s="7"/>
@@ -56526,7 +56521,7 @@
       <c r="Y745" s="5"/>
       <c r="Z745" s="5"/>
     </row>
-    <row r="746" spans="1:26" ht="17.399999999999999">
+    <row r="746" spans="1:26" ht="16.5">
       <c r="A746" s="7"/>
       <c r="B746" s="7"/>
       <c r="C746" s="7"/>
@@ -56554,7 +56549,7 @@
       <c r="Y746" s="5"/>
       <c r="Z746" s="5"/>
     </row>
-    <row r="747" spans="1:26" ht="17.399999999999999">
+    <row r="747" spans="1:26" ht="16.5">
       <c r="A747" s="7"/>
       <c r="B747" s="7"/>
       <c r="C747" s="7"/>
@@ -56582,7 +56577,7 @@
       <c r="Y747" s="5"/>
       <c r="Z747" s="5"/>
     </row>
-    <row r="748" spans="1:26" ht="17.399999999999999">
+    <row r="748" spans="1:26" ht="16.5">
       <c r="A748" s="7"/>
       <c r="B748" s="7"/>
       <c r="C748" s="7"/>
@@ -56610,7 +56605,7 @@
       <c r="Y748" s="5"/>
       <c r="Z748" s="5"/>
     </row>
-    <row r="749" spans="1:26" ht="17.399999999999999">
+    <row r="749" spans="1:26" ht="16.5">
       <c r="A749" s="7"/>
       <c r="B749" s="7"/>
       <c r="C749" s="7"/>
@@ -56638,7 +56633,7 @@
       <c r="Y749" s="5"/>
       <c r="Z749" s="5"/>
     </row>
-    <row r="750" spans="1:26" ht="17.399999999999999">
+    <row r="750" spans="1:26" ht="16.5">
       <c r="A750" s="7"/>
       <c r="B750" s="7"/>
       <c r="C750" s="7"/>
@@ -56666,7 +56661,7 @@
       <c r="Y750" s="5"/>
       <c r="Z750" s="5"/>
     </row>
-    <row r="751" spans="1:26" ht="17.399999999999999">
+    <row r="751" spans="1:26" ht="16.5">
       <c r="A751" s="7"/>
       <c r="B751" s="7"/>
       <c r="C751" s="7"/>
@@ -56694,7 +56689,7 @@
       <c r="Y751" s="5"/>
       <c r="Z751" s="5"/>
     </row>
-    <row r="752" spans="1:26" ht="17.399999999999999">
+    <row r="752" spans="1:26" ht="16.5">
       <c r="A752" s="7"/>
       <c r="B752" s="7"/>
       <c r="C752" s="7"/>
@@ -56722,7 +56717,7 @@
       <c r="Y752" s="5"/>
       <c r="Z752" s="5"/>
     </row>
-    <row r="753" spans="1:26" ht="17.399999999999999">
+    <row r="753" spans="1:26" ht="16.5">
       <c r="A753" s="7"/>
       <c r="B753" s="7"/>
       <c r="C753" s="7"/>
@@ -56750,7 +56745,7 @@
       <c r="Y753" s="5"/>
       <c r="Z753" s="5"/>
     </row>
-    <row r="754" spans="1:26" ht="17.399999999999999">
+    <row r="754" spans="1:26" ht="16.5">
       <c r="A754" s="7"/>
       <c r="B754" s="7"/>
       <c r="C754" s="7"/>
@@ -56778,7 +56773,7 @@
       <c r="Y754" s="5"/>
       <c r="Z754" s="5"/>
     </row>
-    <row r="755" spans="1:26" ht="17.399999999999999">
+    <row r="755" spans="1:26" ht="16.5">
       <c r="A755" s="7"/>
       <c r="B755" s="7"/>
       <c r="C755" s="7"/>
@@ -56806,7 +56801,7 @@
       <c r="Y755" s="5"/>
       <c r="Z755" s="5"/>
     </row>
-    <row r="756" spans="1:26" ht="17.399999999999999">
+    <row r="756" spans="1:26" ht="16.5">
       <c r="A756" s="7"/>
       <c r="B756" s="7"/>
       <c r="C756" s="7"/>
@@ -56834,7 +56829,7 @@
       <c r="Y756" s="5"/>
       <c r="Z756" s="5"/>
     </row>
-    <row r="757" spans="1:26" ht="17.399999999999999">
+    <row r="757" spans="1:26" ht="16.5">
       <c r="A757" s="7"/>
       <c r="B757" s="7"/>
       <c r="C757" s="7"/>
@@ -56862,7 +56857,7 @@
       <c r="Y757" s="5"/>
       <c r="Z757" s="5"/>
     </row>
-    <row r="758" spans="1:26" ht="17.399999999999999">
+    <row r="758" spans="1:26" ht="16.5">
       <c r="A758" s="7"/>
       <c r="B758" s="7"/>
       <c r="C758" s="7"/>
@@ -56890,7 +56885,7 @@
       <c r="Y758" s="5"/>
       <c r="Z758" s="5"/>
     </row>
-    <row r="759" spans="1:26" ht="17.399999999999999">
+    <row r="759" spans="1:26" ht="16.5">
       <c r="A759" s="7"/>
       <c r="B759" s="7"/>
       <c r="C759" s="7"/>
@@ -56918,7 +56913,7 @@
       <c r="Y759" s="5"/>
       <c r="Z759" s="5"/>
     </row>
-    <row r="760" spans="1:26" ht="17.399999999999999">
+    <row r="760" spans="1:26" ht="16.5">
       <c r="A760" s="7"/>
       <c r="B760" s="7"/>
       <c r="C760" s="7"/>
@@ -56946,7 +56941,7 @@
       <c r="Y760" s="5"/>
       <c r="Z760" s="5"/>
     </row>
-    <row r="761" spans="1:26" ht="17.399999999999999">
+    <row r="761" spans="1:26" ht="16.5">
       <c r="A761" s="7"/>
       <c r="B761" s="7"/>
       <c r="C761" s="7"/>
@@ -56974,7 +56969,7 @@
       <c r="Y761" s="5"/>
       <c r="Z761" s="5"/>
     </row>
-    <row r="762" spans="1:26" ht="17.399999999999999">
+    <row r="762" spans="1:26" ht="16.5">
       <c r="A762" s="7"/>
       <c r="B762" s="7"/>
       <c r="C762" s="7"/>
@@ -57002,7 +56997,7 @@
       <c r="Y762" s="5"/>
       <c r="Z762" s="5"/>
     </row>
-    <row r="763" spans="1:26" ht="17.399999999999999">
+    <row r="763" spans="1:26" ht="16.5">
       <c r="A763" s="7"/>
       <c r="B763" s="7"/>
       <c r="C763" s="7"/>
@@ -57030,7 +57025,7 @@
       <c r="Y763" s="5"/>
       <c r="Z763" s="5"/>
     </row>
-    <row r="764" spans="1:26" ht="17.399999999999999">
+    <row r="764" spans="1:26" ht="16.5">
       <c r="A764" s="7"/>
       <c r="B764" s="7"/>
       <c r="C764" s="7"/>
@@ -57058,7 +57053,7 @@
       <c r="Y764" s="5"/>
       <c r="Z764" s="5"/>
     </row>
-    <row r="765" spans="1:26" ht="17.399999999999999">
+    <row r="765" spans="1:26" ht="16.5">
       <c r="A765" s="7"/>
       <c r="B765" s="7"/>
       <c r="C765" s="7"/>
@@ -57086,7 +57081,7 @@
       <c r="Y765" s="5"/>
       <c r="Z765" s="5"/>
     </row>
-    <row r="766" spans="1:26" ht="17.399999999999999">
+    <row r="766" spans="1:26" ht="16.5">
       <c r="A766" s="7"/>
       <c r="B766" s="7"/>
       <c r="C766" s="7"/>
@@ -57114,7 +57109,7 @@
       <c r="Y766" s="5"/>
       <c r="Z766" s="5"/>
     </row>
-    <row r="767" spans="1:26" ht="17.399999999999999">
+    <row r="767" spans="1:26" ht="16.5">
       <c r="A767" s="7"/>
       <c r="B767" s="7"/>
       <c r="C767" s="7"/>
@@ -57142,7 +57137,7 @@
       <c r="Y767" s="5"/>
       <c r="Z767" s="5"/>
     </row>
-    <row r="768" spans="1:26" ht="17.399999999999999">
+    <row r="768" spans="1:26" ht="16.5">
       <c r="A768" s="7"/>
       <c r="B768" s="7"/>
       <c r="C768" s="7"/>
@@ -57170,7 +57165,7 @@
       <c r="Y768" s="5"/>
       <c r="Z768" s="5"/>
     </row>
-    <row r="769" spans="1:26" ht="17.399999999999999">
+    <row r="769" spans="1:26" ht="16.5">
       <c r="A769" s="7"/>
       <c r="B769" s="7"/>
       <c r="C769" s="7"/>
@@ -57198,7 +57193,7 @@
       <c r="Y769" s="5"/>
       <c r="Z769" s="5"/>
     </row>
-    <row r="770" spans="1:26" ht="17.399999999999999">
+    <row r="770" spans="1:26" ht="16.5">
       <c r="A770" s="7"/>
       <c r="B770" s="7"/>
       <c r="C770" s="7"/>
@@ -57226,7 +57221,7 @@
       <c r="Y770" s="5"/>
       <c r="Z770" s="5"/>
     </row>
-    <row r="771" spans="1:26" ht="17.399999999999999">
+    <row r="771" spans="1:26" ht="16.5">
       <c r="A771" s="7"/>
       <c r="B771" s="7"/>
       <c r="C771" s="7"/>
@@ -57254,7 +57249,7 @@
       <c r="Y771" s="5"/>
       <c r="Z771" s="5"/>
     </row>
-    <row r="772" spans="1:26" ht="17.399999999999999">
+    <row r="772" spans="1:26" ht="16.5">
       <c r="A772" s="7"/>
       <c r="B772" s="7"/>
       <c r="C772" s="7"/>
@@ -57282,7 +57277,7 @@
       <c r="Y772" s="5"/>
       <c r="Z772" s="5"/>
     </row>
-    <row r="773" spans="1:26" ht="17.399999999999999">
+    <row r="773" spans="1:26" ht="16.5">
       <c r="A773" s="7"/>
       <c r="B773" s="7"/>
       <c r="C773" s="7"/>
@@ -57310,7 +57305,7 @@
       <c r="Y773" s="5"/>
       <c r="Z773" s="5"/>
     </row>
-    <row r="774" spans="1:26" ht="17.399999999999999">
+    <row r="774" spans="1:26" ht="16.5">
       <c r="A774" s="7"/>
       <c r="B774" s="7"/>
       <c r="C774" s="7"/>
@@ -57338,7 +57333,7 @@
       <c r="Y774" s="5"/>
       <c r="Z774" s="5"/>
     </row>
-    <row r="775" spans="1:26" ht="17.399999999999999">
+    <row r="775" spans="1:26" ht="16.5">
       <c r="A775" s="7"/>
       <c r="B775" s="7"/>
       <c r="C775" s="7"/>
@@ -57366,7 +57361,7 @@
       <c r="Y775" s="5"/>
       <c r="Z775" s="5"/>
     </row>
-    <row r="776" spans="1:26" ht="17.399999999999999">
+    <row r="776" spans="1:26" ht="16.5">
       <c r="A776" s="7"/>
       <c r="B776" s="7"/>
       <c r="C776" s="7"/>
@@ -57394,7 +57389,7 @@
       <c r="Y776" s="5"/>
       <c r="Z776" s="5"/>
     </row>
-    <row r="777" spans="1:26" ht="17.399999999999999">
+    <row r="777" spans="1:26" ht="16.5">
       <c r="A777" s="7"/>
       <c r="B777" s="7"/>
       <c r="C777" s="7"/>
@@ -57422,7 +57417,7 @@
       <c r="Y777" s="5"/>
       <c r="Z777" s="5"/>
     </row>
-    <row r="778" spans="1:26" ht="17.399999999999999">
+    <row r="778" spans="1:26" ht="16.5">
       <c r="A778" s="7"/>
       <c r="B778" s="7"/>
       <c r="C778" s="7"/>
@@ -57450,7 +57445,7 @@
       <c r="Y778" s="5"/>
       <c r="Z778" s="5"/>
     </row>
-    <row r="779" spans="1:26" ht="17.399999999999999">
+    <row r="779" spans="1:26" ht="16.5">
       <c r="A779" s="7"/>
       <c r="B779" s="7"/>
       <c r="C779" s="7"/>
@@ -57478,7 +57473,7 @@
       <c r="Y779" s="5"/>
       <c r="Z779" s="5"/>
     </row>
-    <row r="780" spans="1:26" ht="17.399999999999999">
+    <row r="780" spans="1:26" ht="16.5">
       <c r="A780" s="7"/>
       <c r="B780" s="7"/>
       <c r="C780" s="7"/>
@@ -57506,7 +57501,7 @@
       <c r="Y780" s="5"/>
       <c r="Z780" s="5"/>
     </row>
-    <row r="781" spans="1:26" ht="17.399999999999999">
+    <row r="781" spans="1:26" ht="16.5">
       <c r="A781" s="7"/>
       <c r="B781" s="7"/>
       <c r="C781" s="7"/>
@@ -57534,7 +57529,7 @@
       <c r="Y781" s="5"/>
       <c r="Z781" s="5"/>
     </row>
-    <row r="782" spans="1:26" ht="17.399999999999999">
+    <row r="782" spans="1:26" ht="16.5">
       <c r="A782" s="7"/>
       <c r="B782" s="7"/>
       <c r="C782" s="7"/>
@@ -57562,7 +57557,7 @@
       <c r="Y782" s="5"/>
       <c r="Z782" s="5"/>
     </row>
-    <row r="783" spans="1:26" ht="17.399999999999999">
+    <row r="783" spans="1:26" ht="16.5">
       <c r="A783" s="7"/>
       <c r="B783" s="7"/>
       <c r="C783" s="7"/>
@@ -57590,7 +57585,7 @@
       <c r="Y783" s="5"/>
       <c r="Z783" s="5"/>
     </row>
-    <row r="784" spans="1:26" ht="17.399999999999999">
+    <row r="784" spans="1:26" ht="16.5">
       <c r="A784" s="7"/>
       <c r="B784" s="7"/>
       <c r="C784" s="7"/>
@@ -57618,7 +57613,7 @@
       <c r="Y784" s="5"/>
       <c r="Z784" s="5"/>
     </row>
-    <row r="785" spans="1:26" ht="17.399999999999999">
+    <row r="785" spans="1:26" ht="16.5">
       <c r="A785" s="7"/>
       <c r="B785" s="7"/>
       <c r="C785" s="7"/>
@@ -57646,7 +57641,7 @@
       <c r="Y785" s="5"/>
       <c r="Z785" s="5"/>
     </row>
-    <row r="786" spans="1:26" ht="17.399999999999999">
+    <row r="786" spans="1:26" ht="16.5">
       <c r="A786" s="7"/>
       <c r="B786" s="7"/>
       <c r="C786" s="7"/>
@@ -57674,7 +57669,7 @@
       <c r="Y786" s="5"/>
       <c r="Z786" s="5"/>
     </row>
-    <row r="787" spans="1:26" ht="17.399999999999999">
+    <row r="787" spans="1:26" ht="16.5">
       <c r="A787" s="7"/>
       <c r="B787" s="7"/>
       <c r="C787" s="7"/>
@@ -57702,7 +57697,7 @@
       <c r="Y787" s="5"/>
       <c r="Z787" s="5"/>
     </row>
-    <row r="788" spans="1:26" ht="17.399999999999999">
+    <row r="788" spans="1:26" ht="16.5">
       <c r="A788" s="7"/>
       <c r="B788" s="7"/>
       <c r="C788" s="7"/>
@@ -57730,7 +57725,7 @@
       <c r="Y788" s="5"/>
       <c r="Z788" s="5"/>
     </row>
-    <row r="789" spans="1:26" ht="17.399999999999999">
+    <row r="789" spans="1:26" ht="16.5">
       <c r="A789" s="7"/>
       <c r="B789" s="7"/>
       <c r="C789" s="7"/>
@@ -57758,7 +57753,7 @@
       <c r="Y789" s="5"/>
       <c r="Z789" s="5"/>
     </row>
-    <row r="790" spans="1:26" ht="17.399999999999999">
+    <row r="790" spans="1:26" ht="16.5">
       <c r="A790" s="7"/>
       <c r="B790" s="7"/>
       <c r="C790" s="7"/>
@@ -57786,7 +57781,7 @@
       <c r="Y790" s="5"/>
       <c r="Z790" s="5"/>
     </row>
-    <row r="791" spans="1:26" ht="17.399999999999999">
+    <row r="791" spans="1:26" ht="16.5">
       <c r="A791" s="7"/>
       <c r="B791" s="7"/>
       <c r="C791" s="7"/>
@@ -57814,7 +57809,7 @@
       <c r="Y791" s="5"/>
       <c r="Z791" s="5"/>
     </row>
-    <row r="792" spans="1:26" ht="17.399999999999999">
+    <row r="792" spans="1:26" ht="16.5">
       <c r="A792" s="7"/>
       <c r="B792" s="7"/>
       <c r="C792" s="7"/>
@@ -57842,7 +57837,7 @@
       <c r="Y792" s="5"/>
       <c r="Z792" s="5"/>
     </row>
-    <row r="793" spans="1:26" ht="17.399999999999999">
+    <row r="793" spans="1:26" ht="16.5">
       <c r="A793" s="7"/>
       <c r="B793" s="7"/>
       <c r="C793" s="7"/>
@@ -57870,7 +57865,7 @@
       <c r="Y793" s="5"/>
       <c r="Z793" s="5"/>
     </row>
-    <row r="794" spans="1:26" ht="17.399999999999999">
+    <row r="794" spans="1:26" ht="16.5">
       <c r="A794" s="7"/>
       <c r="B794" s="7"/>
       <c r="C794" s="7"/>
@@ -57898,7 +57893,7 @@
       <c r="Y794" s="5"/>
       <c r="Z794" s="5"/>
     </row>
-    <row r="795" spans="1:26" ht="17.399999999999999">
+    <row r="795" spans="1:26" ht="16.5">
       <c r="A795" s="7"/>
       <c r="B795" s="7"/>
       <c r="C795" s="7"/>
@@ -57926,7 +57921,7 @@
       <c r="Y795" s="5"/>
       <c r="Z795" s="5"/>
     </row>
-    <row r="796" spans="1:26" ht="17.399999999999999">
+    <row r="796" spans="1:26" ht="16.5">
       <c r="A796" s="7"/>
       <c r="B796" s="7"/>
       <c r="C796" s="7"/>
@@ -57954,7 +57949,7 @@
       <c r="Y796" s="5"/>
       <c r="Z796" s="5"/>
     </row>
-    <row r="797" spans="1:26" ht="17.399999999999999">
+    <row r="797" spans="1:26" ht="16.5">
       <c r="A797" s="7"/>
       <c r="B797" s="7"/>
       <c r="C797" s="7"/>
@@ -57982,7 +57977,7 @@
       <c r="Y797" s="5"/>
       <c r="Z797" s="5"/>
     </row>
-    <row r="798" spans="1:26" ht="17.399999999999999">
+    <row r="798" spans="1:26" ht="16.5">
       <c r="A798" s="7"/>
       <c r="B798" s="7"/>
       <c r="C798" s="7"/>
@@ -58010,7 +58005,7 @@
       <c r="Y798" s="5"/>
       <c r="Z798" s="5"/>
     </row>
-    <row r="799" spans="1:26" ht="17.399999999999999">
+    <row r="799" spans="1:26" ht="16.5">
       <c r="A799" s="7"/>
       <c r="B799" s="7"/>
       <c r="C799" s="7"/>
@@ -58038,7 +58033,7 @@
       <c r="Y799" s="5"/>
       <c r="Z799" s="5"/>
     </row>
-    <row r="800" spans="1:26" ht="17.399999999999999">
+    <row r="800" spans="1:26" ht="16.5">
       <c r="A800" s="7"/>
       <c r="B800" s="7"/>
       <c r="C800" s="7"/>
@@ -58066,7 +58061,7 @@
       <c r="Y800" s="5"/>
       <c r="Z800" s="5"/>
     </row>
-    <row r="801" spans="1:26" ht="17.399999999999999">
+    <row r="801" spans="1:26" ht="16.5">
       <c r="A801" s="7"/>
       <c r="B801" s="7"/>
       <c r="C801" s="7"/>
@@ -58094,7 +58089,7 @@
       <c r="Y801" s="5"/>
       <c r="Z801" s="5"/>
     </row>
-    <row r="802" spans="1:26" ht="17.399999999999999">
+    <row r="802" spans="1:26" ht="16.5">
       <c r="A802" s="7"/>
       <c r="B802" s="7"/>
       <c r="C802" s="7"/>
@@ -58122,7 +58117,7 @@
       <c r="Y802" s="5"/>
       <c r="Z802" s="5"/>
     </row>
-    <row r="803" spans="1:26" ht="17.399999999999999">
+    <row r="803" spans="1:26" ht="16.5">
       <c r="A803" s="7"/>
       <c r="B803" s="7"/>
       <c r="C803" s="7"/>
@@ -58150,7 +58145,7 @@
       <c r="Y803" s="5"/>
       <c r="Z803" s="5"/>
     </row>
-    <row r="804" spans="1:26" ht="17.399999999999999">
+    <row r="804" spans="1:26" ht="16.5">
       <c r="A804" s="7"/>
       <c r="B804" s="7"/>
       <c r="C804" s="7"/>
@@ -58178,7 +58173,7 @@
       <c r="Y804" s="5"/>
       <c r="Z804" s="5"/>
     </row>
-    <row r="805" spans="1:26" ht="17.399999999999999">
+    <row r="805" spans="1:26" ht="16.5">
       <c r="A805" s="7"/>
       <c r="B805" s="7"/>
       <c r="C805" s="7"/>
@@ -58206,7 +58201,7 @@
       <c r="Y805" s="5"/>
       <c r="Z805" s="5"/>
     </row>
-    <row r="806" spans="1:26" ht="17.399999999999999">
+    <row r="806" spans="1:26" ht="16.5">
       <c r="A806" s="7"/>
       <c r="B806" s="7"/>
       <c r="C806" s="7"/>
@@ -58234,7 +58229,7 @@
       <c r="Y806" s="5"/>
       <c r="Z806" s="5"/>
     </row>
-    <row r="807" spans="1:26" ht="17.399999999999999">
+    <row r="807" spans="1:26" ht="16.5">
       <c r="A807" s="7"/>
       <c r="B807" s="7"/>
       <c r="C807" s="7"/>
@@ -58262,7 +58257,7 @@
       <c r="Y807" s="5"/>
       <c r="Z807" s="5"/>
     </row>
-    <row r="808" spans="1:26" ht="17.399999999999999">
+    <row r="808" spans="1:26" ht="16.5">
       <c r="A808" s="7"/>
       <c r="B808" s="7"/>
       <c r="C808" s="7"/>
@@ -58290,7 +58285,7 @@
       <c r="Y808" s="5"/>
       <c r="Z808" s="5"/>
     </row>
-    <row r="809" spans="1:26" ht="17.399999999999999">
+    <row r="809" spans="1:26" ht="16.5">
       <c r="A809" s="7"/>
       <c r="B809" s="7"/>
       <c r="C809" s="7"/>
@@ -58318,7 +58313,7 @@
       <c r="Y809" s="5"/>
       <c r="Z809" s="5"/>
     </row>
-    <row r="810" spans="1:26" ht="17.399999999999999">
+    <row r="810" spans="1:26" ht="16.5">
       <c r="A810" s="7"/>
       <c r="B810" s="7"/>
       <c r="C810" s="7"/>
@@ -58346,7 +58341,7 @@
       <c r="Y810" s="5"/>
       <c r="Z810" s="5"/>
     </row>
-    <row r="811" spans="1:26" ht="17.399999999999999">
+    <row r="811" spans="1:26" ht="16.5">
       <c r="A811" s="7"/>
       <c r="B811" s="7"/>
       <c r="C811" s="7"/>
@@ -58374,7 +58369,7 @@
       <c r="Y811" s="5"/>
       <c r="Z811" s="5"/>
     </row>
-    <row r="812" spans="1:26" ht="17.399999999999999">
+    <row r="812" spans="1:26" ht="16.5">
       <c r="A812" s="7"/>
       <c r="B812" s="7"/>
       <c r="C812" s="7"/>
@@ -58402,7 +58397,7 @@
       <c r="Y812" s="5"/>
       <c r="Z812" s="5"/>
     </row>
-    <row r="813" spans="1:26" ht="17.399999999999999">
+    <row r="813" spans="1:26" ht="16.5">
       <c r="A813" s="7"/>
       <c r="B813" s="7"/>
       <c r="C813" s="7"/>
@@ -58430,7 +58425,7 @@
       <c r="Y813" s="5"/>
       <c r="Z813" s="5"/>
     </row>
-    <row r="814" spans="1:26" ht="17.399999999999999">
+    <row r="814" spans="1:26" ht="16.5">
       <c r="A814" s="7"/>
       <c r="B814" s="7"/>
       <c r="C814" s="7"/>
@@ -58458,7 +58453,7 @@
       <c r="Y814" s="5"/>
       <c r="Z814" s="5"/>
     </row>
-    <row r="815" spans="1:26" ht="17.399999999999999">
+    <row r="815" spans="1:26" ht="16.5">
       <c r="A815" s="7"/>
       <c r="B815" s="7"/>
       <c r="C815" s="7"/>
@@ -58486,7 +58481,7 @@
       <c r="Y815" s="5"/>
       <c r="Z815" s="5"/>
     </row>
-    <row r="816" spans="1:26" ht="17.399999999999999">
+    <row r="816" spans="1:26" ht="16.5">
       <c r="A816" s="7"/>
       <c r="B816" s="7"/>
       <c r="C816" s="7"/>
@@ -58514,7 +58509,7 @@
       <c r="Y816" s="5"/>
       <c r="Z816" s="5"/>
     </row>
-    <row r="817" spans="1:26" ht="17.399999999999999">
+    <row r="817" spans="1:26" ht="16.5">
       <c r="A817" s="7"/>
       <c r="B817" s="7"/>
       <c r="C817" s="7"/>
@@ -58542,7 +58537,7 @@
       <c r="Y817" s="5"/>
       <c r="Z817" s="5"/>
     </row>
-    <row r="818" spans="1:26" ht="17.399999999999999">
+    <row r="818" spans="1:26" ht="16.5">
       <c r="A818" s="7"/>
       <c r="B818" s="7"/>
       <c r="C818" s="7"/>
@@ -58570,7 +58565,7 @@
       <c r="Y818" s="5"/>
       <c r="Z818" s="5"/>
     </row>
-    <row r="819" spans="1:26" ht="17.399999999999999">
+    <row r="819" spans="1:26" ht="16.5">
       <c r="A819" s="7"/>
       <c r="B819" s="7"/>
       <c r="C819" s="7"/>
@@ -58598,7 +58593,7 @@
       <c r="Y819" s="5"/>
       <c r="Z819" s="5"/>
     </row>
-    <row r="820" spans="1:26" ht="17.399999999999999">
+    <row r="820" spans="1:26" ht="16.5">
       <c r="A820" s="7"/>
       <c r="B820" s="7"/>
       <c r="C820" s="7"/>
@@ -58626,7 +58621,7 @@
       <c r="Y820" s="5"/>
       <c r="Z820" s="5"/>
     </row>
-    <row r="821" spans="1:26" ht="17.399999999999999">
+    <row r="821" spans="1:26" ht="16.5">
       <c r="A821" s="7"/>
       <c r="B821" s="7"/>
       <c r="C821" s="7"/>
@@ -58654,7 +58649,7 @@
       <c r="Y821" s="5"/>
       <c r="Z821" s="5"/>
     </row>
-    <row r="822" spans="1:26" ht="17.399999999999999">
+    <row r="822" spans="1:26" ht="16.5">
       <c r="A822" s="7"/>
       <c r="B822" s="7"/>
       <c r="C822" s="7"/>
@@ -58682,7 +58677,7 @@
       <c r="Y822" s="5"/>
       <c r="Z822" s="5"/>
     </row>
-    <row r="823" spans="1:26" ht="17.399999999999999">
+    <row r="823" spans="1:26" ht="16.5">
       <c r="A823" s="7"/>
       <c r="B823" s="7"/>
       <c r="C823" s="7"/>
@@ -58710,7 +58705,7 @@
       <c r="Y823" s="5"/>
       <c r="Z823" s="5"/>
     </row>
-    <row r="824" spans="1:26" ht="17.399999999999999">
+    <row r="824" spans="1:26" ht="16.5">
       <c r="A824" s="7"/>
       <c r="B824" s="7"/>
       <c r="C824" s="7"/>
@@ -58738,7 +58733,7 @@
       <c r="Y824" s="5"/>
       <c r="Z824" s="5"/>
     </row>
-    <row r="825" spans="1:26" ht="17.399999999999999">
+    <row r="825" spans="1:26" ht="16.5">
       <c r="A825" s="7"/>
       <c r="B825" s="7"/>
       <c r="C825" s="7"/>
@@ -58766,7 +58761,7 @@
       <c r="Y825" s="5"/>
       <c r="Z825" s="5"/>
     </row>
-    <row r="826" spans="1:26" ht="17.399999999999999">
+    <row r="826" spans="1:26" ht="16.5">
       <c r="A826" s="7"/>
       <c r="B826" s="7"/>
       <c r="C826" s="7"/>
@@ -58794,7 +58789,7 @@
       <c r="Y826" s="5"/>
       <c r="Z826" s="5"/>
     </row>
-    <row r="827" spans="1:26" ht="17.399999999999999">
+    <row r="827" spans="1:26" ht="16.5">
       <c r="A827" s="7"/>
       <c r="B827" s="7"/>
       <c r="C827" s="7"/>
@@ -58822,7 +58817,7 @@
       <c r="Y827" s="5"/>
       <c r="Z827" s="5"/>
     </row>
-    <row r="828" spans="1:26" ht="17.399999999999999">
+    <row r="828" spans="1:26" ht="16.5">
       <c r="A828" s="7"/>
       <c r="B828" s="7"/>
       <c r="C828" s="7"/>
@@ -58850,7 +58845,7 @@
       <c r="Y828" s="5"/>
       <c r="Z828" s="5"/>
     </row>
-    <row r="829" spans="1:26" ht="17.399999999999999">
+    <row r="829" spans="1:26" ht="16.5">
       <c r="A829" s="7"/>
       <c r="B829" s="7"/>
       <c r="C829" s="7"/>
@@ -58878,7 +58873,7 @@
       <c r="Y829" s="5"/>
       <c r="Z829" s="5"/>
     </row>
-    <row r="830" spans="1:26" ht="17.399999999999999">
+    <row r="830" spans="1:26" ht="16.5">
       <c r="A830" s="7"/>
       <c r="B830" s="7"/>
       <c r="C830" s="7"/>
@@ -58906,7 +58901,7 @@
       <c r="Y830" s="5"/>
       <c r="Z830" s="5"/>
     </row>
-    <row r="831" spans="1:26" ht="17.399999999999999">
+    <row r="831" spans="1:26" ht="16.5">
       <c r="A831" s="7"/>
       <c r="B831" s="7"/>
       <c r="C831" s="7"/>
@@ -58934,7 +58929,7 @@
       <c r="Y831" s="5"/>
       <c r="Z831" s="5"/>
     </row>
-    <row r="832" spans="1:26" ht="17.399999999999999">
+    <row r="832" spans="1:26" ht="16.5">
       <c r="A832" s="7"/>
       <c r="B832" s="7"/>
       <c r="C832" s="7"/>
@@ -58962,7 +58957,7 @@
       <c r="Y832" s="5"/>
       <c r="Z832" s="5"/>
     </row>
-    <row r="833" spans="1:26" ht="17.399999999999999">
+    <row r="833" spans="1:26" ht="16.5">
       <c r="A833" s="7"/>
       <c r="B833" s="7"/>
       <c r="C833" s="7"/>
@@ -58990,7 +58985,7 @@
       <c r="Y833" s="5"/>
       <c r="Z833" s="5"/>
     </row>
-    <row r="834" spans="1:26" ht="17.399999999999999">
+    <row r="834" spans="1:26" ht="16.5">
       <c r="A834" s="7"/>
       <c r="B834" s="7"/>
       <c r="C834" s="7"/>
@@ -59018,7 +59013,7 @@
       <c r="Y834" s="5"/>
       <c r="Z834" s="5"/>
     </row>
-    <row r="835" spans="1:26" ht="17.399999999999999">
+    <row r="835" spans="1:26" ht="16.5">
       <c r="A835" s="7"/>
       <c r="B835" s="7"/>
       <c r="C835" s="7"/>
@@ -59046,7 +59041,7 @@
       <c r="Y835" s="5"/>
       <c r="Z835" s="5"/>
     </row>
-    <row r="836" spans="1:26" ht="17.399999999999999">
+    <row r="836" spans="1:26" ht="16.5">
       <c r="A836" s="7"/>
       <c r="B836" s="7"/>
       <c r="C836" s="7"/>
@@ -59074,7 +59069,7 @@
       <c r="Y836" s="5"/>
       <c r="Z836" s="5"/>
     </row>
-    <row r="837" spans="1:26" ht="17.399999999999999">
+    <row r="837" spans="1:26" ht="16.5">
       <c r="A837" s="7"/>
       <c r="B837" s="7"/>
       <c r="C837" s="7"/>
@@ -59102,7 +59097,7 @@
       <c r="Y837" s="5"/>
       <c r="Z837" s="5"/>
     </row>
-    <row r="838" spans="1:26" ht="17.399999999999999">
+    <row r="838" spans="1:26" ht="16.5">
       <c r="A838" s="7"/>
       <c r="B838" s="7"/>
       <c r="C838" s="7"/>
@@ -59130,7 +59125,7 @@
       <c r="Y838" s="5"/>
       <c r="Z838" s="5"/>
     </row>
-    <row r="839" spans="1:26" ht="17.399999999999999">
+    <row r="839" spans="1:26" ht="16.5">
       <c r="A839" s="7"/>
       <c r="B839" s="7"/>
       <c r="C839" s="7"/>
@@ -59158,7 +59153,7 @@
       <c r="Y839" s="5"/>
       <c r="Z839" s="5"/>
     </row>
-    <row r="840" spans="1:26" ht="17.399999999999999">
+    <row r="840" spans="1:26" ht="16.5">
       <c r="A840" s="7"/>
       <c r="B840" s="7"/>
       <c r="C840" s="7"/>
@@ -59186,7 +59181,7 @@
       <c r="Y840" s="5"/>
       <c r="Z840" s="5"/>
     </row>
-    <row r="841" spans="1:26" ht="17.399999999999999">
+    <row r="841" spans="1:26" ht="16.5">
       <c r="A841" s="7"/>
       <c r="B841" s="7"/>
       <c r="C841" s="7"/>
@@ -59214,7 +59209,7 @@
       <c r="Y841" s="5"/>
       <c r="Z841" s="5"/>
     </row>
-    <row r="842" spans="1:26" ht="17.399999999999999">
+    <row r="842" spans="1:26" ht="16.5">
       <c r="A842" s="7"/>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
@@ -59242,7 +59237,7 @@
       <c r="Y842" s="5"/>
       <c r="Z842" s="5"/>
     </row>
-    <row r="843" spans="1:26" ht="17.399999999999999">
+    <row r="843" spans="1:26" ht="16.5">
       <c r="A843" s="7"/>
       <c r="B843" s="7"/>
       <c r="C843" s="7"/>
@@ -59270,7 +59265,7 @@
       <c r="Y843" s="5"/>
       <c r="Z843" s="5"/>
     </row>
-    <row r="844" spans="1:26" ht="17.399999999999999">
+    <row r="844" spans="1:26" ht="16.5">
       <c r="A844" s="7"/>
       <c r="B844" s="7"/>
       <c r="C844" s="7"/>
@@ -59298,7 +59293,7 @@
       <c r="Y844" s="5"/>
       <c r="Z844" s="5"/>
     </row>
-    <row r="845" spans="1:26" ht="17.399999999999999">
+    <row r="845" spans="1:26" ht="16.5">
       <c r="A845" s="7"/>
       <c r="B845" s="7"/>
       <c r="C845" s="7"/>
@@ -59326,7 +59321,7 @@
       <c r="Y845" s="5"/>
       <c r="Z845" s="5"/>
     </row>
-    <row r="846" spans="1:26" ht="17.399999999999999">
+    <row r="846" spans="1:26" ht="16.5">
       <c r="A846" s="7"/>
       <c r="B846" s="7"/>
       <c r="C846" s="7"/>
@@ -59354,7 +59349,7 @@
       <c r="Y846" s="5"/>
       <c r="Z846" s="5"/>
     </row>
-    <row r="847" spans="1:26" ht="17.399999999999999">
+    <row r="847" spans="1:26" ht="16.5">
       <c r="A847" s="7"/>
       <c r="B847" s="7"/>
       <c r="C847" s="7"/>
@@ -59382,7 +59377,7 @@
       <c r="Y847" s="5"/>
       <c r="Z847" s="5"/>
     </row>
-    <row r="848" spans="1:26" ht="17.399999999999999">
+    <row r="848" spans="1:26" ht="16.5">
       <c r="A848" s="7"/>
       <c r="B848" s="7"/>
       <c r="C848" s="7"/>
@@ -59410,7 +59405,7 @@
       <c r="Y848" s="5"/>
       <c r="Z848" s="5"/>
     </row>
-    <row r="849" spans="1:26" ht="17.399999999999999">
+    <row r="849" spans="1:26" ht="16.5">
       <c r="A849" s="7"/>
       <c r="B849" s="7"/>
       <c r="C849" s="7"/>
@@ -59438,7 +59433,7 @@
       <c r="Y849" s="5"/>
       <c r="Z849" s="5"/>
     </row>
-    <row r="850" spans="1:26" ht="17.399999999999999">
+    <row r="850" spans="1:26" ht="16.5">
       <c r="A850" s="7"/>
       <c r="B850" s="7"/>
       <c r="C850" s="7"/>
@@ -59466,7 +59461,7 @@
       <c r="Y850" s="5"/>
       <c r="Z850" s="5"/>
     </row>
-    <row r="851" spans="1:26" ht="17.399999999999999">
+    <row r="851" spans="1:26" ht="16.5">
       <c r="A851" s="7"/>
       <c r="B851" s="7"/>
       <c r="C851" s="7"/>
@@ -59494,7 +59489,7 @@
       <c r="Y851" s="5"/>
       <c r="Z851" s="5"/>
     </row>
-    <row r="852" spans="1:26" ht="17.399999999999999">
+    <row r="852" spans="1:26" ht="16.5">
       <c r="A852" s="7"/>
       <c r="B852" s="7"/>
       <c r="C852" s="7"/>
@@ -59522,7 +59517,7 @@
       <c r="Y852" s="5"/>
       <c r="Z852" s="5"/>
     </row>
-    <row r="853" spans="1:26" ht="17.399999999999999">
+    <row r="853" spans="1:26" ht="16.5">
       <c r="A853" s="7"/>
       <c r="B853" s="7"/>
       <c r="C853" s="7"/>
@@ -59550,7 +59545,7 @@
       <c r="Y853" s="5"/>
       <c r="Z853" s="5"/>
     </row>
-    <row r="854" spans="1:26" ht="17.399999999999999">
+    <row r="854" spans="1:26" ht="16.5">
       <c r="A854" s="7"/>
       <c r="B854" s="7"/>
       <c r="C854" s="7"/>
@@ -59578,7 +59573,7 @@
       <c r="Y854" s="5"/>
       <c r="Z854" s="5"/>
     </row>
-    <row r="855" spans="1:26" ht="17.399999999999999">
+    <row r="855" spans="1:26" ht="16.5">
       <c r="A855" s="7"/>
       <c r="B855" s="7"/>
       <c r="C855" s="7"/>
@@ -59606,7 +59601,7 @@
       <c r="Y855" s="5"/>
       <c r="Z855" s="5"/>
     </row>
-    <row r="856" spans="1:26" ht="17.399999999999999">
+    <row r="856" spans="1:26" ht="16.5">
       <c r="A856" s="7"/>
       <c r="B856" s="7"/>
       <c r="C856" s="7"/>
@@ -59634,7 +59629,7 @@
       <c r="Y856" s="5"/>
       <c r="Z856" s="5"/>
     </row>
-    <row r="857" spans="1:26" ht="17.399999999999999">
+    <row r="857" spans="1:26" ht="16.5">
       <c r="A857" s="7"/>
       <c r="B857" s="7"/>
       <c r="C857" s="7"/>
@@ -59662,7 +59657,7 @@
       <c r="Y857" s="5"/>
       <c r="Z857" s="5"/>
     </row>
-    <row r="858" spans="1:26" ht="17.399999999999999">
+    <row r="858" spans="1:26" ht="16.5">
       <c r="A858" s="7"/>
       <c r="B858" s="7"/>
       <c r="C858" s="7"/>
@@ -59690,7 +59685,7 @@
       <c r="Y858" s="5"/>
       <c r="Z858" s="5"/>
     </row>
-    <row r="859" spans="1:26" ht="17.399999999999999">
+    <row r="859" spans="1:26" ht="16.5">
       <c r="A859" s="7"/>
       <c r="B859" s="7"/>
       <c r="C859" s="7"/>
@@ -59718,7 +59713,7 @@
       <c r="Y859" s="5"/>
       <c r="Z859" s="5"/>
     </row>
-    <row r="860" spans="1:26" ht="17.399999999999999">
+    <row r="860" spans="1:26" ht="16.5">
       <c r="A860" s="7"/>
       <c r="B860" s="7"/>
       <c r="C860" s="7"/>
@@ -59746,7 +59741,7 @@
       <c r="Y860" s="5"/>
       <c r="Z860" s="5"/>
     </row>
-    <row r="861" spans="1:26" ht="17.399999999999999">
+    <row r="861" spans="1:26" ht="16.5">
       <c r="A861" s="7"/>
       <c r="B861" s="7"/>
       <c r="C861" s="7"/>
@@ -59774,7 +59769,7 @@
       <c r="Y861" s="5"/>
       <c r="Z861" s="5"/>
     </row>
-    <row r="862" spans="1:26" ht="17.399999999999999">
+    <row r="862" spans="1:26" ht="16.5">
       <c r="A862" s="7"/>
       <c r="B862" s="7"/>
       <c r="C862" s="7"/>
@@ -59802,7 +59797,7 @@
       <c r="Y862" s="5"/>
       <c r="Z862" s="5"/>
     </row>
-    <row r="863" spans="1:26" ht="17.399999999999999">
+    <row r="863" spans="1:26" ht="16.5">
       <c r="A863" s="7"/>
       <c r="B863" s="7"/>
       <c r="C863" s="7"/>
@@ -59830,7 +59825,7 @@
       <c r="Y863" s="5"/>
       <c r="Z863" s="5"/>
     </row>
-    <row r="864" spans="1:26" ht="17.399999999999999">
+    <row r="864" spans="1:26" ht="16.5">
       <c r="A864" s="7"/>
       <c r="B864" s="7"/>
       <c r="C864" s="7"/>
@@ -59858,7 +59853,7 @@
       <c r="Y864" s="5"/>
       <c r="Z864" s="5"/>
     </row>
-    <row r="865" spans="1:26" ht="17.399999999999999">
+    <row r="865" spans="1:26" ht="16.5">
       <c r="A865" s="7"/>
       <c r="B865" s="7"/>
       <c r="C865" s="7"/>
@@ -59886,7 +59881,7 @@
       <c r="Y865" s="5"/>
       <c r="Z865" s="5"/>
     </row>
-    <row r="866" spans="1:26" ht="17.399999999999999">
+    <row r="866" spans="1:26" ht="16.5">
       <c r="A866" s="7"/>
       <c r="B866" s="7"/>
       <c r="C866" s="7"/>
@@ -59914,7 +59909,7 @@
       <c r="Y866" s="5"/>
       <c r="Z866" s="5"/>
     </row>
-    <row r="867" spans="1:26" ht="17.399999999999999">
+    <row r="867" spans="1:26" ht="16.5">
       <c r="A867" s="7"/>
       <c r="B867" s="7"/>
       <c r="C867" s="7"/>
@@ -59942,7 +59937,7 @@
       <c r="Y867" s="5"/>
       <c r="Z867" s="5"/>
     </row>
-    <row r="868" spans="1:26" ht="17.399999999999999">
+    <row r="868" spans="1:26" ht="16.5">
       <c r="A868" s="7"/>
       <c r="B868" s="7"/>
       <c r="C868" s="7"/>
@@ -59970,7 +59965,7 @@
       <c r="Y868" s="5"/>
       <c r="Z868" s="5"/>
     </row>
-    <row r="869" spans="1:26" ht="17.399999999999999">
+    <row r="869" spans="1:26" ht="16.5">
       <c r="A869" s="7"/>
       <c r="B869" s="7"/>
       <c r="C869" s="7"/>
@@ -59998,7 +59993,7 @@
       <c r="Y869" s="5"/>
       <c r="Z869" s="5"/>
     </row>
-    <row r="870" spans="1:26" ht="17.399999999999999">
+    <row r="870" spans="1:26" ht="16.5">
       <c r="A870" s="7"/>
       <c r="B870" s="7"/>
       <c r="C870" s="7"/>
@@ -60026,7 +60021,7 @@
       <c r="Y870" s="5"/>
       <c r="Z870" s="5"/>
     </row>
-    <row r="871" spans="1:26" ht="17.399999999999999">
+    <row r="871" spans="1:26" ht="16.5">
       <c r="A871" s="7"/>
       <c r="B871" s="7"/>
       <c r="C871" s="7"/>
@@ -60054,7 +60049,7 @@
       <c r="Y871" s="5"/>
       <c r="Z871" s="5"/>
     </row>
-    <row r="872" spans="1:26" ht="17.399999999999999">
+    <row r="872" spans="1:26" ht="16.5">
       <c r="A872" s="7"/>
       <c r="B872" s="7"/>
       <c r="C872" s="7"/>
@@ -60082,7 +60077,7 @@
       <c r="Y872" s="5"/>
       <c r="Z872" s="5"/>
     </row>
-    <row r="873" spans="1:26" ht="17.399999999999999">
+    <row r="873" spans="1:26" ht="16.5">
       <c r="A873" s="7"/>
       <c r="B873" s="7"/>
       <c r="C873" s="7"/>
@@ -60110,7 +60105,7 @@
       <c r="Y873" s="5"/>
       <c r="Z873" s="5"/>
     </row>
-    <row r="874" spans="1:26" ht="17.399999999999999">
+    <row r="874" spans="1:26" ht="16.5">
       <c r="A874" s="7"/>
       <c r="B874" s="7"/>
       <c r="C874" s="7"/>
@@ -60138,7 +60133,7 @@
       <c r="Y874" s="5"/>
       <c r="Z874" s="5"/>
     </row>
-    <row r="875" spans="1:26" ht="17.399999999999999">
+    <row r="875" spans="1:26" ht="16.5">
       <c r="A875" s="7"/>
       <c r="B875" s="7"/>
       <c r="C875" s="7"/>
@@ -60166,7 +60161,7 @@
       <c r="Y875" s="5"/>
       <c r="Z875" s="5"/>
     </row>
-    <row r="876" spans="1:26" ht="17.399999999999999">
+    <row r="876" spans="1:26" ht="16.5">
       <c r="A876" s="7"/>
       <c r="B876" s="7"/>
       <c r="C876" s="7"/>
@@ -60194,7 +60189,7 @@
       <c r="Y876" s="5"/>
       <c r="Z876" s="5"/>
     </row>
-    <row r="877" spans="1:26" ht="17.399999999999999">
+    <row r="877" spans="1:26" ht="16.5">
       <c r="A877" s="7"/>
       <c r="B877" s="7"/>
       <c r="C877" s="7"/>
@@ -60222,7 +60217,7 @@
       <c r="Y877" s="5"/>
       <c r="Z877" s="5"/>
     </row>
-    <row r="878" spans="1:26" ht="17.399999999999999">
+    <row r="878" spans="1:26" ht="16.5">
       <c r="A878" s="7"/>
       <c r="B878" s="7"/>
       <c r="C878" s="7"/>
@@ -60250,7 +60245,7 @@
       <c r="Y878" s="5"/>
       <c r="Z878" s="5"/>
     </row>
-    <row r="879" spans="1:26" ht="17.399999999999999">
+    <row r="879" spans="1:26" ht="16.5">
       <c r="A879" s="7"/>
       <c r="B879" s="7"/>
       <c r="C879" s="7"/>
@@ -60278,7 +60273,7 @@
       <c r="Y879" s="5"/>
       <c r="Z879" s="5"/>
     </row>
-    <row r="880" spans="1:26" ht="17.399999999999999">
+    <row r="880" spans="1:26" ht="16.5">
       <c r="A880" s="7"/>
       <c r="B880" s="7"/>
       <c r="C880" s="7"/>
@@ -60306,7 +60301,7 @@
       <c r="Y880" s="5"/>
       <c r="Z880" s="5"/>
     </row>
-    <row r="881" spans="1:26" ht="17.399999999999999">
+    <row r="881" spans="1:26" ht="16.5">
       <c r="A881" s="7"/>
       <c r="B881" s="7"/>
       <c r="C881" s="7"/>
@@ -60334,7 +60329,7 @@
       <c r="Y881" s="5"/>
       <c r="Z881" s="5"/>
     </row>
-    <row r="882" spans="1:26" ht="17.399999999999999">
+    <row r="882" spans="1:26" ht="16.5">
       <c r="A882" s="7"/>
       <c r="B882" s="7"/>
       <c r="C882" s="7"/>
@@ -60362,7 +60357,7 @@
       <c r="Y882" s="5"/>
       <c r="Z882" s="5"/>
     </row>
-    <row r="883" spans="1:26" ht="17.399999999999999">
+    <row r="883" spans="1:26" ht="16.5">
       <c r="A883" s="7"/>
       <c r="B883" s="7"/>
       <c r="C883" s="7"/>
@@ -60390,7 +60385,7 @@
       <c r="Y883" s="5"/>
       <c r="Z883" s="5"/>
     </row>
-    <row r="884" spans="1:26" ht="17.399999999999999">
+    <row r="884" spans="1:26" ht="16.5">
       <c r="A884" s="7"/>
       <c r="B884" s="7"/>
       <c r="C884" s="7"/>
@@ -60418,7 +60413,7 @@
       <c r="Y884" s="5"/>
       <c r="Z884" s="5"/>
     </row>
-    <row r="885" spans="1:26" ht="17.399999999999999">
+    <row r="885" spans="1:26" ht="16.5">
       <c r="A885" s="7"/>
       <c r="B885" s="7"/>
       <c r="C885" s="7"/>
@@ -60446,7 +60441,7 @@
       <c r="Y885" s="5"/>
       <c r="Z885" s="5"/>
     </row>
-    <row r="886" spans="1:26" ht="17.399999999999999">
+    <row r="886" spans="1:26" ht="16.5">
       <c r="A886" s="7"/>
       <c r="B886" s="7"/>
       <c r="C886" s="7"/>
@@ -60474,7 +60469,7 @@
       <c r="Y886" s="5"/>
       <c r="Z886" s="5"/>
     </row>
-    <row r="887" spans="1:26" ht="17.399999999999999">
+    <row r="887" spans="1:26" ht="16.5">
       <c r="A887" s="7"/>
       <c r="B887" s="7"/>
       <c r="C887" s="7"/>
@@ -60502,7 +60497,7 @@
       <c r="Y887" s="5"/>
       <c r="Z887" s="5"/>
     </row>
-    <row r="888" spans="1:26" ht="17.399999999999999">
+    <row r="888" spans="1:26" ht="16.5">
       <c r="A888" s="7"/>
       <c r="B888" s="7"/>
       <c r="C888" s="7"/>
@@ -60530,7 +60525,7 @@
       <c r="Y888" s="5"/>
       <c r="Z888" s="5"/>
     </row>
-    <row r="889" spans="1:26" ht="17.399999999999999">
+    <row r="889" spans="1:26" ht="16.5">
       <c r="A889" s="7"/>
       <c r="B889" s="7"/>
       <c r="C889" s="7"/>
@@ -60558,7 +60553,7 @@
       <c r="Y889" s="5"/>
       <c r="Z889" s="5"/>
     </row>
-    <row r="890" spans="1:26" ht="17.399999999999999">
+    <row r="890" spans="1:26" ht="16.5">
       <c r="A890" s="7"/>
       <c r="B890" s="7"/>
       <c r="C890" s="7"/>
@@ -60586,7 +60581,7 @@
       <c r="Y890" s="5"/>
       <c r="Z890" s="5"/>
     </row>
-    <row r="891" spans="1:26" ht="17.399999999999999">
+    <row r="891" spans="1:26" ht="16.5">
       <c r="A891" s="7"/>
       <c r="B891" s="7"/>
       <c r="C891" s="7"/>
@@ -60614,7 +60609,7 @@
       <c r="Y891" s="5"/>
       <c r="Z891" s="5"/>
     </row>
-    <row r="892" spans="1:26" ht="17.399999999999999">
+    <row r="892" spans="1:26" ht="16.5">
       <c r="A892" s="7"/>
       <c r="B892" s="7"/>
       <c r="C892" s="7"/>
@@ -60642,7 +60637,7 @@
       <c r="Y892" s="5"/>
       <c r="Z892" s="5"/>
     </row>
-    <row r="893" spans="1:26" ht="17.399999999999999">
+    <row r="893" spans="1:26" ht="16.5">
       <c r="A893" s="7"/>
       <c r="B893" s="7"/>
       <c r="C893" s="7"/>
@@ -60670,7 +60665,7 @@
       <c r="Y893" s="5"/>
       <c r="Z893" s="5"/>
     </row>
-    <row r="894" spans="1:26" ht="17.399999999999999">
+    <row r="894" spans="1:26" ht="16.5">
       <c r="A894" s="7"/>
       <c r="B894" s="7"/>
       <c r="C894" s="7"/>
@@ -60698,7 +60693,7 @@
       <c r="Y894" s="5"/>
       <c r="Z894" s="5"/>
     </row>
-    <row r="895" spans="1:26" ht="17.399999999999999">
+    <row r="895" spans="1:26" ht="16.5">
       <c r="A895" s="7"/>
       <c r="B895" s="7"/>
       <c r="C895" s="7"/>
@@ -60726,7 +60721,7 @@
       <c r="Y895" s="5"/>
       <c r="Z895" s="5"/>
     </row>
-    <row r="896" spans="1:26" ht="17.399999999999999">
+    <row r="896" spans="1:26" ht="16.5">
       <c r="A896" s="7"/>
       <c r="B896" s="7"/>
       <c r="C896" s="7"/>
@@ -60754,7 +60749,7 @@
       <c r="Y896" s="5"/>
       <c r="Z896" s="5"/>
     </row>
-    <row r="897" spans="1:26" ht="17.399999999999999">
+    <row r="897" spans="1:26" ht="16.5">
       <c r="A897" s="7"/>
       <c r="B897" s="7"/>
       <c r="C897" s="7"/>
@@ -60782,7 +60777,7 @@
       <c r="Y897" s="5"/>
       <c r="Z897" s="5"/>
     </row>
-    <row r="898" spans="1:26" ht="17.399999999999999">
+    <row r="898" spans="1:26" ht="16.5">
       <c r="A898" s="7"/>
       <c r="B898" s="7"/>
       <c r="C898" s="7"/>
@@ -60810,7 +60805,7 @@
       <c r="Y898" s="5"/>
       <c r="Z898" s="5"/>
     </row>
-    <row r="899" spans="1:26" ht="17.399999999999999">
+    <row r="899" spans="1:26" ht="16.5">
       <c r="A899" s="7"/>
       <c r="B899" s="7"/>
       <c r="C899" s="7"/>
@@ -60838,7 +60833,7 @@
       <c r="Y899" s="5"/>
       <c r="Z899" s="5"/>
     </row>
-    <row r="900" spans="1:26" ht="17.399999999999999">
+    <row r="900" spans="1:26" ht="16.5">
       <c r="A900" s="7"/>
       <c r="B900" s="7"/>
       <c r="C900" s="7"/>
@@ -60866,7 +60861,7 @@
       <c r="Y900" s="5"/>
       <c r="Z900" s="5"/>
     </row>
-    <row r="901" spans="1:26" ht="17.399999999999999">
+    <row r="901" spans="1:26" ht="16.5">
       <c r="A901" s="7"/>
       <c r="B901" s="7"/>
       <c r="C901" s="7"/>
@@ -60894,7 +60889,7 @@
       <c r="Y901" s="5"/>
       <c r="Z901" s="5"/>
     </row>
-    <row r="902" spans="1:26" ht="17.399999999999999">
+    <row r="902" spans="1:26" ht="16.5">
       <c r="A902" s="7"/>
       <c r="B902" s="7"/>
       <c r="C902" s="7"/>
@@ -60922,7 +60917,7 @@
       <c r="Y902" s="5"/>
       <c r="Z902" s="5"/>
     </row>
-    <row r="903" spans="1:26" ht="17.399999999999999">
+    <row r="903" spans="1:26" ht="16.5">
       <c r="A903" s="7"/>
       <c r="B903" s="7"/>
       <c r="C903" s="7"/>
@@ -60950,7 +60945,7 @@
       <c r="Y903" s="5"/>
       <c r="Z903" s="5"/>
     </row>
-    <row r="904" spans="1:26" ht="17.399999999999999">
+    <row r="904" spans="1:26" ht="16.5">
       <c r="A904" s="7"/>
       <c r="B904" s="7"/>
       <c r="C904" s="7"/>
@@ -60978,7 +60973,7 @@
       <c r="Y904" s="5"/>
       <c r="Z904" s="5"/>
     </row>
-    <row r="905" spans="1:26" ht="17.399999999999999">
+    <row r="905" spans="1:26" ht="16.5">
       <c r="A905" s="7"/>
       <c r="B905" s="7"/>
       <c r="C905" s="7"/>
@@ -61006,7 +61001,7 @@
       <c r="Y905" s="5"/>
       <c r="Z905" s="5"/>
     </row>
-    <row r="906" spans="1:26" ht="17.399999999999999">
+    <row r="906" spans="1:26" ht="16.5">
       <c r="A906" s="7"/>
       <c r="B906" s="7"/>
       <c r="C906" s="7"/>
@@ -61034,7 +61029,7 @@
       <c r="Y906" s="5"/>
       <c r="Z906" s="5"/>
     </row>
-    <row r="907" spans="1:26" ht="17.399999999999999">
+    <row r="907" spans="1:26" ht="16.5">
       <c r="A907" s="7"/>
       <c r="B907" s="7"/>
       <c r="C907" s="7"/>
@@ -61062,7 +61057,7 @@
       <c r="Y907" s="5"/>
       <c r="Z907" s="5"/>
     </row>
-    <row r="908" spans="1:26" ht="17.399999999999999">
+    <row r="908" spans="1:26" ht="16.5">
       <c r="A908" s="7"/>
       <c r="B908" s="7"/>
       <c r="C908" s="7"/>
@@ -61090,7 +61085,7 @@
       <c r="Y908" s="5"/>
       <c r="Z908" s="5"/>
     </row>
-    <row r="909" spans="1:26" ht="17.399999999999999">
+    <row r="909" spans="1:26" ht="16.5">
       <c r="A909" s="7"/>
       <c r="B909" s="7"/>
       <c r="C909" s="7"/>
@@ -61118,7 +61113,7 @@
       <c r="Y909" s="5"/>
       <c r="Z909" s="5"/>
     </row>
-    <row r="910" spans="1:26" ht="17.399999999999999">
+    <row r="910" spans="1:26" ht="16.5">
       <c r="A910" s="7"/>
       <c r="B910" s="7"/>
       <c r="C910" s="7"/>
@@ -61146,7 +61141,7 @@
       <c r="Y910" s="5"/>
       <c r="Z910" s="5"/>
     </row>
-    <row r="911" spans="1:26" ht="17.399999999999999">
+    <row r="911" spans="1:26" ht="16.5">
       <c r="A911" s="7"/>
       <c r="B911" s="7"/>
       <c r="C911" s="7"/>
@@ -61174,7 +61169,7 @@
       <c r="Y911" s="5"/>
       <c r="Z911" s="5"/>
     </row>
-    <row r="912" spans="1:26" ht="17.399999999999999">
+    <row r="912" spans="1:26" ht="16.5">
       <c r="A912" s="7"/>
       <c r="B912" s="7"/>
       <c r="C912" s="7"/>
@@ -61202,7 +61197,7 @@
       <c r="Y912" s="5"/>
       <c r="Z912" s="5"/>
     </row>
-    <row r="913" spans="1:26" ht="17.399999999999999">
+    <row r="913" spans="1:26" ht="16.5">
       <c r="A913" s="7"/>
       <c r="B913" s="7"/>
       <c r="C913" s="7"/>
@@ -61230,7 +61225,7 @@
       <c r="Y913" s="5"/>
       <c r="Z913" s="5"/>
     </row>
-    <row r="914" spans="1:26" ht="17.399999999999999">
+    <row r="914" spans="1:26" ht="16.5">
       <c r="A914" s="7"/>
       <c r="B914" s="7"/>
       <c r="C914" s="7"/>
@@ -61258,7 +61253,7 @@
       <c r="Y914" s="5"/>
       <c r="Z914" s="5"/>
     </row>
-    <row r="915" spans="1:26" ht="17.399999999999999">
+    <row r="915" spans="1:26" ht="16.5">
       <c r="A915" s="7"/>
       <c r="B915" s="7"/>
       <c r="C915" s="7"/>
@@ -61286,7 +61281,7 @@
       <c r="Y915" s="5"/>
       <c r="Z915" s="5"/>
     </row>
-    <row r="916" spans="1:26" ht="17.399999999999999">
+    <row r="916" spans="1:26" ht="16.5">
       <c r="A916" s="7"/>
       <c r="B916" s="7"/>
       <c r="C916" s="7"/>
@@ -61314,7 +61309,7 @@
       <c r="Y916" s="5"/>
       <c r="Z916" s="5"/>
     </row>
-    <row r="917" spans="1:26" ht="17.399999999999999">
+    <row r="917" spans="1:26" ht="16.5">
       <c r="A917" s="7"/>
       <c r="B917" s="7"/>
       <c r="C917" s="7"/>
@@ -61342,7 +61337,7 @@
       <c r="Y917" s="5"/>
       <c r="Z917" s="5"/>
     </row>
-    <row r="918" spans="1:26" ht="17.399999999999999">
+    <row r="918" spans="1:26" ht="16.5">
       <c r="A918" s="7"/>
       <c r="B918" s="7"/>
       <c r="C918" s="7"/>
@@ -61370,7 +61365,7 @@
       <c r="Y918" s="5"/>
       <c r="Z918" s="5"/>
     </row>
-    <row r="919" spans="1:26" ht="17.399999999999999">
+    <row r="919" spans="1:26" ht="16.5">
       <c r="A919" s="7"/>
       <c r="B919" s="7"/>
       <c r="C919" s="7"/>
@@ -61398,7 +61393,7 @@
       <c r="Y919" s="5"/>
       <c r="Z919" s="5"/>
     </row>
-    <row r="920" spans="1:26" ht="17.399999999999999">
+    <row r="920" spans="1:26" ht="16.5">
       <c r="A920" s="7"/>
       <c r="B920" s="7"/>
       <c r="C920" s="7"/>
@@ -61426,7 +61421,7 @@
       <c r="Y920" s="5"/>
       <c r="Z920" s="5"/>
     </row>
-    <row r="921" spans="1:26" ht="17.399999999999999">
+    <row r="921" spans="1:26" ht="16.5">
       <c r="A921" s="7"/>
       <c r="B921" s="7"/>
       <c r="C921" s="7"/>
@@ -61454,7 +61449,7 @@
       <c r="Y921" s="5"/>
       <c r="Z921" s="5"/>
     </row>
-    <row r="922" spans="1:26" ht="17.399999999999999">
+    <row r="922" spans="1:26" ht="16.5">
       <c r="A922" s="7"/>
       <c r="B922" s="7"/>
       <c r="C922" s="7"/>
@@ -61482,7 +61477,7 @@
       <c r="Y922" s="5"/>
       <c r="Z922" s="5"/>
     </row>
-    <row r="923" spans="1:26" ht="17.399999999999999">
+    <row r="923" spans="1:26" ht="16.5">
       <c r="A923" s="7"/>
       <c r="B923" s="7"/>
       <c r="C923" s="7"/>
@@ -61510,7 +61505,7 @@
       <c r="Y923" s="5"/>
       <c r="Z923" s="5"/>
     </row>
-    <row r="924" spans="1:26" ht="17.399999999999999">
+    <row r="924" spans="1:26" ht="16.5">
       <c r="A924" s="7"/>
       <c r="B924" s="7"/>
       <c r="C924" s="7"/>
@@ -61538,7 +61533,7 @@
       <c r="Y924" s="5"/>
       <c r="Z924" s="5"/>
     </row>
-    <row r="925" spans="1:26" ht="17.399999999999999">
+    <row r="925" spans="1:26" ht="16.5">
       <c r="A925" s="7"/>
       <c r="B925" s="7"/>
       <c r="C925" s="7"/>
@@ -61566,7 +61561,7 @@
       <c r="Y925" s="5"/>
       <c r="Z925" s="5"/>
     </row>
-    <row r="926" spans="1:26" ht="17.399999999999999">
+    <row r="926" spans="1:26" ht="16.5">
       <c r="A926" s="7"/>
       <c r="B926" s="7"/>
       <c r="C926" s="7"/>
@@ -61594,7 +61589,7 @@
       <c r="Y926" s="5"/>
       <c r="Z926" s="5"/>
     </row>
-    <row r="927" spans="1:26" ht="17.399999999999999">
+    <row r="927" spans="1:26" ht="16.5">
       <c r="A927" s="7"/>
       <c r="B927" s="7"/>
       <c r="C927" s="7"/>
@@ -61622,7 +61617,7 @@
       <c r="Y927" s="5"/>
       <c r="Z927" s="5"/>
     </row>
-    <row r="928" spans="1:26" ht="17.399999999999999">
+    <row r="928" spans="1:26" ht="16.5">
       <c r="A928" s="7"/>
       <c r="B928" s="7"/>
       <c r="C928" s="7"/>
@@ -61650,7 +61645,7 @@
       <c r="Y928" s="5"/>
       <c r="Z928" s="5"/>
     </row>
-    <row r="929" spans="1:26" ht="17.399999999999999">
+    <row r="929" spans="1:26" ht="16.5">
       <c r="A929" s="7"/>
       <c r="B929" s="7"/>
       <c r="C929" s="7"/>
@@ -61678,7 +61673,7 @@
       <c r="Y929" s="5"/>
       <c r="Z929" s="5"/>
     </row>
-    <row r="930" spans="1:26" ht="17.399999999999999">
+    <row r="930" spans="1:26" ht="16.5">
       <c r="A930" s="7"/>
       <c r="B930" s="7"/>
       <c r="C930" s="7"/>
@@ -61706,7 +61701,7 @@
       <c r="Y930" s="5"/>
       <c r="Z930" s="5"/>
     </row>
-    <row r="931" spans="1:26" ht="17.399999999999999">
+    <row r="931" spans="1:26" ht="16.5">
       <c r="A931" s="7"/>
       <c r="B931" s="7"/>
       <c r="C931" s="7"/>
@@ -61734,7 +61729,7 @@
       <c r="Y931" s="5"/>
       <c r="Z931" s="5"/>
     </row>
-    <row r="932" spans="1:26" ht="17.399999999999999">
+    <row r="932" spans="1:26" ht="16.5">
       <c r="A932" s="7"/>
       <c r="B932" s="7"/>
       <c r="C932" s="7"/>
@@ -61762,7 +61757,7 @@
       <c r="Y932" s="5"/>
       <c r="Z932" s="5"/>
     </row>
-    <row r="933" spans="1:26" ht="17.399999999999999">
+    <row r="933" spans="1:26" ht="16.5">
       <c r="A933" s="7"/>
       <c r="B933" s="7"/>
       <c r="C933" s="7"/>
@@ -61790,7 +61785,7 @@
       <c r="Y933" s="5"/>
       <c r="Z933" s="5"/>
     </row>
-    <row r="934" spans="1:26" ht="17.399999999999999">
+    <row r="934" spans="1:26" ht="16.5">
       <c r="A934" s="7"/>
       <c r="B934" s="7"/>
       <c r="C934" s="7"/>
@@ -61818,7 +61813,7 @@
       <c r="Y934" s="5"/>
       <c r="Z934" s="5"/>
     </row>
-    <row r="935" spans="1:26" ht="17.399999999999999">
+    <row r="935" spans="1:26" ht="16.5">
       <c r="A935" s="7"/>
       <c r="B935" s="7"/>
       <c r="C935" s="7"/>
@@ -61846,7 +61841,7 @@
       <c r="Y935" s="5"/>
       <c r="Z935" s="5"/>
     </row>
-    <row r="936" spans="1:26" ht="17.399999999999999">
+    <row r="936" spans="1:26" ht="16.5">
       <c r="A936" s="7"/>
       <c r="B936" s="7"/>
       <c r="C936" s="7"/>
@@ -61874,7 +61869,7 @@
       <c r="Y936" s="5"/>
       <c r="Z936" s="5"/>
     </row>
-    <row r="937" spans="1:26" ht="17.399999999999999">
+    <row r="937" spans="1:26" ht="16.5">
       <c r="A937" s="7"/>
       <c r="B937" s="7"/>
       <c r="C937" s="7"/>
@@ -61902,7 +61897,7 @@
       <c r="Y937" s="5"/>
       <c r="Z937" s="5"/>
     </row>
-    <row r="938" spans="1:26" ht="17.399999999999999">
+    <row r="938" spans="1:26" ht="16.5">
       <c r="A938" s="7"/>
       <c r="B938" s="7"/>
       <c r="C938" s="7"/>
@@ -61930,7 +61925,7 @@
       <c r="Y938" s="5"/>
       <c r="Z938" s="5"/>
     </row>
-    <row r="939" spans="1:26" ht="17.399999999999999">
+    <row r="939" spans="1:26" ht="16.5">
       <c r="A939" s="7"/>
       <c r="B939" s="7"/>
       <c r="C939" s="7"/>
@@ -61958,7 +61953,7 @@
       <c r="Y939" s="5"/>
       <c r="Z939" s="5"/>
     </row>
-    <row r="940" spans="1:26" ht="17.399999999999999">
+    <row r="940" spans="1:26" ht="16.5">
       <c r="A940" s="7"/>
       <c r="B940" s="7"/>
       <c r="C940" s="7"/>
@@ -61986,7 +61981,7 @@
       <c r="Y940" s="5"/>
       <c r="Z940" s="5"/>
     </row>
-    <row r="941" spans="1:26" ht="17.399999999999999">
+    <row r="941" spans="1:26" ht="16.5">
       <c r="A941" s="7"/>
       <c r="B941" s="7"/>
       <c r="C941" s="7"/>
@@ -62014,7 +62009,7 @@
       <c r="Y941" s="5"/>
       <c r="Z941" s="5"/>
     </row>
-    <row r="942" spans="1:26" ht="17.399999999999999">
+    <row r="942" spans="1:26" ht="16.5">
       <c r="A942" s="7"/>
       <c r="B942" s="7"/>
       <c r="C942" s="7"/>
@@ -62042,7 +62037,7 @@
       <c r="Y942" s="5"/>
       <c r="Z942" s="5"/>
     </row>
-    <row r="943" spans="1:26" ht="17.399999999999999">
+    <row r="943" spans="1:26" ht="16.5">
       <c r="A943" s="7"/>
       <c r="B943" s="7"/>
       <c r="C943" s="7"/>
@@ -62070,7 +62065,7 @@
       <c r="Y943" s="5"/>
       <c r="Z943" s="5"/>
     </row>
-    <row r="944" spans="1:26" ht="17.399999999999999">
+    <row r="944" spans="1:26" ht="16.5">
       <c r="A944" s="7"/>
       <c r="B944" s="7"/>
       <c r="C944" s="7"/>
@@ -62098,7 +62093,7 @@
       <c r="Y944" s="5"/>
       <c r="Z944" s="5"/>
     </row>
-    <row r="945" spans="1:26" ht="17.399999999999999">
+    <row r="945" spans="1:26" ht="16.5">
       <c r="A945" s="7"/>
       <c r="B945" s="7"/>
       <c r="C945" s="7"/>
@@ -62126,7 +62121,7 @@
       <c r="Y945" s="5"/>
       <c r="Z945" s="5"/>
     </row>
-    <row r="946" spans="1:26" ht="17.399999999999999">
+    <row r="946" spans="1:26" ht="16.5">
       <c r="A946" s="7"/>
       <c r="B946" s="7"/>
       <c r="C946" s="7"/>
@@ -62154,7 +62149,7 @@
       <c r="Y946" s="5"/>
       <c r="Z946" s="5"/>
     </row>
-    <row r="947" spans="1:26" ht="17.399999999999999">
+    <row r="947" spans="1:26" ht="16.5">
       <c r="A947" s="7"/>
       <c r="B947" s="7"/>
       <c r="C947" s="7"/>
@@ -62182,7 +62177,7 @@
       <c r="Y947" s="5"/>
       <c r="Z947" s="5"/>
     </row>
-    <row r="948" spans="1:26" ht="17.399999999999999">
+    <row r="948" spans="1:26" ht="16.5">
       <c r="A948" s="7"/>
       <c r="B948" s="7"/>
       <c r="C948" s="7"/>
@@ -62210,7 +62205,7 @@
       <c r="Y948" s="5"/>
       <c r="Z948" s="5"/>
     </row>
-    <row r="949" spans="1:26" ht="17.399999999999999">
+    <row r="949" spans="1:26" ht="16.5">
       <c r="A949" s="7"/>
       <c r="B949" s="7"/>
       <c r="C949" s="7"/>
@@ -62238,7 +62233,7 @@
       <c r="Y949" s="5"/>
       <c r="Z949" s="5"/>
     </row>
-    <row r="950" spans="1:26" ht="17.399999999999999">
+    <row r="950" spans="1:26" ht="16.5">
       <c r="A950" s="7"/>
       <c r="B950" s="7"/>
       <c r="C950" s="7"/>
@@ -62266,7 +62261,7 @@
       <c r="Y950" s="5"/>
       <c r="Z950" s="5"/>
     </row>
-    <row r="951" spans="1:26" ht="17.399999999999999">
+    <row r="951" spans="1:26" ht="16.5">
       <c r="A951" s="7"/>
       <c r="B951" s="7"/>
       <c r="C951" s="7"/>
@@ -62294,7 +62289,7 @@
       <c r="Y951" s="5"/>
       <c r="Z951" s="5"/>
     </row>
-    <row r="952" spans="1:26" ht="17.399999999999999">
+    <row r="952" spans="1:26" ht="16.5">
       <c r="A952" s="7"/>
       <c r="B952" s="7"/>
       <c r="C952" s="7"/>
@@ -62322,7 +62317,7 @@
       <c r="Y952" s="5"/>
       <c r="Z952" s="5"/>
     </row>
-    <row r="953" spans="1:26" ht="17.399999999999999">
+    <row r="953" spans="1:26" ht="16.5">
       <c r="A953" s="7"/>
       <c r="B953" s="7"/>
       <c r="C953" s="7"/>
@@ -62350,7 +62345,7 @@
       <c r="Y953" s="5"/>
       <c r="Z953" s="5"/>
     </row>
-    <row r="954" spans="1:26" ht="17.399999999999999">
+    <row r="954" spans="1:26" ht="16.5">
       <c r="A954" s="7"/>
       <c r="B954" s="7"/>
       <c r="C954" s="7"/>
@@ -62378,7 +62373,7 @@
       <c r="Y954" s="5"/>
       <c r="Z954" s="5"/>
     </row>
-    <row r="955" spans="1:26" ht="17.399999999999999">
+    <row r="955" spans="1:26" ht="16.5">
       <c r="A955" s="7"/>
       <c r="B955" s="7"/>
       <c r="C955" s="7"/>
@@ -62406,7 +62401,7 @@
       <c r="Y955" s="5"/>
       <c r="Z955" s="5"/>
     </row>
-    <row r="956" spans="1:26" ht="17.399999999999999">
+    <row r="956" spans="1:26" ht="16.5">
       <c r="A956" s="7"/>
       <c r="B956" s="7"/>
       <c r="C956" s="7"/>
@@ -62434,7 +62429,7 @@
       <c r="Y956" s="5"/>
       <c r="Z956" s="5"/>
     </row>
-    <row r="957" spans="1:26" ht="17.399999999999999">
+    <row r="957" spans="1:26" ht="16.5">
       <c r="A957" s="7"/>
       <c r="B957" s="7"/>
       <c r="C957" s="7"/>
@@ -62462,7 +62457,7 @@
       <c r="Y957" s="5"/>
       <c r="Z957" s="5"/>
     </row>
-    <row r="958" spans="1:26" ht="17.399999999999999">
+    <row r="958" spans="1:26" ht="16.5">
       <c r="A958" s="7"/>
       <c r="B958" s="7"/>
       <c r="C958" s="7"/>
@@ -62490,7 +62485,7 @@
       <c r="Y958" s="5"/>
       <c r="Z958" s="5"/>
     </row>
-    <row r="959" spans="1:26" ht="17.399999999999999">
+    <row r="959" spans="1:26" ht="16.5">
       <c r="A959" s="7"/>
       <c r="B959" s="7"/>
       <c r="C959" s="7"/>
@@ -62518,7 +62513,7 @@
       <c r="Y959" s="5"/>
       <c r="Z959" s="5"/>
     </row>
-    <row r="960" spans="1:26" ht="17.399999999999999">
+    <row r="960" spans="1:26" ht="16.5">
       <c r="A960" s="7"/>
       <c r="B960" s="7"/>
       <c r="C960" s="7"/>
@@ -62546,7 +62541,7 @@
       <c r="Y960" s="5"/>
       <c r="Z960" s="5"/>
     </row>
-    <row r="961" spans="1:26" ht="17.399999999999999">
+    <row r="961" spans="1:26" ht="16.5">
       <c r="A961" s="7"/>
       <c r="B961" s="7"/>
       <c r="C961" s="7"/>
@@ -62574,7 +62569,7 @@
       <c r="Y961" s="5"/>
       <c r="Z961" s="5"/>
     </row>
-    <row r="962" spans="1:26" ht="17.399999999999999">
+    <row r="962" spans="1:26" ht="16.5">
       <c r="A962" s="7"/>
       <c r="B962" s="7"/>
       <c r="C962" s="7"/>
@@ -62602,7 +62597,7 @@
       <c r="Y962" s="5"/>
       <c r="Z962" s="5"/>
     </row>
-    <row r="963" spans="1:26" ht="17.399999999999999">
+    <row r="963" spans="1:26" ht="16.5">
       <c r="A963" s="7"/>
       <c r="B963" s="7"/>
       <c r="C963" s="7"/>
@@ -62630,7 +62625,7 @@
       <c r="Y963" s="5"/>
       <c r="Z963" s="5"/>
     </row>
-    <row r="964" spans="1:26" ht="17.399999999999999">
+    <row r="964" spans="1:26" ht="16.5">
       <c r="A964" s="7"/>
       <c r="B964" s="7"/>
       <c r="C964" s="7"/>
@@ -62658,7 +62653,7 @@
       <c r="Y964" s="5"/>
       <c r="Z964" s="5"/>
     </row>
-    <row r="965" spans="1:26" ht="17.399999999999999">
+    <row r="965" spans="1:26" ht="16.5">
       <c r="A965" s="7"/>
       <c r="B965" s="7"/>
       <c r="C965" s="7"/>
@@ -62686,7 +62681,7 @@
       <c r="Y965" s="5"/>
       <c r="Z965" s="5"/>
     </row>
-    <row r="966" spans="1:26" ht="17.399999999999999">
+    <row r="966" spans="1:26" ht="16.5">
       <c r="A966" s="7"/>
       <c r="B966" s="7"/>
       <c r="C966" s="7"/>
@@ -62714,7 +62709,7 @@
       <c r="Y966" s="5"/>
       <c r="Z966" s="5"/>
     </row>
-    <row r="967" spans="1:26" ht="17.399999999999999">
+    <row r="967" spans="1:26" ht="16.5">
       <c r="A967" s="7"/>
       <c r="B967" s="7"/>
       <c r="C967" s="7"/>
@@ -62742,7 +62737,7 @@
       <c r="Y967" s="5"/>
       <c r="Z967" s="5"/>
     </row>
-    <row r="968" spans="1:26" ht="17.399999999999999">
+    <row r="968" spans="1:26" ht="16.5">
       <c r="A968" s="7"/>
       <c r="B968" s="7"/>
       <c r="C968" s="7"/>
@@ -62770,7 +62765,7 @@
       <c r="Y968" s="5"/>
       <c r="Z968" s="5"/>
     </row>
-    <row r="969" spans="1:26" ht="17.399999999999999">
+    <row r="969" spans="1:26" ht="16.5">
       <c r="A969" s="7"/>
       <c r="B969" s="7"/>
       <c r="C969" s="7"/>
@@ -62798,7 +62793,7 @@
       <c r="Y969" s="5"/>
       <c r="Z969" s="5"/>
     </row>
-    <row r="970" spans="1:26" ht="17.399999999999999">
+    <row r="970" spans="1:26" ht="16.5">
       <c r="A970" s="7"/>
       <c r="B970" s="7"/>
       <c r="C970" s="7"/>
@@ -62826,7 +62821,7 @@
       <c r="Y970" s="5"/>
       <c r="Z970" s="5"/>
     </row>
-    <row r="971" spans="1:26" ht="17.399999999999999">
+    <row r="971" spans="1:26" ht="16.5">
       <c r="A971" s="7"/>
       <c r="B971" s="7"/>
       <c r="C971" s="7"/>
@@ -62854,7 +62849,7 @@
       <c r="Y971" s="5"/>
       <c r="Z971" s="5"/>
     </row>
-    <row r="972" spans="1:26" ht="17.399999999999999">
+    <row r="972" spans="1:26" ht="16.5">
       <c r="A972" s="7"/>
       <c r="B972" s="7"/>
       <c r="C972" s="7"/>
@@ -62882,7 +62877,7 @@
       <c r="Y972" s="5"/>
       <c r="Z972" s="5"/>
     </row>
-    <row r="973" spans="1:26" ht="17.399999999999999">
+    <row r="973" spans="1:26" ht="16.5">
       <c r="A973" s="7"/>
       <c r="B973" s="7"/>
       <c r="C973" s="7"/>
@@ -62910,7 +62905,7 @@
       <c r="Y973" s="5"/>
       <c r="Z973" s="5"/>
     </row>
-    <row r="974" spans="1:26" ht="17.399999999999999">
+    <row r="974" spans="1:26" ht="16.5">
       <c r="A974" s="7"/>
       <c r="B974" s="7"/>
       <c r="C974" s="7"/>
@@ -62938,7 +62933,7 @@
       <c r="Y974" s="5"/>
       <c r="Z974" s="5"/>
     </row>
-    <row r="975" spans="1:26" ht="17.399999999999999">
+    <row r="975" spans="1:26" ht="16.5">
       <c r="A975" s="7"/>
       <c r="B975" s="7"/>
       <c r="C975" s="7"/>
@@ -62966,7 +62961,7 @@
       <c r="Y975" s="5"/>
       <c r="Z975" s="5"/>
     </row>
-    <row r="976" spans="1:26" ht="17.399999999999999">
+    <row r="976" spans="1:26" ht="16.5">
       <c r="A976" s="7"/>
       <c r="B976" s="7"/>
       <c r="C976" s="7"/>
@@ -62994,7 +62989,7 @@
       <c r="Y976" s="5"/>
       <c r="Z976" s="5"/>
     </row>
-    <row r="977" spans="1:26" ht="17.399999999999999">
+    <row r="977" spans="1:26" ht="16.5">
       <c r="A977" s="7"/>
       <c r="B977" s="7"/>
       <c r="C977" s="7"/>
@@ -63022,7 +63017,7 @@
       <c r="Y977" s="5"/>
       <c r="Z977" s="5"/>
     </row>
-    <row r="978" spans="1:26" ht="17.399999999999999">
+    <row r="978" spans="1:26" ht="16.5">
       <c r="A978" s="7"/>
       <c r="B978" s="7"/>
       <c r="C978" s="7"/>
@@ -63050,7 +63045,7 @@
       <c r="Y978" s="5"/>
       <c r="Z978" s="5"/>
     </row>
-    <row r="979" spans="1:26" ht="17.399999999999999">
+    <row r="979" spans="1:26" ht="16.5">
       <c r="A979" s="7"/>
       <c r="B979" s="7"/>
       <c r="C979" s="7"/>
@@ -63078,7 +63073,7 @@
       <c r="Y979" s="5"/>
       <c r="Z979" s="5"/>
     </row>
-    <row r="980" spans="1:26" ht="17.399999999999999">
+    <row r="980" spans="1:26" ht="16.5">
       <c r="A980" s="7"/>
       <c r="B980" s="7"/>
       <c r="C980" s="7"/>
@@ -63106,7 +63101,7 @@
       <c r="Y980" s="5"/>
       <c r="Z980" s="5"/>
     </row>
-    <row r="981" spans="1:26" ht="17.399999999999999">
+    <row r="981" spans="1:26" ht="16.5">
       <c r="A981" s="7"/>
       <c r="B981" s="7"/>
       <c r="C981" s="7"/>
@@ -63134,7 +63129,7 @@
       <c r="Y981" s="5"/>
       <c r="Z981" s="5"/>
     </row>
-    <row r="982" spans="1:26" ht="17.399999999999999">
+    <row r="982" spans="1:26" ht="16.5">
       <c r="A982" s="7"/>
       <c r="B982" s="7"/>
       <c r="C982" s="7"/>
@@ -63162,7 +63157,7 @@
       <c r="Y982" s="5"/>
       <c r="Z982" s="5"/>
     </row>
-    <row r="983" spans="1:26" ht="17.399999999999999">
+    <row r="983" spans="1:26" ht="16.5">
       <c r="A983" s="7"/>
       <c r="B983" s="7"/>
       <c r="C983" s="7"/>
@@ -63190,7 +63185,7 @@
       <c r="Y983" s="5"/>
       <c r="Z983" s="5"/>
     </row>
-    <row r="984" spans="1:26" ht="17.399999999999999">
+    <row r="984" spans="1:26" ht="16.5">
       <c r="A984" s="7"/>
       <c r="B984" s="7"/>
       <c r="C984" s="7"/>
@@ -63218,7 +63213,7 @@
       <c r="Y984" s="5"/>
       <c r="Z984" s="5"/>
     </row>
-    <row r="985" spans="1:26" ht="17.399999999999999">
+    <row r="985" spans="1:26" ht="16.5">
       <c r="A985" s="7"/>
       <c r="B985" s="7"/>
       <c r="C985" s="7"/>
@@ -63246,7 +63241,7 @@
       <c r="Y985" s="5"/>
       <c r="Z985" s="5"/>
     </row>
-    <row r="986" spans="1:26" ht="17.399999999999999">
+    <row r="986" spans="1:26" ht="16.5">
       <c r="A986" s="7"/>
       <c r="B986" s="7"/>
       <c r="C986" s="7"/>
@@ -63274,7 +63269,7 @@
       <c r="Y986" s="5"/>
       <c r="Z986" s="5"/>
     </row>
-    <row r="987" spans="1:26" ht="17.399999999999999">
+    <row r="987" spans="1:26" ht="16.5">
       <c r="A987" s="7"/>
       <c r="B987" s="7"/>
       <c r="C987" s="7"/>
@@ -63302,7 +63297,7 @@
       <c r="Y987" s="5"/>
       <c r="Z987" s="5"/>
     </row>
-    <row r="988" spans="1:26" ht="17.399999999999999">
+    <row r="988" spans="1:26" ht="16.5">
       <c r="A988" s="7"/>
       <c r="B988" s="7"/>
       <c r="C988" s="7"/>
@@ -63330,7 +63325,7 @@
       <c r="Y988" s="5"/>
       <c r="Z988" s="5"/>
     </row>
-    <row r="989" spans="1:26" ht="17.399999999999999">
+    <row r="989" spans="1:26" ht="16.5">
       <c r="A989" s="7"/>
       <c r="B989" s="7"/>
       <c r="C989" s="7"/>
@@ -63358,7 +63353,7 @@
       <c r="Y989" s="5"/>
       <c r="Z989" s="5"/>
     </row>
-    <row r="990" spans="1:26" ht="17.399999999999999">
+    <row r="990" spans="1:26" ht="16.5">
       <c r="A990" s="7"/>
       <c r="B990" s="7"/>
       <c r="C990" s="7"/>
@@ -63386,7 +63381,7 @@
       <c r="Y990" s="5"/>
       <c r="Z990" s="5"/>
     </row>
-    <row r="991" spans="1:26" ht="17.399999999999999">
+    <row r="991" spans="1:26" ht="16.5">
       <c r="A991" s="7"/>
       <c r="B991" s="7"/>
       <c r="C991" s="7"/>
@@ -63414,7 +63409,7 @@
       <c r="Y991" s="5"/>
       <c r="Z991" s="5"/>
     </row>
-    <row r="992" spans="1:26" ht="17.399999999999999">
+    <row r="992" spans="1:26" ht="16.5">
       <c r="A992" s="7"/>
       <c r="B992" s="7"/>
       <c r="C992" s="7"/>
@@ -63442,7 +63437,7 @@
       <c r="Y992" s="5"/>
       <c r="Z992" s="5"/>
     </row>
-    <row r="993" spans="1:26" ht="17.399999999999999">
+    <row r="993" spans="1:26" ht="16.5">
       <c r="A993" s="7"/>
       <c r="B993" s="7"/>
       <c r="C993" s="7"/>
@@ -63470,7 +63465,7 @@
       <c r="Y993" s="5"/>
       <c r="Z993" s="5"/>
     </row>
-    <row r="994" spans="1:26" ht="17.399999999999999">
+    <row r="994" spans="1:26" ht="16.5">
       <c r="A994" s="7"/>
       <c r="B994" s="7"/>
       <c r="C994" s="7"/>
@@ -63498,7 +63493,7 @@
       <c r="Y994" s="5"/>
       <c r="Z994" s="5"/>
     </row>
-    <row r="995" spans="1:26" ht="17.399999999999999">
+    <row r="995" spans="1:26" ht="16.5">
       <c r="A995" s="7"/>
       <c r="B995" s="7"/>
       <c r="C995" s="7"/>
@@ -63526,7 +63521,7 @@
       <c r="Y995" s="5"/>
       <c r="Z995" s="5"/>
     </row>
-    <row r="996" spans="1:26" ht="17.399999999999999">
+    <row r="996" spans="1:26" ht="16.5">
       <c r="A996" s="7"/>
       <c r="B996" s="7"/>
       <c r="C996" s="7"/>
@@ -63554,7 +63549,7 @@
       <c r="Y996" s="5"/>
       <c r="Z996" s="5"/>
     </row>
-    <row r="997" spans="1:26" ht="17.399999999999999">
+    <row r="997" spans="1:26" ht="16.5">
       <c r="A997" s="7"/>
       <c r="B997" s="7"/>
       <c r="C997" s="7"/>
@@ -63582,7 +63577,7 @@
       <c r="Y997" s="5"/>
       <c r="Z997" s="5"/>
     </row>
-    <row r="998" spans="1:26" ht="17.399999999999999">
+    <row r="998" spans="1:26" ht="16.5">
       <c r="A998" s="7"/>
       <c r="B998" s="7"/>
       <c r="C998" s="7"/>
@@ -63610,7 +63605,7 @@
       <c r="Y998" s="5"/>
       <c r="Z998" s="5"/>
     </row>
-    <row r="999" spans="1:26" ht="17.399999999999999">
+    <row r="999" spans="1:26" ht="16.5">
       <c r="A999" s="7"/>
       <c r="B999" s="7"/>
       <c r="C999" s="7"/>
@@ -63638,7 +63633,7 @@
       <c r="Y999" s="5"/>
       <c r="Z999" s="5"/>
     </row>
-    <row r="1000" spans="1:26" ht="17.399999999999999">
+    <row r="1000" spans="1:26" ht="16.5">
       <c r="A1000" s="7"/>
       <c r="B1000" s="7"/>
       <c r="C1000" s="7"/>
@@ -63666,7 +63661,7 @@
       <c r="Y1000" s="5"/>
       <c r="Z1000" s="5"/>
     </row>
-    <row r="1001" spans="1:26" ht="17.399999999999999">
+    <row r="1001" spans="1:26" ht="16.5">
       <c r="A1001" s="7"/>
       <c r="B1001" s="7"/>
       <c r="C1001" s="7"/>
@@ -63694,7 +63689,7 @@
       <c r="Y1001" s="5"/>
       <c r="Z1001" s="5"/>
     </row>
-    <row r="1002" spans="1:26" ht="17.399999999999999">
+    <row r="1002" spans="1:26" ht="16.5">
       <c r="A1002" s="7"/>
       <c r="B1002" s="7"/>
       <c r="C1002" s="7"/>
@@ -63722,7 +63717,7 @@
       <c r="Y1002" s="5"/>
       <c r="Z1002" s="5"/>
     </row>
-    <row r="1003" spans="1:26" ht="17.399999999999999">
+    <row r="1003" spans="1:26" ht="16.5">
       <c r="A1003" s="7"/>
       <c r="B1003" s="7"/>
       <c r="C1003" s="7"/>
@@ -63750,7 +63745,7 @@
       <c r="Y1003" s="5"/>
       <c r="Z1003" s="5"/>
     </row>
-    <row r="1004" spans="1:26" ht="17.399999999999999">
+    <row r="1004" spans="1:26" ht="16.5">
       <c r="A1004" s="7"/>
       <c r="B1004" s="7"/>
       <c r="C1004" s="7"/>
@@ -63778,7 +63773,7 @@
       <c r="Y1004" s="5"/>
       <c r="Z1004" s="5"/>
     </row>
-    <row r="1005" spans="1:26" ht="17.399999999999999">
+    <row r="1005" spans="1:26" ht="16.5">
       <c r="A1005" s="7"/>
       <c r="B1005" s="7"/>
       <c r="C1005" s="7"/>
@@ -63806,7 +63801,7 @@
       <c r="Y1005" s="5"/>
       <c r="Z1005" s="5"/>
     </row>
-    <row r="1006" spans="1:26" ht="17.399999999999999">
+    <row r="1006" spans="1:26" ht="16.5">
       <c r="A1006" s="7"/>
       <c r="B1006" s="7"/>
       <c r="C1006" s="7"/>
@@ -63834,7 +63829,7 @@
       <c r="Y1006" s="5"/>
       <c r="Z1006" s="5"/>
     </row>
-    <row r="1007" spans="1:26" ht="17.399999999999999">
+    <row r="1007" spans="1:26" ht="16.5">
       <c r="A1007" s="7"/>
       <c r="B1007" s="7"/>
       <c r="C1007" s="7"/>
@@ -63862,7 +63857,7 @@
       <c r="Y1007" s="5"/>
       <c r="Z1007" s="5"/>
     </row>
-    <row r="1008" spans="1:26" ht="17.399999999999999">
+    <row r="1008" spans="1:26" ht="16.5">
       <c r="A1008" s="7"/>
       <c r="B1008" s="7"/>
       <c r="C1008" s="7"/>
@@ -63890,7 +63885,7 @@
       <c r="Y1008" s="5"/>
       <c r="Z1008" s="5"/>
     </row>
-    <row r="1009" spans="1:26" ht="17.399999999999999">
+    <row r="1009" spans="1:26" ht="16.5">
       <c r="A1009" s="7"/>
       <c r="B1009" s="7"/>
       <c r="C1009" s="7"/>
@@ -63918,7 +63913,7 @@
       <c r="Y1009" s="5"/>
       <c r="Z1009" s="5"/>
     </row>
-    <row r="1010" spans="1:26" ht="17.399999999999999">
+    <row r="1010" spans="1:26" ht="16.5">
       <c r="A1010" s="7"/>
       <c r="B1010" s="7"/>
       <c r="C1010" s="7"/>
@@ -63946,7 +63941,7 @@
       <c r="Y1010" s="5"/>
       <c r="Z1010" s="5"/>
     </row>
-    <row r="1011" spans="1:26" ht="17.399999999999999">
+    <row r="1011" spans="1:26" ht="16.5">
       <c r="A1011" s="7"/>
       <c r="B1011" s="7"/>
       <c r="C1011" s="7"/>
@@ -63974,7 +63969,7 @@
       <c r="Y1011" s="5"/>
       <c r="Z1011" s="5"/>
     </row>
-    <row r="1012" spans="1:26" ht="17.399999999999999">
+    <row r="1012" spans="1:26" ht="16.5">
       <c r="A1012" s="7"/>
       <c r="B1012" s="7"/>
       <c r="C1012" s="7"/>
@@ -64002,7 +63997,7 @@
       <c r="Y1012" s="5"/>
       <c r="Z1012" s="5"/>
     </row>
-    <row r="1013" spans="1:26" ht="17.399999999999999">
+    <row r="1013" spans="1:26" ht="16.5">
       <c r="A1013" s="7"/>
       <c r="B1013" s="7"/>
       <c r="C1013" s="7"/>
@@ -64030,7 +64025,7 @@
       <c r="Y1013" s="5"/>
       <c r="Z1013" s="5"/>
     </row>
-    <row r="1014" spans="1:26" ht="17.399999999999999">
+    <row r="1014" spans="1:26" ht="16.5">
       <c r="E1014" s="5"/>
     </row>
   </sheetData>
@@ -64043,14 +64038,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
@@ -65099,13 +65094,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="5" max="26" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E130E280-0607-452A-9E79-C841259C9BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C8C0B9-AA6B-4A79-AFF2-EBAC271D5367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4695" yWindow="2010" windowWidth="24255" windowHeight="18210" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="-285" yWindow="1815" windowWidth="27870" windowHeight="11085" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -737,11 +737,6 @@
     <t>MainScript_1_1_11</t>
   </si>
   <si>
-    <t xml:space="preserve">멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,
-</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">마을 입구 쪽이였다.
 사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.
 </t>
@@ -1322,162 +1317,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">._x000D_
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>뭐지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">….?"_x000D_
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이상한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>기척을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>순간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>느꼈다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">…_x000D_
 </t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -3547,390 +3386,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수도에서 떨어진 변방의 평온한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시골마을인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>라노스마을
-해가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>높이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>떠올랐고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바람은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따뜻했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조용한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>속에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오늘도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변함없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>숨을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>죽이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>살아가고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>"</t>
     </r>
     <r>
@@ -4675,6 +4130,742 @@
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기척을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>느꼈다...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.?"
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멀리서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보이는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흙먼지와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>울음소리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갑작스러운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수도에서 떨어진 변방의 평온한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시골마을인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라노스마을
+해가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠올랐고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>&lt;웨이브&gt;나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조용한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변함없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살아가고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>웨이브</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&gt;
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -5291,19 +5482,19 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -5413,7 +5604,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="3"/>
@@ -5608,7 +5799,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="3"/>
@@ -5725,7 +5916,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -5764,7 +5955,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="3"/>
@@ -5802,7 +5993,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="3"/>
@@ -5840,7 +6031,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="3"/>
@@ -5878,7 +6069,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="3"/>
@@ -5916,7 +6107,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="3"/>
@@ -5955,7 +6146,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="3"/>
@@ -5994,7 +6185,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="3"/>
@@ -6033,7 +6224,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="3"/>
@@ -6072,7 +6263,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -6110,7 +6301,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -6147,7 +6338,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -6186,11 +6377,11 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -6227,7 +6418,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -6266,7 +6457,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -6305,7 +6496,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -6344,7 +6535,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -6383,7 +6574,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -6422,7 +6613,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3"/>
@@ -6461,15 +6652,15 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -6504,7 +6695,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -6543,7 +6734,7 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -6582,7 +6773,7 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -6616,12 +6807,12 @@
         <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" ref="D36:D95" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <f t="shared" ref="D36:D94" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -6660,7 +6851,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -6699,7 +6890,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -6738,7 +6929,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -6776,10 +6967,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -6818,7 +7009,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -6857,7 +7048,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -6896,7 +7087,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -6935,7 +7126,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -6974,11 +7165,11 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -7015,7 +7206,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -7054,7 +7245,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -7093,7 +7284,7 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3"/>
@@ -7132,7 +7323,7 @@
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="3"/>
@@ -7171,17 +7362,17 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -7212,13 +7403,13 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3"/>
       <c r="J51" s="3"/>
@@ -7254,13 +7445,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -7295,13 +7486,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -7338,7 +7529,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -7377,7 +7568,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -7416,7 +7607,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -7455,7 +7646,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -7494,7 +7685,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -7533,7 +7724,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -7572,11 +7763,11 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -7613,7 +7804,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -7652,7 +7843,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -7691,7 +7882,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -7730,7 +7921,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -7769,7 +7960,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -7808,7 +7999,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -7847,7 +8038,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -7886,7 +8077,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -7925,7 +8116,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -7964,7 +8155,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -8003,7 +8194,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -8042,7 +8233,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -8081,7 +8272,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -8120,7 +8311,7 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="3"/>
@@ -8159,7 +8350,7 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
@@ -8198,11 +8389,11 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -8239,7 +8430,7 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
@@ -8278,15 +8469,15 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -8324,7 +8515,7 @@
         <v>MainScene_1_5_4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="3"/>
@@ -8366,7 +8557,7 @@
         <v>MainScene_1_5_5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="3"/>
@@ -8405,7 +8596,7 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="3"/>
@@ -8444,7 +8635,7 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="3"/>
@@ -8483,7 +8674,7 @@
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="3"/>
@@ -8522,7 +8713,7 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="3"/>
@@ -8561,7 +8752,7 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="3"/>
@@ -8600,7 +8791,7 @@
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="3"/>
@@ -8639,7 +8830,7 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="3"/>
@@ -8678,7 +8869,7 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="3"/>
@@ -8717,7 +8908,7 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="3"/>
@@ -8756,7 +8947,7 @@
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="3"/>
@@ -8795,7 +8986,7 @@
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="3"/>
@@ -8834,7 +9025,7 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="3"/>
@@ -8873,11 +9064,11 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
@@ -8914,7 +9105,7 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="3"/>
@@ -34416,7 +34607,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -34437,13 +34628,13 @@
         <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -34477,17 +34668,17 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -34521,7 +34712,7 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>30</v>
@@ -34562,10 +34753,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -34603,10 +34794,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -34644,7 +34835,7 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>30</v>
@@ -34670,7 +34861,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="30">
+    <row r="7" spans="1:26" ht="33">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -34685,7 +34876,7 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>30</v>
@@ -34711,7 +34902,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="30">
+    <row r="8" spans="1:26" ht="33">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -34726,7 +34917,7 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>30</v>
@@ -34752,7 +34943,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="30">
+    <row r="9" spans="1:26" ht="33">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -34767,10 +34958,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -34808,7 +34999,7 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>30</v>
@@ -34849,7 +35040,7 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>30</v>
@@ -34890,7 +35081,7 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>31</v>
@@ -34931,7 +35122,7 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>30</v>
@@ -34972,10 +35163,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -35013,10 +35204,10 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -35054,7 +35245,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>30</v>
@@ -35094,10 +35285,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -35134,7 +35325,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>30</v>
@@ -35174,10 +35365,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -35215,7 +35406,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>30</v>
@@ -35256,10 +35447,10 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -35296,7 +35487,7 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>30</v>
@@ -35337,7 +35528,7 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>30</v>
@@ -35378,7 +35569,7 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>30</v>
@@ -35419,10 +35610,10 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="5"/>
@@ -35460,13 +35651,13 @@
         <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -35503,7 +35694,7 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>30</v>
@@ -35544,10 +35735,10 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -35585,10 +35776,10 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -35626,10 +35817,10 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -35667,10 +35858,10 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -35708,7 +35899,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
@@ -35749,10 +35940,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -35790,10 +35981,10 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -35831,10 +36022,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -35872,10 +36063,10 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -35913,10 +36104,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -35954,10 +36145,10 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -35995,7 +36186,7 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>30</v>
@@ -36036,7 +36227,7 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
@@ -36077,7 +36268,7 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>30</v>
@@ -36118,10 +36309,10 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -36159,10 +36350,10 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -36199,7 +36390,7 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>30</v>
@@ -36240,7 +36431,7 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>30</v>
@@ -36281,13 +36472,13 @@
         <v>MainScript_1_2_20</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -36324,7 +36515,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>30</v>
@@ -36365,10 +36556,10 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -36406,7 +36597,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -36447,7 +36638,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -36488,7 +36679,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>30</v>
@@ -36529,7 +36720,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>30</v>
@@ -36570,7 +36761,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>30</v>
@@ -36611,7 +36802,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>30</v>
@@ -36652,10 +36843,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -36693,10 +36884,10 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -36734,7 +36925,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -36775,7 +36966,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>30</v>
@@ -36816,7 +37007,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>30</v>
@@ -36857,7 +37048,7 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>30</v>
@@ -36898,13 +37089,13 @@
         <v>MainScript_1_3_15</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -36941,7 +37132,7 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>30</v>
@@ -36982,7 +37173,7 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -37023,7 +37214,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -37064,7 +37255,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -37105,10 +37296,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -37146,7 +37337,7 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -37187,7 +37378,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -37228,7 +37419,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -37269,7 +37460,7 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -37310,7 +37501,7 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -37351,7 +37542,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -37392,10 +37583,10 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -37433,10 +37624,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -37474,10 +37665,10 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -37515,7 +37706,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -37556,13 +37747,13 @@
         <v>MainScript_1_4_16</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -37599,7 +37790,7 @@
         <v>MainScript_1_5_1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>30</v>
@@ -37640,7 +37831,7 @@
         <v>MainScript_1_5_2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>30</v>
@@ -37681,16 +37872,16 @@
         <v>MainScript_1_5_3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -37726,10 +37917,10 @@
         <v>MainScript_1_5_4</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -37767,16 +37958,16 @@
         <v>MainScript_1_5_5</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -37812,7 +38003,7 @@
         <v>MainScript_2_1_1</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>30</v>
@@ -37853,7 +38044,7 @@
         <v>MainScript_2_1_2</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>30</v>
@@ -37894,7 +38085,7 @@
         <v>MainScript_2_1_3</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>30</v>
@@ -37935,7 +38126,7 @@
         <v>MainScript_2_1_4</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>30</v>
@@ -37976,7 +38167,7 @@
         <v>MainScript_2_1_5</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>30</v>
@@ -38017,7 +38208,7 @@
         <v>MainScript_2_1_6</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>30</v>
@@ -38058,7 +38249,7 @@
         <v>MainScript_2_1_7</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>30</v>
@@ -38099,7 +38290,7 @@
         <v>MainScript_2_1_8</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>30</v>
@@ -38140,7 +38331,7 @@
         <v>MainScript_2_1_9</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>30</v>
@@ -38181,7 +38372,7 @@
         <v>MainScript_2_1_10</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>30</v>
@@ -38222,7 +38413,7 @@
         <v>MainScript_2_1_11</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>30</v>
@@ -38263,16 +38454,16 @@
         <v>MainScript_2_1_12</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -64067,19 +64258,19 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
@@ -65111,7 +65302,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>27</v>
@@ -65119,34 +65310,34 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>154</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>157</v>
       </c>
       <c r="C4" s="6"/>
     </row>

--- a/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
+++ b/JsonFile/Assets/ExcelFiles/TRPG_ScriptData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C8C0B9-AA6B-4A79-AFF2-EBAC271D5367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E130E280-0607-452A-9E79-C841259C9BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="1815" windowWidth="27870" windowHeight="11085" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
+    <workbookView xWindow="4695" yWindow="2010" windowWidth="24255" windowHeight="18210" activeTab="1" xr2:uid="{CCA8FC88-E37F-4EF6-A133-22F9C68BD387}"/>
   </bookViews>
   <sheets>
     <sheet name="Story_Master_Main" sheetId="1" r:id="rId1"/>
@@ -737,6 +737,11 @@
     <t>MainScript_1_1_11</t>
   </si>
   <si>
+    <t xml:space="preserve">멀리서 보이는 흙먼지와 짐승 같은 울음소리, 갑작스러운 비명,
+</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">마을 입구 쪽이였다.
 사람들이 하나 둘 당황한 표정으로 그쪽을 바라보고 있었다.
 </t>
@@ -1317,6 +1322,162 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">._x000D_
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>뭐지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">….?"_x000D_
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이상한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기척을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>순간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>느꼈다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">…_x000D_
 </t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -3386,6 +3547,390 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수도에서 떨어진 변방의 평온한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시골마을인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라노스마을
+해가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠올랐고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바람은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조용한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오늘도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변함없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살아가고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>"</t>
     </r>
     <r>
@@ -4130,742 +4675,6 @@
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이상한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기척을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>느꼈다...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뭐지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.?"
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>멀리서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보이는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>흙먼지와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>짐승</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>울음소리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>갑작스러운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수도에서 떨어진 변방의 평온한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시골마을인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>라노스마을
-해가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>높이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>떠올랐고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바람은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따뜻했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>&lt;웨이브&gt;나는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조용한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>속에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오늘도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변함없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>숨을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>죽이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>살아가고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.&lt;/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>웨이브</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">&gt;
-</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -5482,19 +5291,19 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -5604,7 +5413,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="3"/>
@@ -5799,7 +5608,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="3"/>
@@ -5916,7 +5725,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -5955,7 +5764,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="3"/>
@@ -5993,7 +5802,7 @@
         <v>MainScene_1_1_14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="3"/>
@@ -6031,7 +5840,7 @@
         <v>MainScene_1_1_15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="3"/>
@@ -6069,7 +5878,7 @@
         <v>MainScene_1_1_16</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="3"/>
@@ -6107,7 +5916,7 @@
         <v>MainScene_1_1_17</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="3"/>
@@ -6146,7 +5955,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="3"/>
@@ -6185,7 +5994,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="3"/>
@@ -6224,7 +6033,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="3"/>
@@ -6263,7 +6072,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -6301,7 +6110,7 @@
         <v>MainScene_1_1_22</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -6338,7 +6147,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="3"/>
@@ -6377,11 +6186,11 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -6418,7 +6227,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="3"/>
@@ -6457,7 +6266,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="3"/>
@@ -6496,7 +6305,7 @@
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="3"/>
@@ -6535,7 +6344,7 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="3"/>
@@ -6574,7 +6383,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="3"/>
@@ -6613,7 +6422,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="3"/>
@@ -6652,15 +6461,15 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -6695,7 +6504,7 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="3"/>
@@ -6734,7 +6543,7 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="3"/>
@@ -6773,7 +6582,7 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="3"/>
@@ -6807,12 +6616,12 @@
         <v>10</v>
       </c>
       <c r="D36" s="3" t="str">
-        <f t="shared" ref="D36:D94" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
+        <f t="shared" ref="D36:D95" si="2">CONCATENATE("MainScene_",A36,"_",B36,"_",C36)</f>
         <v>MainScene_1_2_10</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="3"/>
@@ -6851,7 +6660,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="3"/>
@@ -6890,7 +6699,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="3"/>
@@ -6929,7 +6738,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="3"/>
@@ -6967,10 +6776,10 @@
         <v>MainScene_1_2_14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="3"/>
@@ -7009,7 +6818,7 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="3"/>
@@ -7048,7 +6857,7 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="3"/>
@@ -7087,7 +6896,7 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="3"/>
@@ -7126,7 +6935,7 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="3"/>
@@ -7165,11 +6974,11 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -7206,7 +7015,7 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="3"/>
@@ -7245,7 +7054,7 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="3"/>
@@ -7284,7 +7093,7 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="3"/>
@@ -7323,7 +7132,7 @@
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="3"/>
@@ -7362,17 +7171,17 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -7403,13 +7212,13 @@
         <v>MainScene_1_3_5</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3"/>
       <c r="J51" s="3"/>
@@ -7445,13 +7254,13 @@
         <v>MainScene_1_3_6</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -7486,13 +7295,13 @@
         <v>MainScene_1_3_7</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -7529,7 +7338,7 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="3"/>
@@ -7568,7 +7377,7 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="3"/>
@@ -7607,7 +7416,7 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="3"/>
@@ -7646,7 +7455,7 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="3"/>
@@ -7685,7 +7494,7 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>
@@ -7724,7 +7533,7 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>
@@ -7763,11 +7572,11 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -7804,7 +7613,7 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="3"/>
@@ -7843,7 +7652,7 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="3"/>
@@ -7882,7 +7691,7 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="3"/>
@@ -7921,7 +7730,7 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="3"/>
@@ -7960,7 +7769,7 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="3"/>
@@ -7999,7 +7808,7 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="3"/>
@@ -8038,7 +7847,7 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="3"/>
@@ -8077,7 +7886,7 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
@@ -8116,7 +7925,7 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
@@ -8155,7 +7964,7 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
@@ -8194,7 +8003,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="3"/>
@@ -8233,7 +8042,7 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="3"/>
@@ -8272,7 +8081,7 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="3"/>
@@ -8311,7 +8120,7 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="3"/>
@@ -8350,7 +8159,7 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="3"/>
@@ -8389,11 +8198,11 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -8430,7 +8239,7 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="3"/>
@@ -8469,15 +8278,15 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -8515,7 +8324,7 @@
         <v>MainScene_1_5_4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="3"/>
@@ -8557,7 +8366,7 @@
         <v>MainScene_1_5_5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="3"/>
@@ -8596,7 +8405,7 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="3"/>
@@ -8635,7 +8444,7 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="3"/>
@@ -8674,7 +8483,7 @@
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="3"/>
@@ -8713,7 +8522,7 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="3"/>
@@ -8752,7 +8561,7 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="3"/>
@@ -8791,7 +8600,7 @@
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="3"/>
@@ -8830,7 +8639,7 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="3"/>
@@ -8869,7 +8678,7 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="3"/>
@@ -8908,7 +8717,7 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="3"/>
@@ -8947,7 +8756,7 @@
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="3"/>
@@ -8986,7 +8795,7 @@
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="3"/>
@@ -9025,7 +8834,7 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="3"/>
@@ -9064,11 +8873,11 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
@@ -9105,7 +8914,7 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="3"/>
@@ -34607,7 +34416,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5">
       <c r="A1" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -34628,13 +34437,13 @@
         <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -34668,17 +34477,17 @@
         <v>MainScript_1_1_1</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -34712,7 +34521,7 @@
         <v>MainScript_1_1_2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>30</v>
@@ -34753,10 +34562,10 @@
         <v>MainScript_1_1_3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -34794,10 +34603,10 @@
         <v>MainScript_1_1_4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -34835,7 +34644,7 @@
         <v>MainScript_1_1_5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>30</v>
@@ -34861,7 +34670,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="33">
+    <row r="7" spans="1:26" ht="30">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -34876,7 +34685,7 @@
         <v>MainScript_1_1_6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>233</v>
+        <v>52</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>30</v>
@@ -34902,7 +34711,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="33">
+    <row r="8" spans="1:26" ht="30">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -34917,7 +34726,7 @@
         <v>MainScript_1_1_7</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>234</v>
+        <v>51</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>30</v>
@@ -34943,7 +34752,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" ht="33">
+    <row r="9" spans="1:26" ht="30">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -34958,10 +34767,10 @@
         <v>MainScript_1_1_8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -34999,7 +34808,7 @@
         <v>MainScript_1_1_9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>30</v>
@@ -35040,7 +34849,7 @@
         <v>MainScript_1_1_10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>30</v>
@@ -35081,7 +34890,7 @@
         <v>MainScript_1_1_11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>31</v>
@@ -35122,7 +34931,7 @@
         <v>MainScript_1_1_12</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>30</v>
@@ -35163,10 +34972,10 @@
         <v>MainScript_1_1_13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -35204,10 +35013,10 @@
         <v>MainScript_1_1_14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -35245,7 +35054,7 @@
         <v>MainScript_1_1_15</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>30</v>
@@ -35285,10 +35094,10 @@
         <v>MainScript_1_1_16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G17" s="5"/>
       <c r="I17" s="5"/>
@@ -35325,7 +35134,7 @@
         <v>MainScript_1_1_17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>30</v>
@@ -35365,10 +35174,10 @@
         <v>MainScript_1_1_18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -35406,7 +35215,7 @@
         <v>MainScript_1_1_19</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>30</v>
@@ -35447,10 +35256,10 @@
         <v>MainScript_1_1_20</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -35487,7 +35296,7 @@
         <v>MainScript_1_1_21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>30</v>
@@ -35528,7 +35337,7 @@
         <v>MainScript_1_1_22</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>30</v>
@@ -35569,7 +35378,7 @@
         <v>MainScript_1_1_23</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>30</v>
@@ -35610,10 +35419,10 @@
         <v>MainScript_1_1_24</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="5"/>
@@ -35651,13 +35460,13 @@
         <v>MainScript_1_1_25</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -35694,7 +35503,7 @@
         <v>MainScript_1_2_1</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>30</v>
@@ -35735,10 +35544,10 @@
         <v>MainScript_1_2_2</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -35776,10 +35585,10 @@
         <v>MainScript_1_2_3</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -35817,10 +35626,10 @@
         <v>MainScript_1_2_4</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -35858,10 +35667,10 @@
         <v>MainScript_1_2_5</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -35899,7 +35708,7 @@
         <v>MainScript_1_2_6</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>30</v>
@@ -35940,10 +35749,10 @@
         <v>MainScript_1_2_7</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -35981,10 +35790,10 @@
         <v>MainScript_1_2_8</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -36022,10 +35831,10 @@
         <v>MainScript_1_2_9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -36063,10 +35872,10 @@
         <v>MainScript_1_2_10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -36104,10 +35913,10 @@
         <v>MainScript_1_2_11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -36145,10 +35954,10 @@
         <v>MainScript_1_2_12</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -36186,7 +35995,7 @@
         <v>MainScript_1_2_13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>30</v>
@@ -36227,7 +36036,7 @@
         <v>MainScript_1_2_14</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
@@ -36268,7 +36077,7 @@
         <v>MainScript_1_2_15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>30</v>
@@ -36309,10 +36118,10 @@
         <v>MainScript_1_2_16</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -36350,10 +36159,10 @@
         <v>MainScript_1_2_17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -36390,7 +36199,7 @@
         <v>MainScript_1_2_18</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>30</v>
@@ -36431,7 +36240,7 @@
         <v>MainScript_1_2_19</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>30</v>
@@ -36472,13 +36281,13 @@
         <v>MainScript_1_2_20</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -36515,7 +36324,7 @@
         <v>MainScript_1_3_1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>30</v>
@@ -36556,10 +36365,10 @@
         <v>MainScript_1_3_2</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -36597,7 +36406,7 @@
         <v>MainScript_1_3_3</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>30</v>
@@ -36638,7 +36447,7 @@
         <v>MainScript_1_3_4</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>30</v>
@@ -36679,7 +36488,7 @@
         <v>MainScript_1_3_5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>30</v>
@@ -36720,7 +36529,7 @@
         <v>MainScript_1_3_6</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>30</v>
@@ -36761,7 +36570,7 @@
         <v>MainScript_1_3_7</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>30</v>
@@ -36802,7 +36611,7 @@
         <v>MainScript_1_3_8</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>30</v>
@@ -36843,10 +36652,10 @@
         <v>MainScript_1_3_9</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -36884,10 +36693,10 @@
         <v>MainScript_1_3_10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -36925,7 +36734,7 @@
         <v>MainScript_1_3_11</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>30</v>
@@ -36966,7 +36775,7 @@
         <v>MainScript_1_3_12</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>30</v>
@@ -37007,7 +36816,7 @@
         <v>MainScript_1_3_13</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>30</v>
@@ -37048,7 +36857,7 @@
         <v>MainScript_1_3_14</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>30</v>
@@ -37089,13 +36898,13 @@
         <v>MainScript_1_3_15</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -37132,7 +36941,7 @@
         <v>MainScript_1_4_1</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>30</v>
@@ -37173,7 +36982,7 @@
         <v>MainScript_1_4_2</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>30</v>
@@ -37214,7 +37023,7 @@
         <v>MainScript_1_4_3</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>30</v>
@@ -37255,7 +37064,7 @@
         <v>MainScript_1_4_4</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>30</v>
@@ -37296,10 +37105,10 @@
         <v>MainScript_1_4_5</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -37337,7 +37146,7 @@
         <v>MainScript_1_4_6</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>30</v>
@@ -37378,7 +37187,7 @@
         <v>MainScript_1_4_7</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>30</v>
@@ -37419,7 +37228,7 @@
         <v>MainScript_1_4_8</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>30</v>
@@ -37460,7 +37269,7 @@
         <v>MainScript_1_4_9</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>30</v>
@@ -37501,7 +37310,7 @@
         <v>MainScript_1_4_10</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>30</v>
@@ -37542,7 +37351,7 @@
         <v>MainScript_1_4_11</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
@@ -37583,10 +37392,10 @@
         <v>MainScript_1_4_12</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -37624,10 +37433,10 @@
         <v>MainScript_1_4_13</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -37665,10 +37474,10 @@
         <v>MainScript_1_4_14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -37706,7 +37515,7 @@
         <v>MainScript_1_4_15</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>30</v>
@@ -37747,13 +37556,13 @@
         <v>MainScript_1_4_16</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -37790,7 +37599,7 @@
         <v>MainScript_1_5_1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>30</v>
@@ -37831,7 +37640,7 @@
         <v>MainScript_1_5_2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>30</v>
@@ -37872,16 +37681,16 @@
         <v>MainScript_1_5_3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -37917,10 +37726,10 @@
         <v>MainScript_1_5_4</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -37958,16 +37767,16 @@
         <v>MainScript_1_5_5</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -38003,7 +37812,7 @@
         <v>MainScript_2_1_1</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>30</v>
@@ -38044,7 +37853,7 @@
         <v>MainScript_2_1_2</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>30</v>
@@ -38085,7 +37894,7 @@
         <v>MainScript_2_1_3</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>30</v>
@@ -38126,7 +37935,7 @@
         <v>MainScript_2_1_4</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>30</v>
@@ -38167,7 +37976,7 @@
         <v>MainScript_2_1_5</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>30</v>
@@ -38208,7 +38017,7 @@
         <v>MainScript_2_1_6</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>30</v>
@@ -38249,7 +38058,7 @@
         <v>MainScript_2_1_7</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>30</v>
@@ -38290,7 +38099,7 @@
         <v>MainScript_2_1_8</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>30</v>
@@ -38331,7 +38140,7 @@
         <v>MainScript_2_1_9</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>30</v>
@@ -38372,7 +38181,7 @@
         <v>MainScript_2_1_10</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>30</v>
@@ -38413,7 +38222,7 @@
         <v>MainScript_2_1_11</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>30</v>
@@ -38454,16 +38263,16 @@
         <v>MainScript_2_1_12</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G